--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/detector-simulator-py/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15AAAC1-8C2F-9A42-BD2D-EA2DC04D13CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127086A6-DFCE-EC42-BEBA-E6222BE726E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23720" yWindow="5720" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34740" yWindow="4480" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -937,44 +937,18 @@
         <v>2061</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="I2" s="6">
-        <v>6801</v>
-      </c>
-      <c r="J2" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="6">
-        <v>1.43</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="M2" s="6">
-        <v>4.21</v>
-      </c>
-      <c r="N2" s="6">
-        <v>7.3289156000000002</v>
-      </c>
-      <c r="O2" s="6">
-        <v>-76.304032000000007</v>
-      </c>
-      <c r="P2" s="6">
-        <v>196.852</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>9.5950000000000006</v>
-      </c>
-      <c r="R2" s="6">
-        <v>9.5202500000000008</v>
-      </c>
-      <c r="S2" s="6">
-        <f>(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
-        <v>934.76971602454307</v>
-      </c>
-      <c r="T2" s="6">
-        <f>IF(I2&gt;6800,-7,-5)</f>
-        <v>-7</v>
-      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
       <c r="U2" s="7" t="s">
         <v>138</v>
       </c>
@@ -1038,11 +1012,11 @@
         <v>7.5767499999999997</v>
       </c>
       <c r="S3" s="6">
-        <f>(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
+        <f t="shared" ref="S2:S33" si="0">(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
         <v>1286.8653667451285</v>
       </c>
       <c r="T3" s="6">
-        <f>IF(I3&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T2:T33" si="1">IF(I3&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
       <c r="U3" s="7" t="s">
@@ -1108,11 +1082,11 @@
         <v>9.4290710000000004</v>
       </c>
       <c r="S4" s="6">
-        <f>(0.000000000000000138*G4/(1.673534E-24*1.3*0.000000066726*F4*1.8986E+30/(E4*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>56.120615203365361</v>
       </c>
       <c r="T4" s="6">
-        <f>IF(I4&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="U4" s="7" t="s">
@@ -1176,11 +1150,11 @@
         <v>6.5536899999999996</v>
       </c>
       <c r="S5" s="8">
-        <f>(0.000000000000000138*G5/(1.673534E-24*1.3*0.000000066726*F5*1.8986E+30/(E5*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1130.2166328238993</v>
       </c>
       <c r="T5" s="6">
-        <f>IF(I5&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
       <c r="U5" s="7" t="s">
@@ -1246,11 +1220,11 @@
         <v>9.4846599999999999</v>
       </c>
       <c r="S6" s="6">
-        <f>(0.000000000000000138*G6/(1.673534E-24*1.3*0.000000066726*F6*1.8986E+30/(E6*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>955.72600175951948</v>
       </c>
       <c r="T6" s="6">
-        <f>IF(I6&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="U6" s="7" t="s">
@@ -1316,11 +1290,11 @@
         <v>10.178599999999999</v>
       </c>
       <c r="S7">
-        <f>(0.000000000000000138*G7/(1.673534E-24*1.3*0.000000066726*F7*1.8986E+30/(E7*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1121.1126749906216</v>
       </c>
       <c r="T7">
-        <f>IF(I7&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V7" s="2"/>
@@ -1383,11 +1357,11 @@
         <v>9.8728300000000004</v>
       </c>
       <c r="S8">
-        <f>(0.000000000000000138*G8/(1.673534E-24*1.3*0.000000066726*F8*1.8986E+30/(E8*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>243.60813720463176</v>
       </c>
       <c r="T8">
-        <f>IF(I8&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V8" s="2"/>
@@ -1450,11 +1424,11 @@
         <v>8.5984200000000008</v>
       </c>
       <c r="S9">
-        <f>(0.000000000000000138*G9/(1.673534E-24*1.3*0.000000066726*F9*1.8986E+30/(E9*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>39.515068300859213</v>
       </c>
       <c r="T9">
-        <f>IF(I9&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1514,11 +1488,11 @@
         <v>9.5193600000000007</v>
       </c>
       <c r="S10">
-        <f>(0.000000000000000138*G10/(1.673534E-24*1.3*0.000000066726*F10*1.8986E+30/(E10*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>200.46131426194896</v>
       </c>
       <c r="T10">
-        <f>IF(I10&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1575,11 +1549,11 @@
         <v>9.5635499999999993</v>
       </c>
       <c r="S11">
-        <f>(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>2101.5864855136347</v>
       </c>
       <c r="T11">
-        <f>IF(I11&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V11" s="2"/>
@@ -1639,11 +1613,11 @@
         <v>9.77332</v>
       </c>
       <c r="S12">
-        <f>(0.000000000000000138*G12/(1.673534E-24*1.3*0.000000066726*F12*1.8986E+30/(E12*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>387.53401759458865</v>
       </c>
       <c r="T12">
-        <f>IF(I12&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -1700,11 +1674,11 @@
         <v>9.4517399999999991</v>
       </c>
       <c r="S13">
-        <f>(0.000000000000000138*G13/(1.673534E-24*1.3*0.000000066726*F13*1.8986E+30/(E13*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>338.15838787809196</v>
       </c>
       <c r="T13">
-        <f>IF(I13&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -1764,11 +1738,11 @@
         <v>7.89255</v>
       </c>
       <c r="S14">
-        <f>(0.000000000000000138*G14/(1.673534E-24*1.3*0.000000066726*F14*1.8986E+30/(E14*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>211.51519610586323</v>
       </c>
       <c r="T14">
-        <f>IF(I14&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V14" s="2"/>
@@ -1831,11 +1805,11 @@
         <v>7.5933599999999997</v>
       </c>
       <c r="S15">
-        <f>(0.000000000000000138*G15/(1.673534E-24*1.3*0.000000066726*F15*1.8986E+30/(E15*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>797.33090232058362</v>
       </c>
       <c r="T15">
-        <f>IF(I15&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1895,11 +1869,11 @@
         <v>8.0141600000000004</v>
       </c>
       <c r="S16">
-        <f>(0.000000000000000138*G16/(1.673534E-24*1.3*0.000000066726*F16*1.8986E+30/(E16*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>599.63628364223177</v>
       </c>
       <c r="T16">
-        <f>IF(I16&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V16" s="2"/>
@@ -1962,11 +1936,11 @@
         <v>8.7641200000000001</v>
       </c>
       <c r="S17">
-        <f>(0.000000000000000138*G17/(1.673534E-24*1.3*0.000000066726*F17*1.8986E+30/(E17*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>597.79498778467087</v>
       </c>
       <c r="T17">
-        <f>IF(I17&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2026,11 +2000,11 @@
         <v>7.41432</v>
       </c>
       <c r="S18">
-        <f>(0.000000000000000138*G18/(1.673534E-24*1.3*0.000000066726*F18*1.8986E+30/(E18*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>349.61677638948368</v>
       </c>
       <c r="T18">
-        <f>IF(I18&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2087,11 +2061,11 @@
         <v>8.2268799999999995</v>
       </c>
       <c r="S19">
-        <f>(0.000000000000000138*G19/(1.673534E-24*1.3*0.000000066726*F19*1.8986E+30/(E19*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1280.5918535006856</v>
       </c>
       <c r="T19">
-        <f>IF(I19&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2151,11 +2125,11 @@
         <v>7.5086599999999999</v>
       </c>
       <c r="S20">
-        <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>988.21070019970352</v>
       </c>
       <c r="T20">
-        <f>IF(I20&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2215,11 +2189,11 @@
         <v>9.6495599999999992</v>
       </c>
       <c r="S21">
-        <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>956.09264119622901</v>
       </c>
       <c r="T21">
-        <f>IF(I21&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2279,11 +2253,11 @@
         <v>7.9077599999999997</v>
       </c>
       <c r="S22">
-        <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>742.8583931109747</v>
       </c>
       <c r="T22">
-        <f>IF(I22&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2343,11 +2317,11 @@
         <v>8.4183900000000005</v>
       </c>
       <c r="S23">
-        <f>(0.000000000000000138*G23/(1.673534E-24*1.3*0.000000066726*F23*1.8986E+30/(E23*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>574.11765847468712</v>
       </c>
       <c r="T23">
-        <f>IF(I23&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2407,11 +2381,11 @@
         <v>7.8097899999999996</v>
       </c>
       <c r="S24">
-        <f>(0.000000000000000138*G24/(1.673534E-24*1.3*0.000000066726*F24*1.8986E+30/(E24*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>668.81110409377118</v>
       </c>
       <c r="T24">
-        <f>IF(I24&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2471,11 +2445,11 @@
         <v>9.2170199999999998</v>
       </c>
       <c r="S25">
-        <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1103.5971886171305</v>
       </c>
       <c r="T25">
-        <f>IF(I25&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2532,11 +2506,11 @@
         <v>9.7262599999999999</v>
       </c>
       <c r="S26">
-        <f>(0.000000000000000138*G26/(1.673534E-24*1.3*0.000000066726*F26*1.8986E+30/(E26*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>662.28004924519439</v>
       </c>
       <c r="T26">
-        <f>IF(I26&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2596,11 +2570,11 @@
         <v>7.8311200000000003</v>
       </c>
       <c r="S27">
-        <f>(0.000000000000000138*G27/(1.673534E-24*1.3*0.000000066726*F27*1.8986E+30/(E27*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>3894.9775251994533</v>
       </c>
       <c r="T27">
-        <f>IF(I27&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2660,11 +2634,11 @@
         <v>9.2088699999999992</v>
       </c>
       <c r="S28">
-        <f>(0.000000000000000138*G28/(1.673534E-24*1.3*0.000000066726*F28*1.8986E+30/(E28*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>948.15286253702118</v>
       </c>
       <c r="T28">
-        <f>IF(I28&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2724,11 +2698,11 @@
         <v>9.8633100000000002</v>
       </c>
       <c r="S29">
-        <f>(0.000000000000000138*G29/(1.673534E-24*1.3*0.000000066726*F29*1.8986E+30/(E29*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>443.85469120292152</v>
       </c>
       <c r="T29">
-        <f>IF(I29&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2788,11 +2762,11 @@
         <v>8.5839300000000005</v>
       </c>
       <c r="S30">
-        <f>(0.000000000000000138*G30/(1.673534E-24*1.3*0.000000066726*F30*1.8986E+30/(E30*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>570.64953846380126</v>
       </c>
       <c r="T30">
-        <f>IF(I30&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2852,11 +2826,11 @@
         <v>7.5749199999999997</v>
       </c>
       <c r="S31">
-        <f>(0.000000000000000138*G31/(1.673534E-24*1.3*0.000000066726*F31*1.8986E+30/(E31*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>518.80488815900412</v>
       </c>
       <c r="T31">
-        <f>IF(I31&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2916,11 +2890,11 @@
         <v>8.23752</v>
       </c>
       <c r="S32">
-        <f>(0.000000000000000138*G32/(1.673534E-24*1.3*0.000000066726*F32*1.8986E+30/(E32*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>99.730517672190274</v>
       </c>
       <c r="T32">
-        <f>IF(I32&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2977,11 +2951,11 @@
         <v>9.7632399999999997</v>
       </c>
       <c r="S33">
-        <f>(0.000000000000000138*G33/(1.673534E-24*1.3*0.000000066726*F33*1.8986E+30/(E33*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>582.97620763372299</v>
       </c>
       <c r="T33">
-        <f>IF(I33&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -3041,11 +3015,11 @@
         <v>9.95702</v>
       </c>
       <c r="S34">
-        <f>(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
+        <f t="shared" ref="S34:S65" si="2">(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
         <v>1492.9814393090719</v>
       </c>
       <c r="T34">
-        <f>IF(I34&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T34:T65" si="3">IF(I34&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -3105,11 +3079,11 @@
         <v>8.4517299999999995</v>
       </c>
       <c r="S35">
-        <f>(0.000000000000000138*G35/(1.673534E-24*1.3*0.000000066726*F35*1.8986E+30/(E35*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>965.25628287035329</v>
       </c>
       <c r="T35">
-        <f>IF(I35&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3166,11 +3140,11 @@
         <v>10.367800000000001</v>
       </c>
       <c r="S36">
-        <f>(0.000000000000000138*G36/(1.673534E-24*1.3*0.000000066726*F36*1.8986E+30/(E36*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>160.76196513632402</v>
       </c>
       <c r="T36">
-        <f>IF(I36&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3230,11 +3204,11 @@
         <v>9.6000599999999991</v>
       </c>
       <c r="S37">
-        <f>(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>972.96006983022733</v>
       </c>
       <c r="T37">
-        <f>IF(I37&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3294,11 +3268,11 @@
         <v>8.2424300000000006</v>
       </c>
       <c r="S38">
-        <f>(0.000000000000000138*G38/(1.673534E-24*1.3*0.000000066726*F38*1.8986E+30/(E38*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>457.63140850776114</v>
       </c>
       <c r="T38">
-        <f>IF(I38&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3358,11 +3332,11 @@
         <v>8.1740100000000009</v>
       </c>
       <c r="S39">
-        <f>(0.000000000000000138*G39/(1.673534E-24*1.3*0.000000066726*F39*1.8986E+30/(E39*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>789.006338593706</v>
       </c>
       <c r="T39">
-        <f>IF(I39&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3422,11 +3396,11 @@
         <v>9.4135299999999997</v>
       </c>
       <c r="S40">
-        <f>(0.000000000000000138*G40/(1.673534E-24*1.3*0.000000066726*F40*1.8986E+30/(E40*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1175.9460676296278</v>
       </c>
       <c r="T40">
-        <f>IF(I40&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3483,11 +3457,11 @@
         <v>9.3678899999999992</v>
       </c>
       <c r="S41">
-        <f>(0.000000000000000138*G41/(1.673534E-24*1.3*0.000000066726*F41*1.8986E+30/(E41*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1399.2265914107247</v>
       </c>
       <c r="T41">
-        <f>IF(I41&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3544,11 +3518,11 @@
         <v>9.3503900000000009</v>
       </c>
       <c r="S42">
-        <f>(0.000000000000000138*G42/(1.673534E-24*1.3*0.000000066726*F42*1.8986E+30/(E42*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>353.31388599481477</v>
       </c>
       <c r="T42">
-        <f>IF(I42&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3608,11 +3582,11 @@
         <v>9.1879500000000007</v>
       </c>
       <c r="S43">
-        <f>(0.000000000000000138*G43/(1.673534E-24*1.3*0.000000066726*F43*1.8986E+30/(E43*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>882.20971786077962</v>
       </c>
       <c r="T43">
-        <f>IF(I43&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3672,11 +3646,11 @@
         <v>7.9756099999999996</v>
       </c>
       <c r="S44">
-        <f>(0.000000000000000138*G44/(1.673534E-24*1.3*0.000000066726*F44*1.8986E+30/(E44*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>431.57254486096394</v>
       </c>
       <c r="T44">
-        <f>IF(I44&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3736,11 +3710,11 @@
         <v>8.8952899999999993</v>
       </c>
       <c r="S45">
-        <f>(0.000000000000000138*G45/(1.673534E-24*1.3*0.000000066726*F45*1.8986E+30/(E45*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>974.78820571370204</v>
       </c>
       <c r="T45">
-        <f>IF(I45&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3800,11 +3774,11 @@
         <v>9.5843900000000009</v>
       </c>
       <c r="S46">
-        <f>(0.000000000000000138*G46/(1.673534E-24*1.3*0.000000066726*F46*1.8986E+30/(E46*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1460.8182255852041</v>
       </c>
       <c r="T46">
-        <f>IF(I46&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3861,11 +3835,11 @@
         <v>9.6598100000000002</v>
       </c>
       <c r="S47">
-        <f>(0.000000000000000138*G47/(1.673534E-24*1.3*0.000000066726*F47*1.8986E+30/(E47*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1324.5165539963698</v>
       </c>
       <c r="T47">
-        <f>IF(I47&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3922,11 +3896,11 @@
         <v>9.7596699999999998</v>
       </c>
       <c r="S48">
-        <f>(0.000000000000000138*G48/(1.673534E-24*1.3*0.000000066726*F48*1.8986E+30/(E48*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>55.915145726222889</v>
       </c>
       <c r="T48">
-        <f>IF(I48&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3983,11 +3957,11 @@
         <v>8.9365100000000002</v>
       </c>
       <c r="S49">
-        <f>(0.000000000000000138*G49/(1.673534E-24*1.3*0.000000066726*F49*1.8986E+30/(E49*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>77.040187113891676</v>
       </c>
       <c r="T49">
-        <f>IF(I49&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4044,11 +4018,11 @@
         <v>9.4724400000000006</v>
       </c>
       <c r="S50">
-        <f>(0.000000000000000138*G50/(1.673534E-24*1.3*0.000000066726*F50*1.8986E+30/(E50*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>83.670803141549356</v>
       </c>
       <c r="T50">
-        <f>IF(I50&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -4105,11 +4079,11 @@
         <v>7.4165299999999998</v>
       </c>
       <c r="S51">
-        <f>(0.000000000000000138*G51/(1.673534E-24*1.3*0.000000066726*F51*1.8986E+30/(E51*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>777.64358420307099</v>
       </c>
       <c r="T51">
-        <f>IF(I51&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4169,11 +4143,11 @@
         <v>9.7777600000000007</v>
       </c>
       <c r="S52">
-        <f>(0.000000000000000138*G52/(1.673534E-24*1.3*0.000000066726*F52*1.8986E+30/(E52*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>755.33252275944176</v>
       </c>
       <c r="T52">
-        <f>IF(I52&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4230,11 +4204,11 @@
         <v>9.641</v>
       </c>
       <c r="S53">
-        <f>(0.000000000000000138*G53/(1.673534E-24*1.3*0.000000066726*F53*1.8986E+30/(E53*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>318.17832033985127</v>
       </c>
       <c r="T53">
-        <f>IF(I53&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4294,11 +4268,11 @@
         <v>9.0746900000000004</v>
       </c>
       <c r="S54">
-        <f>(0.000000000000000138*G54/(1.673534E-24*1.3*0.000000066726*F54*1.8986E+30/(E54*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>36.149567272802649</v>
       </c>
       <c r="T54">
-        <f>IF(I54&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4358,11 +4332,11 @@
         <v>9.8465900000000008</v>
       </c>
       <c r="S55">
-        <f>(0.000000000000000138*G55/(1.673534E-24*1.3*0.000000066726*F55*1.8986E+30/(E55*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>224.58825733889913</v>
       </c>
       <c r="T55">
-        <f>IF(I55&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4419,11 +4393,11 @@
         <v>9.6080000000000005</v>
       </c>
       <c r="S56">
-        <f>(0.000000000000000138*G56/(1.673534E-24*1.3*0.000000066726*F56*1.8986E+30/(E56*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1039.84328949877</v>
       </c>
       <c r="T56">
-        <f>IF(I56&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4483,11 +4457,11 @@
         <v>9.9823299999999993</v>
       </c>
       <c r="S57">
-        <f>(0.000000000000000138*G57/(1.673534E-24*1.3*0.000000066726*F57*1.8986E+30/(E57*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1107.9861243219782</v>
       </c>
       <c r="T57">
-        <f>IF(I57&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4544,11 +4518,11 @@
         <v>9.7295700000000007</v>
       </c>
       <c r="S58">
-        <f>(0.000000000000000138*G58/(1.673534E-24*1.3*0.000000066726*F58*1.8986E+30/(E58*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>487.59044264912109</v>
       </c>
       <c r="T58">
-        <f>IF(I58&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4608,11 +4582,11 @@
         <v>8.8910300000000007</v>
       </c>
       <c r="S59">
-        <f>(0.000000000000000138*G59/(1.673534E-24*1.3*0.000000066726*F59*1.8986E+30/(E59*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>795.95548671567838</v>
       </c>
       <c r="T59">
-        <f>IF(I59&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4672,11 +4646,11 @@
         <v>9.6608199999999993</v>
       </c>
       <c r="S60">
-        <f>(0.000000000000000138*G60/(1.673534E-24*1.3*0.000000066726*F60*1.8986E+30/(E60*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>355.42536038318485</v>
       </c>
       <c r="T60">
-        <f>IF(I60&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4736,11 +4710,11 @@
         <v>8.9943600000000004</v>
       </c>
       <c r="S61">
-        <f>(0.000000000000000138*G61/(1.673534E-24*1.3*0.000000066726*F61*1.8986E+30/(E61*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>267.77715667890726</v>
       </c>
       <c r="T61">
-        <f>IF(I61&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4800,11 +4774,11 @@
         <v>9.8670799999999996</v>
       </c>
       <c r="S62">
-        <f>(0.000000000000000138*G62/(1.673534E-24*1.3*0.000000066726*F62*1.8986E+30/(E62*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>2057.1154637812851</v>
       </c>
       <c r="T62">
-        <f>IF(I62&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4864,11 +4838,11 @@
         <v>9.8192900000000005</v>
       </c>
       <c r="S63">
-        <f>(0.000000000000000138*G63/(1.673534E-24*1.3*0.000000066726*F63*1.8986E+30/(E63*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>621.55661806820979</v>
       </c>
       <c r="T63">
-        <f>IF(I63&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4925,11 +4899,11 @@
         <v>9.6464700000000008</v>
       </c>
       <c r="S64">
-        <f>(0.000000000000000138*G64/(1.673534E-24*1.3*0.000000066726*F64*1.8986E+30/(E64*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>103.20465157174387</v>
       </c>
       <c r="T64">
-        <f>IF(I64&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4989,11 +4963,11 @@
         <v>9.2569999999999997</v>
       </c>
       <c r="S65">
-        <f>(0.000000000000000138*G65/(1.673534E-24*1.3*0.000000066726*F65*1.8986E+30/(E65*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1277.1766379712274</v>
       </c>
       <c r="T65">
-        <f>IF(I65&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -5053,11 +5027,11 @@
         <v>9.9122599999999998</v>
       </c>
       <c r="S66">
-        <f>(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
+        <f t="shared" ref="S66:S79" si="4">(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
         <v>1247.4798366438731</v>
       </c>
       <c r="T66">
-        <f>IF(I66&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T66:T79" si="5">IF(I66&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
@@ -5117,11 +5091,11 @@
         <v>9.1661699999999993</v>
       </c>
       <c r="S67">
-        <f>(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>93.704022194109143</v>
       </c>
       <c r="T67">
-        <f>IF(I67&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5181,11 +5155,11 @@
         <v>8.0700400000000005</v>
       </c>
       <c r="S68">
-        <f>(0.000000000000000138*G68/(1.673534E-24*1.3*0.000000066726*F68*1.8986E+30/(E68*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>863.09804630713359</v>
       </c>
       <c r="T68">
-        <f>IF(I68&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-7</v>
       </c>
     </row>
@@ -5245,11 +5219,11 @@
         <v>9.20974</v>
       </c>
       <c r="S69">
-        <f>(0.000000000000000138*G69/(1.673534E-24*1.3*0.000000066726*F69*1.8986E+30/(E69*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>140.68549179703928</v>
       </c>
       <c r="T69">
-        <f>IF(I69&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5306,11 +5280,11 @@
         <v>9.3767099999999992</v>
       </c>
       <c r="S70">
-        <f>(0.000000000000000138*G70/(1.673534E-24*1.3*0.000000066726*F70*1.8986E+30/(E70*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>701.18164217622461</v>
       </c>
       <c r="T70">
-        <f>IF(I70&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5370,11 +5344,11 @@
         <v>9.5723000000000003</v>
       </c>
       <c r="S71">
-        <f>(0.000000000000000138*G71/(1.673534E-24*1.3*0.000000066726*F71*1.8986E+30/(E71*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1226.0598654781754</v>
       </c>
       <c r="T71">
-        <f>IF(I71&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5434,11 +5408,11 @@
         <v>9.3950700000000005</v>
       </c>
       <c r="S72">
-        <f>(0.000000000000000138*G72/(1.673534E-24*1.3*0.000000066726*F72*1.8986E+30/(E72*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>2192.2225820487197</v>
       </c>
       <c r="T72">
-        <f>IF(I72&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5498,11 +5472,11 @@
         <v>9.9720200000000006</v>
       </c>
       <c r="S73">
-        <f>(0.000000000000000138*G73/(1.673534E-24*1.3*0.000000066726*F73*1.8986E+30/(E73*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1209.5375438309629</v>
       </c>
       <c r="T73">
-        <f>IF(I73&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5562,11 +5536,11 @@
         <v>9.6124899999999993</v>
       </c>
       <c r="S74">
-        <f>(0.000000000000000138*G74/(1.673534E-24*1.3*0.000000066726*F74*1.8986E+30/(E74*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>136.24063220140397</v>
       </c>
       <c r="T74">
-        <f>IF(I74&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5626,11 +5600,11 @@
         <v>9.8979599999999994</v>
       </c>
       <c r="S75">
-        <f>(0.000000000000000138*G75/(1.673534E-24*1.3*0.000000066726*F75*1.8986E+30/(E75*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1257.117296864338</v>
       </c>
       <c r="T75">
-        <f>IF(I75&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5690,11 +5664,11 @@
         <v>10.028499999999999</v>
       </c>
       <c r="S76">
-        <f>(0.000000000000000138*G76/(1.673534E-24*1.3*0.000000066726*F76*1.8986E+30/(E76*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>2049.4439875099679</v>
       </c>
       <c r="T76">
-        <f>IF(I76&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5754,11 +5728,11 @@
         <v>9.9369700000000005</v>
       </c>
       <c r="S77">
-        <f>(0.000000000000000138*G77/(1.673534E-24*1.3*0.000000066726*F77*1.8986E+30/(E77*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>422.11900227636102</v>
       </c>
       <c r="T77">
-        <f>IF(I77&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5818,11 +5792,11 @@
         <v>9.3251000000000008</v>
       </c>
       <c r="S78">
-        <f>(0.000000000000000138*G78/(1.673534E-24*1.3*0.000000066726*F78*1.8986E+30/(E78*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>162.15983922320817</v>
       </c>
       <c r="T78">
-        <f>IF(I78&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5882,11 +5856,11 @@
         <v>9.7388899999999996</v>
       </c>
       <c r="S79">
-        <f>(0.000000000000000138*G79/(1.673534E-24*1.3*0.000000066726*F79*1.8986E+30/(E79*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>120.66830436099001</v>
       </c>
       <c r="T79">
-        <f>IF(I79&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127086A6-DFCE-EC42-BEBA-E6222BE726E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9440D2-5C4A-2043-948C-627C5A6DA88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34740" yWindow="4480" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -937,18 +937,44 @@
         <v>2061</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
+      <c r="I2" s="6">
+        <v>6801</v>
+      </c>
+      <c r="J2" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1.43</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="M2" s="6">
+        <v>4.21</v>
+      </c>
+      <c r="N2" s="6">
+        <v>7.3289156000000002</v>
+      </c>
+      <c r="O2" s="6">
+        <v>-76.304032000000007</v>
+      </c>
+      <c r="P2" s="6">
+        <v>196.852</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>9.5950000000000006</v>
+      </c>
+      <c r="R2" s="6">
+        <v>9.5202500000000008</v>
+      </c>
+      <c r="S2" s="6">
+        <f t="shared" ref="S2:S33" si="0">(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
+        <v>934.76971602454307</v>
+      </c>
+      <c r="T2" s="6">
+        <f t="shared" ref="T2:T33" si="1">IF(I2&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
       <c r="U2" s="7" t="s">
         <v>138</v>
       </c>
@@ -1012,11 +1038,11 @@
         <v>7.5767499999999997</v>
       </c>
       <c r="S3" s="6">
-        <f t="shared" ref="S2:S33" si="0">(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1286.8653667451285</v>
       </c>
       <c r="T3" s="6">
-        <f t="shared" ref="T2:T33" si="1">IF(I3&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
       <c r="U3" s="7" t="s">

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9440D2-5C4A-2043-948C-627C5A6DA88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02884B69-2385-A341-98C4-5D1D351D5428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34740" yWindow="4480" windowWidth="33600" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02884B69-2385-A341-98C4-5D1D351D5428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF0A03E-0F62-5149-AF0C-CED0BE51F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="140">
   <si>
     <t>#pl_name</t>
   </si>
@@ -453,6 +453,9 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>WASP-12 b</t>
   </si>
 </sst>
 </file>
@@ -816,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH79"/>
+  <dimension ref="A1:BH80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
@@ -5057,7 +5060,7 @@
         <v>1247.4798366438731</v>
       </c>
       <c r="T66">
-        <f t="shared" ref="T66:T79" si="5">IF(I66&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T66:T80" si="5">IF(I66&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
@@ -5886,6 +5889,33 @@
         <v>120.66830436099001</v>
       </c>
       <c r="T79">
+        <f t="shared" si="5"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80">
+        <v>6200</v>
+      </c>
+      <c r="J80">
+        <v>1.2</v>
+      </c>
+      <c r="N80">
+        <v>97.636728000000005</v>
+      </c>
+      <c r="O80">
+        <v>29.672419000000001</v>
+      </c>
+      <c r="P80">
+        <v>427</v>
+      </c>
+      <c r="T80">
         <f t="shared" si="5"/>
         <v>-5</v>
       </c>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A350165-11CD-384A-97C3-9E8028631666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F862D4-3F96-2D46-9781-6AA4098864CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17740" yWindow="1780" windowWidth="33600" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="141">
   <si>
     <t>#pl_name</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>WASP-12 b</t>
+  </si>
+  <si>
+    <t>eps boo b</t>
   </si>
 </sst>
 </file>
@@ -831,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH80"/>
+  <dimension ref="A1:BH81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
@@ -986,11 +989,11 @@
         <v>10.178599999999999</v>
       </c>
       <c r="S2">
-        <f>(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
+        <f t="shared" ref="S2:S33" si="0">(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
         <v>1121.1126749906216</v>
       </c>
       <c r="T2">
-        <f>IF(I2&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T2:T33" si="1">IF(I2&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="BE2" s="3"/>
@@ -1053,11 +1056,11 @@
         <v>9.8728300000000004</v>
       </c>
       <c r="S3">
-        <f>(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>243.60813720463176</v>
       </c>
       <c r="T3">
-        <f>IF(I3&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="BE3" s="3"/>
@@ -1120,11 +1123,11 @@
         <v>8.5984200000000008</v>
       </c>
       <c r="S4">
-        <f>(0.000000000000000138*G4/(1.673534E-24*1.3*0.000000066726*F4*1.8986E+30/(E4*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>39.515068300859213</v>
       </c>
       <c r="T4">
-        <f>IF(I4&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="BE4" s="3"/>
@@ -1187,11 +1190,11 @@
         <v>9.5193600000000007</v>
       </c>
       <c r="S5">
-        <f>(0.000000000000000138*G5/(1.673534E-24*1.3*0.000000066726*F5*1.8986E+30/(E5*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>200.46131426194896</v>
       </c>
       <c r="T5">
-        <f>IF(I5&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="BE5" s="3"/>
@@ -1251,11 +1254,11 @@
         <v>9.5635499999999993</v>
       </c>
       <c r="S6">
-        <f>(0.000000000000000138*G6/(1.673534E-24*1.3*0.000000066726*F6*1.8986E+30/(E6*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>2101.5864855136347</v>
       </c>
       <c r="T6">
-        <f>IF(I6&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="BE6" s="3"/>
@@ -1315,11 +1318,11 @@
         <v>9.77332</v>
       </c>
       <c r="S7">
-        <f>(0.000000000000000138*G7/(1.673534E-24*1.3*0.000000066726*F7*1.8986E+30/(E7*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>387.53401759458865</v>
       </c>
       <c r="T7">
-        <f>IF(I7&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
       <c r="V7" s="2"/>
@@ -1379,11 +1382,11 @@
         <v>9.4517399999999991</v>
       </c>
       <c r="S8">
-        <f>(0.000000000000000138*G8/(1.673534E-24*1.3*0.000000066726*F8*1.8986E+30/(E8*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>338.15838787809196</v>
       </c>
       <c r="T8">
-        <f>IF(I8&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
       <c r="V8" s="2"/>
@@ -1446,11 +1449,11 @@
         <v>7.89255</v>
       </c>
       <c r="S9">
-        <f>(0.000000000000000138*G9/(1.673534E-24*1.3*0.000000066726*F9*1.8986E+30/(E9*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>211.51519610586323</v>
       </c>
       <c r="T9">
-        <f>IF(I9&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1510,11 +1513,11 @@
         <v>7.5933599999999997</v>
       </c>
       <c r="S10">
-        <f>(0.000000000000000138*G10/(1.673534E-24*1.3*0.000000066726*F10*1.8986E+30/(E10*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>797.33090232058362</v>
       </c>
       <c r="T10">
-        <f>IF(I10&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1574,11 +1577,11 @@
         <v>8.0141600000000004</v>
       </c>
       <c r="S11">
-        <f>(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>599.63628364223177</v>
       </c>
       <c r="T11">
-        <f>IF(I11&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V11" s="2"/>
@@ -1641,11 +1644,11 @@
         <v>8.7641200000000001</v>
       </c>
       <c r="S12">
-        <f>(0.000000000000000138*G12/(1.673534E-24*1.3*0.000000066726*F12*1.8986E+30/(E12*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>597.79498778467087</v>
       </c>
       <c r="T12">
-        <f>IF(I12&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1705,11 +1708,11 @@
         <v>7.41432</v>
       </c>
       <c r="S13">
-        <f>(0.000000000000000138*G13/(1.673534E-24*1.3*0.000000066726*F13*1.8986E+30/(E13*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>349.61677638948368</v>
       </c>
       <c r="T13">
-        <f>IF(I13&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1766,11 +1769,11 @@
         <v>8.2268799999999995</v>
       </c>
       <c r="S14">
-        <f>(0.000000000000000138*G14/(1.673534E-24*1.3*0.000000066726*F14*1.8986E+30/(E14*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1280.5918535006856</v>
       </c>
       <c r="T14">
-        <f>IF(I14&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V14" s="2"/>
@@ -1833,11 +1836,11 @@
         <v>7.5086599999999999</v>
       </c>
       <c r="S15">
-        <f>(0.000000000000000138*G15/(1.673534E-24*1.3*0.000000066726*F15*1.8986E+30/(E15*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>988.21070019970352</v>
       </c>
       <c r="T15">
-        <f>IF(I15&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1897,11 +1900,11 @@
         <v>9.6495599999999992</v>
       </c>
       <c r="S16">
-        <f>(0.000000000000000138*G16/(1.673534E-24*1.3*0.000000066726*F16*1.8986E+30/(E16*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>956.09264119622901</v>
       </c>
       <c r="T16">
-        <f>IF(I16&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V16" s="2"/>
@@ -1964,11 +1967,11 @@
         <v>7.9077599999999997</v>
       </c>
       <c r="S17">
-        <f>(0.000000000000000138*G17/(1.673534E-24*1.3*0.000000066726*F17*1.8986E+30/(E17*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>742.8583931109747</v>
       </c>
       <c r="T17">
-        <f>IF(I17&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2026,11 +2029,11 @@
         <v>9.5202500000000008</v>
       </c>
       <c r="S18" s="6">
-        <f>(0.000000000000000138*G18/(1.673534E-24*1.3*0.000000066726*F18*1.8986E+30/(E18*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>934.76971602454307</v>
       </c>
       <c r="T18" s="6">
-        <f>IF(I18&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
       <c r="U18" s="7" t="s">
@@ -2093,11 +2096,11 @@
         <v>8.4183900000000005</v>
       </c>
       <c r="S19">
-        <f>(0.000000000000000138*G19/(1.673534E-24*1.3*0.000000066726*F19*1.8986E+30/(E19*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>574.11765847468712</v>
       </c>
       <c r="T19">
-        <f>IF(I19&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2157,11 +2160,11 @@
         <v>7.8097899999999996</v>
       </c>
       <c r="S20">
-        <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>668.81110409377118</v>
       </c>
       <c r="T20">
-        <f>IF(I20&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2221,11 +2224,11 @@
         <v>9.2170199999999998</v>
       </c>
       <c r="S21">
-        <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1103.5971886171305</v>
       </c>
       <c r="T21">
-        <f>IF(I21&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2282,11 +2285,11 @@
         <v>9.7262599999999999</v>
       </c>
       <c r="S22">
-        <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>662.28004924519439</v>
       </c>
       <c r="T22">
-        <f>IF(I22&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2346,11 +2349,11 @@
         <v>7.8311200000000003</v>
       </c>
       <c r="S23">
-        <f>(0.000000000000000138*G23/(1.673534E-24*1.3*0.000000066726*F23*1.8986E+30/(E23*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>3894.9775251994533</v>
       </c>
       <c r="T23">
-        <f>IF(I23&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2410,11 +2413,11 @@
         <v>9.2088699999999992</v>
       </c>
       <c r="S24">
-        <f>(0.000000000000000138*G24/(1.673534E-24*1.3*0.000000066726*F24*1.8986E+30/(E24*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>948.15286253702118</v>
       </c>
       <c r="T24">
-        <f>IF(I24&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2474,11 +2477,11 @@
         <v>9.8633100000000002</v>
       </c>
       <c r="S25">
-        <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>443.85469120292152</v>
       </c>
       <c r="T25">
-        <f>IF(I25&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2538,11 +2541,11 @@
         <v>8.5839300000000005</v>
       </c>
       <c r="S26">
-        <f>(0.000000000000000138*G26/(1.673534E-24*1.3*0.000000066726*F26*1.8986E+30/(E26*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>570.64953846380126</v>
       </c>
       <c r="T26">
-        <f>IF(I26&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2602,11 +2605,11 @@
         <v>7.5749199999999997</v>
       </c>
       <c r="S27">
-        <f>(0.000000000000000138*G27/(1.673534E-24*1.3*0.000000066726*F27*1.8986E+30/(E27*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>518.80488815900412</v>
       </c>
       <c r="T27">
-        <f>IF(I27&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2666,11 +2669,11 @@
         <v>8.23752</v>
       </c>
       <c r="S28">
-        <f>(0.000000000000000138*G28/(1.673534E-24*1.3*0.000000066726*F28*1.8986E+30/(E28*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>99.730517672190274</v>
       </c>
       <c r="T28">
-        <f>IF(I28&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2727,11 +2730,11 @@
         <v>9.7632399999999997</v>
       </c>
       <c r="S29">
-        <f>(0.000000000000000138*G29/(1.673534E-24*1.3*0.000000066726*F29*1.8986E+30/(E29*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>582.97620763372299</v>
       </c>
       <c r="T29">
-        <f>IF(I29&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2791,11 +2794,11 @@
         <v>9.95702</v>
       </c>
       <c r="S30">
-        <f>(0.000000000000000138*G30/(1.673534E-24*1.3*0.000000066726*F30*1.8986E+30/(E30*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1492.9814393090719</v>
       </c>
       <c r="T30">
-        <f>IF(I30&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2855,11 +2858,11 @@
         <v>8.4517299999999995</v>
       </c>
       <c r="S31">
-        <f>(0.000000000000000138*G31/(1.673534E-24*1.3*0.000000066726*F31*1.8986E+30/(E31*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>965.25628287035329</v>
       </c>
       <c r="T31">
-        <f>IF(I31&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2919,11 +2922,11 @@
         <v>7.5767499999999997</v>
       </c>
       <c r="S32" s="6">
-        <f>(0.000000000000000138*G32/(1.673534E-24*1.3*0.000000066726*F32*1.8986E+30/(E32*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1286.8653667451285</v>
       </c>
       <c r="T32" s="6">
-        <f>IF(I32&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
       <c r="U32" s="7" t="s">
@@ -2983,11 +2986,11 @@
         <v>10.367800000000001</v>
       </c>
       <c r="S33">
-        <f>(0.000000000000000138*G33/(1.673534E-24*1.3*0.000000066726*F33*1.8986E+30/(E33*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>160.76196513632402</v>
       </c>
       <c r="T33">
-        <f>IF(I33&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -3047,11 +3050,11 @@
         <v>9.6000599999999991</v>
       </c>
       <c r="S34">
-        <f>(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
+        <f t="shared" ref="S34:S59" si="2">(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
         <v>972.96006983022733</v>
       </c>
       <c r="T34">
-        <f>IF(I34&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T34:T65" si="3">IF(I34&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -3111,11 +3114,11 @@
         <v>8.2424300000000006</v>
       </c>
       <c r="S35">
-        <f>(0.000000000000000138*G35/(1.673534E-24*1.3*0.000000066726*F35*1.8986E+30/(E35*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>457.63140850776114</v>
       </c>
       <c r="T35">
-        <f>IF(I35&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3175,11 +3178,11 @@
         <v>8.1740100000000009</v>
       </c>
       <c r="S36">
-        <f>(0.000000000000000138*G36/(1.673534E-24*1.3*0.000000066726*F36*1.8986E+30/(E36*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>789.006338593706</v>
       </c>
       <c r="T36">
-        <f>IF(I36&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3239,11 +3242,11 @@
         <v>9.4290710000000004</v>
       </c>
       <c r="S37" s="6">
-        <f>(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>56.120615203365361</v>
       </c>
       <c r="T37" s="6">
-        <f>IF(I37&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
       <c r="U37" s="7" t="s">
@@ -3306,11 +3309,11 @@
         <v>9.4135299999999997</v>
       </c>
       <c r="S38">
-        <f>(0.000000000000000138*G38/(1.673534E-24*1.3*0.000000066726*F38*1.8986E+30/(E38*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1175.9460676296278</v>
       </c>
       <c r="T38">
-        <f>IF(I38&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3367,11 +3370,11 @@
         <v>9.3678899999999992</v>
       </c>
       <c r="S39">
-        <f>(0.000000000000000138*G39/(1.673534E-24*1.3*0.000000066726*F39*1.8986E+30/(E39*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1399.2265914107247</v>
       </c>
       <c r="T39">
-        <f>IF(I39&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3428,11 +3431,11 @@
         <v>9.3503900000000009</v>
       </c>
       <c r="S40">
-        <f>(0.000000000000000138*G40/(1.673534E-24*1.3*0.000000066726*F40*1.8986E+30/(E40*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>353.31388599481477</v>
       </c>
       <c r="T40">
-        <f>IF(I40&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3492,11 +3495,11 @@
         <v>9.1879500000000007</v>
       </c>
       <c r="S41">
-        <f>(0.000000000000000138*G41/(1.673534E-24*1.3*0.000000066726*F41*1.8986E+30/(E41*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>882.20971786077962</v>
       </c>
       <c r="T41">
-        <f>IF(I41&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3556,11 +3559,11 @@
         <v>7.9756099999999996</v>
       </c>
       <c r="S42">
-        <f>(0.000000000000000138*G42/(1.673534E-24*1.3*0.000000066726*F42*1.8986E+30/(E42*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>431.57254486096394</v>
       </c>
       <c r="T42">
-        <f>IF(I42&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3620,11 +3623,11 @@
         <v>8.8952899999999993</v>
       </c>
       <c r="S43">
-        <f>(0.000000000000000138*G43/(1.673534E-24*1.3*0.000000066726*F43*1.8986E+30/(E43*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>974.78820571370204</v>
       </c>
       <c r="T43">
-        <f>IF(I43&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3684,11 +3687,11 @@
         <v>9.5843900000000009</v>
       </c>
       <c r="S44">
-        <f>(0.000000000000000138*G44/(1.673534E-24*1.3*0.000000066726*F44*1.8986E+30/(E44*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1460.8182255852041</v>
       </c>
       <c r="T44">
-        <f>IF(I44&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3745,11 +3748,11 @@
         <v>9.6598100000000002</v>
       </c>
       <c r="S45">
-        <f>(0.000000000000000138*G45/(1.673534E-24*1.3*0.000000066726*F45*1.8986E+30/(E45*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1324.5165539963698</v>
       </c>
       <c r="T45">
-        <f>IF(I45&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3806,11 +3809,11 @@
         <v>9.7596699999999998</v>
       </c>
       <c r="S46">
-        <f>(0.000000000000000138*G46/(1.673534E-24*1.3*0.000000066726*F46*1.8986E+30/(E46*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>55.915145726222889</v>
       </c>
       <c r="T46">
-        <f>IF(I46&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3867,11 +3870,11 @@
         <v>8.9365100000000002</v>
       </c>
       <c r="S47">
-        <f>(0.000000000000000138*G47/(1.673534E-24*1.3*0.000000066726*F47*1.8986E+30/(E47*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>77.040187113891676</v>
       </c>
       <c r="T47">
-        <f>IF(I47&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3928,11 +3931,11 @@
         <v>9.4724400000000006</v>
       </c>
       <c r="S48">
-        <f>(0.000000000000000138*G48/(1.673534E-24*1.3*0.000000066726*F48*1.8986E+30/(E48*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>83.670803141549356</v>
       </c>
       <c r="T48">
-        <f>IF(I48&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3989,11 +3992,11 @@
         <v>7.4165299999999998</v>
       </c>
       <c r="S49">
-        <f>(0.000000000000000138*G49/(1.673534E-24*1.3*0.000000066726*F49*1.8986E+30/(E49*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>777.64358420307099</v>
       </c>
       <c r="T49">
-        <f>IF(I49&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4053,11 +4056,11 @@
         <v>9.7777600000000007</v>
       </c>
       <c r="S50">
-        <f>(0.000000000000000138*G50/(1.673534E-24*1.3*0.000000066726*F50*1.8986E+30/(E50*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>755.33252275944176</v>
       </c>
       <c r="T50">
-        <f>IF(I50&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4114,11 +4117,11 @@
         <v>9.641</v>
       </c>
       <c r="S51">
-        <f>(0.000000000000000138*G51/(1.673534E-24*1.3*0.000000066726*F51*1.8986E+30/(E51*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>318.17832033985127</v>
       </c>
       <c r="T51">
-        <f>IF(I51&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4178,11 +4181,11 @@
         <v>9.0746900000000004</v>
       </c>
       <c r="S52">
-        <f>(0.000000000000000138*G52/(1.673534E-24*1.3*0.000000066726*F52*1.8986E+30/(E52*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>36.149567272802649</v>
       </c>
       <c r="T52">
-        <f>IF(I52&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4242,11 +4245,11 @@
         <v>9.8465900000000008</v>
       </c>
       <c r="S53">
-        <f>(0.000000000000000138*G53/(1.673534E-24*1.3*0.000000066726*F53*1.8986E+30/(E53*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>224.58825733889913</v>
       </c>
       <c r="T53">
-        <f>IF(I53&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4303,11 +4306,11 @@
         <v>9.6080000000000005</v>
       </c>
       <c r="S54">
-        <f>(0.000000000000000138*G54/(1.673534E-24*1.3*0.000000066726*F54*1.8986E+30/(E54*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1039.84328949877</v>
       </c>
       <c r="T54">
-        <f>IF(I54&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4367,11 +4370,11 @@
         <v>9.9823299999999993</v>
       </c>
       <c r="S55">
-        <f>(0.000000000000000138*G55/(1.673534E-24*1.3*0.000000066726*F55*1.8986E+30/(E55*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1107.9861243219782</v>
       </c>
       <c r="T55">
-        <f>IF(I55&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4428,11 +4431,11 @@
         <v>9.7295700000000007</v>
       </c>
       <c r="S56">
-        <f>(0.000000000000000138*G56/(1.673534E-24*1.3*0.000000066726*F56*1.8986E+30/(E56*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>487.59044264912109</v>
       </c>
       <c r="T56">
-        <f>IF(I56&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4492,11 +4495,11 @@
         <v>8.8910300000000007</v>
       </c>
       <c r="S57">
-        <f>(0.000000000000000138*G57/(1.673534E-24*1.3*0.000000066726*F57*1.8986E+30/(E57*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>795.95548671567838</v>
       </c>
       <c r="T57">
-        <f>IF(I57&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4556,11 +4559,11 @@
         <v>9.6608199999999993</v>
       </c>
       <c r="S58">
-        <f>(0.000000000000000138*G58/(1.673534E-24*1.3*0.000000066726*F58*1.8986E+30/(E58*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>355.42536038318485</v>
       </c>
       <c r="T58">
-        <f>IF(I58&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4620,11 +4623,11 @@
         <v>8.9943600000000004</v>
       </c>
       <c r="S59">
-        <f>(0.000000000000000138*G59/(1.673534E-24*1.3*0.000000066726*F59*1.8986E+30/(E59*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>267.77715667890726</v>
       </c>
       <c r="T59">
-        <f>IF(I59&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4654,7 +4657,7 @@
         <v>11.4986</v>
       </c>
       <c r="T60">
-        <f>IF(I60&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4714,11 +4717,11 @@
         <v>9.8670799999999996</v>
       </c>
       <c r="S61">
-        <f>(0.000000000000000138*G61/(1.673534E-24*1.3*0.000000066726*F61*1.8986E+30/(E61*7149200000)^2))/100000</f>
+        <f t="shared" ref="S61:S80" si="4">(0.000000000000000138*G61/(1.673534E-24*1.3*0.000000066726*F61*1.8986E+30/(E61*7149200000)^2))/100000</f>
         <v>2057.1154637812851</v>
       </c>
       <c r="T61">
-        <f>IF(I61&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4778,11 +4781,11 @@
         <v>9.8192900000000005</v>
       </c>
       <c r="S62">
-        <f>(0.000000000000000138*G62/(1.673534E-24*1.3*0.000000066726*F62*1.8986E+30/(E62*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>621.55661806820979</v>
       </c>
       <c r="T62">
-        <f>IF(I62&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4839,11 +4842,11 @@
         <v>9.6464700000000008</v>
       </c>
       <c r="S63">
-        <f>(0.000000000000000138*G63/(1.673534E-24*1.3*0.000000066726*F63*1.8986E+30/(E63*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>103.20465157174387</v>
       </c>
       <c r="T63">
-        <f>IF(I63&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4903,11 +4906,11 @@
         <v>9.2569999999999997</v>
       </c>
       <c r="S64">
-        <f>(0.000000000000000138*G64/(1.673534E-24*1.3*0.000000066726*F64*1.8986E+30/(E64*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1277.1766379712274</v>
       </c>
       <c r="T64">
-        <f>IF(I64&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4967,11 +4970,11 @@
         <v>9.9122599999999998</v>
       </c>
       <c r="S65">
-        <f>(0.000000000000000138*G65/(1.673534E-24*1.3*0.000000066726*F65*1.8986E+30/(E65*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1247.4798366438731</v>
       </c>
       <c r="T65">
-        <f>IF(I65&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -5031,11 +5034,11 @@
         <v>9.1661699999999993</v>
       </c>
       <c r="S66">
-        <f>(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>93.704022194109143</v>
       </c>
       <c r="T66">
-        <f>IF(I66&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T66:T80" si="5">IF(I66&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -5093,11 +5096,11 @@
         <v>6.5536899999999996</v>
       </c>
       <c r="S67" s="8">
-        <f>(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1130.2166328238993</v>
       </c>
       <c r="T67" s="6">
-        <f>IF(I67&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-7</v>
       </c>
       <c r="U67" s="7" t="s">
@@ -5160,11 +5163,11 @@
         <v>8.0700400000000005</v>
       </c>
       <c r="S68">
-        <f>(0.000000000000000138*G68/(1.673534E-24*1.3*0.000000066726*F68*1.8986E+30/(E68*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>863.09804630713359</v>
       </c>
       <c r="T68">
-        <f>IF(I68&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-7</v>
       </c>
     </row>
@@ -5224,11 +5227,11 @@
         <v>9.20974</v>
       </c>
       <c r="S69">
-        <f>(0.000000000000000138*G69/(1.673534E-24*1.3*0.000000066726*F69*1.8986E+30/(E69*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>140.68549179703928</v>
       </c>
       <c r="T69">
-        <f>IF(I69&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5288,11 +5291,11 @@
         <v>9.4846599999999999</v>
       </c>
       <c r="S70" s="6">
-        <f>(0.000000000000000138*G70/(1.673534E-24*1.3*0.000000066726*F70*1.8986E+30/(E70*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>955.72600175951948</v>
       </c>
       <c r="T70" s="6">
-        <f>IF(I70&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
       <c r="U70" s="7" t="s">
@@ -5352,11 +5355,11 @@
         <v>9.3767099999999992</v>
       </c>
       <c r="S71">
-        <f>(0.000000000000000138*G71/(1.673534E-24*1.3*0.000000066726*F71*1.8986E+30/(E71*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>701.18164217622461</v>
       </c>
       <c r="T71">
-        <f>IF(I71&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5416,11 +5419,11 @@
         <v>9.5723000000000003</v>
       </c>
       <c r="S72">
-        <f>(0.000000000000000138*G72/(1.673534E-24*1.3*0.000000066726*F72*1.8986E+30/(E72*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1226.0598654781754</v>
       </c>
       <c r="T72">
-        <f>IF(I72&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5480,11 +5483,11 @@
         <v>9.3950700000000005</v>
       </c>
       <c r="S73">
-        <f>(0.000000000000000138*G73/(1.673534E-24*1.3*0.000000066726*F73*1.8986E+30/(E73*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>2192.2225820487197</v>
       </c>
       <c r="T73">
-        <f>IF(I73&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5544,11 +5547,11 @@
         <v>9.9720200000000006</v>
       </c>
       <c r="S74">
-        <f>(0.000000000000000138*G74/(1.673534E-24*1.3*0.000000066726*F74*1.8986E+30/(E74*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1209.5375438309629</v>
       </c>
       <c r="T74">
-        <f>IF(I74&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5608,11 +5611,11 @@
         <v>9.6124899999999993</v>
       </c>
       <c r="S75">
-        <f>(0.000000000000000138*G75/(1.673534E-24*1.3*0.000000066726*F75*1.8986E+30/(E75*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>136.24063220140397</v>
       </c>
       <c r="T75">
-        <f>IF(I75&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5672,11 +5675,11 @@
         <v>9.8979599999999994</v>
       </c>
       <c r="S76">
-        <f>(0.000000000000000138*G76/(1.673534E-24*1.3*0.000000066726*F76*1.8986E+30/(E76*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>1257.117296864338</v>
       </c>
       <c r="T76">
-        <f>IF(I76&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5736,11 +5739,11 @@
         <v>10.028499999999999</v>
       </c>
       <c r="S77">
-        <f>(0.000000000000000138*G77/(1.673534E-24*1.3*0.000000066726*F77*1.8986E+30/(E77*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>2049.4439875099679</v>
       </c>
       <c r="T77">
-        <f>IF(I77&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5800,11 +5803,11 @@
         <v>9.9369700000000005</v>
       </c>
       <c r="S78">
-        <f>(0.000000000000000138*G78/(1.673534E-24*1.3*0.000000066726*F78*1.8986E+30/(E78*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>422.11900227636102</v>
       </c>
       <c r="T78">
-        <f>IF(I78&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5864,11 +5867,11 @@
         <v>9.3251000000000008</v>
       </c>
       <c r="S79">
-        <f>(0.000000000000000138*G79/(1.673534E-24*1.3*0.000000066726*F79*1.8986E+30/(E79*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>162.15983922320817</v>
       </c>
       <c r="T79">
-        <f>IF(I79&gt;6800,-7,-5)</f>
+        <f t="shared" si="5"/>
         <v>-5</v>
       </c>
     </row>
@@ -5928,12 +5931,17 @@
         <v>9.7388899999999996</v>
       </c>
       <c r="S80">
-        <f>(0.000000000000000138*G80/(1.673534E-24*1.3*0.000000066726*F80*1.8986E+30/(E80*7149200000)^2))/100000</f>
+        <f t="shared" si="4"/>
         <v>120.66830436099001</v>
       </c>
       <c r="T80">
-        <f>IF(I80&gt;6800,-7,-5)</f>
-        <v>-5</v>
+        <f t="shared" si="5"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/waltzerclone/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F862D4-3F96-2D46-9781-6AA4098864CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DC096E-5C4E-9D4F-9092-4AD1AC0C6EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17740" yWindow="1780" windowWidth="33600" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="2200" windowWidth="33600" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="144">
   <si>
     <t>#pl_name</t>
   </si>
@@ -104,9 +104,6 @@
     <t>KELT-9 b</t>
   </si>
   <si>
-    <t>B9.5-A0</t>
-  </si>
-  <si>
     <t>TOI-257 b</t>
   </si>
   <si>
@@ -459,6 +456,18 @@
   </si>
   <si>
     <t>eps boo b</t>
+  </si>
+  <si>
+    <t>HAT-P-32 b</t>
+  </si>
+  <si>
+    <t>HAT-P-7 b</t>
+  </si>
+  <si>
+    <t>Kepler-13 b</t>
+  </si>
+  <si>
+    <t>TrES-4 b</t>
   </si>
 </sst>
 </file>
@@ -491,7 +500,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,13 +519,66 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor theme="5" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="5" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -525,7 +587,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -558,6 +620,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -834,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH81"/>
+  <dimension ref="A1:BH86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
@@ -927,74 +1011,36 @@
         <v>18</v>
       </c>
       <c r="T1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="U1" s="4" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>4.4652997599999997</v>
-      </c>
-      <c r="D2">
-        <v>5.561E-2</v>
-      </c>
-      <c r="E2">
-        <v>1.319</v>
-      </c>
-      <c r="F2">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="G2">
-        <v>1322</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2">
-        <v>5980</v>
-      </c>
-      <c r="J2">
-        <v>1.1739999999999999</v>
-      </c>
-      <c r="K2">
-        <v>1.151</v>
-      </c>
-      <c r="L2">
-        <v>0.13</v>
-      </c>
-      <c r="M2">
-        <v>4.359</v>
-      </c>
-      <c r="N2">
-        <v>344.44536319999997</v>
-      </c>
-      <c r="O2">
-        <v>38.674919000000003</v>
-      </c>
-      <c r="P2">
-        <v>158.97900000000001</v>
-      </c>
-      <c r="Q2">
-        <v>9.827</v>
-      </c>
-      <c r="R2" s="9">
-        <v>10.178599999999999</v>
-      </c>
-      <c r="S2">
-        <f t="shared" ref="S2:S33" si="0">(0.000000000000000138*G2/(1.673534E-24*1.3*0.000000066726*F2*1.8986E+30/(E2*7149200000)^2))/100000</f>
-        <v>1121.1126749906216</v>
-      </c>
-      <c r="T2">
-        <f t="shared" ref="T2:T33" si="1">IF(I2&gt;6800,-7,-5)</f>
-        <v>-5</v>
+      <c r="A2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="17">
+        <v>4907.77490234375</v>
+      </c>
+      <c r="J2" s="17"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17">
+        <v>221.24648617076679</v>
+      </c>
+      <c r="O2" s="17">
+        <v>27.074315757773469</v>
+      </c>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="17">
+        <v>2.1833524703979492</v>
+      </c>
+      <c r="R2" s="17">
+        <v>2.1833524703979492</v>
       </c>
       <c r="BE2" s="3"/>
       <c r="BG2" s="3"/>
@@ -1002,65 +1048,65 @@
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3">
-        <v>4.6276700000000002</v>
+        <v>4.4652997599999997</v>
       </c>
       <c r="D3">
-        <v>5.96E-2</v>
+        <v>5.561E-2</v>
       </c>
       <c r="E3">
-        <v>1.42</v>
+        <v>1.319</v>
       </c>
       <c r="F3">
-        <v>3.44</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="G3">
-        <v>1624</v>
+        <v>1322</v>
       </c>
       <c r="H3" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>6600</v>
+        <v>5980</v>
       </c>
       <c r="J3">
-        <v>1.82</v>
+        <v>1.1739999999999999</v>
       </c>
       <c r="K3">
-        <v>2.65</v>
+        <v>1.151</v>
       </c>
       <c r="L3">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="M3">
-        <v>4.25</v>
+        <v>4.359</v>
       </c>
       <c r="N3">
-        <v>260.11617189999998</v>
+        <v>344.44536319999997</v>
       </c>
       <c r="O3">
-        <v>38.242168200000002</v>
+        <v>38.674919000000003</v>
       </c>
       <c r="P3">
-        <v>222.66300000000001</v>
+        <v>158.97900000000001</v>
       </c>
       <c r="Q3">
-        <v>9.9879999999999995</v>
+        <v>9.827</v>
       </c>
       <c r="R3" s="9">
-        <v>9.8728300000000004</v>
+        <v>10.178599999999999</v>
       </c>
       <c r="S3">
-        <f t="shared" si="0"/>
-        <v>243.60813720463176</v>
+        <f>(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
+        <v>1121.1126749906216</v>
       </c>
       <c r="T3">
-        <f t="shared" si="1"/>
+        <f>IF(I3&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="BE3" s="3"/>
@@ -1069,65 +1115,65 @@
     </row>
     <row r="4" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4">
-        <v>5.6335157999999996</v>
+        <v>4.6276700000000002</v>
       </c>
       <c r="D4">
-        <v>6.8140000000000006E-2</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E4">
-        <v>0.95099999999999996</v>
+        <v>1.42</v>
       </c>
       <c r="F4">
-        <v>9.02</v>
+        <v>3.44</v>
       </c>
       <c r="G4">
-        <v>1540</v>
+        <v>1624</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="I4">
-        <v>6380</v>
+        <v>6600</v>
       </c>
       <c r="J4">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="K4">
-        <v>1.33</v>
+        <v>2.65</v>
       </c>
       <c r="L4">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="M4">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="N4">
-        <v>245.1514324</v>
+        <v>260.11617189999998</v>
       </c>
       <c r="O4">
-        <v>41.047960099999997</v>
+        <v>38.242168200000002</v>
       </c>
       <c r="P4">
-        <v>127.774</v>
+        <v>222.66300000000001</v>
       </c>
       <c r="Q4">
-        <v>8.7200000000000006</v>
+        <v>9.9879999999999995</v>
       </c>
       <c r="R4" s="9">
-        <v>8.5984200000000008</v>
+        <v>9.8728300000000004</v>
       </c>
       <c r="S4">
-        <f t="shared" si="0"/>
-        <v>39.515068300859213</v>
+        <f>(0.000000000000000138*G4/(1.673534E-24*1.3*0.000000066726*F4*1.8986E+30/(E4*7149200000)^2))/100000</f>
+        <v>243.60813720463176</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
+        <f>IF(I4&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="BE4" s="3"/>
@@ -1136,65 +1182,65 @@
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5">
-        <v>3.2122199999999999</v>
+        <v>5.6335157999999996</v>
       </c>
       <c r="D5">
-        <v>4.1399999999999999E-2</v>
+        <v>6.8140000000000006E-2</v>
       </c>
       <c r="E5">
-        <v>1.1499999999999999</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="F5">
-        <v>2.4700000000000002</v>
+        <v>9.02</v>
       </c>
       <c r="G5">
-        <v>1463</v>
+        <v>1540</v>
       </c>
       <c r="H5" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="I5">
-        <v>5302</v>
+        <v>6380</v>
       </c>
       <c r="J5">
-        <v>1.1100000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="K5">
-        <v>1.1299999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="L5">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="M5">
-        <v>4.3600000000000003</v>
+        <v>4.16</v>
       </c>
       <c r="N5">
-        <v>155.6814593</v>
+        <v>245.1514324</v>
       </c>
       <c r="O5">
-        <v>50.128711500000001</v>
+        <v>41.047960099999997</v>
       </c>
       <c r="P5">
-        <v>81.764700000000005</v>
+        <v>127.774</v>
       </c>
       <c r="Q5">
-        <v>9.7629999999999999</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="R5" s="9">
-        <v>9.5193600000000007</v>
+        <v>8.5984200000000008</v>
       </c>
       <c r="S5">
-        <f t="shared" si="0"/>
-        <v>200.46131426194896</v>
+        <f>(0.000000000000000138*G5/(1.673534E-24*1.3*0.000000066726*F5*1.8986E+30/(E5*7149200000)^2))/100000</f>
+        <v>39.515068300859213</v>
       </c>
       <c r="T5">
-        <f t="shared" si="1"/>
+        <f>IF(I5&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="BE5" s="3"/>
@@ -1203,62 +1249,65 @@
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6">
-        <v>4.7947813000000004</v>
+        <v>3.2122199999999999</v>
       </c>
       <c r="D6">
-        <v>6.2770000000000006E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="E6">
-        <v>1.631</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F6">
-        <v>0.57399999999999995</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="G6">
-        <v>1772</v>
+        <v>1463</v>
+      </c>
+      <c r="H6" t="s">
+        <v>94</v>
       </c>
       <c r="I6">
-        <v>6212</v>
+        <v>5302</v>
       </c>
       <c r="J6">
-        <v>2.1970000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="K6">
-        <v>1.4350000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L6">
-        <v>3.6999999999999998E-2</v>
+        <v>0.24</v>
       </c>
       <c r="M6">
-        <v>3.9114</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N6">
-        <v>28.282571900000001</v>
+        <v>155.6814593</v>
       </c>
       <c r="O6">
-        <v>52.053920900000001</v>
+        <v>50.128711500000001</v>
       </c>
       <c r="P6">
-        <v>233.22</v>
+        <v>81.764700000000005</v>
       </c>
       <c r="Q6">
-        <v>9.7270000000000003</v>
+        <v>9.7629999999999999</v>
       </c>
       <c r="R6" s="9">
-        <v>9.5635499999999993</v>
+        <v>9.5193600000000007</v>
       </c>
       <c r="S6">
-        <f t="shared" si="0"/>
-        <v>2101.5864855136347</v>
+        <f>(0.000000000000000138*G6/(1.673534E-24*1.3*0.000000066726*F6*1.8986E+30/(E6*7149200000)^2))/100000</f>
+        <v>200.46131426194896</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
+        <f>IF(I6&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="BE6" s="3"/>
@@ -1266,64 +1315,36 @@
       <c r="BH6" s="3"/>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>4.7869491000000002</v>
-      </c>
-      <c r="D7">
-        <v>6.5549999999999997E-2</v>
-      </c>
-      <c r="E7">
-        <v>1.6759999999999999</v>
-      </c>
-      <c r="F7">
-        <v>3.58</v>
-      </c>
-      <c r="G7">
-        <v>1930</v>
-      </c>
-      <c r="I7">
-        <v>7394</v>
-      </c>
-      <c r="J7">
-        <v>1.9259999999999999</v>
-      </c>
-      <c r="K7">
-        <v>1.6479999999999999</v>
-      </c>
-      <c r="L7">
-        <v>-6.9000000000000006E-2</v>
-      </c>
-      <c r="M7">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="N7">
-        <v>130.5056385</v>
-      </c>
-      <c r="O7">
-        <v>3.7105662000000001</v>
-      </c>
-      <c r="P7">
-        <v>341.26299999999998</v>
-      </c>
-      <c r="Q7">
-        <v>9.7739999999999991</v>
-      </c>
-      <c r="R7" s="9">
-        <v>9.77332</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="0"/>
-        <v>387.53401759458865</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+      <c r="A7" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="17">
+        <v>6245.11328125</v>
+      </c>
+      <c r="J7" s="17">
+        <v>1.208241820335388</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="17">
+        <v>4.2744002342224121</v>
+      </c>
+      <c r="N7" s="17">
+        <v>31.04275939878713</v>
+      </c>
+      <c r="O7" s="17">
+        <v>46.687851647860192</v>
+      </c>
+      <c r="P7" s="11">
+        <v>283.38339999999999</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>11.12930202484131</v>
+      </c>
+      <c r="R7" s="17">
+        <v>11.12930202484131</v>
       </c>
       <c r="V7" s="2"/>
       <c r="Z7" s="2"/>
@@ -1331,580 +1352,541 @@
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8">
-        <v>2.7443245200000002</v>
+        <v>4.7947813000000004</v>
       </c>
       <c r="D8">
-        <v>4.7390000000000002E-2</v>
+        <v>6.2770000000000006E-2</v>
       </c>
       <c r="E8">
-        <v>1.87</v>
+        <v>1.631</v>
       </c>
       <c r="F8">
-        <v>6.78</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="G8">
-        <v>2562</v>
+        <v>1772</v>
       </c>
       <c r="I8">
-        <v>8450</v>
+        <v>6212</v>
       </c>
       <c r="J8">
-        <v>1.8580000000000001</v>
+        <v>2.1970000000000001</v>
       </c>
       <c r="K8">
-        <v>1.89</v>
+        <v>1.4350000000000001</v>
       </c>
       <c r="L8">
-        <v>-5.8999999999999997E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="M8">
-        <v>4.181</v>
+        <v>3.9114</v>
       </c>
       <c r="N8">
-        <v>74.552333200000007</v>
+        <v>28.282571900000001</v>
       </c>
       <c r="O8">
-        <v>9.9979794000000002</v>
+        <v>52.053920900000001</v>
       </c>
       <c r="P8">
-        <v>330.73899999999998</v>
+        <v>233.22</v>
       </c>
       <c r="Q8">
-        <v>9.4700000000000006</v>
+        <v>9.7270000000000003</v>
       </c>
       <c r="R8" s="9">
-        <v>9.4517399999999991</v>
+        <v>9.5635499999999993</v>
       </c>
       <c r="S8">
-        <f t="shared" si="0"/>
-        <v>338.15838787809196</v>
+        <f>(0.000000000000000138*G8/(1.673534E-24*1.3*0.000000066726*F8*1.8986E+30/(E8*7149200000)^2))/100000</f>
+        <v>2101.5864855136347</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I8&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
       <c r="V8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="2">
-        <v>6.1349779</v>
-      </c>
-      <c r="D9" s="2">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="F9" s="2">
-        <v>2.14</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1361</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="2">
-        <v>5742</v>
-      </c>
-      <c r="J9" s="2">
-        <v>2.04</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1.27</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="M9" s="2">
-        <v>3.92</v>
-      </c>
-      <c r="N9" s="2">
-        <v>203.50995599999999</v>
-      </c>
-      <c r="O9" s="2">
-        <v>53.728187599999998</v>
-      </c>
-      <c r="P9" s="2">
-        <v>92.258899999999997</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="R9" s="10">
-        <v>7.89255</v>
+    <row r="9" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>4.7869491000000002</v>
+      </c>
+      <c r="D9">
+        <v>6.5549999999999997E-2</v>
+      </c>
+      <c r="E9">
+        <v>1.6759999999999999</v>
+      </c>
+      <c r="F9">
+        <v>3.58</v>
+      </c>
+      <c r="G9">
+        <v>1930</v>
+      </c>
+      <c r="I9">
+        <v>7394</v>
+      </c>
+      <c r="J9">
+        <v>1.9259999999999999</v>
+      </c>
+      <c r="K9">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="L9">
+        <v>-6.9000000000000006E-2</v>
+      </c>
+      <c r="M9">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="N9">
+        <v>130.5056385</v>
+      </c>
+      <c r="O9">
+        <v>3.7105662000000001</v>
+      </c>
+      <c r="P9">
+        <v>341.26299999999998</v>
+      </c>
+      <c r="Q9">
+        <v>9.7739999999999991</v>
+      </c>
+      <c r="R9" s="9">
+        <v>9.77332</v>
       </c>
       <c r="S9">
-        <f t="shared" si="0"/>
-        <v>211.51519610586323</v>
+        <f>(0.000000000000000138*G9/(1.673534E-24*1.3*0.000000066726*F9*1.8986E+30/(E9*7149200000)^2))/100000</f>
+        <v>387.53401759458865</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I9&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>11.53533</v>
-      </c>
-      <c r="D10">
-        <v>0.10970000000000001</v>
-      </c>
-      <c r="E10">
-        <v>1.026</v>
-      </c>
-      <c r="F10">
-        <v>0.41499999999999998</v>
-      </c>
-      <c r="G10">
-        <v>1228.3</v>
-      </c>
-      <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10">
-        <v>5521</v>
-      </c>
-      <c r="J10">
-        <v>2.3359999999999999</v>
-      </c>
-      <c r="K10">
-        <v>1.3240000000000001</v>
-      </c>
-      <c r="L10">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="M10">
-        <v>3.823</v>
-      </c>
-      <c r="N10">
-        <v>4.4471631</v>
-      </c>
-      <c r="O10">
-        <v>-66.358928500000005</v>
-      </c>
-      <c r="P10">
-        <v>79.5702</v>
-      </c>
-      <c r="Q10">
-        <v>7.79</v>
-      </c>
-      <c r="R10" s="9">
-        <v>7.5933599999999997</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="0"/>
-        <v>797.33090232058362</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2.8758900000000001</v>
-      </c>
-      <c r="D11" s="2">
-        <v>4.3639999999999998E-2</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.74</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.38</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1626</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="2">
-        <v>6179</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.41</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1.42</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0.32</v>
-      </c>
-      <c r="M11" s="2">
-        <v>4.37</v>
-      </c>
-      <c r="N11" s="2">
-        <v>247.62298269999999</v>
-      </c>
-      <c r="O11" s="2">
-        <v>38.347534899999999</v>
-      </c>
-      <c r="P11" s="2">
-        <v>75.8643</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>8.15</v>
-      </c>
-      <c r="R11" s="10">
-        <v>8.0141600000000004</v>
+      <c r="A10" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="17">
+        <v>6424.27685546875</v>
+      </c>
+      <c r="J10" s="17">
+        <v>2.0702402591705318</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17">
+        <v>292.24718620018581</v>
+      </c>
+      <c r="O10" s="17">
+        <v>47.969544064101818</v>
+      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="17">
+        <v>10.36768245697021</v>
+      </c>
+      <c r="R10" s="17">
+        <v>10.36768245697021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>2.7443245200000002</v>
+      </c>
+      <c r="D11">
+        <v>4.7390000000000002E-2</v>
+      </c>
+      <c r="E11">
+        <v>1.87</v>
+      </c>
+      <c r="F11">
+        <v>6.78</v>
+      </c>
+      <c r="G11">
+        <v>2562</v>
+      </c>
+      <c r="I11">
+        <v>8450</v>
+      </c>
+      <c r="J11">
+        <v>1.8580000000000001</v>
+      </c>
+      <c r="K11">
+        <v>1.89</v>
+      </c>
+      <c r="L11">
+        <v>-5.8999999999999997E-2</v>
+      </c>
+      <c r="M11">
+        <v>4.181</v>
+      </c>
+      <c r="N11">
+        <v>74.552333200000007</v>
+      </c>
+      <c r="O11">
+        <v>9.9979794000000002</v>
+      </c>
+      <c r="P11">
+        <v>330.73899999999998</v>
+      </c>
+      <c r="Q11">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="R11" s="9">
+        <v>9.4517399999999991</v>
       </c>
       <c r="S11">
-        <f t="shared" si="0"/>
-        <v>599.63628364223177</v>
+        <f>(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
+        <v>338.15838787809196</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I11&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
       <c r="V11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>19.502103999999999</v>
-      </c>
-      <c r="D12">
-        <v>0.1482</v>
-      </c>
-      <c r="E12">
-        <v>0.52993221999999995</v>
-      </c>
-      <c r="F12">
-        <v>3.0425219999999999E-2</v>
-      </c>
-      <c r="G12">
-        <v>253.08</v>
-      </c>
-      <c r="H12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12">
-        <v>6310</v>
-      </c>
-      <c r="J12">
-        <v>1.43</v>
-      </c>
-      <c r="K12">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L12">
-        <v>-0.16</v>
-      </c>
-      <c r="M12">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="N12">
-        <v>253.78488530000001</v>
-      </c>
-      <c r="O12">
-        <v>20.491523999999998</v>
-      </c>
-      <c r="P12">
-        <v>107.898</v>
-      </c>
-      <c r="Q12">
-        <v>8.8550000000000004</v>
-      </c>
-      <c r="R12" s="9">
-        <v>8.7641200000000001</v>
+    <row r="12" spans="1:60" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2">
+        <v>6.1349779</v>
+      </c>
+      <c r="D12" s="2">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2.14</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1361</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5742</v>
+      </c>
+      <c r="J12" s="2">
+        <v>2.04</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="M12" s="2">
+        <v>3.92</v>
+      </c>
+      <c r="N12" s="2">
+        <v>203.50995599999999</v>
+      </c>
+      <c r="O12" s="2">
+        <v>53.728187599999998</v>
+      </c>
+      <c r="P12" s="2">
+        <v>92.258899999999997</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="R12" s="10">
+        <v>7.89255</v>
       </c>
       <c r="S12">
-        <f t="shared" si="0"/>
-        <v>597.79498778467087</v>
+        <f>(0.000000000000000138*G12/(1.673534E-24*1.3*0.000000066726*F12*1.8986E+30/(E12*7149200000)^2))/100000</f>
+        <v>211.51519610586323</v>
       </c>
       <c r="T12">
-        <f t="shared" si="1"/>
+        <f>IF(I12&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="13" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2.2185756699999999</v>
-      </c>
-      <c r="D13" s="2">
-        <v>3.1260000000000003E-2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1209</v>
-      </c>
-      <c r="H13" s="1" t="s">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="2">
-        <v>5052</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0.79</v>
-      </c>
-      <c r="L13" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="M13" s="2">
-        <v>4.49</v>
-      </c>
-      <c r="N13" s="2">
-        <v>300.1821223</v>
-      </c>
-      <c r="O13" s="2">
-        <v>22.7097759</v>
-      </c>
-      <c r="P13" s="2">
-        <v>19.7638</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>7.67</v>
-      </c>
-      <c r="R13" s="10">
-        <v>7.41432</v>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>11.53533</v>
+      </c>
+      <c r="D13">
+        <v>0.10970000000000001</v>
+      </c>
+      <c r="E13">
+        <v>1.026</v>
+      </c>
+      <c r="F13">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="G13">
+        <v>1228.3</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13">
+        <v>5521</v>
+      </c>
+      <c r="J13">
+        <v>2.3359999999999999</v>
+      </c>
+      <c r="K13">
+        <v>1.3240000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M13">
+        <v>3.823</v>
+      </c>
+      <c r="N13">
+        <v>4.4471631</v>
+      </c>
+      <c r="O13">
+        <v>-66.358928500000005</v>
+      </c>
+      <c r="P13">
+        <v>79.5702</v>
+      </c>
+      <c r="Q13">
+        <v>7.79</v>
+      </c>
+      <c r="R13" s="9">
+        <v>7.5933599999999997</v>
       </c>
       <c r="S13">
-        <f t="shared" si="0"/>
-        <v>349.61677638948368</v>
+        <f>(0.000000000000000138*G13/(1.673534E-24*1.3*0.000000066726*F13*1.8986E+30/(E13*7149200000)^2))/100000</f>
+        <v>797.33090232058362</v>
       </c>
       <c r="T13">
-        <f t="shared" si="1"/>
+        <f>IF(I13&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>3.3089580000000001</v>
-      </c>
-      <c r="D14">
-        <v>5.2080000000000001E-2</v>
-      </c>
-      <c r="E14">
-        <v>1.5449999999999999</v>
-      </c>
-      <c r="F14">
-        <v>1.0169999999999999</v>
-      </c>
-      <c r="G14">
-        <v>2132</v>
-      </c>
-      <c r="I14">
-        <v>6272</v>
-      </c>
-      <c r="J14">
-        <v>2.5910000000000002</v>
-      </c>
-      <c r="K14">
-        <v>1.72</v>
-      </c>
-      <c r="L14">
-        <v>0.3</v>
-      </c>
-      <c r="M14">
-        <v>3.8479999999999999</v>
-      </c>
-      <c r="N14">
-        <v>319.6995877</v>
-      </c>
-      <c r="O14">
-        <v>-26.6163743</v>
-      </c>
-      <c r="P14">
-        <v>161.49799999999999</v>
-      </c>
-      <c r="Q14">
-        <v>8.3239999999999998</v>
-      </c>
-      <c r="R14" s="9">
-        <v>8.2268799999999995</v>
+    <row r="14" spans="1:60" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2.8758900000000001</v>
+      </c>
+      <c r="D14" s="2">
+        <v>4.3639999999999998E-2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1626</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6179</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.41</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1.42</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="M14" s="2">
+        <v>4.37</v>
+      </c>
+      <c r="N14" s="2">
+        <v>247.62298269999999</v>
+      </c>
+      <c r="O14" s="2">
+        <v>38.347534899999999</v>
+      </c>
+      <c r="P14" s="2">
+        <v>75.8643</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>8.15</v>
+      </c>
+      <c r="R14" s="10">
+        <v>8.0141600000000004</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
-        <v>1280.5918535006856</v>
+        <f>(0.000000000000000138*G14/(1.673534E-24*1.3*0.000000066726*F14*1.8986E+30/(E14*7149200000)^2))/100000</f>
+        <v>599.63628364223177</v>
       </c>
       <c r="T14">
-        <f t="shared" si="1"/>
+        <f>IF(I14&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="V14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>19.502103999999999</v>
+      </c>
+      <c r="D15">
+        <v>0.1482</v>
+      </c>
+      <c r="E15">
+        <v>0.52993221999999995</v>
+      </c>
+      <c r="F15">
+        <v>3.0425219999999999E-2</v>
+      </c>
+      <c r="G15">
+        <v>253.08</v>
+      </c>
+      <c r="H15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15">
+        <v>6310</v>
+      </c>
+      <c r="J15">
+        <v>1.43</v>
+      </c>
+      <c r="K15">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L15">
+        <v>-0.16</v>
+      </c>
+      <c r="M15">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="N15">
+        <v>253.78488530000001</v>
+      </c>
+      <c r="O15">
+        <v>20.491523999999998</v>
+      </c>
+      <c r="P15">
+        <v>107.898</v>
+      </c>
+      <c r="Q15">
+        <v>8.8550000000000004</v>
+      </c>
+      <c r="R15" s="9">
+        <v>8.7641200000000001</v>
+      </c>
+      <c r="S15">
+        <f>(0.000000000000000138*G15/(1.673534E-24*1.3*0.000000066726*F15*1.8986E+30/(E15*7149200000)^2))/100000</f>
+        <v>597.79498778467087</v>
+      </c>
+      <c r="T15">
+        <f>IF(I15&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:60" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3.5247485900000002</v>
-      </c>
-      <c r="D15" s="2">
-        <v>4.7070000000000001E-2</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1.39</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.73</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1459</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="2">
-        <v>6091</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1.19</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1.23</v>
-      </c>
-      <c r="L15" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="M15" s="2">
-        <v>4.45</v>
-      </c>
-      <c r="N15" s="2">
-        <v>330.79502189999999</v>
-      </c>
-      <c r="O15" s="2">
-        <v>18.884241899999999</v>
-      </c>
-      <c r="P15" s="2">
-        <v>48.301600000000001</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>7.65</v>
-      </c>
-      <c r="R15" s="10">
-        <v>7.5086599999999999</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>988.21070019970352</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16">
-        <v>6.0344680000000004</v>
-      </c>
-      <c r="D16">
-        <v>6.3560000000000005E-2</v>
-      </c>
-      <c r="E16">
-        <v>0.437</v>
-      </c>
-      <c r="F16">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G16">
-        <v>1076</v>
-      </c>
-      <c r="H16" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16">
-        <v>5540</v>
-      </c>
-      <c r="J16">
-        <v>1.0589999999999999</v>
-      </c>
-      <c r="K16">
-        <v>1.02</v>
-      </c>
-      <c r="L16">
-        <v>0.04</v>
-      </c>
-      <c r="M16">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="N16">
-        <v>349.55926649999998</v>
-      </c>
-      <c r="O16">
-        <v>-56.9039857</v>
-      </c>
-      <c r="P16">
-        <v>94.171899999999994</v>
-      </c>
-      <c r="Q16">
-        <v>9.8089999999999993</v>
-      </c>
-      <c r="R16" s="9">
-        <v>9.6495599999999992</v>
+      <c r="C16" s="2">
+        <v>2.2185756699999999</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3.1260000000000003E-2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1209</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5052</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="L16" s="2">
+        <v>-0.02</v>
+      </c>
+      <c r="M16" s="2">
+        <v>4.49</v>
+      </c>
+      <c r="N16" s="2">
+        <v>300.1821223</v>
+      </c>
+      <c r="O16" s="2">
+        <v>22.7097759</v>
+      </c>
+      <c r="P16" s="2">
+        <v>19.7638</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>7.67</v>
+      </c>
+      <c r="R16" s="10">
+        <v>7.41432</v>
       </c>
       <c r="S16">
-        <f t="shared" si="0"/>
-        <v>956.09264119622901</v>
+        <f>(0.000000000000000138*G16/(1.673534E-24*1.3*0.000000066726*F16*1.8986E+30/(E16*7149200000)^2))/100000</f>
+        <v>349.61677638948368</v>
       </c>
       <c r="T16">
-        <f t="shared" si="1"/>
+        <f>IF(I16&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
       <c r="V16" s="2"/>
@@ -1913,4041 +1895,4269 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
       </c>
       <c r="C17">
-        <v>14.2767</v>
+        <v>3.3089580000000001</v>
       </c>
       <c r="D17">
-        <v>0.12280000000000001</v>
+        <v>5.2080000000000001E-2</v>
       </c>
       <c r="E17">
-        <v>0.83599999999999997</v>
+        <v>1.5449999999999999</v>
       </c>
       <c r="F17">
-        <v>0.19</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="G17">
-        <v>789.15</v>
-      </c>
-      <c r="H17" t="s">
-        <v>46</v>
+        <v>2132</v>
       </c>
       <c r="I17">
-        <v>5080</v>
+        <v>6272</v>
       </c>
       <c r="J17">
-        <v>2.9430000000000001</v>
+        <v>2.5910000000000002</v>
       </c>
       <c r="K17">
-        <v>1.212</v>
+        <v>1.72</v>
       </c>
       <c r="L17">
-        <v>-0.08</v>
+        <v>0.3</v>
       </c>
       <c r="M17">
-        <v>3.5840000000000001</v>
+        <v>3.8479999999999999</v>
       </c>
       <c r="N17">
-        <v>353.03318630000001</v>
+        <v>319.6995877</v>
       </c>
       <c r="O17">
-        <v>-21.801200699999999</v>
+        <v>-26.6163743</v>
       </c>
       <c r="P17">
-        <v>95.548299999999998</v>
+        <v>161.49799999999999</v>
       </c>
       <c r="Q17">
-        <v>8.15</v>
+        <v>8.3239999999999998</v>
       </c>
       <c r="R17" s="9">
-        <v>7.9077599999999997</v>
+        <v>8.2268799999999995</v>
       </c>
       <c r="S17">
-        <f t="shared" si="0"/>
-        <v>742.8583931109747</v>
+        <f>(0.000000000000000138*G17/(1.673534E-24*1.3*0.000000066726*F17*1.8986E+30/(E17*7149200000)^2))/100000</f>
+        <v>1280.5918535006856</v>
       </c>
       <c r="T17">
-        <f t="shared" si="1"/>
+        <f>IF(I17&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="6">
-        <v>4.1268799999999999</v>
-      </c>
-      <c r="D18" s="6">
-        <v>5.6800000000000003E-2</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="G18" s="6">
-        <v>2061</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6">
-        <v>6801</v>
-      </c>
-      <c r="J18" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="K18" s="6">
-        <v>1.43</v>
-      </c>
-      <c r="L18" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="M18" s="6">
-        <v>4.21</v>
-      </c>
-      <c r="N18" s="6">
-        <v>7.3289156000000002</v>
-      </c>
-      <c r="O18" s="6">
-        <v>-76.304032000000007</v>
-      </c>
-      <c r="P18" s="6">
-        <v>196.852</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>9.5950000000000006</v>
-      </c>
-      <c r="R18" s="9">
-        <v>9.5202500000000008</v>
-      </c>
-      <c r="S18" s="6">
-        <f t="shared" si="0"/>
-        <v>934.76971602454307</v>
-      </c>
-      <c r="T18" s="6">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-      <c r="U18" s="7" t="s">
-        <v>138</v>
+    <row r="18" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3.5247485900000002</v>
+      </c>
+      <c r="D18" s="2">
+        <v>4.7070000000000001E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.39</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1459</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6091</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1.19</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1.23</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="M18" s="2">
+        <v>4.45</v>
+      </c>
+      <c r="N18" s="2">
+        <v>330.79502189999999</v>
+      </c>
+      <c r="O18" s="2">
+        <v>18.884241899999999</v>
+      </c>
+      <c r="P18" s="2">
+        <v>48.301600000000001</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>7.65</v>
+      </c>
+      <c r="R18" s="10">
+        <v>7.5086599999999999</v>
+      </c>
+      <c r="S18">
+        <f>(0.000000000000000138*G18/(1.673534E-24*1.3*0.000000066726*F18*1.8986E+30/(E18*7149200000)^2))/100000</f>
+        <v>988.21070019970352</v>
+      </c>
+      <c r="T18">
+        <f>IF(I18&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19">
-        <v>18.712024</v>
+        <v>6.0344680000000004</v>
       </c>
       <c r="D19">
-        <v>0.14499999999999999</v>
+        <v>6.3560000000000005E-2</v>
       </c>
       <c r="E19">
-        <v>0.80944318999999998</v>
+        <v>0.437</v>
       </c>
       <c r="F19">
-        <v>0.23314467</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G19">
-        <v>798.3</v>
+        <v>1076</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="I19">
-        <v>6128</v>
+        <v>5540</v>
       </c>
       <c r="J19">
-        <v>1.266</v>
+        <v>1.0589999999999999</v>
       </c>
       <c r="K19">
-        <v>1.1641999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="L19">
-        <v>4.2999999999999997E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M19">
-        <v>4.2960000000000003</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N19">
-        <v>306.74113399999999</v>
+        <v>349.55926649999998</v>
       </c>
       <c r="O19">
-        <v>33.744388200000003</v>
+        <v>-56.9039857</v>
       </c>
       <c r="P19">
-        <v>80.666499999999999</v>
+        <v>94.171899999999994</v>
       </c>
       <c r="Q19">
-        <v>8.5579999999999998</v>
+        <v>9.8089999999999993</v>
       </c>
       <c r="R19" s="9">
-        <v>8.4183900000000005</v>
+        <v>9.6495599999999992</v>
       </c>
       <c r="S19">
-        <f t="shared" si="0"/>
-        <v>574.11765847468712</v>
+        <f>(0.000000000000000138*G19/(1.673534E-24*1.3*0.000000066726*F19*1.8986E+30/(E19*7149200000)^2))/100000</f>
+        <v>956.09264119622901</v>
       </c>
       <c r="T19">
-        <f t="shared" si="1"/>
+        <f>IF(I19&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3.4148839999999998</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4.7899999999999998E-2</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1.23</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1.02</v>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>14.2767</v>
+      </c>
+      <c r="D20">
+        <v>0.12280000000000001</v>
+      </c>
+      <c r="E20">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="F20">
+        <v>0.19</v>
       </c>
       <c r="G20">
-        <v>1762</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="2">
-        <v>5392</v>
-      </c>
-      <c r="J20" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1.26</v>
-      </c>
-      <c r="L20" s="2">
-        <v>0.34</v>
-      </c>
-      <c r="M20" s="2">
-        <v>3.88</v>
-      </c>
-      <c r="N20" s="2">
-        <v>152.53193490000001</v>
-      </c>
-      <c r="O20" s="2">
-        <v>18.185728399999999</v>
-      </c>
-      <c r="P20" s="2">
-        <v>73.612300000000005</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>8.0185200000000005</v>
-      </c>
-      <c r="R20" s="10">
-        <v>7.8097899999999996</v>
+        <v>789.15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20">
+        <v>5080</v>
+      </c>
+      <c r="J20">
+        <v>2.9430000000000001</v>
+      </c>
+      <c r="K20">
+        <v>1.212</v>
+      </c>
+      <c r="L20">
+        <v>-0.08</v>
+      </c>
+      <c r="M20">
+        <v>3.5840000000000001</v>
+      </c>
+      <c r="N20">
+        <v>353.03318630000001</v>
+      </c>
+      <c r="O20">
+        <v>-21.801200699999999</v>
+      </c>
+      <c r="P20">
+        <v>95.548299999999998</v>
+      </c>
+      <c r="Q20">
+        <v>8.15</v>
+      </c>
+      <c r="R20" s="9">
+        <v>7.9077599999999997</v>
       </c>
       <c r="S20">
-        <f t="shared" si="0"/>
-        <v>668.81110409377118</v>
+        <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
+        <v>742.8583931109747</v>
       </c>
       <c r="T20">
-        <f t="shared" si="1"/>
+        <f>IF(I20&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21">
-        <v>11.814299999999999</v>
-      </c>
-      <c r="D21">
-        <v>0.1066</v>
-      </c>
-      <c r="E21">
-        <v>0.66</v>
-      </c>
-      <c r="F21">
-        <v>0.11</v>
-      </c>
-      <c r="G21">
-        <v>1089</v>
-      </c>
-      <c r="H21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21">
-        <v>5576</v>
-      </c>
-      <c r="J21">
-        <v>1.7470000000000001</v>
-      </c>
-      <c r="K21">
-        <v>1.157</v>
-      </c>
-      <c r="L21">
-        <v>0.42099999999999999</v>
-      </c>
-      <c r="M21">
-        <v>4.016</v>
-      </c>
-      <c r="N21">
-        <v>154.67109769999999</v>
-      </c>
-      <c r="O21">
-        <v>10.1288464</v>
-      </c>
-      <c r="P21">
-        <v>132.345</v>
-      </c>
-      <c r="Q21">
-        <v>9.3800000000000008</v>
+      <c r="A21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="6">
+        <v>4.1268799999999999</v>
+      </c>
+      <c r="D21" s="6">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.44</v>
+      </c>
+      <c r="F21" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="G21" s="6">
+        <v>2061</v>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6">
+        <v>6801</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1.43</v>
+      </c>
+      <c r="L21" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="M21" s="6">
+        <v>4.21</v>
+      </c>
+      <c r="N21" s="6">
+        <v>7.3289156000000002</v>
+      </c>
+      <c r="O21" s="6">
+        <v>-76.304032000000007</v>
+      </c>
+      <c r="P21" s="6">
+        <v>196.852</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>9.5950000000000006</v>
       </c>
       <c r="R21" s="9">
-        <v>9.2170199999999998</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
-        <v>1103.5971886171305</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <v>9.5202500000000008</v>
+      </c>
+      <c r="S21" s="6">
+        <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
+        <v>934.76971602454307</v>
+      </c>
+      <c r="T21" s="6">
+        <f>IF(I21&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22">
-        <v>11.168454000000001</v>
+        <v>18.712024</v>
       </c>
       <c r="D22">
-        <v>0.10356</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0.80944318999999998</v>
       </c>
       <c r="F22">
-        <v>0.39800000000000002</v>
+        <v>0.23314467</v>
       </c>
       <c r="G22">
-        <v>1030</v>
+        <v>798.3</v>
+      </c>
+      <c r="H22" t="s">
+        <v>54</v>
       </c>
       <c r="I22">
-        <v>6154</v>
+        <v>6128</v>
       </c>
       <c r="J22">
-        <v>1.161</v>
+        <v>1.266</v>
       </c>
       <c r="K22">
-        <v>1.1879999999999999</v>
+        <v>1.1641999999999999</v>
       </c>
       <c r="L22">
-        <v>0.1</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="M22">
-        <v>4.3789999999999996</v>
+        <v>4.2960000000000003</v>
       </c>
       <c r="N22">
-        <v>73.766792699999996</v>
+        <v>306.74113399999999</v>
       </c>
       <c r="O22">
-        <v>18.654323000000002</v>
+        <v>33.744388200000003</v>
       </c>
       <c r="P22">
-        <v>130.72</v>
+        <v>80.666499999999999</v>
       </c>
       <c r="Q22">
-        <v>9.8219999999999992</v>
+        <v>8.5579999999999998</v>
       </c>
       <c r="R22" s="9">
-        <v>9.7262599999999999</v>
+        <v>8.4183900000000005</v>
       </c>
       <c r="S22">
-        <f t="shared" si="0"/>
-        <v>662.28004924519439</v>
+        <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
+        <v>574.11765847468712</v>
       </c>
       <c r="T22">
-        <f t="shared" si="1"/>
+        <f>IF(I22&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23">
-        <v>4.73620865</v>
-      </c>
-      <c r="D23">
-        <v>6.2300000000000001E-2</v>
-      </c>
-      <c r="E23">
-        <v>1.35</v>
-      </c>
-      <c r="F23">
-        <v>0.20499999999999999</v>
+    <row r="23" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3.4148839999999998</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1.23</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1.02</v>
       </c>
       <c r="G23">
-        <v>1712</v>
-      </c>
-      <c r="H23" t="s">
-        <v>38</v>
-      </c>
-      <c r="I23">
-        <v>5375</v>
-      </c>
-      <c r="J23">
-        <v>2.69</v>
-      </c>
-      <c r="K23">
-        <v>1.44</v>
-      </c>
-      <c r="L23">
-        <v>0.17</v>
-      </c>
-      <c r="M23">
-        <v>3.7</v>
-      </c>
-      <c r="N23">
-        <v>161.70690529999999</v>
-      </c>
-      <c r="O23">
-        <v>-9.3993646000000002</v>
-      </c>
-      <c r="P23">
-        <v>99.159599999999998</v>
-      </c>
-      <c r="Q23">
-        <v>8.0399999999999991</v>
-      </c>
-      <c r="R23" s="9">
-        <v>7.8311200000000003</v>
+        <v>1762</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5392</v>
+      </c>
+      <c r="J23" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1.26</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="M23" s="2">
+        <v>3.88</v>
+      </c>
+      <c r="N23" s="2">
+        <v>152.53193490000001</v>
+      </c>
+      <c r="O23" s="2">
+        <v>18.185728399999999</v>
+      </c>
+      <c r="P23" s="2">
+        <v>73.612300000000005</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>8.0185200000000005</v>
+      </c>
+      <c r="R23" s="10">
+        <v>7.8097899999999996</v>
       </c>
       <c r="S23">
-        <f t="shared" si="0"/>
-        <v>3894.9775251994533</v>
+        <f>(0.000000000000000138*G23/(1.673534E-24*1.3*0.000000066726*F23*1.8986E+30/(E23*7149200000)^2))/100000</f>
+        <v>668.81110409377118</v>
       </c>
       <c r="T23">
-        <f t="shared" si="1"/>
+        <f>IF(I23&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
         <v>20</v>
       </c>
       <c r="C24">
-        <v>3.0801715999999999</v>
+        <v>11.814299999999999</v>
       </c>
       <c r="D24">
-        <v>4.8809999999999999E-2</v>
+        <v>0.1066</v>
       </c>
       <c r="E24">
-        <v>1.5249999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="F24">
-        <v>1.31</v>
+        <v>0.11</v>
       </c>
       <c r="G24">
-        <v>2087</v>
+        <v>1089</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I24">
-        <v>7454</v>
+        <v>5576</v>
       </c>
       <c r="J24">
-        <v>1.645</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="K24">
-        <v>1.635</v>
+        <v>1.157</v>
       </c>
       <c r="L24">
-        <v>-1.7999999999999999E-2</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="M24">
-        <v>4.22</v>
+        <v>4.016</v>
       </c>
       <c r="N24">
-        <v>125.617407</v>
+        <v>154.67109769999999</v>
       </c>
       <c r="O24">
-        <v>13.735309300000001</v>
+        <v>10.1288464</v>
       </c>
       <c r="P24">
-        <v>226.5</v>
+        <v>132.345</v>
       </c>
       <c r="Q24">
-        <v>9.234</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="R24" s="9">
-        <v>9.2088699999999992</v>
+        <v>9.2170199999999998</v>
       </c>
       <c r="S24">
-        <f t="shared" si="0"/>
-        <v>948.15286253702118</v>
+        <f>(0.000000000000000138*G24/(1.673534E-24*1.3*0.000000066726*F24*1.8986E+30/(E24*7149200000)^2))/100000</f>
+        <v>1103.5971886171305</v>
       </c>
       <c r="T24">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I24&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
       </c>
       <c r="C25">
-        <v>4.6117093000000002</v>
+        <v>11.168454000000001</v>
       </c>
       <c r="D25">
-        <v>6.3700000000000007E-2</v>
+        <v>0.10356</v>
       </c>
       <c r="E25">
-        <v>1.91</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>4.07</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="G25">
-        <v>1935</v>
-      </c>
-      <c r="H25" t="s">
-        <v>111</v>
+        <v>1030</v>
       </c>
       <c r="I25">
-        <v>7500</v>
+        <v>6154</v>
       </c>
       <c r="J25">
-        <v>1.83</v>
+        <v>1.161</v>
       </c>
       <c r="K25">
-        <v>1.62</v>
+        <v>1.1879999999999999</v>
       </c>
       <c r="L25">
-        <v>-0.12</v>
+        <v>0.1</v>
       </c>
       <c r="M25">
-        <v>4.1269999999999998</v>
+        <v>4.3789999999999996</v>
       </c>
       <c r="N25">
-        <v>111.5095293</v>
+        <v>73.766792699999996</v>
       </c>
       <c r="O25">
-        <v>7.6157759</v>
+        <v>18.654323000000002</v>
       </c>
       <c r="P25">
-        <v>300.27600000000001</v>
+        <v>130.72</v>
       </c>
       <c r="Q25">
-        <v>9.8569999999999993</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R25" s="9">
-        <v>9.8633100000000002</v>
+        <v>9.7262599999999999</v>
       </c>
       <c r="S25">
-        <f t="shared" si="0"/>
-        <v>443.85469120292152</v>
+        <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
+        <v>662.28004924519439</v>
       </c>
       <c r="T25">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I25&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
       </c>
       <c r="C26">
-        <v>4.1137899999999998</v>
+        <v>4.73620865</v>
       </c>
       <c r="D26">
-        <v>5.4969999999999998E-2</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="E26">
         <v>1.35</v>
       </c>
       <c r="F26">
-        <v>1.7</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="G26">
-        <v>2080</v>
+        <v>1712</v>
       </c>
       <c r="H26" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="I26">
-        <v>6327</v>
+        <v>5375</v>
       </c>
       <c r="J26">
-        <v>1.93</v>
+        <v>2.69</v>
       </c>
       <c r="K26">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M26">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N26">
-        <v>92.664022599999996</v>
+        <v>161.70690529999999</v>
       </c>
       <c r="O26">
-        <v>30.957133299999999</v>
+        <v>-9.3993646000000002</v>
       </c>
       <c r="P26">
-        <v>134.05799999999999</v>
+        <v>99.159599999999998</v>
       </c>
       <c r="Q26">
-        <v>8.68</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="R26" s="9">
-        <v>8.5839300000000005</v>
+        <v>7.8311200000000003</v>
       </c>
       <c r="S26">
-        <f t="shared" si="0"/>
-        <v>570.64953846380126</v>
+        <f>(0.000000000000000138*G26/(1.673534E-24*1.3*0.000000066726*F26*1.8986E+30/(E26*7149200000)^2))/100000</f>
+        <v>3894.9775251994533</v>
       </c>
       <c r="T26">
-        <f t="shared" si="1"/>
+        <f>IF(I26&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>24</v>
+      <c r="A27" t="s">
+        <v>67</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
       </c>
       <c r="C27">
-        <v>3.4741084999999998</v>
+        <v>3.0801715999999999</v>
       </c>
       <c r="D27">
-        <v>5.4199999999999998E-2</v>
+        <v>4.8809999999999999E-2</v>
       </c>
       <c r="E27">
-        <v>1.7410000000000001</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F27">
-        <v>3.3820000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="G27">
-        <v>2262</v>
+        <v>2087</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="I27">
-        <v>8720</v>
+        <v>7454</v>
       </c>
       <c r="J27">
-        <v>1.5649999999999999</v>
+        <v>1.645</v>
       </c>
       <c r="K27">
-        <v>1.76</v>
+        <v>1.635</v>
       </c>
       <c r="L27">
-        <v>-0.28999999999999998</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="M27">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="N27">
-        <v>294.66141260000001</v>
+        <v>125.617407</v>
       </c>
       <c r="O27">
-        <v>31.219200099999998</v>
+        <v>13.735309300000001</v>
       </c>
       <c r="P27">
-        <v>136.42599999999999</v>
+        <v>226.5</v>
       </c>
       <c r="Q27">
-        <v>7.59</v>
+        <v>9.234</v>
       </c>
       <c r="R27" s="9">
-        <v>7.5749199999999997</v>
+        <v>9.2088699999999992</v>
       </c>
       <c r="S27">
-        <f t="shared" si="0"/>
-        <v>518.80488815900412</v>
+        <f>(0.000000000000000138*G27/(1.673534E-24*1.3*0.000000066726*F27*1.8986E+30/(E27*7149200000)^2))/100000</f>
+        <v>948.15286253702118</v>
       </c>
       <c r="T27">
-        <f t="shared" si="1"/>
+        <f>IF(I27&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
         <v>20</v>
       </c>
       <c r="C28">
-        <v>5.55149296</v>
+        <v>4.6117093000000002</v>
       </c>
       <c r="D28">
-        <v>6.6500000000000004E-2</v>
+        <v>6.3700000000000007E-2</v>
       </c>
       <c r="E28">
-        <v>1.1339999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="F28">
-        <v>4.59</v>
+        <v>4.07</v>
       </c>
       <c r="G28">
-        <v>1391</v>
+        <v>1935</v>
       </c>
       <c r="H28" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="I28">
-        <v>6426</v>
+        <v>7500</v>
       </c>
       <c r="J28">
-        <v>1.3380000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="K28">
-        <v>1.268</v>
+        <v>1.62</v>
       </c>
       <c r="L28">
-        <v>0.13800000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="M28">
-        <v>4.2869999999999999</v>
+        <v>4.1269999999999998</v>
       </c>
       <c r="N28">
-        <v>161.90902729999999</v>
+        <v>111.5095293</v>
       </c>
       <c r="O28">
-        <v>71.655726999999999</v>
+        <v>7.6157759</v>
       </c>
       <c r="P28">
-        <v>96.517300000000006</v>
+        <v>300.27600000000001</v>
       </c>
       <c r="Q28">
-        <v>8.34</v>
+        <v>9.8569999999999993</v>
       </c>
       <c r="R28" s="9">
-        <v>8.23752</v>
+        <v>9.8633100000000002</v>
       </c>
       <c r="S28">
-        <f t="shared" si="0"/>
-        <v>99.730517672190274</v>
+        <f>(0.000000000000000138*G28/(1.673534E-24*1.3*0.000000066726*F28*1.8986E+30/(E28*7149200000)^2))/100000</f>
+        <v>443.85469120292152</v>
       </c>
       <c r="T28">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I28&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
         <v>20</v>
       </c>
       <c r="C29">
-        <v>2.7033900000000002</v>
+        <v>4.1137899999999998</v>
       </c>
       <c r="D29">
-        <v>4.1230000000000003E-2</v>
+        <v>5.4969999999999998E-2</v>
       </c>
       <c r="E29">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="F29">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="G29">
-        <v>1816</v>
+        <v>2080</v>
+      </c>
+      <c r="H29" t="s">
+        <v>54</v>
       </c>
       <c r="I29">
-        <v>6304</v>
+        <v>6327</v>
       </c>
       <c r="J29">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="K29">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="L29">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="N29">
-        <v>148.6431193</v>
+        <v>92.664022599999996</v>
       </c>
       <c r="O29">
-        <v>40.387944599999997</v>
+        <v>30.957133299999999</v>
       </c>
       <c r="P29">
-        <v>210.25200000000001</v>
+        <v>134.05799999999999</v>
       </c>
       <c r="Q29">
-        <v>9.8160000000000007</v>
+        <v>8.68</v>
       </c>
       <c r="R29" s="9">
-        <v>9.7632399999999997</v>
+        <v>8.5839300000000005</v>
       </c>
       <c r="S29">
-        <f t="shared" si="0"/>
-        <v>582.97620763372299</v>
+        <f>(0.000000000000000138*G29/(1.673534E-24*1.3*0.000000066726*F29*1.8986E+30/(E29*7149200000)^2))/100000</f>
+        <v>570.64953846380126</v>
       </c>
       <c r="T29">
-        <f t="shared" si="1"/>
+        <f>IF(I29&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>124</v>
+      <c r="A30" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
       </c>
       <c r="C30">
-        <v>2.9895931999999998</v>
+        <v>3.4741084999999998</v>
       </c>
       <c r="D30">
-        <v>4.317E-2</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="E30">
-        <v>1.6990000000000001</v>
+        <v>1.7410000000000001</v>
       </c>
       <c r="F30">
-        <v>0.90200000000000002</v>
+        <v>3.3820000000000001</v>
       </c>
       <c r="G30">
-        <v>1823</v>
+        <v>2262</v>
       </c>
       <c r="H30" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I30">
-        <v>6206</v>
+        <v>8720</v>
       </c>
       <c r="J30">
-        <v>1.603</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="K30">
-        <v>1.2010000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="L30">
-        <v>-0.11600000000000001</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M30">
-        <v>4.1079999999999997</v>
+        <v>4.29</v>
       </c>
       <c r="N30">
-        <v>157.06262000000001</v>
+        <v>294.66141260000001</v>
       </c>
       <c r="O30">
-        <v>25.573136600000002</v>
+        <v>31.219200099999998</v>
       </c>
       <c r="P30">
-        <v>218.05</v>
+        <v>136.42599999999999</v>
       </c>
       <c r="Q30">
-        <v>9.98</v>
+        <v>7.59</v>
       </c>
       <c r="R30" s="9">
-        <v>9.95702</v>
+        <v>7.5749199999999997</v>
       </c>
       <c r="S30">
-        <f t="shared" si="0"/>
-        <v>1492.9814393090719</v>
+        <f>(0.000000000000000138*G30/(1.673534E-24*1.3*0.000000066726*F30*1.8986E+30/(E30*7149200000)^2))/100000</f>
+        <v>518.80488815900412</v>
       </c>
       <c r="T30">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>IF(I30&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
         <v>20</v>
       </c>
       <c r="C31">
-        <v>2.7347700000000001</v>
+        <v>5.55149296</v>
       </c>
       <c r="D31">
-        <v>4.4150000000000002E-2</v>
+        <v>6.6500000000000004E-2</v>
       </c>
       <c r="E31">
-        <v>1.6</v>
+        <v>1.1339999999999999</v>
       </c>
       <c r="F31">
-        <v>1.39</v>
+        <v>4.59</v>
       </c>
       <c r="G31">
-        <v>2048</v>
+        <v>1391</v>
       </c>
       <c r="H31" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I31">
-        <v>6768</v>
+        <v>6426</v>
       </c>
       <c r="J31">
-        <v>1.81</v>
+        <v>1.3380000000000001</v>
       </c>
       <c r="K31">
-        <v>1.76</v>
+        <v>1.268</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="M31">
-        <v>4.5</v>
+        <v>4.2869999999999999</v>
       </c>
       <c r="N31">
-        <v>78.295591200000004</v>
+        <v>161.90902729999999</v>
       </c>
       <c r="O31">
-        <v>33.317953199999998</v>
+        <v>71.655726999999999</v>
       </c>
       <c r="P31">
-        <v>136.68100000000001</v>
+        <v>96.517300000000006</v>
       </c>
       <c r="Q31">
-        <v>8.56</v>
+        <v>8.34</v>
       </c>
       <c r="R31" s="9">
-        <v>8.4517299999999995</v>
+        <v>8.23752</v>
       </c>
       <c r="S31">
-        <f t="shared" si="0"/>
-        <v>965.25628287035329</v>
+        <f>(0.000000000000000138*G31/(1.673534E-24*1.3*0.000000066726*F31*1.8986E+30/(E31*7149200000)^2))/100000</f>
+        <v>99.730517672190274</v>
       </c>
       <c r="T31">
-        <f t="shared" si="1"/>
+        <f>IF(I31&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="6">
-        <v>1.4811235</v>
-      </c>
-      <c r="D32" s="6">
-        <v>3.4619999999999998E-2</v>
-      </c>
-      <c r="E32" s="6">
-        <v>1.891</v>
-      </c>
-      <c r="F32" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="G32" s="6">
-        <v>4050</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="6">
-        <v>10170</v>
-      </c>
-      <c r="J32" s="6">
-        <v>2.3620000000000001</v>
-      </c>
-      <c r="K32" s="6">
-        <v>2.52</v>
-      </c>
-      <c r="L32" s="6">
-        <v>-0.03</v>
-      </c>
-      <c r="M32" s="6">
-        <v>4.093</v>
-      </c>
-      <c r="N32" s="6">
-        <v>307.85989979999999</v>
-      </c>
-      <c r="O32" s="6">
-        <v>39.9389161</v>
-      </c>
-      <c r="P32" s="6">
-        <v>204.45500000000001</v>
-      </c>
-      <c r="Q32" s="6">
-        <v>7.55</v>
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32">
+        <v>2.7033900000000002</v>
+      </c>
+      <c r="D32">
+        <v>4.1230000000000003E-2</v>
+      </c>
+      <c r="E32">
+        <v>1.56</v>
+      </c>
+      <c r="F32">
+        <v>1.94</v>
+      </c>
+      <c r="G32">
+        <v>1816</v>
+      </c>
+      <c r="I32">
+        <v>6304</v>
+      </c>
+      <c r="J32">
+        <v>1.7</v>
+      </c>
+      <c r="K32">
+        <v>1.96</v>
+      </c>
+      <c r="L32">
+        <v>0.05</v>
+      </c>
+      <c r="M32">
+        <v>4.2</v>
+      </c>
+      <c r="N32">
+        <v>148.6431193</v>
+      </c>
+      <c r="O32">
+        <v>40.387944599999997</v>
+      </c>
+      <c r="P32">
+        <v>210.25200000000001</v>
+      </c>
+      <c r="Q32">
+        <v>9.8160000000000007</v>
       </c>
       <c r="R32" s="9">
-        <v>7.5767499999999997</v>
-      </c>
-      <c r="S32" s="6">
-        <f t="shared" si="0"/>
-        <v>1286.8653667451285</v>
-      </c>
-      <c r="T32" s="6">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-      <c r="U32" s="7" t="s">
-        <v>138</v>
+        <v>9.7632399999999997</v>
+      </c>
+      <c r="S32">
+        <f>(0.000000000000000138*G32/(1.673534E-24*1.3*0.000000066726*F32*1.8986E+30/(E32*7149200000)^2))/100000</f>
+        <v>582.97620763372299</v>
+      </c>
+      <c r="T32">
+        <f>IF(I32&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
         <v>20</v>
       </c>
       <c r="C33">
-        <v>1.7635879999999999</v>
+        <v>2.9895931999999998</v>
       </c>
       <c r="D33">
-        <v>3.6409999999999998E-2</v>
+        <v>4.317E-2</v>
       </c>
       <c r="E33">
-        <v>1.512</v>
+        <v>1.6990000000000001</v>
       </c>
       <c r="F33">
-        <v>9.2799999999999994</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="G33">
-        <v>2550</v>
+        <v>1823</v>
+      </c>
+      <c r="H33" t="s">
+        <v>56</v>
       </c>
       <c r="I33">
-        <v>7650</v>
+        <v>6206</v>
       </c>
       <c r="J33">
-        <v>1.74</v>
+        <v>1.603</v>
       </c>
       <c r="K33">
-        <v>1.72</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="L33">
-        <v>0.2</v>
+        <v>-0.11600000000000001</v>
       </c>
       <c r="M33">
-        <v>4.2</v>
+        <v>4.1079999999999997</v>
       </c>
       <c r="N33">
-        <v>286.97138760000001</v>
+        <v>157.06262000000001</v>
       </c>
       <c r="O33">
-        <v>46.868246300000003</v>
+        <v>25.573136600000002</v>
       </c>
       <c r="P33">
-        <v>519.096</v>
+        <v>218.05</v>
       </c>
       <c r="Q33">
-        <v>9.7910000000000004</v>
+        <v>9.98</v>
       </c>
       <c r="R33" s="9">
-        <v>10.367800000000001</v>
+        <v>9.95702</v>
       </c>
       <c r="S33">
-        <f t="shared" si="0"/>
-        <v>160.76196513632402</v>
+        <f>(0.000000000000000138*G33/(1.673534E-24*1.3*0.000000066726*F33*1.8986E+30/(E33*7149200000)^2))/100000</f>
+        <v>1492.9814393090719</v>
       </c>
       <c r="T33">
-        <f t="shared" si="1"/>
-        <v>-7</v>
+        <f>IF(I33&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34">
+        <v>2.7347700000000001</v>
+      </c>
+      <c r="D34">
+        <v>4.4150000000000002E-2</v>
+      </c>
+      <c r="E34">
+        <v>1.6</v>
+      </c>
+      <c r="F34">
+        <v>1.39</v>
+      </c>
+      <c r="G34">
+        <v>2048</v>
+      </c>
+      <c r="H34" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34">
+        <v>6768</v>
+      </c>
+      <c r="J34">
+        <v>1.81</v>
+      </c>
+      <c r="K34">
+        <v>1.76</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>4.5</v>
+      </c>
+      <c r="N34">
+        <v>78.295591200000004</v>
+      </c>
+      <c r="O34">
+        <v>33.317953199999998</v>
+      </c>
+      <c r="P34">
+        <v>136.68100000000001</v>
+      </c>
+      <c r="Q34">
+        <v>8.56</v>
+      </c>
+      <c r="R34" s="9">
+        <v>8.4517299999999995</v>
+      </c>
+      <c r="S34">
+        <f>(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
+        <v>965.25628287035329</v>
+      </c>
+      <c r="T34">
+        <f>IF(I34&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1.4811235</v>
+      </c>
+      <c r="D35" s="6">
+        <v>3.4619999999999998E-2</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1.891</v>
+      </c>
+      <c r="F35" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="G35" s="6">
+        <v>4050</v>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
+      <c r="U35" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" s="11"/>
+      <c r="I36" s="17">
+        <v>7433.197265625</v>
+      </c>
+      <c r="J36" s="17"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17">
+        <v>286.97138676797078</v>
+      </c>
+      <c r="O36" s="17">
+        <v>46.868244058307063</v>
+      </c>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="17">
+        <v>10.382340431213381</v>
+      </c>
+      <c r="R36" s="17">
+        <v>10.382340431213381</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37">
+        <v>1.7635879999999999</v>
+      </c>
+      <c r="D37">
+        <v>3.6409999999999998E-2</v>
+      </c>
+      <c r="E37">
+        <v>1.512</v>
+      </c>
+      <c r="F37">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="G37">
+        <v>2550</v>
+      </c>
+      <c r="I37">
+        <v>7650</v>
+      </c>
+      <c r="J37">
+        <v>1.74</v>
+      </c>
+      <c r="K37">
+        <v>1.72</v>
+      </c>
+      <c r="L37">
+        <v>0.2</v>
+      </c>
+      <c r="M37">
+        <v>4.2</v>
+      </c>
+      <c r="N37">
+        <v>286.97138760000001</v>
+      </c>
+      <c r="O37">
+        <v>46.868246300000003</v>
+      </c>
+      <c r="P37">
+        <v>519.096</v>
+      </c>
+      <c r="Q37">
+        <v>9.7910000000000004</v>
+      </c>
+      <c r="R37" s="9">
+        <v>10.367800000000001</v>
+      </c>
+      <c r="S37">
+        <f>(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
+        <v>160.76196513632402</v>
+      </c>
+      <c r="T37">
+        <f>IF(I37&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38">
+        <v>0.79205199999999998</v>
+      </c>
+      <c r="D38">
+        <v>1.6789999999999999E-2</v>
+      </c>
+      <c r="E38">
+        <v>0.42109020000000003</v>
+      </c>
+      <c r="F38">
+        <v>9.2250570000000004E-2</v>
+      </c>
+      <c r="G38">
+        <v>1978</v>
+      </c>
+      <c r="H38" t="s">
         <v>99</v>
       </c>
-      <c r="B34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34">
-        <v>0.79205199999999998</v>
-      </c>
-      <c r="D34">
-        <v>1.6789999999999999E-2</v>
-      </c>
-      <c r="E34">
-        <v>0.42109020000000003</v>
-      </c>
-      <c r="F34">
-        <v>9.2250570000000004E-2</v>
-      </c>
-      <c r="G34">
-        <v>1978</v>
-      </c>
-      <c r="H34" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34">
+      <c r="I38">
         <v>5443</v>
       </c>
-      <c r="J34">
+      <c r="J38">
         <v>0.94899999999999995</v>
       </c>
-      <c r="K34">
+      <c r="K38">
         <v>1.02</v>
       </c>
-      <c r="L34">
+      <c r="L38">
         <v>0.27</v>
       </c>
-      <c r="M34">
+      <c r="M38">
         <v>4.3499999999999996</v>
       </c>
-      <c r="N34">
+      <c r="N38">
         <v>358.6688767</v>
       </c>
-      <c r="O34">
+      <c r="O38">
         <v>-37.628223699999999</v>
       </c>
-      <c r="P34">
+      <c r="P38">
         <v>80.437299999999993</v>
       </c>
-      <c r="Q34">
+      <c r="Q38">
         <v>9.7899999999999991</v>
       </c>
-      <c r="R34" s="9">
+      <c r="R38" s="9">
         <v>9.6000599999999991</v>
       </c>
-      <c r="S34">
-        <f t="shared" ref="S34:S59" si="2">(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
+      <c r="S38">
+        <f>(0.000000000000000138*G38/(1.673534E-24*1.3*0.000000066726*F38*1.8986E+30/(E38*7149200000)^2))/100000</f>
         <v>972.96006983022733</v>
       </c>
-      <c r="T34">
-        <f t="shared" ref="T34:T65" si="3">IF(I34&gt;6800,-7,-5)</f>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35">
-        <v>2.1487738099999998</v>
-      </c>
-      <c r="D35">
-        <v>4.0351999999999999E-2</v>
-      </c>
-      <c r="E35">
-        <v>1.597</v>
-      </c>
-      <c r="F35">
-        <v>3.7</v>
-      </c>
-      <c r="G35">
-        <v>2594.3000000000002</v>
-      </c>
-      <c r="H35" t="s">
-        <v>50</v>
-      </c>
-      <c r="I35">
-        <v>7490</v>
-      </c>
-      <c r="J35">
-        <v>2.0819999999999999</v>
-      </c>
-      <c r="K35">
-        <v>1.9</v>
-      </c>
-      <c r="L35">
-        <v>0.15</v>
-      </c>
-      <c r="M35">
-        <v>4.1050000000000004</v>
-      </c>
-      <c r="N35">
-        <v>317.5515264</v>
-      </c>
-      <c r="O35">
-        <v>10.7388967</v>
-      </c>
-      <c r="P35">
-        <v>182.273</v>
-      </c>
-      <c r="Q35">
-        <v>8.2799999999999994</v>
-      </c>
-      <c r="R35" s="9">
-        <v>8.2424300000000006</v>
-      </c>
-      <c r="S35">
-        <f t="shared" si="2"/>
-        <v>457.63140850776114</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="3"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36">
-        <v>2.8240932000000001</v>
-      </c>
-      <c r="D36">
-        <v>4.7399999999999998E-2</v>
-      </c>
-      <c r="E36">
-        <v>1.5149999999999999</v>
-      </c>
-      <c r="F36">
-        <v>1.675</v>
-      </c>
-      <c r="G36">
-        <v>2250</v>
-      </c>
-      <c r="H36" t="s">
-        <v>48</v>
-      </c>
-      <c r="I36">
-        <v>7800</v>
-      </c>
-      <c r="J36">
-        <v>1.79</v>
-      </c>
-      <c r="K36">
-        <v>1.75</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="N36">
-        <v>147.5800667</v>
-      </c>
-      <c r="O36">
-        <v>-66.113925300000005</v>
-      </c>
-      <c r="P36">
-        <v>170.696</v>
-      </c>
-      <c r="Q36">
-        <v>8.1910000000000007</v>
-      </c>
-      <c r="R36" s="9">
-        <v>8.1740100000000009</v>
-      </c>
-      <c r="S36">
-        <f t="shared" si="2"/>
-        <v>789.006338593706</v>
-      </c>
-      <c r="T36">
-        <f t="shared" si="3"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="6">
-        <v>16.249210000000001</v>
-      </c>
-      <c r="D37" s="6">
-        <v>0.12909999999999999</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1.087</v>
-      </c>
-      <c r="F37" s="6">
-        <v>4.34</v>
-      </c>
-      <c r="G37" s="6">
-        <v>805.5</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="6">
-        <v>5756</v>
-      </c>
-      <c r="J37" s="6">
-        <v>1.0860000000000001</v>
-      </c>
-      <c r="K37" s="6">
-        <v>1.0820000000000001</v>
-      </c>
-      <c r="L37" s="6">
-        <v>0.318</v>
-      </c>
-      <c r="M37" s="6">
-        <v>4.4020000000000001</v>
-      </c>
-      <c r="N37" s="6">
-        <v>310.29170019999998</v>
-      </c>
-      <c r="O37" s="6">
-        <v>3.6382967000000002</v>
-      </c>
-      <c r="P37" s="6">
-        <v>93.734499999999997</v>
-      </c>
-      <c r="Q37" s="6">
-        <v>9.48</v>
-      </c>
-      <c r="R37" s="9">
-        <v>9.4290710000000004</v>
-      </c>
-      <c r="S37" s="6">
-        <f t="shared" si="2"/>
-        <v>56.120615203365361</v>
-      </c>
-      <c r="T37" s="6">
-        <f t="shared" si="3"/>
-        <v>-5</v>
-      </c>
-      <c r="U37" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38">
-        <v>8.0277282999999997</v>
-      </c>
-      <c r="D38">
-        <v>8.2337403000000003E-2</v>
-      </c>
-      <c r="E38">
-        <v>0.83243188000000001</v>
-      </c>
-      <c r="F38">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="G38">
-        <v>1074.28</v>
-      </c>
-      <c r="H38" t="s">
-        <v>44</v>
-      </c>
-      <c r="I38">
-        <v>5962.7</v>
-      </c>
-      <c r="J38">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="K38">
-        <v>1.156039</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>4.38</v>
-      </c>
-      <c r="N38">
-        <v>193.3963704</v>
-      </c>
-      <c r="O38">
-        <v>85.129495199999994</v>
-      </c>
-      <c r="P38">
-        <v>114.048</v>
-      </c>
-      <c r="Q38">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="R38" s="9">
-        <v>9.4135299999999997</v>
-      </c>
-      <c r="S38">
-        <f t="shared" si="2"/>
-        <v>1175.9460676296278</v>
-      </c>
       <c r="T38">
-        <f t="shared" si="3"/>
+        <f>IF(I38&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
         <v>20</v>
       </c>
       <c r="C39">
-        <v>12.5199</v>
+        <v>2.1487738099999998</v>
       </c>
       <c r="D39">
-        <v>0.1062</v>
+        <v>4.0351999999999999E-2</v>
       </c>
       <c r="E39">
-        <v>0.41279399999999999</v>
+        <v>1.597</v>
       </c>
       <c r="F39">
-        <v>2.627204E-2</v>
+        <v>3.7</v>
       </c>
       <c r="G39">
-        <v>843</v>
+        <v>2594.3000000000002</v>
+      </c>
+      <c r="H39" t="s">
+        <v>49</v>
       </c>
       <c r="I39">
-        <v>5770</v>
+        <v>7490</v>
       </c>
       <c r="J39">
-        <v>0.96799999999999997</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="K39">
-        <v>1.022</v>
+        <v>1.9</v>
       </c>
       <c r="L39">
-        <v>7.0000000000000007E-2</v>
+        <v>0.15</v>
       </c>
       <c r="M39">
-        <v>4.47</v>
+        <v>4.1050000000000004</v>
       </c>
       <c r="N39">
-        <v>192.1848981</v>
+        <v>317.5515264</v>
       </c>
       <c r="O39">
-        <v>64.855275500000005</v>
+        <v>10.7388967</v>
       </c>
       <c r="P39">
-        <v>84.536199999999994</v>
+        <v>182.273</v>
       </c>
       <c r="Q39">
-        <v>9.5340000000000007</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="R39" s="9">
-        <v>9.3678899999999992</v>
+        <v>8.2424300000000006</v>
       </c>
       <c r="S39">
-        <f t="shared" si="2"/>
-        <v>1399.2265914107247</v>
+        <f>(0.000000000000000138*G39/(1.673534E-24*1.3*0.000000066726*F39*1.8986E+30/(E39*7149200000)^2))/100000</f>
+        <v>457.63140850776114</v>
       </c>
       <c r="T39">
-        <f t="shared" si="3"/>
-        <v>-5</v>
+        <f>IF(I39&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
         <v>20</v>
       </c>
       <c r="C40">
-        <v>4.7202190000000002</v>
+        <v>2.8240932000000001</v>
       </c>
       <c r="D40">
-        <v>6.2600000000000003E-2</v>
+        <v>4.7399999999999998E-2</v>
       </c>
       <c r="E40">
-        <v>1.3959999999999999</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="F40">
-        <v>2.37</v>
+        <v>1.675</v>
       </c>
       <c r="G40">
-        <v>1679</v>
+        <v>2250</v>
+      </c>
+      <c r="H40" t="s">
+        <v>47</v>
       </c>
       <c r="I40">
-        <v>6274</v>
+        <v>7800</v>
       </c>
       <c r="J40">
-        <v>1.925</v>
+        <v>1.79</v>
       </c>
       <c r="K40">
-        <v>1.464</v>
+        <v>1.75</v>
       </c>
       <c r="L40">
-        <v>0.11899999999999999</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>4.0339999999999998</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N40">
-        <v>325.01453629999997</v>
+        <v>147.5800667</v>
       </c>
       <c r="O40">
-        <v>48.4067674</v>
+        <v>-66.113925300000005</v>
       </c>
       <c r="P40">
-        <v>200.49199999999999</v>
+        <v>170.696</v>
       </c>
       <c r="Q40">
-        <v>9.4380000000000006</v>
+        <v>8.1910000000000007</v>
       </c>
       <c r="R40" s="9">
-        <v>9.3503900000000009</v>
+        <v>8.1740100000000009</v>
       </c>
       <c r="S40">
-        <f t="shared" si="2"/>
-        <v>353.31388599481477</v>
+        <f>(0.000000000000000138*G40/(1.673534E-24*1.3*0.000000066726*F40*1.8986E+30/(E40*7149200000)^2))/100000</f>
+        <v>789.006338593706</v>
       </c>
       <c r="T40">
-        <f t="shared" si="3"/>
+        <f>IF(I40&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="6">
+        <v>16.249210000000001</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.12909999999999999</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1.087</v>
+      </c>
+      <c r="F41" s="6">
+        <v>4.34</v>
+      </c>
+      <c r="G41" s="6">
+        <v>805.5</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="6">
+        <v>5756</v>
+      </c>
+      <c r="J41" s="6">
+        <v>1.0860000000000001</v>
+      </c>
+      <c r="K41" s="6">
+        <v>1.0820000000000001</v>
+      </c>
+      <c r="L41" s="6">
+        <v>0.318</v>
+      </c>
+      <c r="M41" s="6">
+        <v>4.4020000000000001</v>
+      </c>
+      <c r="N41" s="6">
+        <v>310.29170019999998</v>
+      </c>
+      <c r="O41" s="6">
+        <v>3.6382967000000002</v>
+      </c>
+      <c r="P41" s="6">
+        <v>93.734499999999997</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>9.48</v>
+      </c>
+      <c r="R41" s="9">
+        <v>9.4290710000000004</v>
+      </c>
+      <c r="S41" s="6">
+        <f>(0.000000000000000138*G41/(1.673534E-24*1.3*0.000000066726*F41*1.8986E+30/(E41*7149200000)^2))/100000</f>
+        <v>56.120615203365361</v>
+      </c>
+      <c r="T41" s="6">
+        <f>IF(I41&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41">
-        <v>4.4258699999999997</v>
-      </c>
-      <c r="D41">
-        <v>5.7779999999999998E-2</v>
-      </c>
-      <c r="E41">
-        <v>2.2303544500000001</v>
-      </c>
-      <c r="F41">
-        <v>1.86578665</v>
-      </c>
-      <c r="G41">
-        <v>1293</v>
-      </c>
-      <c r="H41" t="s">
-        <v>71</v>
-      </c>
-      <c r="I41">
-        <v>6117</v>
-      </c>
-      <c r="J41">
-        <v>1.53</v>
-      </c>
-      <c r="K41">
-        <v>1.3120000000000001</v>
-      </c>
-      <c r="L41">
-        <v>0.25</v>
-      </c>
-      <c r="M41">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="N41">
-        <v>313.5110469</v>
-      </c>
-      <c r="O41">
-        <v>72.580645500000003</v>
-      </c>
-      <c r="P41">
-        <v>139.48400000000001</v>
-      </c>
-      <c r="Q41">
-        <v>9.2700010000000006</v>
-      </c>
-      <c r="R41" s="9">
-        <v>9.1879500000000007</v>
-      </c>
-      <c r="S41">
-        <f t="shared" si="2"/>
-        <v>882.20971786077962</v>
-      </c>
-      <c r="T41">
-        <f t="shared" si="3"/>
+      <c r="U41" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42">
+        <v>8.0277282999999997</v>
+      </c>
+      <c r="D42">
+        <v>8.2337403000000003E-2</v>
+      </c>
+      <c r="E42">
+        <v>0.83243188000000001</v>
+      </c>
+      <c r="F42">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="G42">
+        <v>1074.28</v>
+      </c>
+      <c r="H42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42">
+        <v>5962.7</v>
+      </c>
+      <c r="J42">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K42">
+        <v>1.156039</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>4.38</v>
+      </c>
+      <c r="N42">
+        <v>193.3963704</v>
+      </c>
+      <c r="O42">
+        <v>85.129495199999994</v>
+      </c>
+      <c r="P42">
+        <v>114.048</v>
+      </c>
+      <c r="Q42">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="R42" s="9">
+        <v>9.4135299999999997</v>
+      </c>
+      <c r="S42">
+        <f>(0.000000000000000138*G42/(1.673534E-24*1.3*0.000000066726*F42*1.8986E+30/(E42*7149200000)^2))/100000</f>
+        <v>1175.9460676296278</v>
+      </c>
+      <c r="T42">
+        <f>IF(I42&gt;6800,-7,-5)</f>
         <v>-5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42">
-        <v>2.6502370000000002</v>
-      </c>
-      <c r="D42">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="E42">
-        <v>1.49</v>
-      </c>
-      <c r="F42">
-        <v>3.12</v>
-      </c>
-      <c r="G42">
-        <v>2370</v>
-      </c>
-      <c r="H42" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42">
-        <v>7690</v>
-      </c>
-      <c r="J42">
-        <v>1.92</v>
-      </c>
-      <c r="K42">
-        <v>1.9</v>
-      </c>
-      <c r="L42">
-        <v>0.09</v>
-      </c>
-      <c r="M42">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="N42">
-        <v>316.20369219999998</v>
-      </c>
-      <c r="O42">
-        <v>55.588022100000003</v>
-      </c>
-      <c r="P42">
-        <v>148.92500000000001</v>
-      </c>
-      <c r="Q42">
-        <v>8.0299999999999994</v>
-      </c>
-      <c r="R42" s="9">
-        <v>7.9756099999999996</v>
-      </c>
-      <c r="S42">
-        <f t="shared" si="2"/>
-        <v>431.57254486096394</v>
-      </c>
-      <c r="T42">
-        <f t="shared" si="3"/>
-        <v>-7</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
       </c>
       <c r="C43">
-        <v>1.902603</v>
+        <v>12.5199</v>
       </c>
       <c r="D43">
-        <v>3.8899999999999997E-2</v>
+        <v>0.1062</v>
       </c>
       <c r="E43">
-        <v>1.875</v>
+        <v>0.41279399999999999</v>
       </c>
       <c r="F43">
-        <v>2.2999999999999998</v>
+        <v>2.627204E-2</v>
       </c>
       <c r="G43">
-        <v>2492</v>
-      </c>
-      <c r="H43" t="s">
-        <v>62</v>
+        <v>843</v>
       </c>
       <c r="I43">
-        <v>7300</v>
+        <v>5770</v>
       </c>
       <c r="J43">
-        <v>1.95</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="K43">
-        <v>1.79</v>
+        <v>1.022</v>
       </c>
       <c r="L43">
-        <v>-0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M43">
-        <v>4.0999999999999996</v>
+        <v>4.47</v>
       </c>
       <c r="N43">
-        <v>352.26752069999998</v>
+        <v>192.1848981</v>
       </c>
       <c r="O43">
-        <v>67.034806200000006</v>
+        <v>64.855275500000005</v>
       </c>
       <c r="P43">
-        <v>225.88800000000001</v>
+        <v>84.536199999999994</v>
       </c>
       <c r="Q43">
-        <v>8.952</v>
+        <v>9.5340000000000007</v>
       </c>
       <c r="R43" s="9">
-        <v>8.8952899999999993</v>
+        <v>9.3678899999999992</v>
       </c>
       <c r="S43">
-        <f t="shared" si="2"/>
-        <v>974.78820571370204</v>
+        <f>(0.000000000000000138*G43/(1.673534E-24*1.3*0.000000066726*F43*1.8986E+30/(E43*7149200000)^2))/100000</f>
+        <v>1399.2265914107247</v>
       </c>
       <c r="T43">
-        <f t="shared" si="3"/>
-        <v>-7</v>
+        <f>IF(I43&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
       </c>
       <c r="C44">
-        <v>3.2086640000000002</v>
+        <v>4.7202190000000002</v>
       </c>
       <c r="D44">
-        <v>4.8820000000000002E-2</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="E44">
-        <v>1.44</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="F44">
-        <v>0.7</v>
+        <v>2.37</v>
       </c>
       <c r="G44">
-        <v>1927</v>
-      </c>
-      <c r="H44" t="s">
-        <v>57</v>
+        <v>1679</v>
       </c>
       <c r="I44">
-        <v>5991</v>
+        <v>6274</v>
       </c>
       <c r="J44">
-        <v>2.1680000000000001</v>
+        <v>1.925</v>
       </c>
       <c r="K44">
-        <v>1.5069999999999999</v>
+        <v>1.464</v>
       </c>
       <c r="L44">
-        <v>0.373</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M44">
-        <v>3.9430000000000001</v>
+        <v>4.0339999999999998</v>
       </c>
       <c r="N44">
-        <v>142.74340599999999</v>
+        <v>325.01453629999997</v>
       </c>
       <c r="O44">
-        <v>26.539995099999999</v>
+        <v>48.4067674</v>
       </c>
       <c r="P44">
-        <v>229.06700000000001</v>
+        <v>200.49199999999999</v>
       </c>
       <c r="Q44">
-        <v>9.7210000000000001</v>
+        <v>9.4380000000000006</v>
       </c>
       <c r="R44" s="9">
-        <v>9.5843900000000009</v>
+        <v>9.3503900000000009</v>
       </c>
       <c r="S44">
-        <f t="shared" si="2"/>
-        <v>1460.8182255852041</v>
+        <f>(0.000000000000000138*G44/(1.673534E-24*1.3*0.000000066726*F44*1.8986E+30/(E44*7149200000)^2))/100000</f>
+        <v>353.31388599481477</v>
       </c>
       <c r="T44">
-        <f t="shared" si="3"/>
+        <f>IF(I44&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
       </c>
       <c r="C45">
-        <v>9.5739181000000002</v>
+        <v>4.4258699999999997</v>
       </c>
       <c r="D45">
-        <v>0.1</v>
+        <v>5.7779999999999998E-2</v>
       </c>
       <c r="E45">
-        <v>1.10166148</v>
+        <v>2.2303544500000001</v>
       </c>
       <c r="F45">
-        <v>0.28128386</v>
+        <v>1.86578665</v>
       </c>
       <c r="G45">
-        <v>1199.55</v>
+        <v>1293</v>
+      </c>
+      <c r="H45" t="s">
+        <v>70</v>
       </c>
       <c r="I45">
-        <v>6039</v>
+        <v>6117</v>
       </c>
       <c r="J45">
-        <v>2.032</v>
+        <v>1.53</v>
       </c>
       <c r="K45">
-        <v>1.4642999999999999</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="L45">
-        <v>0.33200000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="M45">
-        <v>3.9860000000000002</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N45">
-        <v>201.9626552</v>
+        <v>313.5110469</v>
       </c>
       <c r="O45">
-        <v>9.0306437000000006</v>
+        <v>72.580645500000003</v>
       </c>
       <c r="P45">
-        <v>223.465</v>
+        <v>139.48400000000001</v>
       </c>
       <c r="Q45">
-        <v>9.8149999999999995</v>
+        <v>9.2700010000000006</v>
       </c>
       <c r="R45" s="9">
-        <v>9.6598100000000002</v>
+        <v>9.1879500000000007</v>
       </c>
       <c r="S45">
-        <f t="shared" si="2"/>
-        <v>1324.5165539963698</v>
+        <f>(0.000000000000000138*G45/(1.673534E-24*1.3*0.000000066726*F45*1.8986E+30/(E45*7149200000)^2))/100000</f>
+        <v>882.20971786077962</v>
       </c>
       <c r="T45">
-        <f t="shared" si="3"/>
+        <f>IF(I45&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
       </c>
       <c r="C46">
-        <v>17.305904000000002</v>
+        <v>2.6502370000000002</v>
       </c>
       <c r="D46">
-        <v>0.16</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="E46">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="F46">
-        <v>6.4</v>
+        <v>3.12</v>
       </c>
       <c r="G46">
-        <v>1221.3900000000001</v>
+        <v>2370</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
       </c>
       <c r="I46">
-        <v>7130</v>
+        <v>7690</v>
       </c>
       <c r="J46">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="K46">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M46">
-        <v>3.9460000000000002</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="N46">
-        <v>164.031654</v>
+        <v>316.20369219999998</v>
       </c>
       <c r="O46">
-        <v>-43.376696699999997</v>
+        <v>55.588022100000003</v>
       </c>
       <c r="P46">
-        <v>328.47500000000002</v>
+        <v>148.92500000000001</v>
       </c>
       <c r="Q46">
-        <v>9.8670000000000009</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="R46" s="9">
-        <v>9.7596699999999998</v>
+        <v>7.9756099999999996</v>
       </c>
       <c r="S46">
-        <f t="shared" si="2"/>
-        <v>55.915145726222889</v>
+        <f>(0.000000000000000138*G46/(1.673534E-24*1.3*0.000000066726*F46*1.8986E+30/(E46*7149200000)^2))/100000</f>
+        <v>431.57254486096394</v>
       </c>
       <c r="T46">
-        <f t="shared" si="3"/>
+        <f>IF(I46&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
       </c>
       <c r="C47">
-        <v>10.261127</v>
+        <v>1.902603</v>
       </c>
       <c r="D47">
-        <v>0.111</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="E47">
-        <v>1.1079506100000001</v>
+        <v>1.875</v>
       </c>
       <c r="F47">
-        <v>5.55960374</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G47">
-        <v>1363.43</v>
+        <v>2492</v>
+      </c>
+      <c r="H47" t="s">
+        <v>61</v>
       </c>
       <c r="I47">
-        <v>6200</v>
+        <v>7300</v>
       </c>
       <c r="J47">
-        <v>2.7505000000000002</v>
+        <v>1.95</v>
       </c>
       <c r="K47">
-        <v>1.7169000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="L47">
-        <v>0.28499999999999998</v>
+        <v>-0.1</v>
       </c>
       <c r="M47">
-        <v>3.7890000000000001</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N47">
-        <v>263.75807529999997</v>
+        <v>352.26752069999998</v>
       </c>
       <c r="O47">
-        <v>40.695042800000003</v>
+        <v>67.034806200000006</v>
       </c>
       <c r="P47">
-        <v>224.73099999999999</v>
+        <v>225.88800000000001</v>
       </c>
       <c r="Q47">
-        <v>9.07</v>
+        <v>8.952</v>
       </c>
       <c r="R47" s="9">
-        <v>8.9365100000000002</v>
+        <v>8.8952899999999993</v>
       </c>
       <c r="S47">
-        <f t="shared" si="2"/>
-        <v>77.040187113891676</v>
+        <f>(0.000000000000000138*G47/(1.673534E-24*1.3*0.000000066726*F47*1.8986E+30/(E47*7149200000)^2))/100000</f>
+        <v>974.78820571370204</v>
       </c>
       <c r="T47">
-        <f t="shared" si="3"/>
-        <v>-5</v>
+        <f>IF(I47&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
       </c>
       <c r="C48">
-        <v>10.655669</v>
+        <v>3.2086640000000002</v>
       </c>
       <c r="D48">
-        <v>0.1166</v>
+        <v>4.8820000000000002E-2</v>
       </c>
       <c r="E48">
-        <v>0.99399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="F48">
-        <v>4.82</v>
+        <v>0.7</v>
       </c>
       <c r="G48">
-        <v>1595</v>
+        <v>1927</v>
+      </c>
+      <c r="H48" t="s">
+        <v>56</v>
       </c>
       <c r="I48">
-        <v>7360</v>
+        <v>5991</v>
       </c>
       <c r="J48">
-        <v>2.36</v>
+        <v>2.1680000000000001</v>
       </c>
       <c r="K48">
-        <v>1.859</v>
+        <v>1.5069999999999999</v>
       </c>
       <c r="L48">
-        <v>9.4E-2</v>
+        <v>0.373</v>
       </c>
       <c r="M48">
-        <v>3.9620000000000002</v>
+        <v>3.9430000000000001</v>
       </c>
       <c r="N48">
-        <v>90.062587800000003</v>
+        <v>142.74340599999999</v>
       </c>
       <c r="O48">
-        <v>11.8840577</v>
+        <v>26.539995099999999</v>
       </c>
       <c r="P48">
-        <v>285.28899999999999</v>
+        <v>229.06700000000001</v>
       </c>
       <c r="Q48">
-        <v>9.5470000000000006</v>
+        <v>9.7210000000000001</v>
       </c>
       <c r="R48" s="9">
-        <v>9.4724400000000006</v>
+        <v>9.5843900000000009</v>
       </c>
       <c r="S48">
-        <f t="shared" si="2"/>
-        <v>83.670803141549356</v>
+        <f>(0.000000000000000138*G48/(1.673534E-24*1.3*0.000000066726*F48*1.8986E+30/(E48*7149200000)^2))/100000</f>
+        <v>1460.8182255852041</v>
       </c>
       <c r="T48">
-        <f t="shared" si="3"/>
-        <v>-7</v>
+        <f>IF(I48&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
       </c>
       <c r="C49">
-        <v>18.388179999999998</v>
+        <v>9.5739181000000002</v>
       </c>
       <c r="D49">
-        <v>0.15279999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="E49">
-        <v>0.63900000000000001</v>
+        <v>1.10166148</v>
       </c>
       <c r="F49">
-        <v>0.13800000000000001</v>
+        <v>0.28128386</v>
       </c>
       <c r="G49">
-        <v>1027</v>
+        <v>1199.55</v>
       </c>
       <c r="I49">
-        <v>6095</v>
+        <v>6039</v>
       </c>
       <c r="J49">
-        <v>1.867</v>
+        <v>2.032</v>
       </c>
       <c r="K49">
-        <v>1.407</v>
+        <v>1.4642999999999999</v>
       </c>
       <c r="L49">
-        <v>0.17499999999999999</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M49">
-        <v>4.0439999999999996</v>
+        <v>3.9860000000000002</v>
       </c>
       <c r="N49">
-        <v>47.517260800000003</v>
+        <v>201.9626552</v>
       </c>
       <c r="O49">
-        <v>-50.8322632</v>
+        <v>9.0306437000000006</v>
       </c>
       <c r="P49">
-        <v>76.902799999999999</v>
+        <v>223.465</v>
       </c>
       <c r="Q49">
-        <v>7.57</v>
+        <v>9.8149999999999995</v>
       </c>
       <c r="R49" s="9">
-        <v>7.4165299999999998</v>
+        <v>9.6598100000000002</v>
       </c>
       <c r="S49">
-        <f t="shared" si="2"/>
-        <v>777.64358420307099</v>
+        <f>(0.000000000000000138*G49/(1.673534E-24*1.3*0.000000066726*F49*1.8986E+30/(E49*7149200000)^2))/100000</f>
+        <v>1324.5165539963698</v>
       </c>
       <c r="T49">
-        <f t="shared" si="3"/>
+        <f>IF(I49&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
       </c>
       <c r="C50">
-        <v>16.067540999999999</v>
+        <v>17.305904000000002</v>
       </c>
       <c r="D50">
-        <v>0.11700000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E50">
-        <v>0.45410017000000003</v>
+        <v>1.07</v>
       </c>
       <c r="F50">
-        <v>4.4363560000000003E-2</v>
+        <v>6.4</v>
       </c>
       <c r="G50">
-        <v>635</v>
-      </c>
-      <c r="H50" t="s">
-        <v>117</v>
+        <v>1221.3900000000001</v>
       </c>
       <c r="I50">
-        <v>5291</v>
+        <v>7130</v>
       </c>
       <c r="J50">
-        <v>0.86599999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="K50">
-        <v>0.83299999999999996</v>
+        <v>1.59</v>
       </c>
       <c r="L50">
-        <v>-4.3999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>4.4800000000000004</v>
+        <v>3.9460000000000002</v>
       </c>
       <c r="N50">
-        <v>81.853282399999998</v>
+        <v>164.031654</v>
       </c>
       <c r="O50">
-        <v>-14.2767404</v>
+        <v>-43.376696699999997</v>
       </c>
       <c r="P50">
-        <v>74.796899999999994</v>
+        <v>328.47500000000002</v>
       </c>
       <c r="Q50">
-        <v>9.9309999999999992</v>
+        <v>9.8670000000000009</v>
       </c>
       <c r="R50" s="9">
-        <v>9.7777600000000007</v>
+        <v>9.7596699999999998</v>
       </c>
       <c r="S50">
-        <f t="shared" si="2"/>
-        <v>755.33252275944176</v>
+        <f>(0.000000000000000138*G50/(1.673534E-24*1.3*0.000000066726*F50*1.8986E+30/(E50*7149200000)^2))/100000</f>
+        <v>55.915145726222889</v>
       </c>
       <c r="T50">
-        <f t="shared" si="3"/>
-        <v>-5</v>
+        <f>IF(I50&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
       </c>
       <c r="C51">
-        <v>9.9558099999999996</v>
+        <v>10.261127</v>
       </c>
       <c r="D51">
-        <v>9.9400000000000002E-2</v>
+        <v>0.111</v>
       </c>
       <c r="E51">
-        <v>1.0580000000000001</v>
+        <v>1.1079506100000001</v>
       </c>
       <c r="F51">
-        <v>1.49</v>
+        <v>5.55960374</v>
       </c>
       <c r="G51">
-        <v>1655</v>
+        <v>1363.43</v>
       </c>
       <c r="I51">
-        <v>4896</v>
+        <v>6200</v>
       </c>
       <c r="J51">
-        <v>3.55</v>
+        <v>2.7505000000000002</v>
       </c>
       <c r="K51">
-        <v>1.31</v>
+        <v>1.7169000000000001</v>
       </c>
       <c r="L51">
-        <v>0.23</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M51">
-        <v>3.48</v>
+        <v>3.7890000000000001</v>
       </c>
       <c r="N51">
-        <v>184.97875790000001</v>
+        <v>263.75807529999997</v>
       </c>
       <c r="O51">
-        <v>-25.827853099999999</v>
+        <v>40.695042800000003</v>
       </c>
       <c r="P51">
-        <v>215.98599999999999</v>
+        <v>224.73099999999999</v>
       </c>
       <c r="Q51">
-        <v>9.9730000000000008</v>
+        <v>9.07</v>
       </c>
       <c r="R51" s="9">
-        <v>9.641</v>
+        <v>8.9365100000000002</v>
       </c>
       <c r="S51">
-        <f t="shared" si="2"/>
-        <v>318.17832033985127</v>
+        <f>(0.000000000000000138*G51/(1.673534E-24*1.3*0.000000066726*F51*1.8986E+30/(E51*7149200000)^2))/100000</f>
+        <v>77.040187113891676</v>
       </c>
       <c r="T51">
-        <f t="shared" si="3"/>
+        <f>IF(I51&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s">
         <v>20</v>
       </c>
       <c r="C52">
-        <v>7.2459899999999999</v>
+        <v>10.655669</v>
       </c>
       <c r="D52">
-        <v>8.8800000000000004E-2</v>
+        <v>0.1166</v>
       </c>
       <c r="E52">
-        <v>1.042</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F52">
-        <v>12.89</v>
+        <v>4.82</v>
       </c>
       <c r="G52">
-        <v>1677</v>
-      </c>
-      <c r="H52" t="s">
-        <v>57</v>
+        <v>1595</v>
       </c>
       <c r="I52">
-        <v>6264</v>
+        <v>7360</v>
       </c>
       <c r="J52">
-        <v>2.738</v>
+        <v>2.36</v>
       </c>
       <c r="K52">
-        <v>1.7649999999999999</v>
+        <v>1.859</v>
       </c>
       <c r="L52">
-        <v>0.34200000000000003</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M52">
-        <v>3.81</v>
+        <v>3.9620000000000002</v>
       </c>
       <c r="N52">
-        <v>83.865928800000006</v>
+        <v>90.062587800000003</v>
       </c>
       <c r="O52">
-        <v>21.294241700000001</v>
+        <v>11.8840577</v>
       </c>
       <c r="P52">
-        <v>225.643</v>
+        <v>285.28899999999999</v>
       </c>
       <c r="Q52">
-        <v>9.24</v>
+        <v>9.5470000000000006</v>
       </c>
       <c r="R52" s="9">
-        <v>9.0746900000000004</v>
+        <v>9.4724400000000006</v>
       </c>
       <c r="S52">
-        <f t="shared" si="2"/>
-        <v>36.149567272802649</v>
+        <f>(0.000000000000000138*G52/(1.673534E-24*1.3*0.000000066726*F52*1.8986E+30/(E52*7149200000)^2))/100000</f>
+        <v>83.670803141549356</v>
       </c>
       <c r="T52">
-        <f t="shared" si="3"/>
-        <v>-5</v>
+        <f>IF(I52&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
         <v>20</v>
       </c>
       <c r="C53">
-        <v>10.331110000000001</v>
+        <v>18.388179999999998</v>
       </c>
       <c r="D53">
-        <v>9.7000000000000003E-2</v>
+        <v>0.15279999999999999</v>
       </c>
       <c r="E53">
-        <v>0.99</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F53">
-        <v>1.53</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="G53">
-        <v>1370</v>
-      </c>
-      <c r="H53" t="s">
-        <v>121</v>
+        <v>1027</v>
       </c>
       <c r="I53">
-        <v>5735</v>
+        <v>6095</v>
       </c>
       <c r="J53">
-        <v>1.66</v>
+        <v>1.867</v>
       </c>
       <c r="K53">
-        <v>1.1399999999999999</v>
+        <v>1.407</v>
       </c>
       <c r="L53">
-        <v>0.26</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M53">
-        <v>4.0599999999999996</v>
+        <v>4.0439999999999996</v>
       </c>
       <c r="N53">
-        <v>110.5126861</v>
+        <v>47.517260800000003</v>
       </c>
       <c r="O53">
-        <v>-57.384998000000003</v>
+        <v>-50.8322632</v>
       </c>
       <c r="P53">
-        <v>179.36600000000001</v>
+        <v>76.902799999999999</v>
       </c>
       <c r="Q53">
-        <v>9.9719999999999995</v>
+        <v>7.57</v>
       </c>
       <c r="R53" s="9">
-        <v>9.8465900000000008</v>
+        <v>7.4165299999999998</v>
       </c>
       <c r="S53">
-        <f t="shared" si="2"/>
-        <v>224.58825733889913</v>
+        <f>(0.000000000000000138*G53/(1.673534E-24*1.3*0.000000066726*F53*1.8986E+30/(E53*7149200000)^2))/100000</f>
+        <v>777.64358420307099</v>
       </c>
       <c r="T53">
-        <f t="shared" si="3"/>
+        <f>IF(I53&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
         <v>20</v>
       </c>
       <c r="C54">
-        <v>6.7535809999999996</v>
+        <v>16.067540999999999</v>
       </c>
       <c r="D54">
-        <v>7.2999999999999995E-2</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="E54">
-        <v>0.58881357999999995</v>
+        <v>0.45410017000000003</v>
       </c>
       <c r="F54">
-        <v>0.10068326</v>
+        <v>4.4363560000000003E-2</v>
       </c>
       <c r="G54">
-        <v>1180</v>
+        <v>635</v>
+      </c>
+      <c r="H54" t="s">
+        <v>116</v>
       </c>
       <c r="I54">
-        <v>5808</v>
+        <v>5291</v>
       </c>
       <c r="J54">
-        <v>1.29</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="K54">
-        <v>1.1000000000000001</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="L54">
-        <v>0.2</v>
+        <v>-4.3999999999999997E-2</v>
       </c>
       <c r="M54">
-        <v>4.26</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="N54">
-        <v>166.26950410000001</v>
+        <v>81.853282399999998</v>
       </c>
       <c r="O54">
-        <v>11.2464069</v>
+        <v>-14.2767404</v>
       </c>
       <c r="P54">
-        <v>130.91900000000001</v>
+        <v>74.796899999999994</v>
       </c>
       <c r="Q54">
-        <v>9.75</v>
+        <v>9.9309999999999992</v>
       </c>
       <c r="R54" s="9">
-        <v>9.6080000000000005</v>
+        <v>9.7777600000000007</v>
       </c>
       <c r="S54">
-        <f t="shared" si="2"/>
-        <v>1039.84328949877</v>
+        <f>(0.000000000000000138*G54/(1.673534E-24*1.3*0.000000066726*F54*1.8986E+30/(E54*7149200000)^2))/100000</f>
+        <v>755.33252275944176</v>
       </c>
       <c r="T54">
-        <f t="shared" si="3"/>
+        <f>IF(I54&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
         <v>20</v>
       </c>
       <c r="C55">
-        <v>10.590547000000001</v>
+        <v>9.9558099999999996</v>
       </c>
       <c r="D55">
-        <v>9.8000000000000004E-2</v>
+        <v>9.9400000000000002E-2</v>
       </c>
       <c r="E55">
-        <v>0.91890603000000004</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="F55">
-        <v>0.18469084999999999</v>
+        <v>1.49</v>
       </c>
       <c r="G55">
-        <v>947</v>
-      </c>
-      <c r="H55" t="s">
-        <v>131</v>
+        <v>1655</v>
       </c>
       <c r="I55">
-        <v>6000</v>
+        <v>4896</v>
       </c>
       <c r="J55">
-        <v>1.0509999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="K55">
-        <v>1.1459999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="L55">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="M55">
-        <v>4.4400000000000004</v>
+        <v>3.48</v>
       </c>
       <c r="N55">
-        <v>161.87955690000001</v>
+        <v>184.97875790000001</v>
       </c>
       <c r="O55">
-        <v>36.329434499999998</v>
+        <v>-25.827853099999999</v>
       </c>
       <c r="P55">
-        <v>130.85499999999999</v>
+        <v>215.98599999999999</v>
       </c>
       <c r="Q55">
-        <v>10.058999999999999</v>
+        <v>9.9730000000000008</v>
       </c>
       <c r="R55" s="9">
-        <v>9.9823299999999993</v>
+        <v>9.641</v>
       </c>
       <c r="S55">
-        <f t="shared" si="2"/>
-        <v>1107.9861243219782</v>
+        <f>(0.000000000000000138*G55/(1.673534E-24*1.3*0.000000066726*F55*1.8986E+30/(E55*7149200000)^2))/100000</f>
+        <v>318.17832033985127</v>
       </c>
       <c r="T55">
-        <f t="shared" si="3"/>
+        <f>IF(I55&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>5.8267310999999999</v>
+        <v>7.2459899999999999</v>
       </c>
       <c r="D56">
-        <v>6.9000000000000006E-2</v>
+        <v>8.8800000000000004E-2</v>
       </c>
       <c r="E56">
-        <v>0.57186287999999996</v>
+        <v>1.042</v>
       </c>
       <c r="F56">
-        <v>0.24698861999999999</v>
+        <v>12.89</v>
       </c>
       <c r="G56">
-        <v>1439</v>
+        <v>1677</v>
+      </c>
+      <c r="H56" t="s">
+        <v>56</v>
       </c>
       <c r="I56">
-        <v>6110</v>
+        <v>6264</v>
       </c>
       <c r="J56">
-        <v>1.6479999999999999</v>
+        <v>2.738</v>
       </c>
       <c r="K56">
-        <v>1.2909999999999999</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="L56">
-        <v>0.124</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="M56">
-        <v>4.1180000000000003</v>
+        <v>3.81</v>
       </c>
       <c r="N56">
-        <v>51.657269100000001</v>
+        <v>83.865928800000006</v>
       </c>
       <c r="O56">
-        <v>40.817270399999998</v>
+        <v>21.294241700000001</v>
       </c>
       <c r="P56">
-        <v>179.14699999999999</v>
+        <v>225.643</v>
       </c>
       <c r="Q56">
-        <v>9.9130000000000003</v>
+        <v>9.24</v>
       </c>
       <c r="R56" s="9">
-        <v>9.7295700000000007</v>
+        <v>9.0746900000000004</v>
       </c>
       <c r="S56">
-        <f t="shared" si="2"/>
-        <v>487.59044264912109</v>
+        <f>(0.000000000000000138*G56/(1.673534E-24*1.3*0.000000066726*F56*1.8986E+30/(E56*7149200000)^2))/100000</f>
+        <v>36.149567272802649</v>
       </c>
       <c r="T56">
-        <f t="shared" si="3"/>
+        <f>IF(I56&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57">
-        <v>6.4025129999999999</v>
+        <v>10.331110000000001</v>
       </c>
       <c r="D57">
-        <v>7.0800000000000002E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="E57">
-        <v>0.82399999999999995</v>
+        <v>0.99</v>
       </c>
       <c r="F57">
-        <v>0.30299999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="G57">
-        <v>1388</v>
+        <v>1370</v>
       </c>
       <c r="H57" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="I57">
-        <v>6400</v>
+        <v>5735</v>
       </c>
       <c r="J57">
-        <v>1.415</v>
+        <v>1.66</v>
       </c>
       <c r="K57">
-        <v>1.3129999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L57">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="M57">
-        <v>4.2</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="N57">
-        <v>125.3050544</v>
+        <v>110.5126861</v>
       </c>
       <c r="O57">
-        <v>-46.484295899999999</v>
+        <v>-57.384998000000003</v>
       </c>
       <c r="P57">
-        <v>123.297</v>
+        <v>179.36600000000001</v>
       </c>
       <c r="Q57">
-        <v>8.9949999999999992</v>
+        <v>9.9719999999999995</v>
       </c>
       <c r="R57" s="9">
-        <v>8.8910300000000007</v>
+        <v>9.8465900000000008</v>
       </c>
       <c r="S57">
-        <f t="shared" si="2"/>
-        <v>795.95548671567838</v>
+        <f>(0.000000000000000138*G57/(1.673534E-24*1.3*0.000000066726*F57*1.8986E+30/(E57*7149200000)^2))/100000</f>
+        <v>224.58825733889913</v>
       </c>
       <c r="T57">
-        <f t="shared" si="3"/>
+        <f>IF(I57&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B58" t="s">
         <v>20</v>
       </c>
       <c r="C58">
-        <v>11.236598499999999</v>
+        <v>6.7535809999999996</v>
       </c>
       <c r="D58">
-        <v>0.1041</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E58">
-        <v>1.17</v>
+        <v>0.58881357999999995</v>
       </c>
       <c r="F58">
-        <v>1.234</v>
+        <v>0.10068326</v>
       </c>
       <c r="G58">
-        <v>1252</v>
-      </c>
-      <c r="H58" t="s">
-        <v>55</v>
+        <v>1180</v>
       </c>
       <c r="I58">
-        <v>6295</v>
+        <v>5808</v>
       </c>
       <c r="J58">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="K58">
-        <v>1.181</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M58">
-        <v>4.2910000000000004</v>
+        <v>4.26</v>
       </c>
       <c r="N58">
-        <v>144.11935940000001</v>
+        <v>166.26950410000001</v>
       </c>
       <c r="O58">
-        <v>-50.463093299999997</v>
+        <v>11.2464069</v>
       </c>
       <c r="P58">
-        <v>141.81200000000001</v>
+        <v>130.91900000000001</v>
       </c>
       <c r="Q58">
-        <v>9.8219999999999992</v>
+        <v>9.75</v>
       </c>
       <c r="R58" s="9">
-        <v>9.6608199999999993</v>
+        <v>9.6080000000000005</v>
       </c>
       <c r="S58">
-        <f t="shared" si="2"/>
-        <v>355.42536038318485</v>
+        <f>(0.000000000000000138*G58/(1.673534E-24*1.3*0.000000066726*F58*1.8986E+30/(E58*7149200000)^2))/100000</f>
+        <v>1039.84328949877</v>
       </c>
       <c r="T58">
-        <f t="shared" si="3"/>
+        <f>IF(I58&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
         <v>20</v>
       </c>
       <c r="C59">
-        <v>4.6336110000000001</v>
+        <v>10.590547000000001</v>
       </c>
       <c r="D59">
-        <v>0.06</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E59">
-        <v>1.37</v>
+        <v>0.91890603000000004</v>
       </c>
       <c r="F59">
-        <v>2.8</v>
+        <v>0.18469084999999999</v>
       </c>
       <c r="G59">
-        <v>1561</v>
+        <v>947</v>
       </c>
       <c r="H59" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="I59">
-        <v>6643</v>
+        <v>6000</v>
       </c>
       <c r="J59">
-        <v>1.71</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="K59">
-        <v>1.4</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M59">
-        <v>4.05</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N59">
-        <v>199.33385029999999</v>
+        <v>161.87955690000001</v>
       </c>
       <c r="O59">
-        <v>-15.2737046</v>
+        <v>36.329434499999998</v>
       </c>
       <c r="P59">
-        <v>161.74299999999999</v>
+        <v>130.85499999999999</v>
       </c>
       <c r="Q59">
-        <v>9.109</v>
+        <v>10.058999999999999</v>
       </c>
       <c r="R59" s="9">
-        <v>8.9943600000000004</v>
+        <v>9.9823299999999993</v>
       </c>
       <c r="S59">
-        <f t="shared" si="2"/>
-        <v>267.77715667890726</v>
+        <f>(0.000000000000000138*G59/(1.673534E-24*1.3*0.000000066726*F59*1.8986E+30/(E59*7149200000)^2))/100000</f>
+        <v>1107.9861243219782</v>
       </c>
       <c r="T59">
-        <f t="shared" si="3"/>
+        <f>IF(I59&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>139</v>
+      <c r="A60" t="s">
+        <v>114</v>
       </c>
       <c r="B60" t="s">
         <v>20</v>
       </c>
+      <c r="C60">
+        <v>5.8267310999999999</v>
+      </c>
+      <c r="D60">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="E60">
+        <v>0.57186287999999996</v>
+      </c>
+      <c r="F60">
+        <v>0.24698861999999999</v>
+      </c>
+      <c r="G60">
+        <v>1439</v>
+      </c>
       <c r="I60">
-        <v>6200</v>
+        <v>6110</v>
       </c>
       <c r="J60">
-        <v>1.2</v>
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="K60">
+        <v>1.2909999999999999</v>
+      </c>
+      <c r="L60">
+        <v>0.124</v>
+      </c>
+      <c r="M60">
+        <v>4.1180000000000003</v>
       </c>
       <c r="N60">
-        <v>97.636728000000005</v>
+        <v>51.657269100000001</v>
       </c>
       <c r="O60">
-        <v>29.672419000000001</v>
+        <v>40.817270399999998</v>
       </c>
       <c r="P60">
-        <v>427</v>
+        <v>179.14699999999999</v>
+      </c>
+      <c r="Q60">
+        <v>9.9130000000000003</v>
       </c>
       <c r="R60" s="9">
-        <v>11.4986</v>
+        <v>9.7295700000000007</v>
+      </c>
+      <c r="S60">
+        <f>(0.000000000000000138*G60/(1.673534E-24*1.3*0.000000066726*F60*1.8986E+30/(E60*7149200000)^2))/100000</f>
+        <v>487.59044264912109</v>
       </c>
       <c r="T60">
-        <f t="shared" si="3"/>
+        <f>IF(I60&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
         <v>20</v>
       </c>
       <c r="C61">
-        <v>5.3220124999999996</v>
+        <v>6.4025129999999999</v>
       </c>
       <c r="D61">
-        <v>6.08E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="E61">
-        <v>1.226</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="F61">
-        <v>0.27300000000000002</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G61">
-        <v>1460</v>
+        <v>1388</v>
       </c>
       <c r="H61" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="I61">
-        <v>5990</v>
+        <v>6400</v>
       </c>
       <c r="J61">
-        <v>1.5609999999999999</v>
+        <v>1.415</v>
       </c>
       <c r="K61">
-        <v>1.06</v>
+        <v>1.3129999999999999</v>
       </c>
       <c r="L61">
-        <v>-0.2</v>
+        <v>0.09</v>
       </c>
       <c r="M61">
-        <v>4.0750000000000002</v>
+        <v>4.2</v>
       </c>
       <c r="N61">
-        <v>210.1935714</v>
+        <v>125.3050544</v>
       </c>
       <c r="O61">
-        <v>-30.583608399999999</v>
+        <v>-46.484295899999999</v>
       </c>
       <c r="P61">
-        <v>200.07499999999999</v>
+        <v>123.297</v>
       </c>
       <c r="Q61">
-        <v>10.068</v>
+        <v>8.9949999999999992</v>
       </c>
       <c r="R61" s="9">
-        <v>9.8670799999999996</v>
+        <v>8.8910300000000007</v>
       </c>
       <c r="S61">
-        <f t="shared" ref="S61:S80" si="4">(0.000000000000000138*G61/(1.673534E-24*1.3*0.000000066726*F61*1.8986E+30/(E61*7149200000)^2))/100000</f>
-        <v>2057.1154637812851</v>
+        <f>(0.000000000000000138*G61/(1.673534E-24*1.3*0.000000066726*F61*1.8986E+30/(E61*7149200000)^2))/100000</f>
+        <v>795.95548671567838</v>
       </c>
       <c r="T61">
-        <f t="shared" si="3"/>
+        <f>IF(I61&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
       <c r="C62">
-        <v>5.21536178778</v>
+        <v>11.236598499999999</v>
       </c>
       <c r="D62">
-        <v>6.6100000000000006E-2</v>
+        <v>0.1041</v>
       </c>
       <c r="E62">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="F62">
-        <v>1.51</v>
+        <v>1.234</v>
       </c>
       <c r="G62">
-        <v>1630</v>
+        <v>1252</v>
       </c>
       <c r="H62" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I62">
-        <v>6250</v>
+        <v>6295</v>
       </c>
       <c r="J62">
-        <v>2.3901400000000002</v>
+        <v>1.28</v>
       </c>
       <c r="K62">
-        <v>1.41</v>
+        <v>1.181</v>
       </c>
       <c r="L62">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>3.9</v>
+        <v>4.2910000000000004</v>
       </c>
       <c r="N62">
-        <v>0.32576100000000002</v>
+        <v>144.11935940000001</v>
       </c>
       <c r="O62">
-        <v>-8.9262511999999994</v>
+        <v>-50.463093299999997</v>
       </c>
       <c r="P62">
-        <v>275.58699999999999</v>
+        <v>141.81200000000001</v>
       </c>
       <c r="Q62">
-        <v>9.9740000000000002</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R62" s="9">
-        <v>9.8192900000000005</v>
+        <v>9.6608199999999993</v>
       </c>
       <c r="S62">
-        <f t="shared" si="4"/>
-        <v>621.55661806820979</v>
+        <f>(0.000000000000000138*G62/(1.673534E-24*1.3*0.000000066726*F62*1.8986E+30/(E62*7149200000)^2))/100000</f>
+        <v>355.42536038318485</v>
       </c>
       <c r="T62">
-        <f t="shared" si="3"/>
+        <f>IF(I62&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
       </c>
       <c r="C63">
-        <v>2.2437499999999999</v>
+        <v>4.6336110000000001</v>
       </c>
       <c r="D63">
-        <v>3.6999999999999998E-2</v>
+        <v>0.06</v>
       </c>
       <c r="E63">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="F63">
-        <v>8.84</v>
+        <v>2.8</v>
       </c>
       <c r="G63">
-        <v>1872</v>
+        <v>1561</v>
+      </c>
+      <c r="H63" t="s">
+        <v>66</v>
       </c>
       <c r="I63">
-        <v>6475</v>
+        <v>6643</v>
       </c>
       <c r="J63">
+        <v>1.71</v>
+      </c>
+      <c r="K63">
         <v>1.4</v>
-      </c>
-      <c r="K63">
-        <v>1.62</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="N63">
-        <v>218.27662470000001</v>
+        <v>199.33385029999999</v>
       </c>
       <c r="O63">
-        <v>21.8946875</v>
+        <v>-15.2737046</v>
       </c>
       <c r="P63">
-        <v>161.99700000000001</v>
+        <v>161.74299999999999</v>
       </c>
       <c r="Q63">
-        <v>9.7449999999999992</v>
+        <v>9.109</v>
       </c>
       <c r="R63" s="9">
-        <v>9.6464700000000008</v>
+        <v>8.9943600000000004</v>
       </c>
       <c r="S63">
-        <f t="shared" si="4"/>
-        <v>103.20465157174387</v>
+        <f>(0.000000000000000138*G63/(1.673534E-24*1.3*0.000000066726*F63*1.8986E+30/(E63*7149200000)^2))/100000</f>
+        <v>267.77715667890726</v>
       </c>
       <c r="T63">
-        <f t="shared" si="3"/>
+        <f>IF(I63&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>74</v>
-      </c>
-      <c r="B64" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64">
-        <v>5.4435399999999996</v>
-      </c>
-      <c r="D64">
-        <v>6.4100000000000004E-2</v>
-      </c>
-      <c r="E64">
-        <v>0.63</v>
-      </c>
-      <c r="F64">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="G64">
-        <v>1270</v>
-      </c>
-      <c r="H64" t="s">
-        <v>75</v>
-      </c>
-      <c r="I64">
-        <v>6050</v>
-      </c>
-      <c r="J64">
-        <v>1.22</v>
-      </c>
-      <c r="K64">
-        <v>1.19</v>
-      </c>
-      <c r="L64">
-        <v>0.19</v>
-      </c>
-      <c r="M64">
-        <v>4.34</v>
-      </c>
-      <c r="N64">
-        <v>144.87510470000001</v>
-      </c>
-      <c r="O64">
-        <v>-20.982419100000001</v>
-      </c>
-      <c r="P64">
-        <v>114.173</v>
-      </c>
-      <c r="Q64">
-        <v>9.3510000000000009</v>
-      </c>
-      <c r="R64" s="9">
-        <v>9.2569999999999997</v>
-      </c>
-      <c r="S64">
-        <f t="shared" si="4"/>
-        <v>1277.1766379712274</v>
-      </c>
-      <c r="T64">
-        <f t="shared" si="3"/>
+      <c r="A64" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="H64" s="11"/>
+      <c r="I64" s="17">
+        <v>6161.02294921875</v>
+      </c>
+      <c r="J64" s="17">
+        <v>1.7061723470687871</v>
+      </c>
+      <c r="K64" s="11">
+        <v>1.3463604</v>
+      </c>
+      <c r="L64" s="11"/>
+      <c r="M64" s="17">
+        <v>3.9825000762939449</v>
+      </c>
+      <c r="N64" s="11">
+        <v>268.30433503422898</v>
+      </c>
+      <c r="O64" s="17">
+        <v>37.211736733677057</v>
+      </c>
+      <c r="P64" s="11">
+        <v>496.26729999999998</v>
+      </c>
+      <c r="Q64" s="17">
+        <v>11.469913482666019</v>
+      </c>
+      <c r="R64" s="17">
+        <v>11.469913482666019</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65">
+        <v>6200</v>
+      </c>
+      <c r="J65">
+        <v>1.2</v>
+      </c>
+      <c r="N65">
+        <v>97.636728000000005</v>
+      </c>
+      <c r="O65">
+        <v>29.672419000000001</v>
+      </c>
+      <c r="P65">
+        <v>427</v>
+      </c>
+      <c r="R65" s="9">
+        <v>11.4986</v>
+      </c>
+      <c r="T65">
+        <f>IF(I65&gt;6800,-7,-5)</f>
         <v>-5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" t="s">
-        <v>20</v>
-      </c>
-      <c r="C65">
-        <v>3.3448285000000002</v>
-      </c>
-      <c r="D65">
-        <v>5.5800000000000002E-2</v>
-      </c>
-      <c r="E65">
-        <v>1.81</v>
-      </c>
-      <c r="F65">
-        <v>1.66</v>
-      </c>
-      <c r="G65">
-        <v>2470</v>
-      </c>
-      <c r="H65" t="s">
-        <v>119</v>
-      </c>
-      <c r="I65">
-        <v>9360</v>
-      </c>
-      <c r="J65">
-        <v>1.67</v>
-      </c>
-      <c r="K65">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="L65">
-        <v>0.21</v>
-      </c>
-      <c r="M65">
-        <v>4.3099999999999996</v>
-      </c>
-      <c r="N65">
-        <v>227.270329</v>
-      </c>
-      <c r="O65">
-        <v>-42.704965799999997</v>
-      </c>
-      <c r="P65">
-        <v>427.678</v>
-      </c>
-      <c r="Q65">
-        <v>9.9459999999999997</v>
-      </c>
-      <c r="R65" s="9">
-        <v>9.9122599999999998</v>
-      </c>
-      <c r="S65">
-        <f t="shared" si="4"/>
-        <v>1247.4798366438731</v>
-      </c>
-      <c r="T65">
-        <f t="shared" si="3"/>
-        <v>-7</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
       </c>
       <c r="C66">
-        <v>0.94145223</v>
+        <v>5.3220124999999996</v>
       </c>
       <c r="D66">
-        <v>2.0240000000000001E-2</v>
+        <v>6.08E-2</v>
       </c>
       <c r="E66">
-        <v>1.24</v>
+        <v>1.226</v>
       </c>
       <c r="F66">
-        <v>10.199999999999999</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="G66">
-        <v>2429</v>
+        <v>1460</v>
       </c>
       <c r="H66" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="I66">
-        <v>6432</v>
+        <v>5990</v>
       </c>
       <c r="J66">
-        <v>1.319</v>
+        <v>1.5609999999999999</v>
       </c>
       <c r="K66">
-        <v>1.294</v>
+        <v>1.06</v>
       </c>
       <c r="L66">
-        <v>0.107</v>
+        <v>-0.2</v>
       </c>
       <c r="M66">
-        <v>4.3099999999999996</v>
+        <v>4.0750000000000002</v>
       </c>
       <c r="N66">
-        <v>24.354461799999999</v>
+        <v>210.1935714</v>
       </c>
       <c r="O66">
-        <v>-45.677793700000002</v>
+        <v>-30.583608399999999</v>
       </c>
       <c r="P66">
-        <v>123.483</v>
+        <v>200.07499999999999</v>
       </c>
       <c r="Q66">
-        <v>9.2799999999999994</v>
+        <v>10.068</v>
       </c>
       <c r="R66" s="9">
-        <v>9.1661699999999993</v>
+        <v>9.8670799999999996</v>
       </c>
       <c r="S66">
-        <f t="shared" si="4"/>
-        <v>93.704022194109143</v>
+        <f>(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
+        <v>2057.1154637812851</v>
       </c>
       <c r="T66">
-        <f t="shared" ref="T66:T80" si="5">IF(I66&gt;6800,-7,-5)</f>
+        <f>IF(I66&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A67" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67" s="6">
-        <v>2.7240329999999999</v>
-      </c>
-      <c r="D67" s="6">
-        <v>5.0529999999999999E-2</v>
-      </c>
-      <c r="E67" s="6">
-        <v>1.619</v>
-      </c>
-      <c r="F67" s="6">
-        <v>1.99</v>
-      </c>
-      <c r="G67" s="6">
-        <v>3353</v>
-      </c>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6">
-        <v>8000</v>
-      </c>
-      <c r="J67" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="K67" s="6">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="L67" s="6">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="M67" s="6">
+      <c r="A67" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67">
+        <v>5.21536178778</v>
+      </c>
+      <c r="D67">
+        <v>6.6100000000000006E-2</v>
+      </c>
+      <c r="E67">
+        <v>1.5</v>
+      </c>
+      <c r="F67">
+        <v>1.51</v>
+      </c>
+      <c r="G67">
+        <v>1630</v>
+      </c>
+      <c r="H67" t="s">
+        <v>56</v>
+      </c>
+      <c r="I67">
+        <v>6250</v>
+      </c>
+      <c r="J67">
+        <v>2.3901400000000002</v>
+      </c>
+      <c r="K67">
+        <v>1.41</v>
+      </c>
+      <c r="L67">
+        <v>-0.18</v>
+      </c>
+      <c r="M67">
         <v>3.9</v>
       </c>
-      <c r="N67" s="6">
-        <v>225.68673200000001</v>
-      </c>
-      <c r="O67" s="6">
-        <v>-3.0314874000000001</v>
-      </c>
-      <c r="P67" s="6">
-        <v>99.730999999999995</v>
-      </c>
-      <c r="Q67" s="6">
-        <v>6.5977600000000001</v>
+      <c r="N67">
+        <v>0.32576100000000002</v>
+      </c>
+      <c r="O67">
+        <v>-8.9262511999999994</v>
+      </c>
+      <c r="P67">
+        <v>275.58699999999999</v>
+      </c>
+      <c r="Q67">
+        <v>9.9740000000000002</v>
       </c>
       <c r="R67" s="9">
-        <v>6.5536899999999996</v>
-      </c>
-      <c r="S67" s="8">
-        <f t="shared" si="4"/>
-        <v>1130.2166328238993</v>
-      </c>
-      <c r="T67" s="6">
-        <f t="shared" si="5"/>
-        <v>-7</v>
-      </c>
-      <c r="U67" s="7" t="s">
-        <v>138</v>
+        <v>9.8192900000000005</v>
+      </c>
+      <c r="S67">
+        <f>(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
+        <v>621.55661806820979</v>
+      </c>
+      <c r="T67">
+        <f>IF(I67&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
         <v>20</v>
       </c>
       <c r="C68">
-        <v>1.21987</v>
+        <v>2.2437499999999999</v>
       </c>
       <c r="D68">
-        <v>2.3900000000000001E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E68">
-        <v>1.593</v>
+        <v>1.38</v>
       </c>
       <c r="F68">
-        <v>2.093</v>
+        <v>8.84</v>
       </c>
       <c r="G68">
-        <v>2781.7</v>
-      </c>
-      <c r="H68" t="s">
-        <v>42</v>
+        <v>1872</v>
       </c>
       <c r="I68">
-        <v>7430</v>
+        <v>6475</v>
       </c>
       <c r="J68">
-        <v>1.444</v>
+        <v>1.4</v>
       </c>
       <c r="K68">
-        <v>1.4950000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="L68">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>4.25</v>
+        <v>4.07</v>
       </c>
       <c r="N68">
-        <v>36.712737500000003</v>
+        <v>218.27662470000001</v>
       </c>
       <c r="O68">
-        <v>37.5504441</v>
+        <v>21.8946875</v>
       </c>
       <c r="P68">
-        <v>121.944</v>
+        <v>161.99700000000001</v>
       </c>
       <c r="Q68">
-        <v>8.14</v>
+        <v>9.7449999999999992</v>
       </c>
       <c r="R68" s="9">
-        <v>8.0700400000000005</v>
+        <v>9.6464700000000008</v>
       </c>
       <c r="S68">
-        <f t="shared" si="4"/>
-        <v>863.09804630713359</v>
+        <f>(0.000000000000000138*G68/(1.673534E-24*1.3*0.000000066726*F68*1.8986E+30/(E68*7149200000)^2))/100000</f>
+        <v>103.20465157174387</v>
       </c>
       <c r="T68">
-        <f t="shared" si="5"/>
-        <v>-7</v>
+        <f>IF(I68&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
       </c>
       <c r="C69">
-        <v>6.87188</v>
+        <v>5.4435399999999996</v>
       </c>
       <c r="D69">
-        <v>7.5219999999999995E-2</v>
+        <v>6.4100000000000004E-2</v>
       </c>
       <c r="E69">
-        <v>1.23</v>
+        <v>0.63</v>
       </c>
       <c r="F69">
-        <v>3.44</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G69">
-        <v>1250</v>
+        <v>1270</v>
       </c>
       <c r="H69" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I69">
-        <v>6180</v>
+        <v>6050</v>
       </c>
       <c r="J69">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="K69">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="L69">
-        <v>-0.02</v>
+        <v>0.19</v>
       </c>
       <c r="M69">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="N69">
-        <v>243.95971940000001</v>
+        <v>144.87510470000001</v>
       </c>
       <c r="O69">
-        <v>10.0324103</v>
+        <v>-20.982419100000001</v>
       </c>
       <c r="P69">
-        <v>136.24</v>
+        <v>114.173</v>
       </c>
       <c r="Q69">
-        <v>9.391</v>
+        <v>9.3510000000000009</v>
       </c>
       <c r="R69" s="9">
-        <v>9.20974</v>
+        <v>9.2569999999999997</v>
       </c>
       <c r="S69">
-        <f t="shared" si="4"/>
-        <v>140.68549179703928</v>
+        <f>(0.000000000000000138*G69/(1.673534E-24*1.3*0.000000066726*F69*1.8986E+30/(E69*7149200000)^2))/100000</f>
+        <v>1277.1766379712274</v>
       </c>
       <c r="T69">
-        <f t="shared" si="5"/>
+        <f>IF(I69&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="6">
-        <v>3.86813881</v>
-      </c>
-      <c r="D70" s="6">
-        <v>4.53E-2</v>
-      </c>
-      <c r="E70" s="6">
-        <v>1</v>
-      </c>
-      <c r="F70" s="6">
-        <v>0.26</v>
-      </c>
-      <c r="G70" s="6">
-        <v>971</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I70" s="6">
-        <v>4792</v>
-      </c>
-      <c r="J70" s="6">
-        <v>0.80100000000000005</v>
-      </c>
-      <c r="K70" s="6">
-        <v>0.83</v>
-      </c>
-      <c r="L70" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="M70" s="6">
-        <v>4.57</v>
-      </c>
-      <c r="N70" s="6">
-        <v>315.02596610000001</v>
-      </c>
-      <c r="O70" s="6">
-        <v>-5.0948570000000002</v>
-      </c>
-      <c r="P70" s="6">
-        <v>49.960500000000003</v>
-      </c>
-      <c r="Q70" s="6">
-        <v>9.8729999999999993</v>
+      <c r="A70" t="s">
+        <v>117</v>
+      </c>
+      <c r="B70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70">
+        <v>3.3448285000000002</v>
+      </c>
+      <c r="D70">
+        <v>5.5800000000000002E-2</v>
+      </c>
+      <c r="E70">
+        <v>1.81</v>
+      </c>
+      <c r="F70">
+        <v>1.66</v>
+      </c>
+      <c r="G70">
+        <v>2470</v>
+      </c>
+      <c r="H70" t="s">
+        <v>118</v>
+      </c>
+      <c r="I70">
+        <v>9360</v>
+      </c>
+      <c r="J70">
+        <v>1.67</v>
+      </c>
+      <c r="K70">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="L70">
+        <v>0.21</v>
+      </c>
+      <c r="M70">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="N70">
+        <v>227.270329</v>
+      </c>
+      <c r="O70">
+        <v>-42.704965799999997</v>
+      </c>
+      <c r="P70">
+        <v>427.678</v>
+      </c>
+      <c r="Q70">
+        <v>9.9459999999999997</v>
       </c>
       <c r="R70" s="9">
-        <v>9.4846599999999999</v>
-      </c>
-      <c r="S70" s="6">
-        <f t="shared" si="4"/>
-        <v>955.72600175951948</v>
-      </c>
-      <c r="T70" s="6">
-        <f t="shared" si="5"/>
-        <v>-5</v>
-      </c>
-      <c r="U70" s="7" t="s">
-        <v>138</v>
+        <v>9.9122599999999998</v>
+      </c>
+      <c r="S70">
+        <f>(0.000000000000000138*G70/(1.673534E-24*1.3*0.000000066726*F70*1.8986E+30/(E70*7149200000)^2))/100000</f>
+        <v>1247.4798366438731</v>
+      </c>
+      <c r="T70">
+        <f>IF(I70&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
         <v>20</v>
       </c>
       <c r="C71">
-        <v>4.9546416000000004</v>
+        <v>0.94145223</v>
       </c>
       <c r="D71">
-        <v>6.1699999999999998E-2</v>
+        <v>2.0240000000000001E-2</v>
       </c>
       <c r="E71">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="F71">
-        <v>0.96</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G71">
-        <v>1487</v>
+        <v>2429</v>
+      </c>
+      <c r="H71" t="s">
+        <v>72</v>
       </c>
       <c r="I71">
-        <v>6400</v>
+        <v>6432</v>
       </c>
       <c r="J71">
-        <v>1.4319999999999999</v>
+        <v>1.319</v>
       </c>
       <c r="K71">
-        <v>1.276</v>
+        <v>1.294</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="M71">
-        <v>4.2320000000000002</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N71">
-        <v>311.04275580000001</v>
+        <v>24.354461799999999</v>
       </c>
       <c r="O71">
-        <v>-39.225485599999999</v>
+        <v>-45.677793700000002</v>
       </c>
       <c r="P71">
-        <v>162.303</v>
+        <v>123.483</v>
       </c>
       <c r="Q71">
-        <v>9.5039999999999996</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R71" s="9">
-        <v>9.3767099999999992</v>
+        <v>9.1661699999999993</v>
       </c>
       <c r="S71">
-        <f t="shared" si="4"/>
-        <v>701.18164217622461</v>
+        <f>(0.000000000000000138*G71/(1.673534E-24*1.3*0.000000066726*F71*1.8986E+30/(E71*7149200000)^2))/100000</f>
+        <v>93.704022194109143</v>
       </c>
       <c r="T71">
-        <f t="shared" si="5"/>
+        <f>IF(I71&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72">
-        <v>2.13775</v>
-      </c>
-      <c r="D72">
-        <v>3.4430000000000002E-2</v>
-      </c>
-      <c r="E72">
-        <v>1.36</v>
-      </c>
-      <c r="F72">
-        <v>0.72</v>
-      </c>
-      <c r="G72">
-        <v>1865</v>
-      </c>
-      <c r="H72" t="s">
-        <v>92</v>
-      </c>
-      <c r="I72">
-        <v>5990</v>
-      </c>
-      <c r="J72">
-        <v>1.42</v>
-      </c>
-      <c r="K72">
-        <v>0.98</v>
-      </c>
-      <c r="L72">
-        <v>0.39</v>
-      </c>
-      <c r="M72">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="N72">
-        <v>304.53884299999999</v>
-      </c>
-      <c r="O72">
-        <v>-1.0760033</v>
-      </c>
-      <c r="P72">
-        <v>149.21600000000001</v>
-      </c>
-      <c r="Q72">
-        <v>9.75</v>
+      <c r="A72" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="6">
+        <v>2.7240329999999999</v>
+      </c>
+      <c r="D72" s="6">
+        <v>5.0529999999999999E-2</v>
+      </c>
+      <c r="E72" s="6">
+        <v>1.619</v>
+      </c>
+      <c r="F72" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="G72" s="6">
+        <v>3353</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6">
+        <v>8000</v>
+      </c>
+      <c r="J72" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="K72" s="6">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="L72" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M72" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="N72" s="6">
+        <v>225.68673200000001</v>
+      </c>
+      <c r="O72" s="6">
+        <v>-3.0314874000000001</v>
+      </c>
+      <c r="P72" s="6">
+        <v>99.730999999999995</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>6.5977600000000001</v>
       </c>
       <c r="R72" s="9">
-        <v>9.5723000000000003</v>
-      </c>
-      <c r="S72">
-        <f t="shared" si="4"/>
-        <v>1226.0598654781754</v>
-      </c>
-      <c r="T72">
-        <f t="shared" si="5"/>
-        <v>-5</v>
+        <v>6.5536899999999996</v>
+      </c>
+      <c r="S72" s="8">
+        <f>(0.000000000000000138*G72/(1.673534E-24*1.3*0.000000066726*F72*1.8986E+30/(E72*7149200000)^2))/100000</f>
+        <v>1130.2166328238993</v>
+      </c>
+      <c r="T72" s="6">
+        <f>IF(I72&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
+      <c r="U72" s="7" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B73" t="s">
         <v>20</v>
       </c>
       <c r="C73">
-        <v>1.8098819799999999</v>
+        <v>1.21987</v>
       </c>
       <c r="D73">
-        <v>3.3000000000000002E-2</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="E73">
-        <v>1.8540000000000001</v>
+        <v>1.593</v>
       </c>
       <c r="F73">
-        <v>0.89400000000000002</v>
+        <v>2.093</v>
       </c>
       <c r="G73">
-        <v>2228</v>
+        <v>2781.7</v>
       </c>
       <c r="H73" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I73">
-        <v>6329</v>
+        <v>7430</v>
       </c>
       <c r="J73">
-        <v>1.756</v>
+        <v>1.444</v>
       </c>
       <c r="K73">
-        <v>1.458</v>
+        <v>1.4950000000000001</v>
       </c>
       <c r="L73">
-        <v>0.36599999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="M73">
-        <v>4.1959999999999997</v>
+        <v>4.25</v>
       </c>
       <c r="N73">
-        <v>26.632936000000001</v>
+        <v>36.712737500000003</v>
       </c>
       <c r="O73">
-        <v>2.7003889999999999</v>
+        <v>37.5504441</v>
       </c>
       <c r="P73">
-        <v>194.459</v>
+        <v>121.944</v>
       </c>
       <c r="Q73">
-        <v>9.5180000000000007</v>
+        <v>8.14</v>
       </c>
       <c r="R73" s="9">
-        <v>9.3950700000000005</v>
+        <v>8.0700400000000005</v>
       </c>
       <c r="S73">
-        <f t="shared" si="4"/>
-        <v>2192.2225820487197</v>
+        <f>(0.000000000000000138*G73/(1.673534E-24*1.3*0.000000066726*F73*1.8986E+30/(E73*7149200000)^2))/100000</f>
+        <v>863.09804630713359</v>
       </c>
       <c r="T73">
-        <f t="shared" si="5"/>
-        <v>-5</v>
+        <f>IF(I73&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="B74" t="s">
         <v>20</v>
       </c>
       <c r="C74">
-        <v>3.6623920000000001</v>
+        <v>6.87188</v>
       </c>
       <c r="D74">
-        <v>5.1900000000000002E-2</v>
+        <v>7.5219999999999995E-2</v>
       </c>
       <c r="E74">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="F74">
-        <v>0.85</v>
+        <v>3.44</v>
       </c>
       <c r="G74">
-        <v>1716.2</v>
+        <v>1250</v>
       </c>
       <c r="H74" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="I74">
-        <v>6600</v>
+        <v>6180</v>
       </c>
       <c r="J74">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="K74">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="L74">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="M74">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="N74">
-        <v>66.370901599999996</v>
+        <v>243.95971940000001</v>
       </c>
       <c r="O74">
-        <v>-30.600436200000001</v>
+        <v>10.0324103</v>
       </c>
       <c r="P74">
-        <v>246.69</v>
+        <v>136.24</v>
       </c>
       <c r="Q74">
-        <v>10.044</v>
+        <v>9.391</v>
       </c>
       <c r="R74" s="9">
-        <v>9.9720200000000006</v>
+        <v>9.20974</v>
       </c>
       <c r="S74">
-        <f t="shared" si="4"/>
-        <v>1209.5375438309629</v>
+        <f>(0.000000000000000138*G74/(1.673534E-24*1.3*0.000000066726*F74*1.8986E+30/(E74*7149200000)^2))/100000</f>
+        <v>140.68549179703928</v>
       </c>
       <c r="T74">
-        <f t="shared" si="5"/>
+        <f>IF(I74&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75">
-        <v>8.1587200000000006</v>
-      </c>
-      <c r="D75">
-        <v>8.0100000000000005E-2</v>
-      </c>
-      <c r="E75">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F75">
-        <v>2.54</v>
-      </c>
-      <c r="G75">
-        <v>1059</v>
-      </c>
-      <c r="H75" t="s">
-        <v>98</v>
-      </c>
-      <c r="I75">
-        <v>5600</v>
-      </c>
-      <c r="J75">
-        <v>1.03</v>
-      </c>
-      <c r="K75">
-        <v>1.34</v>
-      </c>
-      <c r="L75">
-        <v>0.17</v>
-      </c>
-      <c r="M75">
-        <v>4.5</v>
-      </c>
-      <c r="N75">
-        <v>359.90087369999998</v>
-      </c>
-      <c r="O75">
-        <v>-35.031334899999997</v>
-      </c>
-      <c r="P75">
-        <v>89.960599999999999</v>
-      </c>
-      <c r="Q75">
-        <v>9.7889999999999997</v>
+      <c r="A75" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="6">
+        <v>3.86813881</v>
+      </c>
+      <c r="D75" s="6">
+        <v>4.53E-2</v>
+      </c>
+      <c r="E75" s="6">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="G75" s="6">
+        <v>971</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I75" s="6">
+        <v>4792</v>
+      </c>
+      <c r="J75" s="6">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="K75" s="6">
+        <v>0.83</v>
+      </c>
+      <c r="L75" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="M75" s="6">
+        <v>4.57</v>
+      </c>
+      <c r="N75" s="6">
+        <v>315.02596610000001</v>
+      </c>
+      <c r="O75" s="6">
+        <v>-5.0948570000000002</v>
+      </c>
+      <c r="P75" s="6">
+        <v>49.960500000000003</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>9.8729999999999993</v>
       </c>
       <c r="R75" s="9">
-        <v>9.6124899999999993</v>
-      </c>
-      <c r="S75">
-        <f t="shared" si="4"/>
-        <v>136.24063220140397</v>
-      </c>
-      <c r="T75">
-        <f t="shared" si="5"/>
+        <v>9.4846599999999999</v>
+      </c>
+      <c r="S75" s="6">
+        <f>(0.000000000000000138*G75/(1.673534E-24*1.3*0.000000066726*F75*1.8986E+30/(E75*7149200000)^2))/100000</f>
+        <v>955.72600175951948</v>
+      </c>
+      <c r="T75" s="6">
+        <f>IF(I75&gt;6800,-7,-5)</f>
         <v>-5</v>
+      </c>
+      <c r="U75" s="7" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="B76" t="s">
         <v>20</v>
       </c>
       <c r="C76">
-        <v>2.7057899999999999</v>
+        <v>4.9546416000000004</v>
       </c>
       <c r="D76">
-        <v>4.4699999999999997E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="E76">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="F76">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="G76">
-        <v>2190</v>
-      </c>
-      <c r="H76" t="s">
-        <v>128</v>
+        <v>1487</v>
       </c>
       <c r="I76">
-        <v>6480</v>
+        <v>6400</v>
       </c>
       <c r="J76">
-        <v>2.1</v>
+        <v>1.4319999999999999</v>
       </c>
       <c r="K76">
-        <v>1.48</v>
+        <v>1.276</v>
       </c>
       <c r="L76">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>3.96</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="N76">
-        <v>72.660591600000004</v>
+        <v>311.04275580000001</v>
       </c>
       <c r="O76">
-        <v>1.8938364999999999</v>
+        <v>-39.225485599999999</v>
       </c>
       <c r="P76">
-        <v>275.66399999999999</v>
+        <v>162.303</v>
       </c>
       <c r="Q76">
-        <v>10.073</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="R76" s="9">
-        <v>9.8979599999999994</v>
+        <v>9.3767099999999992</v>
       </c>
       <c r="S76">
-        <f t="shared" si="4"/>
-        <v>1257.117296864338</v>
+        <f>(0.000000000000000138*G76/(1.673534E-24*1.3*0.000000066726*F76*1.8986E+30/(E76*7149200000)^2))/100000</f>
+        <v>701.18164217622461</v>
       </c>
       <c r="T76">
-        <f t="shared" si="5"/>
+        <f>IF(I76&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
         <v>20</v>
       </c>
       <c r="C77">
-        <v>3.9501900000000001</v>
+        <v>2.13775</v>
       </c>
       <c r="D77">
-        <v>5.5E-2</v>
+        <v>3.4430000000000002E-2</v>
       </c>
       <c r="E77">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="F77">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="G77">
-        <v>1604</v>
+        <v>1865</v>
       </c>
       <c r="H77" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="I77">
-        <v>6170</v>
+        <v>5990</v>
       </c>
       <c r="J77">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="K77">
-        <v>1.67</v>
+        <v>0.98</v>
       </c>
       <c r="L77">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="M77">
-        <v>4.2699999999999996</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="N77">
-        <v>313.78323929999999</v>
+        <v>304.53884299999999</v>
       </c>
       <c r="O77">
-        <v>-34.135751200000001</v>
+        <v>-1.0760033</v>
       </c>
       <c r="P77">
-        <v>211.21100000000001</v>
+        <v>149.21600000000001</v>
       </c>
       <c r="Q77">
-        <v>10.051</v>
+        <v>9.75</v>
       </c>
       <c r="R77" s="9">
-        <v>10.028499999999999</v>
+        <v>9.5723000000000003</v>
       </c>
       <c r="S77">
-        <f t="shared" si="4"/>
-        <v>2049.4439875099679</v>
+        <f>(0.000000000000000138*G77/(1.673534E-24*1.3*0.000000066726*F77*1.8986E+30/(E77*7149200000)^2))/100000</f>
+        <v>1226.0598654781754</v>
       </c>
       <c r="T77">
-        <f t="shared" si="5"/>
+        <f>IF(I77&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
         <v>20</v>
       </c>
       <c r="C78">
-        <v>2.1846700000000001</v>
+        <v>1.8098819799999999</v>
       </c>
       <c r="D78">
-        <v>3.4160000000000003E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="E78">
-        <v>1.23</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="F78">
-        <v>1.44</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G78">
-        <v>1570</v>
+        <v>2228</v>
       </c>
       <c r="H78" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="I78">
-        <v>5830</v>
+        <v>6329</v>
       </c>
       <c r="J78">
-        <v>1.23</v>
+        <v>1.756</v>
       </c>
       <c r="K78">
-        <v>1.46</v>
+        <v>1.458</v>
       </c>
       <c r="L78">
-        <v>0.14000000000000001</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M78">
-        <v>4.3600000000000003</v>
+        <v>4.1959999999999997</v>
       </c>
       <c r="N78">
-        <v>337.45782430000003</v>
+        <v>26.632936000000001</v>
       </c>
       <c r="O78">
-        <v>-48.003098799999997</v>
+        <v>2.7003889999999999</v>
       </c>
       <c r="P78">
-        <v>137.54400000000001</v>
+        <v>194.459</v>
       </c>
       <c r="Q78">
-        <v>10.092000000000001</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="R78" s="9">
-        <v>9.9369700000000005</v>
+        <v>9.3950700000000005</v>
       </c>
       <c r="S78">
-        <f t="shared" si="4"/>
-        <v>422.11900227636102</v>
+        <f>(0.000000000000000138*G78/(1.673534E-24*1.3*0.000000066726*F78*1.8986E+30/(E78*7149200000)^2))/100000</f>
+        <v>2192.2225820487197</v>
       </c>
       <c r="T78">
-        <f t="shared" si="5"/>
+        <f>IF(I78&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="B79" t="s">
         <v>20</v>
       </c>
       <c r="C79">
-        <v>5.75251</v>
+        <v>3.6623920000000001</v>
       </c>
       <c r="D79">
-        <v>7.17E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
       <c r="E79">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="F79">
-        <v>2.4300000000000002</v>
+        <v>0.85</v>
       </c>
       <c r="G79">
-        <v>1480</v>
+        <v>1716.2</v>
       </c>
       <c r="H79" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="I79">
-        <v>6150</v>
+        <v>6600</v>
       </c>
       <c r="J79">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="K79">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="L79">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="M79">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N79">
-        <v>39.897668899999999</v>
+        <v>66.370901599999996</v>
       </c>
       <c r="O79">
-        <v>-50.008193400000003</v>
+        <v>-30.600436200000001</v>
       </c>
       <c r="P79">
-        <v>158.66</v>
+        <v>246.69</v>
       </c>
       <c r="Q79">
-        <v>9.4749999999999996</v>
+        <v>10.044</v>
       </c>
       <c r="R79" s="9">
-        <v>9.3251000000000008</v>
+        <v>9.9720200000000006</v>
       </c>
       <c r="S79">
-        <f t="shared" si="4"/>
-        <v>162.15983922320817</v>
+        <f>(0.000000000000000138*G79/(1.673534E-24*1.3*0.000000066726*F79*1.8986E+30/(E79*7149200000)^2))/100000</f>
+        <v>1209.5375438309629</v>
       </c>
       <c r="T79">
-        <f t="shared" si="5"/>
+        <f>IF(I79&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>96</v>
+      </c>
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80">
+        <v>8.1587200000000006</v>
+      </c>
+      <c r="D80">
+        <v>8.0100000000000005E-2</v>
+      </c>
+      <c r="E80">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F80">
+        <v>2.54</v>
+      </c>
+      <c r="G80">
+        <v>1059</v>
+      </c>
+      <c r="H80" t="s">
+        <v>97</v>
+      </c>
+      <c r="I80">
+        <v>5600</v>
+      </c>
+      <c r="J80">
+        <v>1.03</v>
+      </c>
+      <c r="K80">
+        <v>1.34</v>
+      </c>
+      <c r="L80">
+        <v>0.17</v>
+      </c>
+      <c r="M80">
+        <v>4.5</v>
+      </c>
+      <c r="N80">
+        <v>359.90087369999998</v>
+      </c>
+      <c r="O80">
+        <v>-35.031334899999997</v>
+      </c>
+      <c r="P80">
+        <v>89.960599999999999</v>
+      </c>
+      <c r="Q80">
+        <v>9.7889999999999997</v>
+      </c>
+      <c r="R80" s="9">
+        <v>9.6124899999999993</v>
+      </c>
+      <c r="S80">
+        <f>(0.000000000000000138*G80/(1.673534E-24*1.3*0.000000066726*F80*1.8986E+30/(E80*7149200000)^2))/100000</f>
+        <v>136.24063220140397</v>
+      </c>
+      <c r="T80">
+        <f>IF(I80&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>132</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81">
+        <v>2.7057899999999999</v>
+      </c>
+      <c r="D81">
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="E81">
+        <v>1.62</v>
+      </c>
+      <c r="F81">
+        <v>1.17</v>
+      </c>
+      <c r="G81">
+        <v>2190</v>
+      </c>
+      <c r="H81" t="s">
+        <v>127</v>
+      </c>
+      <c r="I81" s="16">
+        <v>6480</v>
+      </c>
+      <c r="J81" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="K81">
+        <v>1.48</v>
+      </c>
+      <c r="L81">
+        <v>0.12</v>
+      </c>
+      <c r="M81" s="16">
+        <v>3.96</v>
+      </c>
+      <c r="N81" s="16">
+        <v>72.660591600000004</v>
+      </c>
+      <c r="O81" s="16">
+        <v>1.8938364999999999</v>
+      </c>
+      <c r="P81">
+        <v>275.66399999999999</v>
+      </c>
+      <c r="Q81" s="16">
+        <v>10.073</v>
+      </c>
+      <c r="R81" s="20">
+        <v>9.8979599999999994</v>
+      </c>
+      <c r="S81">
+        <f>(0.000000000000000138*G81/(1.673534E-24*1.3*0.000000066726*F81*1.8986E+30/(E81*7149200000)^2))/100000</f>
+        <v>1257.117296864338</v>
+      </c>
+      <c r="T81">
+        <f>IF(I81&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A82" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82">
+        <v>3.9501900000000001</v>
+      </c>
+      <c r="D82">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E82">
+        <v>1.58</v>
+      </c>
+      <c r="F82">
+        <v>0.5</v>
+      </c>
+      <c r="G82">
+        <v>1604</v>
+      </c>
+      <c r="H82" t="s">
+        <v>54</v>
+      </c>
+      <c r="I82" s="16">
+        <v>6170</v>
+      </c>
+      <c r="J82" s="16">
+        <v>1.48</v>
+      </c>
+      <c r="K82">
+        <v>1.67</v>
+      </c>
+      <c r="L82">
+        <v>0.26</v>
+      </c>
+      <c r="M82" s="16">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="N82" s="16">
+        <v>313.78323929999999</v>
+      </c>
+      <c r="O82" s="16">
+        <v>-34.135751200000001</v>
+      </c>
+      <c r="P82">
+        <v>211.21100000000001</v>
+      </c>
+      <c r="Q82" s="16">
+        <v>10.051</v>
+      </c>
+      <c r="R82" s="20">
+        <v>10.028499999999999</v>
+      </c>
+      <c r="S82">
+        <f>(0.000000000000000138*G82/(1.673534E-24*1.3*0.000000066726*F82*1.8986E+30/(E82*7149200000)^2))/100000</f>
+        <v>2049.4439875099679</v>
+      </c>
+      <c r="T82">
+        <f>IF(I82&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A83" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83">
+        <v>2.1846700000000001</v>
+      </c>
+      <c r="D83">
+        <v>3.4160000000000003E-2</v>
+      </c>
+      <c r="E83">
+        <v>1.23</v>
+      </c>
+      <c r="F83">
+        <v>1.44</v>
+      </c>
+      <c r="G83">
+        <v>1570</v>
+      </c>
+      <c r="H83" t="s">
+        <v>134</v>
+      </c>
+      <c r="I83" s="16">
+        <v>5830</v>
+      </c>
+      <c r="J83" s="16">
+        <v>1.23</v>
+      </c>
+      <c r="K83">
+        <v>1.46</v>
+      </c>
+      <c r="L83">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M83" s="16">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="N83" s="16">
+        <v>337.45782430000003</v>
+      </c>
+      <c r="O83" s="16">
+        <v>-48.003098799999997</v>
+      </c>
+      <c r="P83">
+        <v>137.54400000000001</v>
+      </c>
+      <c r="Q83" s="16">
+        <v>10.092000000000001</v>
+      </c>
+      <c r="R83" s="20">
+        <v>9.9369700000000005</v>
+      </c>
+      <c r="S83">
+        <f>(0.000000000000000138*G83/(1.673534E-24*1.3*0.000000066726*F83*1.8986E+30/(E83*7149200000)^2))/100000</f>
+        <v>422.11900227636102</v>
+      </c>
+      <c r="T83">
+        <f>IF(I83&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A84" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <v>5.75251</v>
+      </c>
+      <c r="D84">
+        <v>7.17E-2</v>
+      </c>
+      <c r="E84">
+        <v>1.02</v>
+      </c>
+      <c r="F84">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="G84">
+        <v>1480</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I84" s="18">
+        <v>6150</v>
+      </c>
+      <c r="J84" s="18">
+        <v>1.64</v>
+      </c>
+      <c r="K84" s="11">
+        <v>1.21</v>
+      </c>
+      <c r="L84" s="11">
+        <v>0.21</v>
+      </c>
+      <c r="M84" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="N84" s="18">
+        <v>39.897668899999999</v>
+      </c>
+      <c r="O84" s="18">
+        <v>-50.008193400000003</v>
+      </c>
+      <c r="P84" s="11">
+        <v>158.66</v>
+      </c>
+      <c r="Q84" s="18">
+        <v>9.4749999999999996</v>
+      </c>
+      <c r="R84" s="18">
+        <v>9.3251000000000008</v>
+      </c>
+      <c r="S84">
+        <f>(0.000000000000000138*G84/(1.673534E-24*1.3*0.000000066726*F84*1.8986E+30/(E84*7149200000)^2))/100000</f>
+        <v>162.15983922320817</v>
+      </c>
+      <c r="T84">
+        <f>IF(I84&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A85" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85">
+        <v>3.1915399999999998</v>
+      </c>
+      <c r="D85">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="E85">
+        <v>1.41</v>
+      </c>
+      <c r="F85">
+        <v>7.29</v>
+      </c>
+      <c r="G85">
+        <v>1729</v>
+      </c>
+      <c r="H85" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80">
-        <v>3.1915399999999998</v>
-      </c>
-      <c r="D80">
-        <v>4.7600000000000003E-2</v>
-      </c>
-      <c r="E80">
-        <v>1.41</v>
-      </c>
-      <c r="F80">
-        <v>7.29</v>
-      </c>
-      <c r="G80">
-        <v>1729</v>
-      </c>
-      <c r="H80" t="s">
-        <v>109</v>
-      </c>
-      <c r="I80">
+      <c r="I85" s="19">
         <v>6429</v>
       </c>
-      <c r="J80">
+      <c r="J85" s="19">
         <v>1.54</v>
       </c>
-      <c r="K80">
+      <c r="K85" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L80">
+      <c r="L85" s="11">
         <v>-0.18</v>
       </c>
-      <c r="M80">
+      <c r="M85" s="19">
         <v>3.95</v>
       </c>
-      <c r="N80">
+      <c r="N85" s="11">
         <v>65.469581399999996</v>
       </c>
-      <c r="O80">
+      <c r="O85" s="19">
         <v>57.817209499999997</v>
       </c>
-      <c r="P80">
+      <c r="P85" s="11">
         <v>213.053</v>
       </c>
-      <c r="Q80">
+      <c r="Q85" s="19">
         <v>9.8539999999999992</v>
       </c>
-      <c r="R80" s="9">
+      <c r="R85" s="19">
         <v>9.7388899999999996</v>
       </c>
-      <c r="S80">
-        <f t="shared" si="4"/>
+      <c r="S85">
+        <f>(0.000000000000000138*G85/(1.673534E-24*1.3*0.000000066726*F85*1.8986E+30/(E85*7149200000)^2))/100000</f>
         <v>120.66830436099001</v>
       </c>
-      <c r="T80">
-        <f t="shared" si="5"/>
+      <c r="T85">
+        <f>IF(I85&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" s="4" t="s">
-        <v>140</v>
-      </c>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
+      <c r="N86" s="11"/>
+      <c r="O86" s="11"/>
+      <c r="P86" s="11"/>
+      <c r="Q86" s="11"/>
+      <c r="R86" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U79" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U80">
-      <sortCondition ref="A1:A80"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U85">
+      <sortCondition ref="A1:A85"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R79">

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/waltzerclone/WALTzER-simulator/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DC096E-5C4E-9D4F-9092-4AD1AC0C6EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D4D5BB-BFFC-0C4C-988C-A73FCF734FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="2200" windowWidth="33600" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22040" yWindow="820" windowWidth="33600" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="145">
   <si>
     <t>#pl_name</t>
   </si>
@@ -468,6 +468,9 @@
   </si>
   <si>
     <t>TrES-4 b</t>
+  </si>
+  <si>
+    <t>B9.5-A0</t>
   </si>
 </sst>
 </file>
@@ -500,7 +503,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,6 +532,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor theme="5" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -587,7 +596,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -621,26 +630,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1021,25 +1027,21 @@
       <c r="A2" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="17">
+      <c r="I2" s="16">
         <v>4907.77490234375</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17">
+      <c r="J2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16">
         <v>221.24648617076679</v>
       </c>
-      <c r="O2" s="17">
+      <c r="O2" s="16">
         <v>27.074315757773469</v>
       </c>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="17">
+      <c r="Q2" s="16">
         <v>2.1833524703979492</v>
       </c>
-      <c r="R2" s="17">
+      <c r="R2" s="16">
         <v>2.1833524703979492</v>
       </c>
       <c r="BE2" s="3"/>
@@ -1315,35 +1317,32 @@
       <c r="BH6" s="3"/>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="17">
+      <c r="B7" s="14"/>
+      <c r="I7" s="16">
         <v>6245.11328125</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>1.208241820335388</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="17">
+      <c r="M7" s="16">
         <v>4.2744002342224121</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="16">
         <v>31.04275939878713</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <v>46.687851647860192</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7">
         <v>283.38339999999999</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="16">
         <v>11.12930202484131</v>
       </c>
-      <c r="R7" s="17">
+      <c r="R7" s="16">
         <v>11.12930202484131</v>
       </c>
       <c r="V7" s="2"/>
@@ -1476,30 +1475,26 @@
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="17">
+      <c r="I10" s="16">
         <v>6424.27685546875</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <v>2.0702402591705318</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17">
+      <c r="M10" s="16"/>
+      <c r="N10" s="16">
         <v>292.24718620018581</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="16">
         <v>47.969544064101818</v>
       </c>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="17">
+      <c r="Q10" s="16">
         <v>10.36768245697021</v>
       </c>
-      <c r="R10" s="17">
+      <c r="R10" s="16">
         <v>10.36768245697021</v>
       </c>
     </row>
@@ -1556,11 +1551,11 @@
         <v>9.4517399999999991</v>
       </c>
       <c r="S11">
-        <f>(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
+        <f t="shared" ref="S11:S35" si="0">(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
         <v>338.15838787809196</v>
       </c>
       <c r="T11">
-        <f>IF(I11&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T11:T34" si="1">IF(I11&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
       <c r="V11" s="2"/>
@@ -1623,11 +1618,11 @@
         <v>7.89255</v>
       </c>
       <c r="S12">
-        <f>(0.000000000000000138*G12/(1.673534E-24*1.3*0.000000066726*F12*1.8986E+30/(E12*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>211.51519610586323</v>
       </c>
       <c r="T12">
-        <f>IF(I12&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1687,11 +1682,11 @@
         <v>7.5933599999999997</v>
       </c>
       <c r="S13">
-        <f>(0.000000000000000138*G13/(1.673534E-24*1.3*0.000000066726*F13*1.8986E+30/(E13*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>797.33090232058362</v>
       </c>
       <c r="T13">
-        <f>IF(I13&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1751,11 +1746,11 @@
         <v>8.0141600000000004</v>
       </c>
       <c r="S14">
-        <f>(0.000000000000000138*G14/(1.673534E-24*1.3*0.000000066726*F14*1.8986E+30/(E14*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>599.63628364223177</v>
       </c>
       <c r="T14">
-        <f>IF(I14&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V14" s="2"/>
@@ -1818,11 +1813,11 @@
         <v>8.7641200000000001</v>
       </c>
       <c r="S15">
-        <f>(0.000000000000000138*G15/(1.673534E-24*1.3*0.000000066726*F15*1.8986E+30/(E15*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>597.79498778467087</v>
       </c>
       <c r="T15">
-        <f>IF(I15&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -1882,11 +1877,11 @@
         <v>7.41432</v>
       </c>
       <c r="S16">
-        <f>(0.000000000000000138*G16/(1.673534E-24*1.3*0.000000066726*F16*1.8986E+30/(E16*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>349.61677638948368</v>
       </c>
       <c r="T16">
-        <f>IF(I16&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
       <c r="V16" s="2"/>
@@ -1946,11 +1941,11 @@
         <v>8.2268799999999995</v>
       </c>
       <c r="S17">
-        <f>(0.000000000000000138*G17/(1.673534E-24*1.3*0.000000066726*F17*1.8986E+30/(E17*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1280.5918535006856</v>
       </c>
       <c r="T17">
-        <f>IF(I17&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2010,11 +2005,11 @@
         <v>7.5086599999999999</v>
       </c>
       <c r="S18">
-        <f>(0.000000000000000138*G18/(1.673534E-24*1.3*0.000000066726*F18*1.8986E+30/(E18*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>988.21070019970352</v>
       </c>
       <c r="T18">
-        <f>IF(I18&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2074,11 +2069,11 @@
         <v>9.6495599999999992</v>
       </c>
       <c r="S19">
-        <f>(0.000000000000000138*G19/(1.673534E-24*1.3*0.000000066726*F19*1.8986E+30/(E19*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>956.09264119622901</v>
       </c>
       <c r="T19">
-        <f>IF(I19&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2138,11 +2133,11 @@
         <v>7.9077599999999997</v>
       </c>
       <c r="S20">
-        <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>742.8583931109747</v>
       </c>
       <c r="T20">
-        <f>IF(I20&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2200,11 +2195,11 @@
         <v>9.5202500000000008</v>
       </c>
       <c r="S21" s="6">
-        <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>934.76971602454307</v>
       </c>
       <c r="T21" s="6">
-        <f>IF(I21&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
       <c r="U21" s="7" t="s">
@@ -2267,11 +2262,11 @@
         <v>8.4183900000000005</v>
       </c>
       <c r="S22">
-        <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>574.11765847468712</v>
       </c>
       <c r="T22">
-        <f>IF(I22&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2331,11 +2326,11 @@
         <v>7.8097899999999996</v>
       </c>
       <c r="S23">
-        <f>(0.000000000000000138*G23/(1.673534E-24*1.3*0.000000066726*F23*1.8986E+30/(E23*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>668.81110409377118</v>
       </c>
       <c r="T23">
-        <f>IF(I23&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2395,11 +2390,11 @@
         <v>9.2170199999999998</v>
       </c>
       <c r="S24">
-        <f>(0.000000000000000138*G24/(1.673534E-24*1.3*0.000000066726*F24*1.8986E+30/(E24*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1103.5971886171305</v>
       </c>
       <c r="T24">
-        <f>IF(I24&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2456,11 +2451,11 @@
         <v>9.7262599999999999</v>
       </c>
       <c r="S25">
-        <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>662.28004924519439</v>
       </c>
       <c r="T25">
-        <f>IF(I25&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2520,11 +2515,11 @@
         <v>7.8311200000000003</v>
       </c>
       <c r="S26">
-        <f>(0.000000000000000138*G26/(1.673534E-24*1.3*0.000000066726*F26*1.8986E+30/(E26*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>3894.9775251994533</v>
       </c>
       <c r="T26">
-        <f>IF(I26&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2584,11 +2579,11 @@
         <v>9.2088699999999992</v>
       </c>
       <c r="S27">
-        <f>(0.000000000000000138*G27/(1.673534E-24*1.3*0.000000066726*F27*1.8986E+30/(E27*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>948.15286253702118</v>
       </c>
       <c r="T27">
-        <f>IF(I27&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2648,11 +2643,11 @@
         <v>9.8633100000000002</v>
       </c>
       <c r="S28">
-        <f>(0.000000000000000138*G28/(1.673534E-24*1.3*0.000000066726*F28*1.8986E+30/(E28*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>443.85469120292152</v>
       </c>
       <c r="T28">
-        <f>IF(I28&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2712,11 +2707,11 @@
         <v>8.5839300000000005</v>
       </c>
       <c r="S29">
-        <f>(0.000000000000000138*G29/(1.673534E-24*1.3*0.000000066726*F29*1.8986E+30/(E29*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>570.64953846380126</v>
       </c>
       <c r="T29">
-        <f>IF(I29&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2776,11 +2771,11 @@
         <v>7.5749199999999997</v>
       </c>
       <c r="S30">
-        <f>(0.000000000000000138*G30/(1.673534E-24*1.3*0.000000066726*F30*1.8986E+30/(E30*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>518.80488815900412</v>
       </c>
       <c r="T30">
-        <f>IF(I30&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
@@ -2840,11 +2835,11 @@
         <v>8.23752</v>
       </c>
       <c r="S31">
-        <f>(0.000000000000000138*G31/(1.673534E-24*1.3*0.000000066726*F31*1.8986E+30/(E31*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>99.730517672190274</v>
       </c>
       <c r="T31">
-        <f>IF(I31&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2901,11 +2896,11 @@
         <v>9.7632399999999997</v>
       </c>
       <c r="S32">
-        <f>(0.000000000000000138*G32/(1.673534E-24*1.3*0.000000066726*F32*1.8986E+30/(E32*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>582.97620763372299</v>
       </c>
       <c r="T32">
-        <f>IF(I32&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -2965,11 +2960,11 @@
         <v>9.95702</v>
       </c>
       <c r="S33">
-        <f>(0.000000000000000138*G33/(1.673534E-24*1.3*0.000000066726*F33*1.8986E+30/(E33*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>1492.9814393090719</v>
       </c>
       <c r="T33">
-        <f>IF(I33&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -3029,11 +3024,11 @@
         <v>8.4517299999999995</v>
       </c>
       <c r="S34">
-        <f>(0.000000000000000138*G34/(1.673534E-24*1.3*0.000000066726*F34*1.8986E+30/(E34*7149200000)^2))/100000</f>
+        <f t="shared" si="0"/>
         <v>965.25628287035329</v>
       </c>
       <c r="T34">
-        <f>IF(I34&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -3041,63 +3036,85 @@
       <c r="A35" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="6">
+      <c r="B35" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="19">
         <v>1.4811235</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="19">
         <v>3.4619999999999998E-2</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="19">
         <v>1.891</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="19">
         <v>2.88</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="19">
         <v>4050</v>
       </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="S35" s="6"/>
+      <c r="H35" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35" s="19">
+        <v>10170</v>
+      </c>
+      <c r="J35" s="19">
+        <v>2.3620000000000001</v>
+      </c>
+      <c r="K35" s="19">
+        <v>2.52</v>
+      </c>
+      <c r="L35" s="19">
+        <v>-0.03</v>
+      </c>
+      <c r="M35" s="19">
+        <v>4.093</v>
+      </c>
+      <c r="N35" s="19">
+        <v>307.85989979999999</v>
+      </c>
+      <c r="O35" s="19">
+        <v>39.9389161</v>
+      </c>
+      <c r="P35" s="19">
+        <v>204.45500000000001</v>
+      </c>
+      <c r="Q35" s="19">
+        <v>7.55</v>
+      </c>
+      <c r="R35" s="19">
+        <v>7.5767499999999997</v>
+      </c>
+      <c r="S35" s="19">
+        <f t="shared" si="0"/>
+        <v>1286.8653667451285</v>
+      </c>
       <c r="T35" s="6"/>
       <c r="U35" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="17">
+      <c r="I36" s="16">
         <v>7433.197265625</v>
       </c>
-      <c r="J36" s="17"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17">
+      <c r="J36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16">
         <v>286.97138676797078</v>
       </c>
-      <c r="O36" s="17">
+      <c r="O36" s="16">
         <v>46.868244058307063</v>
       </c>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="17">
+      <c r="Q36" s="16">
         <v>10.382340431213381</v>
       </c>
-      <c r="R36" s="17">
+      <c r="R36" s="16">
         <v>10.382340431213381</v>
       </c>
     </row>
@@ -3154,11 +3171,11 @@
         <v>10.367800000000001</v>
       </c>
       <c r="S37">
-        <f>(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
+        <f t="shared" ref="S37:S63" si="2">(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
         <v>160.76196513632402</v>
       </c>
       <c r="T37">
-        <f>IF(I37&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T37:T63" si="3">IF(I37&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
@@ -3218,11 +3235,11 @@
         <v>9.6000599999999991</v>
       </c>
       <c r="S38">
-        <f>(0.000000000000000138*G38/(1.673534E-24*1.3*0.000000066726*F38*1.8986E+30/(E38*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>972.96006983022733</v>
       </c>
       <c r="T38">
-        <f>IF(I38&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3282,11 +3299,11 @@
         <v>8.2424300000000006</v>
       </c>
       <c r="S39">
-        <f>(0.000000000000000138*G39/(1.673534E-24*1.3*0.000000066726*F39*1.8986E+30/(E39*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>457.63140850776114</v>
       </c>
       <c r="T39">
-        <f>IF(I39&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3346,11 +3363,11 @@
         <v>8.1740100000000009</v>
       </c>
       <c r="S40">
-        <f>(0.000000000000000138*G40/(1.673534E-24*1.3*0.000000066726*F40*1.8986E+30/(E40*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>789.006338593706</v>
       </c>
       <c r="T40">
-        <f>IF(I40&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3410,11 +3427,11 @@
         <v>9.4290710000000004</v>
       </c>
       <c r="S41" s="6">
-        <f>(0.000000000000000138*G41/(1.673534E-24*1.3*0.000000066726*F41*1.8986E+30/(E41*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>56.120615203365361</v>
       </c>
       <c r="T41" s="6">
-        <f>IF(I41&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
       <c r="U41" s="7" t="s">
@@ -3477,11 +3494,11 @@
         <v>9.4135299999999997</v>
       </c>
       <c r="S42">
-        <f>(0.000000000000000138*G42/(1.673534E-24*1.3*0.000000066726*F42*1.8986E+30/(E42*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1175.9460676296278</v>
       </c>
       <c r="T42">
-        <f>IF(I42&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3538,11 +3555,11 @@
         <v>9.3678899999999992</v>
       </c>
       <c r="S43">
-        <f>(0.000000000000000138*G43/(1.673534E-24*1.3*0.000000066726*F43*1.8986E+30/(E43*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1399.2265914107247</v>
       </c>
       <c r="T43">
-        <f>IF(I43&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3599,11 +3616,11 @@
         <v>9.3503900000000009</v>
       </c>
       <c r="S44">
-        <f>(0.000000000000000138*G44/(1.673534E-24*1.3*0.000000066726*F44*1.8986E+30/(E44*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>353.31388599481477</v>
       </c>
       <c r="T44">
-        <f>IF(I44&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3663,11 +3680,11 @@
         <v>9.1879500000000007</v>
       </c>
       <c r="S45">
-        <f>(0.000000000000000138*G45/(1.673534E-24*1.3*0.000000066726*F45*1.8986E+30/(E45*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>882.20971786077962</v>
       </c>
       <c r="T45">
-        <f>IF(I45&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3727,11 +3744,11 @@
         <v>7.9756099999999996</v>
       </c>
       <c r="S46">
-        <f>(0.000000000000000138*G46/(1.673534E-24*1.3*0.000000066726*F46*1.8986E+30/(E46*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>431.57254486096394</v>
       </c>
       <c r="T46">
-        <f>IF(I46&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3791,11 +3808,11 @@
         <v>8.8952899999999993</v>
       </c>
       <c r="S47">
-        <f>(0.000000000000000138*G47/(1.673534E-24*1.3*0.000000066726*F47*1.8986E+30/(E47*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>974.78820571370204</v>
       </c>
       <c r="T47">
-        <f>IF(I47&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -3855,11 +3872,11 @@
         <v>9.5843900000000009</v>
       </c>
       <c r="S48">
-        <f>(0.000000000000000138*G48/(1.673534E-24*1.3*0.000000066726*F48*1.8986E+30/(E48*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1460.8182255852041</v>
       </c>
       <c r="T48">
-        <f>IF(I48&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3916,11 +3933,11 @@
         <v>9.6598100000000002</v>
       </c>
       <c r="S49">
-        <f>(0.000000000000000138*G49/(1.673534E-24*1.3*0.000000066726*F49*1.8986E+30/(E49*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1324.5165539963698</v>
       </c>
       <c r="T49">
-        <f>IF(I49&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -3977,11 +3994,11 @@
         <v>9.7596699999999998</v>
       </c>
       <c r="S50">
-        <f>(0.000000000000000138*G50/(1.673534E-24*1.3*0.000000066726*F50*1.8986E+30/(E50*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>55.915145726222889</v>
       </c>
       <c r="T50">
-        <f>IF(I50&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -4038,11 +4055,11 @@
         <v>8.9365100000000002</v>
       </c>
       <c r="S51">
-        <f>(0.000000000000000138*G51/(1.673534E-24*1.3*0.000000066726*F51*1.8986E+30/(E51*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>77.040187113891676</v>
       </c>
       <c r="T51">
-        <f>IF(I51&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4099,11 +4116,11 @@
         <v>9.4724400000000006</v>
       </c>
       <c r="S52">
-        <f>(0.000000000000000138*G52/(1.673534E-24*1.3*0.000000066726*F52*1.8986E+30/(E52*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>83.670803141549356</v>
       </c>
       <c r="T52">
-        <f>IF(I52&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
@@ -4160,11 +4177,11 @@
         <v>7.4165299999999998</v>
       </c>
       <c r="S53">
-        <f>(0.000000000000000138*G53/(1.673534E-24*1.3*0.000000066726*F53*1.8986E+30/(E53*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>777.64358420307099</v>
       </c>
       <c r="T53">
-        <f>IF(I53&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4224,11 +4241,11 @@
         <v>9.7777600000000007</v>
       </c>
       <c r="S54">
-        <f>(0.000000000000000138*G54/(1.673534E-24*1.3*0.000000066726*F54*1.8986E+30/(E54*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>755.33252275944176</v>
       </c>
       <c r="T54">
-        <f>IF(I54&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4285,11 +4302,11 @@
         <v>9.641</v>
       </c>
       <c r="S55">
-        <f>(0.000000000000000138*G55/(1.673534E-24*1.3*0.000000066726*F55*1.8986E+30/(E55*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>318.17832033985127</v>
       </c>
       <c r="T55">
-        <f>IF(I55&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4349,11 +4366,11 @@
         <v>9.0746900000000004</v>
       </c>
       <c r="S56">
-        <f>(0.000000000000000138*G56/(1.673534E-24*1.3*0.000000066726*F56*1.8986E+30/(E56*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>36.149567272802649</v>
       </c>
       <c r="T56">
-        <f>IF(I56&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4413,11 +4430,11 @@
         <v>9.8465900000000008</v>
       </c>
       <c r="S57">
-        <f>(0.000000000000000138*G57/(1.673534E-24*1.3*0.000000066726*F57*1.8986E+30/(E57*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>224.58825733889913</v>
       </c>
       <c r="T57">
-        <f>IF(I57&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4474,11 +4491,11 @@
         <v>9.6080000000000005</v>
       </c>
       <c r="S58">
-        <f>(0.000000000000000138*G58/(1.673534E-24*1.3*0.000000066726*F58*1.8986E+30/(E58*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1039.84328949877</v>
       </c>
       <c r="T58">
-        <f>IF(I58&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4538,11 +4555,11 @@
         <v>9.9823299999999993</v>
       </c>
       <c r="S59">
-        <f>(0.000000000000000138*G59/(1.673534E-24*1.3*0.000000066726*F59*1.8986E+30/(E59*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>1107.9861243219782</v>
       </c>
       <c r="T59">
-        <f>IF(I59&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4599,11 +4616,11 @@
         <v>9.7295700000000007</v>
       </c>
       <c r="S60">
-        <f>(0.000000000000000138*G60/(1.673534E-24*1.3*0.000000066726*F60*1.8986E+30/(E60*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>487.59044264912109</v>
       </c>
       <c r="T60">
-        <f>IF(I60&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4663,11 +4680,11 @@
         <v>8.8910300000000007</v>
       </c>
       <c r="S61">
-        <f>(0.000000000000000138*G61/(1.673534E-24*1.3*0.000000066726*F61*1.8986E+30/(E61*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>795.95548671567838</v>
       </c>
       <c r="T61">
-        <f>IF(I61&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4727,11 +4744,11 @@
         <v>9.6608199999999993</v>
       </c>
       <c r="S62">
-        <f>(0.000000000000000138*G62/(1.673534E-24*1.3*0.000000066726*F62*1.8986E+30/(E62*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>355.42536038318485</v>
       </c>
       <c r="T62">
-        <f>IF(I62&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
@@ -4791,45 +4808,43 @@
         <v>8.9943600000000004</v>
       </c>
       <c r="S63">
-        <f>(0.000000000000000138*G63/(1.673534E-24*1.3*0.000000066726*F63*1.8986E+30/(E63*7149200000)^2))/100000</f>
+        <f t="shared" si="2"/>
         <v>267.77715667890726</v>
       </c>
       <c r="T63">
-        <f>IF(I63&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="H64" s="11"/>
-      <c r="I64" s="17">
+      <c r="I64" s="16">
         <v>6161.02294921875</v>
       </c>
-      <c r="J64" s="17">
+      <c r="J64" s="16">
         <v>1.7061723470687871</v>
       </c>
-      <c r="K64" s="11">
+      <c r="K64">
         <v>1.3463604</v>
       </c>
-      <c r="L64" s="11"/>
-      <c r="M64" s="17">
+      <c r="M64" s="16">
         <v>3.9825000762939449</v>
       </c>
-      <c r="N64" s="11">
+      <c r="N64">
         <v>268.30433503422898</v>
       </c>
-      <c r="O64" s="17">
+      <c r="O64" s="16">
         <v>37.211736733677057</v>
       </c>
-      <c r="P64" s="11">
+      <c r="P64">
         <v>496.26729999999998</v>
       </c>
-      <c r="Q64" s="17">
+      <c r="Q64" s="16">
         <v>11.469913482666019</v>
       </c>
-      <c r="R64" s="17">
+      <c r="R64" s="16">
         <v>11.469913482666019</v>
       </c>
     </row>
@@ -4859,7 +4874,7 @@
         <v>11.4986</v>
       </c>
       <c r="T65">
-        <f>IF(I65&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T65:T85" si="4">IF(I65&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -4919,11 +4934,11 @@
         <v>9.8670799999999996</v>
       </c>
       <c r="S66">
-        <f>(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
+        <f t="shared" ref="S66:S85" si="5">(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
         <v>2057.1154637812851</v>
       </c>
       <c r="T66">
-        <f>IF(I66&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -4983,11 +4998,11 @@
         <v>9.8192900000000005</v>
       </c>
       <c r="S67">
-        <f>(0.000000000000000138*G67/(1.673534E-24*1.3*0.000000066726*F67*1.8986E+30/(E67*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>621.55661806820979</v>
       </c>
       <c r="T67">
-        <f>IF(I67&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5044,11 +5059,11 @@
         <v>9.6464700000000008</v>
       </c>
       <c r="S68">
-        <f>(0.000000000000000138*G68/(1.673534E-24*1.3*0.000000066726*F68*1.8986E+30/(E68*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>103.20465157174387</v>
       </c>
       <c r="T68">
-        <f>IF(I68&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5108,11 +5123,11 @@
         <v>9.2569999999999997</v>
       </c>
       <c r="S69">
-        <f>(0.000000000000000138*G69/(1.673534E-24*1.3*0.000000066726*F69*1.8986E+30/(E69*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>1277.1766379712274</v>
       </c>
       <c r="T69">
-        <f>IF(I69&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5172,11 +5187,11 @@
         <v>9.9122599999999998</v>
       </c>
       <c r="S70">
-        <f>(0.000000000000000138*G70/(1.673534E-24*1.3*0.000000066726*F70*1.8986E+30/(E70*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>1247.4798366438731</v>
       </c>
       <c r="T70">
-        <f>IF(I70&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-7</v>
       </c>
     </row>
@@ -5236,11 +5251,11 @@
         <v>9.1661699999999993</v>
       </c>
       <c r="S71">
-        <f>(0.000000000000000138*G71/(1.673534E-24*1.3*0.000000066726*F71*1.8986E+30/(E71*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>93.704022194109143</v>
       </c>
       <c r="T71">
-        <f>IF(I71&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5298,11 +5313,11 @@
         <v>6.5536899999999996</v>
       </c>
       <c r="S72" s="8">
-        <f>(0.000000000000000138*G72/(1.673534E-24*1.3*0.000000066726*F72*1.8986E+30/(E72*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>1130.2166328238993</v>
       </c>
       <c r="T72" s="6">
-        <f>IF(I72&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-7</v>
       </c>
       <c r="U72" s="7" t="s">
@@ -5365,11 +5380,11 @@
         <v>8.0700400000000005</v>
       </c>
       <c r="S73">
-        <f>(0.000000000000000138*G73/(1.673534E-24*1.3*0.000000066726*F73*1.8986E+30/(E73*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>863.09804630713359</v>
       </c>
       <c r="T73">
-        <f>IF(I73&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-7</v>
       </c>
     </row>
@@ -5429,11 +5444,11 @@
         <v>9.20974</v>
       </c>
       <c r="S74">
-        <f>(0.000000000000000138*G74/(1.673534E-24*1.3*0.000000066726*F74*1.8986E+30/(E74*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>140.68549179703928</v>
       </c>
       <c r="T74">
-        <f>IF(I74&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5493,11 +5508,11 @@
         <v>9.4846599999999999</v>
       </c>
       <c r="S75" s="6">
-        <f>(0.000000000000000138*G75/(1.673534E-24*1.3*0.000000066726*F75*1.8986E+30/(E75*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>955.72600175951948</v>
       </c>
       <c r="T75" s="6">
-        <f>IF(I75&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
       <c r="U75" s="7" t="s">
@@ -5557,11 +5572,11 @@
         <v>9.3767099999999992</v>
       </c>
       <c r="S76">
-        <f>(0.000000000000000138*G76/(1.673534E-24*1.3*0.000000066726*F76*1.8986E+30/(E76*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>701.18164217622461</v>
       </c>
       <c r="T76">
-        <f>IF(I76&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5621,11 +5636,11 @@
         <v>9.5723000000000003</v>
       </c>
       <c r="S77">
-        <f>(0.000000000000000138*G77/(1.673534E-24*1.3*0.000000066726*F77*1.8986E+30/(E77*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>1226.0598654781754</v>
       </c>
       <c r="T77">
-        <f>IF(I77&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5685,11 +5700,11 @@
         <v>9.3950700000000005</v>
       </c>
       <c r="S78">
-        <f>(0.000000000000000138*G78/(1.673534E-24*1.3*0.000000066726*F78*1.8986E+30/(E78*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>2192.2225820487197</v>
       </c>
       <c r="T78">
-        <f>IF(I78&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5749,11 +5764,11 @@
         <v>9.9720200000000006</v>
       </c>
       <c r="S79">
-        <f>(0.000000000000000138*G79/(1.673534E-24*1.3*0.000000066726*F79*1.8986E+30/(E79*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>1209.5375438309629</v>
       </c>
       <c r="T79">
-        <f>IF(I79&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5813,11 +5828,11 @@
         <v>9.6124899999999993</v>
       </c>
       <c r="S80">
-        <f>(0.000000000000000138*G80/(1.673534E-24*1.3*0.000000066726*F80*1.8986E+30/(E80*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>136.24063220140397</v>
       </c>
       <c r="T80">
-        <f>IF(I80&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
@@ -5846,10 +5861,10 @@
       <c r="H81" t="s">
         <v>127</v>
       </c>
-      <c r="I81" s="16">
+      <c r="I81" s="15">
         <v>6480</v>
       </c>
-      <c r="J81" s="16">
+      <c r="J81" s="15">
         <v>2.1</v>
       </c>
       <c r="K81">
@@ -5858,38 +5873,38 @@
       <c r="L81">
         <v>0.12</v>
       </c>
-      <c r="M81" s="16">
+      <c r="M81" s="15">
         <v>3.96</v>
       </c>
-      <c r="N81" s="16">
+      <c r="N81" s="15">
         <v>72.660591600000004</v>
       </c>
-      <c r="O81" s="16">
+      <c r="O81" s="15">
         <v>1.8938364999999999</v>
       </c>
       <c r="P81">
         <v>275.66399999999999</v>
       </c>
-      <c r="Q81" s="16">
+      <c r="Q81" s="15">
         <v>10.073</v>
       </c>
-      <c r="R81" s="20">
+      <c r="R81" s="18">
         <v>9.8979599999999994</v>
       </c>
       <c r="S81">
-        <f>(0.000000000000000138*G81/(1.673534E-24*1.3*0.000000066726*F81*1.8986E+30/(E81*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>1257.117296864338</v>
       </c>
       <c r="T81">
-        <f>IF(I81&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="15" t="s">
         <v>20</v>
       </c>
       <c r="C82">
@@ -5910,10 +5925,10 @@
       <c r="H82" t="s">
         <v>54</v>
       </c>
-      <c r="I82" s="16">
+      <c r="I82" s="15">
         <v>6170</v>
       </c>
-      <c r="J82" s="16">
+      <c r="J82" s="15">
         <v>1.48</v>
       </c>
       <c r="K82">
@@ -5922,35 +5937,35 @@
       <c r="L82">
         <v>0.26</v>
       </c>
-      <c r="M82" s="16">
+      <c r="M82" s="15">
         <v>4.2699999999999996</v>
       </c>
-      <c r="N82" s="16">
+      <c r="N82" s="15">
         <v>313.78323929999999</v>
       </c>
-      <c r="O82" s="16">
+      <c r="O82" s="15">
         <v>-34.135751200000001</v>
       </c>
       <c r="P82">
         <v>211.21100000000001</v>
       </c>
-      <c r="Q82" s="16">
+      <c r="Q82" s="15">
         <v>10.051</v>
       </c>
-      <c r="R82" s="20">
+      <c r="R82" s="18">
         <v>10.028499999999999</v>
       </c>
       <c r="S82">
-        <f>(0.000000000000000138*G82/(1.673534E-24*1.3*0.000000066726*F82*1.8986E+30/(E82*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>2049.4439875099679</v>
       </c>
       <c r="T82">
-        <f>IF(I82&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="12" t="s">
         <v>133</v>
       </c>
       <c r="B83" t="s">
@@ -5974,10 +5989,10 @@
       <c r="H83" t="s">
         <v>134</v>
       </c>
-      <c r="I83" s="16">
+      <c r="I83" s="15">
         <v>5830</v>
       </c>
-      <c r="J83" s="16">
+      <c r="J83" s="15">
         <v>1.23</v>
       </c>
       <c r="K83">
@@ -5986,35 +6001,35 @@
       <c r="L83">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M83" s="16">
+      <c r="M83" s="15">
         <v>4.3600000000000003</v>
       </c>
-      <c r="N83" s="16">
+      <c r="N83" s="15">
         <v>337.45782430000003</v>
       </c>
-      <c r="O83" s="16">
+      <c r="O83" s="15">
         <v>-48.003098799999997</v>
       </c>
       <c r="P83">
         <v>137.54400000000001</v>
       </c>
-      <c r="Q83" s="16">
+      <c r="Q83" s="15">
         <v>10.092000000000001</v>
       </c>
-      <c r="R83" s="20">
+      <c r="R83" s="18">
         <v>9.9369700000000005</v>
       </c>
       <c r="S83">
-        <f>(0.000000000000000138*G83/(1.673534E-24*1.3*0.000000066726*F83*1.8986E+30/(E83*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>422.11900227636102</v>
       </c>
       <c r="T83">
-        <f>IF(I83&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="12" t="s">
         <v>79</v>
       </c>
       <c r="B84" t="s">
@@ -6035,50 +6050,50 @@
       <c r="G84">
         <v>1480</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" t="s">
         <v>54</v>
       </c>
-      <c r="I84" s="18">
+      <c r="I84" s="15">
         <v>6150</v>
       </c>
-      <c r="J84" s="18">
+      <c r="J84" s="15">
         <v>1.64</v>
       </c>
-      <c r="K84" s="11">
+      <c r="K84">
         <v>1.21</v>
       </c>
-      <c r="L84" s="11">
+      <c r="L84">
         <v>0.21</v>
       </c>
-      <c r="M84" s="18">
+      <c r="M84" s="15">
         <v>4.3</v>
       </c>
-      <c r="N84" s="18">
+      <c r="N84" s="15">
         <v>39.897668899999999</v>
       </c>
-      <c r="O84" s="18">
+      <c r="O84" s="15">
         <v>-50.008193400000003</v>
       </c>
-      <c r="P84" s="11">
+      <c r="P84">
         <v>158.66</v>
       </c>
-      <c r="Q84" s="18">
+      <c r="Q84" s="15">
         <v>9.4749999999999996</v>
       </c>
-      <c r="R84" s="18">
+      <c r="R84" s="15">
         <v>9.3251000000000008</v>
       </c>
       <c r="S84">
-        <f>(0.000000000000000138*G84/(1.673534E-24*1.3*0.000000066726*F84*1.8986E+30/(E84*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>162.15983922320817</v>
       </c>
       <c r="T84">
-        <f>IF(I84&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="12" t="s">
         <v>107</v>
       </c>
       <c r="B85" t="s">
@@ -6099,60 +6114,50 @@
       <c r="G85">
         <v>1729</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" t="s">
         <v>108</v>
       </c>
-      <c r="I85" s="19">
+      <c r="I85" s="17">
         <v>6429</v>
       </c>
-      <c r="J85" s="19">
+      <c r="J85" s="17">
         <v>1.54</v>
       </c>
-      <c r="K85" s="11">
+      <c r="K85">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L85" s="11">
+      <c r="L85">
         <v>-0.18</v>
       </c>
-      <c r="M85" s="19">
+      <c r="M85" s="17">
         <v>3.95</v>
       </c>
-      <c r="N85" s="11">
+      <c r="N85">
         <v>65.469581399999996</v>
       </c>
-      <c r="O85" s="19">
+      <c r="O85" s="17">
         <v>57.817209499999997</v>
       </c>
-      <c r="P85" s="11">
+      <c r="P85">
         <v>213.053</v>
       </c>
-      <c r="Q85" s="19">
+      <c r="Q85" s="17">
         <v>9.8539999999999992</v>
       </c>
-      <c r="R85" s="19">
+      <c r="R85" s="17">
         <v>9.7388899999999996</v>
       </c>
       <c r="S85">
-        <f>(0.000000000000000138*G85/(1.673534E-24*1.3*0.000000066726*F85*1.8986E+30/(E85*7149200000)^2))/100000</f>
+        <f t="shared" si="5"/>
         <v>120.66830436099001</v>
       </c>
       <c r="T85">
-        <f>IF(I85&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="H86" s="11"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="11"/>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="11"/>
-      <c r="O86" s="11"/>
-      <c r="P86" s="11"/>
-      <c r="Q86" s="11"/>
-      <c r="R86" s="11"/>
+      <c r="R86"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U79" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D4D5BB-BFFC-0C4C-988C-A73FCF734FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0968ED-5547-EE4A-A5BC-D62327CC2110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22040" yWindow="820" windowWidth="33600" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3080" yWindow="860" windowWidth="30820" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="154">
   <si>
     <t>#pl_name</t>
   </si>
@@ -471,6 +471,33 @@
   </si>
   <si>
     <t>B9.5-A0</t>
+  </si>
+  <si>
+    <t>V_MAG</t>
+  </si>
+  <si>
+    <t>B_MAG</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>4236349174325957504 b</t>
+  </si>
+  <si>
+    <t>DWARF</t>
+  </si>
+  <si>
+    <t>4186786759262834816 b</t>
+  </si>
+  <si>
+    <t>GIANT</t>
+  </si>
+  <si>
+    <t>4999199962400320128 b</t>
+  </si>
+  <si>
+    <t>4760966338470589184 b</t>
   </si>
 </sst>
 </file>
@@ -480,7 +507,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,8 +529,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -540,8 +573,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -590,13 +629,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -647,6 +701,28 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -924,14 +1000,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH86"/>
+  <dimension ref="A1:BH89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
     <col min="3" max="4" width="12.5"/>
     <col min="5" max="6" width="11.33203125"/>
-    <col min="7" max="10" width="8.1640625"/>
+    <col min="7" max="8" width="8.1640625"/>
+    <col min="9" max="9" width="9.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625"/>
     <col min="11" max="11" width="9.1640625"/>
     <col min="14" max="15" width="12.5"/>
     <col min="16" max="16" width="9"/>
@@ -983,7 +1061,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1021,13 +1099,22 @@
       </c>
       <c r="U1" s="4" t="s">
         <v>136</v>
+      </c>
+      <c r="V1" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="W1" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="X1" s="20" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="22">
         <v>4907.77490234375</v>
       </c>
       <c r="J2" s="16"/>
@@ -1073,7 +1160,7 @@
       <c r="H3" t="s">
         <v>27</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="21">
         <v>5980</v>
       </c>
       <c r="J3">
@@ -1140,7 +1227,7 @@
       <c r="H4" t="s">
         <v>125</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="21">
         <v>6600</v>
       </c>
       <c r="J4">
@@ -1207,7 +1294,7 @@
       <c r="H5" t="s">
         <v>54</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="21">
         <v>6380</v>
       </c>
       <c r="J5">
@@ -1274,7 +1361,7 @@
       <c r="H6" t="s">
         <v>94</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="21">
         <v>5302</v>
       </c>
       <c r="J6">
@@ -1321,7 +1408,7 @@
         <v>140</v>
       </c>
       <c r="B7" s="14"/>
-      <c r="I7" s="16">
+      <c r="I7" s="22">
         <v>6245.11328125</v>
       </c>
       <c r="J7" s="16">
@@ -1371,7 +1458,7 @@
       <c r="G8">
         <v>1772</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="21">
         <v>6212</v>
       </c>
       <c r="J8">
@@ -1435,7 +1522,7 @@
       <c r="G9">
         <v>1930</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="21">
         <v>7394</v>
       </c>
       <c r="J9">
@@ -1478,7 +1565,7 @@
       <c r="A10" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="22">
         <v>6424.27685546875</v>
       </c>
       <c r="J10" s="16">
@@ -1520,7 +1607,7 @@
       <c r="G11">
         <v>2562</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="21">
         <v>8450</v>
       </c>
       <c r="J11">
@@ -1587,7 +1674,7 @@
       <c r="H12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="23">
         <v>5742</v>
       </c>
       <c r="J12" s="2">
@@ -1651,7 +1738,7 @@
       <c r="H13" t="s">
         <v>31</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="21">
         <v>5521</v>
       </c>
       <c r="J13">
@@ -1715,7 +1802,7 @@
       <c r="H14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="23">
         <v>6179</v>
       </c>
       <c r="J14" s="2">
@@ -1782,7 +1869,7 @@
       <c r="H15" t="s">
         <v>43</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="21">
         <v>6310</v>
       </c>
       <c r="J15">
@@ -1846,7 +1933,7 @@
       <c r="H16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="23">
         <v>5052</v>
       </c>
       <c r="J16" s="2">
@@ -1910,7 +1997,7 @@
       <c r="G17">
         <v>2132</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="21">
         <v>6272</v>
       </c>
       <c r="J17">
@@ -1974,7 +2061,7 @@
       <c r="H18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="23">
         <v>6091</v>
       </c>
       <c r="J18" s="2">
@@ -2038,7 +2125,7 @@
       <c r="H19" t="s">
         <v>94</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="21">
         <v>5540</v>
       </c>
       <c r="J19">
@@ -2102,7 +2189,7 @@
       <c r="H20" t="s">
         <v>45</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="21">
         <v>5080</v>
       </c>
       <c r="J20">
@@ -2164,7 +2251,7 @@
         <v>2061</v>
       </c>
       <c r="H21" s="6"/>
-      <c r="I21" s="6">
+      <c r="I21" s="24">
         <v>6801</v>
       </c>
       <c r="J21" s="6">
@@ -2231,7 +2318,7 @@
       <c r="H22" t="s">
         <v>54</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="21">
         <v>6128</v>
       </c>
       <c r="J22">
@@ -2295,7 +2382,7 @@
       <c r="H23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="23">
         <v>5392</v>
       </c>
       <c r="J23" s="2">
@@ -2359,7 +2446,7 @@
       <c r="H24" t="s">
         <v>33</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="21">
         <v>5576</v>
       </c>
       <c r="J24">
@@ -2420,7 +2507,7 @@
       <c r="G25">
         <v>1030</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="21">
         <v>6154</v>
       </c>
       <c r="J25">
@@ -2484,7 +2571,7 @@
       <c r="H26" t="s">
         <v>37</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="21">
         <v>5375</v>
       </c>
       <c r="J26">
@@ -2548,7 +2635,7 @@
       <c r="H27" t="s">
         <v>41</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="21">
         <v>7454</v>
       </c>
       <c r="J27">
@@ -2612,7 +2699,7 @@
       <c r="H28" t="s">
         <v>110</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="21">
         <v>7500</v>
       </c>
       <c r="J28">
@@ -2676,7 +2763,7 @@
       <c r="H29" t="s">
         <v>54</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="21">
         <v>6327</v>
       </c>
       <c r="J29">
@@ -2740,7 +2827,7 @@
       <c r="H30" t="s">
         <v>24</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="21">
         <v>8720</v>
       </c>
       <c r="J30">
@@ -2804,7 +2891,7 @@
       <c r="H31" t="s">
         <v>52</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="21">
         <v>6426</v>
       </c>
       <c r="J31">
@@ -2865,7 +2952,7 @@
       <c r="G32">
         <v>1816</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="21">
         <v>6304</v>
       </c>
       <c r="J32">
@@ -2929,7 +3016,7 @@
       <c r="H33" t="s">
         <v>56</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="21">
         <v>6206</v>
       </c>
       <c r="J33">
@@ -2993,7 +3080,7 @@
       <c r="H34" t="s">
         <v>56</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="21">
         <v>6768</v>
       </c>
       <c r="J34">
@@ -3057,8 +3144,8 @@
       <c r="H35" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="I35" s="19">
-        <v>10170</v>
+      <c r="I35" s="25">
+        <v>10170.1</v>
       </c>
       <c r="J35" s="19">
         <v>2.3620000000000001</v>
@@ -3100,7 +3187,7 @@
       <c r="A36" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="22">
         <v>7433.197265625</v>
       </c>
       <c r="J36" s="16"/>
@@ -3140,7 +3227,7 @@
       <c r="G37">
         <v>2550</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="21">
         <v>7650</v>
       </c>
       <c r="J37">
@@ -3204,7 +3291,7 @@
       <c r="H38" t="s">
         <v>99</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="21">
         <v>5443</v>
       </c>
       <c r="J38">
@@ -3268,7 +3355,7 @@
       <c r="H39" t="s">
         <v>49</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="21">
         <v>7490</v>
       </c>
       <c r="J39">
@@ -3332,7 +3419,7 @@
       <c r="H40" t="s">
         <v>47</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="21">
         <v>7800</v>
       </c>
       <c r="J40">
@@ -3396,7 +3483,7 @@
       <c r="H41" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="24">
         <v>5756</v>
       </c>
       <c r="J41" s="6">
@@ -3463,7 +3550,7 @@
       <c r="H42" t="s">
         <v>43</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="21">
         <v>5962.7</v>
       </c>
       <c r="J42">
@@ -3524,7 +3611,7 @@
       <c r="G43">
         <v>843</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="21">
         <v>5770</v>
       </c>
       <c r="J43">
@@ -3585,7 +3672,7 @@
       <c r="G44">
         <v>1679</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="21">
         <v>6274</v>
       </c>
       <c r="J44">
@@ -3649,7 +3736,7 @@
       <c r="H45" t="s">
         <v>70</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="21">
         <v>6117</v>
       </c>
       <c r="J45">
@@ -3713,7 +3800,7 @@
       <c r="H46" t="s">
         <v>35</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="21">
         <v>7690</v>
       </c>
       <c r="J46">
@@ -3777,7 +3864,7 @@
       <c r="H47" t="s">
         <v>61</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="21">
         <v>7300</v>
       </c>
       <c r="J47">
@@ -3841,7 +3928,7 @@
       <c r="H48" t="s">
         <v>56</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="21">
         <v>5991</v>
       </c>
       <c r="J48">
@@ -3902,7 +3989,7 @@
       <c r="G49">
         <v>1199.55</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="21">
         <v>6039</v>
       </c>
       <c r="J49">
@@ -3963,7 +4050,7 @@
       <c r="G50">
         <v>1221.3900000000001</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="21">
         <v>7130</v>
       </c>
       <c r="J50">
@@ -4024,7 +4111,7 @@
       <c r="G51">
         <v>1363.43</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="21">
         <v>6200</v>
       </c>
       <c r="J51">
@@ -4085,7 +4172,7 @@
       <c r="G52">
         <v>1595</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="21">
         <v>7360</v>
       </c>
       <c r="J52">
@@ -4146,7 +4233,7 @@
       <c r="G53">
         <v>1027</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="21">
         <v>6095</v>
       </c>
       <c r="J53">
@@ -4210,7 +4297,7 @@
       <c r="H54" t="s">
         <v>116</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="21">
         <v>5291</v>
       </c>
       <c r="J54">
@@ -4271,7 +4358,7 @@
       <c r="G55">
         <v>1655</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="21">
         <v>4896</v>
       </c>
       <c r="J55">
@@ -4335,7 +4422,7 @@
       <c r="H56" t="s">
         <v>56</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="21">
         <v>6264</v>
       </c>
       <c r="J56">
@@ -4399,7 +4486,7 @@
       <c r="H57" t="s">
         <v>120</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="21">
         <v>5735</v>
       </c>
       <c r="J57">
@@ -4460,7 +4547,7 @@
       <c r="G58">
         <v>1180</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="21">
         <v>5808</v>
       </c>
       <c r="J58">
@@ -4524,7 +4611,7 @@
       <c r="H59" t="s">
         <v>130</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="21">
         <v>6000</v>
       </c>
       <c r="J59">
@@ -4585,7 +4672,7 @@
       <c r="G60">
         <v>1439</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="21">
         <v>6110</v>
       </c>
       <c r="J60">
@@ -4649,7 +4736,7 @@
       <c r="H61" t="s">
         <v>63</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="21">
         <v>6400</v>
       </c>
       <c r="J61">
@@ -4713,7 +4800,7 @@
       <c r="H62" t="s">
         <v>54</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="21">
         <v>6295</v>
       </c>
       <c r="J62">
@@ -4777,7 +4864,7 @@
       <c r="H63" t="s">
         <v>66</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="21">
         <v>6643</v>
       </c>
       <c r="J63">
@@ -4820,7 +4907,7 @@
       <c r="A64" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="I64" s="16">
+      <c r="I64" s="22">
         <v>6161.02294921875</v>
       </c>
       <c r="J64" s="16">
@@ -4855,7 +4942,7 @@
       <c r="B65" t="s">
         <v>20</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="21">
         <v>6200</v>
       </c>
       <c r="J65">
@@ -4903,7 +4990,7 @@
       <c r="H66" t="s">
         <v>43</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="21">
         <v>5990</v>
       </c>
       <c r="J66">
@@ -4967,7 +5054,7 @@
       <c r="H67" t="s">
         <v>56</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="21">
         <v>6250</v>
       </c>
       <c r="J67">
@@ -5028,7 +5115,7 @@
       <c r="G68">
         <v>1872</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="21">
         <v>6475</v>
       </c>
       <c r="J68">
@@ -5092,7 +5179,7 @@
       <c r="H69" t="s">
         <v>74</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="21">
         <v>6050</v>
       </c>
       <c r="J69">
@@ -5156,7 +5243,7 @@
       <c r="H70" t="s">
         <v>118</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="21">
         <v>9360</v>
       </c>
       <c r="J70">
@@ -5220,7 +5307,7 @@
       <c r="H71" t="s">
         <v>72</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="21">
         <v>6432</v>
       </c>
       <c r="J71">
@@ -5282,7 +5369,7 @@
         <v>3353</v>
       </c>
       <c r="H72" s="6"/>
-      <c r="I72" s="6">
+      <c r="I72" s="24">
         <v>8000</v>
       </c>
       <c r="J72" s="6">
@@ -5349,7 +5436,7 @@
       <c r="H73" t="s">
         <v>41</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="21">
         <v>7430</v>
       </c>
       <c r="J73">
@@ -5413,7 +5500,7 @@
       <c r="H74" t="s">
         <v>70</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="21">
         <v>6180</v>
       </c>
       <c r="J74">
@@ -5477,7 +5564,7 @@
       <c r="H75" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I75" s="6">
+      <c r="I75" s="24">
         <v>4792</v>
       </c>
       <c r="J75" s="6">
@@ -5541,7 +5628,7 @@
       <c r="G76">
         <v>1487</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="21">
         <v>6400</v>
       </c>
       <c r="J76">
@@ -5605,7 +5692,7 @@
       <c r="H77" t="s">
         <v>91</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="21">
         <v>5990</v>
       </c>
       <c r="J77">
@@ -5669,7 +5756,7 @@
       <c r="H78" t="s">
         <v>52</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="21">
         <v>6329</v>
       </c>
       <c r="J78">
@@ -5733,7 +5820,7 @@
       <c r="H79" t="s">
         <v>127</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="21">
         <v>6600</v>
       </c>
       <c r="J79">
@@ -5797,7 +5884,7 @@
       <c r="H80" t="s">
         <v>97</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="21">
         <v>5600</v>
       </c>
       <c r="J80">
@@ -5836,7 +5923,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>132</v>
       </c>
@@ -5861,7 +5948,7 @@
       <c r="H81" t="s">
         <v>127</v>
       </c>
-      <c r="I81" s="15">
+      <c r="I81" s="26">
         <v>6480</v>
       </c>
       <c r="J81" s="15">
@@ -5900,7 +5987,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12" t="s">
         <v>128</v>
       </c>
@@ -5925,7 +6012,7 @@
       <c r="H82" t="s">
         <v>54</v>
       </c>
-      <c r="I82" s="15">
+      <c r="I82" s="26">
         <v>6170</v>
       </c>
       <c r="J82" s="15">
@@ -5964,7 +6051,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12" t="s">
         <v>133</v>
       </c>
@@ -5989,7 +6076,7 @@
       <c r="H83" t="s">
         <v>134</v>
       </c>
-      <c r="I83" s="15">
+      <c r="I83" s="26">
         <v>5830</v>
       </c>
       <c r="J83" s="15">
@@ -6028,7 +6115,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12" t="s">
         <v>79</v>
       </c>
@@ -6053,7 +6140,7 @@
       <c r="H84" t="s">
         <v>54</v>
       </c>
-      <c r="I84" s="15">
+      <c r="I84" s="26">
         <v>6150</v>
       </c>
       <c r="J84" s="15">
@@ -6092,7 +6179,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>107</v>
       </c>
@@ -6117,7 +6204,7 @@
       <c r="H85" t="s">
         <v>108</v>
       </c>
-      <c r="I85" s="17">
+      <c r="I85" s="27">
         <v>6429</v>
       </c>
       <c r="J85" s="17">
@@ -6156,8 +6243,170 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A86" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="I86" s="26">
+        <v>3460</v>
+      </c>
+      <c r="J86" s="15">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="K86">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>4.6963999999999997</v>
+      </c>
+      <c r="N86">
+        <v>303.19871318011002</v>
+      </c>
+      <c r="O86">
+        <v>-0.37849292589</v>
+      </c>
+      <c r="P86">
+        <v>312.65899999999999</v>
+      </c>
       <c r="R86"/>
+      <c r="V86">
+        <v>10.968999999999999</v>
+      </c>
+      <c r="W86">
+        <v>11.454000000000001</v>
+      </c>
+      <c r="X86" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A87" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="I87" s="26">
+        <v>3496</v>
+      </c>
+      <c r="J87" s="15">
+        <v>83.710999999999999</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>293.64838257128002</v>
+      </c>
+      <c r="O87">
+        <v>-12.35499539692</v>
+      </c>
+      <c r="P87">
+        <v>1655.31</v>
+      </c>
+      <c r="V87">
+        <v>10.977</v>
+      </c>
+      <c r="W87">
+        <v>12.571999999999999</v>
+      </c>
+      <c r="X87" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>152</v>
+      </c>
+      <c r="I88" s="21">
+        <v>5827</v>
+      </c>
+      <c r="J88">
+        <v>6.9720000000000004</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>12.295169568029999</v>
+      </c>
+      <c r="O88">
+        <v>-40.067873380309997</v>
+      </c>
+      <c r="P88">
+        <v>1154.6099999999999</v>
+      </c>
+      <c r="V88">
+        <v>10.988</v>
+      </c>
+      <c r="W88">
+        <v>11.585000000000001</v>
+      </c>
+      <c r="X88" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>153</v>
+      </c>
+      <c r="I89" s="21">
+        <v>5798</v>
+      </c>
+      <c r="J89">
+        <v>1.288</v>
+      </c>
+      <c r="K89">
+        <v>1.04</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>4.2351999999999999</v>
+      </c>
+      <c r="N89">
+        <v>78.92072949976</v>
+      </c>
+      <c r="O89">
+        <v>-61.051005597089997</v>
+      </c>
+      <c r="P89">
+        <v>216.126</v>
+      </c>
+      <c r="V89">
+        <v>11.000999999999999</v>
+      </c>
+      <c r="W89">
+        <v>11.773999999999999</v>
+      </c>
+      <c r="X89" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:U79" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0968ED-5547-EE4A-A5BC-D62327CC2110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20204847-1E00-1043-A943-A875E9A4A40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="860" windowWidth="30820" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="720" windowWidth="30820" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20204847-1E00-1043-A943-A875E9A4A40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F477CA90-EA84-2A4D-91D1-7C97C04DEB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="720" windowWidth="30820" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="600" windowWidth="43100" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$U$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$Y$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="168">
   <si>
     <t>#pl_name</t>
   </si>
@@ -494,10 +494,52 @@
     <t>GIANT</t>
   </si>
   <si>
-    <t>4999199962400320128 b</t>
-  </si>
-  <si>
-    <t>4760966338470589184 b</t>
+    <t>4470854526137662336 b</t>
+  </si>
+  <si>
+    <t>5104401338026192896 b</t>
+  </si>
+  <si>
+    <t>4658692653094984064 b</t>
+  </si>
+  <si>
+    <t>4484082200778102912 b</t>
+  </si>
+  <si>
+    <t>4589034532709089664 b</t>
+  </si>
+  <si>
+    <t>4530045738181114112 b</t>
+  </si>
+  <si>
+    <t>4501593121729029760 b</t>
+  </si>
+  <si>
+    <t>4537788189826607744 b</t>
+  </si>
+  <si>
+    <t>4506750419706094208 b</t>
+  </si>
+  <si>
+    <t>4502235206461528320 b</t>
+  </si>
+  <si>
+    <t>4502894466759683328 b</t>
+  </si>
+  <si>
+    <t>4471023610402254336 b</t>
+  </si>
+  <si>
+    <t>4507794990110778496 b</t>
+  </si>
+  <si>
+    <t>4509331003532495104 b</t>
+  </si>
+  <si>
+    <t>4113444695135680128 b</t>
+  </si>
+  <si>
+    <t>Roland</t>
   </si>
 </sst>
 </file>
@@ -536,48 +578,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor theme="5" tint="0.59999389629810485"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor theme="5" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -650,79 +656,56 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1000,5420 +983,5961 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH89"/>
+  <dimension ref="A1:BH102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="4" width="12.5"/>
-    <col min="5" max="6" width="11.33203125"/>
-    <col min="7" max="8" width="8.1640625"/>
-    <col min="9" max="9" width="9.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1640625"/>
-    <col min="11" max="11" width="9.1640625"/>
-    <col min="14" max="15" width="12.5"/>
-    <col min="16" max="16" width="9"/>
-    <col min="17" max="17" width="9.1640625"/>
-    <col min="18" max="18" width="9.1640625" style="9"/>
-    <col min="19" max="19" width="14.1640625" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625"/>
-    <col min="23" max="23" width="9.83203125"/>
-    <col min="24" max="24" width="9"/>
-    <col min="25" max="25" width="8.1640625"/>
-    <col min="26" max="27" width="11.33203125"/>
-    <col min="29" max="29" width="9.83203125"/>
-    <col min="30" max="30" width="9"/>
-    <col min="32" max="32" width="9.83203125"/>
-    <col min="33" max="33" width="9"/>
-    <col min="35" max="35" width="9.83203125"/>
-    <col min="36" max="36" width="9"/>
-    <col min="41" max="41" width="9.83203125"/>
-    <col min="42" max="42" width="9"/>
-    <col min="47" max="47" width="9.83203125"/>
-    <col min="48" max="48" width="9"/>
-    <col min="50" max="50" width="9.83203125"/>
-    <col min="51" max="51" width="9"/>
-    <col min="60" max="60" width="8.1640625"/>
+    <col min="1" max="1" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="11.1640625" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="11.33203125" style="1"/>
+    <col min="28" max="28" width="8" style="1"/>
+    <col min="29" max="29" width="9.83203125" style="1"/>
+    <col min="30" max="30" width="9" style="1"/>
+    <col min="31" max="31" width="8" style="1"/>
+    <col min="32" max="32" width="9.83203125" style="1"/>
+    <col min="33" max="33" width="9" style="1"/>
+    <col min="34" max="34" width="8" style="1"/>
+    <col min="35" max="35" width="9.83203125" style="1"/>
+    <col min="36" max="36" width="9" style="1"/>
+    <col min="37" max="40" width="8" style="1"/>
+    <col min="41" max="41" width="9.83203125" style="1"/>
+    <col min="42" max="42" width="9" style="1"/>
+    <col min="43" max="46" width="8" style="1"/>
+    <col min="47" max="47" width="9.83203125" style="1"/>
+    <col min="48" max="48" width="9" style="1"/>
+    <col min="49" max="49" width="8" style="1"/>
+    <col min="50" max="50" width="9.83203125" style="1"/>
+    <col min="51" max="51" width="9" style="1"/>
+    <col min="52" max="59" width="8" style="1"/>
+    <col min="60" max="60" width="8.1640625" style="1"/>
+    <col min="61" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="V1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="W1" s="20" t="s">
+      <c r="W1" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="X1" s="4" t="s">
         <v>147</v>
       </c>
+      <c r="Y1" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="5">
         <v>4907.77490234375</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16">
+      <c r="J2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6">
         <v>221.24648617076679</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O2" s="6">
         <v>27.074315757773469</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="6">
         <v>2.1833524703979492</v>
       </c>
-      <c r="R2" s="16">
+      <c r="R2" s="6">
         <v>2.1833524703979492</v>
       </c>
-      <c r="BE2" s="3"/>
-      <c r="BG2" s="3"/>
-      <c r="BH2" s="3"/>
+      <c r="BE2" s="7"/>
+      <c r="BG2" s="7"/>
+      <c r="BH2" s="7"/>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1">
         <v>4.4652997599999997</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>5.561E-2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>1.319</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>0.52500000000000002</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>1322</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="2">
         <v>5980</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>1.1739999999999999</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>1.151</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>0.13</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>4.359</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>344.44536319999997</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>38.674919000000003</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>158.97900000000001</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>9.827</v>
       </c>
-      <c r="R3" s="9">
+      <c r="R3" s="1">
         <v>10.178599999999999</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <f>(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
         <v>1121.1126749906216</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <f>IF(I3&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE3" s="3"/>
-      <c r="BG3" s="3"/>
-      <c r="BH3" s="3"/>
+      <c r="BE3" s="7"/>
+      <c r="BG3" s="7"/>
+      <c r="BH3" s="7"/>
     </row>
     <row r="4" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1">
         <v>4.6276700000000002</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>5.96E-2</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1.42</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>3.44</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>1624</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="2">
         <v>6600</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>1.82</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>2.65</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>0.11</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>4.25</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>260.11617189999998</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>38.242168200000002</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>222.66300000000001</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>9.9879999999999995</v>
       </c>
-      <c r="R4" s="9">
+      <c r="R4" s="1">
         <v>9.8728300000000004</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <f>(0.000000000000000138*G4/(1.673534E-24*1.3*0.000000066726*F4*1.8986E+30/(E4*7149200000)^2))/100000</f>
         <v>243.60813720463176</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <f>IF(I4&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE4" s="3"/>
-      <c r="BG4" s="3"/>
-      <c r="BH4" s="3"/>
+      <c r="BE4" s="7"/>
+      <c r="BG4" s="7"/>
+      <c r="BH4" s="7"/>
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1">
         <v>5.6335157999999996</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>6.8140000000000006E-2</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.95099999999999996</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>9.02</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>1540</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="2">
         <v>6380</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>1.39</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>1.33</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>0.18</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>4.16</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>245.1514324</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>41.047960099999997</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>127.774</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>8.7200000000000006</v>
       </c>
-      <c r="R5" s="9">
+      <c r="R5" s="1">
         <v>8.5984200000000008</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <f>(0.000000000000000138*G5/(1.673534E-24*1.3*0.000000066726*F5*1.8986E+30/(E5*7149200000)^2))/100000</f>
         <v>39.515068300859213</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <f>IF(I5&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE5" s="3"/>
-      <c r="BG5" s="3"/>
-      <c r="BH5" s="3"/>
+      <c r="BE5" s="7"/>
+      <c r="BG5" s="7"/>
+      <c r="BH5" s="7"/>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
         <v>3.2122199999999999</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>1.1499999999999999</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>1463</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="2">
         <v>5302</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>1.1100000000000001</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>1.1299999999999999</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>0.24</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>4.3600000000000003</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>155.6814593</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>50.128711500000001</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>81.764700000000005</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>9.7629999999999999</v>
       </c>
-      <c r="R6" s="9">
+      <c r="R6" s="1">
         <v>9.5193600000000007</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <f>(0.000000000000000138*G6/(1.673534E-24*1.3*0.000000066726*F6*1.8986E+30/(E6*7149200000)^2))/100000</f>
         <v>200.46131426194896</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <f>IF(I6&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE6" s="3"/>
-      <c r="BG6" s="3"/>
-      <c r="BH6" s="3"/>
+      <c r="BE6" s="7"/>
+      <c r="BG6" s="7"/>
+      <c r="BH6" s="7"/>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="I7" s="22">
+      <c r="B7" s="6"/>
+      <c r="I7" s="5">
         <v>6245.11328125</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="6">
         <v>1.208241820335388</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="6">
         <v>4.2744002342224121</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="6">
         <v>31.04275939878713</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="6">
         <v>46.687851647860192</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>283.38339999999999</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="6">
         <v>11.12930202484131</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="6">
         <v>11.12930202484131</v>
       </c>
-      <c r="V7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
+      <c r="V7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1">
         <v>4.7947813000000004</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>6.2770000000000006E-2</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>1.631</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.57399999999999995</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>1772</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="2">
         <v>6212</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>2.1970000000000001</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>1.4350000000000001</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>3.9114</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>28.282571900000001</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>52.053920900000001</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>233.22</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>9.7270000000000003</v>
       </c>
-      <c r="R8" s="9">
+      <c r="R8" s="1">
         <v>9.5635499999999993</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <f>(0.000000000000000138*G8/(1.673534E-24*1.3*0.000000066726*F8*1.8986E+30/(E8*7149200000)^2))/100000</f>
         <v>2101.5864855136347</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <f>IF(I8&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="V8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
+      <c r="V8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
     </row>
     <row r="9" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1">
         <v>4.7869491000000002</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>6.5549999999999997E-2</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>1.6759999999999999</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>3.58</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>1930</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="2">
         <v>7394</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>1.9259999999999999</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>1.6479999999999999</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>-6.9000000000000006E-2</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>4.1100000000000003</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>130.5056385</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>3.7105662000000001</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>341.26299999999998</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>9.7739999999999991</v>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="1">
         <v>9.77332</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <f>(0.000000000000000138*G9/(1.673534E-24*1.3*0.000000066726*F9*1.8986E+30/(E9*7149200000)^2))/100000</f>
         <v>387.53401759458865</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <f>IF(I9&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="5">
         <v>6424.27685546875</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="6">
         <v>2.0702402591705318</v>
       </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16">
+      <c r="M10" s="6"/>
+      <c r="N10" s="6">
         <v>292.24718620018581</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="6">
         <v>47.969544064101818</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="6">
         <v>10.36768245697021</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="6">
         <v>10.36768245697021</v>
       </c>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1">
         <v>2.7443245200000002</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>4.7390000000000002E-2</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>1.87</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>6.78</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>2562</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="2">
         <v>8450</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>1.8580000000000001</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>1.89</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>-5.8999999999999997E-2</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>4.181</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>74.552333200000007</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>9.9979794000000002</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>330.73899999999998</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>9.4700000000000006</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="1">
         <v>9.4517399999999991</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <f t="shared" ref="S11:S35" si="0">(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
         <v>338.15838787809196</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <f t="shared" ref="T11:T34" si="1">IF(I11&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
-      <c r="V11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
+      <c r="V11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
     </row>
     <row r="12" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="9">
         <v>6.1349779</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="9">
         <v>7.1300000000000002E-2</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="9">
         <v>1.1399999999999999</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="9">
         <v>2.14</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="9">
         <v>1361</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="11">
         <v>5742</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="9">
         <v>2.04</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="9">
         <v>1.27</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="9">
         <v>0.28699999999999998</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="9">
         <v>3.92</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="9">
         <v>203.50995599999999</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="9">
         <v>53.728187599999998</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="9">
         <v>92.258899999999997</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="9">
         <v>8.0500000000000007</v>
       </c>
-      <c r="R12" s="10">
+      <c r="R12" s="9">
         <v>7.89255</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <f t="shared" si="0"/>
         <v>211.51519610586323</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="1">
         <v>11.53533</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>0.10970000000000001</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>1.026</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>0.41499999999999998</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>1228.3</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="2">
         <v>5521</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>2.3359999999999999</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>1.3240000000000001</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>3.823</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>4.4471631</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>-66.358928500000005</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>79.5702</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>7.79</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="1">
         <v>7.5933599999999997</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <f t="shared" si="0"/>
         <v>797.33090232058362</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="14" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="9">
         <v>2.8758900000000001</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="9">
         <v>4.3639999999999998E-2</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="9">
         <v>0.74</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="9">
         <v>0.38</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="9">
         <v>1626</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="11">
         <v>6179</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="9">
         <v>1.41</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="9">
         <v>1.42</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="9">
         <v>0.32</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="9">
         <v>4.37</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="9">
         <v>247.62298269999999</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14" s="9">
         <v>38.347534899999999</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="9">
         <v>75.8643</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="9">
         <v>8.15</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="9">
         <v>8.0141600000000004</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <f t="shared" si="0"/>
         <v>599.63628364223177</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
+      <c r="V14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
     </row>
     <row r="15" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1">
         <v>19.502103999999999</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>0.1482</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>0.52993221999999995</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>3.0425219999999999E-2</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>253.08</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="2">
         <v>6310</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>1.43</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-0.16</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>4.1900000000000004</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>253.78488530000001</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>20.491523999999998</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>107.898</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>8.8550000000000004</v>
       </c>
-      <c r="R15" s="9">
+      <c r="R15" s="1">
         <v>8.7641200000000001</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <f t="shared" si="0"/>
         <v>597.79498778467087</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="16" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="9">
         <v>2.2185756699999999</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="9">
         <v>3.1260000000000003E-2</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="9">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="9">
         <v>1.1299999999999999</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="9">
         <v>1209</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="11">
         <v>5052</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="9">
         <v>0.75</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="9">
         <v>0.79</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="9">
         <v>-0.02</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="9">
         <v>4.49</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="9">
         <v>300.1821223</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16" s="9">
         <v>22.7097759</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="9">
         <v>19.7638</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="9">
         <v>7.67</v>
       </c>
-      <c r="R16" s="10">
+      <c r="R16" s="9">
         <v>7.41432</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <f t="shared" si="0"/>
         <v>349.61677638948368</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
+      <c r="V16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1">
         <v>3.3089580000000001</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>5.2080000000000001E-2</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>1.5449999999999999</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>1.0169999999999999</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>2132</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="2">
         <v>6272</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>2.5910000000000002</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>1.72</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>0.3</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>3.8479999999999999</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>319.6995877</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-26.6163743</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>161.49799999999999</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>8.3239999999999998</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="1">
         <v>8.2268799999999995</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <f t="shared" si="0"/>
         <v>1280.5918535006856</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="9">
         <v>3.5247485900000002</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="9">
         <v>4.7070000000000001E-2</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="9">
         <v>1.39</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="9">
         <v>0.73</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="9">
         <v>1459</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="11">
         <v>6091</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="9">
         <v>1.19</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="9">
         <v>1.23</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="9">
         <v>0.01</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" s="9">
         <v>4.45</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="9">
         <v>330.79502189999999</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18" s="9">
         <v>18.884241899999999</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="9">
         <v>48.301600000000001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="9">
         <v>7.65</v>
       </c>
-      <c r="R18" s="10">
+      <c r="R18" s="9">
         <v>7.5086599999999999</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <f t="shared" si="0"/>
         <v>988.21070019970352</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19">
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1">
         <v>6.0344680000000004</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>6.3560000000000005E-2</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>0.437</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>1076</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="2">
         <v>5540</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>1.0589999999999999</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>1.02</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>0.04</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>349.55926649999998</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>-56.9039857</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>94.171899999999994</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>9.8089999999999993</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R19" s="1">
         <v>9.6495599999999992</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <f t="shared" si="0"/>
         <v>956.09264119622901</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20">
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1">
         <v>14.2767</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>0.12280000000000001</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>0.83599999999999997</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>0.19</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>789.15</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="2">
         <v>5080</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>2.9430000000000001</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>1.212</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-0.08</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>3.5840000000000001</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>353.03318630000001</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-21.801200699999999</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>95.548299999999998</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>8.15</v>
       </c>
-      <c r="R20" s="9">
+      <c r="R20" s="1">
         <v>7.9077599999999997</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <f t="shared" si="0"/>
         <v>742.8583931109747</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="6">
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1">
         <v>4.1268799999999999</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="1">
         <v>5.6800000000000003E-2</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="1">
         <v>1.44</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="1">
         <v>1.17</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="1">
         <v>2061</v>
       </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="24">
+      <c r="I21" s="2">
         <v>6801</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="1">
         <v>1.56</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="1">
         <v>1.43</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="1">
         <v>0.02</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="1">
         <v>4.21</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="1">
         <v>7.3289156000000002</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="1">
         <v>-76.304032000000007</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="1">
         <v>196.852</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="Q21" s="1">
         <v>9.5950000000000006</v>
       </c>
-      <c r="R21" s="9">
+      <c r="R21" s="1">
         <v>9.5202500000000008</v>
       </c>
-      <c r="S21" s="6">
+      <c r="S21" s="1">
         <f t="shared" si="0"/>
         <v>934.76971602454307</v>
       </c>
-      <c r="T21" s="6">
+      <c r="T21" s="1">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
-      <c r="U21" s="7" t="s">
+      <c r="U21" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22">
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1">
         <v>18.712024</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>0.14499999999999999</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>0.80944318999999998</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>0.23314467</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>798.3</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="2">
         <v>6128</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>1.266</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>1.1641999999999999</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>4.2960000000000003</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>306.74113399999999</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>33.744388200000003</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>80.666499999999999</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>8.5579999999999998</v>
       </c>
-      <c r="R22" s="9">
+      <c r="R22" s="1">
         <v>8.4183900000000005</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <f t="shared" si="0"/>
         <v>574.11765847468712</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="9">
         <v>3.4148839999999998</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="9">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="9">
         <v>1.23</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="9">
         <v>1.02</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>1762</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="11">
         <v>5392</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="9">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="9">
         <v>1.26</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="9">
         <v>0.34</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="9">
         <v>3.88</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="9">
         <v>152.53193490000001</v>
       </c>
-      <c r="O23" s="2">
+      <c r="O23" s="9">
         <v>18.185728399999999</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="9">
         <v>73.612300000000005</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="9">
         <v>8.0185200000000005</v>
       </c>
-      <c r="R23" s="10">
+      <c r="R23" s="9">
         <v>7.8097899999999996</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="1">
         <f t="shared" si="0"/>
         <v>668.81110409377118</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1">
         <v>11.814299999999999</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>0.1066</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>0.66</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>0.11</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>1089</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="21">
+      <c r="I24" s="2">
         <v>5576</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>1.7470000000000001</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>1.157</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>0.42099999999999999</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>4.016</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>154.67109769999999</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>10.1288464</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>132.345</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>9.3800000000000008</v>
       </c>
-      <c r="R24" s="9">
+      <c r="R24" s="1">
         <v>9.2170199999999998</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="1">
         <f t="shared" si="0"/>
         <v>1103.5971886171305</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25">
+      <c r="B25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="1">
         <v>11.168454000000001</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>0.10356</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>0.39800000000000002</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>1030</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="2">
         <v>6154</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="1">
         <v>1.161</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>1.1879999999999999</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>0.1</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="1">
         <v>4.3789999999999996</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="1">
         <v>73.766792699999996</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="1">
         <v>18.654323000000002</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="1">
         <v>130.72</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="1">
         <v>9.8219999999999992</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="1">
         <v>9.7262599999999999</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="1">
         <f t="shared" si="0"/>
         <v>662.28004924519439</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="1">
         <v>4.73620865</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>6.2300000000000001E-2</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>1.35</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>1712</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="2">
         <v>5375</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>2.69</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>1.44</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>0.17</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>3.7</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>161.70690529999999</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>-9.3993646000000002</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>99.159599999999998</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="1">
         <v>8.0399999999999991</v>
       </c>
-      <c r="R26" s="9">
+      <c r="R26" s="1">
         <v>7.8311200000000003</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="1">
         <f t="shared" si="0"/>
         <v>3894.9775251994533</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27">
+      <c r="B27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="1">
         <v>3.0801715999999999</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>4.8809999999999999E-2</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>1.5249999999999999</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>1.31</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>2087</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="2">
         <v>7454</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>1.645</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>1.635</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>4.22</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>125.617407</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>13.735309300000001</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>226.5</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="1">
         <v>9.234</v>
       </c>
-      <c r="R27" s="9">
+      <c r="R27" s="1">
         <v>9.2088699999999992</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <f t="shared" si="0"/>
         <v>948.15286253702118</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="1">
         <v>4.6117093000000002</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>1.91</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>4.07</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>1935</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="2">
         <v>7500</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>1.83</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>1.62</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>-0.12</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>4.1269999999999998</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>111.5095293</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>7.6157759</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>300.27600000000001</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="1">
         <v>9.8569999999999993</v>
       </c>
-      <c r="R28" s="9">
+      <c r="R28" s="1">
         <v>9.8633100000000002</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="1">
         <f t="shared" si="0"/>
         <v>443.85469120292152</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29">
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1">
         <v>4.1137899999999998</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>5.4969999999999998E-2</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>1.35</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>1.7</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>2080</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="2">
         <v>6327</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>1.93</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>1.54</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>0</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>4.5</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>92.664022599999996</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>30.957133299999999</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>134.05799999999999</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="1">
         <v>8.68</v>
       </c>
-      <c r="R29" s="9">
+      <c r="R29" s="1">
         <v>8.5839300000000005</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="1">
         <f t="shared" si="0"/>
         <v>570.64953846380126</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30">
+      <c r="B30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="1">
         <v>3.4741084999999998</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>5.4199999999999998E-2</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>1.7410000000000001</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>3.3820000000000001</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>2262</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="2">
         <v>8720</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>1.5649999999999999</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>1.76</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>-0.28999999999999998</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="1">
         <v>4.29</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="1">
         <v>294.66141260000001</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="1">
         <v>31.219200099999998</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="1">
         <v>136.42599999999999</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="1">
         <v>7.59</v>
       </c>
-      <c r="R30" s="9">
+      <c r="R30" s="1">
         <v>7.5749199999999997</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="1">
         <f t="shared" si="0"/>
         <v>518.80488815900412</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="1">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31">
+      <c r="B31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="1">
         <v>5.55149296</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>6.6500000000000004E-2</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>1.1339999999999999</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>4.59</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>1391</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="2">
         <v>6426</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
         <v>1.3380000000000001</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>1.268</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>0.13800000000000001</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="1">
         <v>4.2869999999999999</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="1">
         <v>161.90902729999999</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="1">
         <v>71.655726999999999</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="1">
         <v>96.517300000000006</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="1">
         <v>8.34</v>
       </c>
-      <c r="R31" s="9">
+      <c r="R31" s="1">
         <v>8.23752</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="1">
         <f t="shared" si="0"/>
         <v>99.730517672190274</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32">
+      <c r="B32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="1">
         <v>2.7033900000000002</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>4.1230000000000003E-2</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>1.56</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>1.94</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>1816</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="2">
         <v>6304</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>1.7</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>1.96</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>0.05</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="1">
         <v>4.2</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="1">
         <v>148.6431193</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="1">
         <v>40.387944599999997</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="1">
         <v>210.25200000000001</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="1">
         <v>9.8160000000000007</v>
       </c>
-      <c r="R32" s="9">
+      <c r="R32" s="1">
         <v>9.7632399999999997</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="1">
         <f t="shared" si="0"/>
         <v>582.97620763372299</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33">
+      <c r="B33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="1">
         <v>2.9895931999999998</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>4.317E-2</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>1.6990000000000001</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>0.90200000000000002</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>1823</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="2">
         <v>6206</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="1">
         <v>1.603</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>1.2010000000000001</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="1">
         <v>-0.11600000000000001</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="1">
         <v>4.1079999999999997</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="1">
         <v>157.06262000000001</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="1">
         <v>25.573136600000002</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="1">
         <v>218.05</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="1">
         <v>9.98</v>
       </c>
-      <c r="R33" s="9">
+      <c r="R33" s="1">
         <v>9.95702</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="1">
         <f t="shared" si="0"/>
         <v>1492.9814393090719</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34">
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1">
         <v>2.7347700000000001</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>4.4150000000000002E-2</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>1.6</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1">
         <v>1.39</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>2048</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="2">
         <v>6768</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
         <v>1.81</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>1.76</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="1">
         <v>0</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="1">
         <v>4.5</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="1">
         <v>78.295591200000004</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="1">
         <v>33.317953199999998</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="1">
         <v>136.68100000000001</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="1">
         <v>8.56</v>
       </c>
-      <c r="R34" s="9">
+      <c r="R34" s="1">
         <v>8.4517299999999995</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="1">
         <f t="shared" si="0"/>
         <v>965.25628287035329</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="1">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="19">
+      <c r="B35" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="13">
         <v>1.4811235</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="13">
         <v>3.4619999999999998E-2</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="13">
         <v>1.891</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="13">
         <v>2.88</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="13">
         <v>4050</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="H35" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="14">
         <v>10170.1</v>
       </c>
-      <c r="J35" s="19">
+      <c r="J35" s="13">
         <v>2.3620000000000001</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="13">
         <v>2.52</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="13">
         <v>-0.03</v>
       </c>
-      <c r="M35" s="19">
+      <c r="M35" s="13">
         <v>4.093</v>
       </c>
-      <c r="N35" s="19">
+      <c r="N35" s="13">
         <v>307.85989979999999</v>
       </c>
-      <c r="O35" s="19">
+      <c r="O35" s="13">
         <v>39.9389161</v>
       </c>
-      <c r="P35" s="19">
+      <c r="P35" s="13">
         <v>204.45500000000001</v>
       </c>
-      <c r="Q35" s="19">
+      <c r="Q35" s="13">
         <v>7.55</v>
       </c>
-      <c r="R35" s="19">
+      <c r="R35" s="13">
         <v>7.5767499999999997</v>
       </c>
-      <c r="S35" s="19">
+      <c r="S35" s="13">
         <f t="shared" si="0"/>
         <v>1286.8653667451285</v>
       </c>
-      <c r="T35" s="6"/>
-      <c r="U35" s="7" t="s">
+      <c r="U35" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="I36" s="22">
+      <c r="I36" s="5">
         <v>7433.197265625</v>
       </c>
-      <c r="J36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16">
+      <c r="J36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6">
         <v>286.97138676797078</v>
       </c>
-      <c r="O36" s="16">
+      <c r="O36" s="6">
         <v>46.868244058307063</v>
       </c>
-      <c r="Q36" s="16">
+      <c r="Q36" s="6">
         <v>10.382340431213381</v>
       </c>
-      <c r="R36" s="16">
+      <c r="R36" s="6">
         <v>10.382340431213381</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B37" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37">
+      <c r="B37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1">
         <v>1.7635879999999999</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
         <v>3.6409999999999998E-2</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>1.512</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1">
         <v>9.2799999999999994</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="1">
         <v>2550</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="2">
         <v>7650</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="1">
         <v>1.74</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="1">
         <v>1.72</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="1">
         <v>0.2</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="1">
         <v>4.2</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="1">
         <v>286.97138760000001</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="1">
         <v>46.868246300000003</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="1">
         <v>519.096</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="1">
         <v>9.7910000000000004</v>
       </c>
-      <c r="R37" s="9">
+      <c r="R37" s="1">
         <v>10.367800000000001</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="1">
         <f t="shared" ref="S37:S63" si="2">(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
         <v>160.76196513632402</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="1">
         <f t="shared" ref="T37:T63" si="3">IF(I37&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38">
+      <c r="B38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
         <v>0.79205199999999998</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>1.6789999999999999E-2</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="1">
         <v>0.42109020000000003</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="1">
         <v>9.2250570000000004E-2</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="1">
         <v>1978</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="2">
         <v>5443</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="1">
         <v>0.94899999999999995</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="1">
         <v>1.02</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="1">
         <v>0.27</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="1">
         <v>4.3499999999999996</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="1">
         <v>358.6688767</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="1">
         <v>-37.628223699999999</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="1">
         <v>80.437299999999993</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="1">
         <v>9.7899999999999991</v>
       </c>
-      <c r="R38" s="9">
+      <c r="R38" s="1">
         <v>9.6000599999999991</v>
       </c>
-      <c r="S38">
+      <c r="S38" s="1">
         <f t="shared" si="2"/>
         <v>972.96006983022733</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39">
+      <c r="B39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="1">
         <v>2.1487738099999998</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>4.0351999999999999E-2</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="1">
         <v>1.597</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>3.7</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="1">
         <v>2594.3000000000002</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="2">
         <v>7490</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="1">
         <v>2.0819999999999999</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="1">
         <v>1.9</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="1">
         <v>0.15</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="1">
         <v>4.1050000000000004</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="1">
         <v>317.5515264</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="1">
         <v>10.7388967</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="1">
         <v>182.273</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="1">
         <v>8.2799999999999994</v>
       </c>
-      <c r="R39" s="9">
+      <c r="R39" s="1">
         <v>8.2424300000000006</v>
       </c>
-      <c r="S39">
+      <c r="S39" s="1">
         <f t="shared" si="2"/>
         <v>457.63140850776114</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="1">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40">
+      <c r="B40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="1">
         <v>2.8240932000000001</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>4.7399999999999998E-2</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="1">
         <v>1.5149999999999999</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="1">
         <v>1.675</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="1">
         <v>2250</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="2">
         <v>7800</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="1">
         <v>1.79</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="1">
         <v>1.75</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="1">
         <v>0</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="1">
         <v>147.5800667</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="1">
         <v>-66.113925300000005</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="1">
         <v>170.696</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="1">
         <v>8.1910000000000007</v>
       </c>
-      <c r="R40" s="9">
+      <c r="R40" s="1">
         <v>8.1740100000000009</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="1">
         <f t="shared" si="2"/>
         <v>789.006338593706</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="1">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="6">
+      <c r="B41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="1">
         <v>16.249210000000001</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="1">
         <v>0.12909999999999999</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="1">
         <v>1.087</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="1">
         <v>4.34</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="1">
         <v>805.5</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H41" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="24">
+      <c r="I41" s="2">
         <v>5756</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="1">
         <v>1.0860000000000001</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="1">
         <v>1.0820000000000001</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="1">
         <v>0.318</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="1">
         <v>4.4020000000000001</v>
       </c>
-      <c r="N41" s="6">
+      <c r="N41" s="1">
         <v>310.29170019999998</v>
       </c>
-      <c r="O41" s="6">
+      <c r="O41" s="1">
         <v>3.6382967000000002</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="1">
         <v>93.734499999999997</v>
       </c>
-      <c r="Q41" s="6">
+      <c r="Q41" s="1">
         <v>9.48</v>
       </c>
-      <c r="R41" s="9">
+      <c r="R41" s="1">
         <v>9.4290710000000004</v>
       </c>
-      <c r="S41" s="6">
+      <c r="S41" s="1">
         <f t="shared" si="2"/>
         <v>56.120615203365361</v>
       </c>
-      <c r="T41" s="6">
+      <c r="T41" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
-      <c r="U41" s="7" t="s">
+      <c r="U41" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42">
+      <c r="B42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1">
         <v>8.0277282999999997</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="1">
         <v>8.2337403000000003E-2</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="1">
         <v>0.83243188000000001</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="1">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="1">
         <v>1074.28</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="2">
         <v>5962.7</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="1">
         <v>1.1499999999999999</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="1">
         <v>1.156039</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="1">
         <v>0</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="1">
         <v>4.38</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="1">
         <v>193.3963704</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="1">
         <v>85.129495199999994</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="1">
         <v>114.048</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="1">
         <v>9.5399999999999991</v>
       </c>
-      <c r="R42" s="9">
+      <c r="R42" s="1">
         <v>9.4135299999999997</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="1">
         <f t="shared" si="2"/>
         <v>1175.9460676296278</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B43" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43">
+      <c r="B43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="1">
         <v>12.5199</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="1">
         <v>0.1062</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="1">
         <v>0.41279399999999999</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="1">
         <v>2.627204E-2</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="1">
         <v>843</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="2">
         <v>5770</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="1">
         <v>0.96799999999999997</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="1">
         <v>1.022</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="1">
         <v>4.47</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="1">
         <v>192.1848981</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="1">
         <v>64.855275500000005</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="1">
         <v>84.536199999999994</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="1">
         <v>9.5340000000000007</v>
       </c>
-      <c r="R43" s="9">
+      <c r="R43" s="1">
         <v>9.3678899999999992</v>
       </c>
-      <c r="S43">
+      <c r="S43" s="1">
         <f t="shared" si="2"/>
         <v>1399.2265914107247</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B44" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44">
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1">
         <v>4.7202190000000002</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
         <v>6.2600000000000003E-2</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="1">
         <v>1.3959999999999999</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="1">
         <v>2.37</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="1">
         <v>1679</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="2">
         <v>6274</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="1">
         <v>1.925</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="1">
         <v>1.464</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="1">
         <v>0.11899999999999999</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="1">
         <v>4.0339999999999998</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="1">
         <v>325.01453629999997</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="1">
         <v>48.4067674</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="1">
         <v>200.49199999999999</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="1">
         <v>9.4380000000000006</v>
       </c>
-      <c r="R44" s="9">
+      <c r="R44" s="1">
         <v>9.3503900000000009</v>
       </c>
-      <c r="S44">
+      <c r="S44" s="1">
         <f t="shared" si="2"/>
         <v>353.31388599481477</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B45" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45">
+      <c r="B45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="1">
         <v>4.4258699999999997</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>5.7779999999999998E-2</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="1">
         <v>2.2303544500000001</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="1">
         <v>1.86578665</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="1">
         <v>1293</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I45" s="21">
+      <c r="I45" s="2">
         <v>6117</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="1">
         <v>1.53</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="1">
         <v>1.3120000000000001</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="1">
         <v>0.25</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="1">
         <v>313.5110469</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="1">
         <v>72.580645500000003</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="1">
         <v>139.48400000000001</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="1">
         <v>9.2700010000000006</v>
       </c>
-      <c r="R45" s="9">
+      <c r="R45" s="1">
         <v>9.1879500000000007</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="1">
         <f t="shared" si="2"/>
         <v>882.20971786077962</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46">
+      <c r="B46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="1">
         <v>2.6502370000000002</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="1">
         <v>1.49</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="1">
         <v>3.12</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="1">
         <v>2370</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I46" s="21">
+      <c r="I46" s="2">
         <v>7690</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="1">
         <v>1.92</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="1">
         <v>1.9</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="1">
         <v>0.09</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="1">
         <v>4.1500000000000004</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="1">
         <v>316.20369219999998</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="1">
         <v>55.588022100000003</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="1">
         <v>148.92500000000001</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="1">
         <v>8.0299999999999994</v>
       </c>
-      <c r="R46" s="9">
+      <c r="R46" s="1">
         <v>7.9756099999999996</v>
       </c>
-      <c r="S46">
+      <c r="S46" s="1">
         <f t="shared" si="2"/>
         <v>431.57254486096394</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="1">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47">
+      <c r="B47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1">
         <v>1.902603</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="1">
         <v>1.875</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="1">
         <v>2492</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I47" s="21">
+      <c r="I47" s="2">
         <v>7300</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="1">
         <v>1.95</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="1">
         <v>1.79</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="1">
         <v>-0.1</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="1">
         <v>352.26752069999998</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="1">
         <v>67.034806200000006</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="1">
         <v>225.88800000000001</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="1">
         <v>8.952</v>
       </c>
-      <c r="R47" s="9">
+      <c r="R47" s="1">
         <v>8.8952899999999993</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="1">
         <f t="shared" si="2"/>
         <v>974.78820571370204</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="1">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48">
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1">
         <v>3.2086640000000002</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
         <v>4.8820000000000002E-2</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="1">
         <v>1.44</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="1">
         <v>0.7</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="1">
         <v>1927</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="2">
         <v>5991</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="1">
         <v>2.1680000000000001</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="1">
         <v>1.5069999999999999</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="1">
         <v>0.373</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="1">
         <v>3.9430000000000001</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="1">
         <v>142.74340599999999</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="1">
         <v>26.539995099999999</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="1">
         <v>229.06700000000001</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="1">
         <v>9.7210000000000001</v>
       </c>
-      <c r="R48" s="9">
+      <c r="R48" s="1">
         <v>9.5843900000000009</v>
       </c>
-      <c r="S48">
+      <c r="S48" s="1">
         <f t="shared" si="2"/>
         <v>1460.8182255852041</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49">
+      <c r="B49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="1">
         <v>9.5739181000000002</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>0.1</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="1">
         <v>1.10166148</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="1">
         <v>0.28128386</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="1">
         <v>1199.55</v>
       </c>
-      <c r="I49" s="21">
+      <c r="I49" s="2">
         <v>6039</v>
       </c>
-      <c r="J49">
+      <c r="J49" s="1">
         <v>2.032</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="1">
         <v>1.4642999999999999</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="1">
         <v>0.33200000000000002</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="1">
         <v>3.9860000000000002</v>
       </c>
-      <c r="N49">
+      <c r="N49" s="1">
         <v>201.9626552</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="1">
         <v>9.0306437000000006</v>
       </c>
-      <c r="P49">
+      <c r="P49" s="1">
         <v>223.465</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="1">
         <v>9.8149999999999995</v>
       </c>
-      <c r="R49" s="9">
+      <c r="R49" s="1">
         <v>9.6598100000000002</v>
       </c>
-      <c r="S49">
+      <c r="S49" s="1">
         <f t="shared" si="2"/>
         <v>1324.5165539963698</v>
       </c>
-      <c r="T49">
+      <c r="T49" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50">
+      <c r="B50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="1">
         <v>17.305904000000002</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="1">
         <v>0.16</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="1">
         <v>1.07</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="1">
         <v>6.4</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="1">
         <v>1221.3900000000001</v>
       </c>
-      <c r="I50" s="21">
+      <c r="I50" s="2">
         <v>7130</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="1">
         <v>2.02</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="1">
         <v>1.59</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="1">
         <v>0</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="1">
         <v>3.9460000000000002</v>
       </c>
-      <c r="N50">
+      <c r="N50" s="1">
         <v>164.031654</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="1">
         <v>-43.376696699999997</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="1">
         <v>328.47500000000002</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="1">
         <v>9.8670000000000009</v>
       </c>
-      <c r="R50" s="9">
+      <c r="R50" s="1">
         <v>9.7596699999999998</v>
       </c>
-      <c r="S50">
+      <c r="S50" s="1">
         <f t="shared" si="2"/>
         <v>55.915145726222889</v>
       </c>
-      <c r="T50">
+      <c r="T50" s="1">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51">
+      <c r="B51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="1">
         <v>10.261127</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="1">
         <v>0.111</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="1">
         <v>1.1079506100000001</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="1">
         <v>5.55960374</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="1">
         <v>1363.43</v>
       </c>
-      <c r="I51" s="21">
+      <c r="I51" s="2">
         <v>6200</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="1">
         <v>2.7505000000000002</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="1">
         <v>1.7169000000000001</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="1">
         <v>0.28499999999999998</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="1">
         <v>3.7890000000000001</v>
       </c>
-      <c r="N51">
+      <c r="N51" s="1">
         <v>263.75807529999997</v>
       </c>
-      <c r="O51">
+      <c r="O51" s="1">
         <v>40.695042800000003</v>
       </c>
-      <c r="P51">
+      <c r="P51" s="1">
         <v>224.73099999999999</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="1">
         <v>9.07</v>
       </c>
-      <c r="R51" s="9">
+      <c r="R51" s="1">
         <v>8.9365100000000002</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="1">
         <f t="shared" si="2"/>
         <v>77.040187113891676</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B52" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52">
+      <c r="B52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="1">
         <v>10.655669</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="1">
         <v>0.1166</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="1">
         <v>0.99399999999999999</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="1">
         <v>4.82</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="1">
         <v>1595</v>
       </c>
-      <c r="I52" s="21">
+      <c r="I52" s="2">
         <v>7360</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="1">
         <v>2.36</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="1">
         <v>1.859</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="1">
         <v>9.4E-2</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="1">
         <v>3.9620000000000002</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="1">
         <v>90.062587800000003</v>
       </c>
-      <c r="O52">
+      <c r="O52" s="1">
         <v>11.8840577</v>
       </c>
-      <c r="P52">
+      <c r="P52" s="1">
         <v>285.28899999999999</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="1">
         <v>9.5470000000000006</v>
       </c>
-      <c r="R52" s="9">
+      <c r="R52" s="1">
         <v>9.4724400000000006</v>
       </c>
-      <c r="S52">
+      <c r="S52" s="1">
         <f t="shared" si="2"/>
         <v>83.670803141549356</v>
       </c>
-      <c r="T52">
+      <c r="T52" s="1">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B53" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53">
+      <c r="B53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="1">
         <v>18.388179999999998</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="1">
         <v>0.15279999999999999</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="1">
         <v>0.63900000000000001</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="1">
         <v>0.13800000000000001</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="1">
         <v>1027</v>
       </c>
-      <c r="I53" s="21">
+      <c r="I53" s="2">
         <v>6095</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="1">
         <v>1.867</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="1">
         <v>1.407</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="1">
         <v>0.17499999999999999</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="1">
         <v>4.0439999999999996</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="1">
         <v>47.517260800000003</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="1">
         <v>-50.8322632</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="1">
         <v>76.902799999999999</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="1">
         <v>7.57</v>
       </c>
-      <c r="R53" s="9">
+      <c r="R53" s="1">
         <v>7.4165299999999998</v>
       </c>
-      <c r="S53">
+      <c r="S53" s="1">
         <f t="shared" si="2"/>
         <v>777.64358420307099</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54">
+      <c r="B54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="1">
         <v>16.067540999999999</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
         <v>0.11700000000000001</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="1">
         <v>0.45410017000000003</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="1">
         <v>4.4363560000000003E-2</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="1">
         <v>635</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I54" s="21">
+      <c r="I54" s="2">
         <v>5291</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="1">
         <v>0.86599999999999999</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="1">
         <v>0.83299999999999996</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="1">
         <v>-4.3999999999999997E-2</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="1">
         <v>4.4800000000000004</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="1">
         <v>81.853282399999998</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="1">
         <v>-14.2767404</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="1">
         <v>74.796899999999994</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="1">
         <v>9.9309999999999992</v>
       </c>
-      <c r="R54" s="9">
+      <c r="R54" s="1">
         <v>9.7777600000000007</v>
       </c>
-      <c r="S54">
+      <c r="S54" s="1">
         <f t="shared" si="2"/>
         <v>755.33252275944176</v>
       </c>
-      <c r="T54">
+      <c r="T54" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B55" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55">
+      <c r="B55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="1">
         <v>9.9558099999999996</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="1">
         <v>9.9400000000000002E-2</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="1">
         <v>1.0580000000000001</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="1">
         <v>1.49</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="1">
         <v>1655</v>
       </c>
-      <c r="I55" s="21">
+      <c r="I55" s="2">
         <v>4896</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="1">
         <v>3.55</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="1">
         <v>1.31</v>
       </c>
-      <c r="L55">
+      <c r="L55" s="1">
         <v>0.23</v>
       </c>
-      <c r="M55">
+      <c r="M55" s="1">
         <v>3.48</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="1">
         <v>184.97875790000001</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="1">
         <v>-25.827853099999999</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="1">
         <v>215.98599999999999</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="1">
         <v>9.9730000000000008</v>
       </c>
-      <c r="R55" s="9">
+      <c r="R55" s="1">
         <v>9.641</v>
       </c>
-      <c r="S55">
+      <c r="S55" s="1">
         <f t="shared" si="2"/>
         <v>318.17832033985127</v>
       </c>
-      <c r="T55">
+      <c r="T55" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B56" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56">
+      <c r="B56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="1">
         <v>7.2459899999999999</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>8.8800000000000004E-2</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="1">
         <v>1.042</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="1">
         <v>12.89</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="1">
         <v>1677</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I56" s="21">
+      <c r="I56" s="2">
         <v>6264</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="1">
         <v>2.738</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="1">
         <v>1.7649999999999999</v>
       </c>
-      <c r="L56">
+      <c r="L56" s="1">
         <v>0.34200000000000003</v>
       </c>
-      <c r="M56">
+      <c r="M56" s="1">
         <v>3.81</v>
       </c>
-      <c r="N56">
+      <c r="N56" s="1">
         <v>83.865928800000006</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="1">
         <v>21.294241700000001</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="1">
         <v>225.643</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="1">
         <v>9.24</v>
       </c>
-      <c r="R56" s="9">
+      <c r="R56" s="1">
         <v>9.0746900000000004</v>
       </c>
-      <c r="S56">
+      <c r="S56" s="1">
         <f t="shared" si="2"/>
         <v>36.149567272802649</v>
       </c>
-      <c r="T56">
+      <c r="T56" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B57" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57">
+      <c r="B57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="1">
         <v>10.331110000000001</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="1">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="1">
         <v>0.99</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="1">
         <v>1.53</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="1">
         <v>1370</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I57" s="21">
+      <c r="I57" s="2">
         <v>5735</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="1">
         <v>1.66</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="1">
         <v>1.1399999999999999</v>
       </c>
-      <c r="L57">
+      <c r="L57" s="1">
         <v>0.26</v>
       </c>
-      <c r="M57">
+      <c r="M57" s="1">
         <v>4.0599999999999996</v>
       </c>
-      <c r="N57">
+      <c r="N57" s="1">
         <v>110.5126861</v>
       </c>
-      <c r="O57">
+      <c r="O57" s="1">
         <v>-57.384998000000003</v>
       </c>
-      <c r="P57">
+      <c r="P57" s="1">
         <v>179.36600000000001</v>
       </c>
-      <c r="Q57">
+      <c r="Q57" s="1">
         <v>9.9719999999999995</v>
       </c>
-      <c r="R57" s="9">
+      <c r="R57" s="1">
         <v>9.8465900000000008</v>
       </c>
-      <c r="S57">
+      <c r="S57" s="1">
         <f t="shared" si="2"/>
         <v>224.58825733889913</v>
       </c>
-      <c r="T57">
+      <c r="T57" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B58" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58">
+      <c r="B58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1">
         <v>6.7535809999999996</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="1">
         <v>0.58881357999999995</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="1">
         <v>0.10068326</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="1">
         <v>1180</v>
       </c>
-      <c r="I58" s="21">
+      <c r="I58" s="2">
         <v>5808</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="1">
         <v>1.29</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L58">
+      <c r="L58" s="1">
         <v>0.2</v>
       </c>
-      <c r="M58">
+      <c r="M58" s="1">
         <v>4.26</v>
       </c>
-      <c r="N58">
+      <c r="N58" s="1">
         <v>166.26950410000001</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="1">
         <v>11.2464069</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="1">
         <v>130.91900000000001</v>
       </c>
-      <c r="Q58">
+      <c r="Q58" s="1">
         <v>9.75</v>
       </c>
-      <c r="R58" s="9">
+      <c r="R58" s="1">
         <v>9.6080000000000005</v>
       </c>
-      <c r="S58">
+      <c r="S58" s="1">
         <f t="shared" si="2"/>
         <v>1039.84328949877</v>
       </c>
-      <c r="T58">
+      <c r="T58" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59">
+      <c r="B59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="1">
         <v>10.590547000000001</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="1">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="1">
         <v>0.91890603000000004</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="1">
         <v>0.18469084999999999</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="1">
         <v>947</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I59" s="21">
+      <c r="I59" s="2">
         <v>6000</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="1">
         <v>1.0509999999999999</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="1">
         <v>1.1459999999999999</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="1">
         <v>0.09</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="1">
         <v>4.4400000000000004</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="1">
         <v>161.87955690000001</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="1">
         <v>36.329434499999998</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="1">
         <v>130.85499999999999</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="1">
         <v>10.058999999999999</v>
       </c>
-      <c r="R59" s="9">
+      <c r="R59" s="1">
         <v>9.9823299999999993</v>
       </c>
-      <c r="S59">
+      <c r="S59" s="1">
         <f t="shared" si="2"/>
         <v>1107.9861243219782</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B60" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60">
+      <c r="B60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="1">
         <v>5.8267310999999999</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="1">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="1">
         <v>0.57186287999999996</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="1">
         <v>0.24698861999999999</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="1">
         <v>1439</v>
       </c>
-      <c r="I60" s="21">
+      <c r="I60" s="2">
         <v>6110</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="1">
         <v>1.6479999999999999</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="1">
         <v>1.2909999999999999</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="1">
         <v>0.124</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="1">
         <v>4.1180000000000003</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="1">
         <v>51.657269100000001</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="1">
         <v>40.817270399999998</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="1">
         <v>179.14699999999999</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="1">
         <v>9.9130000000000003</v>
       </c>
-      <c r="R60" s="9">
+      <c r="R60" s="1">
         <v>9.7295700000000007</v>
       </c>
-      <c r="S60">
+      <c r="S60" s="1">
         <f t="shared" si="2"/>
         <v>487.59044264912109</v>
       </c>
-      <c r="T60">
+      <c r="T60" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B61" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61">
+      <c r="B61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="1">
         <v>6.4025129999999999</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="1">
         <v>7.0800000000000002E-2</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="1">
         <v>0.82399999999999995</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="1">
         <v>0.30299999999999999</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="1">
         <v>1388</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I61" s="21">
+      <c r="I61" s="2">
         <v>6400</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="1">
         <v>1.415</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="1">
         <v>1.3129999999999999</v>
       </c>
-      <c r="L61">
+      <c r="L61" s="1">
         <v>0.09</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="1">
         <v>4.2</v>
       </c>
-      <c r="N61">
+      <c r="N61" s="1">
         <v>125.3050544</v>
       </c>
-      <c r="O61">
+      <c r="O61" s="1">
         <v>-46.484295899999999</v>
       </c>
-      <c r="P61">
+      <c r="P61" s="1">
         <v>123.297</v>
       </c>
-      <c r="Q61">
+      <c r="Q61" s="1">
         <v>8.9949999999999992</v>
       </c>
-      <c r="R61" s="9">
+      <c r="R61" s="1">
         <v>8.8910300000000007</v>
       </c>
-      <c r="S61">
+      <c r="S61" s="1">
         <f t="shared" si="2"/>
         <v>795.95548671567838</v>
       </c>
-      <c r="T61">
+      <c r="T61" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B62" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62">
+      <c r="B62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="1">
         <v>11.236598499999999</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="1">
         <v>0.1041</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="1">
         <v>1.17</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="1">
         <v>1.234</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="1">
         <v>1252</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I62" s="21">
+      <c r="I62" s="2">
         <v>6295</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="1">
         <v>1.28</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="1">
         <v>1.181</v>
       </c>
-      <c r="L62">
+      <c r="L62" s="1">
         <v>0</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="1">
         <v>4.2910000000000004</v>
       </c>
-      <c r="N62">
+      <c r="N62" s="1">
         <v>144.11935940000001</v>
       </c>
-      <c r="O62">
+      <c r="O62" s="1">
         <v>-50.463093299999997</v>
       </c>
-      <c r="P62">
+      <c r="P62" s="1">
         <v>141.81200000000001</v>
       </c>
-      <c r="Q62">
+      <c r="Q62" s="1">
         <v>9.8219999999999992</v>
       </c>
-      <c r="R62" s="9">
+      <c r="R62" s="1">
         <v>9.6608199999999993</v>
       </c>
-      <c r="S62">
+      <c r="S62" s="1">
         <f t="shared" si="2"/>
         <v>355.42536038318485</v>
       </c>
-      <c r="T62">
+      <c r="T62" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B63" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63">
+      <c r="B63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="1">
         <v>4.6336110000000001</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>0.06</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="1">
         <v>1.37</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="1">
         <v>2.8</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="1">
         <v>1561</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I63" s="21">
+      <c r="I63" s="2">
         <v>6643</v>
       </c>
-      <c r="J63">
+      <c r="J63" s="1">
         <v>1.71</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="1">
         <v>1.4</v>
       </c>
-      <c r="L63">
+      <c r="L63" s="1">
         <v>0</v>
       </c>
-      <c r="M63">
+      <c r="M63" s="1">
         <v>4.05</v>
       </c>
-      <c r="N63">
+      <c r="N63" s="1">
         <v>199.33385029999999</v>
       </c>
-      <c r="O63">
+      <c r="O63" s="1">
         <v>-15.2737046</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="1">
         <v>161.74299999999999</v>
       </c>
-      <c r="Q63">
+      <c r="Q63" s="1">
         <v>9.109</v>
       </c>
-      <c r="R63" s="9">
+      <c r="R63" s="1">
         <v>8.9943600000000004</v>
       </c>
-      <c r="S63">
+      <c r="S63" s="1">
         <f t="shared" si="2"/>
         <v>267.77715667890726</v>
       </c>
-      <c r="T63">
+      <c r="T63" s="1">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="I64" s="22">
+      <c r="I64" s="5">
         <v>6161.02294921875</v>
       </c>
-      <c r="J64" s="16">
+      <c r="J64" s="6">
         <v>1.7061723470687871</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="1">
         <v>1.3463604</v>
       </c>
-      <c r="M64" s="16">
+      <c r="M64" s="6">
         <v>3.9825000762939449</v>
       </c>
-      <c r="N64">
+      <c r="N64" s="1">
         <v>268.30433503422898</v>
       </c>
-      <c r="O64" s="16">
+      <c r="O64" s="6">
         <v>37.211736733677057</v>
       </c>
-      <c r="P64">
+      <c r="P64" s="1">
         <v>496.26729999999998</v>
       </c>
-      <c r="Q64" s="16">
+      <c r="Q64" s="6">
         <v>11.469913482666019</v>
       </c>
-      <c r="R64" s="16">
+      <c r="R64" s="6">
         <v>11.469913482666019</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B65" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" s="21">
+      <c r="B65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="2">
         <v>6200</v>
       </c>
-      <c r="J65">
+      <c r="J65" s="1">
         <v>1.2</v>
       </c>
-      <c r="N65">
+      <c r="N65" s="1">
         <v>97.636728000000005</v>
       </c>
-      <c r="O65">
+      <c r="O65" s="1">
         <v>29.672419000000001</v>
       </c>
-      <c r="P65">
+      <c r="P65" s="1">
         <v>427</v>
       </c>
-      <c r="R65" s="9">
+      <c r="R65" s="1">
         <v>11.4986</v>
       </c>
-      <c r="T65">
+      <c r="T65" s="1">
         <f t="shared" ref="T65:T85" si="4">IF(I65&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="A66" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B66" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66">
+      <c r="B66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="1">
         <v>5.3220124999999996</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>6.08E-2</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="1">
         <v>1.226</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="1">
         <v>0.27300000000000002</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="1">
         <v>1460</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I66" s="21">
+      <c r="I66" s="2">
         <v>5990</v>
       </c>
-      <c r="J66">
+      <c r="J66" s="1">
         <v>1.5609999999999999</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="1">
         <v>1.06</v>
       </c>
-      <c r="L66">
+      <c r="L66" s="1">
         <v>-0.2</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="1">
         <v>4.0750000000000002</v>
       </c>
-      <c r="N66">
+      <c r="N66" s="1">
         <v>210.1935714</v>
       </c>
-      <c r="O66">
+      <c r="O66" s="1">
         <v>-30.583608399999999</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="1">
         <v>200.07499999999999</v>
       </c>
-      <c r="Q66">
+      <c r="Q66" s="1">
         <v>10.068</v>
       </c>
-      <c r="R66" s="9">
+      <c r="R66" s="1">
         <v>9.8670799999999996</v>
       </c>
-      <c r="S66">
+      <c r="S66" s="1">
         <f t="shared" ref="S66:S85" si="5">(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
         <v>2057.1154637812851</v>
       </c>
-      <c r="T66">
+      <c r="T66" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="A67" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B67" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67">
+      <c r="B67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="1">
         <v>5.21536178778</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>6.6100000000000006E-2</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="1">
         <v>1.5</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="1">
         <v>1.51</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="1">
         <v>1630</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I67" s="21">
+      <c r="I67" s="2">
         <v>6250</v>
       </c>
-      <c r="J67">
+      <c r="J67" s="1">
         <v>2.3901400000000002</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="1">
         <v>1.41</v>
       </c>
-      <c r="L67">
+      <c r="L67" s="1">
         <v>-0.18</v>
       </c>
-      <c r="M67">
+      <c r="M67" s="1">
         <v>3.9</v>
       </c>
-      <c r="N67">
+      <c r="N67" s="1">
         <v>0.32576100000000002</v>
       </c>
-      <c r="O67">
+      <c r="O67" s="1">
         <v>-8.9262511999999994</v>
       </c>
-      <c r="P67">
+      <c r="P67" s="1">
         <v>275.58699999999999</v>
       </c>
-      <c r="Q67">
+      <c r="Q67" s="1">
         <v>9.9740000000000002</v>
       </c>
-      <c r="R67" s="9">
+      <c r="R67" s="1">
         <v>9.8192900000000005</v>
       </c>
-      <c r="S67">
+      <c r="S67" s="1">
         <f t="shared" si="5"/>
         <v>621.55661806820979</v>
       </c>
-      <c r="T67">
+      <c r="T67" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="A68" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B68" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68">
+      <c r="B68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="1">
         <v>2.2437499999999999</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="1">
         <v>1.38</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="1">
         <v>8.84</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="1">
         <v>1872</v>
       </c>
-      <c r="I68" s="21">
+      <c r="I68" s="2">
         <v>6475</v>
       </c>
-      <c r="J68">
+      <c r="J68" s="1">
         <v>1.4</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="1">
         <v>1.62</v>
       </c>
-      <c r="L68">
+      <c r="L68" s="1">
         <v>0</v>
       </c>
-      <c r="M68">
+      <c r="M68" s="1">
         <v>4.07</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="1">
         <v>218.27662470000001</v>
       </c>
-      <c r="O68">
+      <c r="O68" s="1">
         <v>21.8946875</v>
       </c>
-      <c r="P68">
+      <c r="P68" s="1">
         <v>161.99700000000001</v>
       </c>
-      <c r="Q68">
+      <c r="Q68" s="1">
         <v>9.7449999999999992</v>
       </c>
-      <c r="R68" s="9">
+      <c r="R68" s="1">
         <v>9.6464700000000008</v>
       </c>
-      <c r="S68">
+      <c r="S68" s="1">
         <f t="shared" si="5"/>
         <v>103.20465157174387</v>
       </c>
-      <c r="T68">
+      <c r="T68" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B69" t="s">
-        <v>20</v>
-      </c>
-      <c r="C69">
+      <c r="B69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="1">
         <v>5.4435399999999996</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>6.4100000000000004E-2</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="1">
         <v>0.63</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="1">
         <v>0.10100000000000001</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="1">
         <v>1270</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I69" s="21">
+      <c r="I69" s="2">
         <v>6050</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="1">
         <v>1.22</v>
       </c>
-      <c r="K69">
+      <c r="K69" s="1">
         <v>1.19</v>
       </c>
-      <c r="L69">
+      <c r="L69" s="1">
         <v>0.19</v>
       </c>
-      <c r="M69">
+      <c r="M69" s="1">
         <v>4.34</v>
       </c>
-      <c r="N69">
+      <c r="N69" s="1">
         <v>144.87510470000001</v>
       </c>
-      <c r="O69">
+      <c r="O69" s="1">
         <v>-20.982419100000001</v>
       </c>
-      <c r="P69">
+      <c r="P69" s="1">
         <v>114.173</v>
       </c>
-      <c r="Q69">
+      <c r="Q69" s="1">
         <v>9.3510000000000009</v>
       </c>
-      <c r="R69" s="9">
+      <c r="R69" s="1">
         <v>9.2569999999999997</v>
       </c>
-      <c r="S69">
+      <c r="S69" s="1">
         <f t="shared" si="5"/>
         <v>1277.1766379712274</v>
       </c>
-      <c r="T69">
+      <c r="T69" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B70" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70">
+      <c r="B70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="1">
         <v>3.3448285000000002</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
         <v>5.5800000000000002E-2</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="1">
         <v>1.81</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="1">
         <v>1.66</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="1">
         <v>2470</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I70" s="21">
+      <c r="I70" s="2">
         <v>9360</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="1">
         <v>1.67</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="1">
         <v>2.0699999999999998</v>
       </c>
-      <c r="L70">
+      <c r="L70" s="1">
         <v>0.21</v>
       </c>
-      <c r="M70">
+      <c r="M70" s="1">
         <v>4.3099999999999996</v>
       </c>
-      <c r="N70">
+      <c r="N70" s="1">
         <v>227.270329</v>
       </c>
-      <c r="O70">
+      <c r="O70" s="1">
         <v>-42.704965799999997</v>
       </c>
-      <c r="P70">
+      <c r="P70" s="1">
         <v>427.678</v>
       </c>
-      <c r="Q70">
+      <c r="Q70" s="1">
         <v>9.9459999999999997</v>
       </c>
-      <c r="R70" s="9">
+      <c r="R70" s="1">
         <v>9.9122599999999998</v>
       </c>
-      <c r="S70">
+      <c r="S70" s="1">
         <f t="shared" si="5"/>
         <v>1247.4798366438731</v>
       </c>
-      <c r="T70">
+      <c r="T70" s="1">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B71" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71">
+      <c r="B71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="1">
         <v>0.94145223</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>2.0240000000000001E-2</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="1">
         <v>1.24</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="1">
         <v>10.199999999999999</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="1">
         <v>2429</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I71" s="21">
+      <c r="I71" s="2">
         <v>6432</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="1">
         <v>1.319</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="1">
         <v>1.294</v>
       </c>
-      <c r="L71">
+      <c r="L71" s="1">
         <v>0.107</v>
       </c>
-      <c r="M71">
+      <c r="M71" s="1">
         <v>4.3099999999999996</v>
       </c>
-      <c r="N71">
+      <c r="N71" s="1">
         <v>24.354461799999999</v>
       </c>
-      <c r="O71">
+      <c r="O71" s="1">
         <v>-45.677793700000002</v>
       </c>
-      <c r="P71">
+      <c r="P71" s="1">
         <v>123.483</v>
       </c>
-      <c r="Q71">
+      <c r="Q71" s="1">
         <v>9.2799999999999994</v>
       </c>
-      <c r="R71" s="9">
+      <c r="R71" s="1">
         <v>9.1661699999999993</v>
       </c>
-      <c r="S71">
+      <c r="S71" s="1">
         <f t="shared" si="5"/>
         <v>93.704022194109143</v>
       </c>
-      <c r="T71">
+      <c r="T71" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B72" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" s="6">
+      <c r="B72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="1">
         <v>2.7240329999999999</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="1">
         <v>5.0529999999999999E-2</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="1">
         <v>1.619</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="1">
         <v>1.99</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G72" s="1">
         <v>3353</v>
       </c>
-      <c r="H72" s="6"/>
-      <c r="I72" s="24">
+      <c r="I72" s="2">
         <v>8000</v>
       </c>
-      <c r="J72" s="6">
+      <c r="J72" s="1">
         <v>2.36</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="1">
         <v>2.0299999999999998</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="1">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="1">
         <v>3.9</v>
       </c>
-      <c r="N72" s="6">
+      <c r="N72" s="1">
         <v>225.68673200000001</v>
       </c>
-      <c r="O72" s="6">
+      <c r="O72" s="1">
         <v>-3.0314874000000001</v>
       </c>
-      <c r="P72" s="6">
+      <c r="P72" s="1">
         <v>99.730999999999995</v>
       </c>
-      <c r="Q72" s="6">
+      <c r="Q72" s="1">
         <v>6.5977600000000001</v>
       </c>
-      <c r="R72" s="9">
+      <c r="R72" s="1">
         <v>6.5536899999999996</v>
       </c>
-      <c r="S72" s="8">
+      <c r="S72" s="15">
         <f t="shared" si="5"/>
         <v>1130.2166328238993</v>
       </c>
-      <c r="T72" s="6">
+      <c r="T72" s="1">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
-      <c r="U72" s="7" t="s">
+      <c r="U72" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B73" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73">
+      <c r="B73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="1">
         <v>1.21987</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="1">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="1">
         <v>1.593</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="1">
         <v>2.093</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="1">
         <v>2781.7</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I73" s="21">
+      <c r="I73" s="2">
         <v>7430</v>
       </c>
-      <c r="J73">
+      <c r="J73" s="1">
         <v>1.444</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="1">
         <v>1.4950000000000001</v>
       </c>
-      <c r="L73">
+      <c r="L73" s="1">
         <v>0.1</v>
       </c>
-      <c r="M73">
+      <c r="M73" s="1">
         <v>4.25</v>
       </c>
-      <c r="N73">
+      <c r="N73" s="1">
         <v>36.712737500000003</v>
       </c>
-      <c r="O73">
+      <c r="O73" s="1">
         <v>37.5504441</v>
       </c>
-      <c r="P73">
+      <c r="P73" s="1">
         <v>121.944</v>
       </c>
-      <c r="Q73">
+      <c r="Q73" s="1">
         <v>8.14</v>
       </c>
-      <c r="R73" s="9">
+      <c r="R73" s="1">
         <v>8.0700400000000005</v>
       </c>
-      <c r="S73">
+      <c r="S73" s="1">
         <f t="shared" si="5"/>
         <v>863.09804630713359</v>
       </c>
-      <c r="T73">
+      <c r="T73" s="1">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B74" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74">
+      <c r="B74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="1">
         <v>6.87188</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="1">
         <v>7.5219999999999995E-2</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="1">
         <v>1.23</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="1">
         <v>3.44</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="1">
         <v>1250</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I74" s="21">
+      <c r="I74" s="2">
         <v>6180</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="1">
         <v>1.52</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="1">
         <v>1.76</v>
       </c>
-      <c r="L74">
+      <c r="L74" s="1">
         <v>-0.02</v>
       </c>
-      <c r="M74">
+      <c r="M74" s="1">
         <v>4.25</v>
       </c>
-      <c r="N74">
+      <c r="N74" s="1">
         <v>243.95971940000001</v>
       </c>
-      <c r="O74">
+      <c r="O74" s="1">
         <v>10.0324103</v>
       </c>
-      <c r="P74">
+      <c r="P74" s="1">
         <v>136.24</v>
       </c>
-      <c r="Q74">
+      <c r="Q74" s="1">
         <v>9.391</v>
       </c>
-      <c r="R74" s="9">
+      <c r="R74" s="1">
         <v>9.20974</v>
       </c>
-      <c r="S74">
+      <c r="S74" s="1">
         <f t="shared" si="5"/>
         <v>140.68549179703928</v>
       </c>
-      <c r="T74">
+      <c r="T74" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B75" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75" s="6">
+      <c r="B75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="1">
         <v>3.86813881</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="1">
         <v>4.53E-2</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="1">
         <v>0.26</v>
       </c>
-      <c r="G75" s="6">
+      <c r="G75" s="1">
         <v>971</v>
       </c>
-      <c r="H75" s="6" t="s">
+      <c r="H75" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I75" s="24">
+      <c r="I75" s="2">
         <v>4792</v>
       </c>
-      <c r="J75" s="6">
+      <c r="J75" s="1">
         <v>0.80100000000000005</v>
       </c>
-      <c r="K75" s="6">
+      <c r="K75" s="1">
         <v>0.83</v>
       </c>
-      <c r="L75" s="6">
+      <c r="L75" s="1">
         <v>0.35</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="1">
         <v>4.57</v>
       </c>
-      <c r="N75" s="6">
+      <c r="N75" s="1">
         <v>315.02596610000001</v>
       </c>
-      <c r="O75" s="6">
+      <c r="O75" s="1">
         <v>-5.0948570000000002</v>
       </c>
-      <c r="P75" s="6">
+      <c r="P75" s="1">
         <v>49.960500000000003</v>
       </c>
-      <c r="Q75" s="6">
+      <c r="Q75" s="1">
         <v>9.8729999999999993</v>
       </c>
-      <c r="R75" s="9">
+      <c r="R75" s="1">
         <v>9.4846599999999999</v>
       </c>
-      <c r="S75" s="6">
+      <c r="S75" s="1">
         <f t="shared" si="5"/>
         <v>955.72600175951948</v>
       </c>
-      <c r="T75" s="6">
+      <c r="T75" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
-      <c r="U75" s="7" t="s">
+      <c r="U75" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="A76" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B76" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76">
+      <c r="B76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="1">
         <v>4.9546416000000004</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
         <v>6.1699999999999998E-2</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="1">
         <v>1.33</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="1">
         <v>0.96</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="1">
         <v>1487</v>
       </c>
-      <c r="I76" s="21">
+      <c r="I76" s="2">
         <v>6400</v>
       </c>
-      <c r="J76">
+      <c r="J76" s="1">
         <v>1.4319999999999999</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="1">
         <v>1.276</v>
       </c>
-      <c r="L76">
+      <c r="L76" s="1">
         <v>0</v>
       </c>
-      <c r="M76">
+      <c r="M76" s="1">
         <v>4.2320000000000002</v>
       </c>
-      <c r="N76">
+      <c r="N76" s="1">
         <v>311.04275580000001</v>
       </c>
-      <c r="O76">
+      <c r="O76" s="1">
         <v>-39.225485599999999</v>
       </c>
-      <c r="P76">
+      <c r="P76" s="1">
         <v>162.303</v>
       </c>
-      <c r="Q76">
+      <c r="Q76" s="1">
         <v>9.5039999999999996</v>
       </c>
-      <c r="R76" s="9">
+      <c r="R76" s="1">
         <v>9.3767099999999992</v>
       </c>
-      <c r="S76">
+      <c r="S76" s="1">
         <f t="shared" si="5"/>
         <v>701.18164217622461</v>
       </c>
-      <c r="T76">
+      <c r="T76" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B77" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77">
+      <c r="B77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="1">
         <v>2.13775</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
         <v>3.4430000000000002E-2</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="1">
         <v>1.36</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="1">
         <v>0.72</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="1">
         <v>1865</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I77" s="21">
+      <c r="I77" s="2">
         <v>5990</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="1">
         <v>1.42</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="1">
         <v>0.98</v>
       </c>
-      <c r="L77">
+      <c r="L77" s="1">
         <v>0.39</v>
       </c>
-      <c r="M77">
+      <c r="M77" s="1">
         <v>4.3899999999999997</v>
       </c>
-      <c r="N77">
+      <c r="N77" s="1">
         <v>304.53884299999999</v>
       </c>
-      <c r="O77">
+      <c r="O77" s="1">
         <v>-1.0760033</v>
       </c>
-      <c r="P77">
+      <c r="P77" s="1">
         <v>149.21600000000001</v>
       </c>
-      <c r="Q77">
+      <c r="Q77" s="1">
         <v>9.75</v>
       </c>
-      <c r="R77" s="9">
+      <c r="R77" s="1">
         <v>9.5723000000000003</v>
       </c>
-      <c r="S77">
+      <c r="S77" s="1">
         <f t="shared" si="5"/>
         <v>1226.0598654781754</v>
       </c>
-      <c r="T77">
+      <c r="T77" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B78" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78">
+      <c r="B78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="1">
         <v>1.8098819799999999</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="1">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="1">
         <v>1.8540000000000001</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="1">
         <v>0.89400000000000002</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="1">
         <v>2228</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I78" s="21">
+      <c r="I78" s="2">
         <v>6329</v>
       </c>
-      <c r="J78">
+      <c r="J78" s="1">
         <v>1.756</v>
       </c>
-      <c r="K78">
+      <c r="K78" s="1">
         <v>1.458</v>
       </c>
-      <c r="L78">
+      <c r="L78" s="1">
         <v>0.36599999999999999</v>
       </c>
-      <c r="M78">
+      <c r="M78" s="1">
         <v>4.1959999999999997</v>
       </c>
-      <c r="N78">
+      <c r="N78" s="1">
         <v>26.632936000000001</v>
       </c>
-      <c r="O78">
+      <c r="O78" s="1">
         <v>2.7003889999999999</v>
       </c>
-      <c r="P78">
+      <c r="P78" s="1">
         <v>194.459</v>
       </c>
-      <c r="Q78">
+      <c r="Q78" s="1">
         <v>9.5180000000000007</v>
       </c>
-      <c r="R78" s="9">
+      <c r="R78" s="1">
         <v>9.3950700000000005</v>
       </c>
-      <c r="S78">
+      <c r="S78" s="1">
         <f t="shared" si="5"/>
         <v>2192.2225820487197</v>
       </c>
-      <c r="T78">
+      <c r="T78" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79">
+      <c r="B79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="1">
         <v>3.6623920000000001</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
         <v>5.1900000000000002E-2</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="1">
         <v>1.53</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="1">
         <v>0.85</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="1">
         <v>1716.2</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="I79" s="21">
+      <c r="I79" s="2">
         <v>6600</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="1">
         <v>1.51</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="1">
         <v>1.39</v>
       </c>
-      <c r="L79">
+      <c r="L79" s="1">
         <v>0.03</v>
       </c>
-      <c r="M79">
+      <c r="M79" s="1">
         <v>4.2</v>
       </c>
-      <c r="N79">
+      <c r="N79" s="1">
         <v>66.370901599999996</v>
       </c>
-      <c r="O79">
+      <c r="O79" s="1">
         <v>-30.600436200000001</v>
       </c>
-      <c r="P79">
+      <c r="P79" s="1">
         <v>246.69</v>
       </c>
-      <c r="Q79">
+      <c r="Q79" s="1">
         <v>10.044</v>
       </c>
-      <c r="R79" s="9">
+      <c r="R79" s="1">
         <v>9.9720200000000006</v>
       </c>
-      <c r="S79">
+      <c r="S79" s="1">
         <f t="shared" si="5"/>
         <v>1209.5375438309629</v>
       </c>
-      <c r="T79">
+      <c r="T79" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80">
+      <c r="B80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="1">
         <v>8.1587200000000006</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
         <v>8.0100000000000005E-2</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="1">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="1">
         <v>2.54</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="1">
         <v>1059</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I80" s="21">
+      <c r="I80" s="2">
         <v>5600</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="1">
         <v>1.03</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="1">
         <v>1.34</v>
       </c>
-      <c r="L80">
+      <c r="L80" s="1">
         <v>0.17</v>
       </c>
-      <c r="M80">
+      <c r="M80" s="1">
         <v>4.5</v>
       </c>
-      <c r="N80">
+      <c r="N80" s="1">
         <v>359.90087369999998</v>
       </c>
-      <c r="O80">
+      <c r="O80" s="1">
         <v>-35.031334899999997</v>
       </c>
-      <c r="P80">
+      <c r="P80" s="1">
         <v>89.960599999999999</v>
       </c>
-      <c r="Q80">
+      <c r="Q80" s="1">
         <v>9.7889999999999997</v>
       </c>
-      <c r="R80" s="9">
+      <c r="R80" s="1">
         <v>9.6124899999999993</v>
       </c>
-      <c r="S80">
+      <c r="S80" s="1">
         <f t="shared" si="5"/>
         <v>136.24063220140397</v>
       </c>
-      <c r="T80">
+      <c r="T80" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B81" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81">
+      <c r="B81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="1">
         <v>2.7057899999999999</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="1">
         <v>4.4699999999999997E-2</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="1">
         <v>1.62</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="1">
         <v>1.17</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="1">
         <v>2190</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="I81" s="26">
+      <c r="I81" s="14">
         <v>6480</v>
       </c>
-      <c r="J81" s="15">
+      <c r="J81" s="13">
         <v>2.1</v>
       </c>
-      <c r="K81">
+      <c r="K81" s="1">
         <v>1.48</v>
       </c>
-      <c r="L81">
+      <c r="L81" s="1">
         <v>0.12</v>
       </c>
-      <c r="M81" s="15">
+      <c r="M81" s="13">
         <v>3.96</v>
       </c>
-      <c r="N81" s="15">
+      <c r="N81" s="13">
         <v>72.660591600000004</v>
       </c>
-      <c r="O81" s="15">
+      <c r="O81" s="13">
         <v>1.8938364999999999</v>
       </c>
-      <c r="P81">
+      <c r="P81" s="1">
         <v>275.66399999999999</v>
       </c>
-      <c r="Q81" s="15">
+      <c r="Q81" s="13">
         <v>10.073</v>
       </c>
-      <c r="R81" s="18">
+      <c r="R81" s="13">
         <v>9.8979599999999994</v>
       </c>
-      <c r="S81">
+      <c r="S81" s="1">
         <f t="shared" si="5"/>
         <v>1257.117296864338</v>
       </c>
-      <c r="T81">
+      <c r="T81" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82">
+      <c r="B82" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="1">
         <v>3.9501900000000001</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="1">
         <v>1.58</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="1">
         <v>0.5</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="1">
         <v>1604</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I82" s="26">
+      <c r="I82" s="14">
         <v>6170</v>
       </c>
-      <c r="J82" s="15">
+      <c r="J82" s="13">
         <v>1.48</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="1">
         <v>1.67</v>
       </c>
-      <c r="L82">
+      <c r="L82" s="1">
         <v>0.26</v>
       </c>
-      <c r="M82" s="15">
+      <c r="M82" s="13">
         <v>4.2699999999999996</v>
       </c>
-      <c r="N82" s="15">
+      <c r="N82" s="13">
         <v>313.78323929999999</v>
       </c>
-      <c r="O82" s="15">
+      <c r="O82" s="13">
         <v>-34.135751200000001</v>
       </c>
-      <c r="P82">
+      <c r="P82" s="1">
         <v>211.21100000000001</v>
       </c>
-      <c r="Q82" s="15">
+      <c r="Q82" s="13">
         <v>10.051</v>
       </c>
-      <c r="R82" s="18">
+      <c r="R82" s="13">
         <v>10.028499999999999</v>
       </c>
-      <c r="S82">
+      <c r="S82" s="1">
         <f t="shared" si="5"/>
         <v>2049.4439875099679</v>
       </c>
-      <c r="T82">
+      <c r="T82" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B83" t="s">
-        <v>20</v>
-      </c>
-      <c r="C83">
+      <c r="B83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="1">
         <v>2.1846700000000001</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="1">
         <v>3.4160000000000003E-2</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="1">
         <v>1.23</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="1">
         <v>1.44</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="1">
         <v>1570</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I83" s="26">
+      <c r="I83" s="14">
         <v>5830</v>
       </c>
-      <c r="J83" s="15">
+      <c r="J83" s="13">
         <v>1.23</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="1">
         <v>1.46</v>
       </c>
-      <c r="L83">
+      <c r="L83" s="1">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M83" s="15">
+      <c r="M83" s="13">
         <v>4.3600000000000003</v>
       </c>
-      <c r="N83" s="15">
+      <c r="N83" s="13">
         <v>337.45782430000003</v>
       </c>
-      <c r="O83" s="15">
+      <c r="O83" s="13">
         <v>-48.003098799999997</v>
       </c>
-      <c r="P83">
+      <c r="P83" s="1">
         <v>137.54400000000001</v>
       </c>
-      <c r="Q83" s="15">
+      <c r="Q83" s="13">
         <v>10.092000000000001</v>
       </c>
-      <c r="R83" s="18">
+      <c r="R83" s="13">
         <v>9.9369700000000005</v>
       </c>
-      <c r="S83">
+      <c r="S83" s="1">
         <f t="shared" si="5"/>
         <v>422.11900227636102</v>
       </c>
-      <c r="T83">
+      <c r="T83" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B84" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84">
+      <c r="B84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="1">
         <v>5.75251</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="1">
         <v>7.17E-2</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="1">
         <v>1.02</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="1">
         <v>1480</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I84" s="26">
+      <c r="I84" s="14">
         <v>6150</v>
       </c>
-      <c r="J84" s="15">
+      <c r="J84" s="13">
         <v>1.64</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="1">
         <v>1.21</v>
       </c>
-      <c r="L84">
+      <c r="L84" s="1">
         <v>0.21</v>
       </c>
-      <c r="M84" s="15">
+      <c r="M84" s="13">
         <v>4.3</v>
       </c>
-      <c r="N84" s="15">
+      <c r="N84" s="13">
         <v>39.897668899999999</v>
       </c>
-      <c r="O84" s="15">
+      <c r="O84" s="13">
         <v>-50.008193400000003</v>
       </c>
-      <c r="P84">
+      <c r="P84" s="1">
         <v>158.66</v>
       </c>
-      <c r="Q84" s="15">
+      <c r="Q84" s="13">
         <v>9.4749999999999996</v>
       </c>
-      <c r="R84" s="15">
+      <c r="R84" s="13">
         <v>9.3251000000000008</v>
       </c>
-      <c r="S84">
+      <c r="S84" s="1">
         <f t="shared" si="5"/>
         <v>162.15983922320817</v>
       </c>
-      <c r="T84">
+      <c r="T84" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B85" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85">
+      <c r="B85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" s="1">
         <v>3.1915399999999998</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="1">
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="1">
         <v>1.41</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="1">
         <v>7.29</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="1">
         <v>1729</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I85" s="27">
+      <c r="I85" s="17">
         <v>6429</v>
       </c>
-      <c r="J85" s="17">
+      <c r="J85" s="18">
         <v>1.54</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L85">
+      <c r="L85" s="1">
         <v>-0.18</v>
       </c>
-      <c r="M85" s="17">
+      <c r="M85" s="18">
         <v>3.95</v>
       </c>
-      <c r="N85">
+      <c r="N85" s="1">
         <v>65.469581399999996</v>
       </c>
-      <c r="O85" s="17">
+      <c r="O85" s="18">
         <v>57.817209499999997</v>
       </c>
-      <c r="P85">
+      <c r="P85" s="1">
         <v>213.053</v>
       </c>
-      <c r="Q85" s="17">
+      <c r="Q85" s="18">
         <v>9.8539999999999992</v>
       </c>
-      <c r="R85" s="17">
+      <c r="R85" s="18">
         <v>9.7388899999999996</v>
       </c>
-      <c r="S85">
+      <c r="S85" s="1">
         <f t="shared" si="5"/>
         <v>120.66830436099001</v>
       </c>
-      <c r="T85">
+      <c r="T85" s="1">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I86" s="26">
+      <c r="I86" s="2">
         <v>3460</v>
       </c>
-      <c r="J86" s="15">
+      <c r="J86" s="1">
         <v>0.54700000000000004</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="1">
         <v>0.54300000000000004</v>
       </c>
-      <c r="L86">
+      <c r="L86" s="1">
         <v>0</v>
       </c>
-      <c r="M86">
+      <c r="M86" s="1">
         <v>4.6963999999999997</v>
       </c>
-      <c r="N86">
+      <c r="N86" s="1">
         <v>303.19871318011002</v>
       </c>
-      <c r="O86">
+      <c r="O86" s="1">
         <v>-0.37849292589</v>
       </c>
-      <c r="P86">
+      <c r="P86" s="1">
         <v>312.65899999999999</v>
       </c>
-      <c r="R86"/>
-      <c r="V86">
+      <c r="V86" s="1">
         <v>10.968999999999999</v>
       </c>
-      <c r="W86">
+      <c r="W86" s="1">
         <v>11.454000000000001</v>
       </c>
-      <c r="X86" t="s">
+      <c r="X86" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Y86" t="s">
+      <c r="Y86" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I87" s="26">
+      <c r="I87" s="2">
         <v>3496</v>
       </c>
-      <c r="J87" s="15">
+      <c r="J87" s="1">
         <v>83.710999999999999</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="1">
         <v>0</v>
       </c>
-      <c r="L87">
+      <c r="L87" s="1">
         <v>0</v>
       </c>
-      <c r="M87">
+      <c r="M87" s="1">
         <v>0</v>
       </c>
-      <c r="N87">
+      <c r="N87" s="1">
         <v>293.64838257128002</v>
       </c>
-      <c r="O87">
+      <c r="O87" s="1">
         <v>-12.35499539692</v>
       </c>
-      <c r="P87">
+      <c r="P87" s="1">
         <v>1655.31</v>
       </c>
-      <c r="V87">
+      <c r="V87" s="1">
         <v>10.977</v>
       </c>
-      <c r="W87">
+      <c r="W87" s="1">
         <v>12.571999999999999</v>
       </c>
-      <c r="X87" t="s">
+      <c r="X87" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="Y87" t="s">
+      <c r="Y87" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="A88" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I88" s="21">
-        <v>5827</v>
-      </c>
-      <c r="J88">
-        <v>6.9720000000000004</v>
-      </c>
-      <c r="K88">
+      <c r="I88" s="2">
+        <v>5804</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1.179</v>
+      </c>
+      <c r="K88" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="L88" s="1">
         <v>0</v>
       </c>
-      <c r="L88">
+      <c r="M88" s="1">
+        <v>4.3121</v>
+      </c>
+      <c r="N88" s="1">
+        <v>274.86862255196002</v>
+      </c>
+      <c r="O88" s="1">
+        <v>5.3506741626599998</v>
+      </c>
+      <c r="P88" s="1">
+        <v>1644.4</v>
+      </c>
+      <c r="V88" s="1">
+        <v>15.965999999999999</v>
+      </c>
+      <c r="W88" s="1">
+        <v>16.86</v>
+      </c>
+      <c r="X88" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y88" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I89" s="2">
+        <v>5812</v>
+      </c>
+      <c r="J89" s="1">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="K89" s="1">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="L89" s="1">
         <v>0</v>
       </c>
-      <c r="M88">
+      <c r="M89" s="1">
+        <v>4.5917000000000003</v>
+      </c>
+      <c r="N89" s="1">
+        <v>47.805523543809997</v>
+      </c>
+      <c r="O89" s="1">
+        <v>-18.380477788619999</v>
+      </c>
+      <c r="P89" s="1">
+        <v>147.77799999999999</v>
+      </c>
+      <c r="V89" s="1">
+        <v>11.044</v>
+      </c>
+      <c r="W89" s="1">
+        <v>11.662000000000001</v>
+      </c>
+      <c r="X89" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y89" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I90" s="2">
+        <v>5815.4</v>
+      </c>
+      <c r="J90" s="1">
+        <v>4.2549999999999999</v>
+      </c>
+      <c r="K90" s="1">
         <v>0</v>
       </c>
-      <c r="N88">
-        <v>12.295169568029999</v>
-      </c>
-      <c r="O88">
-        <v>-40.067873380309997</v>
-      </c>
-      <c r="P88">
-        <v>1154.6099999999999</v>
-      </c>
-      <c r="V88">
-        <v>10.988</v>
-      </c>
-      <c r="W88">
-        <v>11.585000000000001</v>
-      </c>
-      <c r="X88" t="s">
+      <c r="L90" s="1">
+        <v>-0.19350000000000001</v>
+      </c>
+      <c r="M90" s="1">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1">
+        <v>80.600252814719994</v>
+      </c>
+      <c r="O90" s="1">
+        <v>-68.64221652773</v>
+      </c>
+      <c r="P90" s="1">
+        <v>398.375</v>
+      </c>
+      <c r="V90" s="1">
+        <v>11.137</v>
+      </c>
+      <c r="W90" s="1">
+        <v>11.56</v>
+      </c>
+      <c r="X90" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="Y88" t="s">
+      <c r="Y90" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>153</v>
-      </c>
-      <c r="I89" s="21">
-        <v>5798</v>
-      </c>
-      <c r="J89">
-        <v>1.288</v>
-      </c>
-      <c r="K89">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I91" s="2">
+        <v>5799</v>
+      </c>
+      <c r="J91" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="K91" s="1">
+        <v>1.042</v>
+      </c>
+      <c r="L91" s="1">
+        <v>0</v>
+      </c>
+      <c r="M91" s="1">
+        <v>4.4642999999999997</v>
+      </c>
+      <c r="N91" s="1">
+        <v>278.21725113665002</v>
+      </c>
+      <c r="O91" s="1">
+        <v>11.92287820316</v>
+      </c>
+      <c r="P91" s="1">
+        <v>224.12799999999999</v>
+      </c>
+      <c r="V91" s="1">
+        <v>11.997</v>
+      </c>
+      <c r="W91" s="1">
+        <v>12.47</v>
+      </c>
+      <c r="X91" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y91" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I92" s="2">
+        <v>5806</v>
+      </c>
+      <c r="J92" s="1">
+        <v>27.986999999999998</v>
+      </c>
+      <c r="K92" s="1">
+        <v>0</v>
+      </c>
+      <c r="L92" s="1">
+        <v>0</v>
+      </c>
+      <c r="M92" s="1">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1">
+        <v>278.48921850735002</v>
+      </c>
+      <c r="O92" s="1">
+        <v>31.640052119060002</v>
+      </c>
+      <c r="P92" s="1">
+        <v>7397.91</v>
+      </c>
+      <c r="V92" s="1">
+        <v>12.01</v>
+      </c>
+      <c r="W92" s="1">
+        <v>12.507</v>
+      </c>
+      <c r="X92" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y92" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I93" s="2">
+        <v>5775</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5.1109999999999998</v>
+      </c>
+      <c r="K93" s="1">
+        <v>0</v>
+      </c>
+      <c r="L93" s="1">
+        <v>0</v>
+      </c>
+      <c r="M93" s="1">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1">
+        <v>274.00302978329</v>
+      </c>
+      <c r="O93" s="1">
+        <v>22.9885348444</v>
+      </c>
+      <c r="P93" s="1">
+        <v>1802.37</v>
+      </c>
+      <c r="V93" s="1">
+        <v>12.961</v>
+      </c>
+      <c r="W93" s="1">
+        <v>14.082000000000001</v>
+      </c>
+      <c r="X93" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y93" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I94" s="2">
+        <v>5800.4</v>
+      </c>
+      <c r="J94" s="1">
+        <v>1.4930000000000001</v>
+      </c>
+      <c r="K94" s="1">
         <v>1.04</v>
       </c>
-      <c r="L89">
+      <c r="L94" s="1">
+        <v>-6.6000000000000003E-2</v>
+      </c>
+      <c r="M94" s="1">
+        <v>4.1069000000000004</v>
+      </c>
+      <c r="N94" s="1">
+        <v>270.30880152526998</v>
+      </c>
+      <c r="O94" s="1">
+        <v>15.944626030029999</v>
+      </c>
+      <c r="P94" s="1">
+        <v>579.08500000000004</v>
+      </c>
+      <c r="V94" s="1">
+        <v>12.978999999999999</v>
+      </c>
+      <c r="W94" s="1">
+        <v>13.638999999999999</v>
+      </c>
+      <c r="X94" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y94" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I95" s="2">
+        <v>5800</v>
+      </c>
+      <c r="J95" s="1">
+        <v>1.417</v>
+      </c>
+      <c r="K95" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="L95" s="1">
         <v>0</v>
       </c>
-      <c r="M89">
-        <v>4.2351999999999999</v>
-      </c>
-      <c r="N89">
-        <v>78.92072949976</v>
-      </c>
-      <c r="O89">
-        <v>-61.051005597089997</v>
-      </c>
-      <c r="P89">
-        <v>216.126</v>
-      </c>
-      <c r="V89">
-        <v>11.000999999999999</v>
-      </c>
-      <c r="W89">
-        <v>11.773999999999999</v>
-      </c>
-      <c r="X89" t="s">
+      <c r="M95" s="1">
+        <v>4.1520999999999999</v>
+      </c>
+      <c r="N95" s="1">
+        <v>280.34203579685999</v>
+      </c>
+      <c r="O95" s="1">
+        <v>26.315625519600001</v>
+      </c>
+      <c r="P95" s="1">
+        <v>897.52700000000004</v>
+      </c>
+      <c r="V95" s="1">
+        <v>13.994999999999999</v>
+      </c>
+      <c r="W95" s="1">
+        <v>14.913</v>
+      </c>
+      <c r="X95" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Y89" t="s">
+      <c r="Y95" s="1" t="s">
         <v>137</v>
       </c>
     </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I96" s="2">
+        <v>5824</v>
+      </c>
+      <c r="J96" s="1">
+        <v>4.7249999999999996</v>
+      </c>
+      <c r="K96" s="1">
+        <v>0</v>
+      </c>
+      <c r="L96" s="1">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1">
+        <v>284.95537150204001</v>
+      </c>
+      <c r="O96" s="1">
+        <v>14.42740619077</v>
+      </c>
+      <c r="P96" s="1">
+        <v>1961.4</v>
+      </c>
+      <c r="V96" s="1">
+        <v>14.023</v>
+      </c>
+      <c r="W96" s="1">
+        <v>15.048999999999999</v>
+      </c>
+      <c r="X96" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y96" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I97" s="2">
+        <v>5813</v>
+      </c>
+      <c r="J97" s="1">
+        <v>1.83</v>
+      </c>
+      <c r="K97" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="L97" s="1">
+        <v>0</v>
+      </c>
+      <c r="M97" s="1">
+        <v>3.9344999999999999</v>
+      </c>
+      <c r="N97" s="1">
+        <v>270.99233637095</v>
+      </c>
+      <c r="O97" s="1">
+        <v>16.858729226019999</v>
+      </c>
+      <c r="P97" s="1">
+        <v>1779.6</v>
+      </c>
+      <c r="V97" s="1">
+        <v>14.999000000000001</v>
+      </c>
+      <c r="W97" s="1">
+        <v>15.66</v>
+      </c>
+      <c r="X97" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y97" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I98" s="2">
+        <v>5820</v>
+      </c>
+      <c r="J98" s="1">
+        <v>6.2519999999999998</v>
+      </c>
+      <c r="K98" s="1">
+        <v>0</v>
+      </c>
+      <c r="L98" s="1">
+        <v>0</v>
+      </c>
+      <c r="M98" s="1">
+        <v>0</v>
+      </c>
+      <c r="N98" s="1">
+        <v>267.97432727351003</v>
+      </c>
+      <c r="O98" s="1">
+        <v>17.507747521020001</v>
+      </c>
+      <c r="P98" s="1">
+        <v>6401.77</v>
+      </c>
+      <c r="V98" s="1">
+        <v>15.007999999999999</v>
+      </c>
+      <c r="W98" s="1">
+        <v>15.702999999999999</v>
+      </c>
+      <c r="X98" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y98" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I99" s="2">
+        <v>5800</v>
+      </c>
+      <c r="J99" s="1">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="K99" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="L99" s="1">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1">
+        <v>4.2129000000000003</v>
+      </c>
+      <c r="N99" s="1">
+        <v>270.95467601665001</v>
+      </c>
+      <c r="O99" s="1">
+        <v>3.9944008770699999</v>
+      </c>
+      <c r="P99" s="1">
+        <v>2963.53</v>
+      </c>
+      <c r="V99" s="1">
+        <v>17.052</v>
+      </c>
+      <c r="W99" s="1">
+        <v>17.364000000000001</v>
+      </c>
+      <c r="X99" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y99" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I100" s="2">
+        <v>5816</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5.2939999999999996</v>
+      </c>
+      <c r="K100" s="1">
+        <v>0</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1">
+        <v>284.79622244569998</v>
+      </c>
+      <c r="O100" s="1">
+        <v>15.987368865140001</v>
+      </c>
+      <c r="P100" s="1">
+        <v>3747.72</v>
+      </c>
+      <c r="V100" s="1">
+        <v>15.958</v>
+      </c>
+      <c r="W100" s="1">
+        <v>17.585999999999999</v>
+      </c>
+      <c r="X100" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y100" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I101" s="2">
+        <v>5792</v>
+      </c>
+      <c r="J101" s="1">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1">
+        <v>276.67545984469001</v>
+      </c>
+      <c r="O101" s="1">
+        <v>14.0128749692</v>
+      </c>
+      <c r="P101" s="1">
+        <v>2046.66</v>
+      </c>
+      <c r="V101" s="1">
+        <v>17.097000000000001</v>
+      </c>
+      <c r="W101" s="1">
+        <v>18.082999999999998</v>
+      </c>
+      <c r="X101" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I102" s="2">
+        <v>3501</v>
+      </c>
+      <c r="J102" s="1">
+        <v>50.991</v>
+      </c>
+      <c r="K102" s="1">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1">
+        <v>0</v>
+      </c>
+      <c r="M102" s="1">
+        <v>0</v>
+      </c>
+      <c r="N102" s="1">
+        <v>254.47763000024</v>
+      </c>
+      <c r="O102" s="1">
+        <v>-23.844465202550001</v>
+      </c>
+      <c r="P102" s="1">
+        <v>1025.1500000000001</v>
+      </c>
+      <c r="V102" s="1">
+        <v>11.035</v>
+      </c>
+      <c r="W102" s="1">
+        <v>12.885999999999999</v>
+      </c>
+      <c r="X102" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y102" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U79" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U85">
-      <sortCondition ref="A1:A85"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:Y101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R79">
     <sortCondition ref="Q2"/>
   </sortState>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F477CA90-EA84-2A4D-91D1-7C97C04DEB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C94426-6C83-814D-9CC9-EC671FC572BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="600" windowWidth="43100" windowHeight="25500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13260" yWindow="4480" windowWidth="29920" windowHeight="13340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$Y$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$X$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="167">
   <si>
     <t>#pl_name</t>
   </si>
@@ -537,9 +537,6 @@
   </si>
   <si>
     <t>4113444695135680128 b</t>
-  </si>
-  <si>
-    <t>Roland</t>
   </si>
 </sst>
 </file>
@@ -586,25 +583,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -614,19 +598,6 @@
       <right style="thin">
         <color theme="0"/>
       </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
       <top style="thin">
         <color theme="0"/>
       </top>
@@ -656,56 +627,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -983,5961 +924,5875 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH102"/>
+  <dimension ref="A1:BC102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="11.1640625" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="11.33203125" style="1"/>
-    <col min="28" max="28" width="8" style="1"/>
-    <col min="29" max="29" width="9.83203125" style="1"/>
-    <col min="30" max="30" width="9" style="1"/>
-    <col min="31" max="31" width="8" style="1"/>
-    <col min="32" max="32" width="9.83203125" style="1"/>
-    <col min="33" max="33" width="9" style="1"/>
-    <col min="34" max="34" width="8" style="1"/>
-    <col min="35" max="35" width="9.83203125" style="1"/>
-    <col min="36" max="36" width="9" style="1"/>
-    <col min="37" max="40" width="8" style="1"/>
-    <col min="41" max="41" width="9.83203125" style="1"/>
-    <col min="42" max="42" width="9" style="1"/>
-    <col min="43" max="46" width="8" style="1"/>
-    <col min="47" max="47" width="9.83203125" style="1"/>
-    <col min="48" max="48" width="9" style="1"/>
-    <col min="49" max="49" width="8" style="1"/>
-    <col min="50" max="50" width="9.83203125" style="1"/>
-    <col min="51" max="51" width="9" style="1"/>
-    <col min="52" max="59" width="8" style="1"/>
-    <col min="60" max="60" width="8.1640625" style="1"/>
-    <col min="61" max="16384" width="8" style="1"/>
+    <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="11.1640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="7" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9"/>
+    <col min="27" max="27" width="9.83203125"/>
+    <col min="28" max="28" width="9"/>
+    <col min="30" max="30" width="9.83203125"/>
+    <col min="31" max="31" width="9"/>
+    <col min="36" max="36" width="9.83203125"/>
+    <col min="37" max="37" width="9"/>
+    <col min="42" max="42" width="9.83203125"/>
+    <col min="43" max="43" width="9"/>
+    <col min="45" max="45" width="9.83203125"/>
+    <col min="46" max="46" width="9"/>
+    <col min="55" max="55" width="8.1640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="Y1" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I2">
+        <v>3501</v>
+      </c>
+      <c r="J2">
+        <v>50.991</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>254.47763000024</v>
+      </c>
+      <c r="O2">
+        <v>-23.844465202550001</v>
+      </c>
+      <c r="P2">
+        <v>1025.1500000000001</v>
+      </c>
+      <c r="V2">
+        <v>11.035</v>
+      </c>
+      <c r="W2">
+        <v>12.885999999999999</v>
+      </c>
+      <c r="X2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AZ2" s="3"/>
+      <c r="BB2" s="3"/>
+      <c r="BC2" s="3"/>
+    </row>
+    <row r="3" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3">
+        <v>3496</v>
+      </c>
+      <c r="J3">
+        <v>83.710999999999999</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>293.64838257128002</v>
+      </c>
+      <c r="O3">
+        <v>-12.35499539692</v>
+      </c>
+      <c r="P3">
+        <v>1655.31</v>
+      </c>
+      <c r="V3">
+        <v>10.977</v>
+      </c>
+      <c r="W3">
+        <v>12.571999999999999</v>
+      </c>
+      <c r="X3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AZ3" s="3"/>
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+    </row>
+    <row r="4" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4">
+        <v>3460</v>
+      </c>
+      <c r="J4">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="K4">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>4.6963999999999997</v>
+      </c>
+      <c r="N4">
+        <v>303.19871318011002</v>
+      </c>
+      <c r="O4">
+        <v>-0.37849292589</v>
+      </c>
+      <c r="P4">
+        <v>312.65899999999999</v>
+      </c>
+      <c r="V4">
+        <v>10.968999999999999</v>
+      </c>
+      <c r="W4">
+        <v>11.454000000000001</v>
+      </c>
+      <c r="X4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AZ4" s="3"/>
+      <c r="BB4" s="3"/>
+      <c r="BC4" s="3"/>
+    </row>
+    <row r="5" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I5">
+        <v>5804</v>
+      </c>
+      <c r="J5">
+        <v>1.179</v>
+      </c>
+      <c r="K5">
+        <v>1.04</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>4.3121</v>
+      </c>
+      <c r="N5">
+        <v>274.86862255196002</v>
+      </c>
+      <c r="O5">
+        <v>5.3506741626599998</v>
+      </c>
+      <c r="P5">
+        <v>1644.4</v>
+      </c>
+      <c r="V5">
+        <v>15.965999999999999</v>
+      </c>
+      <c r="W5">
+        <v>16.86</v>
+      </c>
+      <c r="X5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AZ5" s="3"/>
+      <c r="BB5" s="3"/>
+      <c r="BC5" s="3"/>
+    </row>
+    <row r="6" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6">
+        <v>5800</v>
+      </c>
+      <c r="J6">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="K6">
+        <v>1.04</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>4.2129000000000003</v>
+      </c>
+      <c r="N6">
+        <v>270.95467601665001</v>
+      </c>
+      <c r="O6">
+        <v>3.9944008770699999</v>
+      </c>
+      <c r="P6">
+        <v>2963.53</v>
+      </c>
+      <c r="V6">
+        <v>17.052</v>
+      </c>
+      <c r="W6">
+        <v>17.364000000000001</v>
+      </c>
+      <c r="X6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AZ6" s="3"/>
+      <c r="BB6" s="3"/>
+      <c r="BC6" s="3"/>
+    </row>
+    <row r="7" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7">
+        <v>5799</v>
+      </c>
+      <c r="J7">
+        <v>0.99</v>
+      </c>
+      <c r="K7">
+        <v>1.042</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>4.4642999999999997</v>
+      </c>
+      <c r="N7">
+        <v>278.21725113665002</v>
+      </c>
+      <c r="O7">
+        <v>11.92287820316</v>
+      </c>
+      <c r="P7">
+        <v>224.12799999999999</v>
+      </c>
+      <c r="V7">
+        <v>11.997</v>
+      </c>
+      <c r="W7">
+        <v>12.47</v>
+      </c>
+      <c r="X7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8">
+        <v>5800.4</v>
+      </c>
+      <c r="J8">
+        <v>1.4930000000000001</v>
+      </c>
+      <c r="K8">
+        <v>1.04</v>
+      </c>
+      <c r="L8">
+        <v>-6.6000000000000003E-2</v>
+      </c>
+      <c r="M8">
+        <v>4.1069000000000004</v>
+      </c>
+      <c r="N8">
+        <v>270.30880152526998</v>
+      </c>
+      <c r="O8">
+        <v>15.944626030029999</v>
+      </c>
+      <c r="P8">
+        <v>579.08500000000004</v>
+      </c>
+      <c r="V8">
+        <v>12.978999999999999</v>
+      </c>
+      <c r="W8">
+        <v>13.638999999999999</v>
+      </c>
+      <c r="X8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9">
+        <v>5813</v>
+      </c>
+      <c r="J9">
+        <v>1.83</v>
+      </c>
+      <c r="K9">
+        <v>1.05</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>3.9344999999999999</v>
+      </c>
+      <c r="N9">
+        <v>270.99233637095</v>
+      </c>
+      <c r="O9">
+        <v>16.858729226019999</v>
+      </c>
+      <c r="P9">
+        <v>1779.6</v>
+      </c>
+      <c r="V9">
+        <v>14.999000000000001</v>
+      </c>
+      <c r="W9">
+        <v>15.66</v>
+      </c>
+      <c r="X9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10">
+        <v>5820</v>
+      </c>
+      <c r="J10">
+        <v>6.2519999999999998</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>267.97432727351003</v>
+      </c>
+      <c r="O10">
+        <v>17.507747521020001</v>
+      </c>
+      <c r="P10">
+        <v>6401.77</v>
+      </c>
+      <c r="V10">
+        <v>15.007999999999999</v>
+      </c>
+      <c r="W10">
+        <v>15.702999999999999</v>
+      </c>
+      <c r="X10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="I11">
+        <v>5824</v>
+      </c>
+      <c r="J11">
+        <v>4.7249999999999996</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>284.95537150204001</v>
+      </c>
+      <c r="O11">
+        <v>14.42740619077</v>
+      </c>
+      <c r="P11">
+        <v>1961.4</v>
+      </c>
+      <c r="V11">
+        <v>14.023</v>
+      </c>
+      <c r="W11">
+        <v>15.048999999999999</v>
+      </c>
+      <c r="X11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+      <c r="I12">
+        <v>5816</v>
+      </c>
+      <c r="J12">
+        <v>5.2939999999999996</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>284.79622244569998</v>
+      </c>
+      <c r="O12">
+        <v>15.987368865140001</v>
+      </c>
+      <c r="P12">
+        <v>3747.72</v>
+      </c>
+      <c r="V12">
+        <v>15.958</v>
+      </c>
+      <c r="W12">
+        <v>17.585999999999999</v>
+      </c>
+      <c r="X12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I13">
+        <v>5792</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>276.67545984469001</v>
+      </c>
+      <c r="O13">
+        <v>14.0128749692</v>
+      </c>
+      <c r="P13">
+        <v>2046.66</v>
+      </c>
+      <c r="V13">
+        <v>17.097000000000001</v>
+      </c>
+      <c r="W13">
+        <v>18.082999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>157</v>
+      </c>
+      <c r="I14">
+        <v>5775</v>
+      </c>
+      <c r="J14">
+        <v>5.1109999999999998</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>274.00302978329</v>
+      </c>
+      <c r="O14">
+        <v>22.9885348444</v>
+      </c>
+      <c r="P14">
+        <v>1802.37</v>
+      </c>
+      <c r="V14">
+        <v>12.961</v>
+      </c>
+      <c r="W14">
+        <v>14.082000000000001</v>
+      </c>
+      <c r="X14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15">
+        <v>5800</v>
+      </c>
+      <c r="J15">
+        <v>1.417</v>
+      </c>
+      <c r="K15">
+        <v>1.04</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>4.1520999999999999</v>
+      </c>
+      <c r="N15">
+        <v>280.34203579685999</v>
+      </c>
+      <c r="O15">
+        <v>26.315625519600001</v>
+      </c>
+      <c r="P15">
+        <v>897.52700000000004</v>
+      </c>
+      <c r="V15">
+        <v>13.994999999999999</v>
+      </c>
+      <c r="W15">
+        <v>14.913</v>
+      </c>
+      <c r="X15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16">
+        <v>5806</v>
+      </c>
+      <c r="J16">
+        <v>27.986999999999998</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>278.48921850735002</v>
+      </c>
+      <c r="O16">
+        <v>31.640052119060002</v>
+      </c>
+      <c r="P16">
+        <v>7397.91</v>
+      </c>
+      <c r="V16">
+        <v>12.01</v>
+      </c>
+      <c r="W16">
+        <v>12.507</v>
+      </c>
+      <c r="X16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17">
+        <v>5815.4</v>
+      </c>
+      <c r="J17">
+        <v>4.2549999999999999</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>-0.19350000000000001</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>80.600252814719994</v>
+      </c>
+      <c r="O17">
+        <v>-68.64221652773</v>
+      </c>
+      <c r="P17">
+        <v>398.375</v>
+      </c>
+      <c r="V17">
+        <v>11.137</v>
+      </c>
+      <c r="W17">
+        <v>11.56</v>
+      </c>
+      <c r="X17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="I18">
+        <v>5812</v>
+      </c>
+      <c r="J18">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="K18">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>4.5917000000000003</v>
+      </c>
+      <c r="N18">
+        <v>47.805523543809997</v>
+      </c>
+      <c r="O18">
+        <v>-18.380477788619999</v>
+      </c>
+      <c r="P18">
+        <v>147.77799999999999</v>
+      </c>
+      <c r="V18">
+        <v>11.044</v>
+      </c>
+      <c r="W18">
+        <v>11.662000000000001</v>
+      </c>
+      <c r="X18" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I19">
         <v>4907.77490234375</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6">
+      <c r="N19">
         <v>221.24648617076679</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O19">
         <v>27.074315757773469</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q19">
         <v>2.1833524703979492</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R19">
         <v>2.1833524703979492</v>
       </c>
-      <c r="BE2" s="7"/>
-      <c r="BG2" s="7"/>
-      <c r="BH2" s="7"/>
-    </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
         <v>4.4652997599999997</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D20">
         <v>5.561E-2</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E20">
         <v>1.319</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F20">
         <v>0.52500000000000002</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G20">
         <v>1322</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H20" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I20">
         <v>5980</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J20">
         <v>1.1739999999999999</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K20">
         <v>1.151</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L20">
         <v>0.13</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M20">
         <v>4.359</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N20">
         <v>344.44536319999997</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O20">
         <v>38.674919000000003</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P20">
         <v>158.97900000000001</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q20">
         <v>9.827</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R20">
         <v>10.178599999999999</v>
       </c>
-      <c r="S3" s="1">
-        <f>(0.000000000000000138*G3/(1.673534E-24*1.3*0.000000066726*F3*1.8986E+30/(E3*7149200000)^2))/100000</f>
+      <c r="S20">
+        <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
         <v>1121.1126749906216</v>
       </c>
-      <c r="T3" s="1">
-        <f>IF(I3&gt;6800,-7,-5)</f>
+      <c r="T20">
+        <f>IF(I20&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE3" s="7"/>
-      <c r="BG3" s="7"/>
-      <c r="BH3" s="7"/>
-    </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
         <v>4.6276700000000002</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D21">
         <v>5.96E-2</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E21">
         <v>1.42</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F21">
         <v>3.44</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G21">
         <v>1624</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H21" t="s">
         <v>125</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I21">
         <v>6600</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J21">
         <v>1.82</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K21">
         <v>2.65</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L21">
         <v>0.11</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M21">
         <v>4.25</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N21">
         <v>260.11617189999998</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O21">
         <v>38.242168200000002</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P21">
         <v>222.66300000000001</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q21">
         <v>9.9879999999999995</v>
       </c>
-      <c r="R4" s="1">
+      <c r="R21">
         <v>9.8728300000000004</v>
       </c>
-      <c r="S4" s="1">
-        <f>(0.000000000000000138*G4/(1.673534E-24*1.3*0.000000066726*F4*1.8986E+30/(E4*7149200000)^2))/100000</f>
+      <c r="S21">
+        <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
         <v>243.60813720463176</v>
       </c>
-      <c r="T4" s="1">
-        <f>IF(I4&gt;6800,-7,-5)</f>
+      <c r="T21">
+        <f>IF(I21&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE4" s="7"/>
-      <c r="BG4" s="7"/>
-      <c r="BH4" s="7"/>
-    </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22">
         <v>5.6335157999999996</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D22">
         <v>6.8140000000000006E-2</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E22">
         <v>0.95099999999999996</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F22">
         <v>9.02</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G22">
         <v>1540</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H22" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I22">
         <v>6380</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J22">
         <v>1.39</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K22">
         <v>1.33</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L22">
         <v>0.18</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M22">
         <v>4.16</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N22">
         <v>245.1514324</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O22">
         <v>41.047960099999997</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P22">
         <v>127.774</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q22">
         <v>8.7200000000000006</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R22">
         <v>8.5984200000000008</v>
       </c>
-      <c r="S5" s="1">
-        <f>(0.000000000000000138*G5/(1.673534E-24*1.3*0.000000066726*F5*1.8986E+30/(E5*7149200000)^2))/100000</f>
+      <c r="S22">
+        <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
         <v>39.515068300859213</v>
       </c>
-      <c r="T5" s="1">
-        <f>IF(I5&gt;6800,-7,-5)</f>
+      <c r="T22">
+        <f>IF(I22&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE5" s="7"/>
-      <c r="BG5" s="7"/>
-      <c r="BH5" s="7"/>
-    </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
         <v>3.2122199999999999</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D23">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E23">
         <v>1.1499999999999999</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F23">
         <v>2.4700000000000002</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G23">
         <v>1463</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H23" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I23">
         <v>5302</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J23">
         <v>1.1100000000000001</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K23">
         <v>1.1299999999999999</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L23">
         <v>0.24</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M23">
         <v>4.3600000000000003</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N23">
         <v>155.6814593</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O23">
         <v>50.128711500000001</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P23">
         <v>81.764700000000005</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q23">
         <v>9.7629999999999999</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R23">
         <v>9.5193600000000007</v>
       </c>
-      <c r="S6" s="1">
-        <f>(0.000000000000000138*G6/(1.673534E-24*1.3*0.000000066726*F6*1.8986E+30/(E6*7149200000)^2))/100000</f>
+      <c r="S23">
+        <f>(0.000000000000000138*G23/(1.673534E-24*1.3*0.000000066726*F23*1.8986E+30/(E23*7149200000)^2))/100000</f>
         <v>200.46131426194896</v>
       </c>
-      <c r="T6" s="1">
-        <f>IF(I6&gt;6800,-7,-5)</f>
+      <c r="T23">
+        <f>IF(I23&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="BE6" s="7"/>
-      <c r="BG6" s="7"/>
-      <c r="BH6" s="7"/>
-    </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="I7" s="5">
+      <c r="I24">
         <v>6245.11328125</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J24">
         <v>1.208241820335388</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M24">
         <v>4.2744002342224121</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N24">
         <v>31.04275939878713</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O24">
         <v>46.687851647860192</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P24">
         <v>283.38339999999999</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q24">
         <v>11.12930202484131</v>
       </c>
-      <c r="R7" s="6">
+      <c r="R24">
         <v>11.12930202484131</v>
       </c>
-      <c r="V7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-    </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="V24" s="4"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25">
         <v>4.7947813000000004</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D25">
         <v>6.2770000000000006E-2</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E25">
         <v>1.631</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F25">
         <v>0.57399999999999995</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G25">
         <v>1772</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I25">
         <v>6212</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J25">
         <v>2.1970000000000001</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K25">
         <v>1.4350000000000001</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L25">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M25">
         <v>3.9114</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N25">
         <v>28.282571900000001</v>
       </c>
-      <c r="O8" s="1">
+      <c r="O25">
         <v>52.053920900000001</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P25">
         <v>233.22</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q25">
         <v>9.7270000000000003</v>
       </c>
-      <c r="R8" s="1">
+      <c r="R25">
         <v>9.5635499999999993</v>
       </c>
-      <c r="S8" s="1">
-        <f>(0.000000000000000138*G8/(1.673534E-24*1.3*0.000000066726*F8*1.8986E+30/(E8*7149200000)^2))/100000</f>
+      <c r="S25">
+        <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
         <v>2101.5864855136347</v>
       </c>
-      <c r="T8" s="1">
-        <f>IF(I8&gt;6800,-7,-5)</f>
+      <c r="T25">
+        <f>IF(I25&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="V8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-    </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="V25" s="4"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26">
         <v>4.7869491000000002</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D26">
         <v>6.5549999999999997E-2</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E26">
         <v>1.6759999999999999</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F26">
         <v>3.58</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G26">
         <v>1930</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I26">
         <v>7394</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J26">
         <v>1.9259999999999999</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K26">
         <v>1.6479999999999999</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L26">
         <v>-6.9000000000000006E-2</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M26">
         <v>4.1100000000000003</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N26">
         <v>130.5056385</v>
       </c>
-      <c r="O9" s="1">
+      <c r="O26">
         <v>3.7105662000000001</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P26">
         <v>341.26299999999998</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q26">
         <v>9.7739999999999991</v>
       </c>
-      <c r="R9" s="1">
+      <c r="R26">
         <v>9.77332</v>
       </c>
-      <c r="S9" s="1">
-        <f>(0.000000000000000138*G9/(1.673534E-24*1.3*0.000000066726*F9*1.8986E+30/(E9*7149200000)^2))/100000</f>
+      <c r="S26">
+        <f>(0.000000000000000138*G26/(1.673534E-24*1.3*0.000000066726*F26*1.8986E+30/(E26*7149200000)^2))/100000</f>
         <v>387.53401759458865</v>
       </c>
-      <c r="T9" s="1">
-        <f>IF(I9&gt;6800,-7,-5)</f>
+      <c r="T26">
+        <f>IF(I26&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>141</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I27">
         <v>6424.27685546875</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J27">
         <v>2.0702402591705318</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6">
+      <c r="N27">
         <v>292.24718620018581</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O27">
         <v>47.969544064101818</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q27">
         <v>10.36768245697021</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R27">
         <v>10.36768245697021</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
         <v>2.7443245200000002</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D28">
         <v>4.7390000000000002E-2</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E28">
         <v>1.87</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F28">
         <v>6.78</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G28">
         <v>2562</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I28">
         <v>8450</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J28">
         <v>1.8580000000000001</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K28">
         <v>1.89</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L28">
         <v>-5.8999999999999997E-2</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M28">
         <v>4.181</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N28">
         <v>74.552333200000007</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O28">
         <v>9.9979794000000002</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P28">
         <v>330.73899999999998</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q28">
         <v>9.4700000000000006</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R28">
         <v>9.4517399999999991</v>
       </c>
-      <c r="S11" s="1">
-        <f t="shared" ref="S11:S35" si="0">(0.000000000000000138*G11/(1.673534E-24*1.3*0.000000066726*F11*1.8986E+30/(E11*7149200000)^2))/100000</f>
+      <c r="S28">
+        <f t="shared" ref="S28:S52" si="0">(0.000000000000000138*G28/(1.673534E-24*1.3*0.000000066726*F28*1.8986E+30/(E28*7149200000)^2))/100000</f>
         <v>338.15838787809196</v>
       </c>
-      <c r="T11" s="1">
-        <f t="shared" ref="T11:T34" si="1">IF(I11&gt;6800,-7,-5)</f>
+      <c r="T28">
+        <f t="shared" ref="T28:T51" si="1">IF(I28&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
-      <c r="V11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-    </row>
-    <row r="12" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="V28" s="4"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B29" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C29">
         <v>6.1349779</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D29">
         <v>7.1300000000000002E-2</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E29">
         <v>1.1399999999999999</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F29">
         <v>2.14</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G29">
         <v>1361</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H29" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I29">
         <v>5742</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J29">
         <v>2.04</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K29">
         <v>1.27</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L29">
         <v>0.28699999999999998</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M29">
         <v>3.92</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N29">
         <v>203.50995599999999</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O29">
         <v>53.728187599999998</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P29">
         <v>92.258899999999997</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q29">
         <v>8.0500000000000007</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R29">
         <v>7.89255</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S29">
         <f t="shared" si="0"/>
         <v>211.51519610586323</v>
       </c>
-      <c r="T12" s="1">
+      <c r="T29">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30">
         <v>11.53533</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D30">
         <v>0.10970000000000001</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E30">
         <v>1.026</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F30">
         <v>0.41499999999999998</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G30">
         <v>1228.3</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H30" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I30">
         <v>5521</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J30">
         <v>2.3359999999999999</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K30">
         <v>1.3240000000000001</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L30">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M30">
         <v>3.823</v>
       </c>
-      <c r="N13" s="1">
+      <c r="N30">
         <v>4.4471631</v>
       </c>
-      <c r="O13" s="1">
+      <c r="O30">
         <v>-66.358928500000005</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P30">
         <v>79.5702</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q30">
         <v>7.79</v>
       </c>
-      <c r="R13" s="1">
+      <c r="R30">
         <v>7.5933599999999997</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S30">
         <f t="shared" si="0"/>
         <v>797.33090232058362</v>
       </c>
-      <c r="T13" s="1">
+      <c r="T30">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="14" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B31" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C31">
         <v>2.8758900000000001</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D31">
         <v>4.3639999999999998E-2</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E31">
         <v>0.74</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F31">
         <v>0.38</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G31">
         <v>1626</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H31" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I31">
         <v>6179</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J31">
         <v>1.41</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K31">
         <v>1.42</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L31">
         <v>0.32</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M31">
         <v>4.37</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N31">
         <v>247.62298269999999</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O31">
         <v>38.347534899999999</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P31">
         <v>75.8643</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q31">
         <v>8.15</v>
       </c>
-      <c r="R14" s="9">
+      <c r="R31">
         <v>8.0141600000000004</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S31">
         <f t="shared" si="0"/>
         <v>599.63628364223177</v>
       </c>
-      <c r="T14" s="1">
+      <c r="T31">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-    </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="V31" s="4"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32">
         <v>19.502103999999999</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D32">
         <v>0.1482</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E32">
         <v>0.52993221999999995</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F32">
         <v>3.0425219999999999E-2</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G32">
         <v>253.08</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H32" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I32">
         <v>6310</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J32">
         <v>1.43</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K32">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L32">
         <v>-0.16</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M32">
         <v>4.1900000000000004</v>
       </c>
-      <c r="N15" s="1">
+      <c r="N32">
         <v>253.78488530000001</v>
       </c>
-      <c r="O15" s="1">
+      <c r="O32">
         <v>20.491523999999998</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P32">
         <v>107.898</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q32">
         <v>8.8550000000000004</v>
       </c>
-      <c r="R15" s="1">
+      <c r="R32">
         <v>8.7641200000000001</v>
       </c>
-      <c r="S15" s="1">
+      <c r="S32">
         <f t="shared" si="0"/>
         <v>597.79498778467087</v>
       </c>
-      <c r="T15" s="1">
+      <c r="T32">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="16" spans="1:60" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B33" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C33">
         <v>2.2185756699999999</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D33">
         <v>3.1260000000000003E-2</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E33">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F33">
         <v>1.1299999999999999</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G33">
         <v>1209</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H33" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I33">
         <v>5052</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J33">
         <v>0.75</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K33">
         <v>0.79</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L33">
         <v>-0.02</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M33">
         <v>4.49</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N33">
         <v>300.1821223</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O33">
         <v>22.7097759</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P33">
         <v>19.7638</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="Q33">
         <v>7.67</v>
       </c>
-      <c r="R16" s="9">
+      <c r="R33">
         <v>7.41432</v>
       </c>
-      <c r="S16" s="1">
+      <c r="S33">
         <f t="shared" si="0"/>
         <v>349.61677638948368</v>
       </c>
-      <c r="T16" s="1">
+      <c r="T33">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="V33" s="4"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34">
         <v>3.3089580000000001</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D34">
         <v>5.2080000000000001E-2</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E34">
         <v>1.5449999999999999</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F34">
         <v>1.0169999999999999</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G34">
         <v>2132</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I34">
         <v>6272</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J34">
         <v>2.5910000000000002</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K34">
         <v>1.72</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L34">
         <v>0.3</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M34">
         <v>3.8479999999999999</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N34">
         <v>319.6995877</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O34">
         <v>-26.6163743</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P34">
         <v>161.49799999999999</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q34">
         <v>8.3239999999999998</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R34">
         <v>8.2268799999999995</v>
       </c>
-      <c r="S17" s="1">
+      <c r="S34">
         <f t="shared" si="0"/>
         <v>1280.5918535006856</v>
       </c>
-      <c r="T17" s="1">
+      <c r="T34">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B35" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C35">
         <v>3.5247485900000002</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D35">
         <v>4.7070000000000001E-2</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E35">
         <v>1.39</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F35">
         <v>0.73</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G35">
         <v>1459</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H35" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I35">
         <v>6091</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J35">
         <v>1.19</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K35">
         <v>1.23</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L35">
         <v>0.01</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M35">
         <v>4.45</v>
       </c>
-      <c r="N18" s="9">
+      <c r="N35">
         <v>330.79502189999999</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O35">
         <v>18.884241899999999</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P35">
         <v>48.301600000000001</v>
       </c>
-      <c r="Q18" s="9">
+      <c r="Q35">
         <v>7.65</v>
       </c>
-      <c r="R18" s="9">
+      <c r="R35">
         <v>7.5086599999999999</v>
       </c>
-      <c r="S18" s="1">
+      <c r="S35" s="5">
         <f t="shared" si="0"/>
         <v>988.21070019970352</v>
       </c>
-      <c r="T18" s="1">
+      <c r="T35">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>101</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1">
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36">
         <v>6.0344680000000004</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D36">
         <v>6.3560000000000005E-2</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E36">
         <v>0.437</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F36">
         <v>5.5E-2</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G36">
         <v>1076</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H36" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I36">
         <v>5540</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J36">
         <v>1.0589999999999999</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K36">
         <v>1.02</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L36">
         <v>0.04</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M36">
         <v>4.4000000000000004</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N36">
         <v>349.55926649999998</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O36">
         <v>-56.9039857</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P36">
         <v>94.171899999999994</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q36">
         <v>9.8089999999999993</v>
       </c>
-      <c r="R19" s="1">
+      <c r="R36">
         <v>9.6495599999999992</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S36">
         <f t="shared" si="0"/>
         <v>956.09264119622901</v>
       </c>
-      <c r="T19" s="1">
+      <c r="T36">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37">
         <v>14.2767</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D37">
         <v>0.12280000000000001</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E37">
         <v>0.83599999999999997</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F37">
         <v>0.19</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G37">
         <v>789.15</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H37" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I37">
         <v>5080</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J37">
         <v>2.9430000000000001</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K37">
         <v>1.212</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L37">
         <v>-0.08</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M37">
         <v>3.5840000000000001</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N37">
         <v>353.03318630000001</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O37">
         <v>-21.801200699999999</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P37">
         <v>95.548299999999998</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q37">
         <v>8.15</v>
       </c>
-      <c r="R20" s="1">
+      <c r="R37">
         <v>7.9077599999999997</v>
       </c>
-      <c r="S20" s="1">
+      <c r="S37">
         <f t="shared" si="0"/>
         <v>742.8583931109747</v>
       </c>
-      <c r="T20" s="1">
+      <c r="T37">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38">
         <v>4.1268799999999999</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D38">
         <v>5.6800000000000003E-2</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E38">
         <v>1.44</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F38">
         <v>1.17</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G38">
         <v>2061</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I38">
         <v>6801</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J38">
         <v>1.56</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K38">
         <v>1.43</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L38">
         <v>0.02</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M38">
         <v>4.21</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N38">
         <v>7.3289156000000002</v>
       </c>
-      <c r="O21" s="1">
+      <c r="O38">
         <v>-76.304032000000007</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P38">
         <v>196.852</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q38">
         <v>9.5950000000000006</v>
       </c>
-      <c r="R21" s="1">
+      <c r="R38">
         <v>9.5202500000000008</v>
       </c>
-      <c r="S21" s="1">
+      <c r="S38">
         <f t="shared" si="0"/>
         <v>934.76971602454307</v>
       </c>
-      <c r="T21" s="1">
+      <c r="T38">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
-      <c r="U21" s="3" t="s">
+      <c r="U38" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="1">
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39">
         <v>18.712024</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D39">
         <v>0.14499999999999999</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E39">
         <v>0.80944318999999998</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F39">
         <v>0.23314467</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G39">
         <v>798.3</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H39" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I39">
         <v>6128</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J39">
         <v>1.266</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K39">
         <v>1.1641999999999999</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L39">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M39">
         <v>4.2960000000000003</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N39">
         <v>306.74113399999999</v>
       </c>
-      <c r="O22" s="1">
+      <c r="O39">
         <v>33.744388200000003</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P39">
         <v>80.666499999999999</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q39">
         <v>8.5579999999999998</v>
       </c>
-      <c r="R22" s="1">
+      <c r="R39">
         <v>8.4183900000000005</v>
       </c>
-      <c r="S22" s="1">
+      <c r="S39">
         <f t="shared" si="0"/>
         <v>574.11765847468712</v>
       </c>
-      <c r="T22" s="1">
+      <c r="T39">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B40" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C40">
         <v>3.4148839999999998</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D40">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E40">
         <v>1.23</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F40">
         <v>1.02</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G40">
         <v>1762</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H40" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I40">
         <v>5392</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J40">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K40">
         <v>1.26</v>
       </c>
-      <c r="L23" s="9">
+      <c r="L40">
         <v>0.34</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M40">
         <v>3.88</v>
       </c>
-      <c r="N23" s="9">
+      <c r="N40">
         <v>152.53193490000001</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O40">
         <v>18.185728399999999</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P40">
         <v>73.612300000000005</v>
       </c>
-      <c r="Q23" s="9">
+      <c r="Q40">
         <v>8.0185200000000005</v>
       </c>
-      <c r="R23" s="9">
+      <c r="R40">
         <v>7.8097899999999996</v>
       </c>
-      <c r="S23" s="1">
+      <c r="S40">
         <f t="shared" si="0"/>
         <v>668.81110409377118</v>
       </c>
-      <c r="T23" s="1">
+      <c r="T40">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41">
         <v>11.814299999999999</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D41">
         <v>0.1066</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E41">
         <v>0.66</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F41">
         <v>0.11</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G41">
         <v>1089</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H41" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I41">
         <v>5576</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J41">
         <v>1.7470000000000001</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K41">
         <v>1.157</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L41">
         <v>0.42099999999999999</v>
       </c>
-      <c r="M24" s="1">
+      <c r="M41">
         <v>4.016</v>
       </c>
-      <c r="N24" s="1">
+      <c r="N41">
         <v>154.67109769999999</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O41">
         <v>10.1288464</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P41">
         <v>132.345</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q41">
         <v>9.3800000000000008</v>
       </c>
-      <c r="R24" s="1">
+      <c r="R41">
         <v>9.2170199999999998</v>
       </c>
-      <c r="S24" s="1">
+      <c r="S41">
         <f t="shared" si="0"/>
         <v>1103.5971886171305</v>
       </c>
-      <c r="T24" s="1">
+      <c r="T41">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="1">
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42">
         <v>11.168454000000001</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D42">
         <v>0.10356</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E42">
         <v>1</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F42">
         <v>0.39800000000000002</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G42">
         <v>1030</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I42">
         <v>6154</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J42">
         <v>1.161</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K42">
         <v>1.1879999999999999</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L42">
         <v>0.1</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M42">
         <v>4.3789999999999996</v>
       </c>
-      <c r="N25" s="1">
+      <c r="N42">
         <v>73.766792699999996</v>
       </c>
-      <c r="O25" s="1">
+      <c r="O42">
         <v>18.654323000000002</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P42">
         <v>130.72</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q42">
         <v>9.8219999999999992</v>
       </c>
-      <c r="R25" s="1">
+      <c r="R42">
         <v>9.7262599999999999</v>
       </c>
-      <c r="S25" s="1">
+      <c r="S42">
         <f t="shared" si="0"/>
         <v>662.28004924519439</v>
       </c>
-      <c r="T25" s="1">
+      <c r="T42">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="1">
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43">
         <v>4.73620865</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D43">
         <v>6.2300000000000001E-2</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E43">
         <v>1.35</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F43">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G43">
         <v>1712</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H43" t="s">
         <v>37</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I43">
         <v>5375</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J43">
         <v>2.69</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K43">
         <v>1.44</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L43">
         <v>0.17</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M43">
         <v>3.7</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N43">
         <v>161.70690529999999</v>
       </c>
-      <c r="O26" s="1">
+      <c r="O43">
         <v>-9.3993646000000002</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P43">
         <v>99.159599999999998</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q43">
         <v>8.0399999999999991</v>
       </c>
-      <c r="R26" s="1">
+      <c r="R43">
         <v>7.8311200000000003</v>
       </c>
-      <c r="S26" s="1">
+      <c r="S43">
         <f t="shared" si="0"/>
         <v>3894.9775251994533</v>
       </c>
-      <c r="T26" s="1">
+      <c r="T43">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="1">
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44">
         <v>3.0801715999999999</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D44">
         <v>4.8809999999999999E-2</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E44">
         <v>1.5249999999999999</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F44">
         <v>1.31</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G44">
         <v>2087</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H44" t="s">
         <v>41</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I44">
         <v>7454</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J44">
         <v>1.645</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K44">
         <v>1.635</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L44">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M44">
         <v>4.22</v>
       </c>
-      <c r="N27" s="1">
+      <c r="N44">
         <v>125.617407</v>
       </c>
-      <c r="O27" s="1">
+      <c r="O44">
         <v>13.735309300000001</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P44">
         <v>226.5</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q44">
         <v>9.234</v>
       </c>
-      <c r="R27" s="1">
+      <c r="R44">
         <v>9.2088699999999992</v>
       </c>
-      <c r="S27" s="1">
+      <c r="S44">
         <f t="shared" si="0"/>
         <v>948.15286253702118</v>
       </c>
-      <c r="T27" s="1">
+      <c r="T44">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="1">
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45">
         <v>4.6117093000000002</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D45">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E45">
         <v>1.91</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F45">
         <v>4.07</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G45">
         <v>1935</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H45" t="s">
         <v>110</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I45">
         <v>7500</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J45">
         <v>1.83</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K45">
         <v>1.62</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L45">
         <v>-0.12</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M45">
         <v>4.1269999999999998</v>
       </c>
-      <c r="N28" s="1">
+      <c r="N45">
         <v>111.5095293</v>
       </c>
-      <c r="O28" s="1">
+      <c r="O45">
         <v>7.6157759</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P45">
         <v>300.27600000000001</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q45">
         <v>9.8569999999999993</v>
       </c>
-      <c r="R28" s="1">
+      <c r="R45">
         <v>9.8633100000000002</v>
       </c>
-      <c r="S28" s="1">
+      <c r="S45">
         <f t="shared" si="0"/>
         <v>443.85469120292152</v>
       </c>
-      <c r="T28" s="1">
+      <c r="T45">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1">
+      <c r="B46" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46">
         <v>4.1137899999999998</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D46">
         <v>5.4969999999999998E-2</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E46">
         <v>1.35</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F46">
         <v>1.7</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G46">
         <v>2080</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H46" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I46">
         <v>6327</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J46">
         <v>1.93</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K46">
         <v>1.54</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L46">
         <v>0</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M46">
         <v>4.5</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N46">
         <v>92.664022599999996</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O46">
         <v>30.957133299999999</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P46">
         <v>134.05799999999999</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q46">
         <v>8.68</v>
       </c>
-      <c r="R29" s="1">
+      <c r="R46">
         <v>8.5839300000000005</v>
       </c>
-      <c r="S29" s="1">
+      <c r="S46">
         <f t="shared" si="0"/>
         <v>570.64953846380126</v>
       </c>
-      <c r="T29" s="1">
+      <c r="T46">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="1">
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47">
         <v>3.4741084999999998</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D47">
         <v>5.4199999999999998E-2</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E47">
         <v>1.7410000000000001</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F47">
         <v>3.3820000000000001</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G47">
         <v>2262</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H47" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I47">
         <v>8720</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J47">
         <v>1.5649999999999999</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K47">
         <v>1.76</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L47">
         <v>-0.28999999999999998</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M47">
         <v>4.29</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N47">
         <v>294.66141260000001</v>
       </c>
-      <c r="O30" s="1">
+      <c r="O47">
         <v>31.219200099999998</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P47">
         <v>136.42599999999999</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q47">
         <v>7.59</v>
       </c>
-      <c r="R30" s="1">
+      <c r="R47">
         <v>7.5749199999999997</v>
       </c>
-      <c r="S30" s="1">
+      <c r="S47">
         <f t="shared" si="0"/>
         <v>518.80488815900412</v>
       </c>
-      <c r="T30" s="1">
+      <c r="T47">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="1">
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48">
         <v>5.55149296</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D48">
         <v>6.6500000000000004E-2</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E48">
         <v>1.1339999999999999</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F48">
         <v>4.59</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G48">
         <v>1391</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H48" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I48">
         <v>6426</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J48">
         <v>1.3380000000000001</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K48">
         <v>1.268</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L48">
         <v>0.13800000000000001</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M48">
         <v>4.2869999999999999</v>
       </c>
-      <c r="N31" s="1">
+      <c r="N48">
         <v>161.90902729999999</v>
       </c>
-      <c r="O31" s="1">
+      <c r="O48">
         <v>71.655726999999999</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P48">
         <v>96.517300000000006</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q48">
         <v>8.34</v>
       </c>
-      <c r="R31" s="1">
+      <c r="R48">
         <v>8.23752</v>
       </c>
-      <c r="S31" s="1">
+      <c r="S48">
         <f t="shared" si="0"/>
         <v>99.730517672190274</v>
       </c>
-      <c r="T31" s="1">
+      <c r="T48">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="1">
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49">
         <v>2.7033900000000002</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D49">
         <v>4.1230000000000003E-2</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E49">
         <v>1.56</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F49">
         <v>1.94</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G49">
         <v>1816</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I49">
         <v>6304</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J49">
         <v>1.7</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K49">
         <v>1.96</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L49">
         <v>0.05</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M49">
         <v>4.2</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N49">
         <v>148.6431193</v>
       </c>
-      <c r="O32" s="1">
+      <c r="O49">
         <v>40.387944599999997</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P49">
         <v>210.25200000000001</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q49">
         <v>9.8160000000000007</v>
       </c>
-      <c r="R32" s="1">
+      <c r="R49">
         <v>9.7632399999999997</v>
       </c>
-      <c r="S32" s="1">
+      <c r="S49">
         <f t="shared" si="0"/>
         <v>582.97620763372299</v>
       </c>
-      <c r="T32" s="1">
+      <c r="T49">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="1">
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50">
         <v>2.9895931999999998</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D50">
         <v>4.317E-2</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E50">
         <v>1.6990000000000001</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F50">
         <v>0.90200000000000002</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G50">
         <v>1823</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H50" t="s">
         <v>56</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I50">
         <v>6206</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J50">
         <v>1.603</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K50">
         <v>1.2010000000000001</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L50">
         <v>-0.11600000000000001</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M50">
         <v>4.1079999999999997</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N50">
         <v>157.06262000000001</v>
       </c>
-      <c r="O33" s="1">
+      <c r="O50">
         <v>25.573136600000002</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P50">
         <v>218.05</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q50">
         <v>9.98</v>
       </c>
-      <c r="R33" s="1">
+      <c r="R50">
         <v>9.95702</v>
       </c>
-      <c r="S33" s="1">
+      <c r="S50">
         <f t="shared" si="0"/>
         <v>1492.9814393090719</v>
       </c>
-      <c r="T33" s="1">
+      <c r="T50">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="1">
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51">
         <v>2.7347700000000001</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D51">
         <v>4.4150000000000002E-2</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E51">
         <v>1.6</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F51">
         <v>1.39</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G51">
         <v>2048</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H51" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I51">
         <v>6768</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J51">
         <v>1.81</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K51">
         <v>1.76</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L51">
         <v>0</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M51">
         <v>4.5</v>
       </c>
-      <c r="N34" s="1">
+      <c r="N51">
         <v>78.295591200000004</v>
       </c>
-      <c r="O34" s="1">
+      <c r="O51">
         <v>33.317953199999998</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P51">
         <v>136.68100000000001</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q51">
         <v>8.56</v>
       </c>
-      <c r="R34" s="1">
+      <c r="R51">
         <v>8.4517299999999995</v>
       </c>
-      <c r="S34" s="1">
+      <c r="S51">
         <f t="shared" si="0"/>
         <v>965.25628287035329</v>
       </c>
-      <c r="T34" s="1">
+      <c r="T51">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="13">
+      <c r="B52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52">
         <v>1.4811235</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D52">
         <v>3.4619999999999998E-2</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E52">
         <v>1.891</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F52">
         <v>2.88</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G52">
         <v>4050</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H52" t="s">
         <v>144</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I52">
         <v>10170.1</v>
       </c>
-      <c r="J35" s="13">
+      <c r="J52">
         <v>2.3620000000000001</v>
       </c>
-      <c r="K35" s="13">
+      <c r="K52">
         <v>2.52</v>
       </c>
-      <c r="L35" s="13">
+      <c r="L52">
         <v>-0.03</v>
       </c>
-      <c r="M35" s="13">
+      <c r="M52">
         <v>4.093</v>
       </c>
-      <c r="N35" s="13">
+      <c r="N52">
         <v>307.85989979999999</v>
       </c>
-      <c r="O35" s="13">
+      <c r="O52">
         <v>39.9389161</v>
       </c>
-      <c r="P35" s="13">
+      <c r="P52">
         <v>204.45500000000001</v>
       </c>
-      <c r="Q35" s="13">
+      <c r="Q52">
         <v>7.55</v>
       </c>
-      <c r="R35" s="13">
+      <c r="R52">
         <v>7.5767499999999997</v>
       </c>
-      <c r="S35" s="13">
+      <c r="S52">
         <f t="shared" si="0"/>
         <v>1286.8653667451285</v>
       </c>
-      <c r="U35" s="3" t="s">
+      <c r="U52" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36" s="8" t="s">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>142</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I53">
         <v>7433.197265625</v>
       </c>
-      <c r="J36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6">
+      <c r="N53">
         <v>286.97138676797078</v>
       </c>
-      <c r="O36" s="6">
+      <c r="O53">
         <v>46.868244058307063</v>
       </c>
-      <c r="Q36" s="6">
+      <c r="Q53">
         <v>10.382340431213381</v>
       </c>
-      <c r="R36" s="6">
+      <c r="R53">
         <v>10.382340431213381</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="1">
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54">
         <v>1.7635879999999999</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D54">
         <v>3.6409999999999998E-2</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E54">
         <v>1.512</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F54">
         <v>9.2799999999999994</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G54">
         <v>2550</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I54">
         <v>7650</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J54">
         <v>1.74</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K54">
         <v>1.72</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L54">
         <v>0.2</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M54">
         <v>4.2</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N54">
         <v>286.97138760000001</v>
       </c>
-      <c r="O37" s="1">
+      <c r="O54">
         <v>46.868246300000003</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P54">
         <v>519.096</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="Q54">
         <v>9.7910000000000004</v>
       </c>
-      <c r="R37" s="1">
+      <c r="R54">
         <v>10.367800000000001</v>
       </c>
-      <c r="S37" s="1">
-        <f t="shared" ref="S37:S63" si="2">(0.000000000000000138*G37/(1.673534E-24*1.3*0.000000066726*F37*1.8986E+30/(E37*7149200000)^2))/100000</f>
+      <c r="S54">
+        <f t="shared" ref="S54:S80" si="2">(0.000000000000000138*G54/(1.673534E-24*1.3*0.000000066726*F54*1.8986E+30/(E54*7149200000)^2))/100000</f>
         <v>160.76196513632402</v>
       </c>
-      <c r="T37" s="1">
-        <f t="shared" ref="T37:T63" si="3">IF(I37&gt;6800,-7,-5)</f>
+      <c r="T54">
+        <f t="shared" ref="T54:T80" si="3">IF(I54&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1">
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55">
         <v>0.79205199999999998</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D55">
         <v>1.6789999999999999E-2</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E55">
         <v>0.42109020000000003</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F55">
         <v>9.2250570000000004E-2</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G55">
         <v>1978</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H55" t="s">
         <v>99</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I55">
         <v>5443</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J55">
         <v>0.94899999999999995</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K55">
         <v>1.02</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L55">
         <v>0.27</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M55">
         <v>4.3499999999999996</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N55">
         <v>358.6688767</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O55">
         <v>-37.628223699999999</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P55">
         <v>80.437299999999993</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q55">
         <v>9.7899999999999991</v>
       </c>
-      <c r="R38" s="1">
+      <c r="R55">
         <v>9.6000599999999991</v>
       </c>
-      <c r="S38" s="1">
+      <c r="S55">
         <f t="shared" si="2"/>
         <v>972.96006983022733</v>
       </c>
-      <c r="T38" s="1">
+      <c r="T55">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="1">
+      <c r="B56" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56">
         <v>2.1487738099999998</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D56">
         <v>4.0351999999999999E-2</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E56">
         <v>1.597</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F56">
         <v>3.7</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G56">
         <v>2594.3000000000002</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H56" t="s">
         <v>49</v>
       </c>
-      <c r="I39" s="2">
+      <c r="I56">
         <v>7490</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J56">
         <v>2.0819999999999999</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K56">
         <v>1.9</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L56">
         <v>0.15</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M56">
         <v>4.1050000000000004</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N56">
         <v>317.5515264</v>
       </c>
-      <c r="O39" s="1">
+      <c r="O56">
         <v>10.7388967</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P56">
         <v>182.273</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q56">
         <v>8.2799999999999994</v>
       </c>
-      <c r="R39" s="1">
+      <c r="R56">
         <v>8.2424300000000006</v>
       </c>
-      <c r="S39" s="1">
+      <c r="S56">
         <f t="shared" si="2"/>
         <v>457.63140850776114</v>
       </c>
-      <c r="T39" s="1">
+      <c r="T56">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="1">
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57">
         <v>2.8240932000000001</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D57">
         <v>4.7399999999999998E-2</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E57">
         <v>1.5149999999999999</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F57">
         <v>1.675</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G57">
         <v>2250</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H57" t="s">
         <v>47</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I57">
         <v>7800</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J57">
         <v>1.79</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K57">
         <v>1.75</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L57">
         <v>0</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M57">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N57">
         <v>147.5800667</v>
       </c>
-      <c r="O40" s="1">
+      <c r="O57">
         <v>-66.113925300000005</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P57">
         <v>170.696</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q57">
         <v>8.1910000000000007</v>
       </c>
-      <c r="R40" s="1">
+      <c r="R57">
         <v>8.1740100000000009</v>
       </c>
-      <c r="S40" s="1">
+      <c r="S57">
         <f t="shared" si="2"/>
         <v>789.006338593706</v>
       </c>
-      <c r="T40" s="1">
+      <c r="T57">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="1">
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58">
         <v>16.249210000000001</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D58">
         <v>0.12909999999999999</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E58">
         <v>1.087</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F58">
         <v>4.34</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G58">
         <v>805.5</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H58" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="2">
+      <c r="I58">
         <v>5756</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J58">
         <v>1.0860000000000001</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K58">
         <v>1.0820000000000001</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L58">
         <v>0.318</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M58">
         <v>4.4020000000000001</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N58">
         <v>310.29170019999998</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O58">
         <v>3.6382967000000002</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P58">
         <v>93.734499999999997</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q58">
         <v>9.48</v>
       </c>
-      <c r="R41" s="1">
+      <c r="R58">
         <v>9.4290710000000004</v>
       </c>
-      <c r="S41" s="1">
+      <c r="S58">
         <f t="shared" si="2"/>
         <v>56.120615203365361</v>
       </c>
-      <c r="T41" s="1">
+      <c r="T58">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
-      <c r="U41" s="3" t="s">
+      <c r="U58" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="1">
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59">
         <v>8.0277282999999997</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D59">
         <v>8.2337403000000003E-2</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E59">
         <v>0.83243188000000001</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F59">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G59">
         <v>1074.28</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H59" t="s">
         <v>43</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I59">
         <v>5962.7</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J59">
         <v>1.1499999999999999</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K59">
         <v>1.156039</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L59">
         <v>0</v>
       </c>
-      <c r="M42" s="1">
+      <c r="M59">
         <v>4.38</v>
       </c>
-      <c r="N42" s="1">
+      <c r="N59">
         <v>193.3963704</v>
       </c>
-      <c r="O42" s="1">
+      <c r="O59">
         <v>85.129495199999994</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P59">
         <v>114.048</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q59">
         <v>9.5399999999999991</v>
       </c>
-      <c r="R42" s="1">
+      <c r="R59">
         <v>9.4135299999999997</v>
       </c>
-      <c r="S42" s="1">
+      <c r="S59">
         <f t="shared" si="2"/>
         <v>1175.9460676296278</v>
       </c>
-      <c r="T42" s="1">
+      <c r="T59">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="1">
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60">
         <v>12.5199</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D60">
         <v>0.1062</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E60">
         <v>0.41279399999999999</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F60">
         <v>2.627204E-2</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G60">
         <v>843</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I60">
         <v>5770</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J60">
         <v>0.96799999999999997</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K60">
         <v>1.022</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L60">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M43" s="1">
+      <c r="M60">
         <v>4.47</v>
       </c>
-      <c r="N43" s="1">
+      <c r="N60">
         <v>192.1848981</v>
       </c>
-      <c r="O43" s="1">
+      <c r="O60">
         <v>64.855275500000005</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P60">
         <v>84.536199999999994</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q60">
         <v>9.5340000000000007</v>
       </c>
-      <c r="R43" s="1">
+      <c r="R60">
         <v>9.3678899999999992</v>
       </c>
-      <c r="S43" s="1">
+      <c r="S60">
         <f t="shared" si="2"/>
         <v>1399.2265914107247</v>
       </c>
-      <c r="T43" s="1">
+      <c r="T60">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>77</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="1">
+      <c r="B61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61">
         <v>4.7202190000000002</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D61">
         <v>6.2600000000000003E-2</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E61">
         <v>1.3959999999999999</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F61">
         <v>2.37</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G61">
         <v>1679</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I61">
         <v>6274</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J61">
         <v>1.925</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K61">
         <v>1.464</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L61">
         <v>0.11899999999999999</v>
       </c>
-      <c r="M44" s="1">
+      <c r="M61">
         <v>4.0339999999999998</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N61">
         <v>325.01453629999997</v>
       </c>
-      <c r="O44" s="1">
+      <c r="O61">
         <v>48.4067674</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P61">
         <v>200.49199999999999</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q61">
         <v>9.4380000000000006</v>
       </c>
-      <c r="R44" s="1">
+      <c r="R61">
         <v>9.3503900000000009</v>
       </c>
-      <c r="S44" s="1">
+      <c r="S61">
         <f t="shared" si="2"/>
         <v>353.31388599481477</v>
       </c>
-      <c r="T44" s="1">
+      <c r="T61">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="1">
+      <c r="B62" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62">
         <v>4.4258699999999997</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D62">
         <v>5.7779999999999998E-2</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E62">
         <v>2.2303544500000001</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F62">
         <v>1.86578665</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G62">
         <v>1293</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H62" t="s">
         <v>70</v>
       </c>
-      <c r="I45" s="2">
+      <c r="I62">
         <v>6117</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J62">
         <v>1.53</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K62">
         <v>1.3120000000000001</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L62">
         <v>0.25</v>
       </c>
-      <c r="M45" s="1">
+      <c r="M62">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N62">
         <v>313.5110469</v>
       </c>
-      <c r="O45" s="1">
+      <c r="O62">
         <v>72.580645500000003</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P62">
         <v>139.48400000000001</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q62">
         <v>9.2700010000000006</v>
       </c>
-      <c r="R45" s="1">
+      <c r="R62">
         <v>9.1879500000000007</v>
       </c>
-      <c r="S45" s="1">
+      <c r="S62">
         <f t="shared" si="2"/>
         <v>882.20971786077962</v>
       </c>
-      <c r="T45" s="1">
+      <c r="T62">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="1">
+      <c r="B63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63">
         <v>2.6502370000000002</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D63">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E63">
         <v>1.49</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F63">
         <v>3.12</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G63">
         <v>2370</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H63" t="s">
         <v>35</v>
       </c>
-      <c r="I46" s="2">
+      <c r="I63">
         <v>7690</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J63">
         <v>1.92</v>
       </c>
-      <c r="K46" s="1">
+      <c r="K63">
         <v>1.9</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L63">
         <v>0.09</v>
       </c>
-      <c r="M46" s="1">
+      <c r="M63">
         <v>4.1500000000000004</v>
       </c>
-      <c r="N46" s="1">
+      <c r="N63">
         <v>316.20369219999998</v>
       </c>
-      <c r="O46" s="1">
+      <c r="O63">
         <v>55.588022100000003</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P63">
         <v>148.92500000000001</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q63">
         <v>8.0299999999999994</v>
       </c>
-      <c r="R46" s="1">
+      <c r="R63">
         <v>7.9756099999999996</v>
       </c>
-      <c r="S46" s="1">
+      <c r="S63">
         <f t="shared" si="2"/>
         <v>431.57254486096394</v>
       </c>
-      <c r="T46" s="1">
+      <c r="T63">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="1">
+      <c r="B64" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64">
         <v>1.902603</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D64">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E64">
         <v>1.875</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F64">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G64">
         <v>2492</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H64" t="s">
         <v>61</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I64">
         <v>7300</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J64">
         <v>1.95</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K64">
         <v>1.79</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L64">
         <v>-0.1</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M64">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N64">
         <v>352.26752069999998</v>
       </c>
-      <c r="O47" s="1">
+      <c r="O64">
         <v>67.034806200000006</v>
       </c>
-      <c r="P47" s="1">
+      <c r="P64">
         <v>225.88800000000001</v>
       </c>
-      <c r="Q47" s="1">
+      <c r="Q64">
         <v>8.952</v>
       </c>
-      <c r="R47" s="1">
+      <c r="R64">
         <v>8.8952899999999993</v>
       </c>
-      <c r="S47" s="1">
+      <c r="S64">
         <f t="shared" si="2"/>
         <v>974.78820571370204</v>
       </c>
-      <c r="T47" s="1">
+      <c r="T64">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1">
+      <c r="B65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65">
         <v>3.2086640000000002</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D65">
         <v>4.8820000000000002E-2</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E65">
         <v>1.44</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F65">
         <v>0.7</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G65">
         <v>1927</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H65" t="s">
         <v>56</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I65">
         <v>5991</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J65">
         <v>2.1680000000000001</v>
       </c>
-      <c r="K48" s="1">
+      <c r="K65">
         <v>1.5069999999999999</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L65">
         <v>0.373</v>
       </c>
-      <c r="M48" s="1">
+      <c r="M65">
         <v>3.9430000000000001</v>
       </c>
-      <c r="N48" s="1">
+      <c r="N65">
         <v>142.74340599999999</v>
       </c>
-      <c r="O48" s="1">
+      <c r="O65">
         <v>26.539995099999999</v>
       </c>
-      <c r="P48" s="1">
+      <c r="P65">
         <v>229.06700000000001</v>
       </c>
-      <c r="Q48" s="1">
+      <c r="Q65">
         <v>9.7210000000000001</v>
       </c>
-      <c r="R48" s="1">
+      <c r="R65">
         <v>9.5843900000000009</v>
       </c>
-      <c r="S48" s="1">
+      <c r="S65">
         <f t="shared" si="2"/>
         <v>1460.8182255852041</v>
       </c>
-      <c r="T48" s="1">
+      <c r="T65">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="1">
+      <c r="B66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66">
         <v>9.5739181000000002</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D66">
         <v>0.1</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E66">
         <v>1.10166148</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F66">
         <v>0.28128386</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G66">
         <v>1199.55</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I66">
         <v>6039</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J66">
         <v>2.032</v>
       </c>
-      <c r="K49" s="1">
+      <c r="K66">
         <v>1.4642999999999999</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L66">
         <v>0.33200000000000002</v>
       </c>
-      <c r="M49" s="1">
+      <c r="M66">
         <v>3.9860000000000002</v>
       </c>
-      <c r="N49" s="1">
+      <c r="N66">
         <v>201.9626552</v>
       </c>
-      <c r="O49" s="1">
+      <c r="O66">
         <v>9.0306437000000006</v>
       </c>
-      <c r="P49" s="1">
+      <c r="P66">
         <v>223.465</v>
       </c>
-      <c r="Q49" s="1">
+      <c r="Q66">
         <v>9.8149999999999995</v>
       </c>
-      <c r="R49" s="1">
+      <c r="R66">
         <v>9.6598100000000002</v>
       </c>
-      <c r="S49" s="1">
+      <c r="S66">
         <f t="shared" si="2"/>
         <v>1324.5165539963698</v>
       </c>
-      <c r="T49" s="1">
+      <c r="T66">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="1">
+      <c r="B67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67">
         <v>17.305904000000002</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D67">
         <v>0.16</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E67">
         <v>1.07</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F67">
         <v>6.4</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G67">
         <v>1221.3900000000001</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I67">
         <v>7130</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J67">
         <v>2.02</v>
       </c>
-      <c r="K50" s="1">
+      <c r="K67">
         <v>1.59</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L67">
         <v>0</v>
       </c>
-      <c r="M50" s="1">
+      <c r="M67">
         <v>3.9460000000000002</v>
       </c>
-      <c r="N50" s="1">
+      <c r="N67">
         <v>164.031654</v>
       </c>
-      <c r="O50" s="1">
+      <c r="O67">
         <v>-43.376696699999997</v>
       </c>
-      <c r="P50" s="1">
+      <c r="P67">
         <v>328.47500000000002</v>
       </c>
-      <c r="Q50" s="1">
+      <c r="Q67">
         <v>9.8670000000000009</v>
       </c>
-      <c r="R50" s="1">
+      <c r="R67">
         <v>9.7596699999999998</v>
       </c>
-      <c r="S50" s="1">
+      <c r="S67">
         <f t="shared" si="2"/>
         <v>55.915145726222889</v>
       </c>
-      <c r="T50" s="1">
+      <c r="T67">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="1">
+      <c r="B68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68">
         <v>10.261127</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D68">
         <v>0.111</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E68">
         <v>1.1079506100000001</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F68">
         <v>5.55960374</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G68">
         <v>1363.43</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I68">
         <v>6200</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J68">
         <v>2.7505000000000002</v>
       </c>
-      <c r="K51" s="1">
+      <c r="K68">
         <v>1.7169000000000001</v>
       </c>
-      <c r="L51" s="1">
+      <c r="L68">
         <v>0.28499999999999998</v>
       </c>
-      <c r="M51" s="1">
+      <c r="M68">
         <v>3.7890000000000001</v>
       </c>
-      <c r="N51" s="1">
+      <c r="N68">
         <v>263.75807529999997</v>
       </c>
-      <c r="O51" s="1">
+      <c r="O68">
         <v>40.695042800000003</v>
       </c>
-      <c r="P51" s="1">
+      <c r="P68">
         <v>224.73099999999999</v>
       </c>
-      <c r="Q51" s="1">
+      <c r="Q68">
         <v>9.07</v>
       </c>
-      <c r="R51" s="1">
+      <c r="R68">
         <v>8.9365100000000002</v>
       </c>
-      <c r="S51" s="1">
+      <c r="S68">
         <f t="shared" si="2"/>
         <v>77.040187113891676</v>
       </c>
-      <c r="T51" s="1">
+      <c r="T68">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="1">
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69">
         <v>10.655669</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D69">
         <v>0.1166</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E69">
         <v>0.99399999999999999</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F69">
         <v>4.82</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G69">
         <v>1595</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I69">
         <v>7360</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J69">
         <v>2.36</v>
       </c>
-      <c r="K52" s="1">
+      <c r="K69">
         <v>1.859</v>
       </c>
-      <c r="L52" s="1">
+      <c r="L69">
         <v>9.4E-2</v>
       </c>
-      <c r="M52" s="1">
+      <c r="M69">
         <v>3.9620000000000002</v>
       </c>
-      <c r="N52" s="1">
+      <c r="N69">
         <v>90.062587800000003</v>
       </c>
-      <c r="O52" s="1">
+      <c r="O69">
         <v>11.8840577</v>
       </c>
-      <c r="P52" s="1">
+      <c r="P69">
         <v>285.28899999999999</v>
       </c>
-      <c r="Q52" s="1">
+      <c r="Q69">
         <v>9.5470000000000006</v>
       </c>
-      <c r="R52" s="1">
+      <c r="R69">
         <v>9.4724400000000006</v>
       </c>
-      <c r="S52" s="1">
+      <c r="S69">
         <f t="shared" si="2"/>
         <v>83.670803141549356</v>
       </c>
-      <c r="T52" s="1">
+      <c r="T69">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="1">
+      <c r="B70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70">
         <v>18.388179999999998</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D70">
         <v>0.15279999999999999</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E70">
         <v>0.63900000000000001</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F70">
         <v>0.13800000000000001</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G70">
         <v>1027</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I70">
         <v>6095</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J70">
         <v>1.867</v>
       </c>
-      <c r="K53" s="1">
+      <c r="K70">
         <v>1.407</v>
       </c>
-      <c r="L53" s="1">
+      <c r="L70">
         <v>0.17499999999999999</v>
       </c>
-      <c r="M53" s="1">
+      <c r="M70">
         <v>4.0439999999999996</v>
       </c>
-      <c r="N53" s="1">
+      <c r="N70">
         <v>47.517260800000003</v>
       </c>
-      <c r="O53" s="1">
+      <c r="O70">
         <v>-50.8322632</v>
       </c>
-      <c r="P53" s="1">
+      <c r="P70">
         <v>76.902799999999999</v>
       </c>
-      <c r="Q53" s="1">
+      <c r="Q70">
         <v>7.57</v>
       </c>
-      <c r="R53" s="1">
+      <c r="R70">
         <v>7.4165299999999998</v>
       </c>
-      <c r="S53" s="1">
+      <c r="S70">
         <f t="shared" si="2"/>
         <v>777.64358420307099</v>
       </c>
-      <c r="T53" s="1">
+      <c r="T70">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="1">
+      <c r="B71" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71">
         <v>16.067540999999999</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D71">
         <v>0.11700000000000001</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E71">
         <v>0.45410017000000003</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F71">
         <v>4.4363560000000003E-2</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G71">
         <v>635</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H71" t="s">
         <v>116</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I71">
         <v>5291</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J71">
         <v>0.86599999999999999</v>
       </c>
-      <c r="K54" s="1">
+      <c r="K71">
         <v>0.83299999999999996</v>
       </c>
-      <c r="L54" s="1">
+      <c r="L71">
         <v>-4.3999999999999997E-2</v>
       </c>
-      <c r="M54" s="1">
+      <c r="M71">
         <v>4.4800000000000004</v>
       </c>
-      <c r="N54" s="1">
+      <c r="N71">
         <v>81.853282399999998</v>
       </c>
-      <c r="O54" s="1">
+      <c r="O71">
         <v>-14.2767404</v>
       </c>
-      <c r="P54" s="1">
+      <c r="P71">
         <v>74.796899999999994</v>
       </c>
-      <c r="Q54" s="1">
+      <c r="Q71">
         <v>9.9309999999999992</v>
       </c>
-      <c r="R54" s="1">
+      <c r="R71">
         <v>9.7777600000000007</v>
       </c>
-      <c r="S54" s="1">
+      <c r="S71">
         <f t="shared" si="2"/>
         <v>755.33252275944176</v>
       </c>
-      <c r="T54" s="1">
+      <c r="T71">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="1">
+      <c r="B72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72">
         <v>9.9558099999999996</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D72">
         <v>9.9400000000000002E-2</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E72">
         <v>1.0580000000000001</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F72">
         <v>1.49</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G72">
         <v>1655</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I72">
         <v>4896</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J72">
         <v>3.55</v>
       </c>
-      <c r="K55" s="1">
+      <c r="K72">
         <v>1.31</v>
       </c>
-      <c r="L55" s="1">
+      <c r="L72">
         <v>0.23</v>
       </c>
-      <c r="M55" s="1">
+      <c r="M72">
         <v>3.48</v>
       </c>
-      <c r="N55" s="1">
+      <c r="N72">
         <v>184.97875790000001</v>
       </c>
-      <c r="O55" s="1">
+      <c r="O72">
         <v>-25.827853099999999</v>
       </c>
-      <c r="P55" s="1">
+      <c r="P72">
         <v>215.98599999999999</v>
       </c>
-      <c r="Q55" s="1">
+      <c r="Q72">
         <v>9.9730000000000008</v>
       </c>
-      <c r="R55" s="1">
+      <c r="R72">
         <v>9.641</v>
       </c>
-      <c r="S55" s="1">
+      <c r="S72">
         <f t="shared" si="2"/>
         <v>318.17832033985127</v>
       </c>
-      <c r="T55" s="1">
+      <c r="T72">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>68</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="1">
+      <c r="B73" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73">
         <v>7.2459899999999999</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D73">
         <v>8.8800000000000004E-2</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E73">
         <v>1.042</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F73">
         <v>12.89</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G73">
         <v>1677</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H73" t="s">
         <v>56</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I73">
         <v>6264</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J73">
         <v>2.738</v>
       </c>
-      <c r="K56" s="1">
+      <c r="K73">
         <v>1.7649999999999999</v>
       </c>
-      <c r="L56" s="1">
+      <c r="L73">
         <v>0.34200000000000003</v>
       </c>
-      <c r="M56" s="1">
+      <c r="M73">
         <v>3.81</v>
       </c>
-      <c r="N56" s="1">
+      <c r="N73">
         <v>83.865928800000006</v>
       </c>
-      <c r="O56" s="1">
+      <c r="O73">
         <v>21.294241700000001</v>
       </c>
-      <c r="P56" s="1">
+      <c r="P73">
         <v>225.643</v>
       </c>
-      <c r="Q56" s="1">
+      <c r="Q73">
         <v>9.24</v>
       </c>
-      <c r="R56" s="1">
+      <c r="R73">
         <v>9.0746900000000004</v>
       </c>
-      <c r="S56" s="1">
+      <c r="S73">
         <f t="shared" si="2"/>
         <v>36.149567272802649</v>
       </c>
-      <c r="T56" s="1">
+      <c r="T73">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
         <v>119</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="1">
+      <c r="B74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74">
         <v>10.331110000000001</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D74">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E74">
         <v>0.99</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F74">
         <v>1.53</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G74">
         <v>1370</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H74" t="s">
         <v>120</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I74">
         <v>5735</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J74">
         <v>1.66</v>
       </c>
-      <c r="K57" s="1">
+      <c r="K74">
         <v>1.1399999999999999</v>
       </c>
-      <c r="L57" s="1">
+      <c r="L74">
         <v>0.26</v>
       </c>
-      <c r="M57" s="1">
+      <c r="M74">
         <v>4.0599999999999996</v>
       </c>
-      <c r="N57" s="1">
+      <c r="N74">
         <v>110.5126861</v>
       </c>
-      <c r="O57" s="1">
+      <c r="O74">
         <v>-57.384998000000003</v>
       </c>
-      <c r="P57" s="1">
+      <c r="P74">
         <v>179.36600000000001</v>
       </c>
-      <c r="Q57" s="1">
+      <c r="Q74">
         <v>9.9719999999999995</v>
       </c>
-      <c r="R57" s="1">
+      <c r="R74">
         <v>9.8465900000000008</v>
       </c>
-      <c r="S57" s="1">
+      <c r="S74">
         <f t="shared" si="2"/>
         <v>224.58825733889913</v>
       </c>
-      <c r="T57" s="1">
+      <c r="T74">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>92</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" s="1">
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75">
         <v>6.7535809999999996</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D75">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E75">
         <v>0.58881357999999995</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F75">
         <v>0.10068326</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G75">
         <v>1180</v>
       </c>
-      <c r="I58" s="2">
+      <c r="I75">
         <v>5808</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J75">
         <v>1.29</v>
       </c>
-      <c r="K58" s="1">
+      <c r="K75">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L58" s="1">
+      <c r="L75">
         <v>0.2</v>
       </c>
-      <c r="M58" s="1">
+      <c r="M75">
         <v>4.26</v>
       </c>
-      <c r="N58" s="1">
+      <c r="N75">
         <v>166.26950410000001</v>
       </c>
-      <c r="O58" s="1">
+      <c r="O75">
         <v>11.2464069</v>
       </c>
-      <c r="P58" s="1">
+      <c r="P75">
         <v>130.91900000000001</v>
       </c>
-      <c r="Q58" s="1">
+      <c r="Q75">
         <v>9.75</v>
       </c>
-      <c r="R58" s="1">
+      <c r="R75">
         <v>9.6080000000000005</v>
       </c>
-      <c r="S58" s="1">
+      <c r="S75">
         <f t="shared" si="2"/>
         <v>1039.84328949877</v>
       </c>
-      <c r="T58" s="1">
+      <c r="T75">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="1">
+      <c r="B76" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76">
         <v>10.590547000000001</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D76">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E76">
         <v>0.91890603000000004</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F76">
         <v>0.18469084999999999</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G76">
         <v>947</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H76" t="s">
         <v>130</v>
       </c>
-      <c r="I59" s="2">
+      <c r="I76">
         <v>6000</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J76">
         <v>1.0509999999999999</v>
       </c>
-      <c r="K59" s="1">
+      <c r="K76">
         <v>1.1459999999999999</v>
       </c>
-      <c r="L59" s="1">
+      <c r="L76">
         <v>0.09</v>
       </c>
-      <c r="M59" s="1">
+      <c r="M76">
         <v>4.4400000000000004</v>
       </c>
-      <c r="N59" s="1">
+      <c r="N76">
         <v>161.87955690000001</v>
       </c>
-      <c r="O59" s="1">
+      <c r="O76">
         <v>36.329434499999998</v>
       </c>
-      <c r="P59" s="1">
+      <c r="P76">
         <v>130.85499999999999</v>
       </c>
-      <c r="Q59" s="1">
+      <c r="Q76">
         <v>10.058999999999999</v>
       </c>
-      <c r="R59" s="1">
+      <c r="R76">
         <v>9.9823299999999993</v>
       </c>
-      <c r="S59" s="1">
+      <c r="S76">
         <f t="shared" si="2"/>
         <v>1107.9861243219782</v>
       </c>
-      <c r="T59" s="1">
+      <c r="T76">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="1">
+      <c r="B77" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77">
         <v>5.8267310999999999</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D77">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E77">
         <v>0.57186287999999996</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F77">
         <v>0.24698861999999999</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G77">
         <v>1439</v>
       </c>
-      <c r="I60" s="2">
+      <c r="I77">
         <v>6110</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J77">
         <v>1.6479999999999999</v>
       </c>
-      <c r="K60" s="1">
+      <c r="K77">
         <v>1.2909999999999999</v>
       </c>
-      <c r="L60" s="1">
+      <c r="L77">
         <v>0.124</v>
       </c>
-      <c r="M60" s="1">
+      <c r="M77">
         <v>4.1180000000000003</v>
       </c>
-      <c r="N60" s="1">
+      <c r="N77">
         <v>51.657269100000001</v>
       </c>
-      <c r="O60" s="1">
+      <c r="O77">
         <v>40.817270399999998</v>
       </c>
-      <c r="P60" s="1">
+      <c r="P77">
         <v>179.14699999999999</v>
       </c>
-      <c r="Q60" s="1">
+      <c r="Q77">
         <v>9.9130000000000003</v>
       </c>
-      <c r="R60" s="1">
+      <c r="R77">
         <v>9.7295700000000007</v>
       </c>
-      <c r="S60" s="1">
+      <c r="S77">
         <f t="shared" si="2"/>
         <v>487.59044264912109</v>
       </c>
-      <c r="T60" s="1">
+      <c r="T77">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="1">
+      <c r="B78" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78">
         <v>6.4025129999999999</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D78">
         <v>7.0800000000000002E-2</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E78">
         <v>0.82399999999999995</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F78">
         <v>0.30299999999999999</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G78">
         <v>1388</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H78" t="s">
         <v>63</v>
       </c>
-      <c r="I61" s="2">
+      <c r="I78">
         <v>6400</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J78">
         <v>1.415</v>
       </c>
-      <c r="K61" s="1">
+      <c r="K78">
         <v>1.3129999999999999</v>
       </c>
-      <c r="L61" s="1">
+      <c r="L78">
         <v>0.09</v>
       </c>
-      <c r="M61" s="1">
+      <c r="M78">
         <v>4.2</v>
       </c>
-      <c r="N61" s="1">
+      <c r="N78">
         <v>125.3050544</v>
       </c>
-      <c r="O61" s="1">
+      <c r="O78">
         <v>-46.484295899999999</v>
       </c>
-      <c r="P61" s="1">
+      <c r="P78">
         <v>123.297</v>
       </c>
-      <c r="Q61" s="1">
+      <c r="Q78">
         <v>8.9949999999999992</v>
       </c>
-      <c r="R61" s="1">
+      <c r="R78">
         <v>8.8910300000000007</v>
       </c>
-      <c r="S61" s="1">
+      <c r="S78">
         <f t="shared" si="2"/>
         <v>795.95548671567838</v>
       </c>
-      <c r="T61" s="1">
+      <c r="T78">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
         <v>105</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="1">
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79">
         <v>11.236598499999999</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D79">
         <v>0.1041</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E79">
         <v>1.17</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F79">
         <v>1.234</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G79">
         <v>1252</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H79" t="s">
         <v>54</v>
       </c>
-      <c r="I62" s="2">
+      <c r="I79">
         <v>6295</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J79">
         <v>1.28</v>
       </c>
-      <c r="K62" s="1">
+      <c r="K79">
         <v>1.181</v>
       </c>
-      <c r="L62" s="1">
+      <c r="L79">
         <v>0</v>
       </c>
-      <c r="M62" s="1">
+      <c r="M79">
         <v>4.2910000000000004</v>
       </c>
-      <c r="N62" s="1">
+      <c r="N79">
         <v>144.11935940000001</v>
       </c>
-      <c r="O62" s="1">
+      <c r="O79">
         <v>-50.463093299999997</v>
       </c>
-      <c r="P62" s="1">
+      <c r="P79">
         <v>141.81200000000001</v>
       </c>
-      <c r="Q62" s="1">
+      <c r="Q79">
         <v>9.8219999999999992</v>
       </c>
-      <c r="R62" s="1">
+      <c r="R79">
         <v>9.6608199999999993</v>
       </c>
-      <c r="S62" s="1">
+      <c r="S79">
         <f t="shared" si="2"/>
         <v>355.42536038318485</v>
       </c>
-      <c r="T62" s="1">
+      <c r="T79">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="1">
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80">
         <v>4.6336110000000001</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D80">
         <v>0.06</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E80">
         <v>1.37</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F80">
         <v>2.8</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G80">
         <v>1561</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H80" t="s">
         <v>66</v>
       </c>
-      <c r="I63" s="2">
+      <c r="I80">
         <v>6643</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J80">
         <v>1.71</v>
       </c>
-      <c r="K63" s="1">
+      <c r="K80">
         <v>1.4</v>
       </c>
-      <c r="L63" s="1">
+      <c r="L80">
         <v>0</v>
       </c>
-      <c r="M63" s="1">
+      <c r="M80">
         <v>4.05</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N80">
         <v>199.33385029999999</v>
       </c>
-      <c r="O63" s="1">
+      <c r="O80">
         <v>-15.2737046</v>
       </c>
-      <c r="P63" s="1">
+      <c r="P80">
         <v>161.74299999999999</v>
       </c>
-      <c r="Q63" s="1">
+      <c r="Q80">
         <v>9.109</v>
       </c>
-      <c r="R63" s="1">
+      <c r="R80">
         <v>8.9943600000000004</v>
       </c>
-      <c r="S63" s="1">
+      <c r="S80">
         <f t="shared" si="2"/>
         <v>267.77715667890726</v>
       </c>
-      <c r="T63" s="1">
+      <c r="T80">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
         <v>143</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I81">
         <v>6161.02294921875</v>
       </c>
-      <c r="J64" s="6">
+      <c r="J81">
         <v>1.7061723470687871</v>
       </c>
-      <c r="K64" s="1">
+      <c r="K81">
         <v>1.3463604</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M81">
         <v>3.9825000762939449</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N81">
         <v>268.30433503422898</v>
       </c>
-      <c r="O64" s="6">
+      <c r="O81">
         <v>37.211736733677057</v>
       </c>
-      <c r="P64" s="1">
+      <c r="P81">
         <v>496.26729999999998</v>
       </c>
-      <c r="Q64" s="6">
+      <c r="Q81">
         <v>11.469913482666019</v>
       </c>
-      <c r="R64" s="6">
+      <c r="R81">
         <v>11.469913482666019</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A65" s="3" t="s">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
         <v>138</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" s="2">
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82">
         <v>6200</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J82">
         <v>1.2</v>
       </c>
-      <c r="N65" s="1">
+      <c r="N82">
         <v>97.636728000000005</v>
       </c>
-      <c r="O65" s="1">
+      <c r="O82">
         <v>29.672419000000001</v>
       </c>
-      <c r="P65" s="1">
+      <c r="P82">
         <v>427</v>
       </c>
-      <c r="R65" s="1">
+      <c r="R82">
         <v>11.4986</v>
       </c>
-      <c r="T65" s="1">
-        <f t="shared" ref="T65:T85" si="4">IF(I65&gt;6800,-7,-5)</f>
+      <c r="T82">
+        <f t="shared" ref="T82:T102" si="4">IF(I82&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
         <v>131</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="1">
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83">
         <v>5.3220124999999996</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D83">
         <v>6.08E-2</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E83">
         <v>1.226</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F83">
         <v>0.27300000000000002</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G83">
         <v>1460</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H83" t="s">
         <v>43</v>
       </c>
-      <c r="I66" s="2">
+      <c r="I83">
         <v>5990</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J83">
         <v>1.5609999999999999</v>
       </c>
-      <c r="K66" s="1">
+      <c r="K83">
         <v>1.06</v>
       </c>
-      <c r="L66" s="1">
+      <c r="L83">
         <v>-0.2</v>
       </c>
-      <c r="M66" s="1">
+      <c r="M83">
         <v>4.0750000000000002</v>
       </c>
-      <c r="N66" s="1">
+      <c r="N83">
         <v>210.1935714</v>
       </c>
-      <c r="O66" s="1">
+      <c r="O83">
         <v>-30.583608399999999</v>
       </c>
-      <c r="P66" s="1">
+      <c r="P83">
         <v>200.07499999999999</v>
       </c>
-      <c r="Q66" s="1">
+      <c r="Q83">
         <v>10.068</v>
       </c>
-      <c r="R66" s="1">
+      <c r="R83">
         <v>9.8670799999999996</v>
       </c>
-      <c r="S66" s="1">
-        <f t="shared" ref="S66:S85" si="5">(0.000000000000000138*G66/(1.673534E-24*1.3*0.000000066726*F66*1.8986E+30/(E66*7149200000)^2))/100000</f>
+      <c r="S83">
+        <f t="shared" ref="S83:S102" si="5">(0.000000000000000138*G83/(1.673534E-24*1.3*0.000000066726*F83*1.8986E+30/(E83*7149200000)^2))/100000</f>
         <v>2057.1154637812851</v>
       </c>
-      <c r="T66" s="1">
+      <c r="T83">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>122</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67" s="1">
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84">
         <v>5.21536178778</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D84">
         <v>6.6100000000000006E-2</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E84">
         <v>1.5</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F84">
         <v>1.51</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G84">
         <v>1630</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H84" t="s">
         <v>56</v>
       </c>
-      <c r="I67" s="2">
+      <c r="I84">
         <v>6250</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J84">
         <v>2.3901400000000002</v>
       </c>
-      <c r="K67" s="1">
+      <c r="K84">
         <v>1.41</v>
       </c>
-      <c r="L67" s="1">
+      <c r="L84">
         <v>-0.18</v>
       </c>
-      <c r="M67" s="1">
+      <c r="M84">
         <v>3.9</v>
       </c>
-      <c r="N67" s="1">
+      <c r="N84">
         <v>0.32576100000000002</v>
       </c>
-      <c r="O67" s="1">
+      <c r="O84">
         <v>-8.9262511999999994</v>
       </c>
-      <c r="P67" s="1">
+      <c r="P84">
         <v>275.58699999999999</v>
       </c>
-      <c r="Q67" s="1">
+      <c r="Q84">
         <v>9.9740000000000002</v>
       </c>
-      <c r="R67" s="1">
+      <c r="R84">
         <v>9.8192900000000005</v>
       </c>
-      <c r="S67" s="1">
+      <c r="S84">
         <f t="shared" si="5"/>
         <v>621.55661806820979</v>
       </c>
-      <c r="T67" s="1">
+      <c r="T84">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>89</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="1">
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85">
         <v>2.2437499999999999</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D85">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E85">
         <v>1.38</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F85">
         <v>8.84</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G85">
         <v>1872</v>
       </c>
-      <c r="I68" s="2">
+      <c r="I85">
         <v>6475</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J85">
         <v>1.4</v>
       </c>
-      <c r="K68" s="1">
+      <c r="K85">
         <v>1.62</v>
       </c>
-      <c r="L68" s="1">
+      <c r="L85">
         <v>0</v>
       </c>
-      <c r="M68" s="1">
+      <c r="M85">
         <v>4.07</v>
       </c>
-      <c r="N68" s="1">
+      <c r="N85">
         <v>218.27662470000001</v>
       </c>
-      <c r="O68" s="1">
+      <c r="O85">
         <v>21.8946875</v>
       </c>
-      <c r="P68" s="1">
+      <c r="P85">
         <v>161.99700000000001</v>
       </c>
-      <c r="Q68" s="1">
+      <c r="Q85">
         <v>9.7449999999999992</v>
       </c>
-      <c r="R68" s="1">
+      <c r="R85">
         <v>9.6464700000000008</v>
       </c>
-      <c r="S68" s="1">
+      <c r="S85">
         <f t="shared" si="5"/>
         <v>103.20465157174387</v>
       </c>
-      <c r="T68" s="1">
+      <c r="T85">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C69" s="1">
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86">
         <v>5.4435399999999996</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D86">
         <v>6.4100000000000004E-2</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E86">
         <v>0.63</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F86">
         <v>0.10100000000000001</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G86">
         <v>1270</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H86" t="s">
         <v>74</v>
       </c>
-      <c r="I69" s="2">
+      <c r="I86">
         <v>6050</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J86">
         <v>1.22</v>
       </c>
-      <c r="K69" s="1">
+      <c r="K86">
         <v>1.19</v>
       </c>
-      <c r="L69" s="1">
+      <c r="L86">
         <v>0.19</v>
       </c>
-      <c r="M69" s="1">
+      <c r="M86">
         <v>4.34</v>
       </c>
-      <c r="N69" s="1">
+      <c r="N86">
         <v>144.87510470000001</v>
       </c>
-      <c r="O69" s="1">
+      <c r="O86">
         <v>-20.982419100000001</v>
       </c>
-      <c r="P69" s="1">
+      <c r="P86">
         <v>114.173</v>
       </c>
-      <c r="Q69" s="1">
+      <c r="Q86">
         <v>9.3510000000000009</v>
       </c>
-      <c r="R69" s="1">
+      <c r="R86">
         <v>9.2569999999999997</v>
       </c>
-      <c r="S69" s="1">
+      <c r="S86">
         <f t="shared" si="5"/>
         <v>1277.1766379712274</v>
       </c>
-      <c r="T69" s="1">
+      <c r="T86">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="1">
+      <c r="B87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87">
         <v>3.3448285000000002</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D87">
         <v>5.5800000000000002E-2</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E87">
         <v>1.81</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F87">
         <v>1.66</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G87">
         <v>2470</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H87" t="s">
         <v>118</v>
       </c>
-      <c r="I70" s="2">
+      <c r="I87">
         <v>9360</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J87">
         <v>1.67</v>
       </c>
-      <c r="K70" s="1">
+      <c r="K87">
         <v>2.0699999999999998</v>
       </c>
-      <c r="L70" s="1">
+      <c r="L87">
         <v>0.21</v>
       </c>
-      <c r="M70" s="1">
+      <c r="M87">
         <v>4.3099999999999996</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N87">
         <v>227.270329</v>
       </c>
-      <c r="O70" s="1">
+      <c r="O87">
         <v>-42.704965799999997</v>
       </c>
-      <c r="P70" s="1">
+      <c r="P87">
         <v>427.678</v>
       </c>
-      <c r="Q70" s="1">
+      <c r="Q87">
         <v>9.9459999999999997</v>
       </c>
-      <c r="R70" s="1">
+      <c r="R87">
         <v>9.9122599999999998</v>
       </c>
-      <c r="S70" s="1">
+      <c r="S87">
         <f t="shared" si="5"/>
         <v>1247.4798366438731</v>
       </c>
-      <c r="T70" s="1">
+      <c r="T87">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" s="1">
+      <c r="B88" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88">
         <v>0.94145223</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D88">
         <v>2.0240000000000001E-2</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E88">
         <v>1.24</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F88">
         <v>10.199999999999999</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G88">
         <v>2429</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H88" t="s">
         <v>72</v>
       </c>
-      <c r="I71" s="2">
+      <c r="I88">
         <v>6432</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J88">
         <v>1.319</v>
       </c>
-      <c r="K71" s="1">
+      <c r="K88">
         <v>1.294</v>
       </c>
-      <c r="L71" s="1">
+      <c r="L88">
         <v>0.107</v>
       </c>
-      <c r="M71" s="1">
+      <c r="M88">
         <v>4.3099999999999996</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N88">
         <v>24.354461799999999</v>
       </c>
-      <c r="O71" s="1">
+      <c r="O88">
         <v>-45.677793700000002</v>
       </c>
-      <c r="P71" s="1">
+      <c r="P88">
         <v>123.483</v>
       </c>
-      <c r="Q71" s="1">
+      <c r="Q88">
         <v>9.2799999999999994</v>
       </c>
-      <c r="R71" s="1">
+      <c r="R88">
         <v>9.1661699999999993</v>
       </c>
-      <c r="S71" s="1">
+      <c r="S88">
         <f t="shared" si="5"/>
         <v>93.704022194109143</v>
       </c>
-      <c r="T71" s="1">
+      <c r="T88">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>19</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" s="1">
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89">
         <v>2.7240329999999999</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D89">
         <v>5.0529999999999999E-2</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E89">
         <v>1.619</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F89">
         <v>1.99</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G89">
         <v>3353</v>
       </c>
-      <c r="I72" s="2">
+      <c r="I89">
         <v>8000</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J89">
         <v>2.36</v>
       </c>
-      <c r="K72" s="1">
+      <c r="K89">
         <v>2.0299999999999998</v>
       </c>
-      <c r="L72" s="1">
+      <c r="L89">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M72" s="1">
+      <c r="M89">
         <v>3.9</v>
       </c>
-      <c r="N72" s="1">
+      <c r="N89">
         <v>225.68673200000001</v>
       </c>
-      <c r="O72" s="1">
+      <c r="O89">
         <v>-3.0314874000000001</v>
       </c>
-      <c r="P72" s="1">
+      <c r="P89">
         <v>99.730999999999995</v>
       </c>
-      <c r="Q72" s="1">
+      <c r="Q89">
         <v>6.5977600000000001</v>
       </c>
-      <c r="R72" s="1">
+      <c r="R89">
         <v>6.5536899999999996</v>
       </c>
-      <c r="S72" s="15">
+      <c r="S89" s="6">
         <f t="shared" si="5"/>
         <v>1130.2166328238993</v>
       </c>
-      <c r="T72" s="1">
+      <c r="T89">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
-      <c r="U72" s="3" t="s">
+      <c r="U89" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
         <v>40</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="1">
+      <c r="B90" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90">
         <v>1.21987</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D90">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E90">
         <v>1.593</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F90">
         <v>2.093</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G90">
         <v>2781.7</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H90" t="s">
         <v>41</v>
       </c>
-      <c r="I73" s="2">
+      <c r="I90">
         <v>7430</v>
       </c>
-      <c r="J73" s="1">
+      <c r="J90">
         <v>1.444</v>
       </c>
-      <c r="K73" s="1">
+      <c r="K90">
         <v>1.4950000000000001</v>
       </c>
-      <c r="L73" s="1">
+      <c r="L90">
         <v>0.1</v>
       </c>
-      <c r="M73" s="1">
+      <c r="M90">
         <v>4.25</v>
       </c>
-      <c r="N73" s="1">
+      <c r="N90">
         <v>36.712737500000003</v>
       </c>
-      <c r="O73" s="1">
+      <c r="O90">
         <v>37.5504441</v>
       </c>
-      <c r="P73" s="1">
+      <c r="P90">
         <v>121.944</v>
       </c>
-      <c r="Q73" s="1">
+      <c r="Q90">
         <v>8.14</v>
       </c>
-      <c r="R73" s="1">
+      <c r="R90">
         <v>8.0700400000000005</v>
       </c>
-      <c r="S73" s="1">
+      <c r="S90">
         <f t="shared" si="5"/>
         <v>863.09804630713359</v>
       </c>
-      <c r="T73" s="1">
+      <c r="T90">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="1">
+      <c r="B91" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91">
         <v>6.87188</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D91">
         <v>7.5219999999999995E-2</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E91">
         <v>1.23</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F91">
         <v>3.44</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G91">
         <v>1250</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H91" t="s">
         <v>70</v>
       </c>
-      <c r="I74" s="2">
+      <c r="I91">
         <v>6180</v>
       </c>
-      <c r="J74" s="1">
+      <c r="J91">
         <v>1.52</v>
       </c>
-      <c r="K74" s="1">
+      <c r="K91">
         <v>1.76</v>
       </c>
-      <c r="L74" s="1">
+      <c r="L91">
         <v>-0.02</v>
       </c>
-      <c r="M74" s="1">
+      <c r="M91">
         <v>4.25</v>
       </c>
-      <c r="N74" s="1">
+      <c r="N91">
         <v>243.95971940000001</v>
       </c>
-      <c r="O74" s="1">
+      <c r="O91">
         <v>10.0324103</v>
       </c>
-      <c r="P74" s="1">
+      <c r="P91">
         <v>136.24</v>
       </c>
-      <c r="Q74" s="1">
+      <c r="Q91">
         <v>9.391</v>
       </c>
-      <c r="R74" s="1">
+      <c r="R91">
         <v>9.20974</v>
       </c>
-      <c r="S74" s="1">
+      <c r="S91">
         <f t="shared" si="5"/>
         <v>140.68549179703928</v>
       </c>
-      <c r="T74" s="1">
+      <c r="T91">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>112</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75" s="1">
+      <c r="B92" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92">
         <v>3.86813881</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D92">
         <v>4.53E-2</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E92">
         <v>1</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F92">
         <v>0.26</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G92">
         <v>971</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H92" t="s">
         <v>113</v>
       </c>
-      <c r="I75" s="2">
+      <c r="I92">
         <v>4792</v>
       </c>
-      <c r="J75" s="1">
+      <c r="J92">
         <v>0.80100000000000005</v>
       </c>
-      <c r="K75" s="1">
+      <c r="K92">
         <v>0.83</v>
       </c>
-      <c r="L75" s="1">
+      <c r="L92">
         <v>0.35</v>
       </c>
-      <c r="M75" s="1">
+      <c r="M92">
         <v>4.57</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N92">
         <v>315.02596610000001</v>
       </c>
-      <c r="O75" s="1">
+      <c r="O92">
         <v>-5.0948570000000002</v>
       </c>
-      <c r="P75" s="1">
+      <c r="P92">
         <v>49.960500000000003</v>
       </c>
-      <c r="Q75" s="1">
+      <c r="Q92">
         <v>9.8729999999999993</v>
       </c>
-      <c r="R75" s="1">
+      <c r="R92">
         <v>9.4846599999999999</v>
       </c>
-      <c r="S75" s="1">
+      <c r="S92">
         <f t="shared" si="5"/>
         <v>955.72600175951948</v>
       </c>
-      <c r="T75" s="1">
+      <c r="T92">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
-      <c r="U75" s="3" t="s">
+      <c r="U92" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76" s="1">
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93">
         <v>4.9546416000000004</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D93">
         <v>6.1699999999999998E-2</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E93">
         <v>1.33</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F93">
         <v>0.96</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G93">
         <v>1487</v>
       </c>
-      <c r="I76" s="2">
+      <c r="I93">
         <v>6400</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J93">
         <v>1.4319999999999999</v>
       </c>
-      <c r="K76" s="1">
+      <c r="K93">
         <v>1.276</v>
       </c>
-      <c r="L76" s="1">
+      <c r="L93">
         <v>0</v>
       </c>
-      <c r="M76" s="1">
+      <c r="M93">
         <v>4.2320000000000002</v>
       </c>
-      <c r="N76" s="1">
+      <c r="N93">
         <v>311.04275580000001</v>
       </c>
-      <c r="O76" s="1">
+      <c r="O93">
         <v>-39.225485599999999</v>
       </c>
-      <c r="P76" s="1">
+      <c r="P93">
         <v>162.303</v>
       </c>
-      <c r="Q76" s="1">
+      <c r="Q93">
         <v>9.5039999999999996</v>
       </c>
-      <c r="R76" s="1">
+      <c r="R93">
         <v>9.3767099999999992</v>
       </c>
-      <c r="S76" s="1">
+      <c r="S93">
         <f t="shared" si="5"/>
         <v>701.18164217622461</v>
       </c>
-      <c r="T76" s="1">
+      <c r="T93">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
         <v>90</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77" s="1">
+      <c r="B94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94">
         <v>2.13775</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D94">
         <v>3.4430000000000002E-2</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E94">
         <v>1.36</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F94">
         <v>0.72</v>
       </c>
-      <c r="G77" s="1">
+      <c r="G94">
         <v>1865</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H94" t="s">
         <v>91</v>
       </c>
-      <c r="I77" s="2">
+      <c r="I94">
         <v>5990</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J94">
         <v>1.42</v>
       </c>
-      <c r="K77" s="1">
+      <c r="K94">
         <v>0.98</v>
       </c>
-      <c r="L77" s="1">
+      <c r="L94">
         <v>0.39</v>
       </c>
-      <c r="M77" s="1">
+      <c r="M94">
         <v>4.3899999999999997</v>
       </c>
-      <c r="N77" s="1">
+      <c r="N94">
         <v>304.53884299999999</v>
       </c>
-      <c r="O77" s="1">
+      <c r="O94">
         <v>-1.0760033</v>
       </c>
-      <c r="P77" s="1">
+      <c r="P94">
         <v>149.21600000000001</v>
       </c>
-      <c r="Q77" s="1">
+      <c r="Q94">
         <v>9.75</v>
       </c>
-      <c r="R77" s="1">
+      <c r="R94">
         <v>9.5723000000000003</v>
       </c>
-      <c r="S77" s="1">
+      <c r="S94">
         <f t="shared" si="5"/>
         <v>1226.0598654781754</v>
       </c>
-      <c r="T77" s="1">
+      <c r="T94">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78" s="1">
+      <c r="B95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95">
         <v>1.8098819799999999</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D95">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E95">
         <v>1.8540000000000001</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F95">
         <v>0.89400000000000002</v>
       </c>
-      <c r="G78" s="1">
+      <c r="G95">
         <v>2228</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H95" t="s">
         <v>52</v>
       </c>
-      <c r="I78" s="2">
+      <c r="I95">
         <v>6329</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J95">
         <v>1.756</v>
       </c>
-      <c r="K78" s="1">
+      <c r="K95">
         <v>1.458</v>
       </c>
-      <c r="L78" s="1">
+      <c r="L95">
         <v>0.36599999999999999</v>
       </c>
-      <c r="M78" s="1">
+      <c r="M95">
         <v>4.1959999999999997</v>
       </c>
-      <c r="N78" s="1">
+      <c r="N95">
         <v>26.632936000000001</v>
       </c>
-      <c r="O78" s="1">
+      <c r="O95">
         <v>2.7003889999999999</v>
       </c>
-      <c r="P78" s="1">
+      <c r="P95">
         <v>194.459</v>
       </c>
-      <c r="Q78" s="1">
+      <c r="Q95">
         <v>9.5180000000000007</v>
       </c>
-      <c r="R78" s="1">
+      <c r="R95">
         <v>9.3950700000000005</v>
       </c>
-      <c r="S78" s="1">
+      <c r="S95">
         <f t="shared" si="5"/>
         <v>2192.2225820487197</v>
       </c>
-      <c r="T78" s="1">
+      <c r="T95">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79" s="1">
+      <c r="B96" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96">
         <v>3.6623920000000001</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D96">
         <v>5.1900000000000002E-2</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E96">
         <v>1.53</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F96">
         <v>0.85</v>
       </c>
-      <c r="G79" s="1">
+      <c r="G96">
         <v>1716.2</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H96" t="s">
         <v>127</v>
       </c>
-      <c r="I79" s="2">
+      <c r="I96">
         <v>6600</v>
       </c>
-      <c r="J79" s="1">
+      <c r="J96">
         <v>1.51</v>
       </c>
-      <c r="K79" s="1">
+      <c r="K96">
         <v>1.39</v>
       </c>
-      <c r="L79" s="1">
+      <c r="L96">
         <v>0.03</v>
       </c>
-      <c r="M79" s="1">
+      <c r="M96">
         <v>4.2</v>
       </c>
-      <c r="N79" s="1">
+      <c r="N96">
         <v>66.370901599999996</v>
       </c>
-      <c r="O79" s="1">
+      <c r="O96">
         <v>-30.600436200000001</v>
       </c>
-      <c r="P79" s="1">
+      <c r="P96">
         <v>246.69</v>
       </c>
-      <c r="Q79" s="1">
+      <c r="Q96">
         <v>10.044</v>
       </c>
-      <c r="R79" s="1">
+      <c r="R96">
         <v>9.9720200000000006</v>
       </c>
-      <c r="S79" s="1">
+      <c r="S96">
         <f t="shared" si="5"/>
         <v>1209.5375438309629</v>
       </c>
-      <c r="T79" s="1">
+      <c r="T96">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
         <v>96</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" s="1">
+      <c r="B97" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97">
         <v>8.1587200000000006</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D97">
         <v>8.0100000000000005E-2</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E97">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F97">
         <v>2.54</v>
       </c>
-      <c r="G80" s="1">
+      <c r="G97">
         <v>1059</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H97" t="s">
         <v>97</v>
       </c>
-      <c r="I80" s="2">
+      <c r="I97">
         <v>5600</v>
       </c>
-      <c r="J80" s="1">
+      <c r="J97">
         <v>1.03</v>
       </c>
-      <c r="K80" s="1">
+      <c r="K97">
         <v>1.34</v>
       </c>
-      <c r="L80" s="1">
+      <c r="L97">
         <v>0.17</v>
       </c>
-      <c r="M80" s="1">
+      <c r="M97">
         <v>4.5</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N97">
         <v>359.90087369999998</v>
       </c>
-      <c r="O80" s="1">
+      <c r="O97">
         <v>-35.031334899999997</v>
       </c>
-      <c r="P80" s="1">
+      <c r="P97">
         <v>89.960599999999999</v>
       </c>
-      <c r="Q80" s="1">
+      <c r="Q97">
         <v>9.7889999999999997</v>
       </c>
-      <c r="R80" s="1">
+      <c r="R97">
         <v>9.6124899999999993</v>
       </c>
-      <c r="S80" s="1">
+      <c r="S97">
         <f t="shared" si="5"/>
         <v>136.24063220140397</v>
       </c>
-      <c r="T80" s="1">
+      <c r="T97">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
         <v>132</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="1">
+      <c r="B98" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98">
         <v>2.7057899999999999</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D98">
         <v>4.4699999999999997E-2</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E98">
         <v>1.62</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F98">
         <v>1.17</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G98">
         <v>2190</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H98" t="s">
         <v>127</v>
       </c>
-      <c r="I81" s="14">
+      <c r="I98">
         <v>6480</v>
       </c>
-      <c r="J81" s="13">
+      <c r="J98">
         <v>2.1</v>
       </c>
-      <c r="K81" s="1">
+      <c r="K98">
         <v>1.48</v>
       </c>
-      <c r="L81" s="1">
+      <c r="L98">
         <v>0.12</v>
       </c>
-      <c r="M81" s="13">
+      <c r="M98">
         <v>3.96</v>
       </c>
-      <c r="N81" s="13">
+      <c r="N98">
         <v>72.660591600000004</v>
       </c>
-      <c r="O81" s="13">
+      <c r="O98">
         <v>1.8938364999999999</v>
       </c>
-      <c r="P81" s="1">
+      <c r="P98">
         <v>275.66399999999999</v>
       </c>
-      <c r="Q81" s="13">
+      <c r="Q98">
         <v>10.073</v>
       </c>
-      <c r="R81" s="13">
+      <c r="R98">
         <v>9.8979599999999994</v>
       </c>
-      <c r="S81" s="1">
+      <c r="S98">
         <f t="shared" si="5"/>
         <v>1257.117296864338</v>
       </c>
-      <c r="T81" s="1">
+      <c r="T98">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A82" s="16" t="s">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
         <v>128</v>
       </c>
-      <c r="B82" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82" s="1">
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99">
         <v>3.9501900000000001</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D99">
         <v>5.5E-2</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E99">
         <v>1.58</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F99">
         <v>0.5</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G99">
         <v>1604</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H99" t="s">
         <v>54</v>
       </c>
-      <c r="I82" s="14">
+      <c r="I99">
         <v>6170</v>
       </c>
-      <c r="J82" s="13">
+      <c r="J99">
         <v>1.48</v>
       </c>
-      <c r="K82" s="1">
+      <c r="K99">
         <v>1.67</v>
       </c>
-      <c r="L82" s="1">
+      <c r="L99">
         <v>0.26</v>
       </c>
-      <c r="M82" s="13">
+      <c r="M99">
         <v>4.2699999999999996</v>
       </c>
-      <c r="N82" s="13">
+      <c r="N99">
         <v>313.78323929999999</v>
       </c>
-      <c r="O82" s="13">
+      <c r="O99">
         <v>-34.135751200000001</v>
       </c>
-      <c r="P82" s="1">
+      <c r="P99">
         <v>211.21100000000001</v>
       </c>
-      <c r="Q82" s="13">
+      <c r="Q99">
         <v>10.051</v>
       </c>
-      <c r="R82" s="13">
+      <c r="R99">
         <v>10.028499999999999</v>
       </c>
-      <c r="S82" s="1">
+      <c r="S99">
         <f t="shared" si="5"/>
         <v>2049.4439875099679</v>
       </c>
-      <c r="T82" s="1">
+      <c r="T99">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A83" s="16" t="s">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
         <v>133</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C83" s="1">
+      <c r="B100" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100">
         <v>2.1846700000000001</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D100">
         <v>3.4160000000000003E-2</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E100">
         <v>1.23</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F100">
         <v>1.44</v>
       </c>
-      <c r="G83" s="1">
+      <c r="G100">
         <v>1570</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H100" t="s">
         <v>134</v>
       </c>
-      <c r="I83" s="14">
+      <c r="I100">
         <v>5830</v>
       </c>
-      <c r="J83" s="13">
+      <c r="J100">
         <v>1.23</v>
       </c>
-      <c r="K83" s="1">
+      <c r="K100">
         <v>1.46</v>
       </c>
-      <c r="L83" s="1">
+      <c r="L100">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M83" s="13">
+      <c r="M100">
         <v>4.3600000000000003</v>
       </c>
-      <c r="N83" s="13">
+      <c r="N100">
         <v>337.45782430000003</v>
       </c>
-      <c r="O83" s="13">
+      <c r="O100">
         <v>-48.003098799999997</v>
       </c>
-      <c r="P83" s="1">
+      <c r="P100">
         <v>137.54400000000001</v>
       </c>
-      <c r="Q83" s="13">
+      <c r="Q100">
         <v>10.092000000000001</v>
       </c>
-      <c r="R83" s="13">
+      <c r="R100">
         <v>9.9369700000000005</v>
       </c>
-      <c r="S83" s="1">
+      <c r="S100">
         <f t="shared" si="5"/>
         <v>422.11900227636102</v>
       </c>
-      <c r="T83" s="1">
+      <c r="T100">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A84" s="16" t="s">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
         <v>79</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="1">
+      <c r="B101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101">
         <v>5.75251</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D101">
         <v>7.17E-2</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E101">
         <v>1.02</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F101">
         <v>2.4300000000000002</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G101">
         <v>1480</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="H101" t="s">
         <v>54</v>
       </c>
-      <c r="I84" s="14">
+      <c r="I101">
         <v>6150</v>
       </c>
-      <c r="J84" s="13">
+      <c r="J101">
         <v>1.64</v>
       </c>
-      <c r="K84" s="1">
+      <c r="K101">
         <v>1.21</v>
       </c>
-      <c r="L84" s="1">
+      <c r="L101">
         <v>0.21</v>
       </c>
-      <c r="M84" s="13">
+      <c r="M101">
         <v>4.3</v>
       </c>
-      <c r="N84" s="13">
+      <c r="N101">
         <v>39.897668899999999</v>
       </c>
-      <c r="O84" s="13">
+      <c r="O101">
         <v>-50.008193400000003</v>
       </c>
-      <c r="P84" s="1">
+      <c r="P101">
         <v>158.66</v>
       </c>
-      <c r="Q84" s="13">
+      <c r="Q101">
         <v>9.4749999999999996</v>
       </c>
-      <c r="R84" s="13">
+      <c r="R101">
         <v>9.3251000000000008</v>
       </c>
-      <c r="S84" s="1">
+      <c r="S101">
         <f t="shared" si="5"/>
         <v>162.15983922320817</v>
       </c>
-      <c r="T84" s="1">
+      <c r="T101">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A85" s="16" t="s">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
         <v>107</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85" s="1">
+      <c r="B102" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102">
         <v>3.1915399999999998</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D102">
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E102">
         <v>1.41</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F102">
         <v>7.29</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G102">
         <v>1729</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="H102" t="s">
         <v>108</v>
       </c>
-      <c r="I85" s="17">
+      <c r="I102">
         <v>6429</v>
       </c>
-      <c r="J85" s="18">
+      <c r="J102">
         <v>1.54</v>
       </c>
-      <c r="K85" s="1">
+      <c r="K102">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L85" s="1">
+      <c r="L102">
         <v>-0.18</v>
       </c>
-      <c r="M85" s="18">
+      <c r="M102">
         <v>3.95</v>
       </c>
-      <c r="N85" s="1">
+      <c r="N102">
         <v>65.469581399999996</v>
       </c>
-      <c r="O85" s="18">
+      <c r="O102">
         <v>57.817209499999997</v>
       </c>
-      <c r="P85" s="1">
+      <c r="P102">
         <v>213.053</v>
       </c>
-      <c r="Q85" s="18">
+      <c r="Q102">
         <v>9.8539999999999992</v>
       </c>
-      <c r="R85" s="18">
+      <c r="R102">
         <v>9.7388899999999996</v>
       </c>
-      <c r="S85" s="1">
+      <c r="S102">
         <f t="shared" si="5"/>
         <v>120.66830436099001</v>
       </c>
-      <c r="T85" s="1">
+      <c r="T102">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I86" s="2">
-        <v>3460</v>
-      </c>
-      <c r="J86" s="1">
-        <v>0.54700000000000004</v>
-      </c>
-      <c r="K86" s="1">
-        <v>0.54300000000000004</v>
-      </c>
-      <c r="L86" s="1">
-        <v>0</v>
-      </c>
-      <c r="M86" s="1">
-        <v>4.6963999999999997</v>
-      </c>
-      <c r="N86" s="1">
-        <v>303.19871318011002</v>
-      </c>
-      <c r="O86" s="1">
-        <v>-0.37849292589</v>
-      </c>
-      <c r="P86" s="1">
-        <v>312.65899999999999</v>
-      </c>
-      <c r="V86" s="1">
-        <v>10.968999999999999</v>
-      </c>
-      <c r="W86" s="1">
-        <v>11.454000000000001</v>
-      </c>
-      <c r="X86" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y86" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I87" s="2">
-        <v>3496</v>
-      </c>
-      <c r="J87" s="1">
-        <v>83.710999999999999</v>
-      </c>
-      <c r="K87" s="1">
-        <v>0</v>
-      </c>
-      <c r="L87" s="1">
-        <v>0</v>
-      </c>
-      <c r="M87" s="1">
-        <v>0</v>
-      </c>
-      <c r="N87" s="1">
-        <v>293.64838257128002</v>
-      </c>
-      <c r="O87" s="1">
-        <v>-12.35499539692</v>
-      </c>
-      <c r="P87" s="1">
-        <v>1655.31</v>
-      </c>
-      <c r="V87" s="1">
-        <v>10.977</v>
-      </c>
-      <c r="W87" s="1">
-        <v>12.571999999999999</v>
-      </c>
-      <c r="X87" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y87" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I88" s="2">
-        <v>5804</v>
-      </c>
-      <c r="J88" s="1">
-        <v>1.179</v>
-      </c>
-      <c r="K88" s="1">
-        <v>1.04</v>
-      </c>
-      <c r="L88" s="1">
-        <v>0</v>
-      </c>
-      <c r="M88" s="1">
-        <v>4.3121</v>
-      </c>
-      <c r="N88" s="1">
-        <v>274.86862255196002</v>
-      </c>
-      <c r="O88" s="1">
-        <v>5.3506741626599998</v>
-      </c>
-      <c r="P88" s="1">
-        <v>1644.4</v>
-      </c>
-      <c r="V88" s="1">
-        <v>15.965999999999999</v>
-      </c>
-      <c r="W88" s="1">
-        <v>16.86</v>
-      </c>
-      <c r="X88" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y88" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I89" s="2">
-        <v>5812</v>
-      </c>
-      <c r="J89" s="1">
-        <v>0.85599999999999998</v>
-      </c>
-      <c r="K89" s="1">
-        <v>1.0449999999999999</v>
-      </c>
-      <c r="L89" s="1">
-        <v>0</v>
-      </c>
-      <c r="M89" s="1">
-        <v>4.5917000000000003</v>
-      </c>
-      <c r="N89" s="1">
-        <v>47.805523543809997</v>
-      </c>
-      <c r="O89" s="1">
-        <v>-18.380477788619999</v>
-      </c>
-      <c r="P89" s="1">
-        <v>147.77799999999999</v>
-      </c>
-      <c r="V89" s="1">
-        <v>11.044</v>
-      </c>
-      <c r="W89" s="1">
-        <v>11.662000000000001</v>
-      </c>
-      <c r="X89" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y89" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I90" s="2">
-        <v>5815.4</v>
-      </c>
-      <c r="J90" s="1">
-        <v>4.2549999999999999</v>
-      </c>
-      <c r="K90" s="1">
-        <v>0</v>
-      </c>
-      <c r="L90" s="1">
-        <v>-0.19350000000000001</v>
-      </c>
-      <c r="M90" s="1">
-        <v>0</v>
-      </c>
-      <c r="N90" s="1">
-        <v>80.600252814719994</v>
-      </c>
-      <c r="O90" s="1">
-        <v>-68.64221652773</v>
-      </c>
-      <c r="P90" s="1">
-        <v>398.375</v>
-      </c>
-      <c r="V90" s="1">
-        <v>11.137</v>
-      </c>
-      <c r="W90" s="1">
-        <v>11.56</v>
-      </c>
-      <c r="X90" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y90" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I91" s="2">
-        <v>5799</v>
-      </c>
-      <c r="J91" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="K91" s="1">
-        <v>1.042</v>
-      </c>
-      <c r="L91" s="1">
-        <v>0</v>
-      </c>
-      <c r="M91" s="1">
-        <v>4.4642999999999997</v>
-      </c>
-      <c r="N91" s="1">
-        <v>278.21725113665002</v>
-      </c>
-      <c r="O91" s="1">
-        <v>11.92287820316</v>
-      </c>
-      <c r="P91" s="1">
-        <v>224.12799999999999</v>
-      </c>
-      <c r="V91" s="1">
-        <v>11.997</v>
-      </c>
-      <c r="W91" s="1">
-        <v>12.47</v>
-      </c>
-      <c r="X91" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y91" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I92" s="2">
-        <v>5806</v>
-      </c>
-      <c r="J92" s="1">
-        <v>27.986999999999998</v>
-      </c>
-      <c r="K92" s="1">
-        <v>0</v>
-      </c>
-      <c r="L92" s="1">
-        <v>0</v>
-      </c>
-      <c r="M92" s="1">
-        <v>0</v>
-      </c>
-      <c r="N92" s="1">
-        <v>278.48921850735002</v>
-      </c>
-      <c r="O92" s="1">
-        <v>31.640052119060002</v>
-      </c>
-      <c r="P92" s="1">
-        <v>7397.91</v>
-      </c>
-      <c r="V92" s="1">
-        <v>12.01</v>
-      </c>
-      <c r="W92" s="1">
-        <v>12.507</v>
-      </c>
-      <c r="X92" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y92" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I93" s="2">
-        <v>5775</v>
-      </c>
-      <c r="J93" s="1">
-        <v>5.1109999999999998</v>
-      </c>
-      <c r="K93" s="1">
-        <v>0</v>
-      </c>
-      <c r="L93" s="1">
-        <v>0</v>
-      </c>
-      <c r="M93" s="1">
-        <v>0</v>
-      </c>
-      <c r="N93" s="1">
-        <v>274.00302978329</v>
-      </c>
-      <c r="O93" s="1">
-        <v>22.9885348444</v>
-      </c>
-      <c r="P93" s="1">
-        <v>1802.37</v>
-      </c>
-      <c r="V93" s="1">
-        <v>12.961</v>
-      </c>
-      <c r="W93" s="1">
-        <v>14.082000000000001</v>
-      </c>
-      <c r="X93" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y93" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="I94" s="2">
-        <v>5800.4</v>
-      </c>
-      <c r="J94" s="1">
-        <v>1.4930000000000001</v>
-      </c>
-      <c r="K94" s="1">
-        <v>1.04</v>
-      </c>
-      <c r="L94" s="1">
-        <v>-6.6000000000000003E-2</v>
-      </c>
-      <c r="M94" s="1">
-        <v>4.1069000000000004</v>
-      </c>
-      <c r="N94" s="1">
-        <v>270.30880152526998</v>
-      </c>
-      <c r="O94" s="1">
-        <v>15.944626030029999</v>
-      </c>
-      <c r="P94" s="1">
-        <v>579.08500000000004</v>
-      </c>
-      <c r="V94" s="1">
-        <v>12.978999999999999</v>
-      </c>
-      <c r="W94" s="1">
-        <v>13.638999999999999</v>
-      </c>
-      <c r="X94" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y94" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="I95" s="2">
-        <v>5800</v>
-      </c>
-      <c r="J95" s="1">
-        <v>1.417</v>
-      </c>
-      <c r="K95" s="1">
-        <v>1.04</v>
-      </c>
-      <c r="L95" s="1">
-        <v>0</v>
-      </c>
-      <c r="M95" s="1">
-        <v>4.1520999999999999</v>
-      </c>
-      <c r="N95" s="1">
-        <v>280.34203579685999</v>
-      </c>
-      <c r="O95" s="1">
-        <v>26.315625519600001</v>
-      </c>
-      <c r="P95" s="1">
-        <v>897.52700000000004</v>
-      </c>
-      <c r="V95" s="1">
-        <v>13.994999999999999</v>
-      </c>
-      <c r="W95" s="1">
-        <v>14.913</v>
-      </c>
-      <c r="X95" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y95" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I96" s="2">
-        <v>5824</v>
-      </c>
-      <c r="J96" s="1">
-        <v>4.7249999999999996</v>
-      </c>
-      <c r="K96" s="1">
-        <v>0</v>
-      </c>
-      <c r="L96" s="1">
-        <v>0</v>
-      </c>
-      <c r="M96" s="1">
-        <v>0</v>
-      </c>
-      <c r="N96" s="1">
-        <v>284.95537150204001</v>
-      </c>
-      <c r="O96" s="1">
-        <v>14.42740619077</v>
-      </c>
-      <c r="P96" s="1">
-        <v>1961.4</v>
-      </c>
-      <c r="V96" s="1">
-        <v>14.023</v>
-      </c>
-      <c r="W96" s="1">
-        <v>15.048999999999999</v>
-      </c>
-      <c r="X96" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y96" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I97" s="2">
-        <v>5813</v>
-      </c>
-      <c r="J97" s="1">
-        <v>1.83</v>
-      </c>
-      <c r="K97" s="1">
-        <v>1.05</v>
-      </c>
-      <c r="L97" s="1">
-        <v>0</v>
-      </c>
-      <c r="M97" s="1">
-        <v>3.9344999999999999</v>
-      </c>
-      <c r="N97" s="1">
-        <v>270.99233637095</v>
-      </c>
-      <c r="O97" s="1">
-        <v>16.858729226019999</v>
-      </c>
-      <c r="P97" s="1">
-        <v>1779.6</v>
-      </c>
-      <c r="V97" s="1">
-        <v>14.999000000000001</v>
-      </c>
-      <c r="W97" s="1">
-        <v>15.66</v>
-      </c>
-      <c r="X97" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y97" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I98" s="2">
-        <v>5820</v>
-      </c>
-      <c r="J98" s="1">
-        <v>6.2519999999999998</v>
-      </c>
-      <c r="K98" s="1">
-        <v>0</v>
-      </c>
-      <c r="L98" s="1">
-        <v>0</v>
-      </c>
-      <c r="M98" s="1">
-        <v>0</v>
-      </c>
-      <c r="N98" s="1">
-        <v>267.97432727351003</v>
-      </c>
-      <c r="O98" s="1">
-        <v>17.507747521020001</v>
-      </c>
-      <c r="P98" s="1">
-        <v>6401.77</v>
-      </c>
-      <c r="V98" s="1">
-        <v>15.007999999999999</v>
-      </c>
-      <c r="W98" s="1">
-        <v>15.702999999999999</v>
-      </c>
-      <c r="X98" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y98" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I99" s="2">
-        <v>5800</v>
-      </c>
-      <c r="J99" s="1">
-        <v>1.3220000000000001</v>
-      </c>
-      <c r="K99" s="1">
-        <v>1.04</v>
-      </c>
-      <c r="L99" s="1">
-        <v>0</v>
-      </c>
-      <c r="M99" s="1">
-        <v>4.2129000000000003</v>
-      </c>
-      <c r="N99" s="1">
-        <v>270.95467601665001</v>
-      </c>
-      <c r="O99" s="1">
-        <v>3.9944008770699999</v>
-      </c>
-      <c r="P99" s="1">
-        <v>2963.53</v>
-      </c>
-      <c r="V99" s="1">
-        <v>17.052</v>
-      </c>
-      <c r="W99" s="1">
-        <v>17.364000000000001</v>
-      </c>
-      <c r="X99" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y99" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A100" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I100" s="2">
-        <v>5816</v>
-      </c>
-      <c r="J100" s="1">
-        <v>5.2939999999999996</v>
-      </c>
-      <c r="K100" s="1">
-        <v>0</v>
-      </c>
-      <c r="L100" s="1">
-        <v>0</v>
-      </c>
-      <c r="M100" s="1">
-        <v>0</v>
-      </c>
-      <c r="N100" s="1">
-        <v>284.79622244569998</v>
-      </c>
-      <c r="O100" s="1">
-        <v>15.987368865140001</v>
-      </c>
-      <c r="P100" s="1">
-        <v>3747.72</v>
-      </c>
-      <c r="V100" s="1">
-        <v>15.958</v>
-      </c>
-      <c r="W100" s="1">
-        <v>17.585999999999999</v>
-      </c>
-      <c r="X100" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y100" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A101" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I101" s="2">
-        <v>5792</v>
-      </c>
-      <c r="J101" s="1">
-        <v>0</v>
-      </c>
-      <c r="K101" s="1">
-        <v>0</v>
-      </c>
-      <c r="L101" s="1">
-        <v>0</v>
-      </c>
-      <c r="M101" s="1">
-        <v>0</v>
-      </c>
-      <c r="N101" s="1">
-        <v>276.67545984469001</v>
-      </c>
-      <c r="O101" s="1">
-        <v>14.0128749692</v>
-      </c>
-      <c r="P101" s="1">
-        <v>2046.66</v>
-      </c>
-      <c r="V101" s="1">
-        <v>17.097000000000001</v>
-      </c>
-      <c r="W101" s="1">
-        <v>18.082999999999998</v>
-      </c>
-      <c r="X101" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I102" s="2">
-        <v>3501</v>
-      </c>
-      <c r="J102" s="1">
-        <v>50.991</v>
-      </c>
-      <c r="K102" s="1">
-        <v>0</v>
-      </c>
-      <c r="L102" s="1">
-        <v>0</v>
-      </c>
-      <c r="M102" s="1">
-        <v>0</v>
-      </c>
-      <c r="N102" s="1">
-        <v>254.47763000024</v>
-      </c>
-      <c r="O102" s="1">
-        <v>-23.844465202550001</v>
-      </c>
-      <c r="P102" s="1">
-        <v>1025.1500000000001</v>
-      </c>
-      <c r="V102" s="1">
-        <v>11.035</v>
-      </c>
-      <c r="W102" s="1">
-        <v>12.885999999999999</v>
-      </c>
-      <c r="X102" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y102" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Y101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R79">
     <sortCondition ref="Q2"/>
   </sortState>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C94426-6C83-814D-9CC9-EC671FC572BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B881A896-45BB-BA41-9E4E-C494A8DADFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13260" yWindow="4480" windowWidth="29920" windowHeight="13340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="55200" yWindow="13200" windowWidth="19620" windowHeight="13340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -1495,6 +1495,9 @@
       <c r="P13">
         <v>2046.66</v>
       </c>
+      <c r="R13">
+        <v>16.870684000000001</v>
+      </c>
       <c r="V13">
         <v>17.097000000000001</v>
       </c>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B881A896-45BB-BA41-9E4E-C494A8DADFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B23092-5FBC-B647-9913-098037DAD8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55200" yWindow="13200" windowWidth="19620" windowHeight="13340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53100" yWindow="14040" windowWidth="19620" windowHeight="13340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$X$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$X$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="166">
   <si>
     <t>#pl_name</t>
   </si>
@@ -453,9 +453,6 @@
   </si>
   <si>
     <t>WASP-12 b</t>
-  </si>
-  <si>
-    <t>eps boo b</t>
   </si>
   <si>
     <t>HAT-P-32 b</t>
@@ -924,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC102"/>
+  <dimension ref="A1:BC101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -1028,18 +1025,18 @@
         <v>136</v>
       </c>
       <c r="V1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I2">
         <v>3501</v>
@@ -1072,7 +1069,7 @@
         <v>12.885999999999999</v>
       </c>
       <c r="X2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AZ2" s="3"/>
       <c r="BB2" s="3"/>
@@ -1080,7 +1077,7 @@
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I3">
         <v>3496</v>
@@ -1113,7 +1110,7 @@
         <v>12.571999999999999</v>
       </c>
       <c r="X3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AZ3" s="3"/>
       <c r="BB3" s="3"/>
@@ -1121,7 +1118,7 @@
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I4">
         <v>3460</v>
@@ -1154,7 +1151,7 @@
         <v>11.454000000000001</v>
       </c>
       <c r="X4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AZ4" s="3"/>
       <c r="BB4" s="3"/>
@@ -1162,7 +1159,7 @@
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I5">
         <v>5804</v>
@@ -1195,7 +1192,7 @@
         <v>16.86</v>
       </c>
       <c r="X5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AZ5" s="3"/>
       <c r="BB5" s="3"/>
@@ -1203,7 +1200,7 @@
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I6">
         <v>5800</v>
@@ -1236,7 +1233,7 @@
         <v>17.364000000000001</v>
       </c>
       <c r="X6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AZ6" s="3"/>
       <c r="BB6" s="3"/>
@@ -1244,7 +1241,7 @@
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I7">
         <v>5799</v>
@@ -1277,12 +1274,12 @@
         <v>12.47</v>
       </c>
       <c r="X7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I8">
         <v>5800.4</v>
@@ -1315,12 +1312,12 @@
         <v>13.638999999999999</v>
       </c>
       <c r="X8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I9">
         <v>5813</v>
@@ -1353,12 +1350,12 @@
         <v>15.66</v>
       </c>
       <c r="X9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I10">
         <v>5820</v>
@@ -1391,12 +1388,12 @@
         <v>15.702999999999999</v>
       </c>
       <c r="X10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I11">
         <v>5824</v>
@@ -1429,12 +1426,12 @@
         <v>15.048999999999999</v>
       </c>
       <c r="X11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I12">
         <v>5816</v>
@@ -1467,12 +1464,12 @@
         <v>17.585999999999999</v>
       </c>
       <c r="X12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I13">
         <v>5792</v>
@@ -1507,7 +1504,7 @@
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I14">
         <v>5775</v>
@@ -1540,12 +1537,12 @@
         <v>14.082000000000001</v>
       </c>
       <c r="X14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I15">
         <v>5800</v>
@@ -1578,12 +1575,12 @@
         <v>14.913</v>
       </c>
       <c r="X15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I16">
         <v>5806</v>
@@ -1616,12 +1613,12 @@
         <v>12.507</v>
       </c>
       <c r="X16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I17">
         <v>5815.4</v>
@@ -1654,12 +1651,12 @@
         <v>11.56</v>
       </c>
       <c r="X17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I18">
         <v>5812</v>
@@ -1692,87 +1689,131 @@
         <v>11.662000000000001</v>
       </c>
       <c r="X18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>4.4652997599999997</v>
+      </c>
+      <c r="D19">
+        <v>5.561E-2</v>
+      </c>
+      <c r="E19">
+        <v>1.319</v>
+      </c>
+      <c r="F19">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="G19">
+        <v>1322</v>
+      </c>
+      <c r="H19" t="s">
+        <v>27</v>
       </c>
       <c r="I19">
-        <v>4907.77490234375</v>
+        <v>5980</v>
+      </c>
+      <c r="J19">
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="K19">
+        <v>1.151</v>
+      </c>
+      <c r="L19">
+        <v>0.13</v>
+      </c>
+      <c r="M19">
+        <v>4.359</v>
       </c>
       <c r="N19">
-        <v>221.24648617076679</v>
+        <v>344.44536319999997</v>
       </c>
       <c r="O19">
-        <v>27.074315757773469</v>
+        <v>38.674919000000003</v>
+      </c>
+      <c r="P19">
+        <v>158.97900000000001</v>
       </c>
       <c r="Q19">
-        <v>2.1833524703979492</v>
+        <v>9.827</v>
       </c>
       <c r="R19">
-        <v>2.1833524703979492</v>
+        <v>10.178599999999999</v>
+      </c>
+      <c r="S19">
+        <f>(0.000000000000000138*G19/(1.673534E-24*1.3*0.000000066726*F19*1.8986E+30/(E19*7149200000)^2))/100000</f>
+        <v>1121.1126749906216</v>
+      </c>
+      <c r="T19">
+        <f>IF(I19&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
       <c r="C20">
-        <v>4.4652997599999997</v>
+        <v>4.6276700000000002</v>
       </c>
       <c r="D20">
-        <v>5.561E-2</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E20">
-        <v>1.319</v>
+        <v>1.42</v>
       </c>
       <c r="F20">
-        <v>0.52500000000000002</v>
+        <v>3.44</v>
       </c>
       <c r="G20">
-        <v>1322</v>
+        <v>1624</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="I20">
-        <v>5980</v>
+        <v>6600</v>
       </c>
       <c r="J20">
-        <v>1.1739999999999999</v>
+        <v>1.82</v>
       </c>
       <c r="K20">
-        <v>1.151</v>
+        <v>2.65</v>
       </c>
       <c r="L20">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="M20">
-        <v>4.359</v>
+        <v>4.25</v>
       </c>
       <c r="N20">
-        <v>344.44536319999997</v>
+        <v>260.11617189999998</v>
       </c>
       <c r="O20">
-        <v>38.674919000000003</v>
+        <v>38.242168200000002</v>
       </c>
       <c r="P20">
-        <v>158.97900000000001</v>
+        <v>222.66300000000001</v>
       </c>
       <c r="Q20">
-        <v>9.827</v>
+        <v>9.9879999999999995</v>
       </c>
       <c r="R20">
-        <v>10.178599999999999</v>
+        <v>9.8728300000000004</v>
       </c>
       <c r="S20">
         <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
-        <v>1121.1126749906216</v>
+        <v>243.60813720463176</v>
       </c>
       <c r="T20">
         <f>IF(I20&gt;6800,-7,-5)</f>
@@ -1781,62 +1822,62 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
       </c>
       <c r="C21">
-        <v>4.6276700000000002</v>
+        <v>5.6335157999999996</v>
       </c>
       <c r="D21">
-        <v>5.96E-2</v>
+        <v>6.8140000000000006E-2</v>
       </c>
       <c r="E21">
-        <v>1.42</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="F21">
-        <v>3.44</v>
+        <v>9.02</v>
       </c>
       <c r="G21">
-        <v>1624</v>
+        <v>1540</v>
       </c>
       <c r="H21" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="I21">
-        <v>6600</v>
+        <v>6380</v>
       </c>
       <c r="J21">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="K21">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="L21">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="M21">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="N21">
-        <v>260.11617189999998</v>
+        <v>245.1514324</v>
       </c>
       <c r="O21">
-        <v>38.242168200000002</v>
+        <v>41.047960099999997</v>
       </c>
       <c r="P21">
-        <v>222.66300000000001</v>
+        <v>127.774</v>
       </c>
       <c r="Q21">
-        <v>9.9879999999999995</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="R21">
-        <v>9.8728300000000004</v>
+        <v>8.5984200000000008</v>
       </c>
       <c r="S21">
         <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
-        <v>243.60813720463176</v>
+        <v>39.515068300859213</v>
       </c>
       <c r="T21">
         <f>IF(I21&gt;6800,-7,-5)</f>
@@ -1845,62 +1886,62 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22">
-        <v>5.6335157999999996</v>
+        <v>3.2122199999999999</v>
       </c>
       <c r="D22">
-        <v>6.8140000000000006E-2</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="E22">
-        <v>0.95099999999999996</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F22">
-        <v>9.02</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="G22">
-        <v>1540</v>
+        <v>1463</v>
       </c>
       <c r="H22" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="I22">
-        <v>6380</v>
+        <v>5302</v>
       </c>
       <c r="J22">
-        <v>1.39</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="K22">
-        <v>1.33</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="L22">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="M22">
-        <v>4.16</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N22">
-        <v>245.1514324</v>
+        <v>155.6814593</v>
       </c>
       <c r="O22">
-        <v>41.047960099999997</v>
+        <v>50.128711500000001</v>
       </c>
       <c r="P22">
-        <v>127.774</v>
+        <v>81.764700000000005</v>
       </c>
       <c r="Q22">
-        <v>8.7200000000000006</v>
+        <v>9.7629999999999999</v>
       </c>
       <c r="R22">
-        <v>8.5984200000000008</v>
+        <v>9.5193600000000007</v>
       </c>
       <c r="S22">
         <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
-        <v>39.515068300859213</v>
+        <v>200.46131426194896</v>
       </c>
       <c r="T22">
         <f>IF(I22&gt;6800,-7,-5)</f>
@@ -1909,364 +1950,364 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23">
-        <v>3.2122199999999999</v>
-      </c>
-      <c r="D23">
-        <v>4.1399999999999999E-2</v>
-      </c>
-      <c r="E23">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F23">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="G23">
-        <v>1463</v>
-      </c>
-      <c r="H23" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="I23">
-        <v>5302</v>
+        <v>6245.11328125</v>
       </c>
       <c r="J23">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="K23">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="L23">
-        <v>0.24</v>
+        <v>1.208241820335388</v>
       </c>
       <c r="M23">
-        <v>4.3600000000000003</v>
+        <v>4.2744002342224121</v>
       </c>
       <c r="N23">
-        <v>155.6814593</v>
+        <v>31.04275939878713</v>
       </c>
       <c r="O23">
-        <v>50.128711500000001</v>
+        <v>46.687851647860192</v>
       </c>
       <c r="P23">
-        <v>81.764700000000005</v>
+        <v>283.38339999999999</v>
       </c>
       <c r="Q23">
-        <v>9.7629999999999999</v>
+        <v>11.12930202484131</v>
       </c>
       <c r="R23">
-        <v>9.5193600000000007</v>
-      </c>
-      <c r="S23">
-        <f>(0.000000000000000138*G23/(1.673534E-24*1.3*0.000000066726*F23*1.8986E+30/(E23*7149200000)^2))/100000</f>
-        <v>200.46131426194896</v>
-      </c>
-      <c r="T23">
-        <f>IF(I23&gt;6800,-7,-5)</f>
-        <v>-5</v>
-      </c>
+        <v>11.12930202484131</v>
+      </c>
+      <c r="V23" s="4"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>4.7947813000000004</v>
+      </c>
+      <c r="D24">
+        <v>6.2770000000000006E-2</v>
+      </c>
+      <c r="E24">
+        <v>1.631</v>
+      </c>
+      <c r="F24">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="G24">
+        <v>1772</v>
       </c>
       <c r="I24">
-        <v>6245.11328125</v>
+        <v>6212</v>
       </c>
       <c r="J24">
-        <v>1.208241820335388</v>
+        <v>2.1970000000000001</v>
+      </c>
+      <c r="K24">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="L24">
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="M24">
-        <v>4.2744002342224121</v>
+        <v>3.9114</v>
       </c>
       <c r="N24">
-        <v>31.04275939878713</v>
+        <v>28.282571900000001</v>
       </c>
       <c r="O24">
-        <v>46.687851647860192</v>
+        <v>52.053920900000001</v>
       </c>
       <c r="P24">
-        <v>283.38339999999999</v>
+        <v>233.22</v>
       </c>
       <c r="Q24">
-        <v>11.12930202484131</v>
+        <v>9.7270000000000003</v>
       </c>
       <c r="R24">
-        <v>11.12930202484131</v>
+        <v>9.5635499999999993</v>
+      </c>
+      <c r="S24">
+        <f>(0.000000000000000138*G24/(1.673534E-24*1.3*0.000000066726*F24*1.8986E+30/(E24*7149200000)^2))/100000</f>
+        <v>2101.5864855136347</v>
+      </c>
+      <c r="T24">
+        <f>IF(I24&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
       <c r="V24" s="4"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
       </c>
       <c r="C25">
-        <v>4.7947813000000004</v>
+        <v>4.7869491000000002</v>
       </c>
       <c r="D25">
-        <v>6.2770000000000006E-2</v>
+        <v>6.5549999999999997E-2</v>
       </c>
       <c r="E25">
-        <v>1.631</v>
+        <v>1.6759999999999999</v>
       </c>
       <c r="F25">
-        <v>0.57399999999999995</v>
+        <v>3.58</v>
       </c>
       <c r="G25">
-        <v>1772</v>
+        <v>1930</v>
       </c>
       <c r="I25">
-        <v>6212</v>
+        <v>7394</v>
       </c>
       <c r="J25">
-        <v>2.1970000000000001</v>
+        <v>1.9259999999999999</v>
       </c>
       <c r="K25">
-        <v>1.4350000000000001</v>
+        <v>1.6479999999999999</v>
       </c>
       <c r="L25">
-        <v>3.6999999999999998E-2</v>
+        <v>-6.9000000000000006E-2</v>
       </c>
       <c r="M25">
-        <v>3.9114</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="N25">
-        <v>28.282571900000001</v>
+        <v>130.5056385</v>
       </c>
       <c r="O25">
-        <v>52.053920900000001</v>
+        <v>3.7105662000000001</v>
       </c>
       <c r="P25">
-        <v>233.22</v>
+        <v>341.26299999999998</v>
       </c>
       <c r="Q25">
-        <v>9.7270000000000003</v>
+        <v>9.7739999999999991</v>
       </c>
       <c r="R25">
-        <v>9.5635499999999993</v>
+        <v>9.77332</v>
       </c>
       <c r="S25">
         <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
-        <v>2101.5864855136347</v>
+        <v>387.53401759458865</v>
       </c>
       <c r="T25">
         <f>IF(I25&gt;6800,-7,-5)</f>
-        <v>-5</v>
-      </c>
-      <c r="V25" s="4"/>
+        <v>-7</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26">
-        <v>4.7869491000000002</v>
-      </c>
-      <c r="D26">
-        <v>6.5549999999999997E-2</v>
-      </c>
-      <c r="E26">
-        <v>1.6759999999999999</v>
-      </c>
-      <c r="F26">
-        <v>3.58</v>
-      </c>
-      <c r="G26">
-        <v>1930</v>
+        <v>140</v>
       </c>
       <c r="I26">
-        <v>7394</v>
+        <v>6424.27685546875</v>
       </c>
       <c r="J26">
-        <v>1.9259999999999999</v>
-      </c>
-      <c r="K26">
-        <v>1.6479999999999999</v>
-      </c>
-      <c r="L26">
-        <v>-6.9000000000000006E-2</v>
-      </c>
-      <c r="M26">
-        <v>4.1100000000000003</v>
+        <v>2.0702402591705318</v>
       </c>
       <c r="N26">
-        <v>130.5056385</v>
+        <v>292.24718620018581</v>
       </c>
       <c r="O26">
-        <v>3.7105662000000001</v>
-      </c>
-      <c r="P26">
-        <v>341.26299999999998</v>
+        <v>47.969544064101818</v>
       </c>
       <c r="Q26">
-        <v>9.7739999999999991</v>
+        <v>10.36768245697021</v>
       </c>
       <c r="R26">
-        <v>9.77332</v>
-      </c>
-      <c r="S26">
-        <f>(0.000000000000000138*G26/(1.673534E-24*1.3*0.000000066726*F26*1.8986E+30/(E26*7149200000)^2))/100000</f>
-        <v>387.53401759458865</v>
-      </c>
-      <c r="T26">
-        <f>IF(I26&gt;6800,-7,-5)</f>
-        <v>-7</v>
+        <v>10.36768245697021</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>2.7443245200000002</v>
+      </c>
+      <c r="D27">
+        <v>4.7390000000000002E-2</v>
+      </c>
+      <c r="E27">
+        <v>1.87</v>
+      </c>
+      <c r="F27">
+        <v>6.78</v>
+      </c>
+      <c r="G27">
+        <v>2562</v>
       </c>
       <c r="I27">
-        <v>6424.27685546875</v>
+        <v>8450</v>
       </c>
       <c r="J27">
-        <v>2.0702402591705318</v>
+        <v>1.8580000000000001</v>
+      </c>
+      <c r="K27">
+        <v>1.89</v>
+      </c>
+      <c r="L27">
+        <v>-5.8999999999999997E-2</v>
+      </c>
+      <c r="M27">
+        <v>4.181</v>
       </c>
       <c r="N27">
-        <v>292.24718620018581</v>
+        <v>74.552333200000007</v>
       </c>
       <c r="O27">
-        <v>47.969544064101818</v>
+        <v>9.9979794000000002</v>
+      </c>
+      <c r="P27">
+        <v>330.73899999999998</v>
       </c>
       <c r="Q27">
-        <v>10.36768245697021</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="R27">
-        <v>10.36768245697021</v>
-      </c>
+        <v>9.4517399999999991</v>
+      </c>
+      <c r="S27">
+        <f t="shared" ref="S27:S51" si="0">(0.000000000000000138*G27/(1.673534E-24*1.3*0.000000066726*F27*1.8986E+30/(E27*7149200000)^2))/100000</f>
+        <v>338.15838787809196</v>
+      </c>
+      <c r="T27">
+        <f t="shared" ref="T27:T50" si="1">IF(I27&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
+      <c r="V27" s="4"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>2.7443245200000002</v>
+        <v>6.1349779</v>
       </c>
       <c r="D28">
-        <v>4.7390000000000002E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="E28">
-        <v>1.87</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F28">
-        <v>6.78</v>
+        <v>2.14</v>
       </c>
       <c r="G28">
-        <v>2562</v>
+        <v>1361</v>
+      </c>
+      <c r="H28" t="s">
+        <v>39</v>
       </c>
       <c r="I28">
-        <v>8450</v>
+        <v>5742</v>
       </c>
       <c r="J28">
-        <v>1.8580000000000001</v>
+        <v>2.04</v>
       </c>
       <c r="K28">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="L28">
-        <v>-5.8999999999999997E-2</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="M28">
-        <v>4.181</v>
+        <v>3.92</v>
       </c>
       <c r="N28">
-        <v>74.552333200000007</v>
+        <v>203.50995599999999</v>
       </c>
       <c r="O28">
-        <v>9.9979794000000002</v>
+        <v>53.728187599999998</v>
       </c>
       <c r="P28">
-        <v>330.73899999999998</v>
+        <v>92.258899999999997</v>
       </c>
       <c r="Q28">
-        <v>9.4700000000000006</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="R28">
-        <v>9.4517399999999991</v>
+        <v>7.89255</v>
       </c>
       <c r="S28">
-        <f t="shared" ref="S28:S52" si="0">(0.000000000000000138*G28/(1.673534E-24*1.3*0.000000066726*F28*1.8986E+30/(E28*7149200000)^2))/100000</f>
-        <v>338.15838787809196</v>
+        <f t="shared" si="0"/>
+        <v>211.51519610586323</v>
       </c>
       <c r="T28">
-        <f t="shared" ref="T28:T51" si="1">IF(I28&gt;6800,-7,-5)</f>
-        <v>-7</v>
-      </c>
-      <c r="V28" s="4"/>
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C29">
-        <v>6.1349779</v>
+        <v>11.53533</v>
       </c>
       <c r="D29">
-        <v>7.1300000000000002E-2</v>
+        <v>0.10970000000000001</v>
       </c>
       <c r="E29">
-        <v>1.1399999999999999</v>
+        <v>1.026</v>
       </c>
       <c r="F29">
-        <v>2.14</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="G29">
-        <v>1361</v>
+        <v>1228.3</v>
       </c>
       <c r="H29" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I29">
-        <v>5742</v>
+        <v>5521</v>
       </c>
       <c r="J29">
-        <v>2.04</v>
+        <v>2.3359999999999999</v>
       </c>
       <c r="K29">
-        <v>1.27</v>
+        <v>1.3240000000000001</v>
       </c>
       <c r="L29">
-        <v>0.28699999999999998</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M29">
-        <v>3.92</v>
+        <v>3.823</v>
       </c>
       <c r="N29">
-        <v>203.50995599999999</v>
+        <v>4.4471631</v>
       </c>
       <c r="O29">
-        <v>53.728187599999998</v>
+        <v>-66.358928500000005</v>
       </c>
       <c r="P29">
-        <v>92.258899999999997</v>
+        <v>79.5702</v>
       </c>
       <c r="Q29">
-        <v>8.0500000000000007</v>
+        <v>7.79</v>
       </c>
       <c r="R29">
-        <v>7.89255</v>
+        <v>7.5933599999999997</v>
       </c>
       <c r="S29">
         <f t="shared" si="0"/>
-        <v>211.51519610586323</v>
+        <v>797.33090232058362</v>
       </c>
       <c r="T29">
         <f t="shared" si="1"/>
@@ -2275,1210 +2316,1207 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C30">
-        <v>11.53533</v>
+        <v>2.8758900000000001</v>
       </c>
       <c r="D30">
-        <v>0.10970000000000001</v>
+        <v>4.3639999999999998E-2</v>
       </c>
       <c r="E30">
-        <v>1.026</v>
+        <v>0.74</v>
       </c>
       <c r="F30">
-        <v>0.41499999999999998</v>
+        <v>0.38</v>
       </c>
       <c r="G30">
-        <v>1228.3</v>
+        <v>1626</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I30">
-        <v>5521</v>
+        <v>6179</v>
       </c>
       <c r="J30">
-        <v>2.3359999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="K30">
-        <v>1.3240000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="L30">
-        <v>0.28999999999999998</v>
+        <v>0.32</v>
       </c>
       <c r="M30">
-        <v>3.823</v>
+        <v>4.37</v>
       </c>
       <c r="N30">
-        <v>4.4471631</v>
+        <v>247.62298269999999</v>
       </c>
       <c r="O30">
-        <v>-66.358928500000005</v>
+        <v>38.347534899999999</v>
       </c>
       <c r="P30">
-        <v>79.5702</v>
+        <v>75.8643</v>
       </c>
       <c r="Q30">
-        <v>7.79</v>
+        <v>8.15</v>
       </c>
       <c r="R30">
-        <v>7.5933599999999997</v>
+        <v>8.0141600000000004</v>
       </c>
       <c r="S30">
         <f t="shared" si="0"/>
-        <v>797.33090232058362</v>
+        <v>599.63628364223177</v>
       </c>
       <c r="T30">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
+      <c r="V30" s="4"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C31">
-        <v>2.8758900000000001</v>
+        <v>19.502103999999999</v>
       </c>
       <c r="D31">
-        <v>4.3639999999999998E-2</v>
+        <v>0.1482</v>
       </c>
       <c r="E31">
-        <v>0.74</v>
+        <v>0.52993221999999995</v>
       </c>
       <c r="F31">
-        <v>0.38</v>
+        <v>3.0425219999999999E-2</v>
       </c>
       <c r="G31">
-        <v>1626</v>
+        <v>253.08</v>
       </c>
       <c r="H31" t="s">
         <v>43</v>
       </c>
       <c r="I31">
-        <v>6179</v>
+        <v>6310</v>
       </c>
       <c r="J31">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="K31">
-        <v>1.42</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="L31">
-        <v>0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="M31">
-        <v>4.37</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N31">
-        <v>247.62298269999999</v>
+        <v>253.78488530000001</v>
       </c>
       <c r="O31">
-        <v>38.347534899999999</v>
+        <v>20.491523999999998</v>
       </c>
       <c r="P31">
-        <v>75.8643</v>
+        <v>107.898</v>
       </c>
       <c r="Q31">
-        <v>8.15</v>
+        <v>8.8550000000000004</v>
       </c>
       <c r="R31">
-        <v>8.0141600000000004</v>
+        <v>8.7641200000000001</v>
       </c>
       <c r="S31">
         <f t="shared" si="0"/>
-        <v>599.63628364223177</v>
+        <v>597.79498778467087</v>
       </c>
       <c r="T31">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V31" s="4"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C32">
-        <v>19.502103999999999</v>
+        <v>2.2185756699999999</v>
       </c>
       <c r="D32">
-        <v>0.1482</v>
+        <v>3.1260000000000003E-2</v>
       </c>
       <c r="E32">
-        <v>0.52993221999999995</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F32">
-        <v>3.0425219999999999E-2</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="G32">
-        <v>253.08</v>
+        <v>1209</v>
       </c>
       <c r="H32" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I32">
-        <v>6310</v>
+        <v>5052</v>
       </c>
       <c r="J32">
-        <v>1.43</v>
+        <v>0.75</v>
       </c>
       <c r="K32">
-        <v>1.1499999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="L32">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="M32">
-        <v>4.1900000000000004</v>
+        <v>4.49</v>
       </c>
       <c r="N32">
-        <v>253.78488530000001</v>
+        <v>300.1821223</v>
       </c>
       <c r="O32">
-        <v>20.491523999999998</v>
+        <v>22.7097759</v>
       </c>
       <c r="P32">
-        <v>107.898</v>
+        <v>19.7638</v>
       </c>
       <c r="Q32">
-        <v>8.8550000000000004</v>
+        <v>7.67</v>
       </c>
       <c r="R32">
-        <v>8.7641200000000001</v>
+        <v>7.41432</v>
       </c>
       <c r="S32">
         <f t="shared" si="0"/>
-        <v>597.79498778467087</v>
+        <v>349.61677638948368</v>
       </c>
       <c r="T32">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V32" s="4"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C33">
-        <v>2.2185756699999999</v>
+        <v>3.3089580000000001</v>
       </c>
       <c r="D33">
-        <v>3.1260000000000003E-2</v>
+        <v>5.2080000000000001E-2</v>
       </c>
       <c r="E33">
-        <v>1.1299999999999999</v>
+        <v>1.5449999999999999</v>
       </c>
       <c r="F33">
-        <v>1.1299999999999999</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="G33">
-        <v>1209</v>
-      </c>
-      <c r="H33" t="s">
-        <v>29</v>
+        <v>2132</v>
       </c>
       <c r="I33">
-        <v>5052</v>
+        <v>6272</v>
       </c>
       <c r="J33">
-        <v>0.75</v>
+        <v>2.5910000000000002</v>
       </c>
       <c r="K33">
-        <v>0.79</v>
+        <v>1.72</v>
       </c>
       <c r="L33">
-        <v>-0.02</v>
+        <v>0.3</v>
       </c>
       <c r="M33">
-        <v>4.49</v>
+        <v>3.8479999999999999</v>
       </c>
       <c r="N33">
-        <v>300.1821223</v>
+        <v>319.6995877</v>
       </c>
       <c r="O33">
-        <v>22.7097759</v>
+        <v>-26.6163743</v>
       </c>
       <c r="P33">
-        <v>19.7638</v>
+        <v>161.49799999999999</v>
       </c>
       <c r="Q33">
-        <v>7.67</v>
+        <v>8.3239999999999998</v>
       </c>
       <c r="R33">
-        <v>7.41432</v>
+        <v>8.2268799999999995</v>
       </c>
       <c r="S33">
         <f t="shared" si="0"/>
-        <v>349.61677638948368</v>
+        <v>1280.5918535006856</v>
       </c>
       <c r="T33">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V33" s="4"/>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C34">
-        <v>3.3089580000000001</v>
+        <v>3.5247485900000002</v>
       </c>
       <c r="D34">
-        <v>5.2080000000000001E-2</v>
+        <v>4.7070000000000001E-2</v>
       </c>
       <c r="E34">
-        <v>1.5449999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="F34">
-        <v>1.0169999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="G34">
-        <v>2132</v>
+        <v>1459</v>
+      </c>
+      <c r="H34" t="s">
+        <v>27</v>
       </c>
       <c r="I34">
-        <v>6272</v>
+        <v>6091</v>
       </c>
       <c r="J34">
-        <v>2.5910000000000002</v>
+        <v>1.19</v>
       </c>
       <c r="K34">
-        <v>1.72</v>
+        <v>1.23</v>
       </c>
       <c r="L34">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="M34">
-        <v>3.8479999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="N34">
-        <v>319.6995877</v>
+        <v>330.79502189999999</v>
       </c>
       <c r="O34">
-        <v>-26.6163743</v>
+        <v>18.884241899999999</v>
       </c>
       <c r="P34">
-        <v>161.49799999999999</v>
+        <v>48.301600000000001</v>
       </c>
       <c r="Q34">
-        <v>8.3239999999999998</v>
+        <v>7.65</v>
       </c>
       <c r="R34">
-        <v>8.2268799999999995</v>
-      </c>
-      <c r="S34">
+        <v>7.5086599999999999</v>
+      </c>
+      <c r="S34" s="5">
         <f t="shared" si="0"/>
-        <v>1280.5918535006856</v>
+        <v>988.21070019970352</v>
       </c>
       <c r="T34">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C35">
-        <v>3.5247485900000002</v>
+        <v>6.0344680000000004</v>
       </c>
       <c r="D35">
-        <v>4.7070000000000001E-2</v>
+        <v>6.3560000000000005E-2</v>
       </c>
       <c r="E35">
-        <v>1.39</v>
+        <v>0.437</v>
       </c>
       <c r="F35">
-        <v>0.73</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G35">
-        <v>1459</v>
+        <v>1076</v>
       </c>
       <c r="H35" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="I35">
-        <v>6091</v>
+        <v>5540</v>
       </c>
       <c r="J35">
-        <v>1.19</v>
+        <v>1.0589999999999999</v>
       </c>
       <c r="K35">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="L35">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="M35">
-        <v>4.45</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N35">
-        <v>330.79502189999999</v>
+        <v>349.55926649999998</v>
       </c>
       <c r="O35">
-        <v>18.884241899999999</v>
+        <v>-56.9039857</v>
       </c>
       <c r="P35">
-        <v>48.301600000000001</v>
+        <v>94.171899999999994</v>
       </c>
       <c r="Q35">
-        <v>7.65</v>
+        <v>9.8089999999999993</v>
       </c>
       <c r="R35">
-        <v>7.5086599999999999</v>
-      </c>
-      <c r="S35" s="5">
+        <v>9.6495599999999992</v>
+      </c>
+      <c r="S35">
         <f t="shared" si="0"/>
-        <v>988.21070019970352</v>
+        <v>956.09264119622901</v>
       </c>
       <c r="T35">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
         <v>20</v>
       </c>
       <c r="C36">
-        <v>6.0344680000000004</v>
+        <v>14.2767</v>
       </c>
       <c r="D36">
-        <v>6.3560000000000005E-2</v>
+        <v>0.12280000000000001</v>
       </c>
       <c r="E36">
-        <v>0.437</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="F36">
-        <v>5.5E-2</v>
+        <v>0.19</v>
       </c>
       <c r="G36">
-        <v>1076</v>
+        <v>789.15</v>
       </c>
       <c r="H36" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="I36">
-        <v>5540</v>
+        <v>5080</v>
       </c>
       <c r="J36">
-        <v>1.0589999999999999</v>
+        <v>2.9430000000000001</v>
       </c>
       <c r="K36">
-        <v>1.02</v>
+        <v>1.212</v>
       </c>
       <c r="L36">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="M36">
-        <v>4.4000000000000004</v>
+        <v>3.5840000000000001</v>
       </c>
       <c r="N36">
-        <v>349.55926649999998</v>
+        <v>353.03318630000001</v>
       </c>
       <c r="O36">
-        <v>-56.9039857</v>
+        <v>-21.801200699999999</v>
       </c>
       <c r="P36">
-        <v>94.171899999999994</v>
+        <v>95.548299999999998</v>
       </c>
       <c r="Q36">
-        <v>9.8089999999999993</v>
+        <v>8.15</v>
       </c>
       <c r="R36">
-        <v>9.6495599999999992</v>
+        <v>7.9077599999999997</v>
       </c>
       <c r="S36">
         <f t="shared" si="0"/>
-        <v>956.09264119622901</v>
+        <v>742.8583931109747</v>
       </c>
       <c r="T36">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
         <v>20</v>
       </c>
       <c r="C37">
-        <v>14.2767</v>
+        <v>4.1268799999999999</v>
       </c>
       <c r="D37">
-        <v>0.12280000000000001</v>
+        <v>5.6800000000000003E-2</v>
       </c>
       <c r="E37">
-        <v>0.83599999999999997</v>
+        <v>1.44</v>
       </c>
       <c r="F37">
-        <v>0.19</v>
+        <v>1.17</v>
       </c>
       <c r="G37">
-        <v>789.15</v>
-      </c>
-      <c r="H37" t="s">
-        <v>45</v>
+        <v>2061</v>
       </c>
       <c r="I37">
-        <v>5080</v>
+        <v>6801</v>
       </c>
       <c r="J37">
-        <v>2.9430000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="K37">
-        <v>1.212</v>
+        <v>1.43</v>
       </c>
       <c r="L37">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="M37">
-        <v>3.5840000000000001</v>
+        <v>4.21</v>
       </c>
       <c r="N37">
-        <v>353.03318630000001</v>
+        <v>7.3289156000000002</v>
       </c>
       <c r="O37">
-        <v>-21.801200699999999</v>
+        <v>-76.304032000000007</v>
       </c>
       <c r="P37">
-        <v>95.548299999999998</v>
+        <v>196.852</v>
       </c>
       <c r="Q37">
-        <v>8.15</v>
+        <v>9.5950000000000006</v>
       </c>
       <c r="R37">
-        <v>7.9077599999999997</v>
+        <v>9.5202500000000008</v>
       </c>
       <c r="S37">
         <f t="shared" si="0"/>
-        <v>742.8583931109747</v>
+        <v>934.76971602454307</v>
       </c>
       <c r="T37">
         <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-7</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
       </c>
       <c r="C38">
-        <v>4.1268799999999999</v>
+        <v>18.712024</v>
       </c>
       <c r="D38">
-        <v>5.6800000000000003E-2</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E38">
-        <v>1.44</v>
+        <v>0.80944318999999998</v>
       </c>
       <c r="F38">
-        <v>1.17</v>
+        <v>0.23314467</v>
       </c>
       <c r="G38">
-        <v>2061</v>
+        <v>798.3</v>
+      </c>
+      <c r="H38" t="s">
+        <v>54</v>
       </c>
       <c r="I38">
-        <v>6801</v>
+        <v>6128</v>
       </c>
       <c r="J38">
-        <v>1.56</v>
+        <v>1.266</v>
       </c>
       <c r="K38">
-        <v>1.43</v>
+        <v>1.1641999999999999</v>
       </c>
       <c r="L38">
-        <v>0.02</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="M38">
-        <v>4.21</v>
+        <v>4.2960000000000003</v>
       </c>
       <c r="N38">
-        <v>7.3289156000000002</v>
+        <v>306.74113399999999</v>
       </c>
       <c r="O38">
-        <v>-76.304032000000007</v>
+        <v>33.744388200000003</v>
       </c>
       <c r="P38">
-        <v>196.852</v>
+        <v>80.666499999999999</v>
       </c>
       <c r="Q38">
-        <v>9.5950000000000006</v>
+        <v>8.5579999999999998</v>
       </c>
       <c r="R38">
-        <v>9.5202500000000008</v>
+        <v>8.4183900000000005</v>
       </c>
       <c r="S38">
         <f t="shared" si="0"/>
-        <v>934.76971602454307</v>
+        <v>574.11765847468712</v>
       </c>
       <c r="T38">
         <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C39">
-        <v>18.712024</v>
+        <v>3.4148839999999998</v>
       </c>
       <c r="D39">
-        <v>0.14499999999999999</v>
+        <v>4.7899999999999998E-2</v>
       </c>
       <c r="E39">
-        <v>0.80944318999999998</v>
+        <v>1.23</v>
       </c>
       <c r="F39">
-        <v>0.23314467</v>
+        <v>1.02</v>
       </c>
       <c r="G39">
-        <v>798.3</v>
+        <v>1762</v>
       </c>
       <c r="H39" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I39">
-        <v>6128</v>
+        <v>5392</v>
       </c>
       <c r="J39">
-        <v>1.266</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K39">
-        <v>1.1641999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="L39">
-        <v>4.2999999999999997E-2</v>
+        <v>0.34</v>
       </c>
       <c r="M39">
-        <v>4.2960000000000003</v>
+        <v>3.88</v>
       </c>
       <c r="N39">
-        <v>306.74113399999999</v>
+        <v>152.53193490000001</v>
       </c>
       <c r="O39">
-        <v>33.744388200000003</v>
+        <v>18.185728399999999</v>
       </c>
       <c r="P39">
-        <v>80.666499999999999</v>
+        <v>73.612300000000005</v>
       </c>
       <c r="Q39">
-        <v>8.5579999999999998</v>
+        <v>8.0185200000000005</v>
       </c>
       <c r="R39">
-        <v>8.4183900000000005</v>
+        <v>7.8097899999999996</v>
       </c>
       <c r="S39">
         <f t="shared" si="0"/>
-        <v>574.11765847468712</v>
+        <v>668.81110409377118</v>
       </c>
       <c r="T39">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C40">
-        <v>3.4148839999999998</v>
+        <v>11.814299999999999</v>
       </c>
       <c r="D40">
-        <v>4.7899999999999998E-2</v>
+        <v>0.1066</v>
       </c>
       <c r="E40">
-        <v>1.23</v>
+        <v>0.66</v>
       </c>
       <c r="F40">
-        <v>1.02</v>
+        <v>0.11</v>
       </c>
       <c r="G40">
-        <v>1762</v>
+        <v>1089</v>
       </c>
       <c r="H40" t="s">
         <v>33</v>
       </c>
       <c r="I40">
-        <v>5392</v>
+        <v>5576</v>
       </c>
       <c r="J40">
-        <v>2.2000000000000002</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="K40">
-        <v>1.26</v>
+        <v>1.157</v>
       </c>
       <c r="L40">
-        <v>0.34</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="M40">
-        <v>3.88</v>
+        <v>4.016</v>
       </c>
       <c r="N40">
-        <v>152.53193490000001</v>
+        <v>154.67109769999999</v>
       </c>
       <c r="O40">
-        <v>18.185728399999999</v>
+        <v>10.1288464</v>
       </c>
       <c r="P40">
-        <v>73.612300000000005</v>
+        <v>132.345</v>
       </c>
       <c r="Q40">
-        <v>8.0185200000000005</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="R40">
-        <v>7.8097899999999996</v>
+        <v>9.2170199999999998</v>
       </c>
       <c r="S40">
         <f t="shared" si="0"/>
-        <v>668.81110409377118</v>
+        <v>1103.5971886171305</v>
       </c>
       <c r="T40">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
         <v>20</v>
       </c>
       <c r="C41">
-        <v>11.814299999999999</v>
+        <v>11.168454000000001</v>
       </c>
       <c r="D41">
-        <v>0.1066</v>
+        <v>0.10356</v>
       </c>
       <c r="E41">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>0.11</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="G41">
-        <v>1089</v>
-      </c>
-      <c r="H41" t="s">
-        <v>33</v>
+        <v>1030</v>
       </c>
       <c r="I41">
-        <v>5576</v>
+        <v>6154</v>
       </c>
       <c r="J41">
-        <v>1.7470000000000001</v>
+        <v>1.161</v>
       </c>
       <c r="K41">
-        <v>1.157</v>
+        <v>1.1879999999999999</v>
       </c>
       <c r="L41">
-        <v>0.42099999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="M41">
-        <v>4.016</v>
+        <v>4.3789999999999996</v>
       </c>
       <c r="N41">
-        <v>154.67109769999999</v>
+        <v>73.766792699999996</v>
       </c>
       <c r="O41">
-        <v>10.1288464</v>
+        <v>18.654323000000002</v>
       </c>
       <c r="P41">
-        <v>132.345</v>
+        <v>130.72</v>
       </c>
       <c r="Q41">
-        <v>9.3800000000000008</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R41">
-        <v>9.2170199999999998</v>
+        <v>9.7262599999999999</v>
       </c>
       <c r="S41">
         <f t="shared" si="0"/>
-        <v>1103.5971886171305</v>
+        <v>662.28004924519439</v>
       </c>
       <c r="T41">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
         <v>20</v>
       </c>
       <c r="C42">
-        <v>11.168454000000001</v>
+        <v>4.73620865</v>
       </c>
       <c r="D42">
-        <v>0.10356</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="F42">
-        <v>0.39800000000000002</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="G42">
-        <v>1030</v>
+        <v>1712</v>
+      </c>
+      <c r="H42" t="s">
+        <v>37</v>
       </c>
       <c r="I42">
-        <v>6154</v>
+        <v>5375</v>
       </c>
       <c r="J42">
-        <v>1.161</v>
+        <v>2.69</v>
       </c>
       <c r="K42">
-        <v>1.1879999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="L42">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="M42">
-        <v>4.3789999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="N42">
-        <v>73.766792699999996</v>
+        <v>161.70690529999999</v>
       </c>
       <c r="O42">
-        <v>18.654323000000002</v>
+        <v>-9.3993646000000002</v>
       </c>
       <c r="P42">
-        <v>130.72</v>
+        <v>99.159599999999998</v>
       </c>
       <c r="Q42">
-        <v>9.8219999999999992</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="R42">
-        <v>9.7262599999999999</v>
+        <v>7.8311200000000003</v>
       </c>
       <c r="S42">
         <f t="shared" si="0"/>
-        <v>662.28004924519439</v>
+        <v>3894.9775251994533</v>
       </c>
       <c r="T42">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
       </c>
       <c r="C43">
-        <v>4.73620865</v>
+        <v>3.0801715999999999</v>
       </c>
       <c r="D43">
-        <v>6.2300000000000001E-2</v>
+        <v>4.8809999999999999E-2</v>
       </c>
       <c r="E43">
-        <v>1.35</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F43">
-        <v>0.20499999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="G43">
-        <v>1712</v>
+        <v>2087</v>
       </c>
       <c r="H43" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I43">
-        <v>5375</v>
+        <v>7454</v>
       </c>
       <c r="J43">
-        <v>2.69</v>
+        <v>1.645</v>
       </c>
       <c r="K43">
-        <v>1.44</v>
+        <v>1.635</v>
       </c>
       <c r="L43">
-        <v>0.17</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="M43">
-        <v>3.7</v>
+        <v>4.22</v>
       </c>
       <c r="N43">
-        <v>161.70690529999999</v>
+        <v>125.617407</v>
       </c>
       <c r="O43">
-        <v>-9.3993646000000002</v>
+        <v>13.735309300000001</v>
       </c>
       <c r="P43">
-        <v>99.159599999999998</v>
+        <v>226.5</v>
       </c>
       <c r="Q43">
-        <v>8.0399999999999991</v>
+        <v>9.234</v>
       </c>
       <c r="R43">
-        <v>7.8311200000000003</v>
+        <v>9.2088699999999992</v>
       </c>
       <c r="S43">
         <f t="shared" si="0"/>
-        <v>3894.9775251994533</v>
+        <v>948.15286253702118</v>
       </c>
       <c r="T43">
         <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
       </c>
       <c r="C44">
-        <v>3.0801715999999999</v>
+        <v>4.6117093000000002</v>
       </c>
       <c r="D44">
-        <v>4.8809999999999999E-2</v>
+        <v>6.3700000000000007E-2</v>
       </c>
       <c r="E44">
-        <v>1.5249999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="F44">
-        <v>1.31</v>
+        <v>4.07</v>
       </c>
       <c r="G44">
-        <v>2087</v>
+        <v>1935</v>
       </c>
       <c r="H44" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I44">
-        <v>7454</v>
+        <v>7500</v>
       </c>
       <c r="J44">
-        <v>1.645</v>
+        <v>1.83</v>
       </c>
       <c r="K44">
-        <v>1.635</v>
+        <v>1.62</v>
       </c>
       <c r="L44">
-        <v>-1.7999999999999999E-2</v>
+        <v>-0.12</v>
       </c>
       <c r="M44">
-        <v>4.22</v>
+        <v>4.1269999999999998</v>
       </c>
       <c r="N44">
-        <v>125.617407</v>
+        <v>111.5095293</v>
       </c>
       <c r="O44">
-        <v>13.735309300000001</v>
+        <v>7.6157759</v>
       </c>
       <c r="P44">
-        <v>226.5</v>
+        <v>300.27600000000001</v>
       </c>
       <c r="Q44">
-        <v>9.234</v>
+        <v>9.8569999999999993</v>
       </c>
       <c r="R44">
-        <v>9.2088699999999992</v>
+        <v>9.8633100000000002</v>
       </c>
       <c r="S44">
         <f t="shared" si="0"/>
-        <v>948.15286253702118</v>
+        <v>443.85469120292152</v>
       </c>
       <c r="T44">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
       </c>
       <c r="C45">
-        <v>4.6117093000000002</v>
+        <v>4.1137899999999998</v>
       </c>
       <c r="D45">
-        <v>6.3700000000000007E-2</v>
+        <v>5.4969999999999998E-2</v>
       </c>
       <c r="E45">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="F45">
-        <v>4.07</v>
+        <v>1.7</v>
       </c>
       <c r="G45">
-        <v>1935</v>
+        <v>2080</v>
       </c>
       <c r="H45" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="I45">
-        <v>7500</v>
+        <v>6327</v>
       </c>
       <c r="J45">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="K45">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="L45">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>4.1269999999999998</v>
+        <v>4.5</v>
       </c>
       <c r="N45">
-        <v>111.5095293</v>
+        <v>92.664022599999996</v>
       </c>
       <c r="O45">
-        <v>7.6157759</v>
+        <v>30.957133299999999</v>
       </c>
       <c r="P45">
-        <v>300.27600000000001</v>
+        <v>134.05799999999999</v>
       </c>
       <c r="Q45">
-        <v>9.8569999999999993</v>
+        <v>8.68</v>
       </c>
       <c r="R45">
-        <v>9.8633100000000002</v>
+        <v>8.5839300000000005</v>
       </c>
       <c r="S45">
         <f t="shared" si="0"/>
-        <v>443.85469120292152</v>
+        <v>570.64953846380126</v>
       </c>
       <c r="T45">
         <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
       </c>
       <c r="C46">
-        <v>4.1137899999999998</v>
+        <v>3.4741084999999998</v>
       </c>
       <c r="D46">
-        <v>5.4969999999999998E-2</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="E46">
-        <v>1.35</v>
+        <v>1.7410000000000001</v>
       </c>
       <c r="F46">
-        <v>1.7</v>
+        <v>3.3820000000000001</v>
       </c>
       <c r="G46">
-        <v>2080</v>
+        <v>2262</v>
       </c>
       <c r="H46" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I46">
-        <v>6327</v>
+        <v>8720</v>
       </c>
       <c r="J46">
-        <v>1.93</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="K46">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M46">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="N46">
-        <v>92.664022599999996</v>
+        <v>294.66141260000001</v>
       </c>
       <c r="O46">
-        <v>30.957133299999999</v>
+        <v>31.219200099999998</v>
       </c>
       <c r="P46">
-        <v>134.05799999999999</v>
+        <v>136.42599999999999</v>
       </c>
       <c r="Q46">
-        <v>8.68</v>
+        <v>7.59</v>
       </c>
       <c r="R46">
-        <v>8.5839300000000005</v>
+        <v>7.5749199999999997</v>
       </c>
       <c r="S46">
         <f t="shared" si="0"/>
-        <v>570.64953846380126</v>
+        <v>518.80488815900412</v>
       </c>
       <c r="T46">
         <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
       </c>
       <c r="C47">
-        <v>3.4741084999999998</v>
+        <v>5.55149296</v>
       </c>
       <c r="D47">
-        <v>5.4199999999999998E-2</v>
+        <v>6.6500000000000004E-2</v>
       </c>
       <c r="E47">
-        <v>1.7410000000000001</v>
+        <v>1.1339999999999999</v>
       </c>
       <c r="F47">
-        <v>3.3820000000000001</v>
+        <v>4.59</v>
       </c>
       <c r="G47">
-        <v>2262</v>
+        <v>1391</v>
       </c>
       <c r="H47" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I47">
-        <v>8720</v>
+        <v>6426</v>
       </c>
       <c r="J47">
-        <v>1.5649999999999999</v>
+        <v>1.3380000000000001</v>
       </c>
       <c r="K47">
-        <v>1.76</v>
+        <v>1.268</v>
       </c>
       <c r="L47">
-        <v>-0.28999999999999998</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="M47">
-        <v>4.29</v>
+        <v>4.2869999999999999</v>
       </c>
       <c r="N47">
-        <v>294.66141260000001</v>
+        <v>161.90902729999999</v>
       </c>
       <c r="O47">
-        <v>31.219200099999998</v>
+        <v>71.655726999999999</v>
       </c>
       <c r="P47">
-        <v>136.42599999999999</v>
+        <v>96.517300000000006</v>
       </c>
       <c r="Q47">
-        <v>7.59</v>
+        <v>8.34</v>
       </c>
       <c r="R47">
-        <v>7.5749199999999997</v>
+        <v>8.23752</v>
       </c>
       <c r="S47">
         <f t="shared" si="0"/>
-        <v>518.80488815900412</v>
+        <v>99.730517672190274</v>
       </c>
       <c r="T47">
         <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
       </c>
       <c r="C48">
-        <v>5.55149296</v>
+        <v>2.7033900000000002</v>
       </c>
       <c r="D48">
-        <v>6.6500000000000004E-2</v>
+        <v>4.1230000000000003E-2</v>
       </c>
       <c r="E48">
-        <v>1.1339999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="F48">
-        <v>4.59</v>
+        <v>1.94</v>
       </c>
       <c r="G48">
-        <v>1391</v>
-      </c>
-      <c r="H48" t="s">
-        <v>52</v>
+        <v>1816</v>
       </c>
       <c r="I48">
-        <v>6426</v>
+        <v>6304</v>
       </c>
       <c r="J48">
-        <v>1.3380000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="K48">
-        <v>1.268</v>
+        <v>1.96</v>
       </c>
       <c r="L48">
-        <v>0.13800000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="M48">
-        <v>4.2869999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="N48">
-        <v>161.90902729999999</v>
+        <v>148.6431193</v>
       </c>
       <c r="O48">
-        <v>71.655726999999999</v>
+        <v>40.387944599999997</v>
       </c>
       <c r="P48">
-        <v>96.517300000000006</v>
+        <v>210.25200000000001</v>
       </c>
       <c r="Q48">
-        <v>8.34</v>
+        <v>9.8160000000000007</v>
       </c>
       <c r="R48">
-        <v>8.23752</v>
+        <v>9.7632399999999997</v>
       </c>
       <c r="S48">
         <f t="shared" si="0"/>
-        <v>99.730517672190274</v>
+        <v>582.97620763372299</v>
       </c>
       <c r="T48">
         <f t="shared" si="1"/>
@@ -3487,59 +3525,62 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
       </c>
       <c r="C49">
-        <v>2.7033900000000002</v>
+        <v>2.9895931999999998</v>
       </c>
       <c r="D49">
-        <v>4.1230000000000003E-2</v>
+        <v>4.317E-2</v>
       </c>
       <c r="E49">
-        <v>1.56</v>
+        <v>1.6990000000000001</v>
       </c>
       <c r="F49">
-        <v>1.94</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="G49">
-        <v>1816</v>
+        <v>1823</v>
+      </c>
+      <c r="H49" t="s">
+        <v>56</v>
       </c>
       <c r="I49">
-        <v>6304</v>
+        <v>6206</v>
       </c>
       <c r="J49">
-        <v>1.7</v>
+        <v>1.603</v>
       </c>
       <c r="K49">
-        <v>1.96</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="L49">
-        <v>0.05</v>
+        <v>-0.11600000000000001</v>
       </c>
       <c r="M49">
-        <v>4.2</v>
+        <v>4.1079999999999997</v>
       </c>
       <c r="N49">
-        <v>148.6431193</v>
+        <v>157.06262000000001</v>
       </c>
       <c r="O49">
-        <v>40.387944599999997</v>
+        <v>25.573136600000002</v>
       </c>
       <c r="P49">
-        <v>210.25200000000001</v>
+        <v>218.05</v>
       </c>
       <c r="Q49">
-        <v>9.8160000000000007</v>
+        <v>9.98</v>
       </c>
       <c r="R49">
-        <v>9.7632399999999997</v>
+        <v>9.95702</v>
       </c>
       <c r="S49">
         <f t="shared" si="0"/>
-        <v>582.97620763372299</v>
+        <v>1492.9814393090719</v>
       </c>
       <c r="T49">
         <f t="shared" si="1"/>
@@ -3548,62 +3589,62 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
       </c>
       <c r="C50">
-        <v>2.9895931999999998</v>
+        <v>2.7347700000000001</v>
       </c>
       <c r="D50">
-        <v>4.317E-2</v>
+        <v>4.4150000000000002E-2</v>
       </c>
       <c r="E50">
-        <v>1.6990000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="F50">
-        <v>0.90200000000000002</v>
+        <v>1.39</v>
       </c>
       <c r="G50">
-        <v>1823</v>
+        <v>2048</v>
       </c>
       <c r="H50" t="s">
         <v>56</v>
       </c>
       <c r="I50">
-        <v>6206</v>
+        <v>6768</v>
       </c>
       <c r="J50">
-        <v>1.603</v>
+        <v>1.81</v>
       </c>
       <c r="K50">
-        <v>1.2010000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="L50">
-        <v>-0.11600000000000001</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>4.1079999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="N50">
-        <v>157.06262000000001</v>
+        <v>78.295591200000004</v>
       </c>
       <c r="O50">
-        <v>25.573136600000002</v>
+        <v>33.317953199999998</v>
       </c>
       <c r="P50">
-        <v>218.05</v>
+        <v>136.68100000000001</v>
       </c>
       <c r="Q50">
-        <v>9.98</v>
+        <v>8.56</v>
       </c>
       <c r="R50">
-        <v>9.95702</v>
+        <v>8.4517299999999995</v>
       </c>
       <c r="S50">
         <f t="shared" si="0"/>
-        <v>1492.9814393090719</v>
+        <v>965.25628287035329</v>
       </c>
       <c r="T50">
         <f t="shared" si="1"/>
@@ -3612,334 +3653,334 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
       </c>
       <c r="C51">
-        <v>2.7347700000000001</v>
+        <v>1.4811235</v>
       </c>
       <c r="D51">
-        <v>4.4150000000000002E-2</v>
+        <v>3.4619999999999998E-2</v>
       </c>
       <c r="E51">
-        <v>1.6</v>
+        <v>1.891</v>
       </c>
       <c r="F51">
-        <v>1.39</v>
+        <v>2.88</v>
       </c>
       <c r="G51">
-        <v>2048</v>
+        <v>4050</v>
       </c>
       <c r="H51" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="I51">
-        <v>6768</v>
+        <v>10170.1</v>
       </c>
       <c r="J51">
-        <v>1.81</v>
+        <v>2.3620000000000001</v>
       </c>
       <c r="K51">
-        <v>1.76</v>
+        <v>2.52</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="M51">
-        <v>4.5</v>
+        <v>4.093</v>
       </c>
       <c r="N51">
-        <v>78.295591200000004</v>
+        <v>307.85989979999999</v>
       </c>
       <c r="O51">
-        <v>33.317953199999998</v>
+        <v>39.9389161</v>
       </c>
       <c r="P51">
-        <v>136.68100000000001</v>
+        <v>204.45500000000001</v>
       </c>
       <c r="Q51">
-        <v>8.56</v>
+        <v>7.55</v>
       </c>
       <c r="R51">
-        <v>8.4517299999999995</v>
+        <v>7.5767499999999997</v>
       </c>
       <c r="S51">
         <f t="shared" si="0"/>
-        <v>965.25628287035329</v>
-      </c>
-      <c r="T51">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <v>1286.8653667451285</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52">
-        <v>1.4811235</v>
-      </c>
-      <c r="D52">
-        <v>3.4619999999999998E-2</v>
-      </c>
-      <c r="E52">
-        <v>1.891</v>
-      </c>
-      <c r="F52">
-        <v>2.88</v>
-      </c>
-      <c r="G52">
-        <v>4050</v>
-      </c>
-      <c r="H52" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I52">
-        <v>10170.1</v>
-      </c>
-      <c r="J52">
-        <v>2.3620000000000001</v>
-      </c>
-      <c r="K52">
-        <v>2.52</v>
-      </c>
-      <c r="L52">
-        <v>-0.03</v>
-      </c>
-      <c r="M52">
-        <v>4.093</v>
+        <v>7433.197265625</v>
       </c>
       <c r="N52">
-        <v>307.85989979999999</v>
+        <v>286.97138676797078</v>
       </c>
       <c r="O52">
-        <v>39.9389161</v>
-      </c>
-      <c r="P52">
-        <v>204.45500000000001</v>
+        <v>46.868244058307063</v>
       </c>
       <c r="Q52">
-        <v>7.55</v>
+        <v>10.382340431213381</v>
       </c>
       <c r="R52">
-        <v>7.5767499999999997</v>
-      </c>
-      <c r="S52">
-        <f t="shared" si="0"/>
-        <v>1286.8653667451285</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>137</v>
+        <v>10.382340431213381</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53">
+        <v>1.7635879999999999</v>
+      </c>
+      <c r="D53">
+        <v>3.6409999999999998E-2</v>
+      </c>
+      <c r="E53">
+        <v>1.512</v>
+      </c>
+      <c r="F53">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="G53">
+        <v>2550</v>
       </c>
       <c r="I53">
-        <v>7433.197265625</v>
+        <v>7650</v>
+      </c>
+      <c r="J53">
+        <v>1.74</v>
+      </c>
+      <c r="K53">
+        <v>1.72</v>
+      </c>
+      <c r="L53">
+        <v>0.2</v>
+      </c>
+      <c r="M53">
+        <v>4.2</v>
       </c>
       <c r="N53">
-        <v>286.97138676797078</v>
+        <v>286.97138760000001</v>
       </c>
       <c r="O53">
-        <v>46.868244058307063</v>
+        <v>46.868246300000003</v>
+      </c>
+      <c r="P53">
+        <v>519.096</v>
       </c>
       <c r="Q53">
-        <v>10.382340431213381</v>
+        <v>9.7910000000000004</v>
       </c>
       <c r="R53">
-        <v>10.382340431213381</v>
+        <v>10.367800000000001</v>
+      </c>
+      <c r="S53">
+        <f t="shared" ref="S53:S79" si="2">(0.000000000000000138*G53/(1.673534E-24*1.3*0.000000066726*F53*1.8986E+30/(E53*7149200000)^2))/100000</f>
+        <v>160.76196513632402</v>
+      </c>
+      <c r="T53">
+        <f t="shared" ref="T53:T79" si="3">IF(I53&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
         <v>20</v>
       </c>
       <c r="C54">
-        <v>1.7635879999999999</v>
+        <v>0.79205199999999998</v>
       </c>
       <c r="D54">
-        <v>3.6409999999999998E-2</v>
+        <v>1.6789999999999999E-2</v>
       </c>
       <c r="E54">
-        <v>1.512</v>
+        <v>0.42109020000000003</v>
       </c>
       <c r="F54">
-        <v>9.2799999999999994</v>
+        <v>9.2250570000000004E-2</v>
       </c>
       <c r="G54">
-        <v>2550</v>
+        <v>1978</v>
+      </c>
+      <c r="H54" t="s">
+        <v>99</v>
       </c>
       <c r="I54">
-        <v>7650</v>
+        <v>5443</v>
       </c>
       <c r="J54">
-        <v>1.74</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="K54">
-        <v>1.72</v>
+        <v>1.02</v>
       </c>
       <c r="L54">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M54">
-        <v>4.2</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="N54">
-        <v>286.97138760000001</v>
+        <v>358.6688767</v>
       </c>
       <c r="O54">
-        <v>46.868246300000003</v>
+        <v>-37.628223699999999</v>
       </c>
       <c r="P54">
-        <v>519.096</v>
+        <v>80.437299999999993</v>
       </c>
       <c r="Q54">
-        <v>9.7910000000000004</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="R54">
-        <v>10.367800000000001</v>
+        <v>9.6000599999999991</v>
       </c>
       <c r="S54">
-        <f t="shared" ref="S54:S80" si="2">(0.000000000000000138*G54/(1.673534E-24*1.3*0.000000066726*F54*1.8986E+30/(E54*7149200000)^2))/100000</f>
-        <v>160.76196513632402</v>
+        <f t="shared" si="2"/>
+        <v>972.96006983022733</v>
       </c>
       <c r="T54">
-        <f t="shared" ref="T54:T80" si="3">IF(I54&gt;6800,-7,-5)</f>
-        <v>-7</v>
+        <f t="shared" si="3"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
         <v>20</v>
       </c>
       <c r="C55">
-        <v>0.79205199999999998</v>
+        <v>2.1487738099999998</v>
       </c>
       <c r="D55">
-        <v>1.6789999999999999E-2</v>
+        <v>4.0351999999999999E-2</v>
       </c>
       <c r="E55">
-        <v>0.42109020000000003</v>
+        <v>1.597</v>
       </c>
       <c r="F55">
-        <v>9.2250570000000004E-2</v>
+        <v>3.7</v>
       </c>
       <c r="G55">
-        <v>1978</v>
+        <v>2594.3000000000002</v>
       </c>
       <c r="H55" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="I55">
-        <v>5443</v>
+        <v>7490</v>
       </c>
       <c r="J55">
-        <v>0.94899999999999995</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="K55">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="L55">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="M55">
-        <v>4.3499999999999996</v>
+        <v>4.1050000000000004</v>
       </c>
       <c r="N55">
-        <v>358.6688767</v>
+        <v>317.5515264</v>
       </c>
       <c r="O55">
-        <v>-37.628223699999999</v>
+        <v>10.7388967</v>
       </c>
       <c r="P55">
-        <v>80.437299999999993</v>
+        <v>182.273</v>
       </c>
       <c r="Q55">
-        <v>9.7899999999999991</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="R55">
-        <v>9.6000599999999991</v>
+        <v>8.2424300000000006</v>
       </c>
       <c r="S55">
         <f t="shared" si="2"/>
-        <v>972.96006983022733</v>
+        <v>457.63140850776114</v>
       </c>
       <c r="T55">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>2.1487738099999998</v>
+        <v>2.8240932000000001</v>
       </c>
       <c r="D56">
-        <v>4.0351999999999999E-2</v>
+        <v>4.7399999999999998E-2</v>
       </c>
       <c r="E56">
-        <v>1.597</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="F56">
-        <v>3.7</v>
+        <v>1.675</v>
       </c>
       <c r="G56">
-        <v>2594.3000000000002</v>
+        <v>2250</v>
       </c>
       <c r="H56" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I56">
-        <v>7490</v>
+        <v>7800</v>
       </c>
       <c r="J56">
-        <v>2.0819999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="K56">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="L56">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>4.1050000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N56">
-        <v>317.5515264</v>
+        <v>147.5800667</v>
       </c>
       <c r="O56">
-        <v>10.7388967</v>
+        <v>-66.113925300000005</v>
       </c>
       <c r="P56">
-        <v>182.273</v>
+        <v>170.696</v>
       </c>
       <c r="Q56">
-        <v>8.2799999999999994</v>
+        <v>8.1910000000000007</v>
       </c>
       <c r="R56">
-        <v>8.2424300000000006</v>
+        <v>8.1740100000000009</v>
       </c>
       <c r="S56">
         <f t="shared" si="2"/>
-        <v>457.63140850776114</v>
+        <v>789.006338593706</v>
       </c>
       <c r="T56">
         <f t="shared" si="3"/>
@@ -3948,193 +3989,190 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57">
-        <v>2.8240932000000001</v>
+        <v>16.249210000000001</v>
       </c>
       <c r="D57">
-        <v>4.7399999999999998E-2</v>
+        <v>0.12909999999999999</v>
       </c>
       <c r="E57">
-        <v>1.5149999999999999</v>
+        <v>1.087</v>
       </c>
       <c r="F57">
-        <v>1.675</v>
+        <v>4.34</v>
       </c>
       <c r="G57">
-        <v>2250</v>
+        <v>805.5</v>
       </c>
       <c r="H57" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I57">
-        <v>7800</v>
+        <v>5756</v>
       </c>
       <c r="J57">
-        <v>1.79</v>
+        <v>1.0860000000000001</v>
       </c>
       <c r="K57">
-        <v>1.75</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="M57">
-        <v>4.0999999999999996</v>
+        <v>4.4020000000000001</v>
       </c>
       <c r="N57">
-        <v>147.5800667</v>
+        <v>310.29170019999998</v>
       </c>
       <c r="O57">
-        <v>-66.113925300000005</v>
+        <v>3.6382967000000002</v>
       </c>
       <c r="P57">
-        <v>170.696</v>
+        <v>93.734499999999997</v>
       </c>
       <c r="Q57">
-        <v>8.1910000000000007</v>
+        <v>9.48</v>
       </c>
       <c r="R57">
-        <v>8.1740100000000009</v>
+        <v>9.4290710000000004</v>
       </c>
       <c r="S57">
         <f t="shared" si="2"/>
-        <v>789.006338593706</v>
+        <v>56.120615203365361</v>
       </c>
       <c r="T57">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
         <v>20</v>
       </c>
       <c r="C58">
-        <v>16.249210000000001</v>
+        <v>8.0277282999999997</v>
       </c>
       <c r="D58">
-        <v>0.12909999999999999</v>
+        <v>8.2337403000000003E-2</v>
       </c>
       <c r="E58">
-        <v>1.087</v>
+        <v>0.83243188000000001</v>
       </c>
       <c r="F58">
-        <v>4.34</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="G58">
-        <v>805.5</v>
+        <v>1074.28</v>
       </c>
       <c r="H58" t="s">
         <v>43</v>
       </c>
       <c r="I58">
-        <v>5756</v>
+        <v>5962.7</v>
       </c>
       <c r="J58">
-        <v>1.0860000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="K58">
-        <v>1.0820000000000001</v>
+        <v>1.156039</v>
       </c>
       <c r="L58">
-        <v>0.318</v>
+        <v>0</v>
       </c>
       <c r="M58">
-        <v>4.4020000000000001</v>
+        <v>4.38</v>
       </c>
       <c r="N58">
-        <v>310.29170019999998</v>
+        <v>193.3963704</v>
       </c>
       <c r="O58">
-        <v>3.6382967000000002</v>
+        <v>85.129495199999994</v>
       </c>
       <c r="P58">
-        <v>93.734499999999997</v>
+        <v>114.048</v>
       </c>
       <c r="Q58">
-        <v>9.48</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="R58">
-        <v>9.4290710000000004</v>
+        <v>9.4135299999999997</v>
       </c>
       <c r="S58">
         <f t="shared" si="2"/>
-        <v>56.120615203365361</v>
+        <v>1175.9460676296278</v>
       </c>
       <c r="T58">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
-      <c r="U58" s="1" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
         <v>20</v>
       </c>
       <c r="C59">
-        <v>8.0277282999999997</v>
+        <v>12.5199</v>
       </c>
       <c r="D59">
-        <v>8.2337403000000003E-2</v>
+        <v>0.1062</v>
       </c>
       <c r="E59">
-        <v>0.83243188000000001</v>
+        <v>0.41279399999999999</v>
       </c>
       <c r="F59">
-        <v>0.16200000000000001</v>
+        <v>2.627204E-2</v>
       </c>
       <c r="G59">
-        <v>1074.28</v>
-      </c>
-      <c r="H59" t="s">
-        <v>43</v>
+        <v>843</v>
       </c>
       <c r="I59">
-        <v>5962.7</v>
+        <v>5770</v>
       </c>
       <c r="J59">
-        <v>1.1499999999999999</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="K59">
-        <v>1.156039</v>
+        <v>1.022</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M59">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="N59">
-        <v>193.3963704</v>
+        <v>192.1848981</v>
       </c>
       <c r="O59">
-        <v>85.129495199999994</v>
+        <v>64.855275500000005</v>
       </c>
       <c r="P59">
-        <v>114.048</v>
+        <v>84.536199999999994</v>
       </c>
       <c r="Q59">
-        <v>9.5399999999999991</v>
+        <v>9.5340000000000007</v>
       </c>
       <c r="R59">
-        <v>9.4135299999999997</v>
+        <v>9.3678899999999992</v>
       </c>
       <c r="S59">
         <f t="shared" si="2"/>
-        <v>1175.9460676296278</v>
+        <v>1399.2265914107247</v>
       </c>
       <c r="T59">
         <f t="shared" si="3"/>
@@ -4143,59 +4181,59 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s">
         <v>20</v>
       </c>
       <c r="C60">
-        <v>12.5199</v>
+        <v>4.7202190000000002</v>
       </c>
       <c r="D60">
-        <v>0.1062</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="E60">
-        <v>0.41279399999999999</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="F60">
-        <v>2.627204E-2</v>
+        <v>2.37</v>
       </c>
       <c r="G60">
-        <v>843</v>
+        <v>1679</v>
       </c>
       <c r="I60">
-        <v>5770</v>
+        <v>6274</v>
       </c>
       <c r="J60">
-        <v>0.96799999999999997</v>
+        <v>1.925</v>
       </c>
       <c r="K60">
-        <v>1.022</v>
+        <v>1.464</v>
       </c>
       <c r="L60">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M60">
-        <v>4.47</v>
+        <v>4.0339999999999998</v>
       </c>
       <c r="N60">
-        <v>192.1848981</v>
+        <v>325.01453629999997</v>
       </c>
       <c r="O60">
-        <v>64.855275500000005</v>
+        <v>48.4067674</v>
       </c>
       <c r="P60">
-        <v>84.536199999999994</v>
+        <v>200.49199999999999</v>
       </c>
       <c r="Q60">
-        <v>9.5340000000000007</v>
+        <v>9.4380000000000006</v>
       </c>
       <c r="R60">
-        <v>9.3678899999999992</v>
+        <v>9.3503900000000009</v>
       </c>
       <c r="S60">
         <f t="shared" si="2"/>
-        <v>1399.2265914107247</v>
+        <v>353.31388599481477</v>
       </c>
       <c r="T60">
         <f t="shared" si="3"/>
@@ -4204,59 +4242,62 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B61" t="s">
         <v>20</v>
       </c>
       <c r="C61">
-        <v>4.7202190000000002</v>
+        <v>4.4258699999999997</v>
       </c>
       <c r="D61">
-        <v>6.2600000000000003E-2</v>
+        <v>5.7779999999999998E-2</v>
       </c>
       <c r="E61">
-        <v>1.3959999999999999</v>
+        <v>2.2303544500000001</v>
       </c>
       <c r="F61">
-        <v>2.37</v>
+        <v>1.86578665</v>
       </c>
       <c r="G61">
-        <v>1679</v>
+        <v>1293</v>
+      </c>
+      <c r="H61" t="s">
+        <v>70</v>
       </c>
       <c r="I61">
-        <v>6274</v>
+        <v>6117</v>
       </c>
       <c r="J61">
-        <v>1.925</v>
+        <v>1.53</v>
       </c>
       <c r="K61">
-        <v>1.464</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="L61">
-        <v>0.11899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="M61">
-        <v>4.0339999999999998</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N61">
-        <v>325.01453629999997</v>
+        <v>313.5110469</v>
       </c>
       <c r="O61">
-        <v>48.4067674</v>
+        <v>72.580645500000003</v>
       </c>
       <c r="P61">
-        <v>200.49199999999999</v>
+        <v>139.48400000000001</v>
       </c>
       <c r="Q61">
-        <v>9.4380000000000006</v>
+        <v>9.2700010000000006</v>
       </c>
       <c r="R61">
-        <v>9.3503900000000009</v>
+        <v>9.1879500000000007</v>
       </c>
       <c r="S61">
         <f t="shared" si="2"/>
-        <v>353.31388599481477</v>
+        <v>882.20971786077962</v>
       </c>
       <c r="T61">
         <f t="shared" si="3"/>
@@ -4265,126 +4306,126 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
       <c r="C62">
-        <v>4.4258699999999997</v>
+        <v>2.6502370000000002</v>
       </c>
       <c r="D62">
-        <v>5.7779999999999998E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="E62">
-        <v>2.2303544500000001</v>
+        <v>1.49</v>
       </c>
       <c r="F62">
-        <v>1.86578665</v>
+        <v>3.12</v>
       </c>
       <c r="G62">
-        <v>1293</v>
+        <v>2370</v>
       </c>
       <c r="H62" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I62">
-        <v>6117</v>
+        <v>7690</v>
       </c>
       <c r="J62">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="K62">
-        <v>1.3120000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="L62">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="M62">
-        <v>4.0999999999999996</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="N62">
-        <v>313.5110469</v>
+        <v>316.20369219999998</v>
       </c>
       <c r="O62">
-        <v>72.580645500000003</v>
+        <v>55.588022100000003</v>
       </c>
       <c r="P62">
-        <v>139.48400000000001</v>
+        <v>148.92500000000001</v>
       </c>
       <c r="Q62">
-        <v>9.2700010000000006</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="R62">
-        <v>9.1879500000000007</v>
+        <v>7.9756099999999996</v>
       </c>
       <c r="S62">
         <f t="shared" si="2"/>
-        <v>882.20971786077962</v>
+        <v>431.57254486096394</v>
       </c>
       <c r="T62">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
       </c>
       <c r="C63">
-        <v>2.6502370000000002</v>
+        <v>1.902603</v>
       </c>
       <c r="D63">
-        <v>4.5999999999999999E-2</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="E63">
-        <v>1.49</v>
+        <v>1.875</v>
       </c>
       <c r="F63">
-        <v>3.12</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G63">
-        <v>2370</v>
+        <v>2492</v>
       </c>
       <c r="H63" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I63">
-        <v>7690</v>
+        <v>7300</v>
       </c>
       <c r="J63">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="K63">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="L63">
-        <v>0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="M63">
-        <v>4.1500000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N63">
-        <v>316.20369219999998</v>
+        <v>352.26752069999998</v>
       </c>
       <c r="O63">
-        <v>55.588022100000003</v>
+        <v>67.034806200000006</v>
       </c>
       <c r="P63">
-        <v>148.92500000000001</v>
+        <v>225.88800000000001</v>
       </c>
       <c r="Q63">
-        <v>8.0299999999999994</v>
+        <v>8.952</v>
       </c>
       <c r="R63">
-        <v>7.9756099999999996</v>
+        <v>8.8952899999999993</v>
       </c>
       <c r="S63">
         <f t="shared" si="2"/>
-        <v>431.57254486096394</v>
+        <v>974.78820571370204</v>
       </c>
       <c r="T63">
         <f t="shared" si="3"/>
@@ -4393,126 +4434,123 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B64" t="s">
         <v>20</v>
       </c>
       <c r="C64">
-        <v>1.902603</v>
+        <v>3.2086640000000002</v>
       </c>
       <c r="D64">
-        <v>3.8899999999999997E-2</v>
+        <v>4.8820000000000002E-2</v>
       </c>
       <c r="E64">
-        <v>1.875</v>
+        <v>1.44</v>
       </c>
       <c r="F64">
-        <v>2.2999999999999998</v>
+        <v>0.7</v>
       </c>
       <c r="G64">
-        <v>2492</v>
+        <v>1927</v>
       </c>
       <c r="H64" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I64">
-        <v>7300</v>
+        <v>5991</v>
       </c>
       <c r="J64">
-        <v>1.95</v>
+        <v>2.1680000000000001</v>
       </c>
       <c r="K64">
-        <v>1.79</v>
+        <v>1.5069999999999999</v>
       </c>
       <c r="L64">
-        <v>-0.1</v>
+        <v>0.373</v>
       </c>
       <c r="M64">
-        <v>4.0999999999999996</v>
+        <v>3.9430000000000001</v>
       </c>
       <c r="N64">
-        <v>352.26752069999998</v>
+        <v>142.74340599999999</v>
       </c>
       <c r="O64">
-        <v>67.034806200000006</v>
+        <v>26.539995099999999</v>
       </c>
       <c r="P64">
-        <v>225.88800000000001</v>
+        <v>229.06700000000001</v>
       </c>
       <c r="Q64">
-        <v>8.952</v>
+        <v>9.7210000000000001</v>
       </c>
       <c r="R64">
-        <v>8.8952899999999993</v>
+        <v>9.5843900000000009</v>
       </c>
       <c r="S64">
         <f t="shared" si="2"/>
-        <v>974.78820571370204</v>
+        <v>1460.8182255852041</v>
       </c>
       <c r="T64">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
       <c r="C65">
-        <v>3.2086640000000002</v>
+        <v>9.5739181000000002</v>
       </c>
       <c r="D65">
-        <v>4.8820000000000002E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E65">
-        <v>1.44</v>
+        <v>1.10166148</v>
       </c>
       <c r="F65">
-        <v>0.7</v>
+        <v>0.28128386</v>
       </c>
       <c r="G65">
-        <v>1927</v>
-      </c>
-      <c r="H65" t="s">
-        <v>56</v>
+        <v>1199.55</v>
       </c>
       <c r="I65">
-        <v>5991</v>
+        <v>6039</v>
       </c>
       <c r="J65">
-        <v>2.1680000000000001</v>
+        <v>2.032</v>
       </c>
       <c r="K65">
-        <v>1.5069999999999999</v>
+        <v>1.4642999999999999</v>
       </c>
       <c r="L65">
-        <v>0.373</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M65">
-        <v>3.9430000000000001</v>
+        <v>3.9860000000000002</v>
       </c>
       <c r="N65">
-        <v>142.74340599999999</v>
+        <v>201.9626552</v>
       </c>
       <c r="O65">
-        <v>26.539995099999999</v>
+        <v>9.0306437000000006</v>
       </c>
       <c r="P65">
-        <v>229.06700000000001</v>
+        <v>223.465</v>
       </c>
       <c r="Q65">
-        <v>9.7210000000000001</v>
+        <v>9.8149999999999995</v>
       </c>
       <c r="R65">
-        <v>9.5843900000000009</v>
+        <v>9.6598100000000002</v>
       </c>
       <c r="S65">
         <f t="shared" si="2"/>
-        <v>1460.8182255852041</v>
+        <v>1324.5165539963698</v>
       </c>
       <c r="T65">
         <f t="shared" si="3"/>
@@ -4521,303 +4559,306 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
       </c>
       <c r="C66">
-        <v>9.5739181000000002</v>
+        <v>17.305904000000002</v>
       </c>
       <c r="D66">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E66">
-        <v>1.10166148</v>
+        <v>1.07</v>
       </c>
       <c r="F66">
-        <v>0.28128386</v>
+        <v>6.4</v>
       </c>
       <c r="G66">
-        <v>1199.55</v>
+        <v>1221.3900000000001</v>
       </c>
       <c r="I66">
-        <v>6039</v>
+        <v>7130</v>
       </c>
       <c r="J66">
-        <v>2.032</v>
+        <v>2.02</v>
       </c>
       <c r="K66">
-        <v>1.4642999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="L66">
-        <v>0.33200000000000002</v>
+        <v>0</v>
       </c>
       <c r="M66">
-        <v>3.9860000000000002</v>
+        <v>3.9460000000000002</v>
       </c>
       <c r="N66">
-        <v>201.9626552</v>
+        <v>164.031654</v>
       </c>
       <c r="O66">
-        <v>9.0306437000000006</v>
+        <v>-43.376696699999997</v>
       </c>
       <c r="P66">
-        <v>223.465</v>
+        <v>328.47500000000002</v>
       </c>
       <c r="Q66">
-        <v>9.8149999999999995</v>
+        <v>9.8670000000000009</v>
       </c>
       <c r="R66">
-        <v>9.6598100000000002</v>
+        <v>9.7596699999999998</v>
       </c>
       <c r="S66">
         <f t="shared" si="2"/>
-        <v>1324.5165539963698</v>
+        <v>55.915145726222889</v>
       </c>
       <c r="T66">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
         <v>20</v>
       </c>
       <c r="C67">
-        <v>17.305904000000002</v>
+        <v>10.261127</v>
       </c>
       <c r="D67">
-        <v>0.16</v>
+        <v>0.111</v>
       </c>
       <c r="E67">
-        <v>1.07</v>
+        <v>1.1079506100000001</v>
       </c>
       <c r="F67">
-        <v>6.4</v>
+        <v>5.55960374</v>
       </c>
       <c r="G67">
-        <v>1221.3900000000001</v>
+        <v>1363.43</v>
       </c>
       <c r="I67">
-        <v>7130</v>
+        <v>6200</v>
       </c>
       <c r="J67">
-        <v>2.02</v>
+        <v>2.7505000000000002</v>
       </c>
       <c r="K67">
-        <v>1.59</v>
+        <v>1.7169000000000001</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M67">
-        <v>3.9460000000000002</v>
+        <v>3.7890000000000001</v>
       </c>
       <c r="N67">
-        <v>164.031654</v>
+        <v>263.75807529999997</v>
       </c>
       <c r="O67">
-        <v>-43.376696699999997</v>
+        <v>40.695042800000003</v>
       </c>
       <c r="P67">
-        <v>328.47500000000002</v>
+        <v>224.73099999999999</v>
       </c>
       <c r="Q67">
-        <v>9.8670000000000009</v>
+        <v>9.07</v>
       </c>
       <c r="R67">
-        <v>9.7596699999999998</v>
+        <v>8.9365100000000002</v>
       </c>
       <c r="S67">
         <f t="shared" si="2"/>
-        <v>55.915145726222889</v>
+        <v>77.040187113891676</v>
       </c>
       <c r="T67">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
         <v>20</v>
       </c>
       <c r="C68">
-        <v>10.261127</v>
+        <v>10.655669</v>
       </c>
       <c r="D68">
-        <v>0.111</v>
+        <v>0.1166</v>
       </c>
       <c r="E68">
-        <v>1.1079506100000001</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F68">
-        <v>5.55960374</v>
+        <v>4.82</v>
       </c>
       <c r="G68">
-        <v>1363.43</v>
+        <v>1595</v>
       </c>
       <c r="I68">
-        <v>6200</v>
+        <v>7360</v>
       </c>
       <c r="J68">
-        <v>2.7505000000000002</v>
+        <v>2.36</v>
       </c>
       <c r="K68">
-        <v>1.7169000000000001</v>
+        <v>1.859</v>
       </c>
       <c r="L68">
-        <v>0.28499999999999998</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M68">
-        <v>3.7890000000000001</v>
+        <v>3.9620000000000002</v>
       </c>
       <c r="N68">
-        <v>263.75807529999997</v>
+        <v>90.062587800000003</v>
       </c>
       <c r="O68">
-        <v>40.695042800000003</v>
+        <v>11.8840577</v>
       </c>
       <c r="P68">
-        <v>224.73099999999999</v>
+        <v>285.28899999999999</v>
       </c>
       <c r="Q68">
-        <v>9.07</v>
+        <v>9.5470000000000006</v>
       </c>
       <c r="R68">
-        <v>8.9365100000000002</v>
+        <v>9.4724400000000006</v>
       </c>
       <c r="S68">
         <f t="shared" si="2"/>
-        <v>77.040187113891676</v>
+        <v>83.670803141549356</v>
       </c>
       <c r="T68">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
       </c>
       <c r="C69">
-        <v>10.655669</v>
+        <v>18.388179999999998</v>
       </c>
       <c r="D69">
-        <v>0.1166</v>
+        <v>0.15279999999999999</v>
       </c>
       <c r="E69">
-        <v>0.99399999999999999</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F69">
-        <v>4.82</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="G69">
-        <v>1595</v>
+        <v>1027</v>
       </c>
       <c r="I69">
-        <v>7360</v>
+        <v>6095</v>
       </c>
       <c r="J69">
-        <v>2.36</v>
+        <v>1.867</v>
       </c>
       <c r="K69">
-        <v>1.859</v>
+        <v>1.407</v>
       </c>
       <c r="L69">
-        <v>9.4E-2</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M69">
-        <v>3.9620000000000002</v>
+        <v>4.0439999999999996</v>
       </c>
       <c r="N69">
-        <v>90.062587800000003</v>
+        <v>47.517260800000003</v>
       </c>
       <c r="O69">
-        <v>11.8840577</v>
+        <v>-50.8322632</v>
       </c>
       <c r="P69">
-        <v>285.28899999999999</v>
+        <v>76.902799999999999</v>
       </c>
       <c r="Q69">
-        <v>9.5470000000000006</v>
+        <v>7.57</v>
       </c>
       <c r="R69">
-        <v>9.4724400000000006</v>
+        <v>7.4165299999999998</v>
       </c>
       <c r="S69">
         <f t="shared" si="2"/>
-        <v>83.670803141549356</v>
+        <v>777.64358420307099</v>
       </c>
       <c r="T69">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
       </c>
       <c r="C70">
-        <v>18.388179999999998</v>
+        <v>16.067540999999999</v>
       </c>
       <c r="D70">
-        <v>0.15279999999999999</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="E70">
-        <v>0.63900000000000001</v>
+        <v>0.45410017000000003</v>
       </c>
       <c r="F70">
-        <v>0.13800000000000001</v>
+        <v>4.4363560000000003E-2</v>
       </c>
       <c r="G70">
-        <v>1027</v>
+        <v>635</v>
+      </c>
+      <c r="H70" t="s">
+        <v>116</v>
       </c>
       <c r="I70">
-        <v>6095</v>
+        <v>5291</v>
       </c>
       <c r="J70">
-        <v>1.867</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="K70">
-        <v>1.407</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="L70">
-        <v>0.17499999999999999</v>
+        <v>-4.3999999999999997E-2</v>
       </c>
       <c r="M70">
-        <v>4.0439999999999996</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="N70">
-        <v>47.517260800000003</v>
+        <v>81.853282399999998</v>
       </c>
       <c r="O70">
-        <v>-50.8322632</v>
+        <v>-14.2767404</v>
       </c>
       <c r="P70">
-        <v>76.902799999999999</v>
+        <v>74.796899999999994</v>
       </c>
       <c r="Q70">
-        <v>7.57</v>
+        <v>9.9309999999999992</v>
       </c>
       <c r="R70">
-        <v>7.4165299999999998</v>
+        <v>9.7777600000000007</v>
       </c>
       <c r="S70">
         <f t="shared" si="2"/>
-        <v>777.64358420307099</v>
+        <v>755.33252275944176</v>
       </c>
       <c r="T70">
         <f t="shared" si="3"/>
@@ -4826,62 +4867,59 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B71" t="s">
         <v>20</v>
       </c>
       <c r="C71">
-        <v>16.067540999999999</v>
+        <v>9.9558099999999996</v>
       </c>
       <c r="D71">
-        <v>0.11700000000000001</v>
+        <v>9.9400000000000002E-2</v>
       </c>
       <c r="E71">
-        <v>0.45410017000000003</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="F71">
-        <v>4.4363560000000003E-2</v>
+        <v>1.49</v>
       </c>
       <c r="G71">
-        <v>635</v>
-      </c>
-      <c r="H71" t="s">
-        <v>116</v>
+        <v>1655</v>
       </c>
       <c r="I71">
-        <v>5291</v>
+        <v>4896</v>
       </c>
       <c r="J71">
-        <v>0.86599999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="K71">
-        <v>0.83299999999999996</v>
+        <v>1.31</v>
       </c>
       <c r="L71">
-        <v>-4.3999999999999997E-2</v>
+        <v>0.23</v>
       </c>
       <c r="M71">
-        <v>4.4800000000000004</v>
+        <v>3.48</v>
       </c>
       <c r="N71">
-        <v>81.853282399999998</v>
+        <v>184.97875790000001</v>
       </c>
       <c r="O71">
-        <v>-14.2767404</v>
+        <v>-25.827853099999999</v>
       </c>
       <c r="P71">
-        <v>74.796899999999994</v>
+        <v>215.98599999999999</v>
       </c>
       <c r="Q71">
-        <v>9.9309999999999992</v>
+        <v>9.9730000000000008</v>
       </c>
       <c r="R71">
-        <v>9.7777600000000007</v>
+        <v>9.641</v>
       </c>
       <c r="S71">
         <f t="shared" si="2"/>
-        <v>755.33252275944176</v>
+        <v>318.17832033985127</v>
       </c>
       <c r="T71">
         <f t="shared" si="3"/>
@@ -4890,59 +4928,62 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="B72" t="s">
         <v>20</v>
       </c>
       <c r="C72">
-        <v>9.9558099999999996</v>
+        <v>7.2459899999999999</v>
       </c>
       <c r="D72">
-        <v>9.9400000000000002E-2</v>
+        <v>8.8800000000000004E-2</v>
       </c>
       <c r="E72">
-        <v>1.0580000000000001</v>
+        <v>1.042</v>
       </c>
       <c r="F72">
-        <v>1.49</v>
+        <v>12.89</v>
       </c>
       <c r="G72">
-        <v>1655</v>
+        <v>1677</v>
+      </c>
+      <c r="H72" t="s">
+        <v>56</v>
       </c>
       <c r="I72">
-        <v>4896</v>
+        <v>6264</v>
       </c>
       <c r="J72">
-        <v>3.55</v>
+        <v>2.738</v>
       </c>
       <c r="K72">
-        <v>1.31</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="L72">
-        <v>0.23</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="M72">
-        <v>3.48</v>
+        <v>3.81</v>
       </c>
       <c r="N72">
-        <v>184.97875790000001</v>
+        <v>83.865928800000006</v>
       </c>
       <c r="O72">
-        <v>-25.827853099999999</v>
+        <v>21.294241700000001</v>
       </c>
       <c r="P72">
-        <v>215.98599999999999</v>
+        <v>225.643</v>
       </c>
       <c r="Q72">
-        <v>9.9730000000000008</v>
+        <v>9.24</v>
       </c>
       <c r="R72">
-        <v>9.641</v>
+        <v>9.0746900000000004</v>
       </c>
       <c r="S72">
         <f t="shared" si="2"/>
-        <v>318.17832033985127</v>
+        <v>36.149567272802649</v>
       </c>
       <c r="T72">
         <f t="shared" si="3"/>
@@ -4951,62 +4992,62 @@
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="B73" t="s">
         <v>20</v>
       </c>
       <c r="C73">
-        <v>7.2459899999999999</v>
+        <v>10.331110000000001</v>
       </c>
       <c r="D73">
-        <v>8.8800000000000004E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="E73">
-        <v>1.042</v>
+        <v>0.99</v>
       </c>
       <c r="F73">
-        <v>12.89</v>
+        <v>1.53</v>
       </c>
       <c r="G73">
-        <v>1677</v>
+        <v>1370</v>
       </c>
       <c r="H73" t="s">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="I73">
-        <v>6264</v>
+        <v>5735</v>
       </c>
       <c r="J73">
-        <v>2.738</v>
+        <v>1.66</v>
       </c>
       <c r="K73">
-        <v>1.7649999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L73">
-        <v>0.34200000000000003</v>
+        <v>0.26</v>
       </c>
       <c r="M73">
-        <v>3.81</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="N73">
-        <v>83.865928800000006</v>
+        <v>110.5126861</v>
       </c>
       <c r="O73">
-        <v>21.294241700000001</v>
+        <v>-57.384998000000003</v>
       </c>
       <c r="P73">
-        <v>225.643</v>
+        <v>179.36600000000001</v>
       </c>
       <c r="Q73">
-        <v>9.24</v>
+        <v>9.9719999999999995</v>
       </c>
       <c r="R73">
-        <v>9.0746900000000004</v>
+        <v>9.8465900000000008</v>
       </c>
       <c r="S73">
         <f t="shared" si="2"/>
-        <v>36.149567272802649</v>
+        <v>224.58825733889913</v>
       </c>
       <c r="T73">
         <f t="shared" si="3"/>
@@ -5015,62 +5056,59 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
         <v>20</v>
       </c>
       <c r="C74">
-        <v>10.331110000000001</v>
+        <v>6.7535809999999996</v>
       </c>
       <c r="D74">
-        <v>9.7000000000000003E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E74">
-        <v>0.99</v>
+        <v>0.58881357999999995</v>
       </c>
       <c r="F74">
-        <v>1.53</v>
+        <v>0.10068326</v>
       </c>
       <c r="G74">
-        <v>1370</v>
-      </c>
-      <c r="H74" t="s">
-        <v>120</v>
+        <v>1180</v>
       </c>
       <c r="I74">
-        <v>5735</v>
+        <v>5808</v>
       </c>
       <c r="J74">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="K74">
-        <v>1.1399999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L74">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="M74">
-        <v>4.0599999999999996</v>
+        <v>4.26</v>
       </c>
       <c r="N74">
-        <v>110.5126861</v>
+        <v>166.26950410000001</v>
       </c>
       <c r="O74">
-        <v>-57.384998000000003</v>
+        <v>11.2464069</v>
       </c>
       <c r="P74">
-        <v>179.36600000000001</v>
+        <v>130.91900000000001</v>
       </c>
       <c r="Q74">
-        <v>9.9719999999999995</v>
+        <v>9.75</v>
       </c>
       <c r="R74">
-        <v>9.8465900000000008</v>
+        <v>9.6080000000000005</v>
       </c>
       <c r="S74">
         <f t="shared" si="2"/>
-        <v>224.58825733889913</v>
+        <v>1039.84328949877</v>
       </c>
       <c r="T74">
         <f t="shared" si="3"/>
@@ -5079,59 +5117,62 @@
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="B75" t="s">
         <v>20</v>
       </c>
       <c r="C75">
-        <v>6.7535809999999996</v>
+        <v>10.590547000000001</v>
       </c>
       <c r="D75">
-        <v>7.2999999999999995E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E75">
-        <v>0.58881357999999995</v>
+        <v>0.91890603000000004</v>
       </c>
       <c r="F75">
-        <v>0.10068326</v>
+        <v>0.18469084999999999</v>
       </c>
       <c r="G75">
-        <v>1180</v>
+        <v>947</v>
+      </c>
+      <c r="H75" t="s">
+        <v>130</v>
       </c>
       <c r="I75">
-        <v>5808</v>
+        <v>6000</v>
       </c>
       <c r="J75">
-        <v>1.29</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="K75">
-        <v>1.1000000000000001</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="L75">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="M75">
-        <v>4.26</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N75">
-        <v>166.26950410000001</v>
+        <v>161.87955690000001</v>
       </c>
       <c r="O75">
-        <v>11.2464069</v>
+        <v>36.329434499999998</v>
       </c>
       <c r="P75">
-        <v>130.91900000000001</v>
+        <v>130.85499999999999</v>
       </c>
       <c r="Q75">
-        <v>9.75</v>
+        <v>10.058999999999999</v>
       </c>
       <c r="R75">
-        <v>9.6080000000000005</v>
+        <v>9.9823299999999993</v>
       </c>
       <c r="S75">
         <f t="shared" si="2"/>
-        <v>1039.84328949877</v>
+        <v>1107.9861243219782</v>
       </c>
       <c r="T75">
         <f t="shared" si="3"/>
@@ -5140,62 +5181,59 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B76" t="s">
         <v>20</v>
       </c>
       <c r="C76">
-        <v>10.590547000000001</v>
+        <v>5.8267310999999999</v>
       </c>
       <c r="D76">
-        <v>9.8000000000000004E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E76">
-        <v>0.91890603000000004</v>
+        <v>0.57186287999999996</v>
       </c>
       <c r="F76">
-        <v>0.18469084999999999</v>
+        <v>0.24698861999999999</v>
       </c>
       <c r="G76">
-        <v>947</v>
-      </c>
-      <c r="H76" t="s">
-        <v>130</v>
+        <v>1439</v>
       </c>
       <c r="I76">
-        <v>6000</v>
+        <v>6110</v>
       </c>
       <c r="J76">
-        <v>1.0509999999999999</v>
+        <v>1.6479999999999999</v>
       </c>
       <c r="K76">
-        <v>1.1459999999999999</v>
+        <v>1.2909999999999999</v>
       </c>
       <c r="L76">
-        <v>0.09</v>
+        <v>0.124</v>
       </c>
       <c r="M76">
-        <v>4.4400000000000004</v>
+        <v>4.1180000000000003</v>
       </c>
       <c r="N76">
-        <v>161.87955690000001</v>
+        <v>51.657269100000001</v>
       </c>
       <c r="O76">
-        <v>36.329434499999998</v>
+        <v>40.817270399999998</v>
       </c>
       <c r="P76">
-        <v>130.85499999999999</v>
+        <v>179.14699999999999</v>
       </c>
       <c r="Q76">
-        <v>10.058999999999999</v>
+        <v>9.9130000000000003</v>
       </c>
       <c r="R76">
-        <v>9.9823299999999993</v>
+        <v>9.7295700000000007</v>
       </c>
       <c r="S76">
         <f t="shared" si="2"/>
-        <v>1107.9861243219782</v>
+        <v>487.59044264912109</v>
       </c>
       <c r="T76">
         <f t="shared" si="3"/>
@@ -5204,59 +5242,62 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B77" t="s">
         <v>20</v>
       </c>
       <c r="C77">
-        <v>5.8267310999999999</v>
+        <v>6.4025129999999999</v>
       </c>
       <c r="D77">
-        <v>6.9000000000000006E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="E77">
-        <v>0.57186287999999996</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="F77">
-        <v>0.24698861999999999</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G77">
-        <v>1439</v>
+        <v>1388</v>
+      </c>
+      <c r="H77" t="s">
+        <v>63</v>
       </c>
       <c r="I77">
-        <v>6110</v>
+        <v>6400</v>
       </c>
       <c r="J77">
-        <v>1.6479999999999999</v>
+        <v>1.415</v>
       </c>
       <c r="K77">
-        <v>1.2909999999999999</v>
+        <v>1.3129999999999999</v>
       </c>
       <c r="L77">
-        <v>0.124</v>
+        <v>0.09</v>
       </c>
       <c r="M77">
-        <v>4.1180000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="N77">
-        <v>51.657269100000001</v>
+        <v>125.3050544</v>
       </c>
       <c r="O77">
-        <v>40.817270399999998</v>
+        <v>-46.484295899999999</v>
       </c>
       <c r="P77">
-        <v>179.14699999999999</v>
+        <v>123.297</v>
       </c>
       <c r="Q77">
-        <v>9.9130000000000003</v>
+        <v>8.9949999999999992</v>
       </c>
       <c r="R77">
-        <v>9.7295700000000007</v>
+        <v>8.8910300000000007</v>
       </c>
       <c r="S77">
         <f t="shared" si="2"/>
-        <v>487.59044264912109</v>
+        <v>795.95548671567838</v>
       </c>
       <c r="T77">
         <f t="shared" si="3"/>
@@ -5265,62 +5306,62 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="B78" t="s">
         <v>20</v>
       </c>
       <c r="C78">
-        <v>6.4025129999999999</v>
+        <v>11.236598499999999</v>
       </c>
       <c r="D78">
-        <v>7.0800000000000002E-2</v>
+        <v>0.1041</v>
       </c>
       <c r="E78">
-        <v>0.82399999999999995</v>
+        <v>1.17</v>
       </c>
       <c r="F78">
-        <v>0.30299999999999999</v>
+        <v>1.234</v>
       </c>
       <c r="G78">
-        <v>1388</v>
+        <v>1252</v>
       </c>
       <c r="H78" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I78">
-        <v>6400</v>
+        <v>6295</v>
       </c>
       <c r="J78">
-        <v>1.415</v>
+        <v>1.28</v>
       </c>
       <c r="K78">
-        <v>1.3129999999999999</v>
+        <v>1.181</v>
       </c>
       <c r="L78">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>4.2</v>
+        <v>4.2910000000000004</v>
       </c>
       <c r="N78">
-        <v>125.3050544</v>
+        <v>144.11935940000001</v>
       </c>
       <c r="O78">
-        <v>-46.484295899999999</v>
+        <v>-50.463093299999997</v>
       </c>
       <c r="P78">
-        <v>123.297</v>
+        <v>141.81200000000001</v>
       </c>
       <c r="Q78">
-        <v>8.9949999999999992</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R78">
-        <v>8.8910300000000007</v>
+        <v>9.6608199999999993</v>
       </c>
       <c r="S78">
         <f t="shared" si="2"/>
-        <v>795.95548671567838</v>
+        <v>355.42536038318485</v>
       </c>
       <c r="T78">
         <f t="shared" si="3"/>
@@ -5329,62 +5370,62 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
         <v>20</v>
       </c>
       <c r="C79">
-        <v>11.236598499999999</v>
+        <v>4.6336110000000001</v>
       </c>
       <c r="D79">
-        <v>0.1041</v>
+        <v>0.06</v>
       </c>
       <c r="E79">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="F79">
-        <v>1.234</v>
+        <v>2.8</v>
       </c>
       <c r="G79">
-        <v>1252</v>
+        <v>1561</v>
       </c>
       <c r="H79" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="I79">
-        <v>6295</v>
+        <v>6643</v>
       </c>
       <c r="J79">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="K79">
-        <v>1.181</v>
+        <v>1.4</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79">
-        <v>4.2910000000000004</v>
+        <v>4.05</v>
       </c>
       <c r="N79">
-        <v>144.11935940000001</v>
+        <v>199.33385029999999</v>
       </c>
       <c r="O79">
-        <v>-50.463093299999997</v>
+        <v>-15.2737046</v>
       </c>
       <c r="P79">
-        <v>141.81200000000001</v>
+        <v>161.74299999999999</v>
       </c>
       <c r="Q79">
-        <v>9.8219999999999992</v>
+        <v>9.109</v>
       </c>
       <c r="R79">
-        <v>9.6608199999999993</v>
+        <v>8.9943600000000004</v>
       </c>
       <c r="S79">
         <f t="shared" si="2"/>
-        <v>355.42536038318485</v>
+        <v>267.77715667890726</v>
       </c>
       <c r="T79">
         <f t="shared" si="3"/>
@@ -5393,188 +5434,188 @@
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>65</v>
-      </c>
-      <c r="B80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80">
-        <v>4.6336110000000001</v>
-      </c>
-      <c r="D80">
-        <v>0.06</v>
-      </c>
-      <c r="E80">
-        <v>1.37</v>
-      </c>
-      <c r="F80">
-        <v>2.8</v>
-      </c>
-      <c r="G80">
-        <v>1561</v>
-      </c>
-      <c r="H80" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="I80">
-        <v>6643</v>
+        <v>6161.02294921875</v>
       </c>
       <c r="J80">
-        <v>1.71</v>
+        <v>1.7061723470687871</v>
       </c>
       <c r="K80">
-        <v>1.4</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
+        <v>1.3463604</v>
       </c>
       <c r="M80">
-        <v>4.05</v>
+        <v>3.9825000762939449</v>
       </c>
       <c r="N80">
-        <v>199.33385029999999</v>
+        <v>268.30433503422898</v>
       </c>
       <c r="O80">
-        <v>-15.2737046</v>
+        <v>37.211736733677057</v>
       </c>
       <c r="P80">
-        <v>161.74299999999999</v>
+        <v>496.26729999999998</v>
       </c>
       <c r="Q80">
-        <v>9.109</v>
+        <v>11.469913482666019</v>
       </c>
       <c r="R80">
-        <v>8.9943600000000004</v>
-      </c>
-      <c r="S80">
-        <f t="shared" si="2"/>
-        <v>267.77715667890726</v>
-      </c>
-      <c r="T80">
-        <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>11.469913482666019</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>138</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
       </c>
       <c r="I81">
-        <v>6161.02294921875</v>
+        <v>6200</v>
       </c>
       <c r="J81">
-        <v>1.7061723470687871</v>
-      </c>
-      <c r="K81">
-        <v>1.3463604</v>
-      </c>
-      <c r="M81">
-        <v>3.9825000762939449</v>
+        <v>1.2</v>
       </c>
       <c r="N81">
-        <v>268.30433503422898</v>
+        <v>97.636728000000005</v>
       </c>
       <c r="O81">
-        <v>37.211736733677057</v>
+        <v>29.672419000000001</v>
       </c>
       <c r="P81">
-        <v>496.26729999999998</v>
-      </c>
-      <c r="Q81">
-        <v>11.469913482666019</v>
+        <v>427</v>
       </c>
       <c r="R81">
-        <v>11.469913482666019</v>
+        <v>11.4986</v>
+      </c>
+      <c r="T81">
+        <f t="shared" ref="T81:T101" si="4">IF(I81&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
         <v>20</v>
       </c>
+      <c r="C82">
+        <v>5.3220124999999996</v>
+      </c>
+      <c r="D82">
+        <v>6.08E-2</v>
+      </c>
+      <c r="E82">
+        <v>1.226</v>
+      </c>
+      <c r="F82">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="G82">
+        <v>1460</v>
+      </c>
+      <c r="H82" t="s">
+        <v>43</v>
+      </c>
       <c r="I82">
-        <v>6200</v>
+        <v>5990</v>
       </c>
       <c r="J82">
-        <v>1.2</v>
+        <v>1.5609999999999999</v>
+      </c>
+      <c r="K82">
+        <v>1.06</v>
+      </c>
+      <c r="L82">
+        <v>-0.2</v>
+      </c>
+      <c r="M82">
+        <v>4.0750000000000002</v>
       </c>
       <c r="N82">
-        <v>97.636728000000005</v>
+        <v>210.1935714</v>
       </c>
       <c r="O82">
-        <v>29.672419000000001</v>
+        <v>-30.583608399999999</v>
       </c>
       <c r="P82">
-        <v>427</v>
+        <v>200.07499999999999</v>
+      </c>
+      <c r="Q82">
+        <v>10.068</v>
       </c>
       <c r="R82">
-        <v>11.4986</v>
+        <v>9.8670799999999996</v>
+      </c>
+      <c r="S82">
+        <f t="shared" ref="S82:S101" si="5">(0.000000000000000138*G82/(1.673534E-24*1.3*0.000000066726*F82*1.8986E+30/(E82*7149200000)^2))/100000</f>
+        <v>2057.1154637812851</v>
       </c>
       <c r="T82">
-        <f t="shared" ref="T82:T102" si="4">IF(I82&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B83" t="s">
         <v>20</v>
       </c>
       <c r="C83">
-        <v>5.3220124999999996</v>
+        <v>5.21536178778</v>
       </c>
       <c r="D83">
-        <v>6.08E-2</v>
+        <v>6.6100000000000006E-2</v>
       </c>
       <c r="E83">
-        <v>1.226</v>
+        <v>1.5</v>
       </c>
       <c r="F83">
-        <v>0.27300000000000002</v>
+        <v>1.51</v>
       </c>
       <c r="G83">
-        <v>1460</v>
+        <v>1630</v>
       </c>
       <c r="H83" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I83">
-        <v>5990</v>
+        <v>6250</v>
       </c>
       <c r="J83">
-        <v>1.5609999999999999</v>
+        <v>2.3901400000000002</v>
       </c>
       <c r="K83">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="L83">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="M83">
-        <v>4.0750000000000002</v>
+        <v>3.9</v>
       </c>
       <c r="N83">
-        <v>210.1935714</v>
+        <v>0.32576100000000002</v>
       </c>
       <c r="O83">
-        <v>-30.583608399999999</v>
+        <v>-8.9262511999999994</v>
       </c>
       <c r="P83">
-        <v>200.07499999999999</v>
+        <v>275.58699999999999</v>
       </c>
       <c r="Q83">
-        <v>10.068</v>
+        <v>9.9740000000000002</v>
       </c>
       <c r="R83">
-        <v>9.8670799999999996</v>
+        <v>9.8192900000000005</v>
       </c>
       <c r="S83">
-        <f t="shared" ref="S83:S102" si="5">(0.000000000000000138*G83/(1.673534E-24*1.3*0.000000066726*F83*1.8986E+30/(E83*7149200000)^2))/100000</f>
-        <v>2057.1154637812851</v>
+        <f t="shared" si="5"/>
+        <v>621.55661806820979</v>
       </c>
       <c r="T83">
         <f t="shared" si="4"/>
@@ -5583,62 +5624,59 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="B84" t="s">
         <v>20</v>
       </c>
       <c r="C84">
-        <v>5.21536178778</v>
+        <v>2.2437499999999999</v>
       </c>
       <c r="D84">
-        <v>6.6100000000000006E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E84">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="F84">
-        <v>1.51</v>
+        <v>8.84</v>
       </c>
       <c r="G84">
-        <v>1630</v>
-      </c>
-      <c r="H84" t="s">
-        <v>56</v>
+        <v>1872</v>
       </c>
       <c r="I84">
-        <v>6250</v>
+        <v>6475</v>
       </c>
       <c r="J84">
-        <v>2.3901400000000002</v>
+        <v>1.4</v>
       </c>
       <c r="K84">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="L84">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="N84">
-        <v>0.32576100000000002</v>
+        <v>218.27662470000001</v>
       </c>
       <c r="O84">
-        <v>-8.9262511999999994</v>
+        <v>21.8946875</v>
       </c>
       <c r="P84">
-        <v>275.58699999999999</v>
+        <v>161.99700000000001</v>
       </c>
       <c r="Q84">
-        <v>9.9740000000000002</v>
+        <v>9.7449999999999992</v>
       </c>
       <c r="R84">
-        <v>9.8192900000000005</v>
+        <v>9.6464700000000008</v>
       </c>
       <c r="S84">
         <f t="shared" si="5"/>
-        <v>621.55661806820979</v>
+        <v>103.20465157174387</v>
       </c>
       <c r="T84">
         <f t="shared" si="4"/>
@@ -5647,59 +5685,62 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B85" t="s">
         <v>20</v>
       </c>
       <c r="C85">
-        <v>2.2437499999999999</v>
+        <v>5.4435399999999996</v>
       </c>
       <c r="D85">
-        <v>3.6999999999999998E-2</v>
+        <v>6.4100000000000004E-2</v>
       </c>
       <c r="E85">
-        <v>1.38</v>
+        <v>0.63</v>
       </c>
       <c r="F85">
-        <v>8.84</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G85">
-        <v>1872</v>
+        <v>1270</v>
+      </c>
+      <c r="H85" t="s">
+        <v>74</v>
       </c>
       <c r="I85">
-        <v>6475</v>
+        <v>6050</v>
       </c>
       <c r="J85">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="K85">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="M85">
-        <v>4.07</v>
+        <v>4.34</v>
       </c>
       <c r="N85">
-        <v>218.27662470000001</v>
+        <v>144.87510470000001</v>
       </c>
       <c r="O85">
-        <v>21.8946875</v>
+        <v>-20.982419100000001</v>
       </c>
       <c r="P85">
-        <v>161.99700000000001</v>
+        <v>114.173</v>
       </c>
       <c r="Q85">
-        <v>9.7449999999999992</v>
+        <v>9.3510000000000009</v>
       </c>
       <c r="R85">
-        <v>9.6464700000000008</v>
+        <v>9.2569999999999997</v>
       </c>
       <c r="S85">
         <f t="shared" si="5"/>
-        <v>103.20465157174387</v>
+        <v>1277.1766379712274</v>
       </c>
       <c r="T85">
         <f t="shared" si="4"/>
@@ -5708,510 +5749,510 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="B86" t="s">
         <v>20</v>
       </c>
       <c r="C86">
-        <v>5.4435399999999996</v>
+        <v>3.3448285000000002</v>
       </c>
       <c r="D86">
-        <v>6.4100000000000004E-2</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="E86">
-        <v>0.63</v>
+        <v>1.81</v>
       </c>
       <c r="F86">
-        <v>0.10100000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="G86">
-        <v>1270</v>
+        <v>2470</v>
       </c>
       <c r="H86" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="I86">
-        <v>6050</v>
+        <v>9360</v>
       </c>
       <c r="J86">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="K86">
-        <v>1.19</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L86">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="M86">
-        <v>4.34</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N86">
-        <v>144.87510470000001</v>
+        <v>227.270329</v>
       </c>
       <c r="O86">
-        <v>-20.982419100000001</v>
+        <v>-42.704965799999997</v>
       </c>
       <c r="P86">
-        <v>114.173</v>
+        <v>427.678</v>
       </c>
       <c r="Q86">
-        <v>9.3510000000000009</v>
+        <v>9.9459999999999997</v>
       </c>
       <c r="R86">
-        <v>9.2569999999999997</v>
+        <v>9.9122599999999998</v>
       </c>
       <c r="S86">
         <f t="shared" si="5"/>
-        <v>1277.1766379712274</v>
+        <v>1247.4798366438731</v>
       </c>
       <c r="T86">
         <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="B87" t="s">
         <v>20</v>
       </c>
       <c r="C87">
-        <v>3.3448285000000002</v>
+        <v>0.94145223</v>
       </c>
       <c r="D87">
-        <v>5.5800000000000002E-2</v>
+        <v>2.0240000000000001E-2</v>
       </c>
       <c r="E87">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="F87">
-        <v>1.66</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G87">
-        <v>2470</v>
+        <v>2429</v>
       </c>
       <c r="H87" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="I87">
-        <v>9360</v>
+        <v>6432</v>
       </c>
       <c r="J87">
-        <v>1.67</v>
+        <v>1.319</v>
       </c>
       <c r="K87">
-        <v>2.0699999999999998</v>
+        <v>1.294</v>
       </c>
       <c r="L87">
-        <v>0.21</v>
+        <v>0.107</v>
       </c>
       <c r="M87">
         <v>4.3099999999999996</v>
       </c>
       <c r="N87">
-        <v>227.270329</v>
+        <v>24.354461799999999</v>
       </c>
       <c r="O87">
-        <v>-42.704965799999997</v>
+        <v>-45.677793700000002</v>
       </c>
       <c r="P87">
-        <v>427.678</v>
+        <v>123.483</v>
       </c>
       <c r="Q87">
-        <v>9.9459999999999997</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R87">
-        <v>9.9122599999999998</v>
+        <v>9.1661699999999993</v>
       </c>
       <c r="S87">
         <f t="shared" si="5"/>
-        <v>1247.4798366438731</v>
+        <v>93.704022194109143</v>
       </c>
       <c r="T87">
         <f t="shared" si="4"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="B88" t="s">
         <v>20</v>
       </c>
       <c r="C88">
-        <v>0.94145223</v>
+        <v>2.7240329999999999</v>
       </c>
       <c r="D88">
-        <v>2.0240000000000001E-2</v>
+        <v>5.0529999999999999E-2</v>
       </c>
       <c r="E88">
-        <v>1.24</v>
+        <v>1.619</v>
       </c>
       <c r="F88">
-        <v>10.199999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="G88">
-        <v>2429</v>
-      </c>
-      <c r="H88" t="s">
-        <v>72</v>
+        <v>3353</v>
       </c>
       <c r="I88">
-        <v>6432</v>
+        <v>8000</v>
       </c>
       <c r="J88">
-        <v>1.319</v>
+        <v>2.36</v>
       </c>
       <c r="K88">
-        <v>1.294</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="L88">
-        <v>0.107</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M88">
-        <v>4.3099999999999996</v>
+        <v>3.9</v>
       </c>
       <c r="N88">
-        <v>24.354461799999999</v>
+        <v>225.68673200000001</v>
       </c>
       <c r="O88">
-        <v>-45.677793700000002</v>
+        <v>-3.0314874000000001</v>
       </c>
       <c r="P88">
-        <v>123.483</v>
+        <v>99.730999999999995</v>
       </c>
       <c r="Q88">
-        <v>9.2799999999999994</v>
+        <v>6.5977600000000001</v>
       </c>
       <c r="R88">
-        <v>9.1661699999999993</v>
-      </c>
-      <c r="S88">
+        <v>6.5536899999999996</v>
+      </c>
+      <c r="S88" s="6">
         <f t="shared" si="5"/>
-        <v>93.704022194109143</v>
+        <v>1130.2166328238993</v>
       </c>
       <c r="T88">
         <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>-7</v>
+      </c>
+      <c r="U88" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B89" t="s">
         <v>20</v>
       </c>
       <c r="C89">
-        <v>2.7240329999999999</v>
+        <v>1.21987</v>
       </c>
       <c r="D89">
-        <v>5.0529999999999999E-2</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="E89">
-        <v>1.619</v>
+        <v>1.593</v>
       </c>
       <c r="F89">
-        <v>1.99</v>
+        <v>2.093</v>
       </c>
       <c r="G89">
-        <v>3353</v>
+        <v>2781.7</v>
+      </c>
+      <c r="H89" t="s">
+        <v>41</v>
       </c>
       <c r="I89">
-        <v>8000</v>
+        <v>7430</v>
       </c>
       <c r="J89">
-        <v>2.36</v>
+        <v>1.444</v>
       </c>
       <c r="K89">
-        <v>2.0299999999999998</v>
+        <v>1.4950000000000001</v>
       </c>
       <c r="L89">
-        <v>0.28999999999999998</v>
+        <v>0.1</v>
       </c>
       <c r="M89">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="N89">
-        <v>225.68673200000001</v>
+        <v>36.712737500000003</v>
       </c>
       <c r="O89">
-        <v>-3.0314874000000001</v>
+        <v>37.5504441</v>
       </c>
       <c r="P89">
-        <v>99.730999999999995</v>
+        <v>121.944</v>
       </c>
       <c r="Q89">
-        <v>6.5977600000000001</v>
+        <v>8.14</v>
       </c>
       <c r="R89">
-        <v>6.5536899999999996</v>
-      </c>
-      <c r="S89" s="6">
+        <v>8.0700400000000005</v>
+      </c>
+      <c r="S89">
         <f t="shared" si="5"/>
-        <v>1130.2166328238993</v>
+        <v>863.09804630713359</v>
       </c>
       <c r="T89">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
-      <c r="U89" s="1" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B90" t="s">
         <v>20</v>
       </c>
       <c r="C90">
-        <v>1.21987</v>
+        <v>6.87188</v>
       </c>
       <c r="D90">
-        <v>2.3900000000000001E-2</v>
+        <v>7.5219999999999995E-2</v>
       </c>
       <c r="E90">
-        <v>1.593</v>
+        <v>1.23</v>
       </c>
       <c r="F90">
-        <v>2.093</v>
+        <v>3.44</v>
       </c>
       <c r="G90">
-        <v>2781.7</v>
+        <v>1250</v>
       </c>
       <c r="H90" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="I90">
-        <v>7430</v>
+        <v>6180</v>
       </c>
       <c r="J90">
-        <v>1.444</v>
+        <v>1.52</v>
       </c>
       <c r="K90">
-        <v>1.4950000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="L90">
-        <v>0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="M90">
         <v>4.25</v>
       </c>
       <c r="N90">
-        <v>36.712737500000003</v>
+        <v>243.95971940000001</v>
       </c>
       <c r="O90">
-        <v>37.5504441</v>
+        <v>10.0324103</v>
       </c>
       <c r="P90">
-        <v>121.944</v>
+        <v>136.24</v>
       </c>
       <c r="Q90">
-        <v>8.14</v>
+        <v>9.391</v>
       </c>
       <c r="R90">
-        <v>8.0700400000000005</v>
+        <v>9.20974</v>
       </c>
       <c r="S90">
         <f t="shared" si="5"/>
-        <v>863.09804630713359</v>
+        <v>140.68549179703928</v>
       </c>
       <c r="T90">
         <f t="shared" si="4"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="B91" t="s">
         <v>20</v>
       </c>
       <c r="C91">
-        <v>6.87188</v>
+        <v>3.86813881</v>
       </c>
       <c r="D91">
-        <v>7.5219999999999995E-2</v>
+        <v>4.53E-2</v>
       </c>
       <c r="E91">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>3.44</v>
+        <v>0.26</v>
       </c>
       <c r="G91">
-        <v>1250</v>
+        <v>971</v>
       </c>
       <c r="H91" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="I91">
-        <v>6180</v>
+        <v>4792</v>
       </c>
       <c r="J91">
-        <v>1.52</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="K91">
-        <v>1.76</v>
+        <v>0.83</v>
       </c>
       <c r="L91">
-        <v>-0.02</v>
+        <v>0.35</v>
       </c>
       <c r="M91">
-        <v>4.25</v>
+        <v>4.57</v>
       </c>
       <c r="N91">
-        <v>243.95971940000001</v>
+        <v>315.02596610000001</v>
       </c>
       <c r="O91">
-        <v>10.0324103</v>
+        <v>-5.0948570000000002</v>
       </c>
       <c r="P91">
-        <v>136.24</v>
+        <v>49.960500000000003</v>
       </c>
       <c r="Q91">
-        <v>9.391</v>
+        <v>9.8729999999999993</v>
       </c>
       <c r="R91">
-        <v>9.20974</v>
+        <v>9.4846599999999999</v>
       </c>
       <c r="S91">
         <f t="shared" si="5"/>
-        <v>140.68549179703928</v>
+        <v>955.72600175951948</v>
       </c>
       <c r="T91">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
+      <c r="U91" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="B92" t="s">
         <v>20</v>
       </c>
       <c r="C92">
-        <v>3.86813881</v>
+        <v>4.9546416000000004</v>
       </c>
       <c r="D92">
-        <v>4.53E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="F92">
-        <v>0.26</v>
+        <v>0.96</v>
       </c>
       <c r="G92">
-        <v>971</v>
-      </c>
-      <c r="H92" t="s">
-        <v>113</v>
+        <v>1487</v>
       </c>
       <c r="I92">
-        <v>4792</v>
+        <v>6400</v>
       </c>
       <c r="J92">
-        <v>0.80100000000000005</v>
+        <v>1.4319999999999999</v>
       </c>
       <c r="K92">
-        <v>0.83</v>
+        <v>1.276</v>
       </c>
       <c r="L92">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="M92">
-        <v>4.57</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="N92">
-        <v>315.02596610000001</v>
+        <v>311.04275580000001</v>
       </c>
       <c r="O92">
-        <v>-5.0948570000000002</v>
+        <v>-39.225485599999999</v>
       </c>
       <c r="P92">
-        <v>49.960500000000003</v>
+        <v>162.303</v>
       </c>
       <c r="Q92">
-        <v>9.8729999999999993</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="R92">
-        <v>9.4846599999999999</v>
+        <v>9.3767099999999992</v>
       </c>
       <c r="S92">
         <f t="shared" si="5"/>
-        <v>955.72600175951948</v>
+        <v>701.18164217622461</v>
       </c>
       <c r="T92">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
-      <c r="U92" s="1" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B93" t="s">
         <v>20</v>
       </c>
       <c r="C93">
-        <v>4.9546416000000004</v>
+        <v>2.13775</v>
       </c>
       <c r="D93">
-        <v>6.1699999999999998E-2</v>
+        <v>3.4430000000000002E-2</v>
       </c>
       <c r="E93">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="F93">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="G93">
-        <v>1487</v>
+        <v>1865</v>
+      </c>
+      <c r="H93" t="s">
+        <v>91</v>
       </c>
       <c r="I93">
-        <v>6400</v>
+        <v>5990</v>
       </c>
       <c r="J93">
-        <v>1.4319999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="K93">
-        <v>1.276</v>
+        <v>0.98</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="M93">
-        <v>4.2320000000000002</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="N93">
-        <v>311.04275580000001</v>
+        <v>304.53884299999999</v>
       </c>
       <c r="O93">
-        <v>-39.225485599999999</v>
+        <v>-1.0760033</v>
       </c>
       <c r="P93">
-        <v>162.303</v>
+        <v>149.21600000000001</v>
       </c>
       <c r="Q93">
-        <v>9.5039999999999996</v>
+        <v>9.75</v>
       </c>
       <c r="R93">
-        <v>9.3767099999999992</v>
+        <v>9.5723000000000003</v>
       </c>
       <c r="S93">
         <f t="shared" si="5"/>
-        <v>701.18164217622461</v>
+        <v>1226.0598654781754</v>
       </c>
       <c r="T93">
         <f t="shared" si="4"/>
@@ -6220,62 +6261,62 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
       </c>
       <c r="C94">
-        <v>2.13775</v>
+        <v>1.8098819799999999</v>
       </c>
       <c r="D94">
-        <v>3.4430000000000002E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="E94">
-        <v>1.36</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="F94">
-        <v>0.72</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G94">
-        <v>1865</v>
+        <v>2228</v>
       </c>
       <c r="H94" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="I94">
-        <v>5990</v>
+        <v>6329</v>
       </c>
       <c r="J94">
-        <v>1.42</v>
+        <v>1.756</v>
       </c>
       <c r="K94">
-        <v>0.98</v>
+        <v>1.458</v>
       </c>
       <c r="L94">
-        <v>0.39</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M94">
-        <v>4.3899999999999997</v>
+        <v>4.1959999999999997</v>
       </c>
       <c r="N94">
-        <v>304.53884299999999</v>
+        <v>26.632936000000001</v>
       </c>
       <c r="O94">
-        <v>-1.0760033</v>
+        <v>2.7003889999999999</v>
       </c>
       <c r="P94">
-        <v>149.21600000000001</v>
+        <v>194.459</v>
       </c>
       <c r="Q94">
-        <v>9.75</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="R94">
-        <v>9.5723000000000003</v>
+        <v>9.3950700000000005</v>
       </c>
       <c r="S94">
         <f t="shared" si="5"/>
-        <v>1226.0598654781754</v>
+        <v>2192.2225820487197</v>
       </c>
       <c r="T94">
         <f t="shared" si="4"/>
@@ -6284,62 +6325,62 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B95" t="s">
         <v>20</v>
       </c>
       <c r="C95">
-        <v>1.8098819799999999</v>
+        <v>3.6623920000000001</v>
       </c>
       <c r="D95">
-        <v>3.3000000000000002E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
       <c r="E95">
-        <v>1.8540000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="F95">
-        <v>0.89400000000000002</v>
+        <v>0.85</v>
       </c>
       <c r="G95">
-        <v>2228</v>
+        <v>1716.2</v>
       </c>
       <c r="H95" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="I95">
-        <v>6329</v>
+        <v>6600</v>
       </c>
       <c r="J95">
-        <v>1.756</v>
+        <v>1.51</v>
       </c>
       <c r="K95">
-        <v>1.458</v>
+        <v>1.39</v>
       </c>
       <c r="L95">
-        <v>0.36599999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="M95">
-        <v>4.1959999999999997</v>
+        <v>4.2</v>
       </c>
       <c r="N95">
-        <v>26.632936000000001</v>
+        <v>66.370901599999996</v>
       </c>
       <c r="O95">
-        <v>2.7003889999999999</v>
+        <v>-30.600436200000001</v>
       </c>
       <c r="P95">
-        <v>194.459</v>
+        <v>246.69</v>
       </c>
       <c r="Q95">
-        <v>9.5180000000000007</v>
+        <v>10.044</v>
       </c>
       <c r="R95">
-        <v>9.3950700000000005</v>
+        <v>9.9720200000000006</v>
       </c>
       <c r="S95">
         <f t="shared" si="5"/>
-        <v>2192.2225820487197</v>
+        <v>1209.5375438309629</v>
       </c>
       <c r="T95">
         <f t="shared" si="4"/>
@@ -6348,62 +6389,62 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
         <v>20</v>
       </c>
       <c r="C96">
-        <v>3.6623920000000001</v>
+        <v>8.1587200000000006</v>
       </c>
       <c r="D96">
-        <v>5.1900000000000002E-2</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="E96">
-        <v>1.53</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F96">
-        <v>0.85</v>
+        <v>2.54</v>
       </c>
       <c r="G96">
-        <v>1716.2</v>
+        <v>1059</v>
       </c>
       <c r="H96" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="I96">
-        <v>6600</v>
+        <v>5600</v>
       </c>
       <c r="J96">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="K96">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="L96">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="M96">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="N96">
-        <v>66.370901599999996</v>
+        <v>359.90087369999998</v>
       </c>
       <c r="O96">
-        <v>-30.600436200000001</v>
+        <v>-35.031334899999997</v>
       </c>
       <c r="P96">
-        <v>246.69</v>
+        <v>89.960599999999999</v>
       </c>
       <c r="Q96">
-        <v>10.044</v>
+        <v>9.7889999999999997</v>
       </c>
       <c r="R96">
-        <v>9.9720200000000006</v>
+        <v>9.6124899999999993</v>
       </c>
       <c r="S96">
         <f t="shared" si="5"/>
-        <v>1209.5375438309629</v>
+        <v>136.24063220140397</v>
       </c>
       <c r="T96">
         <f t="shared" si="4"/>
@@ -6412,62 +6453,62 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
         <v>20</v>
       </c>
       <c r="C97">
-        <v>8.1587200000000006</v>
+        <v>2.7057899999999999</v>
       </c>
       <c r="D97">
-        <v>8.0100000000000005E-2</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E97">
-        <v>1.1299999999999999</v>
+        <v>1.62</v>
       </c>
       <c r="F97">
-        <v>2.54</v>
+        <v>1.17</v>
       </c>
       <c r="G97">
-        <v>1059</v>
+        <v>2190</v>
       </c>
       <c r="H97" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="I97">
-        <v>5600</v>
+        <v>6480</v>
       </c>
       <c r="J97">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="K97">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="L97">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="M97">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="N97">
-        <v>359.90087369999998</v>
+        <v>72.660591600000004</v>
       </c>
       <c r="O97">
-        <v>-35.031334899999997</v>
+        <v>1.8938364999999999</v>
       </c>
       <c r="P97">
-        <v>89.960599999999999</v>
+        <v>275.66399999999999</v>
       </c>
       <c r="Q97">
-        <v>9.7889999999999997</v>
+        <v>10.073</v>
       </c>
       <c r="R97">
-        <v>9.6124899999999993</v>
+        <v>9.8979599999999994</v>
       </c>
       <c r="S97">
         <f t="shared" si="5"/>
-        <v>136.24063220140397</v>
+        <v>1257.117296864338</v>
       </c>
       <c r="T97">
         <f t="shared" si="4"/>
@@ -6476,62 +6517,62 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B98" t="s">
         <v>20</v>
       </c>
       <c r="C98">
-        <v>2.7057899999999999</v>
+        <v>3.9501900000000001</v>
       </c>
       <c r="D98">
-        <v>4.4699999999999997E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E98">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="F98">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="G98">
-        <v>2190</v>
+        <v>1604</v>
       </c>
       <c r="H98" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="I98">
-        <v>6480</v>
+        <v>6170</v>
       </c>
       <c r="J98">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="K98">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="L98">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="M98">
-        <v>3.96</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="N98">
-        <v>72.660591600000004</v>
+        <v>313.78323929999999</v>
       </c>
       <c r="O98">
-        <v>1.8938364999999999</v>
+        <v>-34.135751200000001</v>
       </c>
       <c r="P98">
-        <v>275.66399999999999</v>
+        <v>211.21100000000001</v>
       </c>
       <c r="Q98">
-        <v>10.073</v>
+        <v>10.051</v>
       </c>
       <c r="R98">
-        <v>9.8979599999999994</v>
+        <v>10.028499999999999</v>
       </c>
       <c r="S98">
         <f t="shared" si="5"/>
-        <v>1257.117296864338</v>
+        <v>2049.4439875099679</v>
       </c>
       <c r="T98">
         <f t="shared" si="4"/>
@@ -6540,62 +6581,62 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B99" t="s">
         <v>20</v>
       </c>
       <c r="C99">
-        <v>3.9501900000000001</v>
+        <v>2.1846700000000001</v>
       </c>
       <c r="D99">
-        <v>5.5E-2</v>
+        <v>3.4160000000000003E-2</v>
       </c>
       <c r="E99">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="F99">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="G99">
-        <v>1604</v>
+        <v>1570</v>
       </c>
       <c r="H99" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="I99">
-        <v>6170</v>
+        <v>5830</v>
       </c>
       <c r="J99">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="K99">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="L99">
-        <v>0.26</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M99">
-        <v>4.2699999999999996</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N99">
-        <v>313.78323929999999</v>
+        <v>337.45782430000003</v>
       </c>
       <c r="O99">
-        <v>-34.135751200000001</v>
+        <v>-48.003098799999997</v>
       </c>
       <c r="P99">
-        <v>211.21100000000001</v>
+        <v>137.54400000000001</v>
       </c>
       <c r="Q99">
-        <v>10.051</v>
+        <v>10.092000000000001</v>
       </c>
       <c r="R99">
-        <v>10.028499999999999</v>
+        <v>9.9369700000000005</v>
       </c>
       <c r="S99">
         <f t="shared" si="5"/>
-        <v>2049.4439875099679</v>
+        <v>422.11900227636102</v>
       </c>
       <c r="T99">
         <f t="shared" si="4"/>
@@ -6604,62 +6645,62 @@
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="B100" t="s">
         <v>20</v>
       </c>
       <c r="C100">
-        <v>2.1846700000000001</v>
+        <v>5.75251</v>
       </c>
       <c r="D100">
-        <v>3.4160000000000003E-2</v>
+        <v>7.17E-2</v>
       </c>
       <c r="E100">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="F100">
-        <v>1.44</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="G100">
-        <v>1570</v>
+        <v>1480</v>
       </c>
       <c r="H100" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="I100">
-        <v>5830</v>
+        <v>6150</v>
       </c>
       <c r="J100">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="K100">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="L100">
-        <v>0.14000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="M100">
-        <v>4.3600000000000003</v>
+        <v>4.3</v>
       </c>
       <c r="N100">
-        <v>337.45782430000003</v>
+        <v>39.897668899999999</v>
       </c>
       <c r="O100">
-        <v>-48.003098799999997</v>
+        <v>-50.008193400000003</v>
       </c>
       <c r="P100">
-        <v>137.54400000000001</v>
+        <v>158.66</v>
       </c>
       <c r="Q100">
-        <v>10.092000000000001</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="R100">
-        <v>9.9369700000000005</v>
+        <v>9.3251000000000008</v>
       </c>
       <c r="S100">
         <f t="shared" si="5"/>
-        <v>422.11900227636102</v>
+        <v>162.15983922320817</v>
       </c>
       <c r="T100">
         <f t="shared" si="4"/>
@@ -6668,135 +6709,71 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
         <v>20</v>
       </c>
       <c r="C101">
-        <v>5.75251</v>
+        <v>3.1915399999999998</v>
       </c>
       <c r="D101">
-        <v>7.17E-2</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="E101">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="F101">
-        <v>2.4300000000000002</v>
+        <v>7.29</v>
       </c>
       <c r="G101">
-        <v>1480</v>
+        <v>1729</v>
       </c>
       <c r="H101" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="I101">
-        <v>6150</v>
+        <v>6429</v>
       </c>
       <c r="J101">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="K101">
-        <v>1.21</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L101">
-        <v>0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="M101">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N101">
-        <v>39.897668899999999</v>
+        <v>65.469581399999996</v>
       </c>
       <c r="O101">
-        <v>-50.008193400000003</v>
+        <v>57.817209499999997</v>
       </c>
       <c r="P101">
-        <v>158.66</v>
+        <v>213.053</v>
       </c>
       <c r="Q101">
-        <v>9.4749999999999996</v>
+        <v>9.8539999999999992</v>
       </c>
       <c r="R101">
-        <v>9.3251000000000008</v>
+        <v>9.7388899999999996</v>
       </c>
       <c r="S101">
         <f t="shared" si="5"/>
-        <v>162.15983922320817</v>
+        <v>120.66830436099001</v>
       </c>
       <c r="T101">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>107</v>
-      </c>
-      <c r="B102" t="s">
-        <v>20</v>
-      </c>
-      <c r="C102">
-        <v>3.1915399999999998</v>
-      </c>
-      <c r="D102">
-        <v>4.7600000000000003E-2</v>
-      </c>
-      <c r="E102">
-        <v>1.41</v>
-      </c>
-      <c r="F102">
-        <v>7.29</v>
-      </c>
-      <c r="G102">
-        <v>1729</v>
-      </c>
-      <c r="H102" t="s">
-        <v>108</v>
-      </c>
-      <c r="I102">
-        <v>6429</v>
-      </c>
-      <c r="J102">
-        <v>1.54</v>
-      </c>
-      <c r="K102">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="L102">
-        <v>-0.18</v>
-      </c>
-      <c r="M102">
-        <v>3.95</v>
-      </c>
-      <c r="N102">
-        <v>65.469581399999996</v>
-      </c>
-      <c r="O102">
-        <v>57.817209499999997</v>
-      </c>
-      <c r="P102">
-        <v>213.053</v>
-      </c>
-      <c r="Q102">
-        <v>9.8539999999999992</v>
-      </c>
-      <c r="R102">
-        <v>9.7388899999999996</v>
-      </c>
-      <c r="S102">
-        <f t="shared" si="5"/>
-        <v>120.66830436099001</v>
-      </c>
-      <c r="T102">
-        <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R79">
+  <autoFilter ref="A1:X101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R78">
     <sortCondition ref="Q2"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B23092-5FBC-B647-9913-098037DAD8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652170AF-4C9F-7F41-B460-9DDB174223D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53100" yWindow="14040" windowWidth="19620" windowHeight="13340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -930,15 +930,15 @@
     <col min="4" max="4" width="12.5" hidden="1" customWidth="1"/>
     <col min="5" max="6" width="11.1640625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="8.5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1640625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="12.1640625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="14" width="12.1640625" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.1640625" customWidth="1"/>
     <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.1640625" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="7" hidden="1" customWidth="1"/>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652170AF-4C9F-7F41-B460-9DDB174223D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F811CB-D2E3-EA4F-BD56-C7A07385F396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$X$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$X$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
   <si>
     <t>#pl_name</t>
   </si>
@@ -459,12 +459,6 @@
   </si>
   <si>
     <t>HAT-P-7 b</t>
-  </si>
-  <si>
-    <t>Kepler-13 b</t>
-  </si>
-  <si>
-    <t>TrES-4 b</t>
   </si>
   <si>
     <t>B9.5-A0</t>
@@ -921,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC101"/>
+  <dimension ref="A1:BC99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -1025,18 +1019,18 @@
         <v>136</v>
       </c>
       <c r="V1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I2">
         <v>3501</v>
@@ -1069,7 +1063,7 @@
         <v>12.885999999999999</v>
       </c>
       <c r="X2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AZ2" s="3"/>
       <c r="BB2" s="3"/>
@@ -1077,7 +1071,7 @@
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I3">
         <v>3496</v>
@@ -1110,7 +1104,7 @@
         <v>12.571999999999999</v>
       </c>
       <c r="X3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AZ3" s="3"/>
       <c r="BB3" s="3"/>
@@ -1118,7 +1112,7 @@
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I4">
         <v>3460</v>
@@ -1151,7 +1145,7 @@
         <v>11.454000000000001</v>
       </c>
       <c r="X4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AZ4" s="3"/>
       <c r="BB4" s="3"/>
@@ -1159,7 +1153,7 @@
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I5">
         <v>5804</v>
@@ -1192,7 +1186,7 @@
         <v>16.86</v>
       </c>
       <c r="X5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AZ5" s="3"/>
       <c r="BB5" s="3"/>
@@ -1200,7 +1194,7 @@
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I6">
         <v>5800</v>
@@ -1233,7 +1227,7 @@
         <v>17.364000000000001</v>
       </c>
       <c r="X6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AZ6" s="3"/>
       <c r="BB6" s="3"/>
@@ -1241,7 +1235,7 @@
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I7">
         <v>5799</v>
@@ -1274,12 +1268,12 @@
         <v>12.47</v>
       </c>
       <c r="X7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I8">
         <v>5800.4</v>
@@ -1312,12 +1306,12 @@
         <v>13.638999999999999</v>
       </c>
       <c r="X8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I9">
         <v>5813</v>
@@ -1350,12 +1344,12 @@
         <v>15.66</v>
       </c>
       <c r="X9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I10">
         <v>5820</v>
@@ -1388,12 +1382,12 @@
         <v>15.702999999999999</v>
       </c>
       <c r="X10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I11">
         <v>5824</v>
@@ -1426,12 +1420,12 @@
         <v>15.048999999999999</v>
       </c>
       <c r="X11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I12">
         <v>5816</v>
@@ -1464,12 +1458,12 @@
         <v>17.585999999999999</v>
       </c>
       <c r="X12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I13">
         <v>5792</v>
@@ -1504,7 +1498,7 @@
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I14">
         <v>5775</v>
@@ -1537,12 +1531,12 @@
         <v>14.082000000000001</v>
       </c>
       <c r="X14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I15">
         <v>5800</v>
@@ -1575,12 +1569,12 @@
         <v>14.913</v>
       </c>
       <c r="X15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I16">
         <v>5806</v>
@@ -1613,12 +1607,12 @@
         <v>12.507</v>
       </c>
       <c r="X16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I17">
         <v>5815.4</v>
@@ -1651,12 +1645,12 @@
         <v>11.56</v>
       </c>
       <c r="X17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I18">
         <v>5812</v>
@@ -1689,7 +1683,7 @@
         <v>11.662000000000001</v>
       </c>
       <c r="X18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
@@ -3674,7 +3668,7 @@
         <v>4050</v>
       </c>
       <c r="H51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I51">
         <v>10170.1</v>
@@ -3716,207 +3710,251 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>141</v>
+        <v>100</v>
+      </c>
+      <c r="B52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52">
+        <v>1.7635879999999999</v>
+      </c>
+      <c r="D52">
+        <v>3.6409999999999998E-2</v>
+      </c>
+      <c r="E52">
+        <v>1.512</v>
+      </c>
+      <c r="F52">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="G52">
+        <v>2550</v>
       </c>
       <c r="I52">
-        <v>7433.197265625</v>
+        <v>7650</v>
+      </c>
+      <c r="J52">
+        <v>1.74</v>
+      </c>
+      <c r="K52">
+        <v>1.72</v>
+      </c>
+      <c r="L52">
+        <v>0.2</v>
+      </c>
+      <c r="M52">
+        <v>4.2</v>
       </c>
       <c r="N52">
-        <v>286.97138676797078</v>
+        <v>286.97138760000001</v>
       </c>
       <c r="O52">
-        <v>46.868244058307063</v>
+        <v>46.868246300000003</v>
+      </c>
+      <c r="P52">
+        <v>519.096</v>
       </c>
       <c r="Q52">
-        <v>10.382340431213381</v>
+        <v>9.7910000000000004</v>
       </c>
       <c r="R52">
-        <v>10.382340431213381</v>
+        <v>10.367800000000001</v>
+      </c>
+      <c r="S52">
+        <f t="shared" ref="S52:S78" si="2">(0.000000000000000138*G52/(1.673534E-24*1.3*0.000000066726*F52*1.8986E+30/(E52*7149200000)^2))/100000</f>
+        <v>160.76196513632402</v>
+      </c>
+      <c r="T52">
+        <f t="shared" ref="T52:T78" si="3">IF(I52&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
         <v>20</v>
       </c>
       <c r="C53">
-        <v>1.7635879999999999</v>
+        <v>0.79205199999999998</v>
       </c>
       <c r="D53">
-        <v>3.6409999999999998E-2</v>
+        <v>1.6789999999999999E-2</v>
       </c>
       <c r="E53">
-        <v>1.512</v>
+        <v>0.42109020000000003</v>
       </c>
       <c r="F53">
-        <v>9.2799999999999994</v>
+        <v>9.2250570000000004E-2</v>
       </c>
       <c r="G53">
-        <v>2550</v>
+        <v>1978</v>
+      </c>
+      <c r="H53" t="s">
+        <v>99</v>
       </c>
       <c r="I53">
-        <v>7650</v>
+        <v>5443</v>
       </c>
       <c r="J53">
-        <v>1.74</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="K53">
-        <v>1.72</v>
+        <v>1.02</v>
       </c>
       <c r="L53">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M53">
-        <v>4.2</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="N53">
-        <v>286.97138760000001</v>
+        <v>358.6688767</v>
       </c>
       <c r="O53">
-        <v>46.868246300000003</v>
+        <v>-37.628223699999999</v>
       </c>
       <c r="P53">
-        <v>519.096</v>
+        <v>80.437299999999993</v>
       </c>
       <c r="Q53">
-        <v>9.7910000000000004</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="R53">
-        <v>10.367800000000001</v>
+        <v>9.6000599999999991</v>
       </c>
       <c r="S53">
-        <f t="shared" ref="S53:S79" si="2">(0.000000000000000138*G53/(1.673534E-24*1.3*0.000000066726*F53*1.8986E+30/(E53*7149200000)^2))/100000</f>
-        <v>160.76196513632402</v>
+        <f t="shared" si="2"/>
+        <v>972.96006983022733</v>
       </c>
       <c r="T53">
-        <f t="shared" ref="T53:T79" si="3">IF(I53&gt;6800,-7,-5)</f>
-        <v>-7</v>
+        <f t="shared" si="3"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
         <v>20</v>
       </c>
       <c r="C54">
-        <v>0.79205199999999998</v>
+        <v>2.1487738099999998</v>
       </c>
       <c r="D54">
-        <v>1.6789999999999999E-2</v>
+        <v>4.0351999999999999E-2</v>
       </c>
       <c r="E54">
-        <v>0.42109020000000003</v>
+        <v>1.597</v>
       </c>
       <c r="F54">
-        <v>9.2250570000000004E-2</v>
+        <v>3.7</v>
       </c>
       <c r="G54">
-        <v>1978</v>
+        <v>2594.3000000000002</v>
       </c>
       <c r="H54" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="I54">
-        <v>5443</v>
+        <v>7490</v>
       </c>
       <c r="J54">
-        <v>0.94899999999999995</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="K54">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="L54">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="M54">
-        <v>4.3499999999999996</v>
+        <v>4.1050000000000004</v>
       </c>
       <c r="N54">
-        <v>358.6688767</v>
+        <v>317.5515264</v>
       </c>
       <c r="O54">
-        <v>-37.628223699999999</v>
+        <v>10.7388967</v>
       </c>
       <c r="P54">
-        <v>80.437299999999993</v>
+        <v>182.273</v>
       </c>
       <c r="Q54">
-        <v>9.7899999999999991</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="R54">
-        <v>9.6000599999999991</v>
+        <v>8.2424300000000006</v>
       </c>
       <c r="S54">
         <f t="shared" si="2"/>
-        <v>972.96006983022733</v>
+        <v>457.63140850776114</v>
       </c>
       <c r="T54">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
         <v>20</v>
       </c>
       <c r="C55">
-        <v>2.1487738099999998</v>
+        <v>2.8240932000000001</v>
       </c>
       <c r="D55">
-        <v>4.0351999999999999E-2</v>
+        <v>4.7399999999999998E-2</v>
       </c>
       <c r="E55">
-        <v>1.597</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="F55">
-        <v>3.7</v>
+        <v>1.675</v>
       </c>
       <c r="G55">
-        <v>2594.3000000000002</v>
+        <v>2250</v>
       </c>
       <c r="H55" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I55">
-        <v>7490</v>
+        <v>7800</v>
       </c>
       <c r="J55">
-        <v>2.0819999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="K55">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="L55">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>4.1050000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N55">
-        <v>317.5515264</v>
+        <v>147.5800667</v>
       </c>
       <c r="O55">
-        <v>10.7388967</v>
+        <v>-66.113925300000005</v>
       </c>
       <c r="P55">
-        <v>182.273</v>
+        <v>170.696</v>
       </c>
       <c r="Q55">
-        <v>8.2799999999999994</v>
+        <v>8.1910000000000007</v>
       </c>
       <c r="R55">
-        <v>8.2424300000000006</v>
+        <v>8.1740100000000009</v>
       </c>
       <c r="S55">
         <f t="shared" si="2"/>
-        <v>457.63140850776114</v>
+        <v>789.006338593706</v>
       </c>
       <c r="T55">
         <f t="shared" si="3"/>
@@ -3925,193 +3963,190 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>2.8240932000000001</v>
+        <v>16.249210000000001</v>
       </c>
       <c r="D56">
-        <v>4.7399999999999998E-2</v>
+        <v>0.12909999999999999</v>
       </c>
       <c r="E56">
-        <v>1.5149999999999999</v>
+        <v>1.087</v>
       </c>
       <c r="F56">
-        <v>1.675</v>
+        <v>4.34</v>
       </c>
       <c r="G56">
-        <v>2250</v>
+        <v>805.5</v>
       </c>
       <c r="H56" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I56">
-        <v>7800</v>
+        <v>5756</v>
       </c>
       <c r="J56">
-        <v>1.79</v>
+        <v>1.0860000000000001</v>
       </c>
       <c r="K56">
-        <v>1.75</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="M56">
-        <v>4.0999999999999996</v>
+        <v>4.4020000000000001</v>
       </c>
       <c r="N56">
-        <v>147.5800667</v>
+        <v>310.29170019999998</v>
       </c>
       <c r="O56">
-        <v>-66.113925300000005</v>
+        <v>3.6382967000000002</v>
       </c>
       <c r="P56">
-        <v>170.696</v>
+        <v>93.734499999999997</v>
       </c>
       <c r="Q56">
-        <v>8.1910000000000007</v>
+        <v>9.48</v>
       </c>
       <c r="R56">
-        <v>8.1740100000000009</v>
+        <v>9.4290710000000004</v>
       </c>
       <c r="S56">
         <f t="shared" si="2"/>
-        <v>789.006338593706</v>
+        <v>56.120615203365361</v>
       </c>
       <c r="T56">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57">
-        <v>16.249210000000001</v>
+        <v>8.0277282999999997</v>
       </c>
       <c r="D57">
-        <v>0.12909999999999999</v>
+        <v>8.2337403000000003E-2</v>
       </c>
       <c r="E57">
-        <v>1.087</v>
+        <v>0.83243188000000001</v>
       </c>
       <c r="F57">
-        <v>4.34</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="G57">
-        <v>805.5</v>
+        <v>1074.28</v>
       </c>
       <c r="H57" t="s">
         <v>43</v>
       </c>
       <c r="I57">
-        <v>5756</v>
+        <v>5962.7</v>
       </c>
       <c r="J57">
-        <v>1.0860000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="K57">
-        <v>1.0820000000000001</v>
+        <v>1.156039</v>
       </c>
       <c r="L57">
-        <v>0.318</v>
+        <v>0</v>
       </c>
       <c r="M57">
-        <v>4.4020000000000001</v>
+        <v>4.38</v>
       </c>
       <c r="N57">
-        <v>310.29170019999998</v>
+        <v>193.3963704</v>
       </c>
       <c r="O57">
-        <v>3.6382967000000002</v>
+        <v>85.129495199999994</v>
       </c>
       <c r="P57">
-        <v>93.734499999999997</v>
+        <v>114.048</v>
       </c>
       <c r="Q57">
-        <v>9.48</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="R57">
-        <v>9.4290710000000004</v>
+        <v>9.4135299999999997</v>
       </c>
       <c r="S57">
         <f t="shared" si="2"/>
-        <v>56.120615203365361</v>
+        <v>1175.9460676296278</v>
       </c>
       <c r="T57">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
-      <c r="U57" s="1" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B58" t="s">
         <v>20</v>
       </c>
       <c r="C58">
-        <v>8.0277282999999997</v>
+        <v>12.5199</v>
       </c>
       <c r="D58">
-        <v>8.2337403000000003E-2</v>
+        <v>0.1062</v>
       </c>
       <c r="E58">
-        <v>0.83243188000000001</v>
+        <v>0.41279399999999999</v>
       </c>
       <c r="F58">
-        <v>0.16200000000000001</v>
+        <v>2.627204E-2</v>
       </c>
       <c r="G58">
-        <v>1074.28</v>
-      </c>
-      <c r="H58" t="s">
-        <v>43</v>
+        <v>843</v>
       </c>
       <c r="I58">
-        <v>5962.7</v>
+        <v>5770</v>
       </c>
       <c r="J58">
-        <v>1.1499999999999999</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="K58">
-        <v>1.156039</v>
+        <v>1.022</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M58">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="N58">
-        <v>193.3963704</v>
+        <v>192.1848981</v>
       </c>
       <c r="O58">
-        <v>85.129495199999994</v>
+        <v>64.855275500000005</v>
       </c>
       <c r="P58">
-        <v>114.048</v>
+        <v>84.536199999999994</v>
       </c>
       <c r="Q58">
-        <v>9.5399999999999991</v>
+        <v>9.5340000000000007</v>
       </c>
       <c r="R58">
-        <v>9.4135299999999997</v>
+        <v>9.3678899999999992</v>
       </c>
       <c r="S58">
         <f t="shared" si="2"/>
-        <v>1175.9460676296278</v>
+        <v>1399.2265914107247</v>
       </c>
       <c r="T58">
         <f t="shared" si="3"/>
@@ -4120,59 +4155,59 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
         <v>20</v>
       </c>
       <c r="C59">
-        <v>12.5199</v>
+        <v>4.7202190000000002</v>
       </c>
       <c r="D59">
-        <v>0.1062</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="E59">
-        <v>0.41279399999999999</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="F59">
-        <v>2.627204E-2</v>
+        <v>2.37</v>
       </c>
       <c r="G59">
-        <v>843</v>
+        <v>1679</v>
       </c>
       <c r="I59">
-        <v>5770</v>
+        <v>6274</v>
       </c>
       <c r="J59">
-        <v>0.96799999999999997</v>
+        <v>1.925</v>
       </c>
       <c r="K59">
-        <v>1.022</v>
+        <v>1.464</v>
       </c>
       <c r="L59">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M59">
-        <v>4.47</v>
+        <v>4.0339999999999998</v>
       </c>
       <c r="N59">
-        <v>192.1848981</v>
+        <v>325.01453629999997</v>
       </c>
       <c r="O59">
-        <v>64.855275500000005</v>
+        <v>48.4067674</v>
       </c>
       <c r="P59">
-        <v>84.536199999999994</v>
+        <v>200.49199999999999</v>
       </c>
       <c r="Q59">
-        <v>9.5340000000000007</v>
+        <v>9.4380000000000006</v>
       </c>
       <c r="R59">
-        <v>9.3678899999999992</v>
+        <v>9.3503900000000009</v>
       </c>
       <c r="S59">
         <f t="shared" si="2"/>
-        <v>1399.2265914107247</v>
+        <v>353.31388599481477</v>
       </c>
       <c r="T59">
         <f t="shared" si="3"/>
@@ -4181,59 +4216,62 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
         <v>20</v>
       </c>
       <c r="C60">
-        <v>4.7202190000000002</v>
+        <v>4.4258699999999997</v>
       </c>
       <c r="D60">
-        <v>6.2600000000000003E-2</v>
+        <v>5.7779999999999998E-2</v>
       </c>
       <c r="E60">
-        <v>1.3959999999999999</v>
+        <v>2.2303544500000001</v>
       </c>
       <c r="F60">
-        <v>2.37</v>
+        <v>1.86578665</v>
       </c>
       <c r="G60">
-        <v>1679</v>
+        <v>1293</v>
+      </c>
+      <c r="H60" t="s">
+        <v>70</v>
       </c>
       <c r="I60">
-        <v>6274</v>
+        <v>6117</v>
       </c>
       <c r="J60">
-        <v>1.925</v>
+        <v>1.53</v>
       </c>
       <c r="K60">
-        <v>1.464</v>
+        <v>1.3120000000000001</v>
       </c>
       <c r="L60">
-        <v>0.11899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="M60">
-        <v>4.0339999999999998</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N60">
-        <v>325.01453629999997</v>
+        <v>313.5110469</v>
       </c>
       <c r="O60">
-        <v>48.4067674</v>
+        <v>72.580645500000003</v>
       </c>
       <c r="P60">
-        <v>200.49199999999999</v>
+        <v>139.48400000000001</v>
       </c>
       <c r="Q60">
-        <v>9.4380000000000006</v>
+        <v>9.2700010000000006</v>
       </c>
       <c r="R60">
-        <v>9.3503900000000009</v>
+        <v>9.1879500000000007</v>
       </c>
       <c r="S60">
         <f t="shared" si="2"/>
-        <v>353.31388599481477</v>
+        <v>882.20971786077962</v>
       </c>
       <c r="T60">
         <f t="shared" si="3"/>
@@ -4242,126 +4280,126 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
         <v>20</v>
       </c>
       <c r="C61">
-        <v>4.4258699999999997</v>
+        <v>2.6502370000000002</v>
       </c>
       <c r="D61">
-        <v>5.7779999999999998E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="E61">
-        <v>2.2303544500000001</v>
+        <v>1.49</v>
       </c>
       <c r="F61">
-        <v>1.86578665</v>
+        <v>3.12</v>
       </c>
       <c r="G61">
-        <v>1293</v>
+        <v>2370</v>
       </c>
       <c r="H61" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I61">
-        <v>6117</v>
+        <v>7690</v>
       </c>
       <c r="J61">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="K61">
-        <v>1.3120000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="L61">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="M61">
-        <v>4.0999999999999996</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="N61">
-        <v>313.5110469</v>
+        <v>316.20369219999998</v>
       </c>
       <c r="O61">
-        <v>72.580645500000003</v>
+        <v>55.588022100000003</v>
       </c>
       <c r="P61">
-        <v>139.48400000000001</v>
+        <v>148.92500000000001</v>
       </c>
       <c r="Q61">
-        <v>9.2700010000000006</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="R61">
-        <v>9.1879500000000007</v>
+        <v>7.9756099999999996</v>
       </c>
       <c r="S61">
         <f t="shared" si="2"/>
-        <v>882.20971786077962</v>
+        <v>431.57254486096394</v>
       </c>
       <c r="T61">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
       <c r="C62">
-        <v>2.6502370000000002</v>
+        <v>1.902603</v>
       </c>
       <c r="D62">
-        <v>4.5999999999999999E-2</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="E62">
-        <v>1.49</v>
+        <v>1.875</v>
       </c>
       <c r="F62">
-        <v>3.12</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G62">
-        <v>2370</v>
+        <v>2492</v>
       </c>
       <c r="H62" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I62">
-        <v>7690</v>
+        <v>7300</v>
       </c>
       <c r="J62">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="K62">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="L62">
-        <v>0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="M62">
-        <v>4.1500000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N62">
-        <v>316.20369219999998</v>
+        <v>352.26752069999998</v>
       </c>
       <c r="O62">
-        <v>55.588022100000003</v>
+        <v>67.034806200000006</v>
       </c>
       <c r="P62">
-        <v>148.92500000000001</v>
+        <v>225.88800000000001</v>
       </c>
       <c r="Q62">
-        <v>8.0299999999999994</v>
+        <v>8.952</v>
       </c>
       <c r="R62">
-        <v>7.9756099999999996</v>
+        <v>8.8952899999999993</v>
       </c>
       <c r="S62">
         <f t="shared" si="2"/>
-        <v>431.57254486096394</v>
+        <v>974.78820571370204</v>
       </c>
       <c r="T62">
         <f t="shared" si="3"/>
@@ -4370,126 +4408,123 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
       </c>
       <c r="C63">
-        <v>1.902603</v>
+        <v>3.2086640000000002</v>
       </c>
       <c r="D63">
-        <v>3.8899999999999997E-2</v>
+        <v>4.8820000000000002E-2</v>
       </c>
       <c r="E63">
-        <v>1.875</v>
+        <v>1.44</v>
       </c>
       <c r="F63">
-        <v>2.2999999999999998</v>
+        <v>0.7</v>
       </c>
       <c r="G63">
-        <v>2492</v>
+        <v>1927</v>
       </c>
       <c r="H63" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I63">
-        <v>7300</v>
+        <v>5991</v>
       </c>
       <c r="J63">
-        <v>1.95</v>
+        <v>2.1680000000000001</v>
       </c>
       <c r="K63">
-        <v>1.79</v>
+        <v>1.5069999999999999</v>
       </c>
       <c r="L63">
-        <v>-0.1</v>
+        <v>0.373</v>
       </c>
       <c r="M63">
-        <v>4.0999999999999996</v>
+        <v>3.9430000000000001</v>
       </c>
       <c r="N63">
-        <v>352.26752069999998</v>
+        <v>142.74340599999999</v>
       </c>
       <c r="O63">
-        <v>67.034806200000006</v>
+        <v>26.539995099999999</v>
       </c>
       <c r="P63">
-        <v>225.88800000000001</v>
+        <v>229.06700000000001</v>
       </c>
       <c r="Q63">
-        <v>8.952</v>
+        <v>9.7210000000000001</v>
       </c>
       <c r="R63">
-        <v>8.8952899999999993</v>
+        <v>9.5843900000000009</v>
       </c>
       <c r="S63">
         <f t="shared" si="2"/>
-        <v>974.78820571370204</v>
+        <v>1460.8182255852041</v>
       </c>
       <c r="T63">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
         <v>20</v>
       </c>
       <c r="C64">
-        <v>3.2086640000000002</v>
+        <v>9.5739181000000002</v>
       </c>
       <c r="D64">
-        <v>4.8820000000000002E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E64">
-        <v>1.44</v>
+        <v>1.10166148</v>
       </c>
       <c r="F64">
-        <v>0.7</v>
+        <v>0.28128386</v>
       </c>
       <c r="G64">
-        <v>1927</v>
-      </c>
-      <c r="H64" t="s">
-        <v>56</v>
+        <v>1199.55</v>
       </c>
       <c r="I64">
-        <v>5991</v>
+        <v>6039</v>
       </c>
       <c r="J64">
-        <v>2.1680000000000001</v>
+        <v>2.032</v>
       </c>
       <c r="K64">
-        <v>1.5069999999999999</v>
+        <v>1.4642999999999999</v>
       </c>
       <c r="L64">
-        <v>0.373</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M64">
-        <v>3.9430000000000001</v>
+        <v>3.9860000000000002</v>
       </c>
       <c r="N64">
-        <v>142.74340599999999</v>
+        <v>201.9626552</v>
       </c>
       <c r="O64">
-        <v>26.539995099999999</v>
+        <v>9.0306437000000006</v>
       </c>
       <c r="P64">
-        <v>229.06700000000001</v>
+        <v>223.465</v>
       </c>
       <c r="Q64">
-        <v>9.7210000000000001</v>
+        <v>9.8149999999999995</v>
       </c>
       <c r="R64">
-        <v>9.5843900000000009</v>
+        <v>9.6598100000000002</v>
       </c>
       <c r="S64">
         <f t="shared" si="2"/>
-        <v>1460.8182255852041</v>
+        <v>1324.5165539963698</v>
       </c>
       <c r="T64">
         <f t="shared" si="3"/>
@@ -4498,303 +4533,306 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
       <c r="C65">
-        <v>9.5739181000000002</v>
+        <v>17.305904000000002</v>
       </c>
       <c r="D65">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E65">
-        <v>1.10166148</v>
+        <v>1.07</v>
       </c>
       <c r="F65">
-        <v>0.28128386</v>
+        <v>6.4</v>
       </c>
       <c r="G65">
-        <v>1199.55</v>
+        <v>1221.3900000000001</v>
       </c>
       <c r="I65">
-        <v>6039</v>
+        <v>7130</v>
       </c>
       <c r="J65">
-        <v>2.032</v>
+        <v>2.02</v>
       </c>
       <c r="K65">
-        <v>1.4642999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="L65">
-        <v>0.33200000000000002</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3.9860000000000002</v>
+        <v>3.9460000000000002</v>
       </c>
       <c r="N65">
-        <v>201.9626552</v>
+        <v>164.031654</v>
       </c>
       <c r="O65">
-        <v>9.0306437000000006</v>
+        <v>-43.376696699999997</v>
       </c>
       <c r="P65">
-        <v>223.465</v>
+        <v>328.47500000000002</v>
       </c>
       <c r="Q65">
-        <v>9.8149999999999995</v>
+        <v>9.8670000000000009</v>
       </c>
       <c r="R65">
-        <v>9.6598100000000002</v>
+        <v>9.7596699999999998</v>
       </c>
       <c r="S65">
         <f t="shared" si="2"/>
-        <v>1324.5165539963698</v>
+        <v>55.915145726222889</v>
       </c>
       <c r="T65">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
       </c>
       <c r="C66">
-        <v>17.305904000000002</v>
+        <v>10.261127</v>
       </c>
       <c r="D66">
-        <v>0.16</v>
+        <v>0.111</v>
       </c>
       <c r="E66">
-        <v>1.07</v>
+        <v>1.1079506100000001</v>
       </c>
       <c r="F66">
-        <v>6.4</v>
+        <v>5.55960374</v>
       </c>
       <c r="G66">
-        <v>1221.3900000000001</v>
+        <v>1363.43</v>
       </c>
       <c r="I66">
-        <v>7130</v>
+        <v>6200</v>
       </c>
       <c r="J66">
-        <v>2.02</v>
+        <v>2.7505000000000002</v>
       </c>
       <c r="K66">
-        <v>1.59</v>
+        <v>1.7169000000000001</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M66">
-        <v>3.9460000000000002</v>
+        <v>3.7890000000000001</v>
       </c>
       <c r="N66">
-        <v>164.031654</v>
+        <v>263.75807529999997</v>
       </c>
       <c r="O66">
-        <v>-43.376696699999997</v>
+        <v>40.695042800000003</v>
       </c>
       <c r="P66">
-        <v>328.47500000000002</v>
+        <v>224.73099999999999</v>
       </c>
       <c r="Q66">
-        <v>9.8670000000000009</v>
+        <v>9.07</v>
       </c>
       <c r="R66">
-        <v>9.7596699999999998</v>
+        <v>8.9365100000000002</v>
       </c>
       <c r="S66">
         <f t="shared" si="2"/>
-        <v>55.915145726222889</v>
+        <v>77.040187113891676</v>
       </c>
       <c r="T66">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="B67" t="s">
         <v>20</v>
       </c>
       <c r="C67">
-        <v>10.261127</v>
+        <v>10.655669</v>
       </c>
       <c r="D67">
-        <v>0.111</v>
+        <v>0.1166</v>
       </c>
       <c r="E67">
-        <v>1.1079506100000001</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F67">
-        <v>5.55960374</v>
+        <v>4.82</v>
       </c>
       <c r="G67">
-        <v>1363.43</v>
+        <v>1595</v>
       </c>
       <c r="I67">
-        <v>6200</v>
+        <v>7360</v>
       </c>
       <c r="J67">
-        <v>2.7505000000000002</v>
+        <v>2.36</v>
       </c>
       <c r="K67">
-        <v>1.7169000000000001</v>
+        <v>1.859</v>
       </c>
       <c r="L67">
-        <v>0.28499999999999998</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M67">
-        <v>3.7890000000000001</v>
+        <v>3.9620000000000002</v>
       </c>
       <c r="N67">
-        <v>263.75807529999997</v>
+        <v>90.062587800000003</v>
       </c>
       <c r="O67">
-        <v>40.695042800000003</v>
+        <v>11.8840577</v>
       </c>
       <c r="P67">
-        <v>224.73099999999999</v>
+        <v>285.28899999999999</v>
       </c>
       <c r="Q67">
-        <v>9.07</v>
+        <v>9.5470000000000006</v>
       </c>
       <c r="R67">
-        <v>8.9365100000000002</v>
+        <v>9.4724400000000006</v>
       </c>
       <c r="S67">
         <f t="shared" si="2"/>
-        <v>77.040187113891676</v>
+        <v>83.670803141549356</v>
       </c>
       <c r="T67">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
         <v>20</v>
       </c>
       <c r="C68">
-        <v>10.655669</v>
+        <v>18.388179999999998</v>
       </c>
       <c r="D68">
-        <v>0.1166</v>
+        <v>0.15279999999999999</v>
       </c>
       <c r="E68">
-        <v>0.99399999999999999</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F68">
-        <v>4.82</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="G68">
-        <v>1595</v>
+        <v>1027</v>
       </c>
       <c r="I68">
-        <v>7360</v>
+        <v>6095</v>
       </c>
       <c r="J68">
-        <v>2.36</v>
+        <v>1.867</v>
       </c>
       <c r="K68">
-        <v>1.859</v>
+        <v>1.407</v>
       </c>
       <c r="L68">
-        <v>9.4E-2</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M68">
-        <v>3.9620000000000002</v>
+        <v>4.0439999999999996</v>
       </c>
       <c r="N68">
-        <v>90.062587800000003</v>
+        <v>47.517260800000003</v>
       </c>
       <c r="O68">
-        <v>11.8840577</v>
+        <v>-50.8322632</v>
       </c>
       <c r="P68">
-        <v>285.28899999999999</v>
+        <v>76.902799999999999</v>
       </c>
       <c r="Q68">
-        <v>9.5470000000000006</v>
+        <v>7.57</v>
       </c>
       <c r="R68">
-        <v>9.4724400000000006</v>
+        <v>7.4165299999999998</v>
       </c>
       <c r="S68">
         <f t="shared" si="2"/>
-        <v>83.670803141549356</v>
+        <v>777.64358420307099</v>
       </c>
       <c r="T68">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
       </c>
       <c r="C69">
-        <v>18.388179999999998</v>
+        <v>16.067540999999999</v>
       </c>
       <c r="D69">
-        <v>0.15279999999999999</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="E69">
-        <v>0.63900000000000001</v>
+        <v>0.45410017000000003</v>
       </c>
       <c r="F69">
-        <v>0.13800000000000001</v>
+        <v>4.4363560000000003E-2</v>
       </c>
       <c r="G69">
-        <v>1027</v>
+        <v>635</v>
+      </c>
+      <c r="H69" t="s">
+        <v>116</v>
       </c>
       <c r="I69">
-        <v>6095</v>
+        <v>5291</v>
       </c>
       <c r="J69">
-        <v>1.867</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="K69">
-        <v>1.407</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="L69">
-        <v>0.17499999999999999</v>
+        <v>-4.3999999999999997E-2</v>
       </c>
       <c r="M69">
-        <v>4.0439999999999996</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="N69">
-        <v>47.517260800000003</v>
+        <v>81.853282399999998</v>
       </c>
       <c r="O69">
-        <v>-50.8322632</v>
+        <v>-14.2767404</v>
       </c>
       <c r="P69">
-        <v>76.902799999999999</v>
+        <v>74.796899999999994</v>
       </c>
       <c r="Q69">
-        <v>7.57</v>
+        <v>9.9309999999999992</v>
       </c>
       <c r="R69">
-        <v>7.4165299999999998</v>
+        <v>9.7777600000000007</v>
       </c>
       <c r="S69">
         <f t="shared" si="2"/>
-        <v>777.64358420307099</v>
+        <v>755.33252275944176</v>
       </c>
       <c r="T69">
         <f t="shared" si="3"/>
@@ -4803,62 +4841,59 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
       </c>
       <c r="C70">
-        <v>16.067540999999999</v>
+        <v>9.9558099999999996</v>
       </c>
       <c r="D70">
-        <v>0.11700000000000001</v>
+        <v>9.9400000000000002E-2</v>
       </c>
       <c r="E70">
-        <v>0.45410017000000003</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="F70">
-        <v>4.4363560000000003E-2</v>
+        <v>1.49</v>
       </c>
       <c r="G70">
-        <v>635</v>
-      </c>
-      <c r="H70" t="s">
-        <v>116</v>
+        <v>1655</v>
       </c>
       <c r="I70">
-        <v>5291</v>
+        <v>4896</v>
       </c>
       <c r="J70">
-        <v>0.86599999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="K70">
-        <v>0.83299999999999996</v>
+        <v>1.31</v>
       </c>
       <c r="L70">
-        <v>-4.3999999999999997E-2</v>
+        <v>0.23</v>
       </c>
       <c r="M70">
-        <v>4.4800000000000004</v>
+        <v>3.48</v>
       </c>
       <c r="N70">
-        <v>81.853282399999998</v>
+        <v>184.97875790000001</v>
       </c>
       <c r="O70">
-        <v>-14.2767404</v>
+        <v>-25.827853099999999</v>
       </c>
       <c r="P70">
-        <v>74.796899999999994</v>
+        <v>215.98599999999999</v>
       </c>
       <c r="Q70">
-        <v>9.9309999999999992</v>
+        <v>9.9730000000000008</v>
       </c>
       <c r="R70">
-        <v>9.7777600000000007</v>
+        <v>9.641</v>
       </c>
       <c r="S70">
         <f t="shared" si="2"/>
-        <v>755.33252275944176</v>
+        <v>318.17832033985127</v>
       </c>
       <c r="T70">
         <f t="shared" si="3"/>
@@ -4867,59 +4902,62 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="B71" t="s">
         <v>20</v>
       </c>
       <c r="C71">
-        <v>9.9558099999999996</v>
+        <v>7.2459899999999999</v>
       </c>
       <c r="D71">
-        <v>9.9400000000000002E-2</v>
+        <v>8.8800000000000004E-2</v>
       </c>
       <c r="E71">
-        <v>1.0580000000000001</v>
+        <v>1.042</v>
       </c>
       <c r="F71">
-        <v>1.49</v>
+        <v>12.89</v>
       </c>
       <c r="G71">
-        <v>1655</v>
+        <v>1677</v>
+      </c>
+      <c r="H71" t="s">
+        <v>56</v>
       </c>
       <c r="I71">
-        <v>4896</v>
+        <v>6264</v>
       </c>
       <c r="J71">
-        <v>3.55</v>
+        <v>2.738</v>
       </c>
       <c r="K71">
-        <v>1.31</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="L71">
-        <v>0.23</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="M71">
-        <v>3.48</v>
+        <v>3.81</v>
       </c>
       <c r="N71">
-        <v>184.97875790000001</v>
+        <v>83.865928800000006</v>
       </c>
       <c r="O71">
-        <v>-25.827853099999999</v>
+        <v>21.294241700000001</v>
       </c>
       <c r="P71">
-        <v>215.98599999999999</v>
+        <v>225.643</v>
       </c>
       <c r="Q71">
-        <v>9.9730000000000008</v>
+        <v>9.24</v>
       </c>
       <c r="R71">
-        <v>9.641</v>
+        <v>9.0746900000000004</v>
       </c>
       <c r="S71">
         <f t="shared" si="2"/>
-        <v>318.17832033985127</v>
+        <v>36.149567272802649</v>
       </c>
       <c r="T71">
         <f t="shared" si="3"/>
@@ -4928,62 +4966,62 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="B72" t="s">
         <v>20</v>
       </c>
       <c r="C72">
-        <v>7.2459899999999999</v>
+        <v>10.331110000000001</v>
       </c>
       <c r="D72">
-        <v>8.8800000000000004E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="E72">
-        <v>1.042</v>
+        <v>0.99</v>
       </c>
       <c r="F72">
-        <v>12.89</v>
+        <v>1.53</v>
       </c>
       <c r="G72">
-        <v>1677</v>
+        <v>1370</v>
       </c>
       <c r="H72" t="s">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="I72">
-        <v>6264</v>
+        <v>5735</v>
       </c>
       <c r="J72">
-        <v>2.738</v>
+        <v>1.66</v>
       </c>
       <c r="K72">
-        <v>1.7649999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L72">
-        <v>0.34200000000000003</v>
+        <v>0.26</v>
       </c>
       <c r="M72">
-        <v>3.81</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="N72">
-        <v>83.865928800000006</v>
+        <v>110.5126861</v>
       </c>
       <c r="O72">
-        <v>21.294241700000001</v>
+        <v>-57.384998000000003</v>
       </c>
       <c r="P72">
-        <v>225.643</v>
+        <v>179.36600000000001</v>
       </c>
       <c r="Q72">
-        <v>9.24</v>
+        <v>9.9719999999999995</v>
       </c>
       <c r="R72">
-        <v>9.0746900000000004</v>
+        <v>9.8465900000000008</v>
       </c>
       <c r="S72">
         <f t="shared" si="2"/>
-        <v>36.149567272802649</v>
+        <v>224.58825733889913</v>
       </c>
       <c r="T72">
         <f t="shared" si="3"/>
@@ -4992,62 +5030,59 @@
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
         <v>20</v>
       </c>
       <c r="C73">
-        <v>10.331110000000001</v>
+        <v>6.7535809999999996</v>
       </c>
       <c r="D73">
-        <v>9.7000000000000003E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E73">
-        <v>0.99</v>
+        <v>0.58881357999999995</v>
       </c>
       <c r="F73">
-        <v>1.53</v>
+        <v>0.10068326</v>
       </c>
       <c r="G73">
-        <v>1370</v>
-      </c>
-      <c r="H73" t="s">
-        <v>120</v>
+        <v>1180</v>
       </c>
       <c r="I73">
-        <v>5735</v>
+        <v>5808</v>
       </c>
       <c r="J73">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="K73">
-        <v>1.1399999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L73">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="M73">
-        <v>4.0599999999999996</v>
+        <v>4.26</v>
       </c>
       <c r="N73">
-        <v>110.5126861</v>
+        <v>166.26950410000001</v>
       </c>
       <c r="O73">
-        <v>-57.384998000000003</v>
+        <v>11.2464069</v>
       </c>
       <c r="P73">
-        <v>179.36600000000001</v>
+        <v>130.91900000000001</v>
       </c>
       <c r="Q73">
-        <v>9.9719999999999995</v>
+        <v>9.75</v>
       </c>
       <c r="R73">
-        <v>9.8465900000000008</v>
+        <v>9.6080000000000005</v>
       </c>
       <c r="S73">
         <f t="shared" si="2"/>
-        <v>224.58825733889913</v>
+        <v>1039.84328949877</v>
       </c>
       <c r="T73">
         <f t="shared" si="3"/>
@@ -5056,59 +5091,62 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="B74" t="s">
         <v>20</v>
       </c>
       <c r="C74">
-        <v>6.7535809999999996</v>
+        <v>10.590547000000001</v>
       </c>
       <c r="D74">
-        <v>7.2999999999999995E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E74">
-        <v>0.58881357999999995</v>
+        <v>0.91890603000000004</v>
       </c>
       <c r="F74">
-        <v>0.10068326</v>
+        <v>0.18469084999999999</v>
       </c>
       <c r="G74">
-        <v>1180</v>
+        <v>947</v>
+      </c>
+      <c r="H74" t="s">
+        <v>130</v>
       </c>
       <c r="I74">
-        <v>5808</v>
+        <v>6000</v>
       </c>
       <c r="J74">
-        <v>1.29</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="K74">
-        <v>1.1000000000000001</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="L74">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="M74">
-        <v>4.26</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N74">
-        <v>166.26950410000001</v>
+        <v>161.87955690000001</v>
       </c>
       <c r="O74">
-        <v>11.2464069</v>
+        <v>36.329434499999998</v>
       </c>
       <c r="P74">
-        <v>130.91900000000001</v>
+        <v>130.85499999999999</v>
       </c>
       <c r="Q74">
-        <v>9.75</v>
+        <v>10.058999999999999</v>
       </c>
       <c r="R74">
-        <v>9.6080000000000005</v>
+        <v>9.9823299999999993</v>
       </c>
       <c r="S74">
         <f t="shared" si="2"/>
-        <v>1039.84328949877</v>
+        <v>1107.9861243219782</v>
       </c>
       <c r="T74">
         <f t="shared" si="3"/>
@@ -5117,62 +5155,59 @@
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B75" t="s">
         <v>20</v>
       </c>
       <c r="C75">
-        <v>10.590547000000001</v>
+        <v>5.8267310999999999</v>
       </c>
       <c r="D75">
-        <v>9.8000000000000004E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E75">
-        <v>0.91890603000000004</v>
+        <v>0.57186287999999996</v>
       </c>
       <c r="F75">
-        <v>0.18469084999999999</v>
+        <v>0.24698861999999999</v>
       </c>
       <c r="G75">
-        <v>947</v>
-      </c>
-      <c r="H75" t="s">
-        <v>130</v>
+        <v>1439</v>
       </c>
       <c r="I75">
-        <v>6000</v>
+        <v>6110</v>
       </c>
       <c r="J75">
-        <v>1.0509999999999999</v>
+        <v>1.6479999999999999</v>
       </c>
       <c r="K75">
-        <v>1.1459999999999999</v>
+        <v>1.2909999999999999</v>
       </c>
       <c r="L75">
-        <v>0.09</v>
+        <v>0.124</v>
       </c>
       <c r="M75">
-        <v>4.4400000000000004</v>
+        <v>4.1180000000000003</v>
       </c>
       <c r="N75">
-        <v>161.87955690000001</v>
+        <v>51.657269100000001</v>
       </c>
       <c r="O75">
-        <v>36.329434499999998</v>
+        <v>40.817270399999998</v>
       </c>
       <c r="P75">
-        <v>130.85499999999999</v>
+        <v>179.14699999999999</v>
       </c>
       <c r="Q75">
-        <v>10.058999999999999</v>
+        <v>9.9130000000000003</v>
       </c>
       <c r="R75">
-        <v>9.9823299999999993</v>
+        <v>9.7295700000000007</v>
       </c>
       <c r="S75">
         <f t="shared" si="2"/>
-        <v>1107.9861243219782</v>
+        <v>487.59044264912109</v>
       </c>
       <c r="T75">
         <f t="shared" si="3"/>
@@ -5181,59 +5216,62 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B76" t="s">
         <v>20</v>
       </c>
       <c r="C76">
-        <v>5.8267310999999999</v>
+        <v>6.4025129999999999</v>
       </c>
       <c r="D76">
-        <v>6.9000000000000006E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="E76">
-        <v>0.57186287999999996</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="F76">
-        <v>0.24698861999999999</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G76">
-        <v>1439</v>
+        <v>1388</v>
+      </c>
+      <c r="H76" t="s">
+        <v>63</v>
       </c>
       <c r="I76">
-        <v>6110</v>
+        <v>6400</v>
       </c>
       <c r="J76">
-        <v>1.6479999999999999</v>
+        <v>1.415</v>
       </c>
       <c r="K76">
-        <v>1.2909999999999999</v>
+        <v>1.3129999999999999</v>
       </c>
       <c r="L76">
-        <v>0.124</v>
+        <v>0.09</v>
       </c>
       <c r="M76">
-        <v>4.1180000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="N76">
-        <v>51.657269100000001</v>
+        <v>125.3050544</v>
       </c>
       <c r="O76">
-        <v>40.817270399999998</v>
+        <v>-46.484295899999999</v>
       </c>
       <c r="P76">
-        <v>179.14699999999999</v>
+        <v>123.297</v>
       </c>
       <c r="Q76">
-        <v>9.9130000000000003</v>
+        <v>8.9949999999999992</v>
       </c>
       <c r="R76">
-        <v>9.7295700000000007</v>
+        <v>8.8910300000000007</v>
       </c>
       <c r="S76">
         <f t="shared" si="2"/>
-        <v>487.59044264912109</v>
+        <v>795.95548671567838</v>
       </c>
       <c r="T76">
         <f t="shared" si="3"/>
@@ -5242,62 +5280,62 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="B77" t="s">
         <v>20</v>
       </c>
       <c r="C77">
-        <v>6.4025129999999999</v>
+        <v>11.236598499999999</v>
       </c>
       <c r="D77">
-        <v>7.0800000000000002E-2</v>
+        <v>0.1041</v>
       </c>
       <c r="E77">
-        <v>0.82399999999999995</v>
+        <v>1.17</v>
       </c>
       <c r="F77">
-        <v>0.30299999999999999</v>
+        <v>1.234</v>
       </c>
       <c r="G77">
-        <v>1388</v>
+        <v>1252</v>
       </c>
       <c r="H77" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I77">
-        <v>6400</v>
+        <v>6295</v>
       </c>
       <c r="J77">
-        <v>1.415</v>
+        <v>1.28</v>
       </c>
       <c r="K77">
-        <v>1.3129999999999999</v>
+        <v>1.181</v>
       </c>
       <c r="L77">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>4.2</v>
+        <v>4.2910000000000004</v>
       </c>
       <c r="N77">
-        <v>125.3050544</v>
+        <v>144.11935940000001</v>
       </c>
       <c r="O77">
-        <v>-46.484295899999999</v>
+        <v>-50.463093299999997</v>
       </c>
       <c r="P77">
-        <v>123.297</v>
+        <v>141.81200000000001</v>
       </c>
       <c r="Q77">
-        <v>8.9949999999999992</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R77">
-        <v>8.8910300000000007</v>
+        <v>9.6608199999999993</v>
       </c>
       <c r="S77">
         <f t="shared" si="2"/>
-        <v>795.95548671567838</v>
+        <v>355.42536038318485</v>
       </c>
       <c r="T77">
         <f t="shared" si="3"/>
@@ -5306,62 +5344,62 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="B78" t="s">
         <v>20</v>
       </c>
       <c r="C78">
-        <v>11.236598499999999</v>
+        <v>4.6336110000000001</v>
       </c>
       <c r="D78">
-        <v>0.1041</v>
+        <v>0.06</v>
       </c>
       <c r="E78">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="F78">
-        <v>1.234</v>
+        <v>2.8</v>
       </c>
       <c r="G78">
-        <v>1252</v>
+        <v>1561</v>
       </c>
       <c r="H78" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="I78">
-        <v>6295</v>
+        <v>6643</v>
       </c>
       <c r="J78">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="K78">
-        <v>1.181</v>
+        <v>1.4</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78">
-        <v>4.2910000000000004</v>
+        <v>4.05</v>
       </c>
       <c r="N78">
-        <v>144.11935940000001</v>
+        <v>199.33385029999999</v>
       </c>
       <c r="O78">
-        <v>-50.463093299999997</v>
+        <v>-15.2737046</v>
       </c>
       <c r="P78">
-        <v>141.81200000000001</v>
+        <v>161.74299999999999</v>
       </c>
       <c r="Q78">
-        <v>9.8219999999999992</v>
+        <v>9.109</v>
       </c>
       <c r="R78">
-        <v>9.6608199999999993</v>
+        <v>8.9943600000000004</v>
       </c>
       <c r="S78">
         <f t="shared" si="2"/>
-        <v>355.42536038318485</v>
+        <v>267.77715667890726</v>
       </c>
       <c r="T78">
         <f t="shared" si="3"/>
@@ -5370,188 +5408,217 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
         <v>20</v>
       </c>
-      <c r="C79">
-        <v>4.6336110000000001</v>
-      </c>
-      <c r="D79">
-        <v>0.06</v>
-      </c>
-      <c r="E79">
-        <v>1.37</v>
-      </c>
-      <c r="F79">
-        <v>2.8</v>
-      </c>
-      <c r="G79">
-        <v>1561</v>
-      </c>
-      <c r="H79" t="s">
-        <v>66</v>
-      </c>
       <c r="I79">
-        <v>6643</v>
+        <v>6200</v>
       </c>
       <c r="J79">
-        <v>1.71</v>
-      </c>
-      <c r="K79">
-        <v>1.4</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>4.05</v>
+        <v>1.2</v>
       </c>
       <c r="N79">
-        <v>199.33385029999999</v>
+        <v>97.636728000000005</v>
       </c>
       <c r="O79">
-        <v>-15.2737046</v>
+        <v>29.672419000000001</v>
       </c>
       <c r="P79">
-        <v>161.74299999999999</v>
-      </c>
-      <c r="Q79">
-        <v>9.109</v>
+        <v>427</v>
       </c>
       <c r="R79">
-        <v>8.9943600000000004</v>
-      </c>
-      <c r="S79">
-        <f t="shared" si="2"/>
-        <v>267.77715667890726</v>
+        <v>11.4986</v>
       </c>
       <c r="T79">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="T79:T99" si="4">IF(I79&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>142</v>
+        <v>131</v>
+      </c>
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80">
+        <v>5.3220124999999996</v>
+      </c>
+      <c r="D80">
+        <v>6.08E-2</v>
+      </c>
+      <c r="E80">
+        <v>1.226</v>
+      </c>
+      <c r="F80">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="G80">
+        <v>1460</v>
+      </c>
+      <c r="H80" t="s">
+        <v>43</v>
       </c>
       <c r="I80">
-        <v>6161.02294921875</v>
+        <v>5990</v>
       </c>
       <c r="J80">
-        <v>1.7061723470687871</v>
+        <v>1.5609999999999999</v>
       </c>
       <c r="K80">
-        <v>1.3463604</v>
+        <v>1.06</v>
+      </c>
+      <c r="L80">
+        <v>-0.2</v>
       </c>
       <c r="M80">
-        <v>3.9825000762939449</v>
+        <v>4.0750000000000002</v>
       </c>
       <c r="N80">
-        <v>268.30433503422898</v>
+        <v>210.1935714</v>
       </c>
       <c r="O80">
-        <v>37.211736733677057</v>
+        <v>-30.583608399999999</v>
       </c>
       <c r="P80">
-        <v>496.26729999999998</v>
+        <v>200.07499999999999</v>
       </c>
       <c r="Q80">
-        <v>11.469913482666019</v>
+        <v>10.068</v>
       </c>
       <c r="R80">
-        <v>11.469913482666019</v>
+        <v>9.8670799999999996</v>
+      </c>
+      <c r="S80">
+        <f t="shared" ref="S80:S99" si="5">(0.000000000000000138*G80/(1.673534E-24*1.3*0.000000066726*F80*1.8986E+30/(E80*7149200000)^2))/100000</f>
+        <v>2057.1154637812851</v>
+      </c>
+      <c r="T80">
+        <f t="shared" si="4"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B81" t="s">
         <v>20</v>
       </c>
+      <c r="C81">
+        <v>5.21536178778</v>
+      </c>
+      <c r="D81">
+        <v>6.6100000000000006E-2</v>
+      </c>
+      <c r="E81">
+        <v>1.5</v>
+      </c>
+      <c r="F81">
+        <v>1.51</v>
+      </c>
+      <c r="G81">
+        <v>1630</v>
+      </c>
+      <c r="H81" t="s">
+        <v>56</v>
+      </c>
       <c r="I81">
-        <v>6200</v>
+        <v>6250</v>
       </c>
       <c r="J81">
-        <v>1.2</v>
+        <v>2.3901400000000002</v>
+      </c>
+      <c r="K81">
+        <v>1.41</v>
+      </c>
+      <c r="L81">
+        <v>-0.18</v>
+      </c>
+      <c r="M81">
+        <v>3.9</v>
       </c>
       <c r="N81">
-        <v>97.636728000000005</v>
+        <v>0.32576100000000002</v>
       </c>
       <c r="O81">
-        <v>29.672419000000001</v>
+        <v>-8.9262511999999994</v>
       </c>
       <c r="P81">
-        <v>427</v>
+        <v>275.58699999999999</v>
+      </c>
+      <c r="Q81">
+        <v>9.9740000000000002</v>
       </c>
       <c r="R81">
-        <v>11.4986</v>
+        <v>9.8192900000000005</v>
+      </c>
+      <c r="S81">
+        <f t="shared" si="5"/>
+        <v>621.55661806820979</v>
       </c>
       <c r="T81">
-        <f t="shared" ref="T81:T101" si="4">IF(I81&gt;6800,-7,-5)</f>
+        <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="B82" t="s">
         <v>20</v>
       </c>
       <c r="C82">
-        <v>5.3220124999999996</v>
+        <v>2.2437499999999999</v>
       </c>
       <c r="D82">
-        <v>6.08E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E82">
-        <v>1.226</v>
+        <v>1.38</v>
       </c>
       <c r="F82">
-        <v>0.27300000000000002</v>
+        <v>8.84</v>
       </c>
       <c r="G82">
-        <v>1460</v>
-      </c>
-      <c r="H82" t="s">
-        <v>43</v>
+        <v>1872</v>
       </c>
       <c r="I82">
-        <v>5990</v>
+        <v>6475</v>
       </c>
       <c r="J82">
-        <v>1.5609999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="K82">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="L82">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>4.0750000000000002</v>
+        <v>4.07</v>
       </c>
       <c r="N82">
-        <v>210.1935714</v>
+        <v>218.27662470000001</v>
       </c>
       <c r="O82">
-        <v>-30.583608399999999</v>
+        <v>21.8946875</v>
       </c>
       <c r="P82">
-        <v>200.07499999999999</v>
+        <v>161.99700000000001</v>
       </c>
       <c r="Q82">
-        <v>10.068</v>
+        <v>9.7449999999999992</v>
       </c>
       <c r="R82">
-        <v>9.8670799999999996</v>
+        <v>9.6464700000000008</v>
       </c>
       <c r="S82">
-        <f t="shared" ref="S82:S101" si="5">(0.000000000000000138*G82/(1.673534E-24*1.3*0.000000066726*F82*1.8986E+30/(E82*7149200000)^2))/100000</f>
-        <v>2057.1154637812851</v>
+        <f t="shared" si="5"/>
+        <v>103.20465157174387</v>
       </c>
       <c r="T82">
         <f t="shared" si="4"/>
@@ -5560,62 +5627,62 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B83" t="s">
         <v>20</v>
       </c>
       <c r="C83">
-        <v>5.21536178778</v>
+        <v>5.4435399999999996</v>
       </c>
       <c r="D83">
-        <v>6.6100000000000006E-2</v>
+        <v>6.4100000000000004E-2</v>
       </c>
       <c r="E83">
-        <v>1.5</v>
+        <v>0.63</v>
       </c>
       <c r="F83">
-        <v>1.51</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G83">
-        <v>1630</v>
+        <v>1270</v>
       </c>
       <c r="H83" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I83">
-        <v>6250</v>
+        <v>6050</v>
       </c>
       <c r="J83">
-        <v>2.3901400000000002</v>
+        <v>1.22</v>
       </c>
       <c r="K83">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="L83">
-        <v>-0.18</v>
+        <v>0.19</v>
       </c>
       <c r="M83">
-        <v>3.9</v>
+        <v>4.34</v>
       </c>
       <c r="N83">
-        <v>0.32576100000000002</v>
+        <v>144.87510470000001</v>
       </c>
       <c r="O83">
-        <v>-8.9262511999999994</v>
+        <v>-20.982419100000001</v>
       </c>
       <c r="P83">
-        <v>275.58699999999999</v>
+        <v>114.173</v>
       </c>
       <c r="Q83">
-        <v>9.9740000000000002</v>
+        <v>9.3510000000000009</v>
       </c>
       <c r="R83">
-        <v>9.8192900000000005</v>
+        <v>9.2569999999999997</v>
       </c>
       <c r="S83">
         <f t="shared" si="5"/>
-        <v>621.55661806820979</v>
+        <v>1277.1766379712274</v>
       </c>
       <c r="T83">
         <f t="shared" si="4"/>
@@ -5624,123 +5691,126 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="B84" t="s">
         <v>20</v>
       </c>
       <c r="C84">
-        <v>2.2437499999999999</v>
+        <v>3.3448285000000002</v>
       </c>
       <c r="D84">
-        <v>3.6999999999999998E-2</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="E84">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="F84">
-        <v>8.84</v>
+        <v>1.66</v>
       </c>
       <c r="G84">
-        <v>1872</v>
+        <v>2470</v>
+      </c>
+      <c r="H84" t="s">
+        <v>118</v>
       </c>
       <c r="I84">
-        <v>6475</v>
+        <v>9360</v>
       </c>
       <c r="J84">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="K84">
-        <v>1.62</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="M84">
-        <v>4.07</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N84">
-        <v>218.27662470000001</v>
+        <v>227.270329</v>
       </c>
       <c r="O84">
-        <v>21.8946875</v>
+        <v>-42.704965799999997</v>
       </c>
       <c r="P84">
-        <v>161.99700000000001</v>
+        <v>427.678</v>
       </c>
       <c r="Q84">
-        <v>9.7449999999999992</v>
+        <v>9.9459999999999997</v>
       </c>
       <c r="R84">
-        <v>9.6464700000000008</v>
+        <v>9.9122599999999998</v>
       </c>
       <c r="S84">
         <f t="shared" si="5"/>
-        <v>103.20465157174387</v>
+        <v>1247.4798366438731</v>
       </c>
       <c r="T84">
         <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B85" t="s">
         <v>20</v>
       </c>
       <c r="C85">
-        <v>5.4435399999999996</v>
+        <v>0.94145223</v>
       </c>
       <c r="D85">
-        <v>6.4100000000000004E-2</v>
+        <v>2.0240000000000001E-2</v>
       </c>
       <c r="E85">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="F85">
-        <v>0.10100000000000001</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G85">
-        <v>1270</v>
+        <v>2429</v>
       </c>
       <c r="H85" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I85">
-        <v>6050</v>
+        <v>6432</v>
       </c>
       <c r="J85">
-        <v>1.22</v>
+        <v>1.319</v>
       </c>
       <c r="K85">
-        <v>1.19</v>
+        <v>1.294</v>
       </c>
       <c r="L85">
-        <v>0.19</v>
+        <v>0.107</v>
       </c>
       <c r="M85">
-        <v>4.34</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N85">
-        <v>144.87510470000001</v>
+        <v>24.354461799999999</v>
       </c>
       <c r="O85">
-        <v>-20.982419100000001</v>
+        <v>-45.677793700000002</v>
       </c>
       <c r="P85">
-        <v>114.173</v>
+        <v>123.483</v>
       </c>
       <c r="Q85">
-        <v>9.3510000000000009</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R85">
-        <v>9.2569999999999997</v>
+        <v>9.1661699999999993</v>
       </c>
       <c r="S85">
         <f t="shared" si="5"/>
-        <v>1277.1766379712274</v>
+        <v>93.704022194109143</v>
       </c>
       <c r="T85">
         <f t="shared" si="4"/>
@@ -5749,318 +5819,318 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="B86" t="s">
         <v>20</v>
       </c>
       <c r="C86">
-        <v>3.3448285000000002</v>
+        <v>2.7240329999999999</v>
       </c>
       <c r="D86">
-        <v>5.5800000000000002E-2</v>
+        <v>5.0529999999999999E-2</v>
       </c>
       <c r="E86">
-        <v>1.81</v>
+        <v>1.619</v>
       </c>
       <c r="F86">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="G86">
-        <v>2470</v>
-      </c>
-      <c r="H86" t="s">
-        <v>118</v>
+        <v>3353</v>
       </c>
       <c r="I86">
-        <v>9360</v>
+        <v>8000</v>
       </c>
       <c r="J86">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="K86">
-        <v>2.0699999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="L86">
-        <v>0.21</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M86">
-        <v>4.3099999999999996</v>
+        <v>3.9</v>
       </c>
       <c r="N86">
-        <v>227.270329</v>
+        <v>225.68673200000001</v>
       </c>
       <c r="O86">
-        <v>-42.704965799999997</v>
+        <v>-3.0314874000000001</v>
       </c>
       <c r="P86">
-        <v>427.678</v>
+        <v>99.730999999999995</v>
       </c>
       <c r="Q86">
-        <v>9.9459999999999997</v>
+        <v>6.5977600000000001</v>
       </c>
       <c r="R86">
-        <v>9.9122599999999998</v>
-      </c>
-      <c r="S86">
+        <v>6.5536899999999996</v>
+      </c>
+      <c r="S86" s="6">
         <f t="shared" si="5"/>
-        <v>1247.4798366438731</v>
+        <v>1130.2166328238993</v>
       </c>
       <c r="T86">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
+      <c r="U86" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B87" t="s">
         <v>20</v>
       </c>
       <c r="C87">
-        <v>0.94145223</v>
+        <v>1.21987</v>
       </c>
       <c r="D87">
-        <v>2.0240000000000001E-2</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="E87">
-        <v>1.24</v>
+        <v>1.593</v>
       </c>
       <c r="F87">
-        <v>10.199999999999999</v>
+        <v>2.093</v>
       </c>
       <c r="G87">
-        <v>2429</v>
+        <v>2781.7</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="I87">
-        <v>6432</v>
+        <v>7430</v>
       </c>
       <c r="J87">
-        <v>1.319</v>
+        <v>1.444</v>
       </c>
       <c r="K87">
-        <v>1.294</v>
+        <v>1.4950000000000001</v>
       </c>
       <c r="L87">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="M87">
-        <v>4.3099999999999996</v>
+        <v>4.25</v>
       </c>
       <c r="N87">
-        <v>24.354461799999999</v>
+        <v>36.712737500000003</v>
       </c>
       <c r="O87">
-        <v>-45.677793700000002</v>
+        <v>37.5504441</v>
       </c>
       <c r="P87">
-        <v>123.483</v>
+        <v>121.944</v>
       </c>
       <c r="Q87">
-        <v>9.2799999999999994</v>
+        <v>8.14</v>
       </c>
       <c r="R87">
-        <v>9.1661699999999993</v>
+        <v>8.0700400000000005</v>
       </c>
       <c r="S87">
         <f t="shared" si="5"/>
-        <v>93.704022194109143</v>
+        <v>863.09804630713359</v>
       </c>
       <c r="T87">
         <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="B88" t="s">
         <v>20</v>
       </c>
       <c r="C88">
-        <v>2.7240329999999999</v>
+        <v>6.87188</v>
       </c>
       <c r="D88">
-        <v>5.0529999999999999E-2</v>
+        <v>7.5219999999999995E-2</v>
       </c>
       <c r="E88">
-        <v>1.619</v>
+        <v>1.23</v>
       </c>
       <c r="F88">
-        <v>1.99</v>
+        <v>3.44</v>
       </c>
       <c r="G88">
-        <v>3353</v>
+        <v>1250</v>
+      </c>
+      <c r="H88" t="s">
+        <v>70</v>
       </c>
       <c r="I88">
-        <v>8000</v>
+        <v>6180</v>
       </c>
       <c r="J88">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="K88">
-        <v>2.0299999999999998</v>
+        <v>1.76</v>
       </c>
       <c r="L88">
-        <v>0.28999999999999998</v>
+        <v>-0.02</v>
       </c>
       <c r="M88">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="N88">
-        <v>225.68673200000001</v>
+        <v>243.95971940000001</v>
       </c>
       <c r="O88">
-        <v>-3.0314874000000001</v>
+        <v>10.0324103</v>
       </c>
       <c r="P88">
-        <v>99.730999999999995</v>
+        <v>136.24</v>
       </c>
       <c r="Q88">
-        <v>6.5977600000000001</v>
+        <v>9.391</v>
       </c>
       <c r="R88">
-        <v>6.5536899999999996</v>
-      </c>
-      <c r="S88" s="6">
+        <v>9.20974</v>
+      </c>
+      <c r="S88">
         <f t="shared" si="5"/>
-        <v>1130.2166328238993</v>
+        <v>140.68549179703928</v>
       </c>
       <c r="T88">
         <f t="shared" si="4"/>
-        <v>-7</v>
-      </c>
-      <c r="U88" s="1" t="s">
-        <v>137</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="B89" t="s">
         <v>20</v>
       </c>
       <c r="C89">
-        <v>1.21987</v>
+        <v>3.86813881</v>
       </c>
       <c r="D89">
-        <v>2.3900000000000001E-2</v>
+        <v>4.53E-2</v>
       </c>
       <c r="E89">
-        <v>1.593</v>
+        <v>1</v>
       </c>
       <c r="F89">
-        <v>2.093</v>
+        <v>0.26</v>
       </c>
       <c r="G89">
-        <v>2781.7</v>
+        <v>971</v>
       </c>
       <c r="H89" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="I89">
-        <v>7430</v>
+        <v>4792</v>
       </c>
       <c r="J89">
-        <v>1.444</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="K89">
-        <v>1.4950000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="L89">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="M89">
-        <v>4.25</v>
+        <v>4.57</v>
       </c>
       <c r="N89">
-        <v>36.712737500000003</v>
+        <v>315.02596610000001</v>
       </c>
       <c r="O89">
-        <v>37.5504441</v>
+        <v>-5.0948570000000002</v>
       </c>
       <c r="P89">
-        <v>121.944</v>
+        <v>49.960500000000003</v>
       </c>
       <c r="Q89">
-        <v>8.14</v>
+        <v>9.8729999999999993</v>
       </c>
       <c r="R89">
-        <v>8.0700400000000005</v>
+        <v>9.4846599999999999</v>
       </c>
       <c r="S89">
         <f t="shared" si="5"/>
-        <v>863.09804630713359</v>
+        <v>955.72600175951948</v>
       </c>
       <c r="T89">
         <f t="shared" si="4"/>
-        <v>-7</v>
+        <v>-5</v>
+      </c>
+      <c r="U89" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B90" t="s">
         <v>20</v>
       </c>
       <c r="C90">
-        <v>6.87188</v>
+        <v>4.9546416000000004</v>
       </c>
       <c r="D90">
-        <v>7.5219999999999995E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="E90">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="F90">
-        <v>3.44</v>
+        <v>0.96</v>
       </c>
       <c r="G90">
-        <v>1250</v>
-      </c>
-      <c r="H90" t="s">
-        <v>70</v>
+        <v>1487</v>
       </c>
       <c r="I90">
-        <v>6180</v>
+        <v>6400</v>
       </c>
       <c r="J90">
-        <v>1.52</v>
+        <v>1.4319999999999999</v>
       </c>
       <c r="K90">
-        <v>1.76</v>
+        <v>1.276</v>
       </c>
       <c r="L90">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>4.25</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="N90">
-        <v>243.95971940000001</v>
+        <v>311.04275580000001</v>
       </c>
       <c r="O90">
-        <v>10.0324103</v>
+        <v>-39.225485599999999</v>
       </c>
       <c r="P90">
-        <v>136.24</v>
+        <v>162.303</v>
       </c>
       <c r="Q90">
-        <v>9.391</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="R90">
-        <v>9.20974</v>
+        <v>9.3767099999999992</v>
       </c>
       <c r="S90">
         <f t="shared" si="5"/>
-        <v>140.68549179703928</v>
+        <v>701.18164217622461</v>
       </c>
       <c r="T90">
         <f t="shared" si="4"/>
@@ -6069,126 +6139,126 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B91" t="s">
         <v>20</v>
       </c>
       <c r="C91">
-        <v>3.86813881</v>
+        <v>2.13775</v>
       </c>
       <c r="D91">
-        <v>4.53E-2</v>
+        <v>3.4430000000000002E-2</v>
       </c>
       <c r="E91">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="F91">
-        <v>0.26</v>
+        <v>0.72</v>
       </c>
       <c r="G91">
-        <v>971</v>
+        <v>1865</v>
       </c>
       <c r="H91" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="I91">
-        <v>4792</v>
+        <v>5990</v>
       </c>
       <c r="J91">
-        <v>0.80100000000000005</v>
+        <v>1.42</v>
       </c>
       <c r="K91">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="L91">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="M91">
-        <v>4.57</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="N91">
-        <v>315.02596610000001</v>
+        <v>304.53884299999999</v>
       </c>
       <c r="O91">
-        <v>-5.0948570000000002</v>
+        <v>-1.0760033</v>
       </c>
       <c r="P91">
-        <v>49.960500000000003</v>
+        <v>149.21600000000001</v>
       </c>
       <c r="Q91">
-        <v>9.8729999999999993</v>
+        <v>9.75</v>
       </c>
       <c r="R91">
-        <v>9.4846599999999999</v>
+        <v>9.5723000000000003</v>
       </c>
       <c r="S91">
         <f t="shared" si="5"/>
-        <v>955.72600175951948</v>
+        <v>1226.0598654781754</v>
       </c>
       <c r="T91">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
-      <c r="U91" s="1" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B92" t="s">
         <v>20</v>
       </c>
       <c r="C92">
-        <v>4.9546416000000004</v>
+        <v>1.8098819799999999</v>
       </c>
       <c r="D92">
-        <v>6.1699999999999998E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="E92">
-        <v>1.33</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="F92">
-        <v>0.96</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G92">
-        <v>1487</v>
+        <v>2228</v>
+      </c>
+      <c r="H92" t="s">
+        <v>52</v>
       </c>
       <c r="I92">
-        <v>6400</v>
+        <v>6329</v>
       </c>
       <c r="J92">
-        <v>1.4319999999999999</v>
+        <v>1.756</v>
       </c>
       <c r="K92">
-        <v>1.276</v>
+        <v>1.458</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M92">
-        <v>4.2320000000000002</v>
+        <v>4.1959999999999997</v>
       </c>
       <c r="N92">
-        <v>311.04275580000001</v>
+        <v>26.632936000000001</v>
       </c>
       <c r="O92">
-        <v>-39.225485599999999</v>
+        <v>2.7003889999999999</v>
       </c>
       <c r="P92">
-        <v>162.303</v>
+        <v>194.459</v>
       </c>
       <c r="Q92">
-        <v>9.5039999999999996</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="R92">
-        <v>9.3767099999999992</v>
+        <v>9.3950700000000005</v>
       </c>
       <c r="S92">
         <f t="shared" si="5"/>
-        <v>701.18164217622461</v>
+        <v>2192.2225820487197</v>
       </c>
       <c r="T92">
         <f t="shared" si="4"/>
@@ -6197,62 +6267,62 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="B93" t="s">
         <v>20</v>
       </c>
       <c r="C93">
-        <v>2.13775</v>
+        <v>3.6623920000000001</v>
       </c>
       <c r="D93">
-        <v>3.4430000000000002E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
       <c r="E93">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="F93">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="G93">
-        <v>1865</v>
+        <v>1716.2</v>
       </c>
       <c r="H93" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="I93">
-        <v>5990</v>
+        <v>6600</v>
       </c>
       <c r="J93">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="K93">
-        <v>0.98</v>
+        <v>1.39</v>
       </c>
       <c r="L93">
-        <v>0.39</v>
+        <v>0.03</v>
       </c>
       <c r="M93">
-        <v>4.3899999999999997</v>
+        <v>4.2</v>
       </c>
       <c r="N93">
-        <v>304.53884299999999</v>
+        <v>66.370901599999996</v>
       </c>
       <c r="O93">
-        <v>-1.0760033</v>
+        <v>-30.600436200000001</v>
       </c>
       <c r="P93">
-        <v>149.21600000000001</v>
+        <v>246.69</v>
       </c>
       <c r="Q93">
-        <v>9.75</v>
+        <v>10.044</v>
       </c>
       <c r="R93">
-        <v>9.5723000000000003</v>
+        <v>9.9720200000000006</v>
       </c>
       <c r="S93">
         <f t="shared" si="5"/>
-        <v>1226.0598654781754</v>
+        <v>1209.5375438309629</v>
       </c>
       <c r="T93">
         <f t="shared" si="4"/>
@@ -6261,62 +6331,62 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
       </c>
       <c r="C94">
-        <v>1.8098819799999999</v>
+        <v>8.1587200000000006</v>
       </c>
       <c r="D94">
-        <v>3.3000000000000002E-2</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="E94">
-        <v>1.8540000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F94">
-        <v>0.89400000000000002</v>
+        <v>2.54</v>
       </c>
       <c r="G94">
-        <v>2228</v>
+        <v>1059</v>
       </c>
       <c r="H94" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="I94">
-        <v>6329</v>
+        <v>5600</v>
       </c>
       <c r="J94">
-        <v>1.756</v>
+        <v>1.03</v>
       </c>
       <c r="K94">
-        <v>1.458</v>
+        <v>1.34</v>
       </c>
       <c r="L94">
-        <v>0.36599999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="M94">
-        <v>4.1959999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="N94">
-        <v>26.632936000000001</v>
+        <v>359.90087369999998</v>
       </c>
       <c r="O94">
-        <v>2.7003889999999999</v>
+        <v>-35.031334899999997</v>
       </c>
       <c r="P94">
-        <v>194.459</v>
+        <v>89.960599999999999</v>
       </c>
       <c r="Q94">
-        <v>9.5180000000000007</v>
+        <v>9.7889999999999997</v>
       </c>
       <c r="R94">
-        <v>9.3950700000000005</v>
+        <v>9.6124899999999993</v>
       </c>
       <c r="S94">
         <f t="shared" si="5"/>
-        <v>2192.2225820487197</v>
+        <v>136.24063220140397</v>
       </c>
       <c r="T94">
         <f t="shared" si="4"/>
@@ -6325,62 +6395,62 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B95" t="s">
         <v>20</v>
       </c>
       <c r="C95">
-        <v>3.6623920000000001</v>
+        <v>2.7057899999999999</v>
       </c>
       <c r="D95">
-        <v>5.1900000000000002E-2</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E95">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="F95">
-        <v>0.85</v>
+        <v>1.17</v>
       </c>
       <c r="G95">
-        <v>1716.2</v>
+        <v>2190</v>
       </c>
       <c r="H95" t="s">
         <v>127</v>
       </c>
       <c r="I95">
-        <v>6600</v>
+        <v>6480</v>
       </c>
       <c r="J95">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="K95">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="L95">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="M95">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="N95">
-        <v>66.370901599999996</v>
+        <v>72.660591600000004</v>
       </c>
       <c r="O95">
-        <v>-30.600436200000001</v>
+        <v>1.8938364999999999</v>
       </c>
       <c r="P95">
-        <v>246.69</v>
+        <v>275.66399999999999</v>
       </c>
       <c r="Q95">
-        <v>10.044</v>
+        <v>10.073</v>
       </c>
       <c r="R95">
-        <v>9.9720200000000006</v>
+        <v>9.8979599999999994</v>
       </c>
       <c r="S95">
         <f t="shared" si="5"/>
-        <v>1209.5375438309629</v>
+        <v>1257.117296864338</v>
       </c>
       <c r="T95">
         <f t="shared" si="4"/>
@@ -6389,62 +6459,62 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="B96" t="s">
         <v>20</v>
       </c>
       <c r="C96">
-        <v>8.1587200000000006</v>
+        <v>3.9501900000000001</v>
       </c>
       <c r="D96">
-        <v>8.0100000000000005E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E96">
-        <v>1.1299999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="F96">
-        <v>2.54</v>
+        <v>0.5</v>
       </c>
       <c r="G96">
-        <v>1059</v>
+        <v>1604</v>
       </c>
       <c r="H96" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="I96">
-        <v>5600</v>
+        <v>6170</v>
       </c>
       <c r="J96">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="K96">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="L96">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="M96">
-        <v>4.5</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="N96">
-        <v>359.90087369999998</v>
+        <v>313.78323929999999</v>
       </c>
       <c r="O96">
-        <v>-35.031334899999997</v>
+        <v>-34.135751200000001</v>
       </c>
       <c r="P96">
-        <v>89.960599999999999</v>
+        <v>211.21100000000001</v>
       </c>
       <c r="Q96">
-        <v>9.7889999999999997</v>
+        <v>10.051</v>
       </c>
       <c r="R96">
-        <v>9.6124899999999993</v>
+        <v>10.028499999999999</v>
       </c>
       <c r="S96">
         <f t="shared" si="5"/>
-        <v>136.24063220140397</v>
+        <v>2049.4439875099679</v>
       </c>
       <c r="T96">
         <f t="shared" si="4"/>
@@ -6453,62 +6523,62 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B97" t="s">
         <v>20</v>
       </c>
       <c r="C97">
-        <v>2.7057899999999999</v>
+        <v>2.1846700000000001</v>
       </c>
       <c r="D97">
-        <v>4.4699999999999997E-2</v>
+        <v>3.4160000000000003E-2</v>
       </c>
       <c r="E97">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="F97">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="G97">
-        <v>2190</v>
+        <v>1570</v>
       </c>
       <c r="H97" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="I97">
-        <v>6480</v>
+        <v>5830</v>
       </c>
       <c r="J97">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="K97">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="L97">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M97">
-        <v>3.96</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N97">
-        <v>72.660591600000004</v>
+        <v>337.45782430000003</v>
       </c>
       <c r="O97">
-        <v>1.8938364999999999</v>
+        <v>-48.003098799999997</v>
       </c>
       <c r="P97">
-        <v>275.66399999999999</v>
+        <v>137.54400000000001</v>
       </c>
       <c r="Q97">
-        <v>10.073</v>
+        <v>10.092000000000001</v>
       </c>
       <c r="R97">
-        <v>9.8979599999999994</v>
+        <v>9.9369700000000005</v>
       </c>
       <c r="S97">
         <f t="shared" si="5"/>
-        <v>1257.117296864338</v>
+        <v>422.11900227636102</v>
       </c>
       <c r="T97">
         <f t="shared" si="4"/>
@@ -6517,62 +6587,62 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B98" t="s">
         <v>20</v>
       </c>
       <c r="C98">
-        <v>3.9501900000000001</v>
+        <v>5.75251</v>
       </c>
       <c r="D98">
-        <v>5.5E-2</v>
+        <v>7.17E-2</v>
       </c>
       <c r="E98">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="F98">
-        <v>0.5</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="G98">
-        <v>1604</v>
+        <v>1480</v>
       </c>
       <c r="H98" t="s">
         <v>54</v>
       </c>
       <c r="I98">
-        <v>6170</v>
+        <v>6150</v>
       </c>
       <c r="J98">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="K98">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="L98">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="M98">
-        <v>4.2699999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="N98">
-        <v>313.78323929999999</v>
+        <v>39.897668899999999</v>
       </c>
       <c r="O98">
-        <v>-34.135751200000001</v>
+        <v>-50.008193400000003</v>
       </c>
       <c r="P98">
-        <v>211.21100000000001</v>
+        <v>158.66</v>
       </c>
       <c r="Q98">
-        <v>10.051</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="R98">
-        <v>10.028499999999999</v>
+        <v>9.3251000000000008</v>
       </c>
       <c r="S98">
         <f t="shared" si="5"/>
-        <v>2049.4439875099679</v>
+        <v>162.15983922320817</v>
       </c>
       <c r="T98">
         <f t="shared" si="4"/>
@@ -6581,199 +6651,71 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="B99" t="s">
         <v>20</v>
       </c>
       <c r="C99">
-        <v>2.1846700000000001</v>
+        <v>3.1915399999999998</v>
       </c>
       <c r="D99">
-        <v>3.4160000000000003E-2</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="E99">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="F99">
-        <v>1.44</v>
+        <v>7.29</v>
       </c>
       <c r="G99">
-        <v>1570</v>
+        <v>1729</v>
       </c>
       <c r="H99" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="I99">
-        <v>5830</v>
+        <v>6429</v>
       </c>
       <c r="J99">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="K99">
-        <v>1.46</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L99">
-        <v>0.14000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="M99">
-        <v>4.3600000000000003</v>
+        <v>3.95</v>
       </c>
       <c r="N99">
-        <v>337.45782430000003</v>
+        <v>65.469581399999996</v>
       </c>
       <c r="O99">
-        <v>-48.003098799999997</v>
+        <v>57.817209499999997</v>
       </c>
       <c r="P99">
-        <v>137.54400000000001</v>
+        <v>213.053</v>
       </c>
       <c r="Q99">
-        <v>10.092000000000001</v>
+        <v>9.8539999999999992</v>
       </c>
       <c r="R99">
-        <v>9.9369700000000005</v>
+        <v>9.7388899999999996</v>
       </c>
       <c r="S99">
         <f t="shared" si="5"/>
-        <v>422.11900227636102</v>
+        <v>120.66830436099001</v>
       </c>
       <c r="T99">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>79</v>
-      </c>
-      <c r="B100" t="s">
-        <v>20</v>
-      </c>
-      <c r="C100">
-        <v>5.75251</v>
-      </c>
-      <c r="D100">
-        <v>7.17E-2</v>
-      </c>
-      <c r="E100">
-        <v>1.02</v>
-      </c>
-      <c r="F100">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="G100">
-        <v>1480</v>
-      </c>
-      <c r="H100" t="s">
-        <v>54</v>
-      </c>
-      <c r="I100">
-        <v>6150</v>
-      </c>
-      <c r="J100">
-        <v>1.64</v>
-      </c>
-      <c r="K100">
-        <v>1.21</v>
-      </c>
-      <c r="L100">
-        <v>0.21</v>
-      </c>
-      <c r="M100">
-        <v>4.3</v>
-      </c>
-      <c r="N100">
-        <v>39.897668899999999</v>
-      </c>
-      <c r="O100">
-        <v>-50.008193400000003</v>
-      </c>
-      <c r="P100">
-        <v>158.66</v>
-      </c>
-      <c r="Q100">
-        <v>9.4749999999999996</v>
-      </c>
-      <c r="R100">
-        <v>9.3251000000000008</v>
-      </c>
-      <c r="S100">
-        <f t="shared" si="5"/>
-        <v>162.15983922320817</v>
-      </c>
-      <c r="T100">
-        <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>107</v>
-      </c>
-      <c r="B101" t="s">
-        <v>20</v>
-      </c>
-      <c r="C101">
-        <v>3.1915399999999998</v>
-      </c>
-      <c r="D101">
-        <v>4.7600000000000003E-2</v>
-      </c>
-      <c r="E101">
-        <v>1.41</v>
-      </c>
-      <c r="F101">
-        <v>7.29</v>
-      </c>
-      <c r="G101">
-        <v>1729</v>
-      </c>
-      <c r="H101" t="s">
-        <v>108</v>
-      </c>
-      <c r="I101">
-        <v>6429</v>
-      </c>
-      <c r="J101">
-        <v>1.54</v>
-      </c>
-      <c r="K101">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="L101">
-        <v>-0.18</v>
-      </c>
-      <c r="M101">
-        <v>3.95</v>
-      </c>
-      <c r="N101">
-        <v>65.469581399999996</v>
-      </c>
-      <c r="O101">
-        <v>57.817209499999997</v>
-      </c>
-      <c r="P101">
-        <v>213.053</v>
-      </c>
-      <c r="Q101">
-        <v>9.8539999999999992</v>
-      </c>
-      <c r="R101">
-        <v>9.7388899999999996</v>
-      </c>
-      <c r="S101">
-        <f t="shared" si="5"/>
-        <v>120.66830436099001</v>
-      </c>
-      <c r="T101">
-        <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R78">
+  <autoFilter ref="A1:X99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">
     <sortCondition ref="Q2"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F811CB-D2E3-EA4F-BD56-C7A07385F396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D736A5-1AF2-8444-9345-6699166DB788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7600" yWindow="7040" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="165">
   <si>
     <t>#pl_name</t>
   </si>
@@ -528,6 +528,9 @@
   </si>
   <si>
     <t>4113444695135680128 b</t>
+  </si>
+  <si>
+    <t>HD 84979 b</t>
   </si>
 </sst>
 </file>
@@ -566,15 +569,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -612,13 +621,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -638,6 +656,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -915,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC99"/>
+  <dimension ref="A1:BC100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -6713,6 +6734,26 @@
         <v>-5</v>
       </c>
     </row>
+    <row r="100" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I100">
+        <v>7065.3916019999997</v>
+      </c>
+      <c r="N100">
+        <v>146.7834014</v>
+      </c>
+      <c r="O100">
+        <v>-54.204010279999999</v>
+      </c>
+      <c r="P100">
+        <v>300.9884644</v>
+      </c>
+      <c r="R100">
+        <v>9.2583198549999999</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D736A5-1AF2-8444-9345-6699166DB788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD93ED1-1396-9F4E-A85A-D0ED3EBB4825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7600" yWindow="7040" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$X$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
   <si>
     <t>#pl_name</t>
   </si>
@@ -462,9 +462,6 @@
   </si>
   <si>
     <t>B9.5-A0</t>
-  </si>
-  <si>
-    <t>V_MAG</t>
   </si>
   <si>
     <t>B_MAG</t>
@@ -636,7 +633,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -647,9 +644,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -936,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BC100"/>
+  <dimension ref="A1:BB100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -958,24 +952,23 @@
     <col min="19" max="19" width="16.1640625" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="7" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13.33203125" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9"/>
-    <col min="27" max="27" width="9.83203125"/>
-    <col min="28" max="28" width="9"/>
-    <col min="30" max="30" width="9.83203125"/>
-    <col min="31" max="31" width="9"/>
-    <col min="36" max="36" width="9.83203125"/>
-    <col min="37" max="37" width="9"/>
-    <col min="42" max="42" width="9.83203125"/>
-    <col min="43" max="43" width="9"/>
-    <col min="45" max="45" width="9.83203125"/>
-    <col min="46" max="46" width="9"/>
-    <col min="55" max="55" width="8.1640625"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9"/>
+    <col min="26" max="26" width="9.83203125"/>
+    <col min="27" max="27" width="9"/>
+    <col min="29" max="29" width="9.83203125"/>
+    <col min="30" max="30" width="9"/>
+    <col min="35" max="35" width="9.83203125"/>
+    <col min="36" max="36" width="9"/>
+    <col min="41" max="41" width="9.83203125"/>
+    <col min="42" max="42" width="9"/>
+    <col min="44" max="44" width="9.83203125"/>
+    <col min="45" max="45" width="9"/>
+    <col min="54" max="54" width="8.1640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1045,13 +1038,10 @@
       <c r="W1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="X1" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:55" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I2">
         <v>3501</v>
@@ -1077,22 +1067,22 @@
       <c r="P2">
         <v>1025.1500000000001</v>
       </c>
+      <c r="Q2">
+        <v>11.035</v>
+      </c>
       <c r="V2">
-        <v>11.035</v>
-      </c>
-      <c r="W2">
         <v>12.885999999999999</v>
       </c>
-      <c r="X2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AZ2" s="3"/>
+      <c r="W2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AY2" s="3"/>
+      <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
-      <c r="BC2" s="3"/>
-    </row>
-    <row r="3" spans="1:55" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I3">
         <v>3496</v>
@@ -1118,22 +1108,22 @@
       <c r="P3">
         <v>1655.31</v>
       </c>
+      <c r="Q3">
+        <v>10.977</v>
+      </c>
       <c r="V3">
-        <v>10.977</v>
-      </c>
-      <c r="W3">
         <v>12.571999999999999</v>
       </c>
-      <c r="X3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AZ3" s="3"/>
+      <c r="W3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AY3" s="3"/>
+      <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
-      <c r="BC3" s="3"/>
-    </row>
-    <row r="4" spans="1:55" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I4">
         <v>3460</v>
@@ -1159,22 +1149,22 @@
       <c r="P4">
         <v>312.65899999999999</v>
       </c>
+      <c r="Q4">
+        <v>10.968999999999999</v>
+      </c>
       <c r="V4">
-        <v>10.968999999999999</v>
-      </c>
-      <c r="W4">
         <v>11.454000000000001</v>
       </c>
-      <c r="X4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ4" s="3"/>
+      <c r="W4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AY4" s="3"/>
+      <c r="BA4" s="3"/>
       <c r="BB4" s="3"/>
-      <c r="BC4" s="3"/>
-    </row>
-    <row r="5" spans="1:55" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I5">
         <v>5804</v>
@@ -1200,22 +1190,22 @@
       <c r="P5">
         <v>1644.4</v>
       </c>
+      <c r="Q5">
+        <v>15.965999999999999</v>
+      </c>
       <c r="V5">
-        <v>15.965999999999999</v>
-      </c>
-      <c r="W5">
         <v>16.86</v>
       </c>
-      <c r="X5" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ5" s="3"/>
+      <c r="W5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AY5" s="3"/>
+      <c r="BA5" s="3"/>
       <c r="BB5" s="3"/>
-      <c r="BC5" s="3"/>
-    </row>
-    <row r="6" spans="1:55" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I6">
         <v>5800</v>
@@ -1241,22 +1231,22 @@
       <c r="P6">
         <v>2963.53</v>
       </c>
+      <c r="Q6">
+        <v>17.052</v>
+      </c>
       <c r="V6">
-        <v>17.052</v>
-      </c>
-      <c r="W6">
         <v>17.364000000000001</v>
       </c>
-      <c r="X6" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ6" s="3"/>
+      <c r="W6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AY6" s="3"/>
+      <c r="BA6" s="3"/>
       <c r="BB6" s="3"/>
-      <c r="BC6" s="3"/>
-    </row>
-    <row r="7" spans="1:55" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I7">
         <v>5799</v>
@@ -1282,19 +1272,19 @@
       <c r="P7">
         <v>224.12799999999999</v>
       </c>
+      <c r="Q7">
+        <v>11.997</v>
+      </c>
       <c r="V7">
-        <v>11.997</v>
-      </c>
-      <c r="W7">
         <v>12.47</v>
       </c>
-      <c r="X7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I8">
         <v>5800.4</v>
@@ -1320,19 +1310,19 @@
       <c r="P8">
         <v>579.08500000000004</v>
       </c>
+      <c r="Q8">
+        <v>12.978999999999999</v>
+      </c>
       <c r="V8">
-        <v>12.978999999999999</v>
-      </c>
-      <c r="W8">
         <v>13.638999999999999</v>
       </c>
-      <c r="X8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I9">
         <v>5813</v>
@@ -1358,19 +1348,19 @@
       <c r="P9">
         <v>1779.6</v>
       </c>
+      <c r="Q9">
+        <v>14.999000000000001</v>
+      </c>
       <c r="V9">
-        <v>14.999000000000001</v>
-      </c>
-      <c r="W9">
         <v>15.66</v>
       </c>
-      <c r="X9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I10">
         <v>5820</v>
@@ -1396,19 +1386,19 @@
       <c r="P10">
         <v>6401.77</v>
       </c>
+      <c r="Q10">
+        <v>15.007999999999999</v>
+      </c>
       <c r="V10">
-        <v>15.007999999999999</v>
-      </c>
-      <c r="W10">
         <v>15.702999999999999</v>
       </c>
-      <c r="X10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I11">
         <v>5824</v>
@@ -1434,19 +1424,19 @@
       <c r="P11">
         <v>1961.4</v>
       </c>
+      <c r="Q11">
+        <v>14.023</v>
+      </c>
       <c r="V11">
-        <v>14.023</v>
-      </c>
-      <c r="W11">
         <v>15.048999999999999</v>
       </c>
-      <c r="X11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I12">
         <v>5816</v>
@@ -1472,19 +1462,19 @@
       <c r="P12">
         <v>3747.72</v>
       </c>
+      <c r="Q12">
+        <v>15.958</v>
+      </c>
       <c r="V12">
-        <v>15.958</v>
-      </c>
-      <c r="W12">
         <v>17.585999999999999</v>
       </c>
-      <c r="X12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I13">
         <v>5792</v>
@@ -1507,19 +1497,19 @@
       <c r="P13">
         <v>2046.66</v>
       </c>
+      <c r="Q13">
+        <v>17.097000000000001</v>
+      </c>
       <c r="R13">
         <v>16.870684000000001</v>
       </c>
       <c r="V13">
-        <v>17.097000000000001</v>
-      </c>
-      <c r="W13">
         <v>18.082999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I14">
         <v>5775</v>
@@ -1545,19 +1535,19 @@
       <c r="P14">
         <v>1802.37</v>
       </c>
+      <c r="Q14">
+        <v>12.961</v>
+      </c>
       <c r="V14">
-        <v>12.961</v>
-      </c>
-      <c r="W14">
         <v>14.082000000000001</v>
       </c>
-      <c r="X14" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I15">
         <v>5800</v>
@@ -1583,19 +1573,19 @@
       <c r="P15">
         <v>897.52700000000004</v>
       </c>
+      <c r="Q15">
+        <v>13.994999999999999</v>
+      </c>
       <c r="V15">
-        <v>13.994999999999999</v>
-      </c>
-      <c r="W15">
         <v>14.913</v>
       </c>
-      <c r="X15" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:55" x14ac:dyDescent="0.2">
+      <c r="W15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I16">
         <v>5806</v>
@@ -1621,19 +1611,19 @@
       <c r="P16">
         <v>7397.91</v>
       </c>
+      <c r="Q16">
+        <v>12.01</v>
+      </c>
       <c r="V16">
-        <v>12.01</v>
-      </c>
-      <c r="W16">
         <v>12.507</v>
       </c>
-      <c r="X16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I17">
         <v>5815.4</v>
@@ -1659,19 +1649,19 @@
       <c r="P17">
         <v>398.375</v>
       </c>
+      <c r="Q17">
+        <v>11.137</v>
+      </c>
       <c r="V17">
-        <v>11.137</v>
-      </c>
-      <c r="W17">
         <v>11.56</v>
       </c>
-      <c r="X17" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I18">
         <v>5812</v>
@@ -1697,17 +1687,17 @@
       <c r="P18">
         <v>147.77799999999999</v>
       </c>
+      <c r="Q18">
+        <v>11.044</v>
+      </c>
       <c r="V18">
-        <v>11.044</v>
-      </c>
-      <c r="W18">
         <v>11.662000000000001</v>
       </c>
-      <c r="X18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -1771,7 +1761,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -1835,7 +1825,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1899,7 +1889,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -1963,7 +1953,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>139</v>
       </c>
@@ -1991,9 +1981,8 @@
       <c r="R23">
         <v>11.12930202484131</v>
       </c>
-      <c r="V23" s="4"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>88</v>
       </c>
@@ -2053,9 +2042,8 @@
         <f>IF(I24&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
-      <c r="V24" s="4"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -2116,7 +2104,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>140</v>
       </c>
@@ -2139,7 +2127,7 @@
         <v>10.36768245697021</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -2199,9 +2187,8 @@
         <f t="shared" ref="T27:T50" si="1">IF(I27&gt;6800,-7,-5)</f>
         <v>-7</v>
       </c>
-      <c r="V27" s="4"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2265,7 +2252,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2329,7 +2316,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -2392,9 +2379,8 @@
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V30" s="4"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2458,7 +2444,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -2521,7 +2507,6 @@
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="V32" s="4"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -2639,7 +2624,7 @@
       <c r="R34">
         <v>7.5086599999999999</v>
       </c>
-      <c r="S34" s="5">
+      <c r="S34" s="4">
         <f t="shared" si="0"/>
         <v>988.21070019970352</v>
       </c>
@@ -5890,7 +5875,7 @@
       <c r="R86">
         <v>6.5536899999999996</v>
       </c>
-      <c r="S86" s="6">
+      <c r="S86" s="5">
         <f t="shared" si="5"/>
         <v>1130.2166328238993</v>
       </c>
@@ -6735,8 +6720,8 @@
       </c>
     </row>
     <row r="100" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
-        <v>164</v>
+      <c r="A100" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="I100">
         <v>7065.3916019999997</v>
@@ -6755,7 +6740,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:W99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">
     <sortCondition ref="Q2"/>
   </sortState>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD93ED1-1396-9F4E-A85A-D0ED3EBB4825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0F22DF-0304-404A-9524-A0448C59AB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7600" yWindow="7040" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="165">
   <si>
     <t>#pl_name</t>
   </si>
@@ -528,6 +528,9 @@
   </si>
   <si>
     <t>HD 84979 b</t>
+  </si>
+  <si>
+    <t>4037578191010248064 b</t>
   </si>
 </sst>
 </file>
@@ -633,7 +636,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -653,6 +656,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -930,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB100"/>
+  <dimension ref="A1:BB101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -5438,7 +5444,7 @@
         <v>11.4986</v>
       </c>
       <c r="T79">
-        <f t="shared" ref="T79:T99" si="4">IF(I79&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T79:T100" si="4">IF(I79&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -5498,7 +5504,7 @@
         <v>9.8670799999999996</v>
       </c>
       <c r="S80">
-        <f t="shared" ref="S80:S99" si="5">(0.000000000000000138*G80/(1.673534E-24*1.3*0.000000066726*F80*1.8986E+30/(E80*7149200000)^2))/100000</f>
+        <f t="shared" ref="S80:S100" si="5">(0.000000000000000138*G80/(1.673534E-24*1.3*0.000000066726*F80*1.8986E+30/(E80*7149200000)^2))/100000</f>
         <v>2057.1154637812851</v>
       </c>
       <c r="T80">
@@ -6272,127 +6278,86 @@
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="A93" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I93" s="1">
+        <v>3472</v>
+      </c>
+      <c r="J93">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="K93">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="N93">
+        <v>272.54430475160001</v>
+      </c>
+      <c r="O93">
+        <v>-37.644513386920003</v>
+      </c>
+      <c r="P93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
         <v>126</v>
       </c>
-      <c r="B93" t="s">
-        <v>20</v>
-      </c>
-      <c r="C93">
+      <c r="B94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94">
         <v>3.6623920000000001</v>
       </c>
-      <c r="D93">
+      <c r="D94">
         <v>5.1900000000000002E-2</v>
       </c>
-      <c r="E93">
+      <c r="E94">
         <v>1.53</v>
       </c>
-      <c r="F93">
+      <c r="F94">
         <v>0.85</v>
       </c>
-      <c r="G93">
+      <c r="G94">
         <v>1716.2</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H94" t="s">
         <v>127</v>
       </c>
-      <c r="I93">
+      <c r="I94">
         <v>6600</v>
       </c>
-      <c r="J93">
+      <c r="J94">
         <v>1.51</v>
       </c>
-      <c r="K93">
+      <c r="K94">
         <v>1.39</v>
       </c>
-      <c r="L93">
+      <c r="L94">
         <v>0.03</v>
       </c>
-      <c r="M93">
+      <c r="M94">
         <v>4.2</v>
       </c>
-      <c r="N93">
+      <c r="N94">
         <v>66.370901599999996</v>
       </c>
-      <c r="O93">
+      <c r="O94">
         <v>-30.600436200000001</v>
       </c>
-      <c r="P93">
+      <c r="P94">
         <v>246.69</v>
       </c>
-      <c r="Q93">
+      <c r="Q94">
         <v>10.044</v>
       </c>
-      <c r="R93">
+      <c r="R94">
         <v>9.9720200000000006</v>
       </c>
-      <c r="S93">
+      <c r="S94">
         <f t="shared" si="5"/>
         <v>1209.5375438309629</v>
-      </c>
-      <c r="T93">
-        <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>96</v>
-      </c>
-      <c r="B94" t="s">
-        <v>20</v>
-      </c>
-      <c r="C94">
-        <v>8.1587200000000006</v>
-      </c>
-      <c r="D94">
-        <v>8.0100000000000005E-2</v>
-      </c>
-      <c r="E94">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F94">
-        <v>2.54</v>
-      </c>
-      <c r="G94">
-        <v>1059</v>
-      </c>
-      <c r="H94" t="s">
-        <v>97</v>
-      </c>
-      <c r="I94">
-        <v>5600</v>
-      </c>
-      <c r="J94">
-        <v>1.03</v>
-      </c>
-      <c r="K94">
-        <v>1.34</v>
-      </c>
-      <c r="L94">
-        <v>0.17</v>
-      </c>
-      <c r="M94">
-        <v>4.5</v>
-      </c>
-      <c r="N94">
-        <v>359.90087369999998</v>
-      </c>
-      <c r="O94">
-        <v>-35.031334899999997</v>
-      </c>
-      <c r="P94">
-        <v>89.960599999999999</v>
-      </c>
-      <c r="Q94">
-        <v>9.7889999999999997</v>
-      </c>
-      <c r="R94">
-        <v>9.6124899999999993</v>
-      </c>
-      <c r="S94">
-        <f t="shared" si="5"/>
-        <v>136.24063220140397</v>
       </c>
       <c r="T94">
         <f t="shared" si="4"/>
@@ -6401,62 +6366,62 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
         <v>20</v>
       </c>
       <c r="C95">
-        <v>2.7057899999999999</v>
+        <v>8.1587200000000006</v>
       </c>
       <c r="D95">
-        <v>4.4699999999999997E-2</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="E95">
-        <v>1.62</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F95">
-        <v>1.17</v>
+        <v>2.54</v>
       </c>
       <c r="G95">
-        <v>2190</v>
+        <v>1059</v>
       </c>
       <c r="H95" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="I95">
-        <v>6480</v>
+        <v>5600</v>
       </c>
       <c r="J95">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="K95">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="L95">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="M95">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="N95">
-        <v>72.660591600000004</v>
+        <v>359.90087369999998</v>
       </c>
       <c r="O95">
-        <v>1.8938364999999999</v>
+        <v>-35.031334899999997</v>
       </c>
       <c r="P95">
-        <v>275.66399999999999</v>
+        <v>89.960599999999999</v>
       </c>
       <c r="Q95">
-        <v>10.073</v>
+        <v>9.7889999999999997</v>
       </c>
       <c r="R95">
-        <v>9.8979599999999994</v>
+        <v>9.6124899999999993</v>
       </c>
       <c r="S95">
         <f t="shared" si="5"/>
-        <v>1257.117296864338</v>
+        <v>136.24063220140397</v>
       </c>
       <c r="T95">
         <f t="shared" si="4"/>
@@ -6465,62 +6430,62 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B96" t="s">
         <v>20</v>
       </c>
       <c r="C96">
-        <v>3.9501900000000001</v>
+        <v>2.7057899999999999</v>
       </c>
       <c r="D96">
-        <v>5.5E-2</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E96">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="F96">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="G96">
-        <v>1604</v>
+        <v>2190</v>
       </c>
       <c r="H96" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="I96">
-        <v>6170</v>
+        <v>6480</v>
       </c>
       <c r="J96">
+        <v>2.1</v>
+      </c>
+      <c r="K96">
         <v>1.48</v>
       </c>
-      <c r="K96">
-        <v>1.67</v>
-      </c>
       <c r="L96">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="M96">
-        <v>4.2699999999999996</v>
+        <v>3.96</v>
       </c>
       <c r="N96">
-        <v>313.78323929999999</v>
+        <v>72.660591600000004</v>
       </c>
       <c r="O96">
-        <v>-34.135751200000001</v>
+        <v>1.8938364999999999</v>
       </c>
       <c r="P96">
-        <v>211.21100000000001</v>
+        <v>275.66399999999999</v>
       </c>
       <c r="Q96">
-        <v>10.051</v>
+        <v>10.073</v>
       </c>
       <c r="R96">
-        <v>10.028499999999999</v>
+        <v>9.8979599999999994</v>
       </c>
       <c r="S96">
         <f t="shared" si="5"/>
-        <v>2049.4439875099679</v>
+        <v>1257.117296864338</v>
       </c>
       <c r="T96">
         <f t="shared" si="4"/>
@@ -6529,62 +6494,62 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B97" t="s">
         <v>20</v>
       </c>
       <c r="C97">
-        <v>2.1846700000000001</v>
+        <v>3.9501900000000001</v>
       </c>
       <c r="D97">
-        <v>3.4160000000000003E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E97">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="F97">
-        <v>1.44</v>
+        <v>0.5</v>
       </c>
       <c r="G97">
-        <v>1570</v>
+        <v>1604</v>
       </c>
       <c r="H97" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="I97">
-        <v>5830</v>
+        <v>6170</v>
       </c>
       <c r="J97">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="K97">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="L97">
-        <v>0.14000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="M97">
-        <v>4.3600000000000003</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="N97">
-        <v>337.45782430000003</v>
+        <v>313.78323929999999</v>
       </c>
       <c r="O97">
-        <v>-48.003098799999997</v>
+        <v>-34.135751200000001</v>
       </c>
       <c r="P97">
-        <v>137.54400000000001</v>
+        <v>211.21100000000001</v>
       </c>
       <c r="Q97">
-        <v>10.092000000000001</v>
+        <v>10.051</v>
       </c>
       <c r="R97">
-        <v>9.9369700000000005</v>
+        <v>10.028499999999999</v>
       </c>
       <c r="S97">
         <f t="shared" si="5"/>
-        <v>422.11900227636102</v>
+        <v>2049.4439875099679</v>
       </c>
       <c r="T97">
         <f t="shared" si="4"/>
@@ -6593,62 +6558,62 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
         <v>20</v>
       </c>
       <c r="C98">
-        <v>5.75251</v>
+        <v>2.1846700000000001</v>
       </c>
       <c r="D98">
-        <v>7.17E-2</v>
+        <v>3.4160000000000003E-2</v>
       </c>
       <c r="E98">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="F98">
-        <v>2.4300000000000002</v>
+        <v>1.44</v>
       </c>
       <c r="G98">
-        <v>1480</v>
+        <v>1570</v>
       </c>
       <c r="H98" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="I98">
-        <v>6150</v>
+        <v>5830</v>
       </c>
       <c r="J98">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="K98">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="L98">
-        <v>0.21</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M98">
-        <v>4.3</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N98">
-        <v>39.897668899999999</v>
+        <v>337.45782430000003</v>
       </c>
       <c r="O98">
-        <v>-50.008193400000003</v>
+        <v>-48.003098799999997</v>
       </c>
       <c r="P98">
-        <v>158.66</v>
+        <v>137.54400000000001</v>
       </c>
       <c r="Q98">
-        <v>9.4749999999999996</v>
+        <v>10.092000000000001</v>
       </c>
       <c r="R98">
-        <v>9.3251000000000008</v>
+        <v>9.9369700000000005</v>
       </c>
       <c r="S98">
         <f t="shared" si="5"/>
-        <v>162.15983922320817</v>
+        <v>422.11900227636102</v>
       </c>
       <c r="T98">
         <f t="shared" si="4"/>
@@ -6657,90 +6622,154 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="B99" t="s">
         <v>20</v>
       </c>
       <c r="C99">
-        <v>3.1915399999999998</v>
+        <v>5.75251</v>
       </c>
       <c r="D99">
-        <v>4.7600000000000003E-2</v>
+        <v>7.17E-2</v>
       </c>
       <c r="E99">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="F99">
-        <v>7.29</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="G99">
-        <v>1729</v>
+        <v>1480</v>
       </c>
       <c r="H99" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="I99">
-        <v>6429</v>
+        <v>6150</v>
       </c>
       <c r="J99">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="K99">
-        <v>0.57999999999999996</v>
+        <v>1.21</v>
       </c>
       <c r="L99">
-        <v>-0.18</v>
+        <v>0.21</v>
       </c>
       <c r="M99">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N99">
-        <v>65.469581399999996</v>
+        <v>39.897668899999999</v>
       </c>
       <c r="O99">
-        <v>57.817209499999997</v>
+        <v>-50.008193400000003</v>
       </c>
       <c r="P99">
-        <v>213.053</v>
+        <v>158.66</v>
       </c>
       <c r="Q99">
-        <v>9.8539999999999992</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="R99">
-        <v>9.7388899999999996</v>
+        <v>9.3251000000000008</v>
       </c>
       <c r="S99">
         <f t="shared" si="5"/>
-        <v>120.66830436099001</v>
+        <v>162.15983922320817</v>
       </c>
       <c r="T99">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100">
+        <v>3.1915399999999998</v>
+      </c>
+      <c r="D100">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="E100">
+        <v>1.41</v>
+      </c>
+      <c r="F100">
+        <v>7.29</v>
+      </c>
+      <c r="G100">
+        <v>1729</v>
+      </c>
+      <c r="H100" t="s">
+        <v>108</v>
+      </c>
+      <c r="I100">
+        <v>6429</v>
+      </c>
+      <c r="J100">
+        <v>1.54</v>
+      </c>
+      <c r="K100">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L100">
+        <v>-0.18</v>
+      </c>
+      <c r="M100">
+        <v>3.95</v>
+      </c>
+      <c r="N100">
+        <v>65.469581399999996</v>
+      </c>
+      <c r="O100">
+        <v>57.817209499999997</v>
+      </c>
+      <c r="P100">
+        <v>213.053</v>
+      </c>
+      <c r="Q100">
+        <v>9.8539999999999992</v>
+      </c>
+      <c r="R100">
+        <v>9.7388899999999996</v>
+      </c>
+      <c r="S100">
+        <f t="shared" si="5"/>
+        <v>120.66830436099001</v>
+      </c>
+      <c r="T100">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="I100">
+      <c r="I101">
         <v>7065.3916019999997</v>
       </c>
-      <c r="N100">
+      <c r="N101">
         <v>146.7834014</v>
       </c>
-      <c r="O100">
+      <c r="O101">
         <v>-54.204010279999999</v>
       </c>
-      <c r="P100">
+      <c r="P101">
         <v>300.9884644</v>
       </c>
-      <c r="R100">
+      <c r="R101">
         <v>9.2583198549999999</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:W100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">
     <sortCondition ref="Q2"/>
   </sortState>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0F22DF-0304-404A-9524-A0448C59AB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9B7E04-4FBA-F649-BE77-51F16EC5FCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
   <si>
     <t>#pl_name</t>
   </si>
@@ -531,6 +531,33 @@
   </si>
   <si>
     <t>4037578191010248064 b</t>
+  </si>
+  <si>
+    <t>VMAG11 b</t>
+  </si>
+  <si>
+    <t>VMAG12 b</t>
+  </si>
+  <si>
+    <t>VMAG13 b</t>
+  </si>
+  <si>
+    <t>VMAG14 b</t>
+  </si>
+  <si>
+    <t>VMAG15 b</t>
+  </si>
+  <si>
+    <t>VMAG16 b</t>
+  </si>
+  <si>
+    <t>VMAG17 b</t>
+  </si>
+  <si>
+    <t>VMAG18 b</t>
+  </si>
+  <si>
+    <t>VMAG19 b</t>
   </si>
 </sst>
 </file>
@@ -936,15 +963,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB101"/>
+  <dimension ref="A1:BB110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="11.1640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="6" width="11.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.5" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -6768,6 +6795,258 @@
         <v>9.2583198549999999</v>
       </c>
     </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="I102" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J102">
+        <v>0.4</v>
+      </c>
+      <c r="K102">
+        <v>0.4</v>
+      </c>
+      <c r="N102">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O102">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P102">
+        <v>11</v>
+      </c>
+      <c r="Q102">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="I103" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J103">
+        <v>0.4</v>
+      </c>
+      <c r="K103">
+        <v>0.4</v>
+      </c>
+      <c r="N103">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O103">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P103">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="Q103">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="I104" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J104">
+        <v>0.4</v>
+      </c>
+      <c r="K104">
+        <v>0.4</v>
+      </c>
+      <c r="N104">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O104">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P104">
+        <v>27.5</v>
+      </c>
+      <c r="Q104">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I105" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J105">
+        <v>0.4</v>
+      </c>
+      <c r="K105">
+        <v>0.4</v>
+      </c>
+      <c r="N105">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O105">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P105">
+        <v>43.7</v>
+      </c>
+      <c r="Q105">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I106" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J106">
+        <v>0.4</v>
+      </c>
+      <c r="K106">
+        <v>0.4</v>
+      </c>
+      <c r="N106">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O106">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P106">
+        <v>69.2</v>
+      </c>
+      <c r="Q106">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I107" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J107">
+        <v>0.4</v>
+      </c>
+      <c r="K107">
+        <v>0.4</v>
+      </c>
+      <c r="N107">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O107">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P107">
+        <v>109.6</v>
+      </c>
+      <c r="Q107">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I108" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J108">
+        <v>0.4</v>
+      </c>
+      <c r="K108">
+        <v>0.4</v>
+      </c>
+      <c r="N108">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O108">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P108">
+        <v>173.8</v>
+      </c>
+      <c r="Q108">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I109" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J109">
+        <v>0.4</v>
+      </c>
+      <c r="K109">
+        <v>0.4</v>
+      </c>
+      <c r="N109">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O109">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P109">
+        <v>275.39999999999998</v>
+      </c>
+      <c r="Q109">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I110" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J110">
+        <v>0.4</v>
+      </c>
+      <c r="K110">
+        <v>0.4</v>
+      </c>
+      <c r="N110">
+        <v>346.62201299999998</v>
+      </c>
+      <c r="O110">
+        <v>-5.0412739999999996</v>
+      </c>
+      <c r="P110">
+        <v>436.5</v>
+      </c>
+      <c r="Q110">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9B7E04-4FBA-F649-BE77-51F16EC5FCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6B6557-630B-6746-BD1C-21D76F1AD0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5214,36 +5214,6 @@
       <c r="G75">
         <v>1439</v>
       </c>
-      <c r="I75">
-        <v>6110</v>
-      </c>
-      <c r="J75">
-        <v>1.6479999999999999</v>
-      </c>
-      <c r="K75">
-        <v>1.2909999999999999</v>
-      </c>
-      <c r="L75">
-        <v>0.124</v>
-      </c>
-      <c r="M75">
-        <v>4.1180000000000003</v>
-      </c>
-      <c r="N75">
-        <v>51.657269100000001</v>
-      </c>
-      <c r="O75">
-        <v>40.817270399999998</v>
-      </c>
-      <c r="P75">
-        <v>179.14699999999999</v>
-      </c>
-      <c r="Q75">
-        <v>9.9130000000000003</v>
-      </c>
-      <c r="R75">
-        <v>9.7295700000000007</v>
-      </c>
       <c r="S75">
         <f t="shared" si="2"/>
         <v>487.59044264912109</v>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6B6557-630B-6746-BD1C-21D76F1AD0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC1F409-F173-C545-82B1-341278B72042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$110</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="173">
   <si>
     <t>#pl_name</t>
   </si>
@@ -459,9 +459,6 @@
   </si>
   <si>
     <t>HAT-P-7 b</t>
-  </si>
-  <si>
-    <t>B9.5-A0</t>
   </si>
   <si>
     <t>B_MAG</t>
@@ -564,10 +561,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,6 +592,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -658,12 +663,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -688,8 +694,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -963,6 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BB110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -982,9 +996,9 @@
     <col min="16" max="16" width="9.1640625" customWidth="1"/>
     <col min="17" max="17" width="12.1640625" customWidth="1"/>
     <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.1640625" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="7" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" customWidth="1"/>
+    <col min="20" max="20" width="7" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9"/>
@@ -1066,15 +1080,15 @@
         <v>136</v>
       </c>
       <c r="V1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I2">
         <v>3501</v>
@@ -1107,15 +1121,15 @@
         <v>12.885999999999999</v>
       </c>
       <c r="W2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AY2" s="3"/>
       <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I3">
         <v>3496</v>
@@ -1148,15 +1162,15 @@
         <v>12.571999999999999</v>
       </c>
       <c r="W3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AY3" s="3"/>
       <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I4">
         <v>3460</v>
@@ -1189,15 +1203,15 @@
         <v>11.454000000000001</v>
       </c>
       <c r="W4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AY4" s="3"/>
       <c r="BA4" s="3"/>
       <c r="BB4" s="3"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I5">
         <v>5804</v>
@@ -1230,15 +1244,15 @@
         <v>16.86</v>
       </c>
       <c r="W5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AY5" s="3"/>
       <c r="BA5" s="3"/>
       <c r="BB5" s="3"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I6">
         <v>5800</v>
@@ -1271,15 +1285,15 @@
         <v>17.364000000000001</v>
       </c>
       <c r="W6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AY6" s="3"/>
       <c r="BA6" s="3"/>
       <c r="BB6" s="3"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I7">
         <v>5799</v>
@@ -1312,12 +1326,12 @@
         <v>12.47</v>
       </c>
       <c r="W7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I8">
         <v>5800.4</v>
@@ -1350,12 +1364,12 @@
         <v>13.638999999999999</v>
       </c>
       <c r="W8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I9">
         <v>5813</v>
@@ -1388,12 +1402,12 @@
         <v>15.66</v>
       </c>
       <c r="W9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I10">
         <v>5820</v>
@@ -1426,12 +1440,12 @@
         <v>15.702999999999999</v>
       </c>
       <c r="W10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I11">
         <v>5824</v>
@@ -1464,12 +1478,12 @@
         <v>15.048999999999999</v>
       </c>
       <c r="W11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I12">
         <v>5816</v>
@@ -1502,12 +1516,12 @@
         <v>17.585999999999999</v>
       </c>
       <c r="W12" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I13">
         <v>5792</v>
@@ -1540,9 +1554,9 @@
         <v>18.082999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I14">
         <v>5775</v>
@@ -1575,12 +1589,12 @@
         <v>14.082000000000001</v>
       </c>
       <c r="W14" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I15">
         <v>5800</v>
@@ -1613,12 +1627,12 @@
         <v>14.913</v>
       </c>
       <c r="W15" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I16">
         <v>5806</v>
@@ -1651,12 +1665,12 @@
         <v>12.507</v>
       </c>
       <c r="W16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I17">
         <v>5815.4</v>
@@ -1689,12 +1703,12 @@
         <v>11.56</v>
       </c>
       <c r="W17" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I18">
         <v>5812</v>
@@ -1727,10 +1741,10 @@
         <v>11.662000000000001</v>
       </c>
       <c r="W18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -1794,7 +1808,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -1858,7 +1872,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1922,7 +1936,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -1986,7 +2000,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>139</v>
       </c>
@@ -2015,7 +2029,7 @@
         <v>11.12930202484131</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>88</v>
       </c>
@@ -2076,7 +2090,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -2137,7 +2151,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>140</v>
       </c>
@@ -2160,7 +2174,7 @@
         <v>10.36768245697021</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -2221,7 +2235,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2285,7 +2299,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2349,7 +2363,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -2413,7 +2427,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2477,7 +2491,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -2541,7 +2555,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -2602,7 +2616,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -2666,7 +2680,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -2730,7 +2744,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2816,49 +2830,11 @@
       <c r="G37">
         <v>2061</v>
       </c>
-      <c r="I37">
-        <v>6801</v>
-      </c>
-      <c r="J37">
-        <v>1.56</v>
-      </c>
-      <c r="K37">
-        <v>1.43</v>
-      </c>
-      <c r="L37">
-        <v>0.02</v>
-      </c>
-      <c r="M37">
-        <v>4.21</v>
-      </c>
-      <c r="N37">
-        <v>7.3289156000000002</v>
-      </c>
-      <c r="O37">
-        <v>-76.304032000000007</v>
-      </c>
-      <c r="P37">
-        <v>196.852</v>
-      </c>
-      <c r="Q37">
-        <v>9.5950000000000006</v>
-      </c>
-      <c r="R37">
-        <v>9.5202500000000008</v>
-      </c>
-      <c r="S37">
-        <f t="shared" si="0"/>
-        <v>934.76971602454307</v>
-      </c>
-      <c r="T37">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
       <c r="U37" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>53</v>
       </c>
@@ -2922,7 +2898,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -2986,7 +2962,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -3050,7 +3026,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -3111,7 +3087,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -3175,7 +3151,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>67</v>
       </c>
@@ -3239,7 +3215,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>109</v>
       </c>
@@ -3303,7 +3279,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -3367,7 +3343,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -3431,7 +3407,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -3495,7 +3471,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -3556,7 +3532,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>123</v>
       </c>
@@ -3620,7 +3596,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -3706,48 +3682,11 @@
       <c r="G51">
         <v>4050</v>
       </c>
-      <c r="H51" t="s">
-        <v>141</v>
-      </c>
-      <c r="I51">
-        <v>10170.1</v>
-      </c>
-      <c r="J51">
-        <v>2.3620000000000001</v>
-      </c>
-      <c r="K51">
-        <v>2.52</v>
-      </c>
-      <c r="L51">
-        <v>-0.03</v>
-      </c>
-      <c r="M51">
-        <v>4.093</v>
-      </c>
-      <c r="N51">
-        <v>307.85989979999999</v>
-      </c>
-      <c r="O51">
-        <v>39.9389161</v>
-      </c>
-      <c r="P51">
-        <v>204.45500000000001</v>
-      </c>
-      <c r="Q51">
-        <v>7.55</v>
-      </c>
-      <c r="R51">
-        <v>7.5767499999999997</v>
-      </c>
-      <c r="S51">
-        <f t="shared" si="0"/>
-        <v>1286.8653667451285</v>
-      </c>
       <c r="U51" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -3808,7 +3747,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -3872,7 +3811,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -3936,7 +3875,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>46</v>
       </c>
@@ -4067,7 +4006,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -4131,7 +4070,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -4192,7 +4131,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>77</v>
       </c>
@@ -4253,7 +4192,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4317,7 +4256,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>34</v>
       </c>
@@ -4381,7 +4320,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -4445,7 +4384,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>87</v>
       </c>
@@ -4509,7 +4448,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>102</v>
       </c>
@@ -4570,7 +4509,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>111</v>
       </c>
@@ -4631,7 +4570,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -4692,7 +4631,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>85</v>
       </c>
@@ -4753,7 +4692,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>22</v>
       </c>
@@ -4814,7 +4753,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>115</v>
       </c>
@@ -4878,7 +4817,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>121</v>
       </c>
@@ -4939,7 +4878,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>68</v>
       </c>
@@ -5003,7 +4942,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>119</v>
       </c>
@@ -5067,7 +5006,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>92</v>
       </c>
@@ -5128,7 +5067,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>129</v>
       </c>
@@ -5192,7 +5131,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>114</v>
       </c>
@@ -5214,16 +5153,17 @@
       <c r="G75">
         <v>1439</v>
       </c>
-      <c r="S75">
-        <f t="shared" si="2"/>
-        <v>487.59044264912109</v>
-      </c>
-      <c r="T75">
-        <f t="shared" si="3"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N75" s="8">
+        <v>51.657269100000001</v>
+      </c>
+      <c r="O75" s="9">
+        <v>40.817270399999998</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>62</v>
       </c>
@@ -5287,7 +5227,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -5351,7 +5291,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>65</v>
       </c>
@@ -5415,7 +5355,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>138</v>
       </c>
@@ -5445,7 +5385,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>131</v>
       </c>
@@ -5509,7 +5449,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>122</v>
       </c>
@@ -5573,7 +5513,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -5634,7 +5574,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -5698,7 +5638,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>117</v>
       </c>
@@ -5762,7 +5702,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>71</v>
       </c>
@@ -5890,7 +5830,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -5954,7 +5894,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>76</v>
       </c>
@@ -6085,7 +6025,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -6146,7 +6086,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -6210,7 +6150,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -6274,9 +6214,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I93" s="1">
         <v>3472</v>
@@ -6297,7 +6237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>126</v>
       </c>
@@ -6361,7 +6301,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -6425,7 +6365,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>132</v>
       </c>
@@ -6489,7 +6429,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>128</v>
       </c>
@@ -6553,7 +6493,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>133</v>
       </c>
@@ -6617,7 +6557,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>79</v>
       </c>
@@ -6681,7 +6621,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -6745,9 +6685,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="16" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I101">
         <v>7065.3916019999997</v>
@@ -6765,9 +6705,9 @@
         <v>9.2583198549999999</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -6797,9 +6737,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -6829,9 +6769,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -6861,9 +6801,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I105" s="1">
         <v>3500</v>
@@ -6887,9 +6827,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I106" s="1">
         <v>3500</v>
@@ -6913,9 +6853,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I107" s="1">
         <v>3500</v>
@@ -6939,9 +6879,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I108" s="1">
         <v>3500</v>
@@ -6965,9 +6905,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I109" s="1">
         <v>3500</v>
@@ -6991,9 +6931,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I110" s="1">
         <v>3500</v>
@@ -7018,7 +6958,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:W110" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="20">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">
     <sortCondition ref="Q2"/>
   </sortState>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC1F409-F173-C545-82B1-341278B72042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493AB0B3-DF4C-8643-BE7F-6065918041ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
   <si>
     <t>#pl_name</t>
   </si>
@@ -365,9 +365,6 @@
     <t>F5V</t>
   </si>
   <si>
-    <t>KELT-19 A b</t>
-  </si>
-  <si>
     <t>A8 V</t>
   </si>
   <si>
@@ -380,9 +377,6 @@
     <t>K</t>
   </si>
   <si>
-    <t>TOI-6038 A b</t>
-  </si>
-  <si>
     <t>TOI-421 c</t>
   </si>
   <si>
@@ -461,6 +455,9 @@
     <t>HAT-P-7 b</t>
   </si>
   <si>
+    <t>B9.5-A0</t>
+  </si>
+  <si>
     <t>B_MAG</t>
   </si>
   <si>
@@ -555,17 +552,22 @@
   </si>
   <si>
     <t>VMAG19 b</t>
+  </si>
+  <si>
+    <t>TOI-6038 b</t>
+  </si>
+  <si>
+    <t>KELT-19 b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,13 +594,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -663,13 +658,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -694,15 +688,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -976,7 +963,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:BB110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -996,9 +982,9 @@
     <col min="16" max="16" width="9.1640625" customWidth="1"/>
     <col min="17" max="17" width="12.1640625" customWidth="1"/>
     <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.1640625" customWidth="1"/>
-    <col min="20" max="20" width="7" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="7" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9"/>
@@ -1074,21 +1060,21 @@
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="V1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I2">
         <v>3501</v>
@@ -1121,15 +1107,15 @@
         <v>12.885999999999999</v>
       </c>
       <c r="W2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AY2" s="3"/>
       <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
     </row>
-    <row r="3" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I3">
         <v>3496</v>
@@ -1162,15 +1148,15 @@
         <v>12.571999999999999</v>
       </c>
       <c r="W3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AY3" s="3"/>
       <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
     </row>
-    <row r="4" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I4">
         <v>3460</v>
@@ -1203,15 +1189,15 @@
         <v>11.454000000000001</v>
       </c>
       <c r="W4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AY4" s="3"/>
       <c r="BA4" s="3"/>
       <c r="BB4" s="3"/>
     </row>
-    <row r="5" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I5">
         <v>5804</v>
@@ -1244,15 +1230,15 @@
         <v>16.86</v>
       </c>
       <c r="W5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AY5" s="3"/>
       <c r="BA5" s="3"/>
       <c r="BB5" s="3"/>
     </row>
-    <row r="6" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I6">
         <v>5800</v>
@@ -1285,15 +1271,15 @@
         <v>17.364000000000001</v>
       </c>
       <c r="W6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AY6" s="3"/>
       <c r="BA6" s="3"/>
       <c r="BB6" s="3"/>
     </row>
-    <row r="7" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I7">
         <v>5799</v>
@@ -1326,12 +1312,12 @@
         <v>12.47</v>
       </c>
       <c r="W7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I8">
         <v>5800.4</v>
@@ -1364,12 +1350,12 @@
         <v>13.638999999999999</v>
       </c>
       <c r="W8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I9">
         <v>5813</v>
@@ -1402,12 +1388,12 @@
         <v>15.66</v>
       </c>
       <c r="W9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I10">
         <v>5820</v>
@@ -1440,12 +1426,12 @@
         <v>15.702999999999999</v>
       </c>
       <c r="W10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I11">
         <v>5824</v>
@@ -1478,12 +1464,12 @@
         <v>15.048999999999999</v>
       </c>
       <c r="W11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I12">
         <v>5816</v>
@@ -1516,12 +1502,12 @@
         <v>17.585999999999999</v>
       </c>
       <c r="W12" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I13">
         <v>5792</v>
@@ -1554,9 +1540,9 @@
         <v>18.082999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I14">
         <v>5775</v>
@@ -1589,12 +1575,12 @@
         <v>14.082000000000001</v>
       </c>
       <c r="W14" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I15">
         <v>5800</v>
@@ -1627,12 +1613,12 @@
         <v>14.913</v>
       </c>
       <c r="W15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I16">
         <v>5806</v>
@@ -1665,12 +1651,12 @@
         <v>12.507</v>
       </c>
       <c r="W16" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I17">
         <v>5815.4</v>
@@ -1703,12 +1689,12 @@
         <v>11.56</v>
       </c>
       <c r="W17" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I18">
         <v>5812</v>
@@ -1741,10 +1727,10 @@
         <v>11.662000000000001</v>
       </c>
       <c r="W18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -1808,9 +1794,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
@@ -1831,7 +1817,7 @@
         <v>1624</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I20">
         <v>6600</v>
@@ -1872,7 +1858,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1936,7 +1922,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -2000,9 +1986,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I23">
         <v>6245.11328125</v>
@@ -2029,7 +2015,7 @@
         <v>11.12930202484131</v>
       </c>
     </row>
-    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>88</v>
       </c>
@@ -2090,7 +2076,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -2151,9 +2137,9 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I26">
         <v>6424.27685546875</v>
@@ -2174,7 +2160,7 @@
         <v>10.36768245697021</v>
       </c>
     </row>
-    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -2235,7 +2221,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2299,7 +2285,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2363,7 +2349,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -2427,7 +2413,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2491,7 +2477,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -2555,7 +2541,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -2616,7 +2602,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -2680,7 +2666,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -2744,7 +2730,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2830,11 +2816,49 @@
       <c r="G37">
         <v>2061</v>
       </c>
+      <c r="I37">
+        <v>6801</v>
+      </c>
+      <c r="J37">
+        <v>1.56</v>
+      </c>
+      <c r="K37">
+        <v>1.43</v>
+      </c>
+      <c r="L37">
+        <v>0.02</v>
+      </c>
+      <c r="M37">
+        <v>4.21</v>
+      </c>
+      <c r="N37">
+        <v>7.3289156000000002</v>
+      </c>
+      <c r="O37">
+        <v>-76.304032000000007</v>
+      </c>
+      <c r="P37">
+        <v>196.852</v>
+      </c>
+      <c r="Q37">
+        <v>9.5950000000000006</v>
+      </c>
+      <c r="R37">
+        <v>9.5202500000000008</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="0"/>
+        <v>934.76971602454307</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
       <c r="U37" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>53</v>
       </c>
@@ -2898,7 +2922,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -2962,7 +2986,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -3026,7 +3050,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -3087,7 +3111,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -3151,7 +3175,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>67</v>
       </c>
@@ -3215,9 +3239,9 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>109</v>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
@@ -3238,7 +3262,7 @@
         <v>1935</v>
       </c>
       <c r="H44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I44">
         <v>7500</v>
@@ -3279,7 +3303,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -3343,7 +3367,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -3407,7 +3431,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -3471,7 +3495,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -3532,9 +3556,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
@@ -3596,7 +3620,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -3682,11 +3706,48 @@
       <c r="G51">
         <v>4050</v>
       </c>
+      <c r="H51" t="s">
+        <v>139</v>
+      </c>
+      <c r="I51">
+        <v>10170.1</v>
+      </c>
+      <c r="J51">
+        <v>2.3620000000000001</v>
+      </c>
+      <c r="K51">
+        <v>2.52</v>
+      </c>
+      <c r="L51">
+        <v>-0.03</v>
+      </c>
+      <c r="M51">
+        <v>4.093</v>
+      </c>
+      <c r="N51">
+        <v>307.85989979999999</v>
+      </c>
+      <c r="O51">
+        <v>39.9389161</v>
+      </c>
+      <c r="P51">
+        <v>204.45500000000001</v>
+      </c>
+      <c r="Q51">
+        <v>7.55</v>
+      </c>
+      <c r="R51">
+        <v>7.5767499999999997</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="0"/>
+        <v>1286.8653667451285</v>
+      </c>
       <c r="U51" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -3747,7 +3808,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -3811,7 +3872,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -3875,7 +3936,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>46</v>
       </c>
@@ -4003,10 +4064,10 @@
         <v>-5</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -4070,7 +4131,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -4131,7 +4192,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>77</v>
       </c>
@@ -4192,7 +4253,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4256,7 +4317,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>34</v>
       </c>
@@ -4320,7 +4381,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -4384,7 +4445,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>87</v>
       </c>
@@ -4448,7 +4509,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>102</v>
       </c>
@@ -4509,9 +4570,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
@@ -4570,7 +4631,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -4631,7 +4692,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>85</v>
       </c>
@@ -4692,7 +4753,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>22</v>
       </c>
@@ -4753,9 +4814,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
@@ -4776,7 +4837,7 @@
         <v>635</v>
       </c>
       <c r="H69" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I69">
         <v>5291</v>
@@ -4817,9 +4878,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
@@ -4878,7 +4939,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>68</v>
       </c>
@@ -4942,9 +5003,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B72" t="s">
         <v>20</v>
@@ -4965,7 +5026,7 @@
         <v>1370</v>
       </c>
       <c r="H72" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I72">
         <v>5735</v>
@@ -5006,7 +5067,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>92</v>
       </c>
@@ -5067,9 +5128,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B74" t="s">
         <v>20</v>
@@ -5090,7 +5151,7 @@
         <v>947</v>
       </c>
       <c r="H74" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I74">
         <v>6000</v>
@@ -5131,9 +5192,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>114</v>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="B75" t="s">
         <v>20</v>
@@ -5153,17 +5214,46 @@
       <c r="G75">
         <v>1439</v>
       </c>
-      <c r="N75" s="8">
+      <c r="I75">
+        <v>6110</v>
+      </c>
+      <c r="J75">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="K75">
+        <v>1.2909999999999999</v>
+      </c>
+      <c r="L75">
+        <v>0.124</v>
+      </c>
+      <c r="M75">
+        <v>4.1180000000000003</v>
+      </c>
+      <c r="N75">
         <v>51.657269100000001</v>
       </c>
-      <c r="O75" s="9">
+      <c r="O75">
         <v>40.817270399999998</v>
       </c>
-      <c r="U75" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="P75">
+        <v>179.14699999999999</v>
+      </c>
+      <c r="Q75">
+        <v>9.9130000000000003</v>
+      </c>
+      <c r="R75">
+        <v>9.7295700000000007</v>
+      </c>
+      <c r="S75">
+        <f t="shared" si="2"/>
+        <v>487.59044264912109</v>
+      </c>
+      <c r="T75">
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>62</v>
       </c>
@@ -5227,7 +5317,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -5291,7 +5381,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>65</v>
       </c>
@@ -5355,9 +5445,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B79" t="s">
         <v>20</v>
@@ -5385,9 +5475,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B80" t="s">
         <v>20</v>
@@ -5449,9 +5539,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B81" t="s">
         <v>20</v>
@@ -5513,7 +5603,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -5574,7 +5664,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -5638,9 +5728,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B84" t="s">
         <v>20</v>
@@ -5661,7 +5751,7 @@
         <v>2470</v>
       </c>
       <c r="H84" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I84">
         <v>9360</v>
@@ -5702,7 +5792,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>71</v>
       </c>
@@ -5827,10 +5917,10 @@
         <v>-7</v>
       </c>
       <c r="U86" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -5894,7 +5984,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>76</v>
       </c>
@@ -5960,7 +6050,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B89" t="s">
         <v>20</v>
@@ -5981,7 +6071,7 @@
         <v>971</v>
       </c>
       <c r="H89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I89">
         <v>4792</v>
@@ -6022,10 +6112,10 @@
         <v>-5</v>
       </c>
       <c r="U89" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -6086,7 +6176,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -6150,7 +6240,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -6214,9 +6304,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I93" s="1">
         <v>3472</v>
@@ -6237,9 +6327,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
@@ -6260,7 +6350,7 @@
         <v>1716.2</v>
       </c>
       <c r="H94" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I94">
         <v>6600</v>
@@ -6301,7 +6391,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -6365,9 +6455,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B96" t="s">
         <v>20</v>
@@ -6388,7 +6478,7 @@
         <v>2190</v>
       </c>
       <c r="H96" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I96">
         <v>6480</v>
@@ -6429,9 +6519,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B97" t="s">
         <v>20</v>
@@ -6493,9 +6583,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B98" t="s">
         <v>20</v>
@@ -6516,7 +6606,7 @@
         <v>1570</v>
       </c>
       <c r="H98" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I98">
         <v>5830</v>
@@ -6557,7 +6647,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>79</v>
       </c>
@@ -6621,7 +6711,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -6685,9 +6775,9 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="16" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I101">
         <v>7065.3916019999997</v>
@@ -6705,9 +6795,9 @@
         <v>9.2583198549999999</v>
       </c>
     </row>
-    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -6737,9 +6827,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -6769,9 +6859,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -6801,9 +6891,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I105" s="1">
         <v>3500</v>
@@ -6827,9 +6917,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I106" s="1">
         <v>3500</v>
@@ -6853,9 +6943,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I107" s="1">
         <v>3500</v>
@@ -6879,9 +6969,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I108" s="1">
         <v>3500</v>
@@ -6905,9 +6995,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I109" s="1">
         <v>3500</v>
@@ -6931,9 +7021,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I110" s="1">
         <v>3500</v>
@@ -6958,13 +7048,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W110" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="20">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:W100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">
     <sortCondition ref="Q2"/>
   </sortState>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493AB0B3-DF4C-8643-BE7F-6065918041ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7148B1E-0D82-8844-854F-EB244557F6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2502,36 +2502,6 @@
       <c r="H32" t="s">
         <v>29</v>
       </c>
-      <c r="I32">
-        <v>5052</v>
-      </c>
-      <c r="J32">
-        <v>0.75</v>
-      </c>
-      <c r="K32">
-        <v>0.79</v>
-      </c>
-      <c r="L32">
-        <v>-0.02</v>
-      </c>
-      <c r="M32">
-        <v>4.49</v>
-      </c>
-      <c r="N32">
-        <v>300.1821223</v>
-      </c>
-      <c r="O32">
-        <v>22.7097759</v>
-      </c>
-      <c r="P32">
-        <v>19.7638</v>
-      </c>
-      <c r="Q32">
-        <v>7.67</v>
-      </c>
-      <c r="R32">
-        <v>7.41432</v>
-      </c>
       <c r="S32">
         <f t="shared" si="0"/>
         <v>349.61677638948368</v>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7148B1E-0D82-8844-854F-EB244557F6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DF0F46-51BE-B44C-A6A1-AD3CA6FA5FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22840" yWindow="4740" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="176">
   <si>
     <t>#pl_name</t>
   </si>
@@ -558,6 +558,12 @@
   </si>
   <si>
     <t>KELT-19 b</t>
+  </si>
+  <si>
+    <t>1242084170974175232 c</t>
+  </si>
+  <si>
+    <t>this is also WASP-14, but i dont want the name resolution</t>
   </si>
 </sst>
 </file>
@@ -963,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB110"/>
+  <dimension ref="A1:BB111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -2502,12 +2508,42 @@
       <c r="H32" t="s">
         <v>29</v>
       </c>
+      <c r="I32">
+        <v>5052</v>
+      </c>
+      <c r="J32">
+        <v>0.75</v>
+      </c>
+      <c r="K32">
+        <v>0.79</v>
+      </c>
+      <c r="L32">
+        <v>-0.02</v>
+      </c>
+      <c r="M32">
+        <v>4.49</v>
+      </c>
+      <c r="N32">
+        <v>300.1821223</v>
+      </c>
+      <c r="O32">
+        <v>22.7097759</v>
+      </c>
+      <c r="P32">
+        <v>19.7638</v>
+      </c>
+      <c r="Q32">
+        <v>7.67</v>
+      </c>
+      <c r="R32">
+        <v>7.41432</v>
+      </c>
       <c r="S32">
-        <f t="shared" si="0"/>
+        <f>(0.000000000000000138*G32/(1.673534E-24*1.3*0.000000066726*F32*1.8986E+30/(E32*7149200000)^2))/100000</f>
         <v>349.61677638948368</v>
       </c>
       <c r="T32">
-        <f t="shared" si="1"/>
+        <f>IF(I32&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -5626,11 +5662,11 @@
         <v>9.6464700000000008</v>
       </c>
       <c r="S82">
-        <f t="shared" si="5"/>
+        <f>(0.000000000000000138*G82/(1.673534E-24*1.3*0.000000066726*F82*1.8986E+30/(E82*7149200000)^2))/100000</f>
         <v>103.20465157174387</v>
       </c>
       <c r="T82">
-        <f t="shared" si="4"/>
+        <f>IF(I82&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
@@ -6489,7 +6525,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>126</v>
       </c>
@@ -6553,7 +6589,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>131</v>
       </c>
@@ -6617,7 +6653,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>79</v>
       </c>
@@ -6681,7 +6717,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -6745,7 +6781,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>161</v>
       </c>
@@ -6765,7 +6801,7 @@
         <v>9.2583198549999999</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>163</v>
       </c>
@@ -6797,7 +6833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>164</v>
       </c>
@@ -6829,7 +6865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>165</v>
       </c>
@@ -6861,7 +6897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>166</v>
       </c>
@@ -6887,7 +6923,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>167</v>
       </c>
@@ -6913,7 +6949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>168</v>
       </c>
@@ -6939,7 +6975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>169</v>
       </c>
@@ -6965,7 +7001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>170</v>
       </c>
@@ -6991,7 +7027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>171</v>
       </c>
@@ -7015,6 +7051,20 @@
       </c>
       <c r="Q110">
         <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="N111">
+        <v>218.27662916581701</v>
+      </c>
+      <c r="O111">
+        <v>21.8946865465029</v>
+      </c>
+      <c r="X111" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/input/Targets_V10p1.xlsx
+++ b/input/Targets_V10p1.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DF0F46-51BE-B44C-A6A1-AD3CA6FA5FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72C89EE-BF20-AD43-9BD0-CA5B67A04639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22840" yWindow="4740" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_V10p1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$W$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Targets_V10p1!$A$1:$X$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -602,7 +602,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -613,6 +613,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -669,7 +675,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -688,10 +694,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -969,6 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BB111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -985,12 +998,12 @@
     <col min="12" max="12" width="8.83203125" customWidth="1"/>
     <col min="13" max="14" width="12.1640625" customWidth="1"/>
     <col min="15" max="15" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" style="8" customWidth="1"/>
     <col min="17" max="17" width="12.1640625" customWidth="1"/>
     <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.1640625" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="7" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" customWidth="1"/>
+    <col min="20" max="20" width="7" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9"/>
@@ -1053,7 +1066,7 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
@@ -1078,483 +1091,381 @@
         <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I2">
-        <v>3501</v>
+        <v>3460</v>
       </c>
       <c r="J2">
-        <v>50.991</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.6963999999999997</v>
       </c>
       <c r="N2">
-        <v>254.47763000024</v>
+        <v>303.19871318011002</v>
       </c>
       <c r="O2">
-        <v>-23.844465202550001</v>
+        <v>-0.37849292589</v>
       </c>
       <c r="P2">
-        <v>1025.1500000000001</v>
+        <v>312.65899999999999</v>
       </c>
       <c r="Q2">
-        <v>11.035</v>
+        <v>10.968999999999999</v>
       </c>
       <c r="V2">
-        <v>12.885999999999999</v>
+        <v>11.454000000000001</v>
       </c>
       <c r="W2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AY2" s="3"/>
       <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I3">
-        <v>3496</v>
+    <row r="3" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="1">
+        <v>3472</v>
       </c>
       <c r="J3">
-        <v>83.710999999999999</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="N3">
-        <v>293.64838257128002</v>
+        <v>272.54430475160001</v>
       </c>
       <c r="O3">
-        <v>-12.35499539692</v>
+        <v>-37.644513386920003</v>
       </c>
       <c r="P3">
-        <v>1655.31</v>
-      </c>
-      <c r="Q3">
-        <v>10.977</v>
-      </c>
-      <c r="V3">
-        <v>12.571999999999999</v>
-      </c>
-      <c r="W3" t="s">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="AY3" s="3"/>
       <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I4">
-        <v>3460</v>
+        <v>3496</v>
       </c>
       <c r="J4">
-        <v>0.54700000000000004</v>
+        <v>83.710999999999999</v>
       </c>
       <c r="K4">
-        <v>0.54300000000000004</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>4.6963999999999997</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>303.19871318011002</v>
+        <v>293.64838257128002</v>
       </c>
       <c r="O4">
-        <v>-0.37849292589</v>
+        <v>-12.35499539692</v>
       </c>
       <c r="P4">
-        <v>312.65899999999999</v>
+        <v>1655.31</v>
       </c>
       <c r="Q4">
-        <v>10.968999999999999</v>
+        <v>10.977</v>
       </c>
       <c r="V4">
-        <v>11.454000000000001</v>
+        <v>12.571999999999999</v>
       </c>
       <c r="W4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AY4" s="3"/>
       <c r="BA4" s="3"/>
       <c r="BB4" s="3"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>146</v>
-      </c>
-      <c r="I5">
-        <v>5804</v>
+    <row r="5" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="I5" s="1">
+        <v>3500</v>
       </c>
       <c r="J5">
-        <v>1.179</v>
+        <v>0.4</v>
       </c>
       <c r="K5">
-        <v>1.04</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>4.3121</v>
+        <v>0.4</v>
       </c>
       <c r="N5">
-        <v>274.86862255196002</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O5">
-        <v>5.3506741626599998</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P5">
-        <v>1644.4</v>
+        <v>11</v>
       </c>
       <c r="Q5">
-        <v>15.965999999999999</v>
-      </c>
-      <c r="V5">
-        <v>16.86</v>
-      </c>
-      <c r="W5" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="AY5" s="3"/>
       <c r="BA5" s="3"/>
       <c r="BB5" s="3"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>157</v>
-      </c>
-      <c r="I6">
-        <v>5800</v>
+    <row r="6" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="I6" s="1">
+        <v>3500</v>
       </c>
       <c r="J6">
-        <v>1.3220000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K6">
-        <v>1.04</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>4.2129000000000003</v>
+        <v>0.4</v>
       </c>
       <c r="N6">
-        <v>270.95467601665001</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O6">
-        <v>3.9944008770699999</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P6">
-        <v>2963.53</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="Q6">
-        <v>17.052</v>
-      </c>
-      <c r="V6">
-        <v>17.364000000000001</v>
-      </c>
-      <c r="W6" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="AY6" s="3"/>
       <c r="BA6" s="3"/>
       <c r="BB6" s="3"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>149</v>
-      </c>
-      <c r="I7">
-        <v>5799</v>
+    <row r="7" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="I7" s="1">
+        <v>3500</v>
       </c>
       <c r="J7">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="K7">
-        <v>1.042</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>4.4642999999999997</v>
+        <v>0.4</v>
       </c>
       <c r="N7">
-        <v>278.21725113665002</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O7">
-        <v>11.92287820316</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P7">
-        <v>224.12799999999999</v>
+        <v>27.5</v>
       </c>
       <c r="Q7">
-        <v>11.997</v>
-      </c>
-      <c r="V7">
-        <v>12.47</v>
-      </c>
-      <c r="W7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I8">
-        <v>5800.4</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="1">
+        <v>3500</v>
       </c>
       <c r="J8">
-        <v>1.4930000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K8">
-        <v>1.04</v>
-      </c>
-      <c r="L8">
-        <v>-6.6000000000000003E-2</v>
-      </c>
-      <c r="M8">
-        <v>4.1069000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="N8">
-        <v>270.30880152526998</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O8">
-        <v>15.944626030029999</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P8">
-        <v>579.08500000000004</v>
+        <v>43.7</v>
       </c>
       <c r="Q8">
-        <v>12.978999999999999</v>
-      </c>
-      <c r="V8">
-        <v>13.638999999999999</v>
-      </c>
-      <c r="W8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>155</v>
-      </c>
-      <c r="I9">
-        <v>5813</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3500</v>
       </c>
       <c r="J9">
-        <v>1.83</v>
+        <v>0.4</v>
       </c>
       <c r="K9">
-        <v>1.05</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>3.9344999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="N9">
-        <v>270.99233637095</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O9">
-        <v>16.858729226019999</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P9">
-        <v>1779.6</v>
+        <v>69.2</v>
       </c>
       <c r="Q9">
-        <v>14.999000000000001</v>
-      </c>
-      <c r="V9">
-        <v>15.66</v>
-      </c>
-      <c r="W9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>156</v>
-      </c>
-      <c r="I10">
-        <v>5820</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3500</v>
       </c>
       <c r="J10">
-        <v>6.2519999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N10">
-        <v>267.97432727351003</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O10">
-        <v>17.507747521020001</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P10">
-        <v>6401.77</v>
+        <v>109.6</v>
       </c>
       <c r="Q10">
-        <v>15.007999999999999</v>
-      </c>
-      <c r="V10">
-        <v>15.702999999999999</v>
-      </c>
-      <c r="W10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>154</v>
-      </c>
-      <c r="I11">
-        <v>5824</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" s="1">
+        <v>3500</v>
       </c>
       <c r="J11">
-        <v>4.7249999999999996</v>
+        <v>0.4</v>
       </c>
       <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N11">
-        <v>284.95537150204001</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O11">
-        <v>14.42740619077</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P11">
-        <v>1961.4</v>
+        <v>173.8</v>
       </c>
       <c r="Q11">
-        <v>14.023</v>
-      </c>
-      <c r="V11">
-        <v>15.048999999999999</v>
-      </c>
-      <c r="W11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>158</v>
-      </c>
-      <c r="I12">
-        <v>5816</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3500</v>
       </c>
       <c r="J12">
-        <v>5.2939999999999996</v>
+        <v>0.4</v>
       </c>
       <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N12">
-        <v>284.79622244569998</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O12">
-        <v>15.987368865140001</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P12">
-        <v>3747.72</v>
+        <v>275.39999999999998</v>
       </c>
       <c r="Q12">
-        <v>15.958</v>
-      </c>
-      <c r="V12">
-        <v>17.585999999999999</v>
-      </c>
-      <c r="W12" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>159</v>
-      </c>
-      <c r="I13">
-        <v>5792</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I13" s="1">
+        <v>3500</v>
+      </c>
+      <c r="J13">
+        <v>0.4</v>
       </c>
       <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N13">
-        <v>276.67545984469001</v>
+        <v>346.62201299999998</v>
       </c>
       <c r="O13">
-        <v>14.0128749692</v>
+        <v>-5.0412739999999996</v>
       </c>
       <c r="P13">
-        <v>2046.66</v>
+        <v>436.5</v>
       </c>
       <c r="Q13">
-        <v>17.097000000000001</v>
-      </c>
-      <c r="R13">
-        <v>16.870684000000001</v>
-      </c>
-      <c r="V13">
-        <v>18.082999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:54" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I14">
-        <v>5775</v>
+        <v>3501</v>
       </c>
       <c r="J14">
-        <v>5.1109999999999998</v>
+        <v>50.991</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1566,19 +1477,19 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>274.00302978329</v>
+        <v>254.47763000024</v>
       </c>
       <c r="O14">
-        <v>22.9885348444</v>
+        <v>-23.844465202550001</v>
       </c>
       <c r="P14">
-        <v>1802.37</v>
+        <v>1025.1500000000001</v>
       </c>
       <c r="Q14">
-        <v>12.961</v>
+        <v>11.035</v>
       </c>
       <c r="V14">
-        <v>14.082000000000001</v>
+        <v>12.885999999999999</v>
       </c>
       <c r="W14" t="s">
         <v>145</v>
@@ -1586,214 +1497,318 @@
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>4.1268799999999999</v>
+      </c>
+      <c r="D15">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="E15">
+        <v>1.44</v>
+      </c>
+      <c r="F15">
+        <v>1.17</v>
+      </c>
+      <c r="G15">
+        <v>2061</v>
       </c>
       <c r="I15">
-        <v>5800</v>
+        <v>6801</v>
       </c>
       <c r="J15">
-        <v>1.417</v>
+        <v>1.56</v>
       </c>
       <c r="K15">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M15">
-        <v>4.1520999999999999</v>
+        <v>4.21</v>
       </c>
       <c r="N15">
-        <v>280.34203579685999</v>
+        <v>7.3289156000000002</v>
       </c>
       <c r="O15">
-        <v>26.315625519600001</v>
-      </c>
-      <c r="P15">
-        <v>897.52700000000004</v>
+        <v>-76.304032000000007</v>
+      </c>
+      <c r="P15" s="8">
+        <v>196.852</v>
       </c>
       <c r="Q15">
-        <v>13.994999999999999</v>
-      </c>
-      <c r="V15">
-        <v>14.913</v>
-      </c>
-      <c r="W15" t="s">
-        <v>143</v>
+        <v>9.5950000000000006</v>
+      </c>
+      <c r="R15">
+        <v>9.5202500000000008</v>
+      </c>
+      <c r="S15">
+        <f>(0.000000000000000138*G15/(1.673534E-24*1.3*0.000000066726*F15*1.8986E+30/(E15*7149200000)^2))/100000</f>
+        <v>934.76971602454307</v>
+      </c>
+      <c r="T15">
+        <f>IF(I15&gt;6800,-7,-5)</f>
+        <v>-7</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>11.53533</v>
+      </c>
+      <c r="D16">
+        <v>0.10970000000000001</v>
+      </c>
+      <c r="E16">
+        <v>1.026</v>
+      </c>
+      <c r="F16">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="G16">
+        <v>1228.3</v>
+      </c>
+      <c r="H16" t="s">
+        <v>31</v>
       </c>
       <c r="I16">
-        <v>5806</v>
+        <v>5521</v>
       </c>
       <c r="J16">
-        <v>27.986999999999998</v>
+        <v>2.3359999999999999</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1.3240000000000001</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>3.823</v>
       </c>
       <c r="N16">
-        <v>278.48921850735002</v>
+        <v>4.4471631</v>
       </c>
       <c r="O16">
-        <v>31.640052119060002</v>
-      </c>
-      <c r="P16">
-        <v>7397.91</v>
+        <v>-66.358928500000005</v>
+      </c>
+      <c r="P16" s="8">
+        <v>79.5702</v>
       </c>
       <c r="Q16">
-        <v>12.01</v>
-      </c>
-      <c r="V16">
-        <v>12.507</v>
-      </c>
-      <c r="W16" t="s">
-        <v>145</v>
+        <v>7.79</v>
+      </c>
+      <c r="R16">
+        <v>7.5933599999999997</v>
+      </c>
+      <c r="S16">
+        <f>(0.000000000000000138*G16/(1.673534E-24*1.3*0.000000066726*F16*1.8986E+30/(E16*7149200000)^2))/100000</f>
+        <v>797.33090232058362</v>
+      </c>
+      <c r="T16">
+        <f>IF(I16&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>2.8240932000000001</v>
+      </c>
+      <c r="D17">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="E17">
+        <v>1.5149999999999999</v>
+      </c>
+      <c r="F17">
+        <v>1.675</v>
+      </c>
+      <c r="G17">
+        <v>2250</v>
+      </c>
+      <c r="H17" t="s">
+        <v>47</v>
       </c>
       <c r="I17">
-        <v>5815.4</v>
+        <v>7800</v>
       </c>
       <c r="J17">
-        <v>4.2549999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="K17">
+        <v>1.75</v>
+      </c>
+      <c r="L17">
         <v>0</v>
       </c>
-      <c r="L17">
-        <v>-0.19350000000000001</v>
-      </c>
       <c r="M17">
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N17">
-        <v>80.600252814719994</v>
+        <v>147.5800667</v>
       </c>
       <c r="O17">
-        <v>-68.64221652773</v>
-      </c>
-      <c r="P17">
-        <v>398.375</v>
+        <v>-66.113925300000005</v>
+      </c>
+      <c r="P17" s="8">
+        <v>170.696</v>
       </c>
       <c r="Q17">
-        <v>11.137</v>
-      </c>
-      <c r="V17">
-        <v>11.56</v>
-      </c>
-      <c r="W17" t="s">
-        <v>145</v>
+        <v>8.1910000000000007</v>
+      </c>
+      <c r="R17">
+        <v>8.1740100000000009</v>
+      </c>
+      <c r="S17">
+        <f>(0.000000000000000138*G17/(1.673534E-24*1.3*0.000000066726*F17*1.8986E+30/(E17*7149200000)^2))/100000</f>
+        <v>789.006338593706</v>
+      </c>
+      <c r="T17">
+        <f>IF(I17&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>147</v>
+        <v>117</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>10.331110000000001</v>
+      </c>
+      <c r="D18">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="E18">
+        <v>0.99</v>
+      </c>
+      <c r="F18">
+        <v>1.53</v>
+      </c>
+      <c r="G18">
+        <v>1370</v>
+      </c>
+      <c r="H18" t="s">
+        <v>118</v>
       </c>
       <c r="I18">
-        <v>5812</v>
+        <v>5735</v>
       </c>
       <c r="J18">
-        <v>0.85599999999999998</v>
+        <v>1.66</v>
       </c>
       <c r="K18">
-        <v>1.0449999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="M18">
-        <v>4.5917000000000003</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="N18">
-        <v>47.805523543809997</v>
+        <v>110.5126861</v>
       </c>
       <c r="O18">
-        <v>-18.380477788619999</v>
-      </c>
-      <c r="P18">
-        <v>147.77799999999999</v>
+        <v>-57.384998000000003</v>
+      </c>
+      <c r="P18" s="8">
+        <v>179.36600000000001</v>
       </c>
       <c r="Q18">
-        <v>11.044</v>
-      </c>
-      <c r="V18">
-        <v>11.662000000000001</v>
-      </c>
-      <c r="W18" t="s">
-        <v>143</v>
+        <v>9.9719999999999995</v>
+      </c>
+      <c r="R18">
+        <v>9.8465900000000008</v>
+      </c>
+      <c r="S18">
+        <f>(0.000000000000000138*G18/(1.673534E-24*1.3*0.000000066726*F18*1.8986E+30/(E18*7149200000)^2))/100000</f>
+        <v>224.58825733889913</v>
+      </c>
+      <c r="T18">
+        <f>IF(I18&gt;6800,-7,-5)</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19">
-        <v>4.4652997599999997</v>
+        <v>6.0344680000000004</v>
       </c>
       <c r="D19">
-        <v>5.561E-2</v>
+        <v>6.3560000000000005E-2</v>
       </c>
       <c r="E19">
-        <v>1.319</v>
+        <v>0.437</v>
       </c>
       <c r="F19">
-        <v>0.52500000000000002</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G19">
-        <v>1322</v>
+        <v>1076</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="I19">
-        <v>5980</v>
+        <v>5540</v>
       </c>
       <c r="J19">
-        <v>1.1739999999999999</v>
+        <v>1.0589999999999999</v>
       </c>
       <c r="K19">
-        <v>1.151</v>
+        <v>1.02</v>
       </c>
       <c r="L19">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="M19">
-        <v>4.359</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N19">
-        <v>344.44536319999997</v>
+        <v>349.55926649999998</v>
       </c>
       <c r="O19">
-        <v>38.674919000000003</v>
-      </c>
-      <c r="P19">
-        <v>158.97900000000001</v>
+        <v>-56.9039857</v>
+      </c>
+      <c r="P19" s="8">
+        <v>94.171899999999994</v>
       </c>
       <c r="Q19">
-        <v>9.827</v>
+        <v>9.8089999999999993</v>
       </c>
       <c r="R19">
-        <v>10.178599999999999</v>
+        <v>9.6495599999999992</v>
       </c>
       <c r="S19">
         <f>(0.000000000000000138*G19/(1.673534E-24*1.3*0.000000066726*F19*1.8986E+30/(E19*7149200000)^2))/100000</f>
-        <v>1121.1126749906216</v>
+        <v>956.09264119622901</v>
       </c>
       <c r="T19">
         <f>IF(I19&gt;6800,-7,-5)</f>
@@ -1801,554 +1816,586 @@
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20">
-        <v>4.6276700000000002</v>
-      </c>
-      <c r="D20">
-        <v>5.96E-2</v>
-      </c>
-      <c r="E20">
-        <v>1.42</v>
-      </c>
-      <c r="F20">
-        <v>3.44</v>
-      </c>
-      <c r="G20">
-        <v>1624</v>
-      </c>
-      <c r="H20" t="s">
-        <v>123</v>
+      <c r="A20" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="I20">
-        <v>6600</v>
-      </c>
-      <c r="J20">
-        <v>1.82</v>
-      </c>
-      <c r="K20">
-        <v>2.65</v>
-      </c>
-      <c r="L20">
-        <v>0.11</v>
-      </c>
-      <c r="M20">
-        <v>4.25</v>
+        <v>7065.3916019999997</v>
       </c>
       <c r="N20">
-        <v>260.11617189999998</v>
+        <v>146.7834014</v>
       </c>
       <c r="O20">
-        <v>38.242168200000002</v>
-      </c>
-      <c r="P20">
-        <v>222.66300000000001</v>
-      </c>
-      <c r="Q20">
-        <v>9.9879999999999995</v>
+        <v>-54.204010279999999</v>
+      </c>
+      <c r="P20" s="8">
+        <v>300.9884644</v>
       </c>
       <c r="R20">
-        <v>9.8728300000000004</v>
-      </c>
-      <c r="S20">
-        <f>(0.000000000000000138*G20/(1.673534E-24*1.3*0.000000066726*F20*1.8986E+30/(E20*7149200000)^2))/100000</f>
-        <v>243.60813720463176</v>
-      </c>
-      <c r="T20">
-        <f>IF(I20&gt;6800,-7,-5)</f>
-        <v>-5</v>
+        <v>9.2583198549999999</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
       </c>
       <c r="C21">
-        <v>5.6335157999999996</v>
+        <v>18.388179999999998</v>
       </c>
       <c r="D21">
-        <v>6.8140000000000006E-2</v>
+        <v>0.15279999999999999</v>
       </c>
       <c r="E21">
-        <v>0.95099999999999996</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F21">
-        <v>9.02</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="G21">
-        <v>1540</v>
-      </c>
-      <c r="H21" t="s">
-        <v>54</v>
+        <v>1027</v>
       </c>
       <c r="I21">
-        <v>6380</v>
+        <v>6095</v>
       </c>
       <c r="J21">
-        <v>1.39</v>
+        <v>1.867</v>
       </c>
       <c r="K21">
-        <v>1.33</v>
+        <v>1.407</v>
       </c>
       <c r="L21">
-        <v>0.18</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M21">
-        <v>4.16</v>
+        <v>4.0439999999999996</v>
       </c>
       <c r="N21">
-        <v>245.1514324</v>
+        <v>47.517260800000003</v>
       </c>
       <c r="O21">
-        <v>41.047960099999997</v>
-      </c>
-      <c r="P21">
-        <v>127.774</v>
+        <v>-50.8322632</v>
+      </c>
+      <c r="P21" s="8">
+        <v>76.902799999999999</v>
       </c>
       <c r="Q21">
-        <v>8.7200000000000006</v>
+        <v>7.57</v>
       </c>
       <c r="R21">
-        <v>8.5984200000000008</v>
+        <v>7.4165299999999998</v>
       </c>
       <c r="S21">
-        <f>(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
-        <v>39.515068300859213</v>
+        <f t="shared" ref="S21:S31" si="0">(0.000000000000000138*G21/(1.673534E-24*1.3*0.000000066726*F21*1.8986E+30/(E21*7149200000)^2))/100000</f>
+        <v>777.64358420307099</v>
       </c>
       <c r="T21">
-        <f>IF(I21&gt;6800,-7,-5)</f>
+        <f t="shared" ref="T21:T31" si="1">IF(I21&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22">
-        <v>3.2122199999999999</v>
+        <v>11.236598499999999</v>
       </c>
       <c r="D22">
-        <v>4.1399999999999999E-2</v>
+        <v>0.1041</v>
       </c>
       <c r="E22">
-        <v>1.1499999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="F22">
-        <v>2.4700000000000002</v>
+        <v>1.234</v>
       </c>
       <c r="G22">
-        <v>1463</v>
+        <v>1252</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="I22">
-        <v>5302</v>
+        <v>6295</v>
       </c>
       <c r="J22">
-        <v>1.1100000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="K22">
-        <v>1.1299999999999999</v>
+        <v>1.181</v>
       </c>
       <c r="L22">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>4.3600000000000003</v>
+        <v>4.2910000000000004</v>
       </c>
       <c r="N22">
-        <v>155.6814593</v>
+        <v>144.11935940000001</v>
       </c>
       <c r="O22">
-        <v>50.128711500000001</v>
-      </c>
-      <c r="P22">
-        <v>81.764700000000005</v>
+        <v>-50.463093299999997</v>
+      </c>
+      <c r="P22" s="8">
+        <v>141.81200000000001</v>
       </c>
       <c r="Q22">
-        <v>9.7629999999999999</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R22">
-        <v>9.5193600000000007</v>
+        <v>9.6608199999999993</v>
       </c>
       <c r="S22">
-        <f>(0.000000000000000138*G22/(1.673534E-24*1.3*0.000000066726*F22*1.8986E+30/(E22*7149200000)^2))/100000</f>
-        <v>200.46131426194896</v>
+        <f t="shared" si="0"/>
+        <v>355.42536038318485</v>
       </c>
       <c r="T22">
-        <f>IF(I22&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>5.75251</v>
+      </c>
+      <c r="D23">
+        <v>7.17E-2</v>
+      </c>
+      <c r="E23">
+        <v>1.02</v>
+      </c>
+      <c r="F23">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="G23">
+        <v>1480</v>
+      </c>
+      <c r="H23" t="s">
+        <v>54</v>
       </c>
       <c r="I23">
-        <v>6245.11328125</v>
+        <v>6150</v>
       </c>
       <c r="J23">
-        <v>1.208241820335388</v>
+        <v>1.64</v>
+      </c>
+      <c r="K23">
+        <v>1.21</v>
+      </c>
+      <c r="L23">
+        <v>0.21</v>
       </c>
       <c r="M23">
-        <v>4.2744002342224121</v>
+        <v>4.3</v>
       </c>
       <c r="N23">
-        <v>31.04275939878713</v>
+        <v>39.897668899999999</v>
       </c>
       <c r="O23">
-        <v>46.687851647860192</v>
-      </c>
-      <c r="P23">
-        <v>283.38339999999999</v>
+        <v>-50.008193400000003</v>
+      </c>
+      <c r="P23" s="8">
+        <v>158.66</v>
       </c>
       <c r="Q23">
-        <v>11.12930202484131</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="R23">
-        <v>11.12930202484131</v>
+        <v>9.3251000000000008</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="0"/>
+        <v>162.15983922320817</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="1"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="B24" t="s">
         <v>20</v>
       </c>
       <c r="C24">
-        <v>4.7947813000000004</v>
+        <v>2.1846700000000001</v>
       </c>
       <c r="D24">
-        <v>6.2770000000000006E-2</v>
+        <v>3.4160000000000003E-2</v>
       </c>
       <c r="E24">
-        <v>1.631</v>
+        <v>1.23</v>
       </c>
       <c r="F24">
-        <v>0.57399999999999995</v>
+        <v>1.44</v>
       </c>
       <c r="G24">
-        <v>1772</v>
+        <v>1570</v>
+      </c>
+      <c r="H24" t="s">
+        <v>132</v>
       </c>
       <c r="I24">
-        <v>6212</v>
+        <v>5830</v>
       </c>
       <c r="J24">
-        <v>2.1970000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="K24">
-        <v>1.4350000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="L24">
-        <v>3.6999999999999998E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M24">
-        <v>3.9114</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="N24">
-        <v>28.282571900000001</v>
+        <v>337.45782430000003</v>
       </c>
       <c r="O24">
-        <v>52.053920900000001</v>
-      </c>
-      <c r="P24">
-        <v>233.22</v>
+        <v>-48.003098799999997</v>
+      </c>
+      <c r="P24" s="8">
+        <v>137.54400000000001</v>
       </c>
       <c r="Q24">
-        <v>9.7270000000000003</v>
+        <v>10.092000000000001</v>
       </c>
       <c r="R24">
-        <v>9.5635499999999993</v>
+        <v>9.9369700000000005</v>
       </c>
       <c r="S24">
-        <f>(0.000000000000000138*G24/(1.673534E-24*1.3*0.000000066726*F24*1.8986E+30/(E24*7149200000)^2))/100000</f>
-        <v>2101.5864855136347</v>
+        <f t="shared" si="0"/>
+        <v>422.11900227636102</v>
       </c>
       <c r="T24">
-        <f>IF(I24&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
       </c>
       <c r="C25">
-        <v>4.7869491000000002</v>
+        <v>6.4025129999999999</v>
       </c>
       <c r="D25">
-        <v>6.5549999999999997E-2</v>
+        <v>7.0800000000000002E-2</v>
       </c>
       <c r="E25">
-        <v>1.6759999999999999</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="F25">
-        <v>3.58</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G25">
-        <v>1930</v>
+        <v>1388</v>
+      </c>
+      <c r="H25" t="s">
+        <v>63</v>
       </c>
       <c r="I25">
-        <v>7394</v>
+        <v>6400</v>
       </c>
       <c r="J25">
-        <v>1.9259999999999999</v>
+        <v>1.415</v>
       </c>
       <c r="K25">
-        <v>1.6479999999999999</v>
+        <v>1.3129999999999999</v>
       </c>
       <c r="L25">
-        <v>-6.9000000000000006E-2</v>
+        <v>0.09</v>
       </c>
       <c r="M25">
-        <v>4.1100000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="N25">
-        <v>130.5056385</v>
+        <v>125.3050544</v>
       </c>
       <c r="O25">
-        <v>3.7105662000000001</v>
-      </c>
-      <c r="P25">
-        <v>341.26299999999998</v>
+        <v>-46.484295899999999</v>
+      </c>
+      <c r="P25" s="8">
+        <v>123.297</v>
       </c>
       <c r="Q25">
-        <v>9.7739999999999991</v>
+        <v>8.9949999999999992</v>
       </c>
       <c r="R25">
-        <v>9.77332</v>
+        <v>8.8910300000000007</v>
       </c>
       <c r="S25">
-        <f>(0.000000000000000138*G25/(1.673534E-24*1.3*0.000000066726*F25*1.8986E+30/(E25*7149200000)^2))/100000</f>
-        <v>387.53401759458865</v>
+        <f t="shared" si="0"/>
+        <v>795.95548671567838</v>
       </c>
       <c r="T25">
-        <f>IF(I25&gt;6800,-7,-5)</f>
-        <v>-7</v>
+        <f t="shared" si="1"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>71</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>0.94145223</v>
+      </c>
+      <c r="D26">
+        <v>2.0240000000000001E-2</v>
+      </c>
+      <c r="E26">
+        <v>1.24</v>
+      </c>
+      <c r="F26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G26">
+        <v>2429</v>
+      </c>
+      <c r="H26" t="s">
+        <v>72</v>
       </c>
       <c r="I26">
-        <v>6424.27685546875</v>
+        <v>6432</v>
       </c>
       <c r="J26">
-        <v>2.0702402591705318</v>
+        <v>1.319</v>
+      </c>
+      <c r="K26">
+        <v>1.294</v>
+      </c>
+      <c r="L26">
+        <v>0.107</v>
+      </c>
+      <c r="M26">
+        <v>4.3099999999999996</v>
       </c>
       <c r="N26">
-        <v>292.24718620018581</v>
+        <v>24.354461799999999</v>
       </c>
       <c r="O26">
-        <v>47.969544064101818</v>
+        <v>-45.677793700000002</v>
+      </c>
+      <c r="P26" s="8">
+        <v>123.483</v>
       </c>
       <c r="Q26">
-        <v>10.36768245697021</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R26">
-        <v>10.36768245697021</v>
+        <v>9.1661699999999993</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="0"/>
+        <v>93.704022194109143</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="1"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
       </c>
       <c r="C27">
-        <v>2.7443245200000002</v>
+        <v>17.305904000000002</v>
       </c>
       <c r="D27">
-        <v>4.7390000000000002E-2</v>
+        <v>0.16</v>
       </c>
       <c r="E27">
-        <v>1.87</v>
+        <v>1.07</v>
       </c>
       <c r="F27">
-        <v>6.78</v>
+        <v>6.4</v>
       </c>
       <c r="G27">
-        <v>2562</v>
+        <v>1221.3900000000001</v>
       </c>
       <c r="I27">
-        <v>8450</v>
+        <v>7130</v>
       </c>
       <c r="J27">
-        <v>1.8580000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="K27">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="L27">
-        <v>-5.8999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>4.181</v>
+        <v>3.9460000000000002</v>
       </c>
       <c r="N27">
-        <v>74.552333200000007</v>
+        <v>164.031654</v>
       </c>
       <c r="O27">
-        <v>9.9979794000000002</v>
-      </c>
-      <c r="P27">
-        <v>330.73899999999998</v>
+        <v>-43.376696699999997</v>
+      </c>
+      <c r="P27" s="8">
+        <v>328.47500000000002</v>
       </c>
       <c r="Q27">
-        <v>9.4700000000000006</v>
+        <v>9.8670000000000009</v>
       </c>
       <c r="R27">
-        <v>9.4517399999999991</v>
+        <v>9.7596699999999998</v>
       </c>
       <c r="S27">
-        <f t="shared" ref="S27:S51" si="0">(0.000000000000000138*G27/(1.673534E-24*1.3*0.000000066726*F27*1.8986E+30/(E27*7149200000)^2))/100000</f>
-        <v>338.15838787809196</v>
+        <f t="shared" si="0"/>
+        <v>55.915145726222889</v>
       </c>
       <c r="T27">
-        <f t="shared" ref="T27:T50" si="1">IF(I27&gt;6800,-7,-5)</f>
+        <f t="shared" si="1"/>
         <v>-7</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C28">
-        <v>6.1349779</v>
+        <v>3.3448285000000002</v>
       </c>
       <c r="D28">
-        <v>7.1300000000000002E-2</v>
+        <v>5.5800000000000002E-2</v>
       </c>
       <c r="E28">
-        <v>1.1399999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="F28">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="G28">
-        <v>1361</v>
+        <v>2470</v>
       </c>
       <c r="H28" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="I28">
-        <v>5742</v>
+        <v>9360</v>
       </c>
       <c r="J28">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="K28">
-        <v>1.27</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L28">
-        <v>0.28699999999999998</v>
+        <v>0.21</v>
       </c>
       <c r="M28">
-        <v>3.92</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="N28">
-        <v>203.50995599999999</v>
+        <v>227.270329</v>
       </c>
       <c r="O28">
-        <v>53.728187599999998</v>
-      </c>
-      <c r="P28">
-        <v>92.258899999999997</v>
+        <v>-42.704965799999997</v>
+      </c>
+      <c r="P28" s="8">
+        <v>427.678</v>
       </c>
       <c r="Q28">
-        <v>8.0500000000000007</v>
+        <v>9.9459999999999997</v>
       </c>
       <c r="R28">
-        <v>7.89255</v>
+        <v>9.9122599999999998</v>
       </c>
       <c r="S28">
         <f t="shared" si="0"/>
-        <v>211.51519610586323</v>
+        <v>1247.4798366438731</v>
       </c>
       <c r="T28">
         <f t="shared" si="1"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
         <v>20</v>
       </c>
       <c r="C29">
-        <v>11.53533</v>
+        <v>4.9546416000000004</v>
       </c>
       <c r="D29">
-        <v>0.10970000000000001</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="E29">
-        <v>1.026</v>
+        <v>1.33</v>
       </c>
       <c r="F29">
-        <v>0.41499999999999998</v>
+        <v>0.96</v>
       </c>
       <c r="G29">
-        <v>1228.3</v>
-      </c>
-      <c r="H29" t="s">
-        <v>31</v>
+        <v>1487</v>
       </c>
       <c r="I29">
-        <v>5521</v>
+        <v>6400</v>
       </c>
       <c r="J29">
-        <v>2.3359999999999999</v>
+        <v>1.4319999999999999</v>
       </c>
       <c r="K29">
-        <v>1.3240000000000001</v>
+        <v>1.276</v>
       </c>
       <c r="L29">
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>3.823</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="N29">
-        <v>4.4471631</v>
+        <v>311.04275580000001</v>
       </c>
       <c r="O29">
-        <v>-66.358928500000005</v>
-      </c>
-      <c r="P29">
-        <v>79.5702</v>
+        <v>-39.225485599999999</v>
+      </c>
+      <c r="P29" s="8">
+        <v>162.303</v>
       </c>
       <c r="Q29">
-        <v>7.79</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="R29">
-        <v>7.5933599999999997</v>
+        <v>9.3767099999999992</v>
       </c>
       <c r="S29">
         <f t="shared" si="0"/>
-        <v>797.33090232058362</v>
+        <v>701.18164217622461</v>
       </c>
       <c r="T29">
         <f t="shared" si="1"/>
@@ -2356,63 +2403,63 @@
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>42</v>
+      <c r="A30" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>2.8758900000000001</v>
+        <v>0.79205199999999998</v>
       </c>
       <c r="D30">
-        <v>4.3639999999999998E-2</v>
+        <v>1.6789999999999999E-2</v>
       </c>
       <c r="E30">
-        <v>0.74</v>
+        <v>0.42109020000000003</v>
       </c>
       <c r="F30">
-        <v>0.38</v>
+        <v>9.2250570000000004E-2</v>
       </c>
       <c r="G30">
-        <v>1626</v>
+        <v>1978</v>
       </c>
       <c r="H30" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="I30">
-        <v>6179</v>
+        <v>5443</v>
       </c>
       <c r="J30">
-        <v>1.41</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="K30">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="L30">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="M30">
-        <v>4.37</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="N30">
-        <v>247.62298269999999</v>
+        <v>358.6688767</v>
       </c>
       <c r="O30">
-        <v>38.347534899999999</v>
-      </c>
-      <c r="P30">
-        <v>75.8643</v>
+        <v>-37.628223699999999</v>
+      </c>
+      <c r="P30" s="8">
+        <v>80.437299999999993</v>
       </c>
       <c r="Q30">
-        <v>8.15</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="R30">
-        <v>8.0141600000000004</v>
+        <v>9.6000599999999991</v>
       </c>
       <c r="S30">
         <f t="shared" si="0"/>
-        <v>599.63628364223177</v>
+        <v>972.96006983022733</v>
       </c>
       <c r="T30">
         <f t="shared" si="1"/>
@@ -2420,1458 +2467,1099 @@
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>59</v>
+      <c r="A31" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="B31" t="s">
         <v>20</v>
       </c>
       <c r="C31">
-        <v>19.502103999999999</v>
+        <v>8.1587200000000006</v>
       </c>
       <c r="D31">
-        <v>0.1482</v>
+        <v>8.0100000000000005E-2</v>
       </c>
       <c r="E31">
-        <v>0.52993221999999995</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F31">
-        <v>3.0425219999999999E-2</v>
+        <v>2.54</v>
       </c>
       <c r="G31">
-        <v>253.08</v>
+        <v>1059</v>
       </c>
       <c r="H31" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="I31">
-        <v>6310</v>
+        <v>5600</v>
       </c>
       <c r="J31">
-        <v>1.43</v>
+        <v>1.03</v>
       </c>
       <c r="K31">
-        <v>1.1499999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="L31">
-        <v>-0.16</v>
+        <v>0.17</v>
       </c>
       <c r="M31">
-        <v>4.1900000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="N31">
-        <v>253.78488530000001</v>
+        <v>359.90087369999998</v>
       </c>
       <c r="O31">
-        <v>20.491523999999998</v>
-      </c>
-      <c r="P31">
-        <v>107.898</v>
+        <v>-35.031334899999997</v>
+      </c>
+      <c r="P31" s="8">
+        <v>89.960599999999999</v>
       </c>
       <c r="Q31">
-        <v>8.8550000000000004</v>
+        <v>9.7889999999999997</v>
       </c>
       <c r="R31">
-        <v>8.7641200000000001</v>
+        <v>9.6124899999999993</v>
       </c>
       <c r="S31">
         <f t="shared" si="0"/>
-        <v>597.79498778467087</v>
+        <v>136.24063220140397</v>
       </c>
       <c r="T31">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32">
-        <v>2.2185756699999999</v>
-      </c>
-      <c r="D32">
-        <v>3.1260000000000003E-2</v>
-      </c>
-      <c r="E32">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F32">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="G32">
-        <v>1209</v>
-      </c>
-      <c r="H32" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
       <c r="I32">
-        <v>5052</v>
+        <v>5775</v>
       </c>
       <c r="J32">
-        <v>0.75</v>
+        <v>5.1109999999999998</v>
       </c>
       <c r="K32">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>300.1821223</v>
+        <v>274.00302978329</v>
       </c>
       <c r="O32">
-        <v>22.7097759</v>
+        <v>22.9885348444</v>
       </c>
       <c r="P32">
-        <v>19.7638</v>
+        <v>1802.37</v>
       </c>
       <c r="Q32">
-        <v>7.67</v>
-      </c>
-      <c r="R32">
-        <v>7.41432</v>
-      </c>
-      <c r="S32">
-        <f>(0.000000000000000138*G32/(1.673534E-24*1.3*0.000000066726*F32*1.8986E+30/(E32*7149200000)^2))/100000</f>
-        <v>349.61677638948368</v>
-      </c>
-      <c r="T32">
-        <f>IF(I32&gt;6800,-7,-5)</f>
+        <v>12.961</v>
+      </c>
+      <c r="V32">
+        <v>14.082000000000001</v>
+      </c>
+      <c r="W32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>159</v>
+      </c>
+      <c r="I33">
+        <v>5792</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>276.67545984469001</v>
+      </c>
+      <c r="O33">
+        <v>14.0128749692</v>
+      </c>
+      <c r="P33">
+        <v>2046.66</v>
+      </c>
+      <c r="Q33">
+        <v>17.097000000000001</v>
+      </c>
+      <c r="R33">
+        <v>16.870684000000001</v>
+      </c>
+      <c r="V33">
+        <v>18.082999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34">
+        <v>5799</v>
+      </c>
+      <c r="J34">
+        <v>0.99</v>
+      </c>
+      <c r="K34">
+        <v>1.042</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>4.4642999999999997</v>
+      </c>
+      <c r="N34">
+        <v>278.21725113665002</v>
+      </c>
+      <c r="O34">
+        <v>11.92287820316</v>
+      </c>
+      <c r="P34">
+        <v>224.12799999999999</v>
+      </c>
+      <c r="Q34">
+        <v>11.997</v>
+      </c>
+      <c r="S34" s="4"/>
+      <c r="V34">
+        <v>12.47</v>
+      </c>
+      <c r="W34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>153</v>
+      </c>
+      <c r="I35">
+        <v>5800</v>
+      </c>
+      <c r="J35">
+        <v>1.417</v>
+      </c>
+      <c r="K35">
+        <v>1.04</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>4.1520999999999999</v>
+      </c>
+      <c r="N35">
+        <v>280.34203579685999</v>
+      </c>
+      <c r="O35">
+        <v>26.315625519600001</v>
+      </c>
+      <c r="P35">
+        <v>897.52700000000004</v>
+      </c>
+      <c r="Q35">
+        <v>13.994999999999999</v>
+      </c>
+      <c r="V35">
+        <v>14.913</v>
+      </c>
+      <c r="W35" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36">
+        <v>5800</v>
+      </c>
+      <c r="J36">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="K36">
+        <v>1.04</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>4.2129000000000003</v>
+      </c>
+      <c r="N36">
+        <v>270.95467601665001</v>
+      </c>
+      <c r="O36">
+        <v>3.9944008770699999</v>
+      </c>
+      <c r="P36">
+        <v>2963.53</v>
+      </c>
+      <c r="Q36">
+        <v>17.052</v>
+      </c>
+      <c r="V36">
+        <v>17.364000000000001</v>
+      </c>
+      <c r="W36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37">
+        <v>5800.4</v>
+      </c>
+      <c r="J37">
+        <v>1.4930000000000001</v>
+      </c>
+      <c r="K37">
+        <v>1.04</v>
+      </c>
+      <c r="L37">
+        <v>-6.6000000000000003E-2</v>
+      </c>
+      <c r="M37">
+        <v>4.1069000000000004</v>
+      </c>
+      <c r="N37">
+        <v>270.30880152526998</v>
+      </c>
+      <c r="O37">
+        <v>15.944626030029999</v>
+      </c>
+      <c r="P37">
+        <v>579.08500000000004</v>
+      </c>
+      <c r="Q37">
+        <v>12.978999999999999</v>
+      </c>
+      <c r="V37">
+        <v>13.638999999999999</v>
+      </c>
+      <c r="W37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>146</v>
+      </c>
+      <c r="I38">
+        <v>5804</v>
+      </c>
+      <c r="J38">
+        <v>1.179</v>
+      </c>
+      <c r="K38">
+        <v>1.04</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>4.3121</v>
+      </c>
+      <c r="N38">
+        <v>274.86862255196002</v>
+      </c>
+      <c r="O38">
+        <v>5.3506741626599998</v>
+      </c>
+      <c r="P38">
+        <v>1644.4</v>
+      </c>
+      <c r="Q38">
+        <v>15.965999999999999</v>
+      </c>
+      <c r="V38">
+        <v>16.86</v>
+      </c>
+      <c r="W38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I39">
+        <v>5806</v>
+      </c>
+      <c r="J39">
+        <v>27.986999999999998</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>278.48921850735002</v>
+      </c>
+      <c r="O39">
+        <v>31.640052119060002</v>
+      </c>
+      <c r="P39">
+        <v>7397.91</v>
+      </c>
+      <c r="Q39">
+        <v>12.01</v>
+      </c>
+      <c r="V39">
+        <v>12.507</v>
+      </c>
+      <c r="W39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>3.9501900000000001</v>
+      </c>
+      <c r="D40">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E40">
+        <v>1.58</v>
+      </c>
+      <c r="F40">
+        <v>0.5</v>
+      </c>
+      <c r="G40">
+        <v>1604</v>
+      </c>
+      <c r="H40" t="s">
+        <v>54</v>
+      </c>
+      <c r="I40">
+        <v>6170</v>
+      </c>
+      <c r="J40">
+        <v>1.48</v>
+      </c>
+      <c r="K40">
+        <v>1.67</v>
+      </c>
+      <c r="L40">
+        <v>0.26</v>
+      </c>
+      <c r="M40">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="N40">
+        <v>313.78323929999999</v>
+      </c>
+      <c r="O40">
+        <v>-34.135751200000001</v>
+      </c>
+      <c r="P40" s="8">
+        <v>211.21100000000001</v>
+      </c>
+      <c r="Q40">
+        <v>10.051</v>
+      </c>
+      <c r="R40">
+        <v>10.028499999999999</v>
+      </c>
+      <c r="S40">
+        <f>(0.000000000000000138*G40/(1.673534E-24*1.3*0.000000066726*F40*1.8986E+30/(E40*7149200000)^2))/100000</f>
+        <v>2049.4439875099679</v>
+      </c>
+      <c r="T40">
+        <f>IF(I40&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33">
-        <v>3.3089580000000001</v>
-      </c>
-      <c r="D33">
-        <v>5.2080000000000001E-2</v>
-      </c>
-      <c r="E33">
-        <v>1.5449999999999999</v>
-      </c>
-      <c r="F33">
-        <v>1.0169999999999999</v>
-      </c>
-      <c r="G33">
-        <v>2132</v>
-      </c>
-      <c r="I33">
-        <v>6272</v>
-      </c>
-      <c r="J33">
-        <v>2.5910000000000002</v>
-      </c>
-      <c r="K33">
-        <v>1.72</v>
-      </c>
-      <c r="L33">
-        <v>0.3</v>
-      </c>
-      <c r="M33">
-        <v>3.8479999999999999</v>
-      </c>
-      <c r="N33">
-        <v>319.6995877</v>
-      </c>
-      <c r="O33">
-        <v>-26.6163743</v>
-      </c>
-      <c r="P33">
-        <v>161.49799999999999</v>
-      </c>
-      <c r="Q33">
-        <v>8.3239999999999998</v>
-      </c>
-      <c r="R33">
-        <v>8.2268799999999995</v>
-      </c>
-      <c r="S33">
-        <f t="shared" si="0"/>
-        <v>1280.5918535006856</v>
-      </c>
-      <c r="T33">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34">
-        <v>3.5247485900000002</v>
-      </c>
-      <c r="D34">
-        <v>4.7070000000000001E-2</v>
-      </c>
-      <c r="E34">
-        <v>1.39</v>
-      </c>
-      <c r="F34">
-        <v>0.73</v>
-      </c>
-      <c r="G34">
-        <v>1459</v>
-      </c>
-      <c r="H34" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34">
-        <v>6091</v>
-      </c>
-      <c r="J34">
-        <v>1.19</v>
-      </c>
-      <c r="K34">
-        <v>1.23</v>
-      </c>
-      <c r="L34">
-        <v>0.01</v>
-      </c>
-      <c r="M34">
-        <v>4.45</v>
-      </c>
-      <c r="N34">
-        <v>330.79502189999999</v>
-      </c>
-      <c r="O34">
-        <v>18.884241899999999</v>
-      </c>
-      <c r="P34">
-        <v>48.301600000000001</v>
-      </c>
-      <c r="Q34">
-        <v>7.65</v>
-      </c>
-      <c r="R34">
-        <v>7.5086599999999999</v>
-      </c>
-      <c r="S34" s="4">
-        <f t="shared" si="0"/>
-        <v>988.21070019970352</v>
-      </c>
-      <c r="T34">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>101</v>
-      </c>
-      <c r="B35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35">
-        <v>6.0344680000000004</v>
-      </c>
-      <c r="D35">
-        <v>6.3560000000000005E-2</v>
-      </c>
-      <c r="E35">
-        <v>0.437</v>
-      </c>
-      <c r="F35">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G35">
-        <v>1076</v>
-      </c>
-      <c r="H35" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35">
-        <v>5540</v>
-      </c>
-      <c r="J35">
-        <v>1.0589999999999999</v>
-      </c>
-      <c r="K35">
-        <v>1.02</v>
-      </c>
-      <c r="L35">
-        <v>0.04</v>
-      </c>
-      <c r="M35">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="N35">
-        <v>349.55926649999998</v>
-      </c>
-      <c r="O35">
-        <v>-56.9039857</v>
-      </c>
-      <c r="P35">
-        <v>94.171899999999994</v>
-      </c>
-      <c r="Q35">
-        <v>9.8089999999999993</v>
-      </c>
-      <c r="R35">
-        <v>9.6495599999999992</v>
-      </c>
-      <c r="S35">
-        <f t="shared" si="0"/>
-        <v>956.09264119622901</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36">
-        <v>14.2767</v>
-      </c>
-      <c r="D36">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="E36">
-        <v>0.83599999999999997</v>
-      </c>
-      <c r="F36">
-        <v>0.19</v>
-      </c>
-      <c r="G36">
-        <v>789.15</v>
-      </c>
-      <c r="H36" t="s">
-        <v>45</v>
-      </c>
-      <c r="I36">
-        <v>5080</v>
-      </c>
-      <c r="J36">
-        <v>2.9430000000000001</v>
-      </c>
-      <c r="K36">
-        <v>1.212</v>
-      </c>
-      <c r="L36">
-        <v>-0.08</v>
-      </c>
-      <c r="M36">
-        <v>3.5840000000000001</v>
-      </c>
-      <c r="N36">
-        <v>353.03318630000001</v>
-      </c>
-      <c r="O36">
-        <v>-21.801200699999999</v>
-      </c>
-      <c r="P36">
-        <v>95.548299999999998</v>
-      </c>
-      <c r="Q36">
-        <v>8.15</v>
-      </c>
-      <c r="R36">
-        <v>7.9077599999999997</v>
-      </c>
-      <c r="S36">
-        <f t="shared" si="0"/>
-        <v>742.8583931109747</v>
-      </c>
-      <c r="T36">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37">
-        <v>4.1268799999999999</v>
-      </c>
-      <c r="D37">
-        <v>5.6800000000000003E-2</v>
-      </c>
-      <c r="E37">
-        <v>1.44</v>
-      </c>
-      <c r="F37">
-        <v>1.17</v>
-      </c>
-      <c r="G37">
-        <v>2061</v>
-      </c>
-      <c r="I37">
-        <v>6801</v>
-      </c>
-      <c r="J37">
-        <v>1.56</v>
-      </c>
-      <c r="K37">
-        <v>1.43</v>
-      </c>
-      <c r="L37">
-        <v>0.02</v>
-      </c>
-      <c r="M37">
-        <v>4.21</v>
-      </c>
-      <c r="N37">
-        <v>7.3289156000000002</v>
-      </c>
-      <c r="O37">
-        <v>-76.304032000000007</v>
-      </c>
-      <c r="P37">
-        <v>196.852</v>
-      </c>
-      <c r="Q37">
-        <v>9.5950000000000006</v>
-      </c>
-      <c r="R37">
-        <v>9.5202500000000008</v>
-      </c>
-      <c r="S37">
-        <f t="shared" si="0"/>
-        <v>934.76971602454307</v>
-      </c>
-      <c r="T37">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38">
-        <v>18.712024</v>
-      </c>
-      <c r="D38">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="E38">
-        <v>0.80944318999999998</v>
-      </c>
-      <c r="F38">
-        <v>0.23314467</v>
-      </c>
-      <c r="G38">
-        <v>798.3</v>
-      </c>
-      <c r="H38" t="s">
-        <v>54</v>
-      </c>
-      <c r="I38">
-        <v>6128</v>
-      </c>
-      <c r="J38">
-        <v>1.266</v>
-      </c>
-      <c r="K38">
-        <v>1.1641999999999999</v>
-      </c>
-      <c r="L38">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="M38">
-        <v>4.2960000000000003</v>
-      </c>
-      <c r="N38">
-        <v>306.74113399999999</v>
-      </c>
-      <c r="O38">
-        <v>33.744388200000003</v>
-      </c>
-      <c r="P38">
-        <v>80.666499999999999</v>
-      </c>
-      <c r="Q38">
-        <v>8.5579999999999998</v>
-      </c>
-      <c r="R38">
-        <v>8.4183900000000005</v>
-      </c>
-      <c r="S38">
-        <f t="shared" si="0"/>
-        <v>574.11765847468712</v>
-      </c>
-      <c r="T38">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39">
-        <v>3.4148839999999998</v>
-      </c>
-      <c r="D39">
-        <v>4.7899999999999998E-2</v>
-      </c>
-      <c r="E39">
-        <v>1.23</v>
-      </c>
-      <c r="F39">
-        <v>1.02</v>
-      </c>
-      <c r="G39">
-        <v>1762</v>
-      </c>
-      <c r="H39" t="s">
-        <v>33</v>
-      </c>
-      <c r="I39">
-        <v>5392</v>
-      </c>
-      <c r="J39">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="K39">
-        <v>1.26</v>
-      </c>
-      <c r="L39">
-        <v>0.34</v>
-      </c>
-      <c r="M39">
-        <v>3.88</v>
-      </c>
-      <c r="N39">
-        <v>152.53193490000001</v>
-      </c>
-      <c r="O39">
-        <v>18.185728399999999</v>
-      </c>
-      <c r="P39">
-        <v>73.612300000000005</v>
-      </c>
-      <c r="Q39">
-        <v>8.0185200000000005</v>
-      </c>
-      <c r="R39">
-        <v>7.8097899999999996</v>
-      </c>
-      <c r="S39">
-        <f t="shared" si="0"/>
-        <v>668.81110409377118</v>
-      </c>
-      <c r="T39">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40">
-        <v>11.814299999999999</v>
-      </c>
-      <c r="D40">
-        <v>0.1066</v>
-      </c>
-      <c r="E40">
-        <v>0.66</v>
-      </c>
-      <c r="F40">
-        <v>0.11</v>
-      </c>
-      <c r="G40">
-        <v>1089</v>
-      </c>
-      <c r="H40" t="s">
-        <v>33</v>
-      </c>
-      <c r="I40">
-        <v>5576</v>
-      </c>
-      <c r="J40">
-        <v>1.7470000000000001</v>
-      </c>
-      <c r="K40">
-        <v>1.157</v>
-      </c>
-      <c r="L40">
-        <v>0.42099999999999999</v>
-      </c>
-      <c r="M40">
-        <v>4.016</v>
-      </c>
-      <c r="N40">
-        <v>154.67109769999999</v>
-      </c>
-      <c r="O40">
-        <v>10.1288464</v>
-      </c>
-      <c r="P40">
-        <v>132.345</v>
-      </c>
-      <c r="Q40">
-        <v>9.3800000000000008</v>
-      </c>
-      <c r="R40">
-        <v>9.2170199999999998</v>
-      </c>
-      <c r="S40">
-        <f t="shared" si="0"/>
-        <v>1103.5971886171305</v>
-      </c>
-      <c r="T40">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41">
-        <v>11.168454000000001</v>
-      </c>
-      <c r="D41">
-        <v>0.10356</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>0.39800000000000002</v>
-      </c>
-      <c r="G41">
-        <v>1030</v>
+        <v>147</v>
       </c>
       <c r="I41">
-        <v>6154</v>
+        <v>5812</v>
       </c>
       <c r="J41">
-        <v>1.161</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="K41">
-        <v>1.1879999999999999</v>
+        <v>1.0449999999999999</v>
       </c>
       <c r="L41">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>4.3789999999999996</v>
+        <v>4.5917000000000003</v>
       </c>
       <c r="N41">
-        <v>73.766792699999996</v>
+        <v>47.805523543809997</v>
       </c>
       <c r="O41">
-        <v>18.654323000000002</v>
+        <v>-18.380477788619999</v>
       </c>
       <c r="P41">
-        <v>130.72</v>
+        <v>147.77799999999999</v>
       </c>
       <c r="Q41">
-        <v>9.8219999999999992</v>
-      </c>
-      <c r="R41">
-        <v>9.7262599999999999</v>
-      </c>
-      <c r="S41">
-        <f t="shared" si="0"/>
-        <v>662.28004924519439</v>
-      </c>
-      <c r="T41">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+        <v>11.044</v>
+      </c>
+      <c r="V41">
+        <v>11.662000000000001</v>
+      </c>
+      <c r="W41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42">
-        <v>4.73620865</v>
-      </c>
-      <c r="D42">
-        <v>6.2300000000000001E-2</v>
-      </c>
-      <c r="E42">
-        <v>1.35</v>
-      </c>
-      <c r="F42">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G42">
-        <v>1712</v>
-      </c>
-      <c r="H42" t="s">
-        <v>37</v>
+        <v>155</v>
       </c>
       <c r="I42">
-        <v>5375</v>
+        <v>5813</v>
       </c>
       <c r="J42">
-        <v>2.69</v>
+        <v>1.83</v>
       </c>
       <c r="K42">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="L42">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>3.7</v>
+        <v>3.9344999999999999</v>
       </c>
       <c r="N42">
-        <v>161.70690529999999</v>
+        <v>270.99233637095</v>
       </c>
       <c r="O42">
-        <v>-9.3993646000000002</v>
+        <v>16.858729226019999</v>
       </c>
       <c r="P42">
-        <v>99.159599999999998</v>
+        <v>1779.6</v>
       </c>
       <c r="Q42">
-        <v>8.0399999999999991</v>
-      </c>
-      <c r="R42">
-        <v>7.8311200000000003</v>
-      </c>
-      <c r="S42">
-        <f t="shared" si="0"/>
-        <v>3894.9775251994533</v>
-      </c>
-      <c r="T42">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+        <v>14.999000000000001</v>
+      </c>
+      <c r="V42">
+        <v>15.66</v>
+      </c>
+      <c r="W42" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>67</v>
-      </c>
-      <c r="B43" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43">
-        <v>3.0801715999999999</v>
-      </c>
-      <c r="D43">
-        <v>4.8809999999999999E-2</v>
-      </c>
-      <c r="E43">
-        <v>1.5249999999999999</v>
-      </c>
-      <c r="F43">
-        <v>1.31</v>
-      </c>
-      <c r="G43">
-        <v>2087</v>
-      </c>
-      <c r="H43" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="I43">
-        <v>7454</v>
+        <v>5815.4</v>
       </c>
       <c r="J43">
-        <v>1.645</v>
+        <v>4.2549999999999999</v>
       </c>
       <c r="K43">
-        <v>1.635</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>-1.7999999999999999E-2</v>
+        <v>-0.19350000000000001</v>
       </c>
       <c r="M43">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>125.617407</v>
+        <v>80.600252814719994</v>
       </c>
       <c r="O43">
-        <v>13.735309300000001</v>
+        <v>-68.64221652773</v>
       </c>
       <c r="P43">
-        <v>226.5</v>
+        <v>398.375</v>
       </c>
       <c r="Q43">
-        <v>9.234</v>
-      </c>
-      <c r="R43">
-        <v>9.2088699999999992</v>
-      </c>
-      <c r="S43">
-        <f t="shared" si="0"/>
-        <v>948.15286253702118</v>
-      </c>
-      <c r="T43">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B44" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44">
-        <v>4.6117093000000002</v>
-      </c>
-      <c r="D44">
-        <v>6.3700000000000007E-2</v>
-      </c>
-      <c r="E44">
-        <v>1.91</v>
-      </c>
-      <c r="F44">
-        <v>4.07</v>
-      </c>
-      <c r="G44">
-        <v>1935</v>
-      </c>
-      <c r="H44" t="s">
-        <v>109</v>
+        <v>11.137</v>
+      </c>
+      <c r="V43">
+        <v>11.56</v>
+      </c>
+      <c r="W43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>158</v>
       </c>
       <c r="I44">
-        <v>7500</v>
+        <v>5816</v>
       </c>
       <c r="J44">
-        <v>1.83</v>
+        <v>5.2939999999999996</v>
       </c>
       <c r="K44">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="L44">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>4.1269999999999998</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>111.5095293</v>
+        <v>284.79622244569998</v>
       </c>
       <c r="O44">
-        <v>7.6157759</v>
+        <v>15.987368865140001</v>
       </c>
       <c r="P44">
-        <v>300.27600000000001</v>
+        <v>3747.72</v>
       </c>
       <c r="Q44">
-        <v>9.8569999999999993</v>
-      </c>
-      <c r="R44">
-        <v>9.8633100000000002</v>
-      </c>
-      <c r="S44">
-        <f t="shared" si="0"/>
-        <v>443.85469120292152</v>
-      </c>
-      <c r="T44">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+        <v>15.958</v>
+      </c>
+      <c r="V44">
+        <v>17.585999999999999</v>
+      </c>
+      <c r="W44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45">
-        <v>4.1137899999999998</v>
-      </c>
-      <c r="D45">
-        <v>5.4969999999999998E-2</v>
-      </c>
-      <c r="E45">
-        <v>1.35</v>
-      </c>
-      <c r="F45">
-        <v>1.7</v>
-      </c>
-      <c r="G45">
-        <v>2080</v>
-      </c>
-      <c r="H45" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="I45">
-        <v>6327</v>
+        <v>5820</v>
       </c>
       <c r="J45">
-        <v>1.93</v>
+        <v>6.2519999999999998</v>
       </c>
       <c r="K45">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>92.664022599999996</v>
+        <v>267.97432727351003</v>
       </c>
       <c r="O45">
-        <v>30.957133299999999</v>
+        <v>17.507747521020001</v>
       </c>
       <c r="P45">
-        <v>134.05799999999999</v>
+        <v>6401.77</v>
       </c>
       <c r="Q45">
-        <v>8.68</v>
-      </c>
-      <c r="R45">
-        <v>8.5839300000000005</v>
-      </c>
-      <c r="S45">
-        <f t="shared" si="0"/>
-        <v>570.64953846380126</v>
-      </c>
-      <c r="T45">
-        <f t="shared" si="1"/>
+        <v>15.007999999999999</v>
+      </c>
+      <c r="V45">
+        <v>15.702999999999999</v>
+      </c>
+      <c r="W45" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>154</v>
+      </c>
+      <c r="I46">
+        <v>5824</v>
+      </c>
+      <c r="J46">
+        <v>4.7249999999999996</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>284.95537150204001</v>
+      </c>
+      <c r="O46">
+        <v>14.42740619077</v>
+      </c>
+      <c r="P46">
+        <v>1961.4</v>
+      </c>
+      <c r="Q46">
+        <v>14.023</v>
+      </c>
+      <c r="V46">
+        <v>15.048999999999999</v>
+      </c>
+      <c r="W46" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47">
+        <v>3.6623920000000001</v>
+      </c>
+      <c r="D47">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="E47">
+        <v>1.53</v>
+      </c>
+      <c r="F47">
+        <v>0.85</v>
+      </c>
+      <c r="G47">
+        <v>1716.2</v>
+      </c>
+      <c r="H47" t="s">
+        <v>125</v>
+      </c>
+      <c r="I47">
+        <v>6600</v>
+      </c>
+      <c r="J47">
+        <v>1.51</v>
+      </c>
+      <c r="K47">
+        <v>1.39</v>
+      </c>
+      <c r="L47">
+        <v>0.03</v>
+      </c>
+      <c r="M47">
+        <v>4.2</v>
+      </c>
+      <c r="N47">
+        <v>66.370901599999996</v>
+      </c>
+      <c r="O47">
+        <v>-30.600436200000001</v>
+      </c>
+      <c r="P47" s="8">
+        <v>246.69</v>
+      </c>
+      <c r="Q47">
+        <v>10.044</v>
+      </c>
+      <c r="R47">
+        <v>9.9720200000000006</v>
+      </c>
+      <c r="S47">
+        <f t="shared" ref="S47:S81" si="2">(0.000000000000000138*G47/(1.673534E-24*1.3*0.000000066726*F47*1.8986E+30/(E47*7149200000)^2))/100000</f>
+        <v>1209.5375438309629</v>
+      </c>
+      <c r="T47">
+        <f t="shared" ref="T47:T91" si="3">IF(I47&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46">
-        <v>3.4741084999999998</v>
-      </c>
-      <c r="D46">
-        <v>5.4199999999999998E-2</v>
-      </c>
-      <c r="E46">
-        <v>1.7410000000000001</v>
-      </c>
-      <c r="F46">
-        <v>3.3820000000000001</v>
-      </c>
-      <c r="G46">
-        <v>2262</v>
-      </c>
-      <c r="H46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I46">
-        <v>8720</v>
-      </c>
-      <c r="J46">
-        <v>1.5649999999999999</v>
-      </c>
-      <c r="K46">
-        <v>1.76</v>
-      </c>
-      <c r="L46">
-        <v>-0.28999999999999998</v>
-      </c>
-      <c r="M46">
-        <v>4.29</v>
-      </c>
-      <c r="N46">
-        <v>294.66141260000001</v>
-      </c>
-      <c r="O46">
-        <v>31.219200099999998</v>
-      </c>
-      <c r="P46">
-        <v>136.42599999999999</v>
-      </c>
-      <c r="Q46">
-        <v>7.59</v>
-      </c>
-      <c r="R46">
-        <v>7.5749199999999997</v>
-      </c>
-      <c r="S46">
-        <f t="shared" si="0"/>
-        <v>518.80488815900412</v>
-      </c>
-      <c r="T46">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47">
-        <v>5.55149296</v>
-      </c>
-      <c r="D47">
-        <v>6.6500000000000004E-2</v>
-      </c>
-      <c r="E47">
-        <v>1.1339999999999999</v>
-      </c>
-      <c r="F47">
-        <v>4.59</v>
-      </c>
-      <c r="G47">
-        <v>1391</v>
-      </c>
-      <c r="H47" t="s">
-        <v>52</v>
-      </c>
-      <c r="I47">
-        <v>6426</v>
-      </c>
-      <c r="J47">
-        <v>1.3380000000000001</v>
-      </c>
-      <c r="K47">
-        <v>1.268</v>
-      </c>
-      <c r="L47">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="M47">
-        <v>4.2869999999999999</v>
-      </c>
-      <c r="N47">
-        <v>161.90902729999999</v>
-      </c>
-      <c r="O47">
-        <v>71.655726999999999</v>
-      </c>
-      <c r="P47">
-        <v>96.517300000000006</v>
-      </c>
-      <c r="Q47">
-        <v>8.34</v>
-      </c>
-      <c r="R47">
-        <v>8.23752</v>
-      </c>
-      <c r="S47">
-        <f t="shared" si="0"/>
-        <v>99.730517672190274</v>
-      </c>
-      <c r="T47">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
       </c>
       <c r="C48">
-        <v>2.7033900000000002</v>
+        <v>5.3220124999999996</v>
       </c>
       <c r="D48">
-        <v>4.1230000000000003E-2</v>
+        <v>6.08E-2</v>
       </c>
       <c r="E48">
-        <v>1.56</v>
+        <v>1.226</v>
       </c>
       <c r="F48">
-        <v>1.94</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="G48">
-        <v>1816</v>
+        <v>1460</v>
+      </c>
+      <c r="H48" t="s">
+        <v>43</v>
       </c>
       <c r="I48">
-        <v>6304</v>
+        <v>5990</v>
       </c>
       <c r="J48">
-        <v>1.7</v>
+        <v>1.5609999999999999</v>
       </c>
       <c r="K48">
-        <v>1.96</v>
+        <v>1.06</v>
       </c>
       <c r="L48">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="M48">
-        <v>4.2</v>
+        <v>4.0750000000000002</v>
       </c>
       <c r="N48">
-        <v>148.6431193</v>
+        <v>210.1935714</v>
       </c>
       <c r="O48">
-        <v>40.387944599999997</v>
-      </c>
-      <c r="P48">
-        <v>210.25200000000001</v>
+        <v>-30.583608399999999</v>
+      </c>
+      <c r="P48" s="8">
+        <v>200.07499999999999</v>
       </c>
       <c r="Q48">
-        <v>9.8160000000000007</v>
+        <v>10.068</v>
       </c>
       <c r="R48">
-        <v>9.7632399999999997</v>
+        <v>9.8670799999999996</v>
       </c>
       <c r="S48">
-        <f t="shared" si="0"/>
-        <v>582.97620763372299</v>
+        <f t="shared" si="2"/>
+        <v>2057.1154637812851</v>
       </c>
       <c r="T48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
       </c>
       <c r="C49">
-        <v>2.9895931999999998</v>
+        <v>3.3089580000000001</v>
       </c>
       <c r="D49">
-        <v>4.317E-2</v>
+        <v>5.2080000000000001E-2</v>
       </c>
       <c r="E49">
-        <v>1.6990000000000001</v>
+        <v>1.5449999999999999</v>
       </c>
       <c r="F49">
-        <v>0.90200000000000002</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="G49">
-        <v>1823</v>
-      </c>
-      <c r="H49" t="s">
-        <v>56</v>
+        <v>2132</v>
       </c>
       <c r="I49">
-        <v>6206</v>
+        <v>6272</v>
       </c>
       <c r="J49">
-        <v>1.603</v>
+        <v>2.5910000000000002</v>
       </c>
       <c r="K49">
-        <v>1.2010000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="L49">
-        <v>-0.11600000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="M49">
-        <v>4.1079999999999997</v>
+        <v>3.8479999999999999</v>
       </c>
       <c r="N49">
-        <v>157.06262000000001</v>
+        <v>319.6995877</v>
       </c>
       <c r="O49">
-        <v>25.573136600000002</v>
-      </c>
-      <c r="P49">
-        <v>218.05</v>
+        <v>-26.6163743</v>
+      </c>
+      <c r="P49" s="8">
+        <v>161.49799999999999</v>
       </c>
       <c r="Q49">
-        <v>9.98</v>
+        <v>8.3239999999999998</v>
       </c>
       <c r="R49">
-        <v>9.95702</v>
+        <v>8.2268799999999995</v>
       </c>
       <c r="S49">
-        <f t="shared" si="0"/>
-        <v>1492.9814393090719</v>
+        <f t="shared" si="2"/>
+        <v>1280.5918535006856</v>
       </c>
       <c r="T49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>55</v>
+      <c r="A50" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
       </c>
       <c r="C50">
-        <v>2.7347700000000001</v>
+        <v>9.9558099999999996</v>
       </c>
       <c r="D50">
-        <v>4.4150000000000002E-2</v>
+        <v>9.9400000000000002E-2</v>
       </c>
       <c r="E50">
-        <v>1.6</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="F50">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="G50">
-        <v>2048</v>
-      </c>
-      <c r="H50" t="s">
-        <v>56</v>
+        <v>1655</v>
       </c>
       <c r="I50">
-        <v>6768</v>
+        <v>4896</v>
       </c>
       <c r="J50">
-        <v>1.81</v>
+        <v>3.55</v>
       </c>
       <c r="K50">
-        <v>1.76</v>
+        <v>1.31</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="M50">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="N50">
-        <v>78.295591200000004</v>
+        <v>184.97875790000001</v>
       </c>
       <c r="O50">
-        <v>33.317953199999998</v>
+        <v>-25.827853099999999</v>
       </c>
       <c r="P50">
-        <v>136.68100000000001</v>
+        <v>215.98599999999999</v>
       </c>
       <c r="Q50">
-        <v>8.56</v>
+        <v>9.9730000000000008</v>
       </c>
       <c r="R50">
-        <v>8.4517299999999995</v>
+        <v>9.641</v>
       </c>
       <c r="S50">
-        <f t="shared" si="0"/>
-        <v>965.25628287035329</v>
+        <f t="shared" si="2"/>
+        <v>318.17832033985127</v>
       </c>
       <c r="T50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>21</v>
+      <c r="A51" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
       </c>
       <c r="C51">
-        <v>1.4811235</v>
+        <v>14.2767</v>
       </c>
       <c r="D51">
-        <v>3.4619999999999998E-2</v>
+        <v>0.12280000000000001</v>
       </c>
       <c r="E51">
-        <v>1.891</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="F51">
-        <v>2.88</v>
+        <v>0.19</v>
       </c>
       <c r="G51">
-        <v>4050</v>
+        <v>789.15</v>
       </c>
       <c r="H51" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="I51">
-        <v>10170.1</v>
+        <v>5080</v>
       </c>
       <c r="J51">
-        <v>2.3620000000000001</v>
+        <v>2.9430000000000001</v>
       </c>
       <c r="K51">
-        <v>2.52</v>
+        <v>1.212</v>
       </c>
       <c r="L51">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="M51">
-        <v>4.093</v>
+        <v>3.5840000000000001</v>
       </c>
       <c r="N51">
-        <v>307.85989979999999</v>
+        <v>353.03318630000001</v>
       </c>
       <c r="O51">
-        <v>39.9389161</v>
+        <v>-21.801200699999999</v>
       </c>
       <c r="P51">
-        <v>204.45500000000001</v>
+        <v>95.548299999999998</v>
       </c>
       <c r="Q51">
-        <v>7.55</v>
+        <v>8.15</v>
       </c>
       <c r="R51">
-        <v>7.5767499999999997</v>
+        <v>7.9077599999999997</v>
       </c>
       <c r="S51">
-        <f t="shared" si="0"/>
-        <v>1286.8653667451285</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>135</v>
+        <f t="shared" si="2"/>
+        <v>742.8583931109747</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="3"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
         <v>20</v>
       </c>
       <c r="C52">
-        <v>1.7635879999999999</v>
+        <v>5.4435399999999996</v>
       </c>
       <c r="D52">
-        <v>3.6409999999999998E-2</v>
+        <v>6.4100000000000004E-2</v>
       </c>
       <c r="E52">
-        <v>1.512</v>
+        <v>0.63</v>
       </c>
       <c r="F52">
-        <v>9.2799999999999994</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G52">
-        <v>2550</v>
+        <v>1270</v>
+      </c>
+      <c r="H52" t="s">
+        <v>74</v>
       </c>
       <c r="I52">
-        <v>7650</v>
+        <v>6050</v>
       </c>
       <c r="J52">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="K52">
-        <v>1.72</v>
+        <v>1.19</v>
       </c>
       <c r="L52">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="M52">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="N52">
-        <v>286.97138760000001</v>
+        <v>144.87510470000001</v>
       </c>
       <c r="O52">
-        <v>46.868246300000003</v>
-      </c>
-      <c r="P52">
-        <v>519.096</v>
+        <v>-20.982419100000001</v>
+      </c>
+      <c r="P52" s="8">
+        <v>114.173</v>
       </c>
       <c r="Q52">
-        <v>9.7910000000000004</v>
+        <v>9.3510000000000009</v>
       </c>
       <c r="R52">
-        <v>10.367800000000001</v>
+        <v>9.2569999999999997</v>
       </c>
       <c r="S52">
-        <f t="shared" ref="S52:S78" si="2">(0.000000000000000138*G52/(1.673534E-24*1.3*0.000000066726*F52*1.8986E+30/(E52*7149200000)^2))/100000</f>
-        <v>160.76196513632402</v>
+        <f t="shared" si="2"/>
+        <v>1277.1766379712274</v>
       </c>
       <c r="T52">
-        <f t="shared" ref="T52:T78" si="3">IF(I52&gt;6800,-7,-5)</f>
-        <v>-7</v>
+        <f t="shared" si="3"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
         <v>20</v>
       </c>
       <c r="C53">
-        <v>0.79205199999999998</v>
+        <v>4.6336110000000001</v>
       </c>
       <c r="D53">
-        <v>1.6789999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="E53">
-        <v>0.42109020000000003</v>
+        <v>1.37</v>
       </c>
       <c r="F53">
-        <v>9.2250570000000004E-2</v>
+        <v>2.8</v>
       </c>
       <c r="G53">
-        <v>1978</v>
+        <v>1561</v>
       </c>
       <c r="H53" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="I53">
-        <v>5443</v>
+        <v>6643</v>
       </c>
       <c r="J53">
-        <v>0.94899999999999995</v>
+        <v>1.71</v>
       </c>
       <c r="K53">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="L53">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>4.3499999999999996</v>
+        <v>4.05</v>
       </c>
       <c r="N53">
-        <v>358.6688767</v>
+        <v>199.33385029999999</v>
       </c>
       <c r="O53">
-        <v>-37.628223699999999</v>
-      </c>
-      <c r="P53">
-        <v>80.437299999999993</v>
+        <v>-15.2737046</v>
+      </c>
+      <c r="P53" s="8">
+        <v>161.74299999999999</v>
       </c>
       <c r="Q53">
-        <v>9.7899999999999991</v>
+        <v>9.109</v>
       </c>
       <c r="R53">
-        <v>9.6000599999999991</v>
+        <v>8.9943600000000004</v>
       </c>
       <c r="S53">
         <f t="shared" si="2"/>
-        <v>972.96006983022733</v>
+        <v>267.77715667890726</v>
       </c>
       <c r="T53">
         <f t="shared" si="3"/>
@@ -3880,379 +3568,385 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="B54" t="s">
         <v>20</v>
       </c>
       <c r="C54">
-        <v>2.1487738099999998</v>
+        <v>16.067540999999999</v>
       </c>
       <c r="D54">
-        <v>4.0351999999999999E-2</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="E54">
-        <v>1.597</v>
+        <v>0.45410017000000003</v>
       </c>
       <c r="F54">
-        <v>3.7</v>
+        <v>4.4363560000000003E-2</v>
       </c>
       <c r="G54">
-        <v>2594.3000000000002</v>
+        <v>635</v>
       </c>
       <c r="H54" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="I54">
-        <v>7490</v>
+        <v>5291</v>
       </c>
       <c r="J54">
-        <v>2.0819999999999999</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="K54">
-        <v>1.9</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="L54">
-        <v>0.15</v>
+        <v>-4.3999999999999997E-2</v>
       </c>
       <c r="M54">
-        <v>4.1050000000000004</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="N54">
-        <v>317.5515264</v>
+        <v>81.853282399999998</v>
       </c>
       <c r="O54">
-        <v>10.7388967</v>
+        <v>-14.2767404</v>
       </c>
       <c r="P54">
-        <v>182.273</v>
+        <v>74.796899999999994</v>
       </c>
       <c r="Q54">
-        <v>8.2799999999999994</v>
+        <v>9.9309999999999992</v>
       </c>
       <c r="R54">
-        <v>8.2424300000000006</v>
+        <v>9.7777600000000007</v>
       </c>
       <c r="S54">
         <f t="shared" si="2"/>
-        <v>457.63140850776114</v>
+        <v>755.33252275944176</v>
       </c>
       <c r="T54">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>46</v>
+      <c r="A55" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="B55" t="s">
         <v>20</v>
       </c>
       <c r="C55">
-        <v>2.8240932000000001</v>
+        <v>4.73620865</v>
       </c>
       <c r="D55">
-        <v>4.7399999999999998E-2</v>
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="E55">
-        <v>1.5149999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="F55">
-        <v>1.675</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="G55">
-        <v>2250</v>
+        <v>1712</v>
       </c>
       <c r="H55" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I55">
-        <v>7800</v>
+        <v>5375</v>
       </c>
       <c r="J55">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
       <c r="K55">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M55">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="N55">
-        <v>147.5800667</v>
+        <v>161.70690529999999</v>
       </c>
       <c r="O55">
-        <v>-66.113925300000005</v>
-      </c>
-      <c r="P55">
-        <v>170.696</v>
+        <v>-9.3993646000000002</v>
+      </c>
+      <c r="P55" s="8">
+        <v>99.159599999999998</v>
       </c>
       <c r="Q55">
-        <v>8.1910000000000007</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="R55">
-        <v>8.1740100000000009</v>
+        <v>7.8311200000000003</v>
       </c>
       <c r="S55">
         <f t="shared" si="2"/>
-        <v>789.006338593706</v>
+        <v>3894.9775251994533</v>
       </c>
       <c r="T55">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>16.249210000000001</v>
+        <v>5.21536178778</v>
       </c>
       <c r="D56">
-        <v>0.12909999999999999</v>
+        <v>6.6100000000000006E-2</v>
       </c>
       <c r="E56">
-        <v>1.087</v>
+        <v>1.5</v>
       </c>
       <c r="F56">
-        <v>4.34</v>
+        <v>1.51</v>
       </c>
       <c r="G56">
-        <v>805.5</v>
+        <v>1630</v>
       </c>
       <c r="H56" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I56">
-        <v>5756</v>
+        <v>6250</v>
       </c>
       <c r="J56">
-        <v>1.0860000000000001</v>
+        <v>2.3901400000000002</v>
       </c>
       <c r="K56">
-        <v>1.0820000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="L56">
-        <v>0.318</v>
+        <v>-0.18</v>
       </c>
       <c r="M56">
-        <v>4.4020000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="N56">
-        <v>310.29170019999998</v>
+        <v>0.32576100000000002</v>
       </c>
       <c r="O56">
-        <v>3.6382967000000002</v>
-      </c>
-      <c r="P56">
-        <v>93.734499999999997</v>
+        <v>-8.9262511999999994</v>
+      </c>
+      <c r="P56" s="8">
+        <v>275.58699999999999</v>
       </c>
       <c r="Q56">
-        <v>9.48</v>
+        <v>9.9740000000000002</v>
       </c>
       <c r="R56">
-        <v>9.4290710000000004</v>
+        <v>9.8192900000000005</v>
       </c>
       <c r="S56">
         <f t="shared" si="2"/>
-        <v>56.120615203365361</v>
+        <v>621.55661806820979</v>
       </c>
       <c r="T56">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
-      <c r="U56" s="1" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57">
-        <v>8.0277282999999997</v>
+        <v>3.86813881</v>
       </c>
       <c r="D57">
-        <v>8.2337403000000003E-2</v>
+        <v>4.53E-2</v>
       </c>
       <c r="E57">
-        <v>0.83243188000000001</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>0.16200000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="G57">
-        <v>1074.28</v>
+        <v>971</v>
       </c>
       <c r="H57" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="I57">
-        <v>5962.7</v>
+        <v>4792</v>
       </c>
       <c r="J57">
-        <v>1.1499999999999999</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="K57">
-        <v>1.156039</v>
+        <v>0.83</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="M57">
-        <v>4.38</v>
+        <v>4.57</v>
       </c>
       <c r="N57">
-        <v>193.3963704</v>
+        <v>315.02596610000001</v>
       </c>
       <c r="O57">
-        <v>85.129495199999994</v>
+        <v>-5.0948570000000002</v>
       </c>
       <c r="P57">
-        <v>114.048</v>
+        <v>49.960500000000003</v>
       </c>
       <c r="Q57">
-        <v>9.5399999999999991</v>
+        <v>9.8729999999999993</v>
       </c>
       <c r="R57">
-        <v>9.4135299999999997</v>
+        <v>9.4846599999999999</v>
       </c>
       <c r="S57">
         <f t="shared" si="2"/>
-        <v>1175.9460676296278</v>
+        <v>955.72600175951948</v>
       </c>
       <c r="T57">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
+      <c r="U57" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
         <v>20</v>
       </c>
       <c r="C58">
-        <v>12.5199</v>
+        <v>2.7240329999999999</v>
       </c>
       <c r="D58">
-        <v>0.1062</v>
+        <v>5.0529999999999999E-2</v>
       </c>
       <c r="E58">
-        <v>0.41279399999999999</v>
+        <v>1.619</v>
       </c>
       <c r="F58">
-        <v>2.627204E-2</v>
+        <v>1.99</v>
       </c>
       <c r="G58">
-        <v>843</v>
+        <v>3353</v>
       </c>
       <c r="I58">
-        <v>5770</v>
+        <v>8000</v>
       </c>
       <c r="J58">
-        <v>0.96799999999999997</v>
+        <v>2.36</v>
       </c>
       <c r="K58">
-        <v>1.022</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="L58">
-        <v>7.0000000000000007E-2</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M58">
-        <v>4.47</v>
+        <v>3.9</v>
       </c>
       <c r="N58">
-        <v>192.1848981</v>
+        <v>225.68673200000001</v>
       </c>
       <c r="O58">
-        <v>64.855275500000005</v>
-      </c>
-      <c r="P58">
-        <v>84.536199999999994</v>
+        <v>-3.0314874000000001</v>
+      </c>
+      <c r="P58" s="8">
+        <v>99.730999999999995</v>
       </c>
       <c r="Q58">
-        <v>9.5340000000000007</v>
+        <v>6.5977600000000001</v>
       </c>
       <c r="R58">
-        <v>9.3678899999999992</v>
-      </c>
-      <c r="S58">
+        <v>6.5536899999999996</v>
+      </c>
+      <c r="S58" s="5">
         <f t="shared" si="2"/>
-        <v>1399.2265914107247</v>
+        <v>1130.2166328238993</v>
       </c>
       <c r="T58">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B59" t="s">
         <v>20</v>
       </c>
       <c r="C59">
-        <v>4.7202190000000002</v>
+        <v>2.13775</v>
       </c>
       <c r="D59">
-        <v>6.2600000000000003E-2</v>
+        <v>3.4430000000000002E-2</v>
       </c>
       <c r="E59">
-        <v>1.3959999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F59">
-        <v>2.37</v>
+        <v>0.72</v>
       </c>
       <c r="G59">
-        <v>1679</v>
+        <v>1865</v>
+      </c>
+      <c r="H59" t="s">
+        <v>91</v>
       </c>
       <c r="I59">
-        <v>6274</v>
+        <v>5990</v>
       </c>
       <c r="J59">
-        <v>1.925</v>
+        <v>1.42</v>
       </c>
       <c r="K59">
-        <v>1.464</v>
+        <v>0.98</v>
       </c>
       <c r="L59">
-        <v>0.11899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="M59">
-        <v>4.0339999999999998</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="N59">
-        <v>325.01453629999997</v>
+        <v>304.53884299999999</v>
       </c>
       <c r="O59">
-        <v>48.4067674</v>
-      </c>
-      <c r="P59">
-        <v>200.49199999999999</v>
+        <v>-1.0760033</v>
+      </c>
+      <c r="P59" s="8">
+        <v>149.21600000000001</v>
       </c>
       <c r="Q59">
-        <v>9.4380000000000006</v>
+        <v>9.75</v>
       </c>
       <c r="R59">
-        <v>9.3503900000000009</v>
+        <v>9.5723000000000003</v>
       </c>
       <c r="S59">
         <f t="shared" si="2"/>
-        <v>353.31388599481477</v>
+        <v>1226.0598654781754</v>
       </c>
       <c r="T59">
         <f t="shared" si="3"/>
@@ -4261,62 +3955,62 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="B60" t="s">
         <v>20</v>
       </c>
       <c r="C60">
-        <v>4.4258699999999997</v>
+        <v>2.7057899999999999</v>
       </c>
       <c r="D60">
-        <v>5.7779999999999998E-2</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="E60">
-        <v>2.2303544500000001</v>
+        <v>1.62</v>
       </c>
       <c r="F60">
-        <v>1.86578665</v>
+        <v>1.17</v>
       </c>
       <c r="G60">
-        <v>1293</v>
+        <v>2190</v>
       </c>
       <c r="H60" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="I60">
-        <v>6117</v>
+        <v>6480</v>
       </c>
       <c r="J60">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="K60">
-        <v>1.3120000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="L60">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="M60">
-        <v>4.0999999999999996</v>
+        <v>3.96</v>
       </c>
       <c r="N60">
-        <v>313.5110469</v>
+        <v>72.660591600000004</v>
       </c>
       <c r="O60">
-        <v>72.580645500000003</v>
-      </c>
-      <c r="P60">
-        <v>139.48400000000001</v>
+        <v>1.8938364999999999</v>
+      </c>
+      <c r="P60" s="8">
+        <v>275.66399999999999</v>
       </c>
       <c r="Q60">
-        <v>9.2700010000000006</v>
+        <v>10.073</v>
       </c>
       <c r="R60">
-        <v>9.1879500000000007</v>
+        <v>9.8979599999999994</v>
       </c>
       <c r="S60">
         <f t="shared" si="2"/>
-        <v>882.20971786077962</v>
+        <v>1257.117296864338</v>
       </c>
       <c r="T60">
         <f t="shared" si="3"/>
@@ -4325,495 +4019,504 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
         <v>20</v>
       </c>
       <c r="C61">
-        <v>2.6502370000000002</v>
+        <v>1.8098819799999999</v>
       </c>
       <c r="D61">
-        <v>4.5999999999999999E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="E61">
-        <v>1.49</v>
+        <v>1.8540000000000001</v>
       </c>
       <c r="F61">
-        <v>3.12</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G61">
-        <v>2370</v>
+        <v>2228</v>
       </c>
       <c r="H61" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I61">
-        <v>7690</v>
+        <v>6329</v>
       </c>
       <c r="J61">
-        <v>1.92</v>
+        <v>1.756</v>
       </c>
       <c r="K61">
-        <v>1.9</v>
+        <v>1.458</v>
       </c>
       <c r="L61">
-        <v>0.09</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M61">
-        <v>4.1500000000000004</v>
+        <v>4.1959999999999997</v>
       </c>
       <c r="N61">
-        <v>316.20369219999998</v>
+        <v>26.632936000000001</v>
       </c>
       <c r="O61">
-        <v>55.588022100000003</v>
-      </c>
-      <c r="P61">
-        <v>148.92500000000001</v>
+        <v>2.7003889999999999</v>
+      </c>
+      <c r="P61" s="8">
+        <v>194.459</v>
       </c>
       <c r="Q61">
-        <v>8.0299999999999994</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="R61">
-        <v>7.9756099999999996</v>
+        <v>9.3950700000000005</v>
       </c>
       <c r="S61">
         <f t="shared" si="2"/>
-        <v>431.57254486096394</v>
+        <v>2192.2225820487197</v>
       </c>
       <c r="T61">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
       <c r="C62">
-        <v>1.902603</v>
+        <v>16.249210000000001</v>
       </c>
       <c r="D62">
-        <v>3.8899999999999997E-2</v>
+        <v>0.12909999999999999</v>
       </c>
       <c r="E62">
-        <v>1.875</v>
+        <v>1.087</v>
       </c>
       <c r="F62">
-        <v>2.2999999999999998</v>
+        <v>4.34</v>
       </c>
       <c r="G62">
-        <v>2492</v>
+        <v>805.5</v>
       </c>
       <c r="H62" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="I62">
-        <v>7300</v>
+        <v>5756</v>
       </c>
       <c r="J62">
-        <v>1.95</v>
+        <v>1.0860000000000001</v>
       </c>
       <c r="K62">
-        <v>1.79</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="L62">
-        <v>-0.1</v>
+        <v>0.318</v>
       </c>
       <c r="M62">
-        <v>4.0999999999999996</v>
+        <v>4.4020000000000001</v>
       </c>
       <c r="N62">
-        <v>352.26752069999998</v>
+        <v>310.29170019999998</v>
       </c>
       <c r="O62">
-        <v>67.034806200000006</v>
-      </c>
-      <c r="P62">
-        <v>225.88800000000001</v>
+        <v>3.6382967000000002</v>
+      </c>
+      <c r="P62" s="8">
+        <v>93.734499999999997</v>
       </c>
       <c r="Q62">
-        <v>8.952</v>
+        <v>9.48</v>
       </c>
       <c r="R62">
-        <v>8.8952899999999993</v>
+        <v>9.4290710000000004</v>
       </c>
       <c r="S62">
         <f t="shared" si="2"/>
-        <v>974.78820571370204</v>
+        <v>56.120615203365361</v>
       </c>
       <c r="T62">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
       </c>
       <c r="C63">
-        <v>3.2086640000000002</v>
+        <v>4.7869491000000002</v>
       </c>
       <c r="D63">
-        <v>4.8820000000000002E-2</v>
+        <v>6.5549999999999997E-2</v>
       </c>
       <c r="E63">
-        <v>1.44</v>
+        <v>1.6759999999999999</v>
       </c>
       <c r="F63">
-        <v>0.7</v>
+        <v>3.58</v>
       </c>
       <c r="G63">
-        <v>1927</v>
-      </c>
-      <c r="H63" t="s">
-        <v>56</v>
+        <v>1930</v>
       </c>
       <c r="I63">
-        <v>5991</v>
+        <v>7394</v>
       </c>
       <c r="J63">
-        <v>2.1680000000000001</v>
+        <v>1.9259999999999999</v>
       </c>
       <c r="K63">
-        <v>1.5069999999999999</v>
+        <v>1.6479999999999999</v>
       </c>
       <c r="L63">
-        <v>0.373</v>
+        <v>-6.9000000000000006E-2</v>
       </c>
       <c r="M63">
-        <v>3.9430000000000001</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="N63">
-        <v>142.74340599999999</v>
+        <v>130.5056385</v>
       </c>
       <c r="O63">
-        <v>26.539995099999999</v>
-      </c>
-      <c r="P63">
-        <v>229.06700000000001</v>
+        <v>3.7105662000000001</v>
+      </c>
+      <c r="P63" s="8">
+        <v>341.26299999999998</v>
       </c>
       <c r="Q63">
-        <v>9.7210000000000001</v>
+        <v>9.7739999999999991</v>
       </c>
       <c r="R63">
-        <v>9.5843900000000009</v>
+        <v>9.77332</v>
       </c>
       <c r="S63">
         <f t="shared" si="2"/>
-        <v>1460.8182255852041</v>
+        <v>387.53401759458865</v>
       </c>
       <c r="T63">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>102</v>
+      <c r="A64" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="B64" t="s">
         <v>20</v>
       </c>
       <c r="C64">
-        <v>9.5739181000000002</v>
+        <v>4.6117093000000002</v>
       </c>
       <c r="D64">
-        <v>0.1</v>
+        <v>6.3700000000000007E-2</v>
       </c>
       <c r="E64">
-        <v>1.10166148</v>
+        <v>1.91</v>
       </c>
       <c r="F64">
-        <v>0.28128386</v>
+        <v>4.07</v>
       </c>
       <c r="G64">
-        <v>1199.55</v>
+        <v>1935</v>
+      </c>
+      <c r="H64" t="s">
+        <v>109</v>
       </c>
       <c r="I64">
-        <v>6039</v>
+        <v>7500</v>
       </c>
       <c r="J64">
-        <v>2.032</v>
+        <v>1.83</v>
       </c>
       <c r="K64">
-        <v>1.4642999999999999</v>
+        <v>1.62</v>
       </c>
       <c r="L64">
-        <v>0.33200000000000002</v>
+        <v>-0.12</v>
       </c>
       <c r="M64">
-        <v>3.9860000000000002</v>
+        <v>4.1269999999999998</v>
       </c>
       <c r="N64">
-        <v>201.9626552</v>
+        <v>111.5095293</v>
       </c>
       <c r="O64">
-        <v>9.0306437000000006</v>
-      </c>
-      <c r="P64">
-        <v>223.465</v>
+        <v>7.6157759</v>
+      </c>
+      <c r="P64" s="8">
+        <v>300.27600000000001</v>
       </c>
       <c r="Q64">
-        <v>9.8149999999999995</v>
+        <v>9.8569999999999993</v>
       </c>
       <c r="R64">
-        <v>9.6598100000000002</v>
+        <v>9.8633100000000002</v>
       </c>
       <c r="S64">
         <f t="shared" si="2"/>
-        <v>1324.5165539963698</v>
+        <v>443.85469120292152</v>
       </c>
       <c r="T64">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
       <c r="C65">
-        <v>17.305904000000002</v>
+        <v>9.5739181000000002</v>
       </c>
       <c r="D65">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E65">
-        <v>1.07</v>
+        <v>1.10166148</v>
       </c>
       <c r="F65">
-        <v>6.4</v>
+        <v>0.28128386</v>
       </c>
       <c r="G65">
-        <v>1221.3900000000001</v>
+        <v>1199.55</v>
       </c>
       <c r="I65">
-        <v>7130</v>
+        <v>6039</v>
       </c>
       <c r="J65">
-        <v>2.02</v>
+        <v>2.032</v>
       </c>
       <c r="K65">
-        <v>1.59</v>
+        <v>1.4642999999999999</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M65">
-        <v>3.9460000000000002</v>
+        <v>3.9860000000000002</v>
       </c>
       <c r="N65">
-        <v>164.031654</v>
+        <v>201.9626552</v>
       </c>
       <c r="O65">
-        <v>-43.376696699999997</v>
-      </c>
-      <c r="P65">
-        <v>328.47500000000002</v>
+        <v>9.0306437000000006</v>
+      </c>
+      <c r="P65" s="8">
+        <v>223.465</v>
       </c>
       <c r="Q65">
-        <v>9.8670000000000009</v>
+        <v>9.8149999999999995</v>
       </c>
       <c r="R65">
-        <v>9.7596699999999998</v>
+        <v>9.6598100000000002</v>
       </c>
       <c r="S65">
         <f t="shared" si="2"/>
-        <v>55.915145726222889</v>
+        <v>1324.5165539963698</v>
       </c>
       <c r="T65">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
       </c>
       <c r="C66">
-        <v>10.261127</v>
+        <v>2.7443245200000002</v>
       </c>
       <c r="D66">
-        <v>0.111</v>
+        <v>4.7390000000000002E-2</v>
       </c>
       <c r="E66">
-        <v>1.1079506100000001</v>
+        <v>1.87</v>
       </c>
       <c r="F66">
-        <v>5.55960374</v>
+        <v>6.78</v>
       </c>
       <c r="G66">
-        <v>1363.43</v>
+        <v>2562</v>
       </c>
       <c r="I66">
-        <v>6200</v>
+        <v>8450</v>
       </c>
       <c r="J66">
-        <v>2.7505000000000002</v>
+        <v>1.8580000000000001</v>
       </c>
       <c r="K66">
-        <v>1.7169000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="L66">
-        <v>0.28499999999999998</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="M66">
-        <v>3.7890000000000001</v>
+        <v>4.181</v>
       </c>
       <c r="N66">
-        <v>263.75807529999997</v>
+        <v>74.552333200000007</v>
       </c>
       <c r="O66">
-        <v>40.695042800000003</v>
-      </c>
-      <c r="P66">
-        <v>224.73099999999999</v>
+        <v>9.9979794000000002</v>
+      </c>
+      <c r="P66" s="8">
+        <v>330.73899999999998</v>
       </c>
       <c r="Q66">
-        <v>9.07</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="R66">
-        <v>8.9365100000000002</v>
+        <v>9.4517399999999991</v>
       </c>
       <c r="S66">
         <f t="shared" si="2"/>
-        <v>77.040187113891676</v>
+        <v>338.15838787809196</v>
       </c>
       <c r="T66">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
         <v>20</v>
       </c>
       <c r="C67">
-        <v>10.655669</v>
+        <v>6.87188</v>
       </c>
       <c r="D67">
-        <v>0.1166</v>
+        <v>7.5219999999999995E-2</v>
       </c>
       <c r="E67">
-        <v>0.99399999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="F67">
-        <v>4.82</v>
+        <v>3.44</v>
       </c>
       <c r="G67">
-        <v>1595</v>
+        <v>1250</v>
+      </c>
+      <c r="H67" t="s">
+        <v>70</v>
       </c>
       <c r="I67">
-        <v>7360</v>
+        <v>6180</v>
       </c>
       <c r="J67">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="K67">
-        <v>1.859</v>
+        <v>1.76</v>
       </c>
       <c r="L67">
-        <v>9.4E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="M67">
-        <v>3.9620000000000002</v>
+        <v>4.25</v>
       </c>
       <c r="N67">
-        <v>90.062587800000003</v>
+        <v>243.95971940000001</v>
       </c>
       <c r="O67">
-        <v>11.8840577</v>
-      </c>
-      <c r="P67">
-        <v>285.28899999999999</v>
+        <v>10.0324103</v>
+      </c>
+      <c r="P67" s="8">
+        <v>136.24</v>
       </c>
       <c r="Q67">
-        <v>9.5470000000000006</v>
+        <v>9.391</v>
       </c>
       <c r="R67">
-        <v>9.4724400000000006</v>
+        <v>9.20974</v>
       </c>
       <c r="S67">
         <f t="shared" si="2"/>
-        <v>83.670803141549356</v>
+        <v>140.68549179703928</v>
       </c>
       <c r="T67">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>22</v>
+      <c r="A68" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="B68" t="s">
         <v>20</v>
       </c>
       <c r="C68">
-        <v>18.388179999999998</v>
+        <v>11.814299999999999</v>
       </c>
       <c r="D68">
-        <v>0.15279999999999999</v>
+        <v>0.1066</v>
       </c>
       <c r="E68">
-        <v>0.63900000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="F68">
-        <v>0.13800000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="G68">
-        <v>1027</v>
+        <v>1089</v>
+      </c>
+      <c r="H68" t="s">
+        <v>33</v>
       </c>
       <c r="I68">
-        <v>6095</v>
+        <v>5576</v>
       </c>
       <c r="J68">
-        <v>1.867</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="K68">
-        <v>1.407</v>
+        <v>1.157</v>
       </c>
       <c r="L68">
-        <v>0.17499999999999999</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="M68">
-        <v>4.0439999999999996</v>
+        <v>4.016</v>
       </c>
       <c r="N68">
-        <v>47.517260800000003</v>
+        <v>154.67109769999999</v>
       </c>
       <c r="O68">
-        <v>-50.8322632</v>
-      </c>
-      <c r="P68">
-        <v>76.902799999999999</v>
+        <v>10.1288464</v>
+      </c>
+      <c r="P68" s="8">
+        <v>132.345</v>
       </c>
       <c r="Q68">
-        <v>7.57</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="R68">
-        <v>7.4165299999999998</v>
+        <v>9.2170199999999998</v>
       </c>
       <c r="S68">
         <f t="shared" si="2"/>
-        <v>777.64358420307099</v>
+        <v>1103.5971886171305</v>
       </c>
       <c r="T68">
         <f t="shared" si="3"/>
@@ -4822,123 +4525,123 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
         <v>20</v>
       </c>
       <c r="C69">
-        <v>16.067540999999999</v>
+        <v>2.1487738099999998</v>
       </c>
       <c r="D69">
-        <v>0.11700000000000001</v>
+        <v>4.0351999999999999E-2</v>
       </c>
       <c r="E69">
-        <v>0.45410017000000003</v>
+        <v>1.597</v>
       </c>
       <c r="F69">
-        <v>4.4363560000000003E-2</v>
+        <v>3.7</v>
       </c>
       <c r="G69">
-        <v>635</v>
+        <v>2594.3000000000002</v>
       </c>
       <c r="H69" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="I69">
-        <v>5291</v>
+        <v>7490</v>
       </c>
       <c r="J69">
-        <v>0.86599999999999999</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="K69">
-        <v>0.83299999999999996</v>
+        <v>1.9</v>
       </c>
       <c r="L69">
-        <v>-4.3999999999999997E-2</v>
+        <v>0.15</v>
       </c>
       <c r="M69">
-        <v>4.4800000000000004</v>
+        <v>4.1050000000000004</v>
       </c>
       <c r="N69">
-        <v>81.853282399999998</v>
+        <v>317.5515264</v>
       </c>
       <c r="O69">
-        <v>-14.2767404</v>
-      </c>
-      <c r="P69">
-        <v>74.796899999999994</v>
+        <v>10.7388967</v>
+      </c>
+      <c r="P69" s="8">
+        <v>182.273</v>
       </c>
       <c r="Q69">
-        <v>9.9309999999999992</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="R69">
-        <v>9.7777600000000007</v>
+        <v>8.2424300000000006</v>
       </c>
       <c r="S69">
         <f t="shared" si="2"/>
-        <v>755.33252275944176</v>
+        <v>457.63140850776114</v>
       </c>
       <c r="T69">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>119</v>
+      <c r="A70" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
       </c>
       <c r="C70">
-        <v>9.9558099999999996</v>
+        <v>6.7535809999999996</v>
       </c>
       <c r="D70">
-        <v>9.9400000000000002E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E70">
-        <v>1.0580000000000001</v>
+        <v>0.58881357999999995</v>
       </c>
       <c r="F70">
-        <v>1.49</v>
+        <v>0.10068326</v>
       </c>
       <c r="G70">
-        <v>1655</v>
+        <v>1180</v>
       </c>
       <c r="I70">
-        <v>4896</v>
+        <v>5808</v>
       </c>
       <c r="J70">
-        <v>3.55</v>
+        <v>1.29</v>
       </c>
       <c r="K70">
-        <v>1.31</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L70">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="M70">
-        <v>3.48</v>
+        <v>4.26</v>
       </c>
       <c r="N70">
-        <v>184.97875790000001</v>
+        <v>166.26950410000001</v>
       </c>
       <c r="O70">
-        <v>-25.827853099999999</v>
-      </c>
-      <c r="P70">
-        <v>215.98599999999999</v>
+        <v>11.2464069</v>
+      </c>
+      <c r="P70" s="8">
+        <v>130.91900000000001</v>
       </c>
       <c r="Q70">
-        <v>9.9730000000000008</v>
+        <v>9.75</v>
       </c>
       <c r="R70">
-        <v>9.641</v>
+        <v>9.6080000000000005</v>
       </c>
       <c r="S70">
         <f t="shared" si="2"/>
-        <v>318.17832033985127</v>
+        <v>1039.84328949877</v>
       </c>
       <c r="T70">
         <f t="shared" si="3"/>
@@ -4947,187 +4650,187 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B71" t="s">
         <v>20</v>
       </c>
       <c r="C71">
-        <v>7.2459899999999999</v>
+        <v>10.655669</v>
       </c>
       <c r="D71">
-        <v>8.8800000000000004E-2</v>
+        <v>0.1166</v>
       </c>
       <c r="E71">
-        <v>1.042</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F71">
-        <v>12.89</v>
+        <v>4.82</v>
       </c>
       <c r="G71">
-        <v>1677</v>
-      </c>
-      <c r="H71" t="s">
-        <v>56</v>
+        <v>1595</v>
       </c>
       <c r="I71">
-        <v>6264</v>
+        <v>7360</v>
       </c>
       <c r="J71">
-        <v>2.738</v>
+        <v>2.36</v>
       </c>
       <c r="K71">
-        <v>1.7649999999999999</v>
+        <v>1.859</v>
       </c>
       <c r="L71">
-        <v>0.34200000000000003</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M71">
-        <v>3.81</v>
+        <v>3.9620000000000002</v>
       </c>
       <c r="N71">
-        <v>83.865928800000006</v>
+        <v>90.062587800000003</v>
       </c>
       <c r="O71">
-        <v>21.294241700000001</v>
-      </c>
-      <c r="P71">
-        <v>225.643</v>
+        <v>11.8840577</v>
+      </c>
+      <c r="P71" s="8">
+        <v>285.28899999999999</v>
       </c>
       <c r="Q71">
-        <v>9.24</v>
+        <v>9.5470000000000006</v>
       </c>
       <c r="R71">
-        <v>9.0746900000000004</v>
+        <v>9.4724400000000006</v>
       </c>
       <c r="S71">
         <f t="shared" si="2"/>
-        <v>36.149567272802649</v>
+        <v>83.670803141549356</v>
       </c>
       <c r="T71">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s">
         <v>20</v>
       </c>
       <c r="C72">
-        <v>10.331110000000001</v>
+        <v>3.0801715999999999</v>
       </c>
       <c r="D72">
-        <v>9.7000000000000003E-2</v>
+        <v>4.8809999999999999E-2</v>
       </c>
       <c r="E72">
-        <v>0.99</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F72">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="G72">
-        <v>1370</v>
+        <v>2087</v>
       </c>
       <c r="H72" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="I72">
-        <v>5735</v>
+        <v>7454</v>
       </c>
       <c r="J72">
-        <v>1.66</v>
+        <v>1.645</v>
       </c>
       <c r="K72">
-        <v>1.1399999999999999</v>
+        <v>1.635</v>
       </c>
       <c r="L72">
-        <v>0.26</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="M72">
-        <v>4.0599999999999996</v>
+        <v>4.22</v>
       </c>
       <c r="N72">
-        <v>110.5126861</v>
+        <v>125.617407</v>
       </c>
       <c r="O72">
-        <v>-57.384998000000003</v>
-      </c>
-      <c r="P72">
-        <v>179.36600000000001</v>
+        <v>13.735309300000001</v>
+      </c>
+      <c r="P72" s="8">
+        <v>226.5</v>
       </c>
       <c r="Q72">
-        <v>9.9719999999999995</v>
+        <v>9.234</v>
       </c>
       <c r="R72">
-        <v>9.8465900000000008</v>
+        <v>9.2088699999999992</v>
       </c>
       <c r="S72">
         <f t="shared" si="2"/>
-        <v>224.58825733889913</v>
+        <v>948.15286253702118</v>
       </c>
       <c r="T72">
         <f t="shared" si="3"/>
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C73">
-        <v>6.7535809999999996</v>
+        <v>3.4148839999999998</v>
       </c>
       <c r="D73">
-        <v>7.2999999999999995E-2</v>
+        <v>4.7899999999999998E-2</v>
       </c>
       <c r="E73">
-        <v>0.58881357999999995</v>
+        <v>1.23</v>
       </c>
       <c r="F73">
-        <v>0.10068326</v>
+        <v>1.02</v>
       </c>
       <c r="G73">
-        <v>1180</v>
+        <v>1762</v>
+      </c>
+      <c r="H73" t="s">
+        <v>33</v>
       </c>
       <c r="I73">
-        <v>5808</v>
+        <v>5392</v>
       </c>
       <c r="J73">
-        <v>1.29</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K73">
-        <v>1.1000000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="L73">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="M73">
-        <v>4.26</v>
+        <v>3.88</v>
       </c>
       <c r="N73">
-        <v>166.26950410000001</v>
+        <v>152.53193490000001</v>
       </c>
       <c r="O73">
-        <v>11.2464069</v>
+        <v>18.185728399999999</v>
       </c>
       <c r="P73">
-        <v>130.91900000000001</v>
+        <v>73.612300000000005</v>
       </c>
       <c r="Q73">
-        <v>9.75</v>
+        <v>8.0185200000000005</v>
       </c>
       <c r="R73">
-        <v>9.6080000000000005</v>
+        <v>7.8097899999999996</v>
       </c>
       <c r="S73">
         <f t="shared" si="2"/>
-        <v>1039.84328949877</v>
+        <v>668.81110409377118</v>
       </c>
       <c r="T73">
         <f t="shared" si="3"/>
@@ -5136,62 +4839,59 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B74" t="s">
         <v>20</v>
       </c>
       <c r="C74">
-        <v>10.590547000000001</v>
+        <v>11.168454000000001</v>
       </c>
       <c r="D74">
-        <v>9.8000000000000004E-2</v>
+        <v>0.10356</v>
       </c>
       <c r="E74">
-        <v>0.91890603000000004</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>0.18469084999999999</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="G74">
-        <v>947</v>
-      </c>
-      <c r="H74" t="s">
-        <v>128</v>
+        <v>1030</v>
       </c>
       <c r="I74">
-        <v>6000</v>
+        <v>6154</v>
       </c>
       <c r="J74">
-        <v>1.0509999999999999</v>
+        <v>1.161</v>
       </c>
       <c r="K74">
-        <v>1.1459999999999999</v>
+        <v>1.1879999999999999</v>
       </c>
       <c r="L74">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="M74">
-        <v>4.4400000000000004</v>
+        <v>4.3789999999999996</v>
       </c>
       <c r="N74">
-        <v>161.87955690000001</v>
+        <v>73.766792699999996</v>
       </c>
       <c r="O74">
-        <v>36.329434499999998</v>
-      </c>
-      <c r="P74">
-        <v>130.85499999999999</v>
+        <v>18.654323000000002</v>
+      </c>
+      <c r="P74" s="8">
+        <v>130.72</v>
       </c>
       <c r="Q74">
-        <v>10.058999999999999</v>
+        <v>9.8219999999999992</v>
       </c>
       <c r="R74">
-        <v>9.9823299999999993</v>
+        <v>9.7262599999999999</v>
       </c>
       <c r="S74">
         <f t="shared" si="2"/>
-        <v>1107.9861243219782</v>
+        <v>662.28004924519439</v>
       </c>
       <c r="T74">
         <f t="shared" si="3"/>
@@ -5199,60 +4899,63 @@
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>172</v>
+      <c r="A75" t="s">
+        <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C75">
-        <v>5.8267310999999999</v>
+        <v>3.5247485900000002</v>
       </c>
       <c r="D75">
-        <v>6.9000000000000006E-2</v>
+        <v>4.7070000000000001E-2</v>
       </c>
       <c r="E75">
-        <v>0.57186287999999996</v>
+        <v>1.39</v>
       </c>
       <c r="F75">
-        <v>0.24698861999999999</v>
+        <v>0.73</v>
       </c>
       <c r="G75">
-        <v>1439</v>
+        <v>1459</v>
+      </c>
+      <c r="H75" t="s">
+        <v>27</v>
       </c>
       <c r="I75">
-        <v>6110</v>
+        <v>6091</v>
       </c>
       <c r="J75">
-        <v>1.6479999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="K75">
-        <v>1.2909999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="L75">
-        <v>0.124</v>
+        <v>0.01</v>
       </c>
       <c r="M75">
-        <v>4.1180000000000003</v>
+        <v>4.45</v>
       </c>
       <c r="N75">
-        <v>51.657269100000001</v>
+        <v>330.79502189999999</v>
       </c>
       <c r="O75">
-        <v>40.817270399999998</v>
+        <v>18.884241899999999</v>
       </c>
       <c r="P75">
-        <v>179.14699999999999</v>
+        <v>48.301600000000001</v>
       </c>
       <c r="Q75">
-        <v>9.9130000000000003</v>
+        <v>7.65</v>
       </c>
       <c r="R75">
-        <v>9.7295700000000007</v>
+        <v>7.5086599999999999</v>
       </c>
       <c r="S75">
         <f t="shared" si="2"/>
-        <v>487.59044264912109</v>
+        <v>988.21070019970352</v>
       </c>
       <c r="T75">
         <f t="shared" si="3"/>
@@ -5260,63 +4963,63 @@
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>62</v>
+      <c r="A76" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B76" t="s">
         <v>20</v>
       </c>
       <c r="C76">
-        <v>6.4025129999999999</v>
+        <v>19.502103999999999</v>
       </c>
       <c r="D76">
-        <v>7.0800000000000002E-2</v>
+        <v>0.1482</v>
       </c>
       <c r="E76">
-        <v>0.82399999999999995</v>
+        <v>0.52993221999999995</v>
       </c>
       <c r="F76">
-        <v>0.30299999999999999</v>
+        <v>3.0425219999999999E-2</v>
       </c>
       <c r="G76">
-        <v>1388</v>
+        <v>253.08</v>
       </c>
       <c r="H76" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I76">
-        <v>6400</v>
+        <v>6310</v>
       </c>
       <c r="J76">
-        <v>1.415</v>
+        <v>1.43</v>
       </c>
       <c r="K76">
-        <v>1.3129999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="L76">
-        <v>0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="M76">
-        <v>4.2</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N76">
-        <v>125.3050544</v>
+        <v>253.78488530000001</v>
       </c>
       <c r="O76">
-        <v>-46.484295899999999</v>
-      </c>
-      <c r="P76">
-        <v>123.297</v>
+        <v>20.491523999999998</v>
+      </c>
+      <c r="P76" s="8">
+        <v>107.898</v>
       </c>
       <c r="Q76">
-        <v>8.9949999999999992</v>
+        <v>8.8550000000000004</v>
       </c>
       <c r="R76">
-        <v>8.8910300000000007</v>
+        <v>8.7641200000000001</v>
       </c>
       <c r="S76">
         <f t="shared" si="2"/>
-        <v>795.95548671567838</v>
+        <v>597.79498778467087</v>
       </c>
       <c r="T76">
         <f t="shared" si="3"/>
@@ -5325,62 +5028,62 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="B77" t="s">
         <v>20</v>
       </c>
       <c r="C77">
-        <v>11.236598499999999</v>
+        <v>7.2459899999999999</v>
       </c>
       <c r="D77">
-        <v>0.1041</v>
+        <v>8.8800000000000004E-2</v>
       </c>
       <c r="E77">
-        <v>1.17</v>
+        <v>1.042</v>
       </c>
       <c r="F77">
-        <v>1.234</v>
+        <v>12.89</v>
       </c>
       <c r="G77">
-        <v>1252</v>
+        <v>1677</v>
       </c>
       <c r="H77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I77">
-        <v>6295</v>
+        <v>6264</v>
       </c>
       <c r="J77">
-        <v>1.28</v>
+        <v>2.738</v>
       </c>
       <c r="K77">
-        <v>1.181</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="M77">
-        <v>4.2910000000000004</v>
+        <v>3.81</v>
       </c>
       <c r="N77">
-        <v>144.11935940000001</v>
+        <v>83.865928800000006</v>
       </c>
       <c r="O77">
-        <v>-50.463093299999997</v>
-      </c>
-      <c r="P77">
-        <v>141.81200000000001</v>
+        <v>21.294241700000001</v>
+      </c>
+      <c r="P77" s="8">
+        <v>225.643</v>
       </c>
       <c r="Q77">
-        <v>9.8219999999999992</v>
+        <v>9.24</v>
       </c>
       <c r="R77">
-        <v>9.6608199999999993</v>
+        <v>9.0746900000000004</v>
       </c>
       <c r="S77">
         <f t="shared" si="2"/>
-        <v>355.42536038318485</v>
+        <v>36.149567272802649</v>
       </c>
       <c r="T77">
         <f t="shared" si="3"/>
@@ -5389,62 +5092,59 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B78" t="s">
         <v>20</v>
       </c>
       <c r="C78">
-        <v>4.6336110000000001</v>
+        <v>2.2437499999999999</v>
       </c>
       <c r="D78">
-        <v>0.06</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E78">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="F78">
-        <v>2.8</v>
+        <v>8.84</v>
       </c>
       <c r="G78">
-        <v>1561</v>
-      </c>
-      <c r="H78" t="s">
-        <v>66</v>
+        <v>1872</v>
       </c>
       <c r="I78">
-        <v>6643</v>
+        <v>6475</v>
       </c>
       <c r="J78">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="K78">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="N78">
-        <v>199.33385029999999</v>
+        <v>218.27662470000001</v>
       </c>
       <c r="O78">
-        <v>-15.2737046</v>
-      </c>
-      <c r="P78">
-        <v>161.74299999999999</v>
+        <v>21.8946875</v>
+      </c>
+      <c r="P78" s="8">
+        <v>161.99700000000001</v>
       </c>
       <c r="Q78">
-        <v>9.109</v>
+        <v>9.7449999999999992</v>
       </c>
       <c r="R78">
-        <v>8.9943600000000004</v>
+        <v>9.6464700000000008</v>
       </c>
       <c r="S78">
         <f t="shared" si="2"/>
-        <v>267.77715667890726</v>
+        <v>103.20465157174387</v>
       </c>
       <c r="T78">
         <f t="shared" si="3"/>
@@ -5453,1607 +5153,1922 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="C79">
+        <v>2.2185756699999999</v>
+      </c>
+      <c r="D79">
+        <v>3.1260000000000003E-2</v>
+      </c>
+      <c r="E79">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F79">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G79">
+        <v>1209</v>
+      </c>
+      <c r="H79" t="s">
+        <v>29</v>
       </c>
       <c r="I79">
-        <v>6200</v>
+        <v>5052</v>
       </c>
       <c r="J79">
-        <v>1.2</v>
+        <v>0.75</v>
+      </c>
+      <c r="K79">
+        <v>0.79</v>
+      </c>
+      <c r="L79">
+        <v>-0.02</v>
+      </c>
+      <c r="M79">
+        <v>4.49</v>
       </c>
       <c r="N79">
-        <v>97.636728000000005</v>
+        <v>300.1821223</v>
       </c>
       <c r="O79">
-        <v>29.672419000000001</v>
+        <v>22.7097759</v>
       </c>
       <c r="P79">
-        <v>427</v>
+        <v>19.7638</v>
+      </c>
+      <c r="Q79">
+        <v>7.67</v>
       </c>
       <c r="R79">
-        <v>11.4986</v>
+        <v>7.41432</v>
+      </c>
+      <c r="S79">
+        <f t="shared" si="2"/>
+        <v>349.61677638948368</v>
       </c>
       <c r="T79">
-        <f t="shared" ref="T79:T100" si="4">IF(I79&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B80" t="s">
         <v>20</v>
       </c>
       <c r="C80">
-        <v>5.3220124999999996</v>
+        <v>2.9895931999999998</v>
       </c>
       <c r="D80">
-        <v>6.08E-2</v>
+        <v>4.317E-2</v>
       </c>
       <c r="E80">
-        <v>1.226</v>
+        <v>1.6990000000000001</v>
       </c>
       <c r="F80">
-        <v>0.27300000000000002</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="G80">
-        <v>1460</v>
+        <v>1823</v>
       </c>
       <c r="H80" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I80">
-        <v>5990</v>
+        <v>6206</v>
       </c>
       <c r="J80">
-        <v>1.5609999999999999</v>
+        <v>1.603</v>
       </c>
       <c r="K80">
-        <v>1.06</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="L80">
-        <v>-0.2</v>
+        <v>-0.11600000000000001</v>
       </c>
       <c r="M80">
-        <v>4.0750000000000002</v>
+        <v>4.1079999999999997</v>
       </c>
       <c r="N80">
-        <v>210.1935714</v>
+        <v>157.06262000000001</v>
       </c>
       <c r="O80">
-        <v>-30.583608399999999</v>
-      </c>
-      <c r="P80">
-        <v>200.07499999999999</v>
+        <v>25.573136600000002</v>
+      </c>
+      <c r="P80" s="8">
+        <v>218.05</v>
       </c>
       <c r="Q80">
-        <v>10.068</v>
+        <v>9.98</v>
       </c>
       <c r="R80">
-        <v>9.8670799999999996</v>
+        <v>9.95702</v>
       </c>
       <c r="S80">
-        <f t="shared" ref="S80:S100" si="5">(0.000000000000000138*G80/(1.673534E-24*1.3*0.000000066726*F80*1.8986E+30/(E80*7149200000)^2))/100000</f>
-        <v>2057.1154637812851</v>
+        <f t="shared" si="2"/>
+        <v>1492.9814393090719</v>
       </c>
       <c r="T80">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="B81" t="s">
         <v>20</v>
       </c>
       <c r="C81">
-        <v>5.21536178778</v>
+        <v>3.2086640000000002</v>
       </c>
       <c r="D81">
-        <v>6.6100000000000006E-2</v>
+        <v>4.8820000000000002E-2</v>
       </c>
       <c r="E81">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="F81">
-        <v>1.51</v>
+        <v>0.7</v>
       </c>
       <c r="G81">
-        <v>1630</v>
+        <v>1927</v>
       </c>
       <c r="H81" t="s">
         <v>56</v>
       </c>
       <c r="I81">
-        <v>6250</v>
+        <v>5991</v>
       </c>
       <c r="J81">
-        <v>2.3901400000000002</v>
+        <v>2.1680000000000001</v>
       </c>
       <c r="K81">
-        <v>1.41</v>
+        <v>1.5069999999999999</v>
       </c>
       <c r="L81">
-        <v>-0.18</v>
+        <v>0.373</v>
       </c>
       <c r="M81">
-        <v>3.9</v>
+        <v>3.9430000000000001</v>
       </c>
       <c r="N81">
-        <v>0.32576100000000002</v>
+        <v>142.74340599999999</v>
       </c>
       <c r="O81">
-        <v>-8.9262511999999994</v>
-      </c>
-      <c r="P81">
-        <v>275.58699999999999</v>
+        <v>26.539995099999999</v>
+      </c>
+      <c r="P81" s="8">
+        <v>229.06700000000001</v>
       </c>
       <c r="Q81">
-        <v>9.9740000000000002</v>
+        <v>9.7210000000000001</v>
       </c>
       <c r="R81">
-        <v>9.8192900000000005</v>
+        <v>9.5843900000000009</v>
       </c>
       <c r="S81">
-        <f t="shared" si="5"/>
-        <v>621.55661806820979</v>
+        <f t="shared" si="2"/>
+        <v>1460.8182255852041</v>
       </c>
       <c r="T81">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="B82" t="s">
         <v>20</v>
       </c>
-      <c r="C82">
-        <v>2.2437499999999999</v>
-      </c>
-      <c r="D82">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="E82">
-        <v>1.38</v>
-      </c>
-      <c r="F82">
-        <v>8.84</v>
-      </c>
-      <c r="G82">
-        <v>1872</v>
-      </c>
       <c r="I82">
-        <v>6475</v>
+        <v>6200</v>
       </c>
       <c r="J82">
-        <v>1.4</v>
-      </c>
-      <c r="K82">
-        <v>1.62</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>4.07</v>
+        <v>1.2</v>
       </c>
       <c r="N82">
-        <v>218.27662470000001</v>
+        <v>97.636728000000005</v>
       </c>
       <c r="O82">
-        <v>21.8946875</v>
-      </c>
-      <c r="P82">
-        <v>161.99700000000001</v>
-      </c>
-      <c r="Q82">
-        <v>9.7449999999999992</v>
+        <v>29.672419000000001</v>
+      </c>
+      <c r="P82" s="8">
+        <v>427</v>
       </c>
       <c r="R82">
-        <v>9.6464700000000008</v>
-      </c>
-      <c r="S82">
-        <f>(0.000000000000000138*G82/(1.673534E-24*1.3*0.000000066726*F82*1.8986E+30/(E82*7149200000)^2))/100000</f>
-        <v>103.20465157174387</v>
+        <v>11.4986</v>
       </c>
       <c r="T82">
-        <f>IF(I82&gt;6800,-7,-5)</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
         <v>20</v>
       </c>
       <c r="C83">
-        <v>5.4435399999999996</v>
+        <v>4.1137899999999998</v>
       </c>
       <c r="D83">
-        <v>6.4100000000000004E-2</v>
+        <v>5.4969999999999998E-2</v>
       </c>
       <c r="E83">
-        <v>0.63</v>
+        <v>1.35</v>
       </c>
       <c r="F83">
-        <v>0.10100000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="G83">
-        <v>1270</v>
+        <v>2080</v>
       </c>
       <c r="H83" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I83">
-        <v>6050</v>
+        <v>6327</v>
       </c>
       <c r="J83">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="K83">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="L83">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>4.34</v>
+        <v>4.5</v>
       </c>
       <c r="N83">
-        <v>144.87510470000001</v>
+        <v>92.664022599999996</v>
       </c>
       <c r="O83">
-        <v>-20.982419100000001</v>
-      </c>
-      <c r="P83">
-        <v>114.173</v>
+        <v>30.957133299999999</v>
+      </c>
+      <c r="P83" s="8">
+        <v>134.05799999999999</v>
       </c>
       <c r="Q83">
-        <v>9.3510000000000009</v>
+        <v>8.68</v>
       </c>
       <c r="R83">
-        <v>9.2569999999999997</v>
+        <v>8.5839300000000005</v>
       </c>
       <c r="S83">
-        <f t="shared" si="5"/>
-        <v>1277.1766379712274</v>
+        <f t="shared" ref="S83:S96" si="4">(0.000000000000000138*G83/(1.673534E-24*1.3*0.000000066726*F83*1.8986E+30/(E83*7149200000)^2))/100000</f>
+        <v>570.64953846380126</v>
       </c>
       <c r="T83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
         <v>20</v>
       </c>
       <c r="C84">
-        <v>3.3448285000000002</v>
+        <v>3.4741084999999998</v>
       </c>
       <c r="D84">
-        <v>5.5800000000000002E-2</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="E84">
-        <v>1.81</v>
+        <v>1.7410000000000001</v>
       </c>
       <c r="F84">
-        <v>1.66</v>
+        <v>3.3820000000000001</v>
       </c>
       <c r="G84">
-        <v>2470</v>
+        <v>2262</v>
       </c>
       <c r="H84" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="I84">
-        <v>9360</v>
+        <v>8720</v>
       </c>
       <c r="J84">
-        <v>1.67</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="K84">
-        <v>2.0699999999999998</v>
+        <v>1.76</v>
       </c>
       <c r="L84">
-        <v>0.21</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M84">
-        <v>4.3099999999999996</v>
+        <v>4.29</v>
       </c>
       <c r="N84">
-        <v>227.270329</v>
+        <v>294.66141260000001</v>
       </c>
       <c r="O84">
-        <v>-42.704965799999997</v>
-      </c>
-      <c r="P84">
-        <v>427.678</v>
+        <v>31.219200099999998</v>
+      </c>
+      <c r="P84" s="8">
+        <v>136.42599999999999</v>
       </c>
       <c r="Q84">
-        <v>9.9459999999999997</v>
+        <v>7.59</v>
       </c>
       <c r="R84">
-        <v>9.9122599999999998</v>
+        <v>7.5749199999999997</v>
       </c>
       <c r="S84">
-        <f t="shared" si="5"/>
-        <v>1247.4798366438731</v>
+        <f t="shared" si="4"/>
+        <v>518.80488815900412</v>
       </c>
       <c r="T84">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-7</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B85" t="s">
         <v>20</v>
       </c>
       <c r="C85">
-        <v>0.94145223</v>
+        <v>2.7347700000000001</v>
       </c>
       <c r="D85">
-        <v>2.0240000000000001E-2</v>
+        <v>4.4150000000000002E-2</v>
       </c>
       <c r="E85">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="F85">
-        <v>10.199999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="G85">
-        <v>2429</v>
+        <v>2048</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I85">
-        <v>6432</v>
+        <v>6768</v>
       </c>
       <c r="J85">
-        <v>1.319</v>
+        <v>1.81</v>
       </c>
       <c r="K85">
-        <v>1.294</v>
+        <v>1.76</v>
       </c>
       <c r="L85">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>4.3099999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="N85">
-        <v>24.354461799999999</v>
+        <v>78.295591200000004</v>
       </c>
       <c r="O85">
-        <v>-45.677793700000002</v>
-      </c>
-      <c r="P85">
-        <v>123.483</v>
+        <v>33.317953199999998</v>
+      </c>
+      <c r="P85" s="8">
+        <v>136.68100000000001</v>
       </c>
       <c r="Q85">
-        <v>9.2799999999999994</v>
+        <v>8.56</v>
       </c>
       <c r="R85">
-        <v>9.1661699999999993</v>
+        <v>8.4517299999999995</v>
       </c>
       <c r="S85">
-        <f t="shared" si="5"/>
-        <v>93.704022194109143</v>
+        <f t="shared" si="4"/>
+        <v>965.25628287035329</v>
       </c>
       <c r="T85">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B86" t="s">
         <v>20</v>
       </c>
       <c r="C86">
-        <v>2.7240329999999999</v>
+        <v>18.712024</v>
       </c>
       <c r="D86">
-        <v>5.0529999999999999E-2</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E86">
-        <v>1.619</v>
+        <v>0.80944318999999998</v>
       </c>
       <c r="F86">
-        <v>1.99</v>
+        <v>0.23314467</v>
       </c>
       <c r="G86">
-        <v>3353</v>
+        <v>798.3</v>
+      </c>
+      <c r="H86" t="s">
+        <v>54</v>
       </c>
       <c r="I86">
-        <v>8000</v>
+        <v>6128</v>
       </c>
       <c r="J86">
-        <v>2.36</v>
+        <v>1.266</v>
       </c>
       <c r="K86">
-        <v>2.0299999999999998</v>
+        <v>1.1641999999999999</v>
       </c>
       <c r="L86">
-        <v>0.28999999999999998</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="M86">
-        <v>3.9</v>
+        <v>4.2960000000000003</v>
       </c>
       <c r="N86">
-        <v>225.68673200000001</v>
+        <v>306.74113399999999</v>
       </c>
       <c r="O86">
-        <v>-3.0314874000000001</v>
-      </c>
-      <c r="P86">
-        <v>99.730999999999995</v>
+        <v>33.744388200000003</v>
+      </c>
+      <c r="P86" s="8">
+        <v>80.666499999999999</v>
       </c>
       <c r="Q86">
-        <v>6.5977600000000001</v>
+        <v>8.5579999999999998</v>
       </c>
       <c r="R86">
-        <v>6.5536899999999996</v>
-      </c>
-      <c r="S86" s="5">
-        <f t="shared" si="5"/>
-        <v>1130.2166328238993</v>
+        <v>8.4183900000000005</v>
+      </c>
+      <c r="S86">
+        <f t="shared" si="4"/>
+        <v>574.11765847468712</v>
       </c>
       <c r="T86">
-        <f t="shared" si="4"/>
-        <v>-7</v>
-      </c>
-      <c r="U86" s="1" t="s">
-        <v>135</v>
+        <f t="shared" si="3"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="B87" t="s">
         <v>20</v>
       </c>
       <c r="C87">
-        <v>1.21987</v>
+        <v>10.590547000000001</v>
       </c>
       <c r="D87">
-        <v>2.3900000000000001E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E87">
-        <v>1.593</v>
+        <v>0.91890603000000004</v>
       </c>
       <c r="F87">
-        <v>2.093</v>
+        <v>0.18469084999999999</v>
       </c>
       <c r="G87">
-        <v>2781.7</v>
+        <v>947</v>
       </c>
       <c r="H87" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="I87">
-        <v>7430</v>
+        <v>6000</v>
       </c>
       <c r="J87">
-        <v>1.444</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="K87">
-        <v>1.4950000000000001</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="L87">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M87">
-        <v>4.25</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N87">
-        <v>36.712737500000003</v>
+        <v>161.87955690000001</v>
       </c>
       <c r="O87">
-        <v>37.5504441</v>
-      </c>
-      <c r="P87">
-        <v>121.944</v>
+        <v>36.329434499999998</v>
+      </c>
+      <c r="P87" s="8">
+        <v>130.85499999999999</v>
       </c>
       <c r="Q87">
-        <v>8.14</v>
+        <v>10.058999999999999</v>
       </c>
       <c r="R87">
-        <v>8.0700400000000005</v>
+        <v>9.9823299999999993</v>
       </c>
       <c r="S87">
-        <f t="shared" si="5"/>
-        <v>863.09804630713359</v>
+        <f t="shared" si="4"/>
+        <v>1107.9861243219782</v>
       </c>
       <c r="T87">
-        <f t="shared" si="4"/>
-        <v>-7</v>
+        <f t="shared" si="3"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B88" t="s">
         <v>20</v>
       </c>
       <c r="C88">
-        <v>6.87188</v>
+        <v>1.21987</v>
       </c>
       <c r="D88">
-        <v>7.5219999999999995E-2</v>
+        <v>2.3900000000000001E-2</v>
       </c>
       <c r="E88">
-        <v>1.23</v>
+        <v>1.593</v>
       </c>
       <c r="F88">
-        <v>3.44</v>
+        <v>2.093</v>
       </c>
       <c r="G88">
-        <v>1250</v>
+        <v>2781.7</v>
       </c>
       <c r="H88" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="I88">
-        <v>6180</v>
+        <v>7430</v>
       </c>
       <c r="J88">
-        <v>1.52</v>
+        <v>1.444</v>
       </c>
       <c r="K88">
-        <v>1.76</v>
+        <v>1.4950000000000001</v>
       </c>
       <c r="L88">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="M88">
         <v>4.25</v>
       </c>
       <c r="N88">
-        <v>243.95971940000001</v>
+        <v>36.712737500000003</v>
       </c>
       <c r="O88">
-        <v>10.0324103</v>
-      </c>
-      <c r="P88">
-        <v>136.24</v>
+        <v>37.5504441</v>
+      </c>
+      <c r="P88" s="8">
+        <v>121.944</v>
       </c>
       <c r="Q88">
-        <v>9.391</v>
+        <v>8.14</v>
       </c>
       <c r="R88">
-        <v>9.20974</v>
+        <v>8.0700400000000005</v>
       </c>
       <c r="S88">
-        <f t="shared" si="5"/>
-        <v>140.68549179703928</v>
+        <f t="shared" si="4"/>
+        <v>863.09804630713359</v>
       </c>
       <c r="T88">
-        <f t="shared" si="4"/>
-        <v>-5</v>
+        <f t="shared" si="3"/>
+        <v>-7</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B89" t="s">
         <v>20</v>
       </c>
       <c r="C89">
-        <v>3.86813881</v>
+        <v>4.6276700000000002</v>
       </c>
       <c r="D89">
-        <v>4.53E-2</v>
+        <v>5.96E-2</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="F89">
-        <v>0.26</v>
+        <v>3.44</v>
       </c>
       <c r="G89">
-        <v>971</v>
+        <v>1624</v>
       </c>
       <c r="H89" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I89">
-        <v>4792</v>
+        <v>6600</v>
       </c>
       <c r="J89">
-        <v>0.80100000000000005</v>
+        <v>1.82</v>
       </c>
       <c r="K89">
-        <v>0.83</v>
+        <v>2.65</v>
       </c>
       <c r="L89">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="M89">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="N89">
-        <v>315.02596610000001</v>
+        <v>260.11617189999998</v>
       </c>
       <c r="O89">
-        <v>-5.0948570000000002</v>
-      </c>
-      <c r="P89">
-        <v>49.960500000000003</v>
+        <v>38.242168200000002</v>
+      </c>
+      <c r="P89" s="8">
+        <v>222.66300000000001</v>
       </c>
       <c r="Q89">
-        <v>9.8729999999999993</v>
+        <v>9.9879999999999995</v>
       </c>
       <c r="R89">
-        <v>9.4846599999999999</v>
+        <v>9.8728300000000004</v>
       </c>
       <c r="S89">
-        <f t="shared" si="5"/>
-        <v>955.72600175951948</v>
+        <f t="shared" si="4"/>
+        <v>243.60813720463176</v>
       </c>
       <c r="T89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
-      </c>
-      <c r="U89" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C90">
-        <v>4.9546416000000004</v>
+        <v>2.8758900000000001</v>
       </c>
       <c r="D90">
-        <v>6.1699999999999998E-2</v>
+        <v>4.3639999999999998E-2</v>
       </c>
       <c r="E90">
-        <v>1.33</v>
+        <v>0.74</v>
       </c>
       <c r="F90">
-        <v>0.96</v>
+        <v>0.38</v>
       </c>
       <c r="G90">
-        <v>1487</v>
+        <v>1626</v>
+      </c>
+      <c r="H90" t="s">
+        <v>43</v>
       </c>
       <c r="I90">
-        <v>6400</v>
+        <v>6179</v>
       </c>
       <c r="J90">
-        <v>1.4319999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="K90">
-        <v>1.276</v>
+        <v>1.42</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M90">
-        <v>4.2320000000000002</v>
+        <v>4.37</v>
       </c>
       <c r="N90">
-        <v>311.04275580000001</v>
+        <v>247.62298269999999</v>
       </c>
       <c r="O90">
-        <v>-39.225485599999999</v>
-      </c>
-      <c r="P90">
-        <v>162.303</v>
+        <v>38.347534899999999</v>
+      </c>
+      <c r="P90" s="8">
+        <v>75.8643</v>
       </c>
       <c r="Q90">
-        <v>9.5039999999999996</v>
+        <v>8.15</v>
       </c>
       <c r="R90">
-        <v>9.3767099999999992</v>
+        <v>8.0141600000000004</v>
       </c>
       <c r="S90">
-        <f t="shared" si="5"/>
-        <v>701.18164217622461</v>
+        <f t="shared" si="4"/>
+        <v>599.63628364223177</v>
       </c>
       <c r="T90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B91" t="s">
         <v>20</v>
       </c>
       <c r="C91">
-        <v>2.13775</v>
+        <v>4.4652997599999997</v>
       </c>
       <c r="D91">
-        <v>3.4430000000000002E-2</v>
+        <v>5.561E-2</v>
       </c>
       <c r="E91">
-        <v>1.36</v>
+        <v>1.319</v>
       </c>
       <c r="F91">
-        <v>0.72</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="G91">
-        <v>1865</v>
+        <v>1322</v>
       </c>
       <c r="H91" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="I91">
-        <v>5990</v>
+        <v>5980</v>
       </c>
       <c r="J91">
-        <v>1.42</v>
+        <v>1.1739999999999999</v>
       </c>
       <c r="K91">
-        <v>0.98</v>
+        <v>1.151</v>
       </c>
       <c r="L91">
-        <v>0.39</v>
+        <v>0.13</v>
       </c>
       <c r="M91">
-        <v>4.3899999999999997</v>
+        <v>4.359</v>
       </c>
       <c r="N91">
-        <v>304.53884299999999</v>
+        <v>344.44536319999997</v>
       </c>
       <c r="O91">
-        <v>-1.0760033</v>
-      </c>
-      <c r="P91">
-        <v>149.21600000000001</v>
+        <v>38.674919000000003</v>
+      </c>
+      <c r="P91" s="8">
+        <v>158.97900000000001</v>
       </c>
       <c r="Q91">
-        <v>9.75</v>
+        <v>9.827</v>
       </c>
       <c r="R91">
-        <v>9.5723000000000003</v>
+        <v>10.178599999999999</v>
       </c>
       <c r="S91">
-        <f t="shared" si="5"/>
-        <v>1226.0598654781754</v>
+        <f t="shared" si="4"/>
+        <v>1121.1126749906216</v>
       </c>
       <c r="T91">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B92" t="s">
         <v>20</v>
       </c>
       <c r="C92">
-        <v>1.8098819799999999</v>
+        <v>1.4811235</v>
       </c>
       <c r="D92">
-        <v>3.3000000000000002E-2</v>
+        <v>3.4619999999999998E-2</v>
       </c>
       <c r="E92">
-        <v>1.8540000000000001</v>
+        <v>1.891</v>
       </c>
       <c r="F92">
-        <v>0.89400000000000002</v>
+        <v>2.88</v>
       </c>
       <c r="G92">
-        <v>2228</v>
+        <v>4050</v>
       </c>
       <c r="H92" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="I92">
-        <v>6329</v>
+        <v>10170.1</v>
       </c>
       <c r="J92">
-        <v>1.756</v>
+        <v>2.3620000000000001</v>
       </c>
       <c r="K92">
-        <v>1.458</v>
+        <v>2.52</v>
       </c>
       <c r="L92">
-        <v>0.36599999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="M92">
-        <v>4.1959999999999997</v>
+        <v>4.093</v>
       </c>
       <c r="N92">
-        <v>26.632936000000001</v>
+        <v>307.85989979999999</v>
       </c>
       <c r="O92">
-        <v>2.7003889999999999</v>
-      </c>
-      <c r="P92">
-        <v>194.459</v>
+        <v>39.9389161</v>
+      </c>
+      <c r="P92" s="8">
+        <v>204.45500000000001</v>
       </c>
       <c r="Q92">
-        <v>9.5180000000000007</v>
+        <v>7.55</v>
       </c>
       <c r="R92">
-        <v>9.3950700000000005</v>
+        <v>7.5767499999999997</v>
       </c>
       <c r="S92">
-        <f t="shared" si="5"/>
-        <v>2192.2225820487197</v>
-      </c>
-      <c r="T92">
         <f t="shared" si="4"/>
+        <v>1286.8653667451285</v>
+      </c>
+      <c r="U92" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93">
+        <v>2.7033900000000002</v>
+      </c>
+      <c r="D93">
+        <v>4.1230000000000003E-2</v>
+      </c>
+      <c r="E93">
+        <v>1.56</v>
+      </c>
+      <c r="F93">
+        <v>1.94</v>
+      </c>
+      <c r="G93">
+        <v>1816</v>
+      </c>
+      <c r="I93">
+        <v>6304</v>
+      </c>
+      <c r="J93">
+        <v>1.7</v>
+      </c>
+      <c r="K93">
+        <v>1.96</v>
+      </c>
+      <c r="L93">
+        <v>0.05</v>
+      </c>
+      <c r="M93">
+        <v>4.2</v>
+      </c>
+      <c r="N93">
+        <v>148.6431193</v>
+      </c>
+      <c r="O93">
+        <v>40.387944599999997</v>
+      </c>
+      <c r="P93" s="8">
+        <v>210.25200000000001</v>
+      </c>
+      <c r="Q93">
+        <v>9.8160000000000007</v>
+      </c>
+      <c r="R93">
+        <v>9.7632399999999997</v>
+      </c>
+      <c r="S93">
+        <f t="shared" si="4"/>
+        <v>582.97620763372299</v>
+      </c>
+      <c r="T93">
+        <f>IF(I93&gt;6800,-7,-5)</f>
         <v>-5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A93" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="I93" s="1">
-        <v>3472</v>
-      </c>
-      <c r="J93">
-        <v>0.41299999999999998</v>
-      </c>
-      <c r="K93">
-        <v>0.40600000000000003</v>
-      </c>
-      <c r="N93">
-        <v>272.54430475160001</v>
-      </c>
-      <c r="O93">
-        <v>-37.644513386920003</v>
-      </c>
-      <c r="P93">
-        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
       </c>
       <c r="C94">
-        <v>3.6623920000000001</v>
+        <v>10.261127</v>
       </c>
       <c r="D94">
-        <v>5.1900000000000002E-2</v>
+        <v>0.111</v>
       </c>
       <c r="E94">
-        <v>1.53</v>
+        <v>1.1079506100000001</v>
       </c>
       <c r="F94">
-        <v>0.85</v>
+        <v>5.55960374</v>
       </c>
       <c r="G94">
-        <v>1716.2</v>
-      </c>
-      <c r="H94" t="s">
-        <v>125</v>
+        <v>1363.43</v>
       </c>
       <c r="I94">
-        <v>6600</v>
+        <v>6200</v>
       </c>
       <c r="J94">
-        <v>1.51</v>
+        <v>2.7505000000000002</v>
       </c>
       <c r="K94">
-        <v>1.39</v>
+        <v>1.7169000000000001</v>
       </c>
       <c r="L94">
-        <v>0.03</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="M94">
-        <v>4.2</v>
+        <v>3.7890000000000001</v>
       </c>
       <c r="N94">
-        <v>66.370901599999996</v>
+        <v>263.75807529999997</v>
       </c>
       <c r="O94">
-        <v>-30.600436200000001</v>
-      </c>
-      <c r="P94">
-        <v>246.69</v>
+        <v>40.695042800000003</v>
+      </c>
+      <c r="P94" s="8">
+        <v>224.73099999999999</v>
       </c>
       <c r="Q94">
-        <v>10.044</v>
+        <v>9.07</v>
       </c>
       <c r="R94">
-        <v>9.9720200000000006</v>
+        <v>8.9365100000000002</v>
       </c>
       <c r="S94">
-        <f t="shared" si="5"/>
-        <v>1209.5375438309629</v>
+        <f t="shared" si="4"/>
+        <v>77.040187113891676</v>
       </c>
       <c r="T94">
+        <f>IF(I94&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95">
+        <v>5.8267310999999999</v>
+      </c>
+      <c r="D95">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="E95">
+        <v>0.57186287999999996</v>
+      </c>
+      <c r="F95">
+        <v>0.24698861999999999</v>
+      </c>
+      <c r="G95">
+        <v>1439</v>
+      </c>
+      <c r="I95">
+        <v>6110</v>
+      </c>
+      <c r="J95">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="K95">
+        <v>1.2909999999999999</v>
+      </c>
+      <c r="L95">
+        <v>0.124</v>
+      </c>
+      <c r="M95">
+        <v>4.1180000000000003</v>
+      </c>
+      <c r="N95">
+        <v>51.657269100000001</v>
+      </c>
+      <c r="O95">
+        <v>40.817270399999998</v>
+      </c>
+      <c r="P95" s="8">
+        <v>179.14699999999999</v>
+      </c>
+      <c r="Q95">
+        <v>9.9130000000000003</v>
+      </c>
+      <c r="R95">
+        <v>9.7295700000000007</v>
+      </c>
+      <c r="S95">
         <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>96</v>
-      </c>
-      <c r="B95" t="s">
-        <v>20</v>
-      </c>
-      <c r="C95">
-        <v>8.1587200000000006</v>
-      </c>
-      <c r="D95">
-        <v>8.0100000000000005E-2</v>
-      </c>
-      <c r="E95">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F95">
-        <v>2.54</v>
-      </c>
-      <c r="G95">
-        <v>1059</v>
-      </c>
-      <c r="H95" t="s">
-        <v>97</v>
-      </c>
-      <c r="I95">
-        <v>5600</v>
-      </c>
-      <c r="J95">
-        <v>1.03</v>
-      </c>
-      <c r="K95">
-        <v>1.34</v>
-      </c>
-      <c r="L95">
-        <v>0.17</v>
-      </c>
-      <c r="M95">
-        <v>4.5</v>
-      </c>
-      <c r="N95">
-        <v>359.90087369999998</v>
-      </c>
-      <c r="O95">
-        <v>-35.031334899999997</v>
-      </c>
-      <c r="P95">
-        <v>89.960599999999999</v>
-      </c>
-      <c r="Q95">
-        <v>9.7889999999999997</v>
-      </c>
-      <c r="R95">
-        <v>9.6124899999999993</v>
-      </c>
-      <c r="S95">
-        <f t="shared" si="5"/>
-        <v>136.24063220140397</v>
+        <v>487.59044264912109</v>
       </c>
       <c r="T95">
-        <f t="shared" si="4"/>
+        <f>IF(I95&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="B96" t="s">
         <v>20</v>
       </c>
       <c r="C96">
-        <v>2.7057899999999999</v>
+        <v>5.6335157999999996</v>
       </c>
       <c r="D96">
-        <v>4.4699999999999997E-2</v>
+        <v>6.8140000000000006E-2</v>
       </c>
       <c r="E96">
-        <v>1.62</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="F96">
-        <v>1.17</v>
+        <v>9.02</v>
       </c>
       <c r="G96">
-        <v>2190</v>
+        <v>1540</v>
       </c>
       <c r="H96" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="I96">
-        <v>6480</v>
+        <v>6380</v>
       </c>
       <c r="J96">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="K96">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="L96">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="M96">
-        <v>3.96</v>
+        <v>4.16</v>
       </c>
       <c r="N96">
-        <v>72.660591600000004</v>
+        <v>245.1514324</v>
       </c>
       <c r="O96">
-        <v>1.8938364999999999</v>
-      </c>
-      <c r="P96">
-        <v>275.66399999999999</v>
+        <v>41.047960099999997</v>
+      </c>
+      <c r="P96" s="8">
+        <v>127.774</v>
       </c>
       <c r="Q96">
-        <v>10.073</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="R96">
-        <v>9.8979599999999994</v>
+        <v>8.5984200000000008</v>
       </c>
       <c r="S96">
-        <f t="shared" si="5"/>
-        <v>1257.117296864338</v>
+        <f t="shared" si="4"/>
+        <v>39.515068300859213</v>
       </c>
       <c r="T96">
-        <f t="shared" si="4"/>
+        <f>IF(I96&gt;6800,-7,-5)</f>
         <v>-5</v>
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>126</v>
-      </c>
-      <c r="B97" t="s">
-        <v>20</v>
-      </c>
-      <c r="C97">
-        <v>3.9501900000000001</v>
-      </c>
-      <c r="D97">
-        <v>5.5E-2</v>
-      </c>
-      <c r="E97">
-        <v>1.58</v>
-      </c>
-      <c r="F97">
-        <v>0.5</v>
-      </c>
-      <c r="G97">
-        <v>1604</v>
-      </c>
-      <c r="H97" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="I97">
-        <v>6170</v>
+        <v>6245.11328125</v>
       </c>
       <c r="J97">
-        <v>1.48</v>
-      </c>
-      <c r="K97">
-        <v>1.67</v>
-      </c>
-      <c r="L97">
-        <v>0.26</v>
+        <v>1.208241820335388</v>
       </c>
       <c r="M97">
-        <v>4.2699999999999996</v>
+        <v>4.2744002342224121</v>
       </c>
       <c r="N97">
-        <v>313.78323929999999</v>
+        <v>31.04275939878713</v>
       </c>
       <c r="O97">
-        <v>-34.135751200000001</v>
-      </c>
-      <c r="P97">
-        <v>211.21100000000001</v>
+        <v>46.687851647860192</v>
+      </c>
+      <c r="P97" s="8">
+        <v>283.38339999999999</v>
       </c>
       <c r="Q97">
-        <v>10.051</v>
+        <v>11.12930202484131</v>
       </c>
       <c r="R97">
-        <v>10.028499999999999</v>
-      </c>
-      <c r="S97">
-        <f t="shared" si="5"/>
-        <v>2049.4439875099679</v>
-      </c>
-      <c r="T97">
-        <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>11.12930202484131</v>
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>131</v>
+      <c r="A98" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B98" t="s">
         <v>20</v>
       </c>
       <c r="C98">
-        <v>2.1846700000000001</v>
+        <v>1.7635879999999999</v>
       </c>
       <c r="D98">
-        <v>3.4160000000000003E-2</v>
+        <v>3.6409999999999998E-2</v>
       </c>
       <c r="E98">
-        <v>1.23</v>
+        <v>1.512</v>
       </c>
       <c r="F98">
-        <v>1.44</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="G98">
-        <v>1570</v>
-      </c>
-      <c r="H98" t="s">
-        <v>132</v>
+        <v>2550</v>
       </c>
       <c r="I98">
-        <v>5830</v>
+        <v>7650</v>
       </c>
       <c r="J98">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="K98">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="L98">
-        <v>0.14000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="M98">
-        <v>4.3600000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="N98">
-        <v>337.45782430000003</v>
+        <v>286.97138760000001</v>
       </c>
       <c r="O98">
-        <v>-48.003098799999997</v>
-      </c>
-      <c r="P98">
-        <v>137.54400000000001</v>
+        <v>46.868246300000003</v>
+      </c>
+      <c r="P98" s="8">
+        <v>519.096</v>
       </c>
       <c r="Q98">
-        <v>10.092000000000001</v>
+        <v>9.7910000000000004</v>
       </c>
       <c r="R98">
-        <v>9.9369700000000005</v>
+        <v>10.367800000000001</v>
       </c>
       <c r="S98">
-        <f t="shared" si="5"/>
-        <v>422.11900227636102</v>
+        <f>(0.000000000000000138*G98/(1.673534E-24*1.3*0.000000066726*F98*1.8986E+30/(E98*7149200000)^2))/100000</f>
+        <v>160.76196513632402</v>
       </c>
       <c r="T98">
-        <f t="shared" si="4"/>
-        <v>-5</v>
+        <f>IF(I98&gt;6800,-7,-5)</f>
+        <v>-7</v>
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>79</v>
-      </c>
-      <c r="B99" t="s">
-        <v>20</v>
-      </c>
-      <c r="C99">
-        <v>5.75251</v>
-      </c>
-      <c r="D99">
-        <v>7.17E-2</v>
-      </c>
-      <c r="E99">
-        <v>1.02</v>
-      </c>
-      <c r="F99">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="G99">
-        <v>1480</v>
-      </c>
-      <c r="H99" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="I99">
-        <v>6150</v>
+        <v>6424.27685546875</v>
       </c>
       <c r="J99">
-        <v>1.64</v>
-      </c>
-      <c r="K99">
-        <v>1.21</v>
-      </c>
-      <c r="L99">
-        <v>0.21</v>
-      </c>
-      <c r="M99">
-        <v>4.3</v>
+        <v>2.0702402591705318</v>
       </c>
       <c r="N99">
-        <v>39.897668899999999</v>
+        <v>292.24718620018581</v>
       </c>
       <c r="O99">
-        <v>-50.008193400000003</v>
-      </c>
-      <c r="P99">
-        <v>158.66</v>
-      </c>
+        <v>47.969544064101818</v>
+      </c>
+      <c r="P99"/>
       <c r="Q99">
-        <v>9.4749999999999996</v>
+        <v>10.36768245697021</v>
       </c>
       <c r="R99">
-        <v>9.3251000000000008</v>
-      </c>
-      <c r="S99">
-        <f t="shared" si="5"/>
-        <v>162.15983922320817</v>
-      </c>
-      <c r="T99">
-        <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>10.36768245697021</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>77</v>
+      </c>
+      <c r="B100" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100">
+        <v>4.7202190000000002</v>
+      </c>
+      <c r="D100">
+        <v>6.2600000000000003E-2</v>
+      </c>
+      <c r="E100">
+        <v>1.3959999999999999</v>
+      </c>
+      <c r="F100">
+        <v>2.37</v>
+      </c>
+      <c r="G100">
+        <v>1679</v>
+      </c>
+      <c r="I100">
+        <v>6274</v>
+      </c>
+      <c r="J100">
+        <v>1.925</v>
+      </c>
+      <c r="K100">
+        <v>1.464</v>
+      </c>
+      <c r="L100">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="M100">
+        <v>4.0339999999999998</v>
+      </c>
+      <c r="N100">
+        <v>325.01453629999997</v>
+      </c>
+      <c r="O100">
+        <v>48.4067674</v>
+      </c>
+      <c r="P100" s="8">
+        <v>200.49199999999999</v>
+      </c>
+      <c r="Q100">
+        <v>9.4380000000000006</v>
+      </c>
+      <c r="R100">
+        <v>9.3503900000000009</v>
+      </c>
+      <c r="S100">
+        <f t="shared" ref="S100:S110" si="5">(0.000000000000000138*G100/(1.673534E-24*1.3*0.000000066726*F100*1.8986E+30/(E100*7149200000)^2))/100000</f>
+        <v>353.31388599481477</v>
+      </c>
+      <c r="T100">
+        <f t="shared" ref="T100:T110" si="6">IF(I100&gt;6800,-7,-5)</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101">
+        <v>3.2122199999999999</v>
+      </c>
+      <c r="D101">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="E101">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F101">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="G101">
+        <v>1463</v>
+      </c>
+      <c r="H101" t="s">
+        <v>94</v>
+      </c>
+      <c r="I101">
+        <v>5302</v>
+      </c>
+      <c r="J101">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K101">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="L101">
+        <v>0.24</v>
+      </c>
+      <c r="M101">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="N101">
+        <v>155.6814593</v>
+      </c>
+      <c r="O101">
+        <v>50.128711500000001</v>
+      </c>
+      <c r="P101">
+        <v>81.764700000000005</v>
+      </c>
+      <c r="Q101">
+        <v>9.7629999999999999</v>
+      </c>
+      <c r="R101">
+        <v>9.5193600000000007</v>
+      </c>
+      <c r="S101">
+        <f t="shared" si="5"/>
+        <v>200.46131426194896</v>
+      </c>
+      <c r="T101">
+        <f t="shared" si="6"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>88</v>
+      </c>
+      <c r="B102" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102">
+        <v>4.7947813000000004</v>
+      </c>
+      <c r="D102">
+        <v>6.2770000000000006E-2</v>
+      </c>
+      <c r="E102">
+        <v>1.631</v>
+      </c>
+      <c r="F102">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="G102">
+        <v>1772</v>
+      </c>
+      <c r="I102">
+        <v>6212</v>
+      </c>
+      <c r="J102">
+        <v>2.1970000000000001</v>
+      </c>
+      <c r="K102">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="L102">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="M102">
+        <v>3.9114</v>
+      </c>
+      <c r="N102">
+        <v>28.282571900000001</v>
+      </c>
+      <c r="O102">
+        <v>52.053920900000001</v>
+      </c>
+      <c r="P102" s="8">
+        <v>233.22</v>
+      </c>
+      <c r="Q102">
+        <v>9.7270000000000003</v>
+      </c>
+      <c r="R102">
+        <v>9.5635499999999993</v>
+      </c>
+      <c r="S102">
+        <f t="shared" si="5"/>
+        <v>2101.5864855136347</v>
+      </c>
+      <c r="T102">
+        <f t="shared" si="6"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>38</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103">
+        <v>6.1349779</v>
+      </c>
+      <c r="D103">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="E103">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="F103">
+        <v>2.14</v>
+      </c>
+      <c r="G103">
+        <v>1361</v>
+      </c>
+      <c r="H103" t="s">
+        <v>39</v>
+      </c>
+      <c r="I103">
+        <v>5742</v>
+      </c>
+      <c r="J103">
+        <v>2.04</v>
+      </c>
+      <c r="K103">
+        <v>1.27</v>
+      </c>
+      <c r="L103">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="M103">
+        <v>3.92</v>
+      </c>
+      <c r="N103">
+        <v>203.50995599999999</v>
+      </c>
+      <c r="O103">
+        <v>53.728187599999998</v>
+      </c>
+      <c r="P103" s="8">
+        <v>92.258899999999997</v>
+      </c>
+      <c r="Q103">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="R103">
+        <v>7.89255</v>
+      </c>
+      <c r="S103">
+        <f t="shared" si="5"/>
+        <v>211.51519610586323</v>
+      </c>
+      <c r="T103">
+        <f t="shared" si="6"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>34</v>
+      </c>
+      <c r="B104" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104">
+        <v>2.6502370000000002</v>
+      </c>
+      <c r="D104">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="E104">
+        <v>1.49</v>
+      </c>
+      <c r="F104">
+        <v>3.12</v>
+      </c>
+      <c r="G104">
+        <v>2370</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104">
+        <v>7690</v>
+      </c>
+      <c r="J104">
+        <v>1.92</v>
+      </c>
+      <c r="K104">
+        <v>1.9</v>
+      </c>
+      <c r="L104">
+        <v>0.09</v>
+      </c>
+      <c r="M104">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="N104">
+        <v>316.20369219999998</v>
+      </c>
+      <c r="O104">
+        <v>55.588022100000003</v>
+      </c>
+      <c r="P104" s="8">
+        <v>148.92500000000001</v>
+      </c>
+      <c r="Q104">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="R104">
+        <v>7.9756099999999996</v>
+      </c>
+      <c r="S104">
+        <f t="shared" si="5"/>
+        <v>431.57254486096394</v>
+      </c>
+      <c r="T104">
+        <f t="shared" si="6"/>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
         <v>107</v>
       </c>
-      <c r="B100" t="s">
-        <v>20</v>
-      </c>
-      <c r="C100">
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105">
         <v>3.1915399999999998</v>
       </c>
-      <c r="D100">
+      <c r="D105">
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="E100">
+      <c r="E105">
         <v>1.41</v>
       </c>
-      <c r="F100">
+      <c r="F105">
         <v>7.29</v>
       </c>
-      <c r="G100">
+      <c r="G105">
         <v>1729</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H105" t="s">
         <v>108</v>
       </c>
-      <c r="I100">
+      <c r="I105">
         <v>6429</v>
       </c>
-      <c r="J100">
+      <c r="J105">
         <v>1.54</v>
       </c>
-      <c r="K100">
+      <c r="K105">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L100">
+      <c r="L105">
         <v>-0.18</v>
       </c>
-      <c r="M100">
+      <c r="M105">
         <v>3.95</v>
       </c>
-      <c r="N100">
+      <c r="N105">
         <v>65.469581399999996</v>
       </c>
-      <c r="O100">
+      <c r="O105">
         <v>57.817209499999997</v>
       </c>
-      <c r="P100">
+      <c r="P105" s="8">
         <v>213.053</v>
       </c>
-      <c r="Q100">
+      <c r="Q105">
         <v>9.8539999999999992</v>
       </c>
-      <c r="R100">
+      <c r="R105">
         <v>9.7388899999999996</v>
       </c>
-      <c r="S100">
+      <c r="S105">
         <f t="shared" si="5"/>
         <v>120.66830436099001</v>
       </c>
-      <c r="T100">
-        <f t="shared" si="4"/>
+      <c r="T105">
+        <f t="shared" si="6"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="101" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="I101">
-        <v>7065.3916019999997</v>
-      </c>
-      <c r="N101">
-        <v>146.7834014</v>
-      </c>
-      <c r="O101">
-        <v>-54.204010279999999</v>
-      </c>
-      <c r="P101">
-        <v>300.9884644</v>
-      </c>
-      <c r="R101">
-        <v>9.2583198549999999</v>
-      </c>
-    </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="I102" s="1">
-        <v>3500</v>
-      </c>
-      <c r="J102">
-        <v>0.4</v>
-      </c>
-      <c r="K102">
-        <v>0.4</v>
-      </c>
-      <c r="N102">
-        <v>346.62201299999998</v>
-      </c>
-      <c r="O102">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P102">
-        <v>11</v>
-      </c>
-      <c r="Q102">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A103" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="I103" s="1">
-        <v>3500</v>
-      </c>
-      <c r="J103">
-        <v>0.4</v>
-      </c>
-      <c r="K103">
-        <v>0.4</v>
-      </c>
-      <c r="N103">
-        <v>346.62201299999998</v>
-      </c>
-      <c r="O103">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P103">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="Q103">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="I104" s="1">
-        <v>3500</v>
-      </c>
-      <c r="J104">
-        <v>0.4</v>
-      </c>
-      <c r="K104">
-        <v>0.4</v>
-      </c>
-      <c r="N104">
-        <v>346.62201299999998</v>
-      </c>
-      <c r="O104">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P104">
-        <v>27.5</v>
-      </c>
-      <c r="Q104">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I105" s="1">
-        <v>3500</v>
-      </c>
-      <c r="J105">
-        <v>0.4</v>
-      </c>
-      <c r="K105">
-        <v>0.4</v>
-      </c>
-      <c r="N105">
-        <v>346.62201299999998</v>
-      </c>
-      <c r="O105">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P105">
-        <v>43.7</v>
-      </c>
-      <c r="Q105">
-        <v>14</v>
-      </c>
-    </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="I106" s="1">
-        <v>3500</v>
+      <c r="A106" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106">
+        <v>12.5199</v>
+      </c>
+      <c r="D106">
+        <v>0.1062</v>
+      </c>
+      <c r="E106">
+        <v>0.41279399999999999</v>
+      </c>
+      <c r="F106">
+        <v>2.627204E-2</v>
+      </c>
+      <c r="G106">
+        <v>843</v>
+      </c>
+      <c r="I106">
+        <v>5770</v>
       </c>
       <c r="J106">
-        <v>0.4</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="K106">
-        <v>0.4</v>
+        <v>1.022</v>
+      </c>
+      <c r="L106">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M106">
+        <v>4.47</v>
       </c>
       <c r="N106">
-        <v>346.62201299999998</v>
+        <v>192.1848981</v>
       </c>
       <c r="O106">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P106">
-        <v>69.2</v>
+        <v>64.855275500000005</v>
+      </c>
+      <c r="P106" s="8">
+        <v>84.536199999999994</v>
       </c>
       <c r="Q106">
-        <v>15</v>
+        <v>9.5340000000000007</v>
+      </c>
+      <c r="R106">
+        <v>9.3678899999999992</v>
+      </c>
+      <c r="S106">
+        <f t="shared" si="5"/>
+        <v>1399.2265914107247</v>
+      </c>
+      <c r="T106">
+        <f t="shared" si="6"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I107" s="1">
-        <v>3500</v>
+      <c r="A107" t="s">
+        <v>60</v>
+      </c>
+      <c r="B107" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107">
+        <v>1.902603</v>
+      </c>
+      <c r="D107">
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="E107">
+        <v>1.875</v>
+      </c>
+      <c r="F107">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G107">
+        <v>2492</v>
+      </c>
+      <c r="H107" t="s">
+        <v>61</v>
+      </c>
+      <c r="I107">
+        <v>7300</v>
       </c>
       <c r="J107">
-        <v>0.4</v>
+        <v>1.95</v>
       </c>
       <c r="K107">
-        <v>0.4</v>
+        <v>1.79</v>
+      </c>
+      <c r="L107">
+        <v>-0.1</v>
+      </c>
+      <c r="M107">
+        <v>4.0999999999999996</v>
       </c>
       <c r="N107">
-        <v>346.62201299999998</v>
+        <v>352.26752069999998</v>
       </c>
       <c r="O107">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P107">
-        <v>109.6</v>
+        <v>67.034806200000006</v>
+      </c>
+      <c r="P107" s="8">
+        <v>225.88800000000001</v>
       </c>
       <c r="Q107">
-        <v>16</v>
+        <v>8.952</v>
+      </c>
+      <c r="R107">
+        <v>8.8952899999999993</v>
+      </c>
+      <c r="S107">
+        <f t="shared" si="5"/>
+        <v>974.78820571370204</v>
+      </c>
+      <c r="T107">
+        <f t="shared" si="6"/>
+        <v>-7</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I108" s="1">
-        <v>3500</v>
+      <c r="A108" t="s">
+        <v>51</v>
+      </c>
+      <c r="B108" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108">
+        <v>5.55149296</v>
+      </c>
+      <c r="D108">
+        <v>6.6500000000000004E-2</v>
+      </c>
+      <c r="E108">
+        <v>1.1339999999999999</v>
+      </c>
+      <c r="F108">
+        <v>4.59</v>
+      </c>
+      <c r="G108">
+        <v>1391</v>
+      </c>
+      <c r="H108" t="s">
+        <v>52</v>
+      </c>
+      <c r="I108">
+        <v>6426</v>
       </c>
       <c r="J108">
-        <v>0.4</v>
+        <v>1.3380000000000001</v>
       </c>
       <c r="K108">
-        <v>0.4</v>
+        <v>1.268</v>
+      </c>
+      <c r="L108">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="M108">
+        <v>4.2869999999999999</v>
       </c>
       <c r="N108">
-        <v>346.62201299999998</v>
+        <v>161.90902729999999</v>
       </c>
       <c r="O108">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P108">
-        <v>173.8</v>
+        <v>71.655726999999999</v>
+      </c>
+      <c r="P108" s="8">
+        <v>96.517300000000006</v>
       </c>
       <c r="Q108">
-        <v>17</v>
+        <v>8.34</v>
+      </c>
+      <c r="R108">
+        <v>8.23752</v>
+      </c>
+      <c r="S108">
+        <f t="shared" si="5"/>
+        <v>99.730517672190274</v>
+      </c>
+      <c r="T108">
+        <f t="shared" si="6"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I109" s="1">
-        <v>3500</v>
+      <c r="A109" t="s">
+        <v>69</v>
+      </c>
+      <c r="B109" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109">
+        <v>4.4258699999999997</v>
+      </c>
+      <c r="D109">
+        <v>5.7779999999999998E-2</v>
+      </c>
+      <c r="E109">
+        <v>2.2303544500000001</v>
+      </c>
+      <c r="F109">
+        <v>1.86578665</v>
+      </c>
+      <c r="G109">
+        <v>1293</v>
+      </c>
+      <c r="H109" t="s">
+        <v>70</v>
+      </c>
+      <c r="I109">
+        <v>6117</v>
       </c>
       <c r="J109">
-        <v>0.4</v>
+        <v>1.53</v>
       </c>
       <c r="K109">
-        <v>0.4</v>
+        <v>1.3120000000000001</v>
+      </c>
+      <c r="L109">
+        <v>0.25</v>
+      </c>
+      <c r="M109">
+        <v>4.0999999999999996</v>
       </c>
       <c r="N109">
-        <v>346.62201299999998</v>
+        <v>313.5110469</v>
       </c>
       <c r="O109">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P109">
-        <v>275.39999999999998</v>
+        <v>72.580645500000003</v>
+      </c>
+      <c r="P109" s="8">
+        <v>139.48400000000001</v>
       </c>
       <c r="Q109">
-        <v>18</v>
+        <v>9.2700010000000006</v>
+      </c>
+      <c r="R109">
+        <v>9.1879500000000007</v>
+      </c>
+      <c r="S109">
+        <f t="shared" si="5"/>
+        <v>882.20971786077962</v>
+      </c>
+      <c r="T109">
+        <f t="shared" si="6"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I110" s="1">
-        <v>3500</v>
+      <c r="A110" t="s">
+        <v>84</v>
+      </c>
+      <c r="B110" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110">
+        <v>8.0277282999999997</v>
+      </c>
+      <c r="D110">
+        <v>8.2337403000000003E-2</v>
+      </c>
+      <c r="E110">
+        <v>0.83243188000000001</v>
+      </c>
+      <c r="F110">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="G110">
+        <v>1074.28</v>
+      </c>
+      <c r="H110" t="s">
+        <v>43</v>
+      </c>
+      <c r="I110">
+        <v>5962.7</v>
       </c>
       <c r="J110">
-        <v>0.4</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="K110">
-        <v>0.4</v>
+        <v>1.156039</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>4.38</v>
       </c>
       <c r="N110">
-        <v>346.62201299999998</v>
+        <v>193.3963704</v>
       </c>
       <c r="O110">
-        <v>-5.0412739999999996</v>
-      </c>
-      <c r="P110">
-        <v>436.5</v>
+        <v>85.129495199999994</v>
+      </c>
+      <c r="P110" s="8">
+        <v>114.048</v>
       </c>
       <c r="Q110">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.2">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="R110">
+        <v>9.4135299999999997</v>
+      </c>
+      <c r="S110">
+        <f t="shared" si="5"/>
+        <v>1175.9460676296278</v>
+      </c>
+      <c r="T110">
+        <f t="shared" si="6"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>174</v>
       </c>
@@ -7063,12 +7078,103 @@
       <c r="O111">
         <v>21.8946865465029</v>
       </c>
+      <c r="P111"/>
       <c r="X111" s="1" t="s">
         <v>175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X111" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="HAT-P-1 b"/>
+        <filter val="HAT-P-14 b"/>
+        <filter val="HAT-P-2 b"/>
+        <filter val="HAT-P-22 b"/>
+        <filter val="HAT-P-32 b"/>
+        <filter val="HAT-P-60 b"/>
+        <filter val="HAT-P-69 b"/>
+        <filter val="HAT-P-7 b"/>
+        <filter val="HAT-P-70 b"/>
+        <filter val="HD 118203 b"/>
+        <filter val="HD 1397 b"/>
+        <filter val="HD 149026 b"/>
+        <filter val="HD 152843 c"/>
+        <filter val="HD 189733 b"/>
+        <filter val="HD 202772 A b"/>
+        <filter val="HD 209458 b"/>
+        <filter val="HD 219666 b"/>
+        <filter val="HD 221416 b"/>
+        <filter val="HD 2685 b"/>
+        <filter val="HD 332231 b"/>
+        <filter val="HD 84979 b"/>
+        <filter val="HD 88133 b"/>
+        <filter val="HD 89345 b"/>
+        <filter val="K2-232 b"/>
+        <filter val="KELT-11 b"/>
+        <filter val="KELT-17 b"/>
+        <filter val="KELT-19 b"/>
+        <filter val="KELT-2 A b"/>
+        <filter val="KELT-20 b"/>
+        <filter val="KELT-24 b"/>
+        <filter val="KELT-3 b"/>
+        <filter val="KELT-4 A b"/>
+        <filter val="KELT-7 b"/>
+        <filter val="KELT-9 b"/>
+        <filter val="KOI-13 b"/>
+        <filter val="LTT 9779 b"/>
+        <filter val="MASCARA-1 b"/>
+        <filter val="MASCARA-4 b"/>
+        <filter val="TIC 393818343 b"/>
+        <filter val="TOI-1135 b"/>
+        <filter val="TOI-1136 d"/>
+        <filter val="TOI-1333 b"/>
+        <filter val="TOI-1408 b"/>
+        <filter val="TOI-1431 b"/>
+        <filter val="TOI-1518 b"/>
+        <filter val="TOI-1789 b"/>
+        <filter val="TOI-1842 b"/>
+        <filter val="TOI-2005 b"/>
+        <filter val="TOI-2145 b"/>
+        <filter val="TOI-2497 b"/>
+        <filter val="TOI-257 b"/>
+        <filter val="TOI-421 c"/>
+        <filter val="TOI-4551 b"/>
+        <filter val="TOI-4603 b"/>
+        <filter val="TOI-481 b"/>
+        <filter val="TOI-5108 b"/>
+        <filter val="TOI-5398 b"/>
+        <filter val="TOI-6038 b"/>
+        <filter val="TOI-622 b"/>
+        <filter val="TOI-677 b"/>
+        <filter val="TOI-778 b"/>
+        <filter val="WASP-12 b"/>
+        <filter val="WASP-131 b"/>
+        <filter val="WASP-136 b"/>
+        <filter val="WASP-14 b"/>
+        <filter val="WASP-166 b"/>
+        <filter val="WASP-178 b"/>
+        <filter val="WASP-18 b"/>
+        <filter val="WASP-189 b"/>
+        <filter val="WASP-33 b"/>
+        <filter val="WASP-38 b"/>
+        <filter val="WASP-69 b"/>
+        <filter val="WASP-7 b"/>
+        <filter val="WASP-74 b"/>
+        <filter val="WASP-76 b"/>
+        <filter val="WASP-79 b"/>
+        <filter val="WASP-8 b"/>
+        <filter val="WASP-82 b"/>
+        <filter val="WASP-94 A b"/>
+        <filter val="WASP-95 b"/>
+        <filter val="WASP-99 b"/>
+        <filter val="XO-3 b"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A15:X110">
+      <sortCondition ref="O1:O111"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R77">
     <sortCondition ref="Q2"/>
   </sortState>
